--- a/data/germany/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
+++ b/data/germany/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BF133"/>
+  <dimension ref="A1:BF138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25899,15 +25899,11 @@
           <t>17 810</t>
         </is>
       </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G125" t="n">
+        <v>0</v>
+      </c>
+      <c r="H125" t="n">
+        <v>2</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
@@ -25929,15 +25925,11 @@
           <t>Dusseldorf</t>
         </is>
       </c>
-      <c r="M125" t="inlineStr">
-        <is>
-          <t>0.79</t>
-        </is>
-      </c>
-      <c r="N125" t="inlineStr">
-        <is>
-          <t>1.49</t>
-        </is>
+      <c r="M125" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="N125" t="n">
+        <v>1.49</v>
       </c>
       <c r="O125" t="inlineStr">
         <is>
@@ -25949,155 +25941,95 @@
           <t>53%</t>
         </is>
       </c>
-      <c r="Q125" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="R125" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="S125" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="T125" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U125" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="V125" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="W125" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="X125" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="Y125" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Z125" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA125" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AB125" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC125" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AD125" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AE125" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AF125" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AG125" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AH125" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AI125" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AJ125" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AK125" t="inlineStr">
-        <is>
-          <t>423</t>
-        </is>
-      </c>
-      <c r="AL125" t="inlineStr">
-        <is>
-          <t>532</t>
-        </is>
-      </c>
-      <c r="AM125" t="inlineStr">
-        <is>
-          <t>355</t>
-        </is>
-      </c>
-      <c r="AN125" t="inlineStr">
-        <is>
-          <t>473</t>
-        </is>
-      </c>
-      <c r="AO125" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="AP125" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="AQ125" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="AR125" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="AS125" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="AT125" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
+      <c r="Q125" t="n">
+        <v>11</v>
+      </c>
+      <c r="R125" t="n">
+        <v>11</v>
+      </c>
+      <c r="S125" t="n">
+        <v>6</v>
+      </c>
+      <c r="T125" t="n">
+        <v>4</v>
+      </c>
+      <c r="U125" t="n">
+        <v>5</v>
+      </c>
+      <c r="V125" t="n">
+        <v>7</v>
+      </c>
+      <c r="W125" t="n">
+        <v>8</v>
+      </c>
+      <c r="X125" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>423</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>532</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>355</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>473</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>86</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>96</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>42</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>31</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>111</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>112</v>
       </c>
       <c r="AU125" t="inlineStr">
         <is>
@@ -26133,15 +26065,11 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="BC125" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BD125" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="BC125" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0</v>
       </c>
       <c r="BE125" t="inlineStr"/>
       <c r="BF125" t="inlineStr"/>
@@ -26179,15 +26107,11 @@
           <t>12 664</t>
         </is>
       </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G126" t="n">
+        <v>3</v>
+      </c>
+      <c r="H126" t="n">
+        <v>1</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
@@ -26209,15 +26133,11 @@
           <t>Preussen Munster</t>
         </is>
       </c>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="N126" t="inlineStr">
-        <is>
-          <t>3.65</t>
-        </is>
+      <c r="M126" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N126" t="n">
+        <v>3.65</v>
       </c>
       <c r="O126" t="inlineStr">
         <is>
@@ -26229,155 +26149,95 @@
           <t>53%</t>
         </is>
       </c>
-      <c r="Q126" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="R126" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="S126" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="T126" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="U126" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="V126" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="W126" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="X126" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="Y126" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Z126" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA126" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB126" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC126" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AD126" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AE126" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AF126" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AG126" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AH126" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AI126" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AJ126" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AK126" t="inlineStr">
-        <is>
-          <t>376</t>
-        </is>
-      </c>
-      <c r="AL126" t="inlineStr">
-        <is>
-          <t>441</t>
-        </is>
-      </c>
-      <c r="AM126" t="inlineStr">
-        <is>
-          <t>305</t>
-        </is>
-      </c>
-      <c r="AN126" t="inlineStr">
-        <is>
-          <t>370</t>
-        </is>
-      </c>
-      <c r="AO126" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="AP126" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="AQ126" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="AR126" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="AS126" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="AT126" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
+      <c r="Q126" t="n">
+        <v>22</v>
+      </c>
+      <c r="R126" t="n">
+        <v>15</v>
+      </c>
+      <c r="S126" t="n">
+        <v>9</v>
+      </c>
+      <c r="T126" t="n">
+        <v>5</v>
+      </c>
+      <c r="U126" t="n">
+        <v>13</v>
+      </c>
+      <c r="V126" t="n">
+        <v>10</v>
+      </c>
+      <c r="W126" t="n">
+        <v>11</v>
+      </c>
+      <c r="X126" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>16</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>9</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>11</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>376</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>441</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>305</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>370</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>95</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>76</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>45</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>39</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>113</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>111</v>
       </c>
       <c r="AU126" t="inlineStr">
         <is>
@@ -26451,15 +26311,11 @@
           <t>17 400</t>
         </is>
       </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G127" t="n">
+        <v>1</v>
+      </c>
+      <c r="H127" t="n">
+        <v>2</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
@@ -26481,15 +26337,11 @@
           <t>Kaiserslautern</t>
         </is>
       </c>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>0.98</t>
-        </is>
-      </c>
-      <c r="N127" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
+      <c r="M127" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="N127" t="n">
+        <v>3</v>
       </c>
       <c r="O127" t="inlineStr">
         <is>
@@ -26501,155 +26353,95 @@
           <t>46%</t>
         </is>
       </c>
-      <c r="Q127" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="R127" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="S127" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="T127" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U127" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="V127" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="W127" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="X127" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Y127" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Z127" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA127" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AB127" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC127" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="AD127" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AE127" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AF127" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AG127" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AH127" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AI127" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AJ127" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AK127" t="inlineStr">
-        <is>
-          <t>343</t>
-        </is>
-      </c>
-      <c r="AL127" t="inlineStr">
-        <is>
-          <t>325</t>
-        </is>
-      </c>
-      <c r="AM127" t="inlineStr">
-        <is>
-          <t>274</t>
-        </is>
-      </c>
-      <c r="AN127" t="inlineStr">
-        <is>
-          <t>273</t>
-        </is>
-      </c>
-      <c r="AO127" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="AP127" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="AQ127" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="AR127" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="AS127" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
-      <c r="AT127" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
+      <c r="Q127" t="n">
+        <v>12</v>
+      </c>
+      <c r="R127" t="n">
+        <v>13</v>
+      </c>
+      <c r="S127" t="n">
+        <v>3</v>
+      </c>
+      <c r="T127" t="n">
+        <v>4</v>
+      </c>
+      <c r="U127" t="n">
+        <v>9</v>
+      </c>
+      <c r="V127" t="n">
+        <v>9</v>
+      </c>
+      <c r="W127" t="n">
+        <v>18</v>
+      </c>
+      <c r="X127" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>27</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>343</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>325</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>274</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>273</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>72</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>96</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>42</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>33</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>119</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>112</v>
       </c>
       <c r="AU127" t="inlineStr">
         <is>
@@ -26723,15 +26515,11 @@
           <t>61 000</t>
         </is>
       </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G128" t="n">
+        <v>5</v>
+      </c>
+      <c r="H128" t="n">
+        <v>1</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
@@ -26753,15 +26541,11 @@
           <t>Braunschweig</t>
         </is>
       </c>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
-      </c>
-      <c r="N128" t="inlineStr">
-        <is>
-          <t>1.21</t>
-        </is>
+      <c r="M128" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="N128" t="n">
+        <v>1.21</v>
       </c>
       <c r="O128" t="inlineStr">
         <is>
@@ -26773,155 +26557,95 @@
           <t>48%</t>
         </is>
       </c>
-      <c r="Q128" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="R128" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="S128" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="T128" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="U128" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="V128" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="W128" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="X128" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Y128" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Z128" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA128" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB128" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC128" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="AD128" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AE128" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AF128" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AG128" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AH128" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AI128" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AJ128" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AK128" t="inlineStr">
-        <is>
-          <t>423</t>
-        </is>
-      </c>
-      <c r="AL128" t="inlineStr">
-        <is>
-          <t>369</t>
-        </is>
-      </c>
-      <c r="AM128" t="inlineStr">
-        <is>
-          <t>347</t>
-        </is>
-      </c>
-      <c r="AN128" t="inlineStr">
-        <is>
-          <t>295</t>
-        </is>
-      </c>
-      <c r="AO128" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="AP128" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="AQ128" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="AR128" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="AS128" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="AT128" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
+      <c r="Q128" t="n">
+        <v>14</v>
+      </c>
+      <c r="R128" t="n">
+        <v>10</v>
+      </c>
+      <c r="S128" t="n">
+        <v>8</v>
+      </c>
+      <c r="T128" t="n">
+        <v>5</v>
+      </c>
+      <c r="U128" t="n">
+        <v>6</v>
+      </c>
+      <c r="V128" t="n">
+        <v>5</v>
+      </c>
+      <c r="W128" t="n">
+        <v>12</v>
+      </c>
+      <c r="X128" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>29</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>11</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>423</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>369</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>347</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>295</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>84</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>64</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>35</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>30</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>115</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>114</v>
       </c>
       <c r="AU128" t="inlineStr">
         <is>
@@ -26995,15 +26719,11 @@
           <t>31 800</t>
         </is>
       </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G129" t="n">
+        <v>2</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
@@ -27025,15 +26745,11 @@
           <t>Regensburg</t>
         </is>
       </c>
-      <c r="M129" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="N129" t="inlineStr">
-        <is>
-          <t>0.51</t>
-        </is>
+      <c r="M129" t="n">
+        <v>2</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.51</v>
       </c>
       <c r="O129" t="inlineStr">
         <is>
@@ -27045,155 +26761,95 @@
           <t>42%</t>
         </is>
       </c>
-      <c r="Q129" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="R129" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="S129" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="T129" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="U129" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="V129" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="W129" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="X129" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="Y129" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Z129" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA129" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB129" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC129" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AD129" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AE129" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AF129" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AG129" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AH129" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AI129" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AJ129" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK129" t="inlineStr">
-        <is>
-          <t>398</t>
-        </is>
-      </c>
-      <c r="AL129" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="AM129" t="inlineStr">
-        <is>
-          <t>318</t>
-        </is>
-      </c>
-      <c r="AN129" t="inlineStr">
-        <is>
-          <t>252</t>
-        </is>
-      </c>
-      <c r="AO129" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="AP129" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="AQ129" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="AR129" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="AS129" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="AT129" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
+      <c r="Q129" t="n">
+        <v>16</v>
+      </c>
+      <c r="R129" t="n">
+        <v>10</v>
+      </c>
+      <c r="S129" t="n">
+        <v>5</v>
+      </c>
+      <c r="T129" t="n">
+        <v>3</v>
+      </c>
+      <c r="U129" t="n">
+        <v>11</v>
+      </c>
+      <c r="V129" t="n">
+        <v>7</v>
+      </c>
+      <c r="W129" t="n">
+        <v>17</v>
+      </c>
+      <c r="X129" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>21</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>398</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>336</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>318</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>252</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>85</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>85</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>45</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>39</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>111</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>109</v>
       </c>
       <c r="AU129" t="inlineStr">
         <is>
@@ -27267,15 +26923,11 @@
           <t>48 591</t>
         </is>
       </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G130" t="n">
+        <v>1</v>
+      </c>
+      <c r="H130" t="n">
+        <v>2</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
@@ -27297,15 +26949,11 @@
           <t>Paderborn</t>
         </is>
       </c>
-      <c r="M130" t="inlineStr">
-        <is>
-          <t>1.40</t>
-        </is>
-      </c>
-      <c r="N130" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
+      <c r="M130" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="N130" t="n">
+        <v>2.1</v>
       </c>
       <c r="O130" t="inlineStr">
         <is>
@@ -27317,155 +26965,95 @@
           <t>43%</t>
         </is>
       </c>
-      <c r="Q130" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="R130" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="S130" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="T130" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="U130" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V130" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="W130" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="X130" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="Y130" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Z130" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA130" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB130" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC130" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="AD130" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="AE130" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AF130" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AG130" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AH130" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AI130" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AJ130" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AK130" t="inlineStr">
-        <is>
-          <t>456</t>
-        </is>
-      </c>
-      <c r="AL130" t="inlineStr">
-        <is>
-          <t>315</t>
-        </is>
-      </c>
-      <c r="AM130" t="inlineStr">
-        <is>
-          <t>392</t>
-        </is>
-      </c>
-      <c r="AN130" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
-      <c r="AO130" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="AP130" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="AQ130" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="AR130" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="AS130" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="AT130" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
+      <c r="Q130" t="n">
+        <v>10</v>
+      </c>
+      <c r="R130" t="n">
+        <v>11</v>
+      </c>
+      <c r="S130" t="n">
+        <v>3</v>
+      </c>
+      <c r="T130" t="n">
+        <v>5</v>
+      </c>
+      <c r="U130" t="n">
+        <v>7</v>
+      </c>
+      <c r="V130" t="n">
+        <v>6</v>
+      </c>
+      <c r="W130" t="n">
+        <v>8</v>
+      </c>
+      <c r="X130" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>25</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>27</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>456</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>315</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>392</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>243</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>128</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>71</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>52</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>37</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>116</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>119</v>
       </c>
       <c r="AU130" t="inlineStr">
         <is>
@@ -27539,15 +27127,11 @@
           <t>25 000</t>
         </is>
       </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G131" t="n">
+        <v>3</v>
+      </c>
+      <c r="H131" t="n">
+        <v>2</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
@@ -27569,15 +27153,11 @@
           <t>Nurnberg</t>
         </is>
       </c>
-      <c r="M131" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
-      <c r="N131" t="inlineStr">
-        <is>
-          <t>1.71</t>
-        </is>
+      <c r="M131" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="N131" t="n">
+        <v>1.71</v>
       </c>
       <c r="O131" t="inlineStr">
         <is>
@@ -27589,155 +27169,95 @@
           <t>49%</t>
         </is>
       </c>
-      <c r="Q131" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="R131" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="S131" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="T131" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="U131" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="V131" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="W131" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="X131" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="Y131" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Z131" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA131" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB131" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC131" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="AD131" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="AE131" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AF131" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AG131" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AH131" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AI131" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AJ131" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AK131" t="inlineStr">
-        <is>
-          <t>394</t>
-        </is>
-      </c>
-      <c r="AL131" t="inlineStr">
-        <is>
-          <t>337</t>
-        </is>
-      </c>
-      <c r="AM131" t="inlineStr">
-        <is>
-          <t>330</t>
-        </is>
-      </c>
-      <c r="AN131" t="inlineStr">
-        <is>
-          <t>280</t>
-        </is>
-      </c>
-      <c r="AO131" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="AP131" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="AQ131" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="AR131" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="AS131" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="AT131" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
+      <c r="Q131" t="n">
+        <v>15</v>
+      </c>
+      <c r="R131" t="n">
+        <v>14</v>
+      </c>
+      <c r="S131" t="n">
+        <v>5</v>
+      </c>
+      <c r="T131" t="n">
+        <v>5</v>
+      </c>
+      <c r="U131" t="n">
+        <v>10</v>
+      </c>
+      <c r="V131" t="n">
+        <v>9</v>
+      </c>
+      <c r="W131" t="n">
+        <v>14</v>
+      </c>
+      <c r="X131" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>22</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>12</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>394</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>337</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>330</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>280</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>114</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>56</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>57</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>22</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>112</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>111</v>
       </c>
       <c r="AU131" t="inlineStr">
         <is>
@@ -27811,15 +27331,11 @@
           <t>21 469</t>
         </is>
       </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G132" t="n">
+        <v>0</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
@@ -27841,15 +27357,11 @@
           <t>Elversberg</t>
         </is>
       </c>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>2.49</t>
-        </is>
-      </c>
-      <c r="N132" t="inlineStr">
-        <is>
-          <t>0.72</t>
-        </is>
+      <c r="M132" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.72</v>
       </c>
       <c r="O132" t="inlineStr">
         <is>
@@ -27861,155 +27373,95 @@
           <t>37%</t>
         </is>
       </c>
-      <c r="Q132" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="R132" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="S132" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="T132" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="U132" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="V132" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="W132" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="X132" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="Y132" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="Z132" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA132" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB132" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC132" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AD132" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AE132" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AF132" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AG132" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AH132" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AI132" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AJ132" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AK132" t="inlineStr">
-        <is>
-          <t>530</t>
-        </is>
-      </c>
-      <c r="AL132" t="inlineStr">
-        <is>
-          <t>357</t>
-        </is>
-      </c>
-      <c r="AM132" t="inlineStr">
-        <is>
-          <t>466</t>
-        </is>
-      </c>
-      <c r="AN132" t="inlineStr">
-        <is>
-          <t>289</t>
-        </is>
-      </c>
-      <c r="AO132" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="AP132" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="AQ132" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="AR132" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AS132" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="AT132" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
+      <c r="Q132" t="n">
+        <v>21</v>
+      </c>
+      <c r="R132" t="n">
+        <v>9</v>
+      </c>
+      <c r="S132" t="n">
+        <v>6</v>
+      </c>
+      <c r="T132" t="n">
+        <v>3</v>
+      </c>
+      <c r="U132" t="n">
+        <v>15</v>
+      </c>
+      <c r="V132" t="n">
+        <v>6</v>
+      </c>
+      <c r="W132" t="n">
+        <v>9</v>
+      </c>
+      <c r="X132" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>530</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>357</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>466</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>289</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>112</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>72</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>63</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>121</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>121</v>
       </c>
       <c r="AU132" t="inlineStr">
         <is>
@@ -28083,15 +27535,11 @@
           <t>50 000</t>
         </is>
       </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G133" t="n">
+        <v>1</v>
+      </c>
+      <c r="H133" t="n">
+        <v>2</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
@@ -28113,15 +27561,11 @@
           <t>Hamburger SV</t>
         </is>
       </c>
-      <c r="M133" t="inlineStr">
-        <is>
-          <t>3.29</t>
-        </is>
-      </c>
-      <c r="N133" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
+      <c r="M133" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="N133" t="n">
+        <v>1.95</v>
       </c>
       <c r="O133" t="inlineStr">
         <is>
@@ -28133,155 +27577,95 @@
           <t>42%</t>
         </is>
       </c>
-      <c r="Q133" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="R133" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="S133" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="T133" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="U133" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="V133" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="W133" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="X133" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="Y133" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Z133" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA133" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB133" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AC133" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="AD133" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AE133" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AF133" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AG133" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AH133" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AI133" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AJ133" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AK133" t="inlineStr">
-        <is>
-          <t>539</t>
-        </is>
-      </c>
-      <c r="AL133" t="inlineStr">
-        <is>
-          <t>382</t>
-        </is>
-      </c>
-      <c r="AM133" t="inlineStr">
-        <is>
-          <t>464</t>
-        </is>
-      </c>
-      <c r="AN133" t="inlineStr">
-        <is>
-          <t>306</t>
-        </is>
-      </c>
-      <c r="AO133" t="inlineStr">
-        <is>
-          <t>143</t>
-        </is>
-      </c>
-      <c r="AP133" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="AQ133" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="AR133" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AS133" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
-      <c r="AT133" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
+      <c r="Q133" t="n">
+        <v>26</v>
+      </c>
+      <c r="R133" t="n">
+        <v>9</v>
+      </c>
+      <c r="S133" t="n">
+        <v>4</v>
+      </c>
+      <c r="T133" t="n">
+        <v>6</v>
+      </c>
+      <c r="U133" t="n">
+        <v>22</v>
+      </c>
+      <c r="V133" t="n">
+        <v>3</v>
+      </c>
+      <c r="W133" t="n">
+        <v>10</v>
+      </c>
+      <c r="X133" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>25</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>18</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>539</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>382</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>464</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>306</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>143</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>73</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>100</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>126</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>124</v>
       </c>
       <c r="AU133" t="inlineStr">
         <is>
@@ -28322,6 +27706,1374 @@
       <c r="BE133" t="inlineStr"/>
       <c r="BF133" t="inlineStr"/>
     </row>
+    <row r="134">
+      <c r="A134" s="1" t="inlineStr">
+        <is>
+          <t>IViLLjPF</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>10.08.2024 08:00</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Hartmann R.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Merkur Spiel-Arena
+ (Düsseldorf)</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>54 600</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>36 103</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>ne1oL3y7</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>Dusseldorf</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>EB3q7jbk</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>Karlsruher SC</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>0.66</t>
+        </is>
+      </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
+      </c>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="Q134" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="R134" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="S134" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T134" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="V134" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="W134" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="X134" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Y134" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Z134" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB134" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC134" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AD134" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AE134" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AF134" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AG134" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AH134" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AI134" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AJ134" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AK134" t="inlineStr">
+        <is>
+          <t>502</t>
+        </is>
+      </c>
+      <c r="AL134" t="inlineStr">
+        <is>
+          <t>487</t>
+        </is>
+      </c>
+      <c r="AM134" t="inlineStr">
+        <is>
+          <t>442</t>
+        </is>
+      </c>
+      <c r="AN134" t="inlineStr">
+        <is>
+          <t>409</t>
+        </is>
+      </c>
+      <c r="AO134" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="AP134" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="AQ134" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="AR134" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="AS134" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="AT134" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="AU134" t="inlineStr">
+        <is>
+          <t>AoL97rX8</t>
+        </is>
+      </c>
+      <c r="AV134" t="inlineStr">
+        <is>
+          <t>thioune daniel</t>
+        </is>
+      </c>
+      <c r="AW134" t="inlineStr">
+        <is>
+          <t>OzPMRhK3</t>
+        </is>
+      </c>
+      <c r="AX134" t="inlineStr">
+        <is>
+          <t>eichner christian</t>
+        </is>
+      </c>
+      <c r="AY134" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>592</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB134" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC134" t="inlineStr"/>
+      <c r="BD134" t="inlineStr"/>
+      <c r="BE134" t="inlineStr"/>
+      <c r="BF134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="1" t="inlineStr">
+        <is>
+          <t>tC1Aa08D</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>10.08.2024 08:00</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Bauer T.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Waldstadion Kaiserlinde
+ (Spiesen-Elversberg)</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>9 970</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>9 502</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>6in2Eknb</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>Elversberg</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>WG9pOTse</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>FC Koln</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>3.39</t>
+        </is>
+      </c>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>45%</t>
+        </is>
+      </c>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>55%</t>
+        </is>
+      </c>
+      <c r="Q135" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R135" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="S135" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T135" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V135" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="W135" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="X135" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="Y135" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Z135" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB135" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC135" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AD135" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AE135" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AF135" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AG135" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AH135" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AI135" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AJ135" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AK135" t="inlineStr">
+        <is>
+          <t>399</t>
+        </is>
+      </c>
+      <c r="AL135" t="inlineStr">
+        <is>
+          <t>505</t>
+        </is>
+      </c>
+      <c r="AM135" t="inlineStr">
+        <is>
+          <t>311</t>
+        </is>
+      </c>
+      <c r="AN135" t="inlineStr">
+        <is>
+          <t>419</t>
+        </is>
+      </c>
+      <c r="AO135" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="AP135" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="AQ135" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="AR135" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="AS135" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="AT135" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="AU135" t="inlineStr">
+        <is>
+          <t>8E8qmw3d</t>
+        </is>
+      </c>
+      <c r="AV135" t="inlineStr">
+        <is>
+          <t>steffen horst</t>
+        </is>
+      </c>
+      <c r="AW135" t="inlineStr">
+        <is>
+          <t>4fX0k7gg</t>
+        </is>
+      </c>
+      <c r="AX135" t="inlineStr">
+        <is>
+          <t>struber gerhard</t>
+        </is>
+      </c>
+      <c r="AY135" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>592</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB135" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC135" t="inlineStr"/>
+      <c r="BD135" t="inlineStr"/>
+      <c r="BE135" t="inlineStr"/>
+      <c r="BF135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="1" t="inlineStr">
+        <is>
+          <t>YJ3eN30K</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>10.08.2024 08:00</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Winter N.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Max-Morlock-Stadion
+ (Nuremberg)</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>44 308</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>50 000</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>6FDqshzF</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>Nurnberg</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>0Ija0Ej9</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>Schalke</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>0.93</t>
+        </is>
+      </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>2.12</t>
+        </is>
+      </c>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>49%</t>
+        </is>
+      </c>
+      <c r="Q136" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="R136" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="S136" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T136" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U136" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V136" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="W136" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="X136" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="Y136" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Z136" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB136" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AD136" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AE136" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AF136" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AG136" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AH136" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AI136" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AJ136" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AK136" t="inlineStr">
+        <is>
+          <t>366</t>
+        </is>
+      </c>
+      <c r="AL136" t="inlineStr">
+        <is>
+          <t>370</t>
+        </is>
+      </c>
+      <c r="AM136" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="AN136" t="inlineStr">
+        <is>
+          <t>315</t>
+        </is>
+      </c>
+      <c r="AO136" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="AP136" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="AQ136" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AR136" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="AS136" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="AT136" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="AU136" t="inlineStr">
+        <is>
+          <t>tO31cZrF</t>
+        </is>
+      </c>
+      <c r="AV136" t="inlineStr">
+        <is>
+          <t>klose miroslav</t>
+        </is>
+      </c>
+      <c r="AW136" t="inlineStr">
+        <is>
+          <t>txZLBQVC</t>
+        </is>
+      </c>
+      <c r="AX136" t="inlineStr">
+        <is>
+          <t>geraerts karel</t>
+        </is>
+      </c>
+      <c r="AY136" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>592</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB136" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC136" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BD136" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BE136" t="inlineStr"/>
+      <c r="BF136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="1" t="inlineStr">
+        <is>
+          <t>h4pSHsOs</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>09.08.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Lechner F.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Fritz Walter Stadion
+ (Kaiserslautern)</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>49 500</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>41 632</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>naWckLmC</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>Kaiserslautern</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>CCQGbik8</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>Greuther Furth</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>46%</t>
+        </is>
+      </c>
+      <c r="Q137" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="R137" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="S137" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T137" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V137" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="W137" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="X137" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y137" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Z137" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB137" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC137" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AD137" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AE137" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AF137" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AG137" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AH137" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AI137" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AJ137" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AK137" t="inlineStr">
+        <is>
+          <t>503</t>
+        </is>
+      </c>
+      <c r="AL137" t="inlineStr">
+        <is>
+          <t>380</t>
+        </is>
+      </c>
+      <c r="AM137" t="inlineStr">
+        <is>
+          <t>423</t>
+        </is>
+      </c>
+      <c r="AN137" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="AO137" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="AP137" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="AQ137" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="AR137" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AS137" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="AT137" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="AU137" t="inlineStr">
+        <is>
+          <t>4bJLk19p</t>
+        </is>
+      </c>
+      <c r="AV137" t="inlineStr">
+        <is>
+          <t>anfang marcus</t>
+        </is>
+      </c>
+      <c r="AW137" t="inlineStr">
+        <is>
+          <t>8E86CPuD</t>
+        </is>
+      </c>
+      <c r="AX137" t="inlineStr">
+        <is>
+          <t>zorniger alexander</t>
+        </is>
+      </c>
+      <c r="AY137" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>592</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB137" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC137" t="inlineStr"/>
+      <c r="BD137" t="inlineStr"/>
+      <c r="BE137" t="inlineStr"/>
+      <c r="BF137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="1" t="inlineStr">
+        <is>
+          <t>StuiCwhJ</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>09.08.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Benen L.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Jahnstadion Regensburg
+ (Regensburg)</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>15 210</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>12 095</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>UiCmEP56</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>Regensburg</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>tbC3EcQn</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>Ulm</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>0.74</t>
+        </is>
+      </c>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>0.47</t>
+        </is>
+      </c>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>49%</t>
+        </is>
+      </c>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="Q138" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="R138" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="S138" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T138" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V138" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W138" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="X138" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="Y138" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Z138" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB138" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC138" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AD138" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="AE138" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AF138" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG138" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AH138" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AI138" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AJ138" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AK138" t="inlineStr">
+        <is>
+          <t>285</t>
+        </is>
+      </c>
+      <c r="AL138" t="inlineStr">
+        <is>
+          <t>351</t>
+        </is>
+      </c>
+      <c r="AM138" t="inlineStr">
+        <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="AN138" t="inlineStr">
+        <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="AO138" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="AP138" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="AQ138" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="AR138" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="AS138" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="AT138" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="AU138" t="inlineStr">
+        <is>
+          <t>zyLSrbZQ</t>
+        </is>
+      </c>
+      <c r="AV138" t="inlineStr">
+        <is>
+          <t>enochs joe</t>
+        </is>
+      </c>
+      <c r="AW138" t="inlineStr">
+        <is>
+          <t>QevvB2nf</t>
+        </is>
+      </c>
+      <c r="AX138" t="inlineStr">
+        <is>
+          <t>worle thomas</t>
+        </is>
+      </c>
+      <c r="AY138" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>592</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB138" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC138" t="inlineStr"/>
+      <c r="BD138" t="inlineStr"/>
+      <c r="BE138" t="inlineStr"/>
+      <c r="BF138" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/germany/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
+++ b/data/germany/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BF138"/>
+  <dimension ref="A1:BF169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27739,15 +27739,11 @@
           <t>36 103</t>
         </is>
       </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G134" t="n">
+        <v>0</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
@@ -27769,15 +27765,11 @@
           <t>Karlsruher SC</t>
         </is>
       </c>
-      <c r="M134" t="inlineStr">
-        <is>
-          <t>1.09</t>
-        </is>
-      </c>
-      <c r="N134" t="inlineStr">
-        <is>
-          <t>0.66</t>
-        </is>
+      <c r="M134" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.66</v>
       </c>
       <c r="O134" t="inlineStr">
         <is>
@@ -27789,155 +27781,95 @@
           <t>47%</t>
         </is>
       </c>
-      <c r="Q134" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="R134" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="S134" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="T134" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U134" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="V134" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="W134" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="X134" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="Y134" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Z134" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA134" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AB134" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC134" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AD134" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AE134" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AF134" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AG134" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AH134" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AI134" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AJ134" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AK134" t="inlineStr">
-        <is>
-          <t>502</t>
-        </is>
-      </c>
-      <c r="AL134" t="inlineStr">
-        <is>
-          <t>487</t>
-        </is>
-      </c>
-      <c r="AM134" t="inlineStr">
-        <is>
-          <t>442</t>
-        </is>
-      </c>
-      <c r="AN134" t="inlineStr">
-        <is>
-          <t>409</t>
-        </is>
-      </c>
-      <c r="AO134" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="AP134" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="AQ134" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="AR134" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="AS134" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="AT134" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
+      <c r="Q134" t="n">
+        <v>20</v>
+      </c>
+      <c r="R134" t="n">
+        <v>9</v>
+      </c>
+      <c r="S134" t="n">
+        <v>6</v>
+      </c>
+      <c r="T134" t="n">
+        <v>2</v>
+      </c>
+      <c r="U134" t="n">
+        <v>14</v>
+      </c>
+      <c r="V134" t="n">
+        <v>7</v>
+      </c>
+      <c r="W134" t="n">
+        <v>7</v>
+      </c>
+      <c r="X134" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>18</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>6</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>502</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>487</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>442</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>409</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>95</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>96</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>61</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>39</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>114</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>114</v>
       </c>
       <c r="AU134" t="inlineStr">
         <is>
@@ -28011,15 +27943,11 @@
           <t>9 502</t>
         </is>
       </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G135" t="n">
+        <v>2</v>
+      </c>
+      <c r="H135" t="n">
+        <v>2</v>
       </c>
       <c r="I135" t="inlineStr">
         <is>
@@ -28041,15 +27969,11 @@
           <t>FC Koln</t>
         </is>
       </c>
-      <c r="M135" t="inlineStr">
-        <is>
-          <t>2.45</t>
-        </is>
-      </c>
-      <c r="N135" t="inlineStr">
-        <is>
-          <t>3.39</t>
-        </is>
+      <c r="M135" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="N135" t="n">
+        <v>3.39</v>
       </c>
       <c r="O135" t="inlineStr">
         <is>
@@ -28061,155 +27985,95 @@
           <t>55%</t>
         </is>
       </c>
-      <c r="Q135" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="R135" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="S135" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="T135" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="U135" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V135" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="W135" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="X135" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="Y135" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Z135" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AA135" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB135" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC135" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AD135" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AE135" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AF135" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AG135" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AH135" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AI135" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AJ135" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AK135" t="inlineStr">
-        <is>
-          <t>399</t>
-        </is>
-      </c>
-      <c r="AL135" t="inlineStr">
-        <is>
-          <t>505</t>
-        </is>
-      </c>
-      <c r="AM135" t="inlineStr">
-        <is>
-          <t>311</t>
-        </is>
-      </c>
-      <c r="AN135" t="inlineStr">
-        <is>
-          <t>419</t>
-        </is>
-      </c>
-      <c r="AO135" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="AP135" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="AQ135" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="AR135" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="AS135" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="AT135" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
+      <c r="Q135" t="n">
+        <v>10</v>
+      </c>
+      <c r="R135" t="n">
+        <v>23</v>
+      </c>
+      <c r="S135" t="n">
+        <v>3</v>
+      </c>
+      <c r="T135" t="n">
+        <v>9</v>
+      </c>
+      <c r="U135" t="n">
+        <v>7</v>
+      </c>
+      <c r="V135" t="n">
+        <v>14</v>
+      </c>
+      <c r="W135" t="n">
+        <v>13</v>
+      </c>
+      <c r="X135" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>17</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>13</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>399</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>505</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>311</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>419</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>66</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>114</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>29</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>76</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>114</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>117</v>
       </c>
       <c r="AU135" t="inlineStr">
         <is>
@@ -28283,15 +28147,11 @@
           <t>50 000</t>
         </is>
       </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G136" t="n">
+        <v>3</v>
+      </c>
+      <c r="H136" t="n">
+        <v>1</v>
       </c>
       <c r="I136" t="inlineStr">
         <is>
@@ -28313,15 +28173,11 @@
           <t>Schalke</t>
         </is>
       </c>
-      <c r="M136" t="inlineStr">
-        <is>
-          <t>0.93</t>
-        </is>
-      </c>
-      <c r="N136" t="inlineStr">
-        <is>
-          <t>2.12</t>
-        </is>
+      <c r="M136" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="N136" t="n">
+        <v>2.12</v>
       </c>
       <c r="O136" t="inlineStr">
         <is>
@@ -28333,155 +28189,95 @@
           <t>49%</t>
         </is>
       </c>
-      <c r="Q136" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="R136" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="S136" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="T136" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="U136" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="V136" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="W136" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="X136" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="Y136" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Z136" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA136" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB136" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC136" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AD136" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AE136" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AF136" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AG136" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AH136" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AI136" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AJ136" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AK136" t="inlineStr">
-        <is>
-          <t>366</t>
-        </is>
-      </c>
-      <c r="AL136" t="inlineStr">
-        <is>
-          <t>370</t>
-        </is>
-      </c>
-      <c r="AM136" t="inlineStr">
-        <is>
-          <t>304</t>
-        </is>
-      </c>
-      <c r="AN136" t="inlineStr">
-        <is>
-          <t>315</t>
-        </is>
-      </c>
-      <c r="AO136" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="AP136" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="AQ136" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="AR136" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="AS136" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="AT136" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
+      <c r="Q136" t="n">
+        <v>8</v>
+      </c>
+      <c r="R136" t="n">
+        <v>17</v>
+      </c>
+      <c r="S136" t="n">
+        <v>5</v>
+      </c>
+      <c r="T136" t="n">
+        <v>5</v>
+      </c>
+      <c r="U136" t="n">
+        <v>3</v>
+      </c>
+      <c r="V136" t="n">
+        <v>12</v>
+      </c>
+      <c r="W136" t="n">
+        <v>12</v>
+      </c>
+      <c r="X136" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>21</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>12</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>366</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>370</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>304</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>315</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>76</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>91</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>22</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>48</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>107</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>103</v>
       </c>
       <c r="AU136" t="inlineStr">
         <is>
@@ -28517,15 +28313,11 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="BC136" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BD136" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="BC136" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>1</v>
       </c>
       <c r="BE136" t="inlineStr"/>
       <c r="BF136" t="inlineStr"/>
@@ -28563,15 +28355,11 @@
           <t>41 632</t>
         </is>
       </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G137" t="n">
+        <v>2</v>
+      </c>
+      <c r="H137" t="n">
+        <v>2</v>
       </c>
       <c r="I137" t="inlineStr">
         <is>
@@ -28593,15 +28381,11 @@
           <t>Greuther Furth</t>
         </is>
       </c>
-      <c r="M137" t="inlineStr">
-        <is>
-          <t>2.02</t>
-        </is>
-      </c>
-      <c r="N137" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
+      <c r="M137" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="N137" t="n">
+        <v>2.7</v>
       </c>
       <c r="O137" t="inlineStr">
         <is>
@@ -28613,155 +28397,95 @@
           <t>46%</t>
         </is>
       </c>
-      <c r="Q137" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="R137" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="S137" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="T137" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="U137" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="V137" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="W137" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="X137" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y137" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Z137" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA137" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB137" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AC137" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AD137" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AE137" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AF137" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AG137" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AH137" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AI137" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AJ137" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AK137" t="inlineStr">
-        <is>
-          <t>503</t>
-        </is>
-      </c>
-      <c r="AL137" t="inlineStr">
-        <is>
-          <t>380</t>
-        </is>
-      </c>
-      <c r="AM137" t="inlineStr">
-        <is>
-          <t>423</t>
-        </is>
-      </c>
-      <c r="AN137" t="inlineStr">
-        <is>
-          <t>304</t>
-        </is>
-      </c>
-      <c r="AO137" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="AP137" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="AQ137" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="AR137" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="AS137" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="AT137" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
+      <c r="Q137" t="n">
+        <v>13</v>
+      </c>
+      <c r="R137" t="n">
+        <v>15</v>
+      </c>
+      <c r="S137" t="n">
+        <v>7</v>
+      </c>
+      <c r="T137" t="n">
+        <v>8</v>
+      </c>
+      <c r="U137" t="n">
+        <v>6</v>
+      </c>
+      <c r="V137" t="n">
+        <v>7</v>
+      </c>
+      <c r="W137" t="n">
+        <v>8</v>
+      </c>
+      <c r="X137" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>18</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>14</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>503</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>380</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>423</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>304</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>97</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>80</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>49</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>30</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>112</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>116</v>
       </c>
       <c r="AU137" t="inlineStr">
         <is>
@@ -28835,15 +28559,11 @@
           <t>12 095</t>
         </is>
       </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G138" t="n">
+        <v>1</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0</v>
       </c>
       <c r="I138" t="inlineStr">
         <is>
@@ -28865,15 +28585,11 @@
           <t>Ulm</t>
         </is>
       </c>
-      <c r="M138" t="inlineStr">
-        <is>
-          <t>0.74</t>
-        </is>
-      </c>
-      <c r="N138" t="inlineStr">
-        <is>
-          <t>0.47</t>
-        </is>
+      <c r="M138" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.47</v>
       </c>
       <c r="O138" t="inlineStr">
         <is>
@@ -28885,155 +28601,95 @@
           <t>51%</t>
         </is>
       </c>
-      <c r="Q138" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="R138" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="S138" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="T138" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="U138" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V138" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="W138" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="X138" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="Y138" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Z138" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA138" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB138" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC138" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="AD138" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="AE138" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AF138" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG138" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="AH138" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AI138" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AJ138" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AK138" t="inlineStr">
-        <is>
-          <t>285</t>
-        </is>
-      </c>
-      <c r="AL138" t="inlineStr">
-        <is>
-          <t>351</t>
-        </is>
-      </c>
-      <c r="AM138" t="inlineStr">
-        <is>
-          <t>214</t>
-        </is>
-      </c>
-      <c r="AN138" t="inlineStr">
-        <is>
-          <t>263</t>
-        </is>
-      </c>
-      <c r="AO138" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="AP138" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="AQ138" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="AR138" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="AS138" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="AT138" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
+      <c r="Q138" t="n">
+        <v>8</v>
+      </c>
+      <c r="R138" t="n">
+        <v>11</v>
+      </c>
+      <c r="S138" t="n">
+        <v>1</v>
+      </c>
+      <c r="T138" t="n">
+        <v>5</v>
+      </c>
+      <c r="U138" t="n">
+        <v>7</v>
+      </c>
+      <c r="V138" t="n">
+        <v>6</v>
+      </c>
+      <c r="W138" t="n">
+        <v>17</v>
+      </c>
+      <c r="X138" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>23</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>22</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>285</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>351</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>214</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>263</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>79</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>106</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>36</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>49</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>110</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>114</v>
       </c>
       <c r="AU138" t="inlineStr">
         <is>
@@ -29074,6 +28730,7833 @@
       <c r="BE138" t="inlineStr"/>
       <c r="BF138" t="inlineStr"/>
     </row>
+    <row r="139">
+      <c r="A139" s="1" t="inlineStr">
+        <is>
+          <t>QHrzGLhf</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>11.08.2024 08:30</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Reichel T.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Eintracht-Stadion
+ (Braunschweig)</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>23 325</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>22 791</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>QqLCC3il</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>Braunschweig</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>YFuz2RLm</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>Magdeburg</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>49%</t>
+        </is>
+      </c>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="Q139" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="R139" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="S139" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="T139" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="V139" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="W139" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="X139" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y139" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Z139" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB139" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC139" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AD139" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AE139" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AF139" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AG139" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AH139" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AI139" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AJ139" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AK139" t="inlineStr">
+        <is>
+          <t>391</t>
+        </is>
+      </c>
+      <c r="AL139" t="inlineStr">
+        <is>
+          <t>411</t>
+        </is>
+      </c>
+      <c r="AM139" t="inlineStr">
+        <is>
+          <t>305</t>
+        </is>
+      </c>
+      <c r="AN139" t="inlineStr">
+        <is>
+          <t>341</t>
+        </is>
+      </c>
+      <c r="AO139" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="AP139" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="AQ139" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="AR139" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AS139" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="AT139" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="AU139" t="inlineStr">
+        <is>
+          <t>SQrxFAMl</t>
+        </is>
+      </c>
+      <c r="AV139" t="inlineStr">
+        <is>
+          <t>scherning daniel</t>
+        </is>
+      </c>
+      <c r="AW139" t="inlineStr">
+        <is>
+          <t>IgZoGKFn</t>
+        </is>
+      </c>
+      <c r="AX139" t="inlineStr">
+        <is>
+          <t>titz christian</t>
+        </is>
+      </c>
+      <c r="AY139" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>592</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB139" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC139" t="inlineStr"/>
+      <c r="BD139" t="inlineStr"/>
+      <c r="BE139" t="inlineStr"/>
+      <c r="BF139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="1" t="inlineStr">
+        <is>
+          <t>KdD11Mw1</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>11.08.2024 08:30</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Schwengers P.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Home Deluxe Arena
+ (Paderborn)</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>12 972</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>G2Op923t</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>Paderborn</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>S0hPB9rA</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>Darmstadt</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>1.05</t>
+        </is>
+      </c>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>46%</t>
+        </is>
+      </c>
+      <c r="Q140" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="R140" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="S140" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T140" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="V140" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="W140" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="X140" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y140" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Z140" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB140" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AD140" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AE140" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AF140" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AG140" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AH140" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AI140" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AJ140" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AK140" t="inlineStr">
+        <is>
+          <t>443</t>
+        </is>
+      </c>
+      <c r="AL140" t="inlineStr">
+        <is>
+          <t>423</t>
+        </is>
+      </c>
+      <c r="AM140" t="inlineStr">
+        <is>
+          <t>372</t>
+        </is>
+      </c>
+      <c r="AN140" t="inlineStr">
+        <is>
+          <t>330</t>
+        </is>
+      </c>
+      <c r="AO140" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="AP140" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="AQ140" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="AR140" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="AS140" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="AT140" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="AU140" t="inlineStr">
+        <is>
+          <t>0AI1QUJH</t>
+        </is>
+      </c>
+      <c r="AV140" t="inlineStr">
+        <is>
+          <t>kwasniok lukas</t>
+        </is>
+      </c>
+      <c r="AW140" t="inlineStr">
+        <is>
+          <t>MDhPV0RQ</t>
+        </is>
+      </c>
+      <c r="AX140" t="inlineStr">
+        <is>
+          <t>lieberknecht torsten</t>
+        </is>
+      </c>
+      <c r="AY140" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>592</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB140" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC140" t="inlineStr"/>
+      <c r="BD140" t="inlineStr"/>
+      <c r="BE140" t="inlineStr"/>
+      <c r="BF140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="1" t="inlineStr">
+        <is>
+          <t>MqxqEaN6</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>11.08.2024 08:30</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Erbst L.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Preussenstadion
+ (Munster)</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>12 794</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>12 422</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>zedZaSL7</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>Preussen Munster</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>dfNCCCzS</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>Hannover</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>0.57</t>
+        </is>
+      </c>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
+      </c>
+      <c r="Q141" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R141" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="S141" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T141" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V141" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="W141" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="X141" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="Y141" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Z141" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB141" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="AD141" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AE141" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AF141" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AG141" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AH141" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AI141" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AJ141" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AK141" t="inlineStr">
+        <is>
+          <t>293</t>
+        </is>
+      </c>
+      <c r="AL141" t="inlineStr">
+        <is>
+          <t>371</t>
+        </is>
+      </c>
+      <c r="AM141" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="AN141" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="AO141" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="AP141" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="AQ141" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="AR141" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="AS141" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="AT141" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="AU141" t="inlineStr">
+        <is>
+          <t>pdPRS0me</t>
+        </is>
+      </c>
+      <c r="AV141" t="inlineStr">
+        <is>
+          <t>hildmann sascha</t>
+        </is>
+      </c>
+      <c r="AW141" t="inlineStr">
+        <is>
+          <t>t0ZPdkUl</t>
+        </is>
+      </c>
+      <c r="AX141" t="inlineStr">
+        <is>
+          <t>leitl stefan</t>
+        </is>
+      </c>
+      <c r="AY141" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>592</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB141" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC141" t="inlineStr"/>
+      <c r="BD141" t="inlineStr"/>
+      <c r="BE141" t="inlineStr"/>
+      <c r="BF141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="1" t="inlineStr">
+        <is>
+          <t>CW9g3r9l</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>10.08.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Gerach T.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Volksparkstadion
+ (Hamburg)</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>57 274</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>57 000</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>v9k3aY5F</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>Hamburger SV</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>2y0u8Wrq</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>Hertha Berlin</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>0.93</t>
+        </is>
+      </c>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="Q142" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="R142" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="S142" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V142" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="W142" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="X142" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y142" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Z142" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB142" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC142" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AD142" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AE142" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AF142" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AG142" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AH142" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AI142" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AJ142" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AK142" t="inlineStr">
+        <is>
+          <t>353</t>
+        </is>
+      </c>
+      <c r="AL142" t="inlineStr">
+        <is>
+          <t>490</t>
+        </is>
+      </c>
+      <c r="AM142" t="inlineStr">
+        <is>
+          <t>311</t>
+        </is>
+      </c>
+      <c r="AN142" t="inlineStr">
+        <is>
+          <t>436</t>
+        </is>
+      </c>
+      <c r="AO142" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="AP142" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="AQ142" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="AR142" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="AS142" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="AT142" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="AU142" t="inlineStr">
+        <is>
+          <t>EDRZkDzS</t>
+        </is>
+      </c>
+      <c r="AV142" t="inlineStr">
+        <is>
+          <t>baumgart steffen</t>
+        </is>
+      </c>
+      <c r="AW142" t="inlineStr">
+        <is>
+          <t>YmfcAeCo</t>
+        </is>
+      </c>
+      <c r="AX142" t="inlineStr">
+        <is>
+          <t>fiel cristian</t>
+        </is>
+      </c>
+      <c r="AY142" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>592</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB142" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC142" t="inlineStr"/>
+      <c r="BD142" t="inlineStr"/>
+      <c r="BE142" t="inlineStr"/>
+      <c r="BF142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="1" t="inlineStr">
+        <is>
+          <t>pzHxyrtm</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>18.08.2024 13:00</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Oldhafer K.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Stadion am Lotter Kreuz
+ (Lotte)</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>10 059</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>4 637</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>hjNlCFPB</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>Lotte</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>EB3q7jbk</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>Karlsruher SC
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr"/>
+      <c r="N143" t="inlineStr"/>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="Q143" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="R143" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="S143" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V143" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="W143" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="X143" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="Y143" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Z143" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB143" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC143" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AD143" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AE143" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AF143" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AG143" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AH143" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AI143" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AJ143" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AK143" t="inlineStr"/>
+      <c r="AL143" t="inlineStr"/>
+      <c r="AM143" t="inlineStr"/>
+      <c r="AN143" t="inlineStr"/>
+      <c r="AO143" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="AP143" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="AQ143" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="AR143" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="AS143" t="inlineStr"/>
+      <c r="AT143" t="inlineStr"/>
+      <c r="AU143" t="inlineStr">
+        <is>
+          <t>KW0bzbwJ</t>
+        </is>
+      </c>
+      <c r="AV143" t="inlineStr">
+        <is>
+          <t>lubbers fabian</t>
+        </is>
+      </c>
+      <c r="AW143" t="inlineStr">
+        <is>
+          <t>OzPMRhK3</t>
+        </is>
+      </c>
+      <c r="AX143" t="inlineStr">
+        <is>
+          <t>eichner christian</t>
+        </is>
+      </c>
+      <c r="AY143" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>593</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB143" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC143" t="inlineStr"/>
+      <c r="BD143" t="inlineStr"/>
+      <c r="BE143" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="BF143" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="1" t="inlineStr">
+        <is>
+          <t>dCPKovw8</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>18.08.2024 13:00</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Zwayer F.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Hansch-Arena
+ (Meppen)</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>13 696</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>12 959</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>rXqBh2xP</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>Meppen</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>v9k3aY5F</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>Hamburger SV
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr"/>
+      <c r="N144" t="inlineStr"/>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>31%</t>
+        </is>
+      </c>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>69%</t>
+        </is>
+      </c>
+      <c r="Q144" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R144" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="S144" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V144" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W144" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="X144" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y144" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Z144" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB144" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC144" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AD144" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AE144" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AF144" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AG144" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AH144" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AI144" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AJ144" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK144" t="inlineStr"/>
+      <c r="AL144" t="inlineStr"/>
+      <c r="AM144" t="inlineStr"/>
+      <c r="AN144" t="inlineStr"/>
+      <c r="AO144" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="AP144" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="AQ144" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="AR144" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="AS144" t="inlineStr"/>
+      <c r="AT144" t="inlineStr"/>
+      <c r="AU144" t="inlineStr">
+        <is>
+          <t>UqphGQrg</t>
+        </is>
+      </c>
+      <c r="AV144" t="inlineStr">
+        <is>
+          <t>beniermann lucas</t>
+        </is>
+      </c>
+      <c r="AW144" t="inlineStr">
+        <is>
+          <t>EDRZkDzS</t>
+        </is>
+      </c>
+      <c r="AX144" t="inlineStr">
+        <is>
+          <t>baumgart steffen</t>
+        </is>
+      </c>
+      <c r="AY144" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ144" t="n">
+        <v>593</v>
+      </c>
+      <c r="BA144" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB144" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC144" t="inlineStr"/>
+      <c r="BD144" t="inlineStr"/>
+      <c r="BE144" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF144" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="1" t="inlineStr">
+        <is>
+          <t>vXAKoaf5</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>18.08.2024 13:00</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Stegemann S.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Rudolf-Harbig-Stadion
+ (Dresden)</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>32 249</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>30 000</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>zL1YsOi1</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>Advancing to next round
+SG Dynamo Dresden</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>ne1oL3y7</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>Dusseldorf</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr"/>
+      <c r="N145" t="inlineStr"/>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>46%</t>
+        </is>
+      </c>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="Q145" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="R145" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="S145" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T145" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V145" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W145" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="X145" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y145" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Z145" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB145" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC145" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AD145" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AE145" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AF145" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AG145" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AH145" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AI145" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AJ145" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AK145" t="inlineStr"/>
+      <c r="AL145" t="inlineStr"/>
+      <c r="AM145" t="inlineStr"/>
+      <c r="AN145" t="inlineStr"/>
+      <c r="AO145" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="AP145" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="AQ145" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="AR145" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="AS145" t="inlineStr"/>
+      <c r="AT145" t="inlineStr"/>
+      <c r="AU145" t="inlineStr">
+        <is>
+          <t>4YhTfKrD</t>
+        </is>
+      </c>
+      <c r="AV145" t="inlineStr">
+        <is>
+          <t>stamm thomas</t>
+        </is>
+      </c>
+      <c r="AW145" t="inlineStr">
+        <is>
+          <t>AoL97rX8</t>
+        </is>
+      </c>
+      <c r="AX145" t="inlineStr">
+        <is>
+          <t>thioune daniel</t>
+        </is>
+      </c>
+      <c r="AY145" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ145" t="n">
+        <v>593</v>
+      </c>
+      <c r="BA145" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB145" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC145" t="inlineStr"/>
+      <c r="BD145" t="inlineStr"/>
+      <c r="BE145" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BF145" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="1" t="inlineStr">
+        <is>
+          <t>YV3TqwPH</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>18.08.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Speckner M.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Stadion am Panzenberg
+ (Bremen)</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>5 000</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>3 500</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>tW75B1ei</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>Bremer</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>G2Op923t</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>Paderborn
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr"/>
+      <c r="N146" t="inlineStr"/>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>37%</t>
+        </is>
+      </c>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>63%</t>
+        </is>
+      </c>
+      <c r="Q146" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R146" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="S146" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V146" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="W146" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="X146" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="Y146" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Z146" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB146" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC146" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AD146" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AE146" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AF146" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AG146" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AH146" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AI146" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AJ146" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AK146" t="inlineStr"/>
+      <c r="AL146" t="inlineStr"/>
+      <c r="AM146" t="inlineStr"/>
+      <c r="AN146" t="inlineStr"/>
+      <c r="AO146" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="AP146" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="AQ146" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="AR146" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="AS146" t="inlineStr"/>
+      <c r="AT146" t="inlineStr"/>
+      <c r="AU146" t="inlineStr">
+        <is>
+          <t>4tvZg2Br</t>
+        </is>
+      </c>
+      <c r="AV146" t="inlineStr">
+        <is>
+          <t>kmiec sebastian</t>
+        </is>
+      </c>
+      <c r="AW146" t="inlineStr">
+        <is>
+          <t>0AI1QUJH</t>
+        </is>
+      </c>
+      <c r="AX146" t="inlineStr">
+        <is>
+          <t>kwasniok lukas</t>
+        </is>
+      </c>
+      <c r="AY146" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ146" t="n">
+        <v>593</v>
+      </c>
+      <c r="BA146" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB146" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC146" t="inlineStr"/>
+      <c r="BD146" t="inlineStr"/>
+      <c r="BE146" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF146" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="1" t="inlineStr">
+        <is>
+          <t>l0ueP5rR</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>18.08.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Schroder R.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Ostseestadion
+ (Rostock)</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>29 000</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>25 600</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>KIHmtCkL</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>Hansa Rostock</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>2y0u8Wrq</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>Hertha Berlin
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr"/>
+      <c r="N147" t="inlineStr"/>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>36%</t>
+        </is>
+      </c>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>64%</t>
+        </is>
+      </c>
+      <c r="Q147" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="R147" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="S147" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V147" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W147" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="X147" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="Y147" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Z147" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB147" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC147" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AD147" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AE147" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AF147" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AG147" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AH147" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AI147" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AJ147" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AK147" t="inlineStr"/>
+      <c r="AL147" t="inlineStr"/>
+      <c r="AM147" t="inlineStr"/>
+      <c r="AN147" t="inlineStr"/>
+      <c r="AO147" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="AP147" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="AQ147" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="AR147" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="AS147" t="inlineStr"/>
+      <c r="AT147" t="inlineStr"/>
+      <c r="AU147" t="inlineStr">
+        <is>
+          <t>G8THUSaE</t>
+        </is>
+      </c>
+      <c r="AV147" t="inlineStr">
+        <is>
+          <t>hollerbach bernd</t>
+        </is>
+      </c>
+      <c r="AW147" t="inlineStr">
+        <is>
+          <t>YmfcAeCo</t>
+        </is>
+      </c>
+      <c r="AX147" t="inlineStr">
+        <is>
+          <t>fiel cristian</t>
+        </is>
+      </c>
+      <c r="AY147" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ147" t="n">
+        <v>593</v>
+      </c>
+      <c r="BA147" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB147" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC147" t="inlineStr"/>
+      <c r="BD147" t="inlineStr"/>
+      <c r="BE147" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF147" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="1" t="inlineStr">
+        <is>
+          <t>t2AoZLAa</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>18.08.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Nouhoum A.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Friedrich-Ebert-Stadium
+ (Hildesheim)</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>10 000</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>5 186</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>E3xs5mIe</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>Hildesheim</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>6in2Eknb</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>Elversberg
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr"/>
+      <c r="N148" t="inlineStr"/>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>31%</t>
+        </is>
+      </c>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>69%</t>
+        </is>
+      </c>
+      <c r="Q148" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="R148" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="S148" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T148" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V148" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="W148" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="X148" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y148" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Z148" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB148" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AC148" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AD148" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AE148" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AF148" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AG148" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AH148" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AI148" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AJ148" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK148" t="inlineStr"/>
+      <c r="AL148" t="inlineStr"/>
+      <c r="AM148" t="inlineStr"/>
+      <c r="AN148" t="inlineStr"/>
+      <c r="AO148" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="AP148" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="AQ148" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="AR148" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="AS148" t="inlineStr"/>
+      <c r="AT148" t="inlineStr"/>
+      <c r="AU148" t="inlineStr">
+        <is>
+          <t>bJ0lIKrp</t>
+        </is>
+      </c>
+      <c r="AV148" t="inlineStr">
+        <is>
+          <t>hartmann marcel</t>
+        </is>
+      </c>
+      <c r="AW148" t="inlineStr">
+        <is>
+          <t>8E8qmw3d</t>
+        </is>
+      </c>
+      <c r="AX148" t="inlineStr">
+        <is>
+          <t>steffen horst</t>
+        </is>
+      </c>
+      <c r="AY148" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ148" t="n">
+        <v>593</v>
+      </c>
+      <c r="BA148" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB148" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC148" t="inlineStr"/>
+      <c r="BD148" t="inlineStr"/>
+      <c r="BE148" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BF148" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="1" t="inlineStr">
+        <is>
+          <t>jFMCm08e</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>18.08.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Heft F.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Jahnstadion Regensburg
+ (Regensburg)</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>15 210</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>12 581</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>UiCmEP56</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>Advancing to next round
+Regensburg</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>8Y2m6ADe</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>Bochum</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr"/>
+      <c r="N149" t="inlineStr"/>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>35%</t>
+        </is>
+      </c>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
+      <c r="Q149" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="R149" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="S149" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T149" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="V149" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="W149" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="X149" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="Y149" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Z149" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB149" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC149" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AD149" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="AE149" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AF149" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AG149" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AH149" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AI149" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AJ149" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AK149" t="inlineStr"/>
+      <c r="AL149" t="inlineStr"/>
+      <c r="AM149" t="inlineStr"/>
+      <c r="AN149" t="inlineStr"/>
+      <c r="AO149" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="AP149" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="AQ149" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AR149" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="AS149" t="inlineStr"/>
+      <c r="AT149" t="inlineStr"/>
+      <c r="AU149" t="inlineStr">
+        <is>
+          <t>zyLSrbZQ</t>
+        </is>
+      </c>
+      <c r="AV149" t="inlineStr">
+        <is>
+          <t>enochs joe</t>
+        </is>
+      </c>
+      <c r="AW149" t="inlineStr">
+        <is>
+          <t>8f6APkLc</t>
+        </is>
+      </c>
+      <c r="AX149" t="inlineStr">
+        <is>
+          <t>zeidler peter</t>
+        </is>
+      </c>
+      <c r="AY149" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ149" t="n">
+        <v>593</v>
+      </c>
+      <c r="BA149" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB149" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC149" t="inlineStr"/>
+      <c r="BD149" t="inlineStr"/>
+      <c r="BE149" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BF149" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="1" t="inlineStr">
+        <is>
+          <t>tvOIPExA</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>18.08.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Brand B.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Hardtwaldstadion
+ (Sandhausen)</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>15 414</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>9 705</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>UZxEj1R4</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>Sandhausen</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>WG9pOTse</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>FC Koln
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr"/>
+      <c r="N150" t="inlineStr"/>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>46%</t>
+        </is>
+      </c>
+      <c r="Q150" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R150" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="S150" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T150" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V150" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="W150" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="X150" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="Y150" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Z150" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB150" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC150" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="AD150" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="AE150" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AF150" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AG150" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AH150" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AI150" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AJ150" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AK150" t="inlineStr"/>
+      <c r="AL150" t="inlineStr"/>
+      <c r="AM150" t="inlineStr"/>
+      <c r="AN150" t="inlineStr"/>
+      <c r="AO150" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="AP150" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="AQ150" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="AR150" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="AS150" t="inlineStr"/>
+      <c r="AT150" t="inlineStr"/>
+      <c r="AU150" t="inlineStr">
+        <is>
+          <t>rZtwKVAL</t>
+        </is>
+      </c>
+      <c r="AV150" t="inlineStr">
+        <is>
+          <t>ristic sreto</t>
+        </is>
+      </c>
+      <c r="AW150" t="inlineStr">
+        <is>
+          <t>4fX0k7gg</t>
+        </is>
+      </c>
+      <c r="AX150" t="inlineStr">
+        <is>
+          <t>struber gerhard</t>
+        </is>
+      </c>
+      <c r="AY150" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ150" t="n">
+        <v>593</v>
+      </c>
+      <c r="BA150" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB150" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC150" t="inlineStr"/>
+      <c r="BD150" t="inlineStr"/>
+      <c r="BE150" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BF150" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="1" t="inlineStr">
+        <is>
+          <t>KSwfVwAO</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>18.08.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Lechner F.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Millerntor-Stadion
+ (Hamburg)</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>29 546</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>6 487</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>WrbkcjCd</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>Teutonia Ottensen</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>S0hPB9rA</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>Darmstadt
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr"/>
+      <c r="N151" t="inlineStr"/>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>31%</t>
+        </is>
+      </c>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>69%</t>
+        </is>
+      </c>
+      <c r="Q151" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R151" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="S151" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T151" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V151" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="W151" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="X151" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="Y151" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Z151" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB151" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC151" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AD151" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AE151" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF151" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AG151" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AH151" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AI151" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AJ151" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AK151" t="inlineStr"/>
+      <c r="AL151" t="inlineStr"/>
+      <c r="AM151" t="inlineStr"/>
+      <c r="AN151" t="inlineStr"/>
+      <c r="AO151" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="AP151" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="AQ151" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="AR151" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="AS151" t="inlineStr"/>
+      <c r="AT151" t="inlineStr"/>
+      <c r="AU151" t="inlineStr">
+        <is>
+          <t>lC9J1RTa</t>
+        </is>
+      </c>
+      <c r="AV151" t="inlineStr">
+        <is>
+          <t>toumi nabil</t>
+        </is>
+      </c>
+      <c r="AW151" t="inlineStr">
+        <is>
+          <t>MDhPV0RQ</t>
+        </is>
+      </c>
+      <c r="AX151" t="inlineStr">
+        <is>
+          <t>lieberknecht torsten</t>
+        </is>
+      </c>
+      <c r="AY151" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ151" t="n">
+        <v>593</v>
+      </c>
+      <c r="BA151" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB151" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC151" t="inlineStr"/>
+      <c r="BD151" t="inlineStr"/>
+      <c r="BE151" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF151" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="1" t="inlineStr">
+        <is>
+          <t>6q2yrHgU</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>18.08.2024 08:00</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Dankert B.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Ludwigspark Stadion
+ (Saarbrücken)</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>16 003</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>14 868</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>fLbhmJ5l</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>Saarbrucken</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>6FDqshzF</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>Nurnberg
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr"/>
+      <c r="N152" t="inlineStr"/>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>56%</t>
+        </is>
+      </c>
+      <c r="Q152" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R152" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="S152" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T152" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U152" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V152" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W152" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="X152" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="Y152" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Z152" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB152" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC152" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="AD152" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AE152" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AF152" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AG152" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AH152" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AI152" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AJ152" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AK152" t="inlineStr"/>
+      <c r="AL152" t="inlineStr"/>
+      <c r="AM152" t="inlineStr"/>
+      <c r="AN152" t="inlineStr"/>
+      <c r="AO152" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="AP152" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="AQ152" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="AR152" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="AS152" t="inlineStr"/>
+      <c r="AT152" t="inlineStr"/>
+      <c r="AU152" t="inlineStr">
+        <is>
+          <t>trS1MB7T</t>
+        </is>
+      </c>
+      <c r="AV152" t="inlineStr">
+        <is>
+          <t>ziehl rudiger</t>
+        </is>
+      </c>
+      <c r="AW152" t="inlineStr">
+        <is>
+          <t>tO31cZrF</t>
+        </is>
+      </c>
+      <c r="AX152" t="inlineStr">
+        <is>
+          <t>klose miroslav</t>
+        </is>
+      </c>
+      <c r="AY152" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ152" t="n">
+        <v>593</v>
+      </c>
+      <c r="BA152" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB152" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC152" t="inlineStr"/>
+      <c r="BD152" t="inlineStr"/>
+      <c r="BE152" t="inlineStr"/>
+      <c r="BF152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="1" t="inlineStr">
+        <is>
+          <t>AiJ3kset</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>18.08.2024 08:00</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Weisbach E.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Friedrich Ludwig Jahn Sportpark
+ (Berlin)</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>19 708</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>5 504</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>UNr2EUfd</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>Viktoria Berlin</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>fTVNku3I</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>Augsburg
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr"/>
+      <c r="N153" t="inlineStr"/>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>24%</t>
+        </is>
+      </c>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>76%</t>
+        </is>
+      </c>
+      <c r="Q153" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R153" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="S153" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T153" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="U153" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V153" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W153" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="X153" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y153" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Z153" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB153" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC153" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AD153" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AE153" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AF153" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AG153" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AH153" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AI153" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AJ153" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AK153" t="inlineStr"/>
+      <c r="AL153" t="inlineStr"/>
+      <c r="AM153" t="inlineStr"/>
+      <c r="AN153" t="inlineStr"/>
+      <c r="AO153" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="AP153" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="AQ153" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="AR153" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="AS153" t="inlineStr"/>
+      <c r="AT153" t="inlineStr"/>
+      <c r="AU153" t="inlineStr">
+        <is>
+          <t>CCww5Qfo</t>
+        </is>
+      </c>
+      <c r="AV153" t="inlineStr">
+        <is>
+          <t>kutrieb dennis</t>
+        </is>
+      </c>
+      <c r="AW153" t="inlineStr">
+        <is>
+          <t>2VSFgl3c</t>
+        </is>
+      </c>
+      <c r="AX153" t="inlineStr">
+        <is>
+          <t>thorup jess</t>
+        </is>
+      </c>
+      <c r="AY153" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ153" t="n">
+        <v>593</v>
+      </c>
+      <c r="BA153" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB153" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC153" t="inlineStr"/>
+      <c r="BD153" t="inlineStr"/>
+      <c r="BE153" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF153" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="1" t="inlineStr">
+        <is>
+          <t>hzyf0b9b</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>17.08.2024 13:00</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Bacher M.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>New Tivoli
+ (Aachen)</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>31 026</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>29 555</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>j3PKcB4E</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>Alemannia Aachen</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>63WsD2ei</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>Holstein Kiel
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr"/>
+      <c r="N154" t="inlineStr"/>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>39%</t>
+        </is>
+      </c>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>61%</t>
+        </is>
+      </c>
+      <c r="Q154" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R154" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="S154" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T154" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U154" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V154" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W154" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="X154" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="Y154" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Z154" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB154" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC154" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AD154" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AE154" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AF154" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AG154" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AH154" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AI154" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AJ154" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AK154" t="inlineStr"/>
+      <c r="AL154" t="inlineStr"/>
+      <c r="AM154" t="inlineStr"/>
+      <c r="AN154" t="inlineStr"/>
+      <c r="AO154" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="AP154" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="AQ154" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="AR154" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="AS154" t="inlineStr"/>
+      <c r="AT154" t="inlineStr"/>
+      <c r="AU154" t="inlineStr">
+        <is>
+          <t>SfKt2E6n</t>
+        </is>
+      </c>
+      <c r="AV154" t="inlineStr">
+        <is>
+          <t>backhaus heiner</t>
+        </is>
+      </c>
+      <c r="AW154" t="inlineStr">
+        <is>
+          <t>A15eUM4C</t>
+        </is>
+      </c>
+      <c r="AX154" t="inlineStr">
+        <is>
+          <t>rapp marcel</t>
+        </is>
+      </c>
+      <c r="AY154" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ154" t="n">
+        <v>593</v>
+      </c>
+      <c r="BA154" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB154" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC154" t="inlineStr"/>
+      <c r="BD154" t="inlineStr"/>
+      <c r="BE154" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF154" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="1" t="inlineStr">
+        <is>
+          <t>CpiTEcOi</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>17.08.2024 13:00</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Hartmann R.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Schüco Arena
+ (Bielefeld)</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>27 332</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>26 044</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>pp38UXK8</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>Advancing to next round
+Arminia Bielefeld</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>dfNCCCzS</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>Hannover</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr"/>
+      <c r="N155" t="inlineStr"/>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>56%</t>
+        </is>
+      </c>
+      <c r="Q155" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R155" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="S155" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T155" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U155" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V155" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W155" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="X155" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="Y155" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Z155" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB155" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC155" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AD155" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AE155" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AF155" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AG155" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AH155" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AI155" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AJ155" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AK155" t="inlineStr"/>
+      <c r="AL155" t="inlineStr"/>
+      <c r="AM155" t="inlineStr"/>
+      <c r="AN155" t="inlineStr"/>
+      <c r="AO155" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="AP155" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="AQ155" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="AR155" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="AS155" t="inlineStr"/>
+      <c r="AT155" t="inlineStr"/>
+      <c r="AU155" t="inlineStr">
+        <is>
+          <t>KrFXELrR</t>
+        </is>
+      </c>
+      <c r="AV155" t="inlineStr">
+        <is>
+          <t>kniat michel</t>
+        </is>
+      </c>
+      <c r="AW155" t="inlineStr">
+        <is>
+          <t>t0ZPdkUl</t>
+        </is>
+      </c>
+      <c r="AX155" t="inlineStr">
+        <is>
+          <t>leitl stefan</t>
+        </is>
+      </c>
+      <c r="AY155" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ155" t="n">
+        <v>593</v>
+      </c>
+      <c r="BA155" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB155" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC155" t="inlineStr"/>
+      <c r="BD155" t="inlineStr"/>
+      <c r="BE155" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="BF155" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="1" t="inlineStr">
+        <is>
+          <t>8CpxDyg4</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>17.08.2024 13:00</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Burda M.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Volksparkstadion
+ (Hamburg)</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>57 274</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>50 971</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>I1Vk6k3R</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>Phonix Lubeck</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>Dortmund
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr"/>
+      <c r="N156" t="inlineStr"/>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="P156" t="inlineStr">
+        <is>
+          <t>80%</t>
+        </is>
+      </c>
+      <c r="Q156" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R156" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="S156" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T156" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="U156" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V156" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W156" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="X156" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="Y156" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Z156" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB156" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC156" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AD156" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AE156" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AF156" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG156" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AH156" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AI156" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AJ156" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AK156" t="inlineStr"/>
+      <c r="AL156" t="inlineStr"/>
+      <c r="AM156" t="inlineStr"/>
+      <c r="AN156" t="inlineStr"/>
+      <c r="AO156" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="AP156" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="AQ156" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AR156" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="AS156" t="inlineStr"/>
+      <c r="AT156" t="inlineStr"/>
+      <c r="AU156" t="inlineStr">
+        <is>
+          <t>AgnJojCs</t>
+        </is>
+      </c>
+      <c r="AV156" t="inlineStr">
+        <is>
+          <t>adigo christiano</t>
+        </is>
+      </c>
+      <c r="AW156" t="inlineStr">
+        <is>
+          <t>IkCftsQm</t>
+        </is>
+      </c>
+      <c r="AX156" t="inlineStr">
+        <is>
+          <t>sahin nuri</t>
+        </is>
+      </c>
+      <c r="AY156" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ156" t="n">
+        <v>593</v>
+      </c>
+      <c r="BA156" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB156" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC156" t="inlineStr"/>
+      <c r="BD156" t="inlineStr"/>
+      <c r="BE156" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF156" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="1" t="inlineStr">
+        <is>
+          <t>bF2q76Mr</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>17.08.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Brych F.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>OSTALB ARENA
+ (Aalen)</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>14 500</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>10 850</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>Oh2C15j0</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>Aalen</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>0Ija0Ej9</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>Schalke
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr"/>
+      <c r="N157" t="inlineStr"/>
+      <c r="O157" t="inlineStr">
+        <is>
+          <t>32%</t>
+        </is>
+      </c>
+      <c r="P157" t="inlineStr">
+        <is>
+          <t>68%</t>
+        </is>
+      </c>
+      <c r="Q157" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R157" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="S157" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T157" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="U157" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V157" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W157" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="X157" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="Y157" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Z157" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB157" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC157" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AD157" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AE157" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AF157" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AG157" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AH157" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AI157" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AJ157" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AK157" t="inlineStr"/>
+      <c r="AL157" t="inlineStr"/>
+      <c r="AM157" t="inlineStr"/>
+      <c r="AN157" t="inlineStr"/>
+      <c r="AO157" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="AP157" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="AQ157" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="AR157" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="AS157" t="inlineStr"/>
+      <c r="AT157" t="inlineStr"/>
+      <c r="AU157" t="inlineStr">
+        <is>
+          <t>8bJFOfzK</t>
+        </is>
+      </c>
+      <c r="AV157" t="inlineStr">
+        <is>
+          <t>kosturkov petar</t>
+        </is>
+      </c>
+      <c r="AW157" t="inlineStr">
+        <is>
+          <t>txZLBQVC</t>
+        </is>
+      </c>
+      <c r="AX157" t="inlineStr">
+        <is>
+          <t>geraerts karel</t>
+        </is>
+      </c>
+      <c r="AY157" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ157" t="n">
+        <v>593</v>
+      </c>
+      <c r="BA157" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB157" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC157" t="inlineStr"/>
+      <c r="BD157" t="inlineStr"/>
+      <c r="BE157" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="BF157" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="1" t="inlineStr">
+        <is>
+          <t>vyk5gjdE</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>17.08.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Benen L.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Volksstadion Greifswald
+ (Greifswald)</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>4 990</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>4 990</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>Q1yNyI5t</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>Greifswald</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>pzHW4oaE</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>Union Berlin
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr"/>
+      <c r="N158" t="inlineStr"/>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>39%</t>
+        </is>
+      </c>
+      <c r="P158" t="inlineStr">
+        <is>
+          <t>61%</t>
+        </is>
+      </c>
+      <c r="Q158" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="R158" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="S158" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T158" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U158" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V158" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W158" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="X158" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y158" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Z158" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB158" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC158" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AD158" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="AE158" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AF158" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AG158" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AH158" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AI158" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AJ158" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AK158" t="inlineStr"/>
+      <c r="AL158" t="inlineStr"/>
+      <c r="AM158" t="inlineStr"/>
+      <c r="AN158" t="inlineStr"/>
+      <c r="AO158" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="AP158" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="AQ158" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AR158" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="AS158" t="inlineStr"/>
+      <c r="AT158" t="inlineStr"/>
+      <c r="AU158" t="inlineStr">
+        <is>
+          <t>Wbz1kusU</t>
+        </is>
+      </c>
+      <c r="AV158" t="inlineStr">
+        <is>
+          <t>fuchs lars</t>
+        </is>
+      </c>
+      <c r="AW158" t="inlineStr">
+        <is>
+          <t>hpYJ6izc</t>
+        </is>
+      </c>
+      <c r="AX158" t="inlineStr">
+        <is>
+          <t>svensson bo</t>
+        </is>
+      </c>
+      <c r="AY158" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ158" t="n">
+        <v>593</v>
+      </c>
+      <c r="BA158" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB158" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC158" t="inlineStr"/>
+      <c r="BD158" t="inlineStr"/>
+      <c r="BE158" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF158" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="1" t="inlineStr">
+        <is>
+          <t>tbKZHNz1</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>17.08.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Braun R.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Audi Sportpark
+ (Ingolstadt)</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>15 800</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>11 655</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>ne5QkLtB</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>Ingolstadt</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>naWckLmC</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>Kaiserslautern
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr"/>
+      <c r="N159" t="inlineStr"/>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>45%</t>
+        </is>
+      </c>
+      <c r="P159" t="inlineStr">
+        <is>
+          <t>55%</t>
+        </is>
+      </c>
+      <c r="Q159" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="R159" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="S159" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T159" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U159" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V159" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="W159" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="X159" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="Y159" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Z159" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB159" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC159" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AD159" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AE159" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AF159" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AG159" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AH159" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AI159" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AJ159" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AK159" t="inlineStr"/>
+      <c r="AL159" t="inlineStr"/>
+      <c r="AM159" t="inlineStr"/>
+      <c r="AN159" t="inlineStr"/>
+      <c r="AO159" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="AP159" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="AQ159" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="AR159" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="AS159" t="inlineStr"/>
+      <c r="AT159" t="inlineStr"/>
+      <c r="AU159" t="inlineStr">
+        <is>
+          <t>CWcD8UM8</t>
+        </is>
+      </c>
+      <c r="AV159" t="inlineStr">
+        <is>
+          <t>wittmann sabrina</t>
+        </is>
+      </c>
+      <c r="AW159" t="inlineStr">
+        <is>
+          <t>4bJLk19p</t>
+        </is>
+      </c>
+      <c r="AX159" t="inlineStr">
+        <is>
+          <t>anfang marcus</t>
+        </is>
+      </c>
+      <c r="AY159" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ159" t="n">
+        <v>593</v>
+      </c>
+      <c r="BA159" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB159" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC159" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BD159" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BE159" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF159" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="1" t="inlineStr">
+        <is>
+          <t>MZjh9ghT</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>17.08.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Dingert C.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Stadion an der Hafenstrasse
+ (Essen)</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>20 352</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>17 000</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>EB0xsr77</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>RW Essen</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>KbS1suSm</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>RB Leipzig
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr"/>
+      <c r="N160" t="inlineStr"/>
+      <c r="O160" t="inlineStr">
+        <is>
+          <t>41%</t>
+        </is>
+      </c>
+      <c r="P160" t="inlineStr">
+        <is>
+          <t>59%</t>
+        </is>
+      </c>
+      <c r="Q160" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R160" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="S160" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T160" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="U160" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V160" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="W160" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="X160" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y160" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Z160" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB160" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC160" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AD160" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AE160" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AF160" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AG160" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AH160" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AI160" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AJ160" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AK160" t="inlineStr"/>
+      <c r="AL160" t="inlineStr"/>
+      <c r="AM160" t="inlineStr"/>
+      <c r="AN160" t="inlineStr"/>
+      <c r="AO160" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="AP160" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="AQ160" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AR160" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="AS160" t="inlineStr"/>
+      <c r="AT160" t="inlineStr"/>
+      <c r="AU160" t="inlineStr">
+        <is>
+          <t>0KMe4S4D</t>
+        </is>
+      </c>
+      <c r="AV160" t="inlineStr">
+        <is>
+          <t>dabrowski christoph</t>
+        </is>
+      </c>
+      <c r="AW160" t="inlineStr">
+        <is>
+          <t>pfoInmcq</t>
+        </is>
+      </c>
+      <c r="AX160" t="inlineStr">
+        <is>
+          <t>rose marko</t>
+        </is>
+      </c>
+      <c r="AY160" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ160" t="n">
+        <v>593</v>
+      </c>
+      <c r="BA160" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB160" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC160" t="inlineStr"/>
+      <c r="BD160" t="inlineStr"/>
+      <c r="BE160" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF160" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="1" t="inlineStr">
+        <is>
+          <t>f1nnRRDE</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>17.08.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Reichel T.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Stadion an der Bremer Brück
+ (Osnabrück)</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>16 667</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>15 500</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>88Xgj1Y5</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>VfL Osnabruck</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>Freiburg
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr"/>
+      <c r="N161" t="inlineStr"/>
+      <c r="O161" t="inlineStr">
+        <is>
+          <t>49%</t>
+        </is>
+      </c>
+      <c r="P161" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="Q161" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="R161" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="S161" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T161" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="U161" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V161" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W161" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="X161" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y161" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Z161" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB161" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC161" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AD161" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AE161" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AF161" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AG161" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AH161" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AI161" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AJ161" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK161" t="inlineStr"/>
+      <c r="AL161" t="inlineStr"/>
+      <c r="AM161" t="inlineStr"/>
+      <c r="AN161" t="inlineStr"/>
+      <c r="AO161" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="AP161" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="AQ161" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="AR161" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="AS161" t="inlineStr"/>
+      <c r="AT161" t="inlineStr"/>
+      <c r="AU161" t="inlineStr">
+        <is>
+          <t>lxrr7DgN</t>
+        </is>
+      </c>
+      <c r="AV161" t="inlineStr">
+        <is>
+          <t>koschinat uwe</t>
+        </is>
+      </c>
+      <c r="AW161" t="inlineStr">
+        <is>
+          <t>YZPE6Sx7</t>
+        </is>
+      </c>
+      <c r="AX161" t="inlineStr">
+        <is>
+          <t>schuster julian</t>
+        </is>
+      </c>
+      <c r="AY161" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ161" t="n">
+        <v>593</v>
+      </c>
+      <c r="BA161" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB161" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC161" t="inlineStr"/>
+      <c r="BD161" t="inlineStr"/>
+      <c r="BE161" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BF161" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="1" t="inlineStr">
+        <is>
+          <t>8QPARz8c</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>17.08.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Michel F.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>MS Technologie Arena
+ (Villingen-Schwenningen)</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>8 000</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>6 800</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>lKLJUxeT</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>Villingen</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>KWixEVWi</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>Heidenheim
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr"/>
+      <c r="N162" t="inlineStr"/>
+      <c r="O162" t="inlineStr">
+        <is>
+          <t>33%</t>
+        </is>
+      </c>
+      <c r="P162" t="inlineStr">
+        <is>
+          <t>67%</t>
+        </is>
+      </c>
+      <c r="Q162" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="R162" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="S162" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T162" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="U162" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V162" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="W162" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="X162" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y162" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Z162" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB162" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC162" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AD162" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AE162" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AF162" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AG162" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AH162" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AI162" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AJ162" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK162" t="inlineStr"/>
+      <c r="AL162" t="inlineStr"/>
+      <c r="AM162" t="inlineStr"/>
+      <c r="AN162" t="inlineStr"/>
+      <c r="AO162" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="AP162" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="AQ162" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="AR162" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="AS162" t="inlineStr"/>
+      <c r="AT162" t="inlineStr"/>
+      <c r="AU162" t="inlineStr">
+        <is>
+          <t>lli2SfLl</t>
+        </is>
+      </c>
+      <c r="AV162" t="inlineStr">
+        <is>
+          <t>klotz mario</t>
+        </is>
+      </c>
+      <c r="AW162" t="inlineStr">
+        <is>
+          <t>4ljanukM</t>
+        </is>
+      </c>
+      <c r="AX162" t="inlineStr">
+        <is>
+          <t>schmidt frank</t>
+        </is>
+      </c>
+      <c r="AY162" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ162" t="n">
+        <v>593</v>
+      </c>
+      <c r="BA162" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB162" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC162" t="inlineStr"/>
+      <c r="BD162" t="inlineStr"/>
+      <c r="BE162" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BF162" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="1" t="inlineStr">
+        <is>
+          <t>0K2qBFNG</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>17.08.2024 08:00</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Badstubner F.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Erzgebirgsstadion
+ (Aue)</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>16 485</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>14 811</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>vsXIDreP</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>Aue</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>88HSzjDr</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>B. Monchengladbach
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr"/>
+      <c r="N163" t="inlineStr"/>
+      <c r="O163" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
+      </c>
+      <c r="P163" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="Q163" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="R163" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="S163" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T163" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="U163" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V163" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="W163" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="X163" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y163" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Z163" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA163" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB163" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC163" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AD163" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AE163" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AF163" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AG163" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH163" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AI163" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AJ163" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK163" t="inlineStr"/>
+      <c r="AL163" t="inlineStr"/>
+      <c r="AM163" t="inlineStr"/>
+      <c r="AN163" t="inlineStr"/>
+      <c r="AO163" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="AP163" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="AQ163" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="AR163" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="AS163" t="inlineStr"/>
+      <c r="AT163" t="inlineStr"/>
+      <c r="AU163" t="inlineStr">
+        <is>
+          <t>rPfNaCdg</t>
+        </is>
+      </c>
+      <c r="AV163" t="inlineStr">
+        <is>
+          <t>dotchev pavel</t>
+        </is>
+      </c>
+      <c r="AW163" t="inlineStr">
+        <is>
+          <t>M5BRZDsC</t>
+        </is>
+      </c>
+      <c r="AX163" t="inlineStr">
+        <is>
+          <t>seoane gerardo</t>
+        </is>
+      </c>
+      <c r="AY163" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ163" t="n">
+        <v>593</v>
+      </c>
+      <c r="BA163" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB163" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC163" t="inlineStr"/>
+      <c r="BD163" t="inlineStr"/>
+      <c r="BE163" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF163" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="1" t="inlineStr">
+        <is>
+          <t>Kj4sifWp</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>17.08.2024 08:00</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Prigan F.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Bruchwegstadion
+ (Mainz)</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>7 134</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>4 235</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>WzEYqEyg</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>Schott Mainz</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>CCQGbik8</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>Greuther Furth
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr"/>
+      <c r="N164" t="inlineStr"/>
+      <c r="O164" t="inlineStr">
+        <is>
+          <t>35%</t>
+        </is>
+      </c>
+      <c r="P164" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
+      <c r="Q164" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R164" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="S164" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T164" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="U164" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V164" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="W164" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X164" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y164" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Z164" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AA164" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB164" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC164" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AD164" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AE164" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AF164" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG164" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AH164" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI164" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AJ164" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK164" t="inlineStr"/>
+      <c r="AL164" t="inlineStr"/>
+      <c r="AM164" t="inlineStr"/>
+      <c r="AN164" t="inlineStr"/>
+      <c r="AO164" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="AP164" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="AQ164" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AR164" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="AS164" t="inlineStr"/>
+      <c r="AT164" t="inlineStr"/>
+      <c r="AU164" t="inlineStr">
+        <is>
+          <t>pvucOaW7</t>
+        </is>
+      </c>
+      <c r="AV164" t="inlineStr">
+        <is>
+          <t>horozovic samuel</t>
+        </is>
+      </c>
+      <c r="AW164" t="inlineStr">
+        <is>
+          <t>8E86CPuD</t>
+        </is>
+      </c>
+      <c r="AX164" t="inlineStr">
+        <is>
+          <t>zorniger alexander</t>
+        </is>
+      </c>
+      <c r="AY164" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ164" t="n">
+        <v>593</v>
+      </c>
+      <c r="BA164" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB164" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC164" t="inlineStr"/>
+      <c r="BD164" t="inlineStr"/>
+      <c r="BE164" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF164" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="1" t="inlineStr">
+        <is>
+          <t>lONsG15D</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>16.08.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Jablonski S.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Donaustadion
+ (Ulm)</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>19 500</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>17 400</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>tbC3EcQn</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>Ulm</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>nVp0wiqd</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>Bayern Munich
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr"/>
+      <c r="N165" t="inlineStr"/>
+      <c r="O165" t="inlineStr">
+        <is>
+          <t>27%</t>
+        </is>
+      </c>
+      <c r="P165" t="inlineStr">
+        <is>
+          <t>73%</t>
+        </is>
+      </c>
+      <c r="Q165" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R165" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="S165" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T165" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U165" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V165" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W165" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="X165" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="Y165" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z165" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA165" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB165" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC165" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="AD165" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AE165" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AF165" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG165" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AH165" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AI165" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AJ165" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AK165" t="inlineStr"/>
+      <c r="AL165" t="inlineStr"/>
+      <c r="AM165" t="inlineStr"/>
+      <c r="AN165" t="inlineStr"/>
+      <c r="AO165" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="AP165" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="AQ165" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="AR165" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="AS165" t="inlineStr"/>
+      <c r="AT165" t="inlineStr"/>
+      <c r="AU165" t="inlineStr">
+        <is>
+          <t>QevvB2nf</t>
+        </is>
+      </c>
+      <c r="AV165" t="inlineStr">
+        <is>
+          <t>worle thomas</t>
+        </is>
+      </c>
+      <c r="AW165" t="inlineStr">
+        <is>
+          <t>K6A2elS9</t>
+        </is>
+      </c>
+      <c r="AX165" t="inlineStr">
+        <is>
+          <t>kompany vincent</t>
+        </is>
+      </c>
+      <c r="AY165" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ165" t="n">
+        <v>593</v>
+      </c>
+      <c r="BA165" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB165" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC165" t="inlineStr"/>
+      <c r="BD165" t="inlineStr"/>
+      <c r="BE165" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF165" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="1" t="inlineStr">
+        <is>
+          <t>pWQQJq6l</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>16.08.2024 13:00</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Siebert D.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Leuna Chemie Stadion
+ (Halle)</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>15 057</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>14 000</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>boX3cIQa</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>Hallescher</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>St. Pauli
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr"/>
+      <c r="N166" t="inlineStr"/>
+      <c r="O166" t="inlineStr">
+        <is>
+          <t>34%</t>
+        </is>
+      </c>
+      <c r="P166" t="inlineStr">
+        <is>
+          <t>66%</t>
+        </is>
+      </c>
+      <c r="Q166" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R166" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="S166" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T166" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="U166" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V166" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W166" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="X166" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="Y166" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Z166" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA166" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB166" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AC166" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="AD166" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AE166" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AF166" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AG166" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AH166" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AI166" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AJ166" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AK166" t="inlineStr"/>
+      <c r="AL166" t="inlineStr"/>
+      <c r="AM166" t="inlineStr"/>
+      <c r="AN166" t="inlineStr"/>
+      <c r="AO166" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="AP166" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="AQ166" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="AR166" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="AS166" t="inlineStr"/>
+      <c r="AT166" t="inlineStr"/>
+      <c r="AU166" t="inlineStr">
+        <is>
+          <t>02hM7hzd</t>
+        </is>
+      </c>
+      <c r="AV166" t="inlineStr">
+        <is>
+          <t>zimmermann mark</t>
+        </is>
+      </c>
+      <c r="AW166" t="inlineStr">
+        <is>
+          <t>0jdIgO6t</t>
+        </is>
+      </c>
+      <c r="AX166" t="inlineStr">
+        <is>
+          <t>blessin alexander</t>
+        </is>
+      </c>
+      <c r="AY166" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ166" t="n">
+        <v>593</v>
+      </c>
+      <c r="BA166" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB166" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC166" t="inlineStr"/>
+      <c r="BD166" t="inlineStr"/>
+      <c r="BE166" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BF166" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="1" t="inlineStr">
+        <is>
+          <t>hIsO3XFj</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>16.08.2024 13:00</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Hempel R.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>BRITA-Arena
+ (Wiesbaden)</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>12 566</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>12 500</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>ObxFt3lm</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>Wehen</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>EuakNmc1</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>Mainz
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr"/>
+      <c r="N167" t="inlineStr"/>
+      <c r="O167" t="inlineStr">
+        <is>
+          <t>35%</t>
+        </is>
+      </c>
+      <c r="P167" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
+      <c r="Q167" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="R167" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="S167" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T167" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="U167" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V167" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="W167" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="X167" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="Y167" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Z167" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB167" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC167" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="AD167" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="AE167" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AF167" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AG167" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AH167" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AI167" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AJ167" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AK167" t="inlineStr"/>
+      <c r="AL167" t="inlineStr"/>
+      <c r="AM167" t="inlineStr"/>
+      <c r="AN167" t="inlineStr"/>
+      <c r="AO167" t="inlineStr">
+        <is>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="AP167" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="AQ167" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="AR167" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="AS167" t="inlineStr"/>
+      <c r="AT167" t="inlineStr"/>
+      <c r="AU167" t="inlineStr">
+        <is>
+          <t>QTAUlvUP</t>
+        </is>
+      </c>
+      <c r="AV167" t="inlineStr">
+        <is>
+          <t>doring nils</t>
+        </is>
+      </c>
+      <c r="AW167" t="inlineStr">
+        <is>
+          <t>vZA6VYpf</t>
+        </is>
+      </c>
+      <c r="AX167" t="inlineStr">
+        <is>
+          <t>henriksen bo</t>
+        </is>
+      </c>
+      <c r="AY167" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ167" t="n">
+        <v>593</v>
+      </c>
+      <c r="BA167" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB167" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC167" t="inlineStr"/>
+      <c r="BD167" t="inlineStr"/>
+      <c r="BE167" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF167" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="1" t="inlineStr">
+        <is>
+          <t>EF8gXauC</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>16.08.2024 13:00</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Petersen M.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Flyeralarm Arena
+ (Wurzburger)</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>13 090</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>12 000</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>nVM1YUFj</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>Wurzburger Kickers</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>hQAtP9Sl</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>Hoffenheim
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M168" t="inlineStr"/>
+      <c r="N168" t="inlineStr"/>
+      <c r="O168" t="inlineStr">
+        <is>
+          <t>31%</t>
+        </is>
+      </c>
+      <c r="P168" t="inlineStr">
+        <is>
+          <t>69%</t>
+        </is>
+      </c>
+      <c r="Q168" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R168" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="S168" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T168" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="U168" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V168" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="W168" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="X168" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="Y168" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Z168" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB168" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC168" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="AD168" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="AE168" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AF168" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AG168" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AH168" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AI168" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AJ168" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AK168" t="inlineStr"/>
+      <c r="AL168" t="inlineStr"/>
+      <c r="AM168" t="inlineStr"/>
+      <c r="AN168" t="inlineStr"/>
+      <c r="AO168" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="AP168" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="AQ168" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="AR168" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="AS168" t="inlineStr"/>
+      <c r="AT168" t="inlineStr"/>
+      <c r="AU168" t="inlineStr">
+        <is>
+          <t>lEwgk7go</t>
+        </is>
+      </c>
+      <c r="AV168" t="inlineStr">
+        <is>
+          <t>zschiesche markus</t>
+        </is>
+      </c>
+      <c r="AW168" t="inlineStr">
+        <is>
+          <t>KUx4Q7x1</t>
+        </is>
+      </c>
+      <c r="AX168" t="inlineStr">
+        <is>
+          <t>matarazzo pellegrino</t>
+        </is>
+      </c>
+      <c r="AY168" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ168" t="n">
+        <v>593</v>
+      </c>
+      <c r="BA168" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB168" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC168" t="inlineStr"/>
+      <c r="BD168" t="inlineStr"/>
+      <c r="BE168" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF168" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="1" t="inlineStr">
+        <is>
+          <t>fcxqFy2l</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>17.08.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Stieler T.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>BayArena
+ (Leverkusen)</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>30 210</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>30 210</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>4jcj2zMd</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>Winner
+Bayer Leverkusen</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>Stuttgart</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>2.77</t>
+        </is>
+      </c>
+      <c r="N169" t="inlineStr">
+        <is>
+          <t>2.32</t>
+        </is>
+      </c>
+      <c r="O169" t="inlineStr">
+        <is>
+          <t>38%</t>
+        </is>
+      </c>
+      <c r="P169" t="inlineStr">
+        <is>
+          <t>62%</t>
+        </is>
+      </c>
+      <c r="Q169" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R169" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="S169" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T169" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U169" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V169" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="W169" t="inlineStr"/>
+      <c r="X169" t="inlineStr"/>
+      <c r="Y169" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Z169" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA169" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB169" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC169" t="inlineStr"/>
+      <c r="AD169" t="inlineStr"/>
+      <c r="AE169" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AF169" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AG169" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AH169" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AI169" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AJ169" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AK169" t="inlineStr">
+        <is>
+          <t>295</t>
+        </is>
+      </c>
+      <c r="AL169" t="inlineStr">
+        <is>
+          <t>578</t>
+        </is>
+      </c>
+      <c r="AM169" t="inlineStr">
+        <is>
+          <t>249</t>
+        </is>
+      </c>
+      <c r="AN169" t="inlineStr">
+        <is>
+          <t>547</t>
+        </is>
+      </c>
+      <c r="AO169" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="AP169" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="AQ169" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="AR169" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="AS169" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="AT169" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="AU169" t="inlineStr">
+        <is>
+          <t>hAcTWKKN</t>
+        </is>
+      </c>
+      <c r="AV169" t="inlineStr">
+        <is>
+          <t>alonso xabi</t>
+        </is>
+      </c>
+      <c r="AW169" t="inlineStr">
+        <is>
+          <t>GzfvcwRj</t>
+        </is>
+      </c>
+      <c r="AX169" t="inlineStr">
+        <is>
+          <t>hoeness sebastian</t>
+        </is>
+      </c>
+      <c r="AY169" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ169" t="n">
+        <v>594</v>
+      </c>
+      <c r="BA169" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB169" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="BC169" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BD169" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE169" t="inlineStr"/>
+      <c r="BF169" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/germany/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
+++ b/data/germany/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BF138"/>
+  <dimension ref="A1:BF173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27739,15 +27739,11 @@
           <t>36 103</t>
         </is>
       </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G134" t="n">
+        <v>0</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
@@ -27769,15 +27765,11 @@
           <t>Karlsruher SC</t>
         </is>
       </c>
-      <c r="M134" t="inlineStr">
-        <is>
-          <t>1.09</t>
-        </is>
-      </c>
-      <c r="N134" t="inlineStr">
-        <is>
-          <t>0.66</t>
-        </is>
+      <c r="M134" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.66</v>
       </c>
       <c r="O134" t="inlineStr">
         <is>
@@ -27789,155 +27781,95 @@
           <t>47%</t>
         </is>
       </c>
-      <c r="Q134" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="R134" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="S134" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="T134" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U134" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="V134" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="W134" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="X134" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="Y134" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Z134" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA134" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AB134" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC134" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AD134" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AE134" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AF134" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AG134" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AH134" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AI134" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AJ134" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AK134" t="inlineStr">
-        <is>
-          <t>502</t>
-        </is>
-      </c>
-      <c r="AL134" t="inlineStr">
-        <is>
-          <t>487</t>
-        </is>
-      </c>
-      <c r="AM134" t="inlineStr">
-        <is>
-          <t>442</t>
-        </is>
-      </c>
-      <c r="AN134" t="inlineStr">
-        <is>
-          <t>409</t>
-        </is>
-      </c>
-      <c r="AO134" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="AP134" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="AQ134" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="AR134" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="AS134" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="AT134" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
+      <c r="Q134" t="n">
+        <v>20</v>
+      </c>
+      <c r="R134" t="n">
+        <v>9</v>
+      </c>
+      <c r="S134" t="n">
+        <v>6</v>
+      </c>
+      <c r="T134" t="n">
+        <v>2</v>
+      </c>
+      <c r="U134" t="n">
+        <v>14</v>
+      </c>
+      <c r="V134" t="n">
+        <v>7</v>
+      </c>
+      <c r="W134" t="n">
+        <v>7</v>
+      </c>
+      <c r="X134" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>18</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>6</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>502</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>487</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>442</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>409</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>95</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>96</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>61</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>39</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>114</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>114</v>
       </c>
       <c r="AU134" t="inlineStr">
         <is>
@@ -28011,15 +27943,11 @@
           <t>9 502</t>
         </is>
       </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G135" t="n">
+        <v>2</v>
+      </c>
+      <c r="H135" t="n">
+        <v>2</v>
       </c>
       <c r="I135" t="inlineStr">
         <is>
@@ -28041,15 +27969,11 @@
           <t>FC Koln</t>
         </is>
       </c>
-      <c r="M135" t="inlineStr">
-        <is>
-          <t>2.45</t>
-        </is>
-      </c>
-      <c r="N135" t="inlineStr">
-        <is>
-          <t>3.39</t>
-        </is>
+      <c r="M135" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="N135" t="n">
+        <v>3.39</v>
       </c>
       <c r="O135" t="inlineStr">
         <is>
@@ -28061,155 +27985,95 @@
           <t>55%</t>
         </is>
       </c>
-      <c r="Q135" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="R135" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="S135" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="T135" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="U135" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V135" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="W135" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="X135" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="Y135" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Z135" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AA135" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB135" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC135" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AD135" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AE135" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AF135" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AG135" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AH135" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AI135" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AJ135" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AK135" t="inlineStr">
-        <is>
-          <t>399</t>
-        </is>
-      </c>
-      <c r="AL135" t="inlineStr">
-        <is>
-          <t>505</t>
-        </is>
-      </c>
-      <c r="AM135" t="inlineStr">
-        <is>
-          <t>311</t>
-        </is>
-      </c>
-      <c r="AN135" t="inlineStr">
-        <is>
-          <t>419</t>
-        </is>
-      </c>
-      <c r="AO135" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="AP135" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="AQ135" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="AR135" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="AS135" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="AT135" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
+      <c r="Q135" t="n">
+        <v>10</v>
+      </c>
+      <c r="R135" t="n">
+        <v>23</v>
+      </c>
+      <c r="S135" t="n">
+        <v>3</v>
+      </c>
+      <c r="T135" t="n">
+        <v>9</v>
+      </c>
+      <c r="U135" t="n">
+        <v>7</v>
+      </c>
+      <c r="V135" t="n">
+        <v>14</v>
+      </c>
+      <c r="W135" t="n">
+        <v>13</v>
+      </c>
+      <c r="X135" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>17</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>13</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>399</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>505</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>311</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>419</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>66</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>114</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>29</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>76</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>114</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>117</v>
       </c>
       <c r="AU135" t="inlineStr">
         <is>
@@ -28283,15 +28147,11 @@
           <t>50 000</t>
         </is>
       </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G136" t="n">
+        <v>3</v>
+      </c>
+      <c r="H136" t="n">
+        <v>1</v>
       </c>
       <c r="I136" t="inlineStr">
         <is>
@@ -28313,15 +28173,11 @@
           <t>Schalke</t>
         </is>
       </c>
-      <c r="M136" t="inlineStr">
-        <is>
-          <t>0.93</t>
-        </is>
-      </c>
-      <c r="N136" t="inlineStr">
-        <is>
-          <t>2.12</t>
-        </is>
+      <c r="M136" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="N136" t="n">
+        <v>2.12</v>
       </c>
       <c r="O136" t="inlineStr">
         <is>
@@ -28333,155 +28189,95 @@
           <t>49%</t>
         </is>
       </c>
-      <c r="Q136" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="R136" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="S136" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="T136" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="U136" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="V136" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="W136" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="X136" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="Y136" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Z136" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA136" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB136" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC136" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AD136" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AE136" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AF136" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AG136" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AH136" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AI136" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AJ136" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AK136" t="inlineStr">
-        <is>
-          <t>366</t>
-        </is>
-      </c>
-      <c r="AL136" t="inlineStr">
-        <is>
-          <t>370</t>
-        </is>
-      </c>
-      <c r="AM136" t="inlineStr">
-        <is>
-          <t>304</t>
-        </is>
-      </c>
-      <c r="AN136" t="inlineStr">
-        <is>
-          <t>315</t>
-        </is>
-      </c>
-      <c r="AO136" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="AP136" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="AQ136" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="AR136" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="AS136" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="AT136" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
+      <c r="Q136" t="n">
+        <v>8</v>
+      </c>
+      <c r="R136" t="n">
+        <v>17</v>
+      </c>
+      <c r="S136" t="n">
+        <v>5</v>
+      </c>
+      <c r="T136" t="n">
+        <v>5</v>
+      </c>
+      <c r="U136" t="n">
+        <v>3</v>
+      </c>
+      <c r="V136" t="n">
+        <v>12</v>
+      </c>
+      <c r="W136" t="n">
+        <v>12</v>
+      </c>
+      <c r="X136" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>21</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>12</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>366</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>370</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>304</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>315</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>76</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>91</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>22</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>48</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>107</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>103</v>
       </c>
       <c r="AU136" t="inlineStr">
         <is>
@@ -28517,15 +28313,11 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="BC136" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BD136" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="BC136" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>1</v>
       </c>
       <c r="BE136" t="inlineStr"/>
       <c r="BF136" t="inlineStr"/>
@@ -28563,15 +28355,11 @@
           <t>41 632</t>
         </is>
       </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G137" t="n">
+        <v>2</v>
+      </c>
+      <c r="H137" t="n">
+        <v>2</v>
       </c>
       <c r="I137" t="inlineStr">
         <is>
@@ -28593,15 +28381,11 @@
           <t>Greuther Furth</t>
         </is>
       </c>
-      <c r="M137" t="inlineStr">
-        <is>
-          <t>2.02</t>
-        </is>
-      </c>
-      <c r="N137" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
+      <c r="M137" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="N137" t="n">
+        <v>2.7</v>
       </c>
       <c r="O137" t="inlineStr">
         <is>
@@ -28613,155 +28397,95 @@
           <t>46%</t>
         </is>
       </c>
-      <c r="Q137" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="R137" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="S137" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="T137" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="U137" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="V137" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="W137" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="X137" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y137" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Z137" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA137" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB137" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AC137" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AD137" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AE137" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AF137" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AG137" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AH137" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AI137" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AJ137" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AK137" t="inlineStr">
-        <is>
-          <t>503</t>
-        </is>
-      </c>
-      <c r="AL137" t="inlineStr">
-        <is>
-          <t>380</t>
-        </is>
-      </c>
-      <c r="AM137" t="inlineStr">
-        <is>
-          <t>423</t>
-        </is>
-      </c>
-      <c r="AN137" t="inlineStr">
-        <is>
-          <t>304</t>
-        </is>
-      </c>
-      <c r="AO137" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="AP137" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="AQ137" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="AR137" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="AS137" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="AT137" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
+      <c r="Q137" t="n">
+        <v>13</v>
+      </c>
+      <c r="R137" t="n">
+        <v>15</v>
+      </c>
+      <c r="S137" t="n">
+        <v>7</v>
+      </c>
+      <c r="T137" t="n">
+        <v>8</v>
+      </c>
+      <c r="U137" t="n">
+        <v>6</v>
+      </c>
+      <c r="V137" t="n">
+        <v>7</v>
+      </c>
+      <c r="W137" t="n">
+        <v>8</v>
+      </c>
+      <c r="X137" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>18</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>14</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>503</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>380</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>423</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>304</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>97</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>80</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>49</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>30</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>112</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>116</v>
       </c>
       <c r="AU137" t="inlineStr">
         <is>
@@ -28835,15 +28559,11 @@
           <t>12 095</t>
         </is>
       </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G138" t="n">
+        <v>1</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0</v>
       </c>
       <c r="I138" t="inlineStr">
         <is>
@@ -28865,15 +28585,11 @@
           <t>Ulm</t>
         </is>
       </c>
-      <c r="M138" t="inlineStr">
-        <is>
-          <t>0.74</t>
-        </is>
-      </c>
-      <c r="N138" t="inlineStr">
-        <is>
-          <t>0.47</t>
-        </is>
+      <c r="M138" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.47</v>
       </c>
       <c r="O138" t="inlineStr">
         <is>
@@ -28885,155 +28601,95 @@
           <t>51%</t>
         </is>
       </c>
-      <c r="Q138" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="R138" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="S138" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="T138" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="U138" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V138" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="W138" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="X138" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="Y138" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Z138" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA138" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB138" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC138" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="AD138" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="AE138" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AF138" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG138" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="AH138" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AI138" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AJ138" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AK138" t="inlineStr">
-        <is>
-          <t>285</t>
-        </is>
-      </c>
-      <c r="AL138" t="inlineStr">
-        <is>
-          <t>351</t>
-        </is>
-      </c>
-      <c r="AM138" t="inlineStr">
-        <is>
-          <t>214</t>
-        </is>
-      </c>
-      <c r="AN138" t="inlineStr">
-        <is>
-          <t>263</t>
-        </is>
-      </c>
-      <c r="AO138" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="AP138" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="AQ138" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="AR138" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="AS138" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="AT138" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
+      <c r="Q138" t="n">
+        <v>8</v>
+      </c>
+      <c r="R138" t="n">
+        <v>11</v>
+      </c>
+      <c r="S138" t="n">
+        <v>1</v>
+      </c>
+      <c r="T138" t="n">
+        <v>5</v>
+      </c>
+      <c r="U138" t="n">
+        <v>7</v>
+      </c>
+      <c r="V138" t="n">
+        <v>6</v>
+      </c>
+      <c r="W138" t="n">
+        <v>17</v>
+      </c>
+      <c r="X138" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>23</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>22</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>285</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>351</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>214</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>263</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>79</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>106</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>36</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>49</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>110</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>114</v>
       </c>
       <c r="AU138" t="inlineStr">
         <is>
@@ -29074,6 +28730,7037 @@
       <c r="BE138" t="inlineStr"/>
       <c r="BF138" t="inlineStr"/>
     </row>
+    <row r="139">
+      <c r="A139" s="1" t="inlineStr">
+        <is>
+          <t>QHrzGLhf</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>11.08.2024 08:30</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Reichel T.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Eintracht-Stadion
+ (Braunschweig)</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>23 325</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>22 791</t>
+        </is>
+      </c>
+      <c r="G139" t="n">
+        <v>1</v>
+      </c>
+      <c r="H139" t="n">
+        <v>3</v>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>QqLCC3il</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>Braunschweig</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>YFuz2RLm</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>Magdeburg</t>
+        </is>
+      </c>
+      <c r="M139" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="N139" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>49%</t>
+        </is>
+      </c>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="Q139" t="n">
+        <v>20</v>
+      </c>
+      <c r="R139" t="n">
+        <v>11</v>
+      </c>
+      <c r="S139" t="n">
+        <v>8</v>
+      </c>
+      <c r="T139" t="n">
+        <v>6</v>
+      </c>
+      <c r="U139" t="n">
+        <v>12</v>
+      </c>
+      <c r="V139" t="n">
+        <v>5</v>
+      </c>
+      <c r="W139" t="n">
+        <v>14</v>
+      </c>
+      <c r="X139" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>9</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>391</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>411</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>305</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>341</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>118</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>59</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>51</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>15</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>118</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>117</v>
+      </c>
+      <c r="AU139" t="inlineStr">
+        <is>
+          <t>SQrxFAMl</t>
+        </is>
+      </c>
+      <c r="AV139" t="inlineStr">
+        <is>
+          <t>scherning daniel</t>
+        </is>
+      </c>
+      <c r="AW139" t="inlineStr">
+        <is>
+          <t>IgZoGKFn</t>
+        </is>
+      </c>
+      <c r="AX139" t="inlineStr">
+        <is>
+          <t>titz christian</t>
+        </is>
+      </c>
+      <c r="AY139" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>592</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB139" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC139" t="inlineStr"/>
+      <c r="BD139" t="inlineStr"/>
+      <c r="BE139" t="inlineStr"/>
+      <c r="BF139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="1" t="inlineStr">
+        <is>
+          <t>KdD11Mw1</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>11.08.2024 08:30</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Schwengers P.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Home Deluxe Arena
+ (Paderborn)</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>12 972</t>
+        </is>
+      </c>
+      <c r="G140" t="n">
+        <v>3</v>
+      </c>
+      <c r="H140" t="n">
+        <v>1</v>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>G2Op923t</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>Paderborn</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>S0hPB9rA</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>Darmstadt</t>
+        </is>
+      </c>
+      <c r="M140" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="N140" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>46%</t>
+        </is>
+      </c>
+      <c r="Q140" t="n">
+        <v>18</v>
+      </c>
+      <c r="R140" t="n">
+        <v>15</v>
+      </c>
+      <c r="S140" t="n">
+        <v>5</v>
+      </c>
+      <c r="T140" t="n">
+        <v>7</v>
+      </c>
+      <c r="U140" t="n">
+        <v>13</v>
+      </c>
+      <c r="V140" t="n">
+        <v>8</v>
+      </c>
+      <c r="W140" t="n">
+        <v>11</v>
+      </c>
+      <c r="X140" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>20</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>8</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>11</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>443</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>423</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>372</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>330</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>72</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>104</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>43</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>45</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>118</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>114</v>
+      </c>
+      <c r="AU140" t="inlineStr">
+        <is>
+          <t>0AI1QUJH</t>
+        </is>
+      </c>
+      <c r="AV140" t="inlineStr">
+        <is>
+          <t>kwasniok lukas</t>
+        </is>
+      </c>
+      <c r="AW140" t="inlineStr">
+        <is>
+          <t>MDhPV0RQ</t>
+        </is>
+      </c>
+      <c r="AX140" t="inlineStr">
+        <is>
+          <t>lieberknecht torsten</t>
+        </is>
+      </c>
+      <c r="AY140" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>592</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB140" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC140" t="inlineStr"/>
+      <c r="BD140" t="inlineStr"/>
+      <c r="BE140" t="inlineStr"/>
+      <c r="BF140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="1" t="inlineStr">
+        <is>
+          <t>MqxqEaN6</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>11.08.2024 08:30</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Erbst L.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Preussenstadion
+ (Munster)</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>12 794</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>12 422</t>
+        </is>
+      </c>
+      <c r="G141" t="n">
+        <v>0</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0</v>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>zedZaSL7</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>Preussen Munster</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>dfNCCCzS</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>Hannover</t>
+        </is>
+      </c>
+      <c r="M141" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
+      </c>
+      <c r="Q141" t="n">
+        <v>11</v>
+      </c>
+      <c r="R141" t="n">
+        <v>9</v>
+      </c>
+      <c r="S141" t="n">
+        <v>4</v>
+      </c>
+      <c r="T141" t="n">
+        <v>1</v>
+      </c>
+      <c r="U141" t="n">
+        <v>7</v>
+      </c>
+      <c r="V141" t="n">
+        <v>8</v>
+      </c>
+      <c r="W141" t="n">
+        <v>13</v>
+      </c>
+      <c r="X141" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>26</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>11</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>293</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>371</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>211</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>304</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>67</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>100</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>29</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>40</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>110</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>108</v>
+      </c>
+      <c r="AU141" t="inlineStr">
+        <is>
+          <t>pdPRS0me</t>
+        </is>
+      </c>
+      <c r="AV141" t="inlineStr">
+        <is>
+          <t>hildmann sascha</t>
+        </is>
+      </c>
+      <c r="AW141" t="inlineStr">
+        <is>
+          <t>t0ZPdkUl</t>
+        </is>
+      </c>
+      <c r="AX141" t="inlineStr">
+        <is>
+          <t>leitl stefan</t>
+        </is>
+      </c>
+      <c r="AY141" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>592</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB141" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC141" t="inlineStr"/>
+      <c r="BD141" t="inlineStr"/>
+      <c r="BE141" t="inlineStr"/>
+      <c r="BF141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="1" t="inlineStr">
+        <is>
+          <t>CW9g3r9l</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>10.08.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Gerach T.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Volksparkstadion
+ (Hamburg)</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>57 274</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>57 000</t>
+        </is>
+      </c>
+      <c r="G142" t="n">
+        <v>1</v>
+      </c>
+      <c r="H142" t="n">
+        <v>1</v>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>v9k3aY5F</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>Hamburger SV</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>2y0u8Wrq</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>Hertha Berlin</t>
+        </is>
+      </c>
+      <c r="M142" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="Q142" t="n">
+        <v>13</v>
+      </c>
+      <c r="R142" t="n">
+        <v>13</v>
+      </c>
+      <c r="S142" t="n">
+        <v>3</v>
+      </c>
+      <c r="T142" t="n">
+        <v>4</v>
+      </c>
+      <c r="U142" t="n">
+        <v>10</v>
+      </c>
+      <c r="V142" t="n">
+        <v>9</v>
+      </c>
+      <c r="W142" t="n">
+        <v>9</v>
+      </c>
+      <c r="X142" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>23</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>9</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>353</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>490</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>311</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>436</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>77</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>125</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>42</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>64</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>113</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>111</v>
+      </c>
+      <c r="AU142" t="inlineStr">
+        <is>
+          <t>EDRZkDzS</t>
+        </is>
+      </c>
+      <c r="AV142" t="inlineStr">
+        <is>
+          <t>baumgart steffen</t>
+        </is>
+      </c>
+      <c r="AW142" t="inlineStr">
+        <is>
+          <t>YmfcAeCo</t>
+        </is>
+      </c>
+      <c r="AX142" t="inlineStr">
+        <is>
+          <t>fiel cristian</t>
+        </is>
+      </c>
+      <c r="AY142" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>592</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB142" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC142" t="inlineStr"/>
+      <c r="BD142" t="inlineStr"/>
+      <c r="BE142" t="inlineStr"/>
+      <c r="BF142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="1" t="inlineStr">
+        <is>
+          <t>pzHxyrtm</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>18.08.2024 13:00</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Oldhafer K.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Stadion am Lotter Kreuz
+ (Lotte)</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>10 059</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>4 637</t>
+        </is>
+      </c>
+      <c r="G143" t="n">
+        <v>0</v>
+      </c>
+      <c r="H143" t="n">
+        <v>5</v>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>hjNlCFPB</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>Lotte</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>EB3q7jbk</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>Karlsruher SC
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr"/>
+      <c r="N143" t="inlineStr"/>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="Q143" t="n">
+        <v>8</v>
+      </c>
+      <c r="R143" t="n">
+        <v>16</v>
+      </c>
+      <c r="S143" t="n">
+        <v>1</v>
+      </c>
+      <c r="T143" t="n">
+        <v>7</v>
+      </c>
+      <c r="U143" t="n">
+        <v>5</v>
+      </c>
+      <c r="V143" t="n">
+        <v>5</v>
+      </c>
+      <c r="W143" t="n">
+        <v>9</v>
+      </c>
+      <c r="X143" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>24</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK143" t="inlineStr"/>
+      <c r="AL143" t="inlineStr"/>
+      <c r="AM143" t="inlineStr"/>
+      <c r="AN143" t="inlineStr"/>
+      <c r="AO143" t="n">
+        <v>97</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>89</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>62</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>74</v>
+      </c>
+      <c r="AS143" t="inlineStr"/>
+      <c r="AT143" t="inlineStr"/>
+      <c r="AU143" t="inlineStr">
+        <is>
+          <t>KW0bzbwJ</t>
+        </is>
+      </c>
+      <c r="AV143" t="inlineStr">
+        <is>
+          <t>lubbers fabian</t>
+        </is>
+      </c>
+      <c r="AW143" t="inlineStr">
+        <is>
+          <t>OzPMRhK3</t>
+        </is>
+      </c>
+      <c r="AX143" t="inlineStr">
+        <is>
+          <t>eichner christian</t>
+        </is>
+      </c>
+      <c r="AY143" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>593</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB143" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC143" t="inlineStr"/>
+      <c r="BD143" t="inlineStr"/>
+      <c r="BE143" t="n">
+        <v>2</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="1" t="inlineStr">
+        <is>
+          <t>dCPKovw8</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>18.08.2024 13:00</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Zwayer F.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Hansch-Arena
+ (Meppen)</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>13 696</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>12 959</t>
+        </is>
+      </c>
+      <c r="G144" t="n">
+        <v>1</v>
+      </c>
+      <c r="H144" t="n">
+        <v>7</v>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>rXqBh2xP</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>Meppen</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>v9k3aY5F</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>Hamburger SV
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr"/>
+      <c r="N144" t="inlineStr"/>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>31%</t>
+        </is>
+      </c>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>69%</t>
+        </is>
+      </c>
+      <c r="Q144" t="n">
+        <v>7</v>
+      </c>
+      <c r="R144" t="n">
+        <v>15</v>
+      </c>
+      <c r="S144" t="n">
+        <v>2</v>
+      </c>
+      <c r="T144" t="n">
+        <v>12</v>
+      </c>
+      <c r="U144" t="n">
+        <v>5</v>
+      </c>
+      <c r="V144" t="n">
+        <v>3</v>
+      </c>
+      <c r="W144" t="n">
+        <v>14</v>
+      </c>
+      <c r="X144" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y144" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z144" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB144" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC144" t="n">
+        <v>20</v>
+      </c>
+      <c r="AD144" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE144" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF144" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG144" t="n">
+        <v>8</v>
+      </c>
+      <c r="AH144" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI144" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK144" t="inlineStr"/>
+      <c r="AL144" t="inlineStr"/>
+      <c r="AM144" t="inlineStr"/>
+      <c r="AN144" t="inlineStr"/>
+      <c r="AO144" t="n">
+        <v>69</v>
+      </c>
+      <c r="AP144" t="n">
+        <v>88</v>
+      </c>
+      <c r="AQ144" t="n">
+        <v>44</v>
+      </c>
+      <c r="AR144" t="n">
+        <v>71</v>
+      </c>
+      <c r="AS144" t="inlineStr"/>
+      <c r="AT144" t="inlineStr"/>
+      <c r="AU144" t="inlineStr">
+        <is>
+          <t>UqphGQrg</t>
+        </is>
+      </c>
+      <c r="AV144" t="inlineStr">
+        <is>
+          <t>beniermann lucas</t>
+        </is>
+      </c>
+      <c r="AW144" t="inlineStr">
+        <is>
+          <t>EDRZkDzS</t>
+        </is>
+      </c>
+      <c r="AX144" t="inlineStr">
+        <is>
+          <t>baumgart steffen</t>
+        </is>
+      </c>
+      <c r="AY144" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ144" t="n">
+        <v>593</v>
+      </c>
+      <c r="BA144" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB144" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC144" t="inlineStr"/>
+      <c r="BD144" t="inlineStr"/>
+      <c r="BE144" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF144" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="1" t="inlineStr">
+        <is>
+          <t>vXAKoaf5</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>18.08.2024 13:00</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Stegemann S.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Rudolf-Harbig-Stadion
+ (Dresden)</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>32 249</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>30 000</t>
+        </is>
+      </c>
+      <c r="G145" t="n">
+        <v>2</v>
+      </c>
+      <c r="H145" t="n">
+        <v>0</v>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>zL1YsOi1</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>Advancing to next round
+SG Dynamo Dresden</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>ne1oL3y7</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>Dusseldorf</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr"/>
+      <c r="N145" t="inlineStr"/>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>46%</t>
+        </is>
+      </c>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="Q145" t="n">
+        <v>19</v>
+      </c>
+      <c r="R145" t="n">
+        <v>9</v>
+      </c>
+      <c r="S145" t="n">
+        <v>4</v>
+      </c>
+      <c r="T145" t="n">
+        <v>5</v>
+      </c>
+      <c r="U145" t="n">
+        <v>10</v>
+      </c>
+      <c r="V145" t="n">
+        <v>3</v>
+      </c>
+      <c r="W145" t="n">
+        <v>10</v>
+      </c>
+      <c r="X145" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y145" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z145" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA145" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB145" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC145" t="n">
+        <v>13</v>
+      </c>
+      <c r="AD145" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE145" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF145" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG145" t="n">
+        <v>8</v>
+      </c>
+      <c r="AH145" t="n">
+        <v>9</v>
+      </c>
+      <c r="AI145" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ145" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK145" t="inlineStr"/>
+      <c r="AL145" t="inlineStr"/>
+      <c r="AM145" t="inlineStr"/>
+      <c r="AN145" t="inlineStr"/>
+      <c r="AO145" t="n">
+        <v>119</v>
+      </c>
+      <c r="AP145" t="n">
+        <v>110</v>
+      </c>
+      <c r="AQ145" t="n">
+        <v>72</v>
+      </c>
+      <c r="AR145" t="n">
+        <v>62</v>
+      </c>
+      <c r="AS145" t="inlineStr"/>
+      <c r="AT145" t="inlineStr"/>
+      <c r="AU145" t="inlineStr">
+        <is>
+          <t>4YhTfKrD</t>
+        </is>
+      </c>
+      <c r="AV145" t="inlineStr">
+        <is>
+          <t>stamm thomas</t>
+        </is>
+      </c>
+      <c r="AW145" t="inlineStr">
+        <is>
+          <t>AoL97rX8</t>
+        </is>
+      </c>
+      <c r="AX145" t="inlineStr">
+        <is>
+          <t>thioune daniel</t>
+        </is>
+      </c>
+      <c r="AY145" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ145" t="n">
+        <v>593</v>
+      </c>
+      <c r="BA145" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB145" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC145" t="inlineStr"/>
+      <c r="BD145" t="inlineStr"/>
+      <c r="BE145" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF145" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="1" t="inlineStr">
+        <is>
+          <t>YV3TqwPH</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>18.08.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Speckner M.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Stadion am Panzenberg
+ (Bremen)</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>5 000</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>3 500</t>
+        </is>
+      </c>
+      <c r="G146" t="n">
+        <v>0</v>
+      </c>
+      <c r="H146" t="n">
+        <v>4</v>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>tW75B1ei</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>Bremer</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>G2Op923t</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>Paderborn
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr"/>
+      <c r="N146" t="inlineStr"/>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>37%</t>
+        </is>
+      </c>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>63%</t>
+        </is>
+      </c>
+      <c r="Q146" t="n">
+        <v>7</v>
+      </c>
+      <c r="R146" t="n">
+        <v>18</v>
+      </c>
+      <c r="S146" t="n">
+        <v>2</v>
+      </c>
+      <c r="T146" t="n">
+        <v>7</v>
+      </c>
+      <c r="U146" t="n">
+        <v>5</v>
+      </c>
+      <c r="V146" t="n">
+        <v>8</v>
+      </c>
+      <c r="W146" t="n">
+        <v>20</v>
+      </c>
+      <c r="X146" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y146" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z146" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB146" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC146" t="n">
+        <v>18</v>
+      </c>
+      <c r="AD146" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE146" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF146" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG146" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH146" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI146" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ146" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK146" t="inlineStr"/>
+      <c r="AL146" t="inlineStr"/>
+      <c r="AM146" t="inlineStr"/>
+      <c r="AN146" t="inlineStr"/>
+      <c r="AO146" t="n">
+        <v>93</v>
+      </c>
+      <c r="AP146" t="n">
+        <v>128</v>
+      </c>
+      <c r="AQ146" t="n">
+        <v>34</v>
+      </c>
+      <c r="AR146" t="n">
+        <v>82</v>
+      </c>
+      <c r="AS146" t="inlineStr"/>
+      <c r="AT146" t="inlineStr"/>
+      <c r="AU146" t="inlineStr">
+        <is>
+          <t>4tvZg2Br</t>
+        </is>
+      </c>
+      <c r="AV146" t="inlineStr">
+        <is>
+          <t>kmiec sebastian</t>
+        </is>
+      </c>
+      <c r="AW146" t="inlineStr">
+        <is>
+          <t>0AI1QUJH</t>
+        </is>
+      </c>
+      <c r="AX146" t="inlineStr">
+        <is>
+          <t>kwasniok lukas</t>
+        </is>
+      </c>
+      <c r="AY146" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ146" t="n">
+        <v>593</v>
+      </c>
+      <c r="BA146" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB146" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC146" t="inlineStr"/>
+      <c r="BD146" t="inlineStr"/>
+      <c r="BE146" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF146" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="1" t="inlineStr">
+        <is>
+          <t>l0ueP5rR</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>18.08.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Schroder R.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Ostseestadion
+ (Rostock)</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>29 000</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>25 600</t>
+        </is>
+      </c>
+      <c r="G147" t="n">
+        <v>1</v>
+      </c>
+      <c r="H147" t="n">
+        <v>5</v>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>KIHmtCkL</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>Hansa Rostock</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>2y0u8Wrq</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>Hertha Berlin
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr"/>
+      <c r="N147" t="inlineStr"/>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>36%</t>
+        </is>
+      </c>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>64%</t>
+        </is>
+      </c>
+      <c r="Q147" t="n">
+        <v>6</v>
+      </c>
+      <c r="R147" t="n">
+        <v>14</v>
+      </c>
+      <c r="S147" t="n">
+        <v>3</v>
+      </c>
+      <c r="T147" t="n">
+        <v>6</v>
+      </c>
+      <c r="U147" t="n">
+        <v>3</v>
+      </c>
+      <c r="V147" t="n">
+        <v>3</v>
+      </c>
+      <c r="W147" t="n">
+        <v>11</v>
+      </c>
+      <c r="X147" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y147" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z147" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA147" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC147" t="n">
+        <v>17</v>
+      </c>
+      <c r="AD147" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE147" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF147" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG147" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH147" t="n">
+        <v>11</v>
+      </c>
+      <c r="AI147" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ147" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK147" t="inlineStr"/>
+      <c r="AL147" t="inlineStr"/>
+      <c r="AM147" t="inlineStr"/>
+      <c r="AN147" t="inlineStr"/>
+      <c r="AO147" t="n">
+        <v>64</v>
+      </c>
+      <c r="AP147" t="n">
+        <v>89</v>
+      </c>
+      <c r="AQ147" t="n">
+        <v>33</v>
+      </c>
+      <c r="AR147" t="n">
+        <v>55</v>
+      </c>
+      <c r="AS147" t="inlineStr"/>
+      <c r="AT147" t="inlineStr"/>
+      <c r="AU147" t="inlineStr">
+        <is>
+          <t>G8THUSaE</t>
+        </is>
+      </c>
+      <c r="AV147" t="inlineStr">
+        <is>
+          <t>hollerbach bernd</t>
+        </is>
+      </c>
+      <c r="AW147" t="inlineStr">
+        <is>
+          <t>YmfcAeCo</t>
+        </is>
+      </c>
+      <c r="AX147" t="inlineStr">
+        <is>
+          <t>fiel cristian</t>
+        </is>
+      </c>
+      <c r="AY147" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ147" t="n">
+        <v>593</v>
+      </c>
+      <c r="BA147" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB147" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC147" t="inlineStr"/>
+      <c r="BD147" t="inlineStr"/>
+      <c r="BE147" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF147" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="1" t="inlineStr">
+        <is>
+          <t>t2AoZLAa</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>18.08.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Nouhoum A.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Friedrich-Ebert-Stadium
+ (Hildesheim)</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>10 000</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>5 186</t>
+        </is>
+      </c>
+      <c r="G148" t="n">
+        <v>0</v>
+      </c>
+      <c r="H148" t="n">
+        <v>7</v>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>E3xs5mIe</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>Hildesheim</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>6in2Eknb</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>Elversberg
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr"/>
+      <c r="N148" t="inlineStr"/>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>31%</t>
+        </is>
+      </c>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>69%</t>
+        </is>
+      </c>
+      <c r="Q148" t="n">
+        <v>6</v>
+      </c>
+      <c r="R148" t="n">
+        <v>19</v>
+      </c>
+      <c r="S148" t="n">
+        <v>1</v>
+      </c>
+      <c r="T148" t="n">
+        <v>9</v>
+      </c>
+      <c r="U148" t="n">
+        <v>2</v>
+      </c>
+      <c r="V148" t="n">
+        <v>7</v>
+      </c>
+      <c r="W148" t="n">
+        <v>14</v>
+      </c>
+      <c r="X148" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y148" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z148" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA148" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB148" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC148" t="n">
+        <v>13</v>
+      </c>
+      <c r="AD148" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE148" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF148" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG148" t="n">
+        <v>6</v>
+      </c>
+      <c r="AH148" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI148" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK148" t="inlineStr"/>
+      <c r="AL148" t="inlineStr"/>
+      <c r="AM148" t="inlineStr"/>
+      <c r="AN148" t="inlineStr"/>
+      <c r="AO148" t="n">
+        <v>80</v>
+      </c>
+      <c r="AP148" t="n">
+        <v>147</v>
+      </c>
+      <c r="AQ148" t="n">
+        <v>36</v>
+      </c>
+      <c r="AR148" t="n">
+        <v>109</v>
+      </c>
+      <c r="AS148" t="inlineStr"/>
+      <c r="AT148" t="inlineStr"/>
+      <c r="AU148" t="inlineStr">
+        <is>
+          <t>bJ0lIKrp</t>
+        </is>
+      </c>
+      <c r="AV148" t="inlineStr">
+        <is>
+          <t>hartmann marcel</t>
+        </is>
+      </c>
+      <c r="AW148" t="inlineStr">
+        <is>
+          <t>8E8qmw3d</t>
+        </is>
+      </c>
+      <c r="AX148" t="inlineStr">
+        <is>
+          <t>steffen horst</t>
+        </is>
+      </c>
+      <c r="AY148" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ148" t="n">
+        <v>593</v>
+      </c>
+      <c r="BA148" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB148" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC148" t="inlineStr"/>
+      <c r="BD148" t="inlineStr"/>
+      <c r="BE148" t="n">
+        <v>3</v>
+      </c>
+      <c r="BF148" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="1" t="inlineStr">
+        <is>
+          <t>jFMCm08e</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>18.08.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Heft F.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Jahnstadion Regensburg
+ (Regensburg)</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>15 210</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>12 581</t>
+        </is>
+      </c>
+      <c r="G149" t="n">
+        <v>1</v>
+      </c>
+      <c r="H149" t="n">
+        <v>0</v>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>UiCmEP56</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>Advancing to next round
+Regensburg</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>8Y2m6ADe</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>Bochum</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr"/>
+      <c r="N149" t="inlineStr"/>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>35%</t>
+        </is>
+      </c>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
+      <c r="Q149" t="n">
+        <v>19</v>
+      </c>
+      <c r="R149" t="n">
+        <v>16</v>
+      </c>
+      <c r="S149" t="n">
+        <v>7</v>
+      </c>
+      <c r="T149" t="n">
+        <v>7</v>
+      </c>
+      <c r="U149" t="n">
+        <v>9</v>
+      </c>
+      <c r="V149" t="n">
+        <v>7</v>
+      </c>
+      <c r="W149" t="n">
+        <v>24</v>
+      </c>
+      <c r="X149" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y149" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z149" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA149" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB149" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC149" t="n">
+        <v>21</v>
+      </c>
+      <c r="AD149" t="n">
+        <v>28</v>
+      </c>
+      <c r="AE149" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF149" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG149" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH149" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI149" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ149" t="n">
+        <v>7</v>
+      </c>
+      <c r="AK149" t="inlineStr"/>
+      <c r="AL149" t="inlineStr"/>
+      <c r="AM149" t="inlineStr"/>
+      <c r="AN149" t="inlineStr"/>
+      <c r="AO149" t="n">
+        <v>76</v>
+      </c>
+      <c r="AP149" t="n">
+        <v>150</v>
+      </c>
+      <c r="AQ149" t="n">
+        <v>22</v>
+      </c>
+      <c r="AR149" t="n">
+        <v>53</v>
+      </c>
+      <c r="AS149" t="inlineStr"/>
+      <c r="AT149" t="inlineStr"/>
+      <c r="AU149" t="inlineStr">
+        <is>
+          <t>zyLSrbZQ</t>
+        </is>
+      </c>
+      <c r="AV149" t="inlineStr">
+        <is>
+          <t>enochs joe</t>
+        </is>
+      </c>
+      <c r="AW149" t="inlineStr">
+        <is>
+          <t>8f6APkLc</t>
+        </is>
+      </c>
+      <c r="AX149" t="inlineStr">
+        <is>
+          <t>zeidler peter</t>
+        </is>
+      </c>
+      <c r="AY149" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ149" t="n">
+        <v>593</v>
+      </c>
+      <c r="BA149" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB149" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC149" t="inlineStr"/>
+      <c r="BD149" t="inlineStr"/>
+      <c r="BE149" t="n">
+        <v>3</v>
+      </c>
+      <c r="BF149" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="1" t="inlineStr">
+        <is>
+          <t>tvOIPExA</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>18.08.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Brand B.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Hardtwaldstadion
+ (Sandhausen)</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>15 414</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>9 705</t>
+        </is>
+      </c>
+      <c r="G150" t="n">
+        <v>2</v>
+      </c>
+      <c r="H150" t="n">
+        <v>3</v>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>UZxEj1R4</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>Sandhausen</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>WG9pOTse</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>FC Koln
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr"/>
+      <c r="N150" t="inlineStr"/>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>46%</t>
+        </is>
+      </c>
+      <c r="Q150" t="n">
+        <v>16</v>
+      </c>
+      <c r="R150" t="n">
+        <v>21</v>
+      </c>
+      <c r="S150" t="n">
+        <v>7</v>
+      </c>
+      <c r="T150" t="n">
+        <v>14</v>
+      </c>
+      <c r="U150" t="n">
+        <v>4</v>
+      </c>
+      <c r="V150" t="n">
+        <v>5</v>
+      </c>
+      <c r="W150" t="n">
+        <v>25</v>
+      </c>
+      <c r="X150" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y150" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z150" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA150" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB150" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC150" t="n">
+        <v>28</v>
+      </c>
+      <c r="AD150" t="n">
+        <v>42</v>
+      </c>
+      <c r="AE150" t="n">
+        <v>11</v>
+      </c>
+      <c r="AF150" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG150" t="n">
+        <v>18</v>
+      </c>
+      <c r="AH150" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI150" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ150" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK150" t="inlineStr"/>
+      <c r="AL150" t="inlineStr"/>
+      <c r="AM150" t="inlineStr"/>
+      <c r="AN150" t="inlineStr"/>
+      <c r="AO150" t="n">
+        <v>97</v>
+      </c>
+      <c r="AP150" t="n">
+        <v>97</v>
+      </c>
+      <c r="AQ150" t="n">
+        <v>41</v>
+      </c>
+      <c r="AR150" t="n">
+        <v>48</v>
+      </c>
+      <c r="AS150" t="inlineStr"/>
+      <c r="AT150" t="inlineStr"/>
+      <c r="AU150" t="inlineStr">
+        <is>
+          <t>rZtwKVAL</t>
+        </is>
+      </c>
+      <c r="AV150" t="inlineStr">
+        <is>
+          <t>ristic sreto</t>
+        </is>
+      </c>
+      <c r="AW150" t="inlineStr">
+        <is>
+          <t>4fX0k7gg</t>
+        </is>
+      </c>
+      <c r="AX150" t="inlineStr">
+        <is>
+          <t>struber gerhard</t>
+        </is>
+      </c>
+      <c r="AY150" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ150" t="n">
+        <v>593</v>
+      </c>
+      <c r="BA150" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB150" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC150" t="inlineStr"/>
+      <c r="BD150" t="inlineStr"/>
+      <c r="BE150" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF150" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="1" t="inlineStr">
+        <is>
+          <t>KSwfVwAO</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>18.08.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Lechner F.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Millerntor-Stadion
+ (Hamburg)</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>29 546</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>6 487</t>
+        </is>
+      </c>
+      <c r="G151" t="n">
+        <v>1</v>
+      </c>
+      <c r="H151" t="n">
+        <v>3</v>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>WrbkcjCd</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>Teutonia Ottensen</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>S0hPB9rA</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>Darmstadt
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr"/>
+      <c r="N151" t="inlineStr"/>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>31%</t>
+        </is>
+      </c>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>69%</t>
+        </is>
+      </c>
+      <c r="Q151" t="n">
+        <v>10</v>
+      </c>
+      <c r="R151" t="n">
+        <v>12</v>
+      </c>
+      <c r="S151" t="n">
+        <v>5</v>
+      </c>
+      <c r="T151" t="n">
+        <v>3</v>
+      </c>
+      <c r="U151" t="n">
+        <v>5</v>
+      </c>
+      <c r="V151" t="n">
+        <v>8</v>
+      </c>
+      <c r="W151" t="n">
+        <v>14</v>
+      </c>
+      <c r="X151" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y151" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z151" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC151" t="n">
+        <v>23</v>
+      </c>
+      <c r="AD151" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF151" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG151" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH151" t="n">
+        <v>12</v>
+      </c>
+      <c r="AI151" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ151" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK151" t="inlineStr"/>
+      <c r="AL151" t="inlineStr"/>
+      <c r="AM151" t="inlineStr"/>
+      <c r="AN151" t="inlineStr"/>
+      <c r="AO151" t="n">
+        <v>80</v>
+      </c>
+      <c r="AP151" t="n">
+        <v>138</v>
+      </c>
+      <c r="AQ151" t="n">
+        <v>50</v>
+      </c>
+      <c r="AR151" t="n">
+        <v>93</v>
+      </c>
+      <c r="AS151" t="inlineStr"/>
+      <c r="AT151" t="inlineStr"/>
+      <c r="AU151" t="inlineStr">
+        <is>
+          <t>lC9J1RTa</t>
+        </is>
+      </c>
+      <c r="AV151" t="inlineStr">
+        <is>
+          <t>toumi nabil</t>
+        </is>
+      </c>
+      <c r="AW151" t="inlineStr">
+        <is>
+          <t>MDhPV0RQ</t>
+        </is>
+      </c>
+      <c r="AX151" t="inlineStr">
+        <is>
+          <t>lieberknecht torsten</t>
+        </is>
+      </c>
+      <c r="AY151" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ151" t="n">
+        <v>593</v>
+      </c>
+      <c r="BA151" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB151" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC151" t="inlineStr"/>
+      <c r="BD151" t="inlineStr"/>
+      <c r="BE151" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF151" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="1" t="inlineStr">
+        <is>
+          <t>6q2yrHgU</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>18.08.2024 08:00</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Dankert B.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Ludwigspark Stadion
+ (Saarbrücken)</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>16 003</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>14 868</t>
+        </is>
+      </c>
+      <c r="G152" t="n">
+        <v>1</v>
+      </c>
+      <c r="H152" t="n">
+        <v>2</v>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>fLbhmJ5l</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>Saarbrucken</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>6FDqshzF</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>Nurnberg
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr"/>
+      <c r="N152" t="inlineStr"/>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>56%</t>
+        </is>
+      </c>
+      <c r="Q152" t="n">
+        <v>7</v>
+      </c>
+      <c r="R152" t="n">
+        <v>8</v>
+      </c>
+      <c r="S152" t="n">
+        <v>4</v>
+      </c>
+      <c r="T152" t="n">
+        <v>4</v>
+      </c>
+      <c r="U152" t="n">
+        <v>3</v>
+      </c>
+      <c r="V152" t="n">
+        <v>4</v>
+      </c>
+      <c r="W152" t="n">
+        <v>19</v>
+      </c>
+      <c r="X152" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y152" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z152" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA152" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC152" t="n">
+        <v>26</v>
+      </c>
+      <c r="AD152" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE152" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF152" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG152" t="n">
+        <v>20</v>
+      </c>
+      <c r="AH152" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI152" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ152" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK152" t="inlineStr"/>
+      <c r="AL152" t="inlineStr"/>
+      <c r="AM152" t="inlineStr"/>
+      <c r="AN152" t="inlineStr"/>
+      <c r="AO152" t="n">
+        <v>122</v>
+      </c>
+      <c r="AP152" t="n">
+        <v>143</v>
+      </c>
+      <c r="AQ152" t="n">
+        <v>80</v>
+      </c>
+      <c r="AR152" t="n">
+        <v>67</v>
+      </c>
+      <c r="AS152" t="inlineStr"/>
+      <c r="AT152" t="inlineStr"/>
+      <c r="AU152" t="inlineStr">
+        <is>
+          <t>trS1MB7T</t>
+        </is>
+      </c>
+      <c r="AV152" t="inlineStr">
+        <is>
+          <t>ziehl rudiger</t>
+        </is>
+      </c>
+      <c r="AW152" t="inlineStr">
+        <is>
+          <t>tO31cZrF</t>
+        </is>
+      </c>
+      <c r="AX152" t="inlineStr">
+        <is>
+          <t>klose miroslav</t>
+        </is>
+      </c>
+      <c r="AY152" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ152" t="n">
+        <v>593</v>
+      </c>
+      <c r="BA152" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB152" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC152" t="inlineStr"/>
+      <c r="BD152" t="inlineStr"/>
+      <c r="BE152" t="inlineStr"/>
+      <c r="BF152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="1" t="inlineStr">
+        <is>
+          <t>AiJ3kset</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>18.08.2024 08:00</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Weisbach E.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Friedrich Ludwig Jahn Sportpark
+ (Berlin)</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>19 708</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>5 504</t>
+        </is>
+      </c>
+      <c r="G153" t="n">
+        <v>1</v>
+      </c>
+      <c r="H153" t="n">
+        <v>4</v>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>UNr2EUfd</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>Viktoria Berlin</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>fTVNku3I</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>Augsburg
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr"/>
+      <c r="N153" t="inlineStr"/>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>24%</t>
+        </is>
+      </c>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>76%</t>
+        </is>
+      </c>
+      <c r="Q153" t="n">
+        <v>5</v>
+      </c>
+      <c r="R153" t="n">
+        <v>14</v>
+      </c>
+      <c r="S153" t="n">
+        <v>2</v>
+      </c>
+      <c r="T153" t="n">
+        <v>7</v>
+      </c>
+      <c r="U153" t="n">
+        <v>3</v>
+      </c>
+      <c r="V153" t="n">
+        <v>4</v>
+      </c>
+      <c r="W153" t="n">
+        <v>6</v>
+      </c>
+      <c r="X153" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y153" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z153" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA153" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC153" t="n">
+        <v>19</v>
+      </c>
+      <c r="AD153" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE153" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF153" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG153" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH153" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI153" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ153" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK153" t="inlineStr"/>
+      <c r="AL153" t="inlineStr"/>
+      <c r="AM153" t="inlineStr"/>
+      <c r="AN153" t="inlineStr"/>
+      <c r="AO153" t="n">
+        <v>71</v>
+      </c>
+      <c r="AP153" t="n">
+        <v>122</v>
+      </c>
+      <c r="AQ153" t="n">
+        <v>40</v>
+      </c>
+      <c r="AR153" t="n">
+        <v>99</v>
+      </c>
+      <c r="AS153" t="inlineStr"/>
+      <c r="AT153" t="inlineStr"/>
+      <c r="AU153" t="inlineStr">
+        <is>
+          <t>CCww5Qfo</t>
+        </is>
+      </c>
+      <c r="AV153" t="inlineStr">
+        <is>
+          <t>kutrieb dennis</t>
+        </is>
+      </c>
+      <c r="AW153" t="inlineStr">
+        <is>
+          <t>2VSFgl3c</t>
+        </is>
+      </c>
+      <c r="AX153" t="inlineStr">
+        <is>
+          <t>thorup jess</t>
+        </is>
+      </c>
+      <c r="AY153" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ153" t="n">
+        <v>593</v>
+      </c>
+      <c r="BA153" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB153" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC153" t="inlineStr"/>
+      <c r="BD153" t="inlineStr"/>
+      <c r="BE153" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF153" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="1" t="inlineStr">
+        <is>
+          <t>hzyf0b9b</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>17.08.2024 13:00</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Bacher M.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>New Tivoli
+ (Aachen)</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>31 026</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>29 555</t>
+        </is>
+      </c>
+      <c r="G154" t="n">
+        <v>2</v>
+      </c>
+      <c r="H154" t="n">
+        <v>3</v>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>j3PKcB4E</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>Alemannia Aachen</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>63WsD2ei</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>Holstein Kiel
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr"/>
+      <c r="N154" t="inlineStr"/>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>39%</t>
+        </is>
+      </c>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>61%</t>
+        </is>
+      </c>
+      <c r="Q154" t="n">
+        <v>9</v>
+      </c>
+      <c r="R154" t="n">
+        <v>8</v>
+      </c>
+      <c r="S154" t="n">
+        <v>6</v>
+      </c>
+      <c r="T154" t="n">
+        <v>5</v>
+      </c>
+      <c r="U154" t="n">
+        <v>2</v>
+      </c>
+      <c r="V154" t="n">
+        <v>3</v>
+      </c>
+      <c r="W154" t="n">
+        <v>14</v>
+      </c>
+      <c r="X154" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y154" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z154" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA154" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB154" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC154" t="n">
+        <v>22</v>
+      </c>
+      <c r="AD154" t="n">
+        <v>27</v>
+      </c>
+      <c r="AE154" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF154" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG154" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH154" t="n">
+        <v>13</v>
+      </c>
+      <c r="AI154" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ154" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK154" t="inlineStr"/>
+      <c r="AL154" t="inlineStr"/>
+      <c r="AM154" t="inlineStr"/>
+      <c r="AN154" t="inlineStr"/>
+      <c r="AO154" t="n">
+        <v>63</v>
+      </c>
+      <c r="AP154" t="n">
+        <v>122</v>
+      </c>
+      <c r="AQ154" t="n">
+        <v>41</v>
+      </c>
+      <c r="AR154" t="n">
+        <v>54</v>
+      </c>
+      <c r="AS154" t="inlineStr"/>
+      <c r="AT154" t="inlineStr"/>
+      <c r="AU154" t="inlineStr">
+        <is>
+          <t>SfKt2E6n</t>
+        </is>
+      </c>
+      <c r="AV154" t="inlineStr">
+        <is>
+          <t>backhaus heiner</t>
+        </is>
+      </c>
+      <c r="AW154" t="inlineStr">
+        <is>
+          <t>A15eUM4C</t>
+        </is>
+      </c>
+      <c r="AX154" t="inlineStr">
+        <is>
+          <t>rapp marcel</t>
+        </is>
+      </c>
+      <c r="AY154" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ154" t="n">
+        <v>593</v>
+      </c>
+      <c r="BA154" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB154" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC154" t="inlineStr"/>
+      <c r="BD154" t="inlineStr"/>
+      <c r="BE154" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF154" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="1" t="inlineStr">
+        <is>
+          <t>CpiTEcOi</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>17.08.2024 13:00</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Hartmann R.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Schüco Arena
+ (Bielefeld)</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>27 332</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>26 044</t>
+        </is>
+      </c>
+      <c r="G155" t="n">
+        <v>2</v>
+      </c>
+      <c r="H155" t="n">
+        <v>0</v>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>pp38UXK8</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>Advancing to next round
+Arminia Bielefeld</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>dfNCCCzS</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>Hannover</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr"/>
+      <c r="N155" t="inlineStr"/>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>56%</t>
+        </is>
+      </c>
+      <c r="Q155" t="n">
+        <v>12</v>
+      </c>
+      <c r="R155" t="n">
+        <v>13</v>
+      </c>
+      <c r="S155" t="n">
+        <v>6</v>
+      </c>
+      <c r="T155" t="n">
+        <v>5</v>
+      </c>
+      <c r="U155" t="n">
+        <v>2</v>
+      </c>
+      <c r="V155" t="n">
+        <v>3</v>
+      </c>
+      <c r="W155" t="n">
+        <v>22</v>
+      </c>
+      <c r="X155" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y155" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z155" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC155" t="n">
+        <v>30</v>
+      </c>
+      <c r="AD155" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE155" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF155" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG155" t="n">
+        <v>21</v>
+      </c>
+      <c r="AH155" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI155" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ155" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK155" t="inlineStr"/>
+      <c r="AL155" t="inlineStr"/>
+      <c r="AM155" t="inlineStr"/>
+      <c r="AN155" t="inlineStr"/>
+      <c r="AO155" t="n">
+        <v>104</v>
+      </c>
+      <c r="AP155" t="n">
+        <v>121</v>
+      </c>
+      <c r="AQ155" t="n">
+        <v>36</v>
+      </c>
+      <c r="AR155" t="n">
+        <v>48</v>
+      </c>
+      <c r="AS155" t="inlineStr"/>
+      <c r="AT155" t="inlineStr"/>
+      <c r="AU155" t="inlineStr">
+        <is>
+          <t>KrFXELrR</t>
+        </is>
+      </c>
+      <c r="AV155" t="inlineStr">
+        <is>
+          <t>kniat michel</t>
+        </is>
+      </c>
+      <c r="AW155" t="inlineStr">
+        <is>
+          <t>t0ZPdkUl</t>
+        </is>
+      </c>
+      <c r="AX155" t="inlineStr">
+        <is>
+          <t>leitl stefan</t>
+        </is>
+      </c>
+      <c r="AY155" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ155" t="n">
+        <v>593</v>
+      </c>
+      <c r="BA155" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB155" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC155" t="inlineStr"/>
+      <c r="BD155" t="inlineStr"/>
+      <c r="BE155" t="n">
+        <v>4</v>
+      </c>
+      <c r="BF155" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="1" t="inlineStr">
+        <is>
+          <t>8CpxDyg4</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>17.08.2024 13:00</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Burda M.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Volksparkstadion
+ (Hamburg)</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>57 274</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>50 971</t>
+        </is>
+      </c>
+      <c r="G156" t="n">
+        <v>1</v>
+      </c>
+      <c r="H156" t="n">
+        <v>4</v>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>I1Vk6k3R</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>Phonix Lubeck</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>Dortmund
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr"/>
+      <c r="N156" t="inlineStr"/>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="P156" t="inlineStr">
+        <is>
+          <t>80%</t>
+        </is>
+      </c>
+      <c r="Q156" t="n">
+        <v>7</v>
+      </c>
+      <c r="R156" t="n">
+        <v>12</v>
+      </c>
+      <c r="S156" t="n">
+        <v>1</v>
+      </c>
+      <c r="T156" t="n">
+        <v>9</v>
+      </c>
+      <c r="U156" t="n">
+        <v>6</v>
+      </c>
+      <c r="V156" t="n">
+        <v>1</v>
+      </c>
+      <c r="W156" t="n">
+        <v>8</v>
+      </c>
+      <c r="X156" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y156" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z156" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA156" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB156" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC156" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD156" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE156" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG156" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH156" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI156" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ156" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK156" t="inlineStr"/>
+      <c r="AL156" t="inlineStr"/>
+      <c r="AM156" t="inlineStr"/>
+      <c r="AN156" t="inlineStr"/>
+      <c r="AO156" t="n">
+        <v>36</v>
+      </c>
+      <c r="AP156" t="n">
+        <v>176</v>
+      </c>
+      <c r="AQ156" t="n">
+        <v>15</v>
+      </c>
+      <c r="AR156" t="n">
+        <v>67</v>
+      </c>
+      <c r="AS156" t="inlineStr"/>
+      <c r="AT156" t="inlineStr"/>
+      <c r="AU156" t="inlineStr">
+        <is>
+          <t>AgnJojCs</t>
+        </is>
+      </c>
+      <c r="AV156" t="inlineStr">
+        <is>
+          <t>adigo christiano</t>
+        </is>
+      </c>
+      <c r="AW156" t="inlineStr">
+        <is>
+          <t>IkCftsQm</t>
+        </is>
+      </c>
+      <c r="AX156" t="inlineStr">
+        <is>
+          <t>sahin nuri</t>
+        </is>
+      </c>
+      <c r="AY156" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ156" t="n">
+        <v>593</v>
+      </c>
+      <c r="BA156" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB156" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC156" t="inlineStr"/>
+      <c r="BD156" t="inlineStr"/>
+      <c r="BE156" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF156" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="1" t="inlineStr">
+        <is>
+          <t>bF2q76Mr</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>17.08.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Brych F.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>OSTALB ARENA
+ (Aalen)</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>14 500</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>10 850</t>
+        </is>
+      </c>
+      <c r="G157" t="n">
+        <v>0</v>
+      </c>
+      <c r="H157" t="n">
+        <v>2</v>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>Oh2C15j0</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>Aalen</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>0Ija0Ej9</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>Schalke
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr"/>
+      <c r="N157" t="inlineStr"/>
+      <c r="O157" t="inlineStr">
+        <is>
+          <t>32%</t>
+        </is>
+      </c>
+      <c r="P157" t="inlineStr">
+        <is>
+          <t>68%</t>
+        </is>
+      </c>
+      <c r="Q157" t="n">
+        <v>4</v>
+      </c>
+      <c r="R157" t="n">
+        <v>16</v>
+      </c>
+      <c r="S157" t="n">
+        <v>1</v>
+      </c>
+      <c r="T157" t="n">
+        <v>8</v>
+      </c>
+      <c r="U157" t="n">
+        <v>1</v>
+      </c>
+      <c r="V157" t="n">
+        <v>4</v>
+      </c>
+      <c r="W157" t="n">
+        <v>18</v>
+      </c>
+      <c r="X157" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y157" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z157" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA157" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB157" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC157" t="n">
+        <v>23</v>
+      </c>
+      <c r="AD157" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE157" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF157" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG157" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH157" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI157" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ157" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK157" t="inlineStr"/>
+      <c r="AL157" t="inlineStr"/>
+      <c r="AM157" t="inlineStr"/>
+      <c r="AN157" t="inlineStr"/>
+      <c r="AO157" t="n">
+        <v>97</v>
+      </c>
+      <c r="AP157" t="n">
+        <v>124</v>
+      </c>
+      <c r="AQ157" t="n">
+        <v>32</v>
+      </c>
+      <c r="AR157" t="n">
+        <v>45</v>
+      </c>
+      <c r="AS157" t="inlineStr"/>
+      <c r="AT157" t="inlineStr"/>
+      <c r="AU157" t="inlineStr">
+        <is>
+          <t>8bJFOfzK</t>
+        </is>
+      </c>
+      <c r="AV157" t="inlineStr">
+        <is>
+          <t>kosturkov petar</t>
+        </is>
+      </c>
+      <c r="AW157" t="inlineStr">
+        <is>
+          <t>txZLBQVC</t>
+        </is>
+      </c>
+      <c r="AX157" t="inlineStr">
+        <is>
+          <t>geraerts karel</t>
+        </is>
+      </c>
+      <c r="AY157" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ157" t="n">
+        <v>593</v>
+      </c>
+      <c r="BA157" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB157" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC157" t="inlineStr"/>
+      <c r="BD157" t="inlineStr"/>
+      <c r="BE157" t="n">
+        <v>2</v>
+      </c>
+      <c r="BF157" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="1" t="inlineStr">
+        <is>
+          <t>vyk5gjdE</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>17.08.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Benen L.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Volksstadion Greifswald
+ (Greifswald)</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>4 990</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>4 990</t>
+        </is>
+      </c>
+      <c r="G158" t="n">
+        <v>0</v>
+      </c>
+      <c r="H158" t="n">
+        <v>1</v>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>Q1yNyI5t</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>Greifswald</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>pzHW4oaE</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>Union Berlin
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr"/>
+      <c r="N158" t="inlineStr"/>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>39%</t>
+        </is>
+      </c>
+      <c r="P158" t="inlineStr">
+        <is>
+          <t>61%</t>
+        </is>
+      </c>
+      <c r="Q158" t="n">
+        <v>6</v>
+      </c>
+      <c r="R158" t="n">
+        <v>15</v>
+      </c>
+      <c r="S158" t="n">
+        <v>3</v>
+      </c>
+      <c r="T158" t="n">
+        <v>5</v>
+      </c>
+      <c r="U158" t="n">
+        <v>3</v>
+      </c>
+      <c r="V158" t="n">
+        <v>4</v>
+      </c>
+      <c r="W158" t="n">
+        <v>11</v>
+      </c>
+      <c r="X158" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y158" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z158" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC158" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD158" t="n">
+        <v>29</v>
+      </c>
+      <c r="AE158" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF158" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG158" t="n">
+        <v>6</v>
+      </c>
+      <c r="AH158" t="n">
+        <v>12</v>
+      </c>
+      <c r="AI158" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ158" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK158" t="inlineStr"/>
+      <c r="AL158" t="inlineStr"/>
+      <c r="AM158" t="inlineStr"/>
+      <c r="AN158" t="inlineStr"/>
+      <c r="AO158" t="n">
+        <v>63</v>
+      </c>
+      <c r="AP158" t="n">
+        <v>127</v>
+      </c>
+      <c r="AQ158" t="n">
+        <v>30</v>
+      </c>
+      <c r="AR158" t="n">
+        <v>72</v>
+      </c>
+      <c r="AS158" t="inlineStr"/>
+      <c r="AT158" t="inlineStr"/>
+      <c r="AU158" t="inlineStr">
+        <is>
+          <t>Wbz1kusU</t>
+        </is>
+      </c>
+      <c r="AV158" t="inlineStr">
+        <is>
+          <t>fuchs lars</t>
+        </is>
+      </c>
+      <c r="AW158" t="inlineStr">
+        <is>
+          <t>hpYJ6izc</t>
+        </is>
+      </c>
+      <c r="AX158" t="inlineStr">
+        <is>
+          <t>svensson bo</t>
+        </is>
+      </c>
+      <c r="AY158" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ158" t="n">
+        <v>593</v>
+      </c>
+      <c r="BA158" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB158" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC158" t="inlineStr"/>
+      <c r="BD158" t="inlineStr"/>
+      <c r="BE158" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF158" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="1" t="inlineStr">
+        <is>
+          <t>tbKZHNz1</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>17.08.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Braun R.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Audi Sportpark
+ (Ingolstadt)</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>15 800</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>11 655</t>
+        </is>
+      </c>
+      <c r="G159" t="n">
+        <v>1</v>
+      </c>
+      <c r="H159" t="n">
+        <v>2</v>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>ne5QkLtB</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>Ingolstadt</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>naWckLmC</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>Kaiserslautern
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr"/>
+      <c r="N159" t="inlineStr"/>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>45%</t>
+        </is>
+      </c>
+      <c r="P159" t="inlineStr">
+        <is>
+          <t>55%</t>
+        </is>
+      </c>
+      <c r="Q159" t="n">
+        <v>13</v>
+      </c>
+      <c r="R159" t="n">
+        <v>13</v>
+      </c>
+      <c r="S159" t="n">
+        <v>10</v>
+      </c>
+      <c r="T159" t="n">
+        <v>4</v>
+      </c>
+      <c r="U159" t="n">
+        <v>2</v>
+      </c>
+      <c r="V159" t="n">
+        <v>8</v>
+      </c>
+      <c r="W159" t="n">
+        <v>14</v>
+      </c>
+      <c r="X159" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y159" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z159" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA159" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC159" t="n">
+        <v>16</v>
+      </c>
+      <c r="AD159" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE159" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF159" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG159" t="n">
+        <v>19</v>
+      </c>
+      <c r="AH159" t="n">
+        <v>14</v>
+      </c>
+      <c r="AI159" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ159" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK159" t="inlineStr"/>
+      <c r="AL159" t="inlineStr"/>
+      <c r="AM159" t="inlineStr"/>
+      <c r="AN159" t="inlineStr"/>
+      <c r="AO159" t="n">
+        <v>90</v>
+      </c>
+      <c r="AP159" t="n">
+        <v>135</v>
+      </c>
+      <c r="AQ159" t="n">
+        <v>62</v>
+      </c>
+      <c r="AR159" t="n">
+        <v>53</v>
+      </c>
+      <c r="AS159" t="inlineStr"/>
+      <c r="AT159" t="inlineStr"/>
+      <c r="AU159" t="inlineStr">
+        <is>
+          <t>CWcD8UM8</t>
+        </is>
+      </c>
+      <c r="AV159" t="inlineStr">
+        <is>
+          <t>wittmann sabrina</t>
+        </is>
+      </c>
+      <c r="AW159" t="inlineStr">
+        <is>
+          <t>4bJLk19p</t>
+        </is>
+      </c>
+      <c r="AX159" t="inlineStr">
+        <is>
+          <t>anfang marcus</t>
+        </is>
+      </c>
+      <c r="AY159" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ159" t="n">
+        <v>593</v>
+      </c>
+      <c r="BA159" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB159" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC159" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD159" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE159" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF159" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="1" t="inlineStr">
+        <is>
+          <t>MZjh9ghT</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>17.08.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Dingert C.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Stadion an der Hafenstrasse
+ (Essen)</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>20 352</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>17 000</t>
+        </is>
+      </c>
+      <c r="G160" t="n">
+        <v>1</v>
+      </c>
+      <c r="H160" t="n">
+        <v>4</v>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>EB0xsr77</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>RW Essen</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>KbS1suSm</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>RB Leipzig
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr"/>
+      <c r="N160" t="inlineStr"/>
+      <c r="O160" t="inlineStr">
+        <is>
+          <t>41%</t>
+        </is>
+      </c>
+      <c r="P160" t="inlineStr">
+        <is>
+          <t>59%</t>
+        </is>
+      </c>
+      <c r="Q160" t="n">
+        <v>7</v>
+      </c>
+      <c r="R160" t="n">
+        <v>14</v>
+      </c>
+      <c r="S160" t="n">
+        <v>2</v>
+      </c>
+      <c r="T160" t="n">
+        <v>9</v>
+      </c>
+      <c r="U160" t="n">
+        <v>4</v>
+      </c>
+      <c r="V160" t="n">
+        <v>5</v>
+      </c>
+      <c r="W160" t="n">
+        <v>10</v>
+      </c>
+      <c r="X160" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y160" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z160" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA160" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB160" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC160" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD160" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE160" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF160" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG160" t="n">
+        <v>9</v>
+      </c>
+      <c r="AH160" t="n">
+        <v>9</v>
+      </c>
+      <c r="AI160" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ160" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK160" t="inlineStr"/>
+      <c r="AL160" t="inlineStr"/>
+      <c r="AM160" t="inlineStr"/>
+      <c r="AN160" t="inlineStr"/>
+      <c r="AO160" t="n">
+        <v>72</v>
+      </c>
+      <c r="AP160" t="n">
+        <v>127</v>
+      </c>
+      <c r="AQ160" t="n">
+        <v>20</v>
+      </c>
+      <c r="AR160" t="n">
+        <v>50</v>
+      </c>
+      <c r="AS160" t="inlineStr"/>
+      <c r="AT160" t="inlineStr"/>
+      <c r="AU160" t="inlineStr">
+        <is>
+          <t>0KMe4S4D</t>
+        </is>
+      </c>
+      <c r="AV160" t="inlineStr">
+        <is>
+          <t>dabrowski christoph</t>
+        </is>
+      </c>
+      <c r="AW160" t="inlineStr">
+        <is>
+          <t>pfoInmcq</t>
+        </is>
+      </c>
+      <c r="AX160" t="inlineStr">
+        <is>
+          <t>rose marko</t>
+        </is>
+      </c>
+      <c r="AY160" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ160" t="n">
+        <v>593</v>
+      </c>
+      <c r="BA160" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB160" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC160" t="inlineStr"/>
+      <c r="BD160" t="inlineStr"/>
+      <c r="BE160" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF160" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="1" t="inlineStr">
+        <is>
+          <t>f1nnRRDE</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>17.08.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Reichel T.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Stadion an der Bremer Brück
+ (Osnabrück)</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>16 667</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>15 500</t>
+        </is>
+      </c>
+      <c r="G161" t="n">
+        <v>0</v>
+      </c>
+      <c r="H161" t="n">
+        <v>4</v>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>88Xgj1Y5</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>VfL Osnabruck</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>Freiburg
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr"/>
+      <c r="N161" t="inlineStr"/>
+      <c r="O161" t="inlineStr">
+        <is>
+          <t>49%</t>
+        </is>
+      </c>
+      <c r="P161" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="Q161" t="n">
+        <v>8</v>
+      </c>
+      <c r="R161" t="n">
+        <v>9</v>
+      </c>
+      <c r="S161" t="n">
+        <v>1</v>
+      </c>
+      <c r="T161" t="n">
+        <v>6</v>
+      </c>
+      <c r="U161" t="n">
+        <v>4</v>
+      </c>
+      <c r="V161" t="n">
+        <v>3</v>
+      </c>
+      <c r="W161" t="n">
+        <v>10</v>
+      </c>
+      <c r="X161" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y161" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z161" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB161" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC161" t="n">
+        <v>18</v>
+      </c>
+      <c r="AD161" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE161" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF161" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG161" t="n">
+        <v>6</v>
+      </c>
+      <c r="AH161" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI161" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK161" t="inlineStr"/>
+      <c r="AL161" t="inlineStr"/>
+      <c r="AM161" t="inlineStr"/>
+      <c r="AN161" t="inlineStr"/>
+      <c r="AO161" t="n">
+        <v>83</v>
+      </c>
+      <c r="AP161" t="n">
+        <v>100</v>
+      </c>
+      <c r="AQ161" t="n">
+        <v>57</v>
+      </c>
+      <c r="AR161" t="n">
+        <v>42</v>
+      </c>
+      <c r="AS161" t="inlineStr"/>
+      <c r="AT161" t="inlineStr"/>
+      <c r="AU161" t="inlineStr">
+        <is>
+          <t>lxrr7DgN</t>
+        </is>
+      </c>
+      <c r="AV161" t="inlineStr">
+        <is>
+          <t>koschinat uwe</t>
+        </is>
+      </c>
+      <c r="AW161" t="inlineStr">
+        <is>
+          <t>YZPE6Sx7</t>
+        </is>
+      </c>
+      <c r="AX161" t="inlineStr">
+        <is>
+          <t>schuster julian</t>
+        </is>
+      </c>
+      <c r="AY161" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ161" t="n">
+        <v>593</v>
+      </c>
+      <c r="BA161" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB161" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC161" t="inlineStr"/>
+      <c r="BD161" t="inlineStr"/>
+      <c r="BE161" t="n">
+        <v>3</v>
+      </c>
+      <c r="BF161" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="1" t="inlineStr">
+        <is>
+          <t>8QPARz8c</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>17.08.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Michel F.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>MS Technologie Arena
+ (Villingen-Schwenningen)</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>8 000</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>6 800</t>
+        </is>
+      </c>
+      <c r="G162" t="n">
+        <v>0</v>
+      </c>
+      <c r="H162" t="n">
+        <v>4</v>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>lKLJUxeT</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>Villingen</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>KWixEVWi</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>Heidenheim
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr"/>
+      <c r="N162" t="inlineStr"/>
+      <c r="O162" t="inlineStr">
+        <is>
+          <t>33%</t>
+        </is>
+      </c>
+      <c r="P162" t="inlineStr">
+        <is>
+          <t>67%</t>
+        </is>
+      </c>
+      <c r="Q162" t="n">
+        <v>6</v>
+      </c>
+      <c r="R162" t="n">
+        <v>18</v>
+      </c>
+      <c r="S162" t="n">
+        <v>1</v>
+      </c>
+      <c r="T162" t="n">
+        <v>9</v>
+      </c>
+      <c r="U162" t="n">
+        <v>2</v>
+      </c>
+      <c r="V162" t="n">
+        <v>7</v>
+      </c>
+      <c r="W162" t="n">
+        <v>12</v>
+      </c>
+      <c r="X162" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y162" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z162" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA162" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB162" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC162" t="n">
+        <v>23</v>
+      </c>
+      <c r="AD162" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE162" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF162" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG162" t="n">
+        <v>7</v>
+      </c>
+      <c r="AH162" t="n">
+        <v>9</v>
+      </c>
+      <c r="AI162" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK162" t="inlineStr"/>
+      <c r="AL162" t="inlineStr"/>
+      <c r="AM162" t="inlineStr"/>
+      <c r="AN162" t="inlineStr"/>
+      <c r="AO162" t="n">
+        <v>70</v>
+      </c>
+      <c r="AP162" t="n">
+        <v>120</v>
+      </c>
+      <c r="AQ162" t="n">
+        <v>35</v>
+      </c>
+      <c r="AR162" t="n">
+        <v>74</v>
+      </c>
+      <c r="AS162" t="inlineStr"/>
+      <c r="AT162" t="inlineStr"/>
+      <c r="AU162" t="inlineStr">
+        <is>
+          <t>lli2SfLl</t>
+        </is>
+      </c>
+      <c r="AV162" t="inlineStr">
+        <is>
+          <t>klotz mario</t>
+        </is>
+      </c>
+      <c r="AW162" t="inlineStr">
+        <is>
+          <t>4ljanukM</t>
+        </is>
+      </c>
+      <c r="AX162" t="inlineStr">
+        <is>
+          <t>schmidt frank</t>
+        </is>
+      </c>
+      <c r="AY162" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ162" t="n">
+        <v>593</v>
+      </c>
+      <c r="BA162" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB162" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC162" t="inlineStr"/>
+      <c r="BD162" t="inlineStr"/>
+      <c r="BE162" t="n">
+        <v>3</v>
+      </c>
+      <c r="BF162" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="1" t="inlineStr">
+        <is>
+          <t>0K2qBFNG</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>17.08.2024 08:00</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Badstubner F.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Erzgebirgsstadion
+ (Aue)</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>16 485</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>14 811</t>
+        </is>
+      </c>
+      <c r="G163" t="n">
+        <v>1</v>
+      </c>
+      <c r="H163" t="n">
+        <v>3</v>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>vsXIDreP</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>Aue</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>88HSzjDr</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>B. Monchengladbach
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr"/>
+      <c r="N163" t="inlineStr"/>
+      <c r="O163" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
+      </c>
+      <c r="P163" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="Q163" t="n">
+        <v>8</v>
+      </c>
+      <c r="R163" t="n">
+        <v>21</v>
+      </c>
+      <c r="S163" t="n">
+        <v>3</v>
+      </c>
+      <c r="T163" t="n">
+        <v>11</v>
+      </c>
+      <c r="U163" t="n">
+        <v>4</v>
+      </c>
+      <c r="V163" t="n">
+        <v>8</v>
+      </c>
+      <c r="W163" t="n">
+        <v>11</v>
+      </c>
+      <c r="X163" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y163" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z163" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA163" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB163" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC163" t="n">
+        <v>20</v>
+      </c>
+      <c r="AD163" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE163" t="n">
+        <v>8</v>
+      </c>
+      <c r="AF163" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG163" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH163" t="n">
+        <v>9</v>
+      </c>
+      <c r="AI163" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK163" t="inlineStr"/>
+      <c r="AL163" t="inlineStr"/>
+      <c r="AM163" t="inlineStr"/>
+      <c r="AN163" t="inlineStr"/>
+      <c r="AO163" t="n">
+        <v>119</v>
+      </c>
+      <c r="AP163" t="n">
+        <v>98</v>
+      </c>
+      <c r="AQ163" t="n">
+        <v>57</v>
+      </c>
+      <c r="AR163" t="n">
+        <v>50</v>
+      </c>
+      <c r="AS163" t="inlineStr"/>
+      <c r="AT163" t="inlineStr"/>
+      <c r="AU163" t="inlineStr">
+        <is>
+          <t>rPfNaCdg</t>
+        </is>
+      </c>
+      <c r="AV163" t="inlineStr">
+        <is>
+          <t>dotchev pavel</t>
+        </is>
+      </c>
+      <c r="AW163" t="inlineStr">
+        <is>
+          <t>M5BRZDsC</t>
+        </is>
+      </c>
+      <c r="AX163" t="inlineStr">
+        <is>
+          <t>seoane gerardo</t>
+        </is>
+      </c>
+      <c r="AY163" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ163" t="n">
+        <v>593</v>
+      </c>
+      <c r="BA163" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB163" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC163" t="inlineStr"/>
+      <c r="BD163" t="inlineStr"/>
+      <c r="BE163" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF163" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="1" t="inlineStr">
+        <is>
+          <t>Kj4sifWp</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>17.08.2024 08:00</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Prigan F.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Bruchwegstadion
+ (Mainz)</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>7 134</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>4 235</t>
+        </is>
+      </c>
+      <c r="G164" t="n">
+        <v>0</v>
+      </c>
+      <c r="H164" t="n">
+        <v>2</v>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>WzEYqEyg</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>Schott Mainz</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>CCQGbik8</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>Greuther Furth
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr"/>
+      <c r="N164" t="inlineStr"/>
+      <c r="O164" t="inlineStr">
+        <is>
+          <t>35%</t>
+        </is>
+      </c>
+      <c r="P164" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
+      <c r="Q164" t="n">
+        <v>4</v>
+      </c>
+      <c r="R164" t="n">
+        <v>13</v>
+      </c>
+      <c r="S164" t="n">
+        <v>0</v>
+      </c>
+      <c r="T164" t="n">
+        <v>6</v>
+      </c>
+      <c r="U164" t="n">
+        <v>4</v>
+      </c>
+      <c r="V164" t="n">
+        <v>5</v>
+      </c>
+      <c r="W164" t="n">
+        <v>3</v>
+      </c>
+      <c r="X164" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y164" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z164" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB164" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC164" t="n">
+        <v>17</v>
+      </c>
+      <c r="AD164" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE164" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG164" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH164" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI164" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK164" t="inlineStr"/>
+      <c r="AL164" t="inlineStr"/>
+      <c r="AM164" t="inlineStr"/>
+      <c r="AN164" t="inlineStr"/>
+      <c r="AO164" t="n">
+        <v>57</v>
+      </c>
+      <c r="AP164" t="n">
+        <v>64</v>
+      </c>
+      <c r="AQ164" t="n">
+        <v>22</v>
+      </c>
+      <c r="AR164" t="n">
+        <v>29</v>
+      </c>
+      <c r="AS164" t="inlineStr"/>
+      <c r="AT164" t="inlineStr"/>
+      <c r="AU164" t="inlineStr">
+        <is>
+          <t>pvucOaW7</t>
+        </is>
+      </c>
+      <c r="AV164" t="inlineStr">
+        <is>
+          <t>horozovic samuel</t>
+        </is>
+      </c>
+      <c r="AW164" t="inlineStr">
+        <is>
+          <t>8E86CPuD</t>
+        </is>
+      </c>
+      <c r="AX164" t="inlineStr">
+        <is>
+          <t>zorniger alexander</t>
+        </is>
+      </c>
+      <c r="AY164" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ164" t="n">
+        <v>593</v>
+      </c>
+      <c r="BA164" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB164" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC164" t="inlineStr"/>
+      <c r="BD164" t="inlineStr"/>
+      <c r="BE164" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF164" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="1" t="inlineStr">
+        <is>
+          <t>lONsG15D</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>16.08.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Jablonski S.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Donaustadion
+ (Ulm)</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>19 500</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>17 400</t>
+        </is>
+      </c>
+      <c r="G165" t="n">
+        <v>0</v>
+      </c>
+      <c r="H165" t="n">
+        <v>4</v>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>tbC3EcQn</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>Ulm</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>nVp0wiqd</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>Bayern Munich
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr"/>
+      <c r="N165" t="inlineStr"/>
+      <c r="O165" t="inlineStr">
+        <is>
+          <t>27%</t>
+        </is>
+      </c>
+      <c r="P165" t="inlineStr">
+        <is>
+          <t>73%</t>
+        </is>
+      </c>
+      <c r="Q165" t="n">
+        <v>5</v>
+      </c>
+      <c r="R165" t="n">
+        <v>14</v>
+      </c>
+      <c r="S165" t="n">
+        <v>0</v>
+      </c>
+      <c r="T165" t="n">
+        <v>5</v>
+      </c>
+      <c r="U165" t="n">
+        <v>4</v>
+      </c>
+      <c r="V165" t="n">
+        <v>3</v>
+      </c>
+      <c r="W165" t="n">
+        <v>17</v>
+      </c>
+      <c r="X165" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y165" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z165" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA165" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB165" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC165" t="n">
+        <v>26</v>
+      </c>
+      <c r="AD165" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE165" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF165" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG165" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH165" t="n">
+        <v>11</v>
+      </c>
+      <c r="AI165" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ165" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK165" t="inlineStr"/>
+      <c r="AL165" t="inlineStr"/>
+      <c r="AM165" t="inlineStr"/>
+      <c r="AN165" t="inlineStr"/>
+      <c r="AO165" t="n">
+        <v>70</v>
+      </c>
+      <c r="AP165" t="n">
+        <v>190</v>
+      </c>
+      <c r="AQ165" t="n">
+        <v>26</v>
+      </c>
+      <c r="AR165" t="n">
+        <v>71</v>
+      </c>
+      <c r="AS165" t="inlineStr"/>
+      <c r="AT165" t="inlineStr"/>
+      <c r="AU165" t="inlineStr">
+        <is>
+          <t>QevvB2nf</t>
+        </is>
+      </c>
+      <c r="AV165" t="inlineStr">
+        <is>
+          <t>worle thomas</t>
+        </is>
+      </c>
+      <c r="AW165" t="inlineStr">
+        <is>
+          <t>K6A2elS9</t>
+        </is>
+      </c>
+      <c r="AX165" t="inlineStr">
+        <is>
+          <t>kompany vincent</t>
+        </is>
+      </c>
+      <c r="AY165" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ165" t="n">
+        <v>593</v>
+      </c>
+      <c r="BA165" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB165" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC165" t="inlineStr"/>
+      <c r="BD165" t="inlineStr"/>
+      <c r="BE165" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF165" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="1" t="inlineStr">
+        <is>
+          <t>pWQQJq6l</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>16.08.2024 13:00</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Siebert D.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Leuna Chemie Stadion
+ (Halle)</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>15 057</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>14 000</t>
+        </is>
+      </c>
+      <c r="G166" t="n">
+        <v>2</v>
+      </c>
+      <c r="H166" t="n">
+        <v>3</v>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>boX3cIQa</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>Hallescher</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>St. Pauli
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr"/>
+      <c r="N166" t="inlineStr"/>
+      <c r="O166" t="inlineStr">
+        <is>
+          <t>34%</t>
+        </is>
+      </c>
+      <c r="P166" t="inlineStr">
+        <is>
+          <t>66%</t>
+        </is>
+      </c>
+      <c r="Q166" t="n">
+        <v>9</v>
+      </c>
+      <c r="R166" t="n">
+        <v>14</v>
+      </c>
+      <c r="S166" t="n">
+        <v>3</v>
+      </c>
+      <c r="T166" t="n">
+        <v>8</v>
+      </c>
+      <c r="U166" t="n">
+        <v>3</v>
+      </c>
+      <c r="V166" t="n">
+        <v>4</v>
+      </c>
+      <c r="W166" t="n">
+        <v>18</v>
+      </c>
+      <c r="X166" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y166" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z166" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB166" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC166" t="n">
+        <v>39</v>
+      </c>
+      <c r="AD166" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE166" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF166" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG166" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH166" t="n">
+        <v>12</v>
+      </c>
+      <c r="AI166" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ166" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK166" t="inlineStr"/>
+      <c r="AL166" t="inlineStr"/>
+      <c r="AM166" t="inlineStr"/>
+      <c r="AN166" t="inlineStr"/>
+      <c r="AO166" t="n">
+        <v>119</v>
+      </c>
+      <c r="AP166" t="n">
+        <v>144</v>
+      </c>
+      <c r="AQ166" t="n">
+        <v>69</v>
+      </c>
+      <c r="AR166" t="n">
+        <v>100</v>
+      </c>
+      <c r="AS166" t="inlineStr"/>
+      <c r="AT166" t="inlineStr"/>
+      <c r="AU166" t="inlineStr">
+        <is>
+          <t>02hM7hzd</t>
+        </is>
+      </c>
+      <c r="AV166" t="inlineStr">
+        <is>
+          <t>zimmermann mark</t>
+        </is>
+      </c>
+      <c r="AW166" t="inlineStr">
+        <is>
+          <t>0jdIgO6t</t>
+        </is>
+      </c>
+      <c r="AX166" t="inlineStr">
+        <is>
+          <t>blessin alexander</t>
+        </is>
+      </c>
+      <c r="AY166" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ166" t="n">
+        <v>593</v>
+      </c>
+      <c r="BA166" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB166" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC166" t="inlineStr"/>
+      <c r="BD166" t="inlineStr"/>
+      <c r="BE166" t="n">
+        <v>3</v>
+      </c>
+      <c r="BF166" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="1" t="inlineStr">
+        <is>
+          <t>hIsO3XFj</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>16.08.2024 13:00</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Hempel R.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>BRITA-Arena
+ (Wiesbaden)</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>12 566</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>12 500</t>
+        </is>
+      </c>
+      <c r="G167" t="n">
+        <v>1</v>
+      </c>
+      <c r="H167" t="n">
+        <v>3</v>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>ObxFt3lm</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>Wehen</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>EuakNmc1</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>Mainz
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr"/>
+      <c r="N167" t="inlineStr"/>
+      <c r="O167" t="inlineStr">
+        <is>
+          <t>35%</t>
+        </is>
+      </c>
+      <c r="P167" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
+      <c r="Q167" t="n">
+        <v>8</v>
+      </c>
+      <c r="R167" t="n">
+        <v>19</v>
+      </c>
+      <c r="S167" t="n">
+        <v>4</v>
+      </c>
+      <c r="T167" t="n">
+        <v>6</v>
+      </c>
+      <c r="U167" t="n">
+        <v>3</v>
+      </c>
+      <c r="V167" t="n">
+        <v>5</v>
+      </c>
+      <c r="W167" t="n">
+        <v>23</v>
+      </c>
+      <c r="X167" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y167" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z167" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA167" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB167" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC167" t="n">
+        <v>40</v>
+      </c>
+      <c r="AD167" t="n">
+        <v>37</v>
+      </c>
+      <c r="AE167" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF167" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG167" t="n">
+        <v>19</v>
+      </c>
+      <c r="AH167" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI167" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ167" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK167" t="inlineStr"/>
+      <c r="AL167" t="inlineStr"/>
+      <c r="AM167" t="inlineStr"/>
+      <c r="AN167" t="inlineStr"/>
+      <c r="AO167" t="n">
+        <v>133</v>
+      </c>
+      <c r="AP167" t="n">
+        <v>112</v>
+      </c>
+      <c r="AQ167" t="n">
+        <v>78</v>
+      </c>
+      <c r="AR167" t="n">
+        <v>140</v>
+      </c>
+      <c r="AS167" t="inlineStr"/>
+      <c r="AT167" t="inlineStr"/>
+      <c r="AU167" t="inlineStr">
+        <is>
+          <t>QTAUlvUP</t>
+        </is>
+      </c>
+      <c r="AV167" t="inlineStr">
+        <is>
+          <t>doring nils</t>
+        </is>
+      </c>
+      <c r="AW167" t="inlineStr">
+        <is>
+          <t>vZA6VYpf</t>
+        </is>
+      </c>
+      <c r="AX167" t="inlineStr">
+        <is>
+          <t>henriksen bo</t>
+        </is>
+      </c>
+      <c r="AY167" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ167" t="n">
+        <v>593</v>
+      </c>
+      <c r="BA167" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB167" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC167" t="inlineStr"/>
+      <c r="BD167" t="inlineStr"/>
+      <c r="BE167" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF167" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="1" t="inlineStr">
+        <is>
+          <t>EF8gXauC</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>16.08.2024 13:00</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Petersen M.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Flyeralarm Arena
+ (Wurzburger)</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>13 090</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>12 000</t>
+        </is>
+      </c>
+      <c r="G168" t="n">
+        <v>2</v>
+      </c>
+      <c r="H168" t="n">
+        <v>3</v>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>nVM1YUFj</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>Wurzburger Kickers</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>hQAtP9Sl</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>Hoffenheim
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M168" t="inlineStr"/>
+      <c r="N168" t="inlineStr"/>
+      <c r="O168" t="inlineStr">
+        <is>
+          <t>31%</t>
+        </is>
+      </c>
+      <c r="P168" t="inlineStr">
+        <is>
+          <t>69%</t>
+        </is>
+      </c>
+      <c r="Q168" t="n">
+        <v>9</v>
+      </c>
+      <c r="R168" t="n">
+        <v>16</v>
+      </c>
+      <c r="S168" t="n">
+        <v>4</v>
+      </c>
+      <c r="T168" t="n">
+        <v>8</v>
+      </c>
+      <c r="U168" t="n">
+        <v>4</v>
+      </c>
+      <c r="V168" t="n">
+        <v>5</v>
+      </c>
+      <c r="W168" t="n">
+        <v>15</v>
+      </c>
+      <c r="X168" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y168" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z168" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA168" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB168" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC168" t="n">
+        <v>29</v>
+      </c>
+      <c r="AD168" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE168" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF168" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG168" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH168" t="n">
+        <v>13</v>
+      </c>
+      <c r="AI168" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ168" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK168" t="inlineStr"/>
+      <c r="AL168" t="inlineStr"/>
+      <c r="AM168" t="inlineStr"/>
+      <c r="AN168" t="inlineStr"/>
+      <c r="AO168" t="n">
+        <v>122</v>
+      </c>
+      <c r="AP168" t="n">
+        <v>159</v>
+      </c>
+      <c r="AQ168" t="n">
+        <v>58</v>
+      </c>
+      <c r="AR168" t="n">
+        <v>102</v>
+      </c>
+      <c r="AS168" t="inlineStr"/>
+      <c r="AT168" t="inlineStr"/>
+      <c r="AU168" t="inlineStr">
+        <is>
+          <t>lEwgk7go</t>
+        </is>
+      </c>
+      <c r="AV168" t="inlineStr">
+        <is>
+          <t>zschiesche markus</t>
+        </is>
+      </c>
+      <c r="AW168" t="inlineStr">
+        <is>
+          <t>KUx4Q7x1</t>
+        </is>
+      </c>
+      <c r="AX168" t="inlineStr">
+        <is>
+          <t>matarazzo pellegrino</t>
+        </is>
+      </c>
+      <c r="AY168" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ168" t="n">
+        <v>593</v>
+      </c>
+      <c r="BA168" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB168" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC168" t="inlineStr"/>
+      <c r="BD168" t="inlineStr"/>
+      <c r="BE168" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF168" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="1" t="inlineStr">
+        <is>
+          <t>fcxqFy2l</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>17.08.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Stieler T.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>BayArena
+ (Leverkusen)</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>30 210</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>30 210</t>
+        </is>
+      </c>
+      <c r="G169" t="n">
+        <v>3</v>
+      </c>
+      <c r="H169" t="n">
+        <v>2</v>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>4jcj2zMd</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>Winner
+Bayer Leverkusen</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>Stuttgart</t>
+        </is>
+      </c>
+      <c r="M169" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="N169" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="O169" t="inlineStr">
+        <is>
+          <t>38%</t>
+        </is>
+      </c>
+      <c r="P169" t="inlineStr">
+        <is>
+          <t>62%</t>
+        </is>
+      </c>
+      <c r="Q169" t="n">
+        <v>12</v>
+      </c>
+      <c r="R169" t="n">
+        <v>11</v>
+      </c>
+      <c r="S169" t="n">
+        <v>4</v>
+      </c>
+      <c r="T169" t="n">
+        <v>4</v>
+      </c>
+      <c r="U169" t="n">
+        <v>8</v>
+      </c>
+      <c r="V169" t="n">
+        <v>7</v>
+      </c>
+      <c r="W169" t="inlineStr"/>
+      <c r="X169" t="inlineStr"/>
+      <c r="Y169" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z169" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA169" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB169" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC169" t="inlineStr"/>
+      <c r="AD169" t="inlineStr"/>
+      <c r="AE169" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF169" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG169" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH169" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI169" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ169" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK169" t="n">
+        <v>295</v>
+      </c>
+      <c r="AL169" t="n">
+        <v>578</v>
+      </c>
+      <c r="AM169" t="n">
+        <v>249</v>
+      </c>
+      <c r="AN169" t="n">
+        <v>547</v>
+      </c>
+      <c r="AO169" t="n">
+        <v>74</v>
+      </c>
+      <c r="AP169" t="n">
+        <v>102</v>
+      </c>
+      <c r="AQ169" t="n">
+        <v>63</v>
+      </c>
+      <c r="AR169" t="n">
+        <v>62</v>
+      </c>
+      <c r="AS169" t="n">
+        <v>90</v>
+      </c>
+      <c r="AT169" t="n">
+        <v>93</v>
+      </c>
+      <c r="AU169" t="inlineStr">
+        <is>
+          <t>hAcTWKKN</t>
+        </is>
+      </c>
+      <c r="AV169" t="inlineStr">
+        <is>
+          <t>alonso xabi</t>
+        </is>
+      </c>
+      <c r="AW169" t="inlineStr">
+        <is>
+          <t>GzfvcwRj</t>
+        </is>
+      </c>
+      <c r="AX169" t="inlineStr">
+        <is>
+          <t>hoeness sebastian</t>
+        </is>
+      </c>
+      <c r="AY169" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ169" t="n">
+        <v>594</v>
+      </c>
+      <c r="BA169" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB169" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="BC169" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD169" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE169" t="inlineStr"/>
+      <c r="BF169" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="1" t="inlineStr">
+        <is>
+          <t>pAXo2Kvn</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>19.08.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Exner F.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Eintracht-Stadion
+ (Braunschweig)</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>23 325</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr"/>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>QqLCC3il</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>Braunschweig</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>Eintracht Frankfurt
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M170" t="inlineStr"/>
+      <c r="N170" t="inlineStr"/>
+      <c r="O170" t="inlineStr">
+        <is>
+          <t>41%</t>
+        </is>
+      </c>
+      <c r="P170" t="inlineStr">
+        <is>
+          <t>59%</t>
+        </is>
+      </c>
+      <c r="Q170" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R170" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="S170" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T170" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="U170" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V170" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W170" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="X170" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y170" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Z170" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB170" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC170" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AD170" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AE170" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AF170" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG170" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AH170" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AI170" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AJ170" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AK170" t="inlineStr"/>
+      <c r="AL170" t="inlineStr"/>
+      <c r="AM170" t="inlineStr"/>
+      <c r="AN170" t="inlineStr"/>
+      <c r="AO170" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="AP170" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="AQ170" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="AR170" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="AS170" t="inlineStr"/>
+      <c r="AT170" t="inlineStr"/>
+      <c r="AU170" t="inlineStr">
+        <is>
+          <t>SQrxFAMl</t>
+        </is>
+      </c>
+      <c r="AV170" t="inlineStr">
+        <is>
+          <t>scherning daniel</t>
+        </is>
+      </c>
+      <c r="AW170" t="inlineStr">
+        <is>
+          <t>UgdQz0fK</t>
+        </is>
+      </c>
+      <c r="AX170" t="inlineStr">
+        <is>
+          <t>toppmoller dino</t>
+        </is>
+      </c>
+      <c r="AY170" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ170" t="n">
+        <v>593</v>
+      </c>
+      <c r="BA170" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB170" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC170" t="inlineStr"/>
+      <c r="BD170" t="inlineStr"/>
+      <c r="BE170" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF170" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="1" t="inlineStr">
+        <is>
+          <t>06NAdG8N</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>19.08.2024 13:00</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Osmers H.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Stadion der Freundschaft
+ (Cottbus)</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>22 450</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr"/>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>6g44VD52</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>Cottbus</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Ig1f1fy3</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>Werder Bremen
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M171" t="inlineStr"/>
+      <c r="N171" t="inlineStr"/>
+      <c r="O171" t="inlineStr">
+        <is>
+          <t>39%</t>
+        </is>
+      </c>
+      <c r="P171" t="inlineStr">
+        <is>
+          <t>61%</t>
+        </is>
+      </c>
+      <c r="Q171" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="R171" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="S171" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T171" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="U171" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V171" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W171" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="X171" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="Y171" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Z171" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AA171" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB171" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC171" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AD171" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="AE171" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AF171" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AG171" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AH171" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AI171" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AJ171" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AK171" t="inlineStr"/>
+      <c r="AL171" t="inlineStr"/>
+      <c r="AM171" t="inlineStr"/>
+      <c r="AN171" t="inlineStr"/>
+      <c r="AO171" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="AP171" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="AQ171" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="AR171" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="AS171" t="inlineStr"/>
+      <c r="AT171" t="inlineStr"/>
+      <c r="AU171" t="inlineStr">
+        <is>
+          <t>tnTvQd1l</t>
+        </is>
+      </c>
+      <c r="AV171" t="inlineStr">
+        <is>
+          <t>wollitz claus dieter</t>
+        </is>
+      </c>
+      <c r="AW171" t="inlineStr">
+        <is>
+          <t>4fuCGs9P</t>
+        </is>
+      </c>
+      <c r="AX171" t="inlineStr">
+        <is>
+          <t>werner ole</t>
+        </is>
+      </c>
+      <c r="AY171" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ171" t="n">
+        <v>593</v>
+      </c>
+      <c r="BA171" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB171" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC171" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BD171" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE171" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF171" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="1" t="inlineStr">
+        <is>
+          <t>Sff03OL7</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>19.08.2024 13:00</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Alt P.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Bieberer Berg Stadion
+ (Offenbach am Main)</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>20 500</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr"/>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>YJURlaIO</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>Advancing to next round
+Offenbach</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>YFuz2RLm</t>
+        </is>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>Magdeburg</t>
+        </is>
+      </c>
+      <c r="M172" t="inlineStr"/>
+      <c r="N172" t="inlineStr"/>
+      <c r="O172" t="inlineStr">
+        <is>
+          <t>26%</t>
+        </is>
+      </c>
+      <c r="P172" t="inlineStr">
+        <is>
+          <t>74%</t>
+        </is>
+      </c>
+      <c r="Q172" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="R172" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="S172" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T172" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="U172" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V172" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W172" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="X172" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="Y172" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Z172" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA172" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB172" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC172" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AD172" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AE172" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AF172" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AG172" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AH172" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AI172" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AJ172" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AK172" t="inlineStr"/>
+      <c r="AL172" t="inlineStr"/>
+      <c r="AM172" t="inlineStr"/>
+      <c r="AN172" t="inlineStr"/>
+      <c r="AO172" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="AP172" t="inlineStr">
+        <is>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="AQ172" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AR172" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="AS172" t="inlineStr"/>
+      <c r="AT172" t="inlineStr"/>
+      <c r="AU172" t="inlineStr">
+        <is>
+          <t>GWkh67yH</t>
+        </is>
+      </c>
+      <c r="AV172" t="inlineStr">
+        <is>
+          <t>neidhart christian</t>
+        </is>
+      </c>
+      <c r="AW172" t="inlineStr">
+        <is>
+          <t>IgZoGKFn</t>
+        </is>
+      </c>
+      <c r="AX172" t="inlineStr">
+        <is>
+          <t>titz christian</t>
+        </is>
+      </c>
+      <c r="AY172" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ172" t="n">
+        <v>593</v>
+      </c>
+      <c r="BA172" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB172" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC172" t="inlineStr"/>
+      <c r="BD172" t="inlineStr"/>
+      <c r="BE172" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="BF172" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="1" t="inlineStr">
+        <is>
+          <t>EkP2bxvB</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>19.08.2024 13:00</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Storks S.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Stadion Oberwerth
+ (Koblenz)</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>9 500</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr"/>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>p8wBsqZt</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>TuS Koblenz</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>nwkTahLL</t>
+        </is>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>Wolfsburg
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M173" t="inlineStr"/>
+      <c r="N173" t="inlineStr"/>
+      <c r="O173" t="inlineStr">
+        <is>
+          <t>24%</t>
+        </is>
+      </c>
+      <c r="P173" t="inlineStr">
+        <is>
+          <t>76%</t>
+        </is>
+      </c>
+      <c r="Q173" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="R173" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="S173" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T173" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U173" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V173" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="W173" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="X173" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="Y173" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Z173" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA173" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB173" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC173" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AD173" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="AE173" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AF173" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AG173" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AH173" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AI173" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AJ173" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AK173" t="inlineStr"/>
+      <c r="AL173" t="inlineStr"/>
+      <c r="AM173" t="inlineStr"/>
+      <c r="AN173" t="inlineStr"/>
+      <c r="AO173" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="AP173" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="AQ173" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="AR173" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="AS173" t="inlineStr"/>
+      <c r="AT173" t="inlineStr"/>
+      <c r="AU173" t="inlineStr">
+        <is>
+          <t>rFNN7oyi</t>
+        </is>
+      </c>
+      <c r="AV173" t="inlineStr">
+        <is>
+          <t>stahl michael</t>
+        </is>
+      </c>
+      <c r="AW173" t="inlineStr">
+        <is>
+          <t>f3ddUIXs</t>
+        </is>
+      </c>
+      <c r="AX173" t="inlineStr">
+        <is>
+          <t>hasenhuttl ralph</t>
+        </is>
+      </c>
+      <c r="AY173" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ173" t="n">
+        <v>593</v>
+      </c>
+      <c r="BA173" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB173" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC173" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BD173" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE173" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF173" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/germany/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
+++ b/data/germany/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BF173"/>
+  <dimension ref="A1:BF185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34794,15 +34794,11 @@
         </is>
       </c>
       <c r="F170" t="inlineStr"/>
-      <c r="G170" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H170" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="G170" t="n">
+        <v>1</v>
+      </c>
+      <c r="H170" t="n">
+        <v>4</v>
       </c>
       <c r="I170" t="inlineStr">
         <is>
@@ -34837,129 +34833,81 @@
           <t>59%</t>
         </is>
       </c>
-      <c r="Q170" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="R170" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="S170" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="T170" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="U170" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="V170" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="W170" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="X170" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y170" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Z170" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA170" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB170" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC170" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AD170" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="AE170" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AF170" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG170" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AH170" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AI170" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AJ170" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="Q170" t="n">
+        <v>7</v>
+      </c>
+      <c r="R170" t="n">
+        <v>14</v>
+      </c>
+      <c r="S170" t="n">
+        <v>1</v>
+      </c>
+      <c r="T170" t="n">
+        <v>10</v>
+      </c>
+      <c r="U170" t="n">
+        <v>5</v>
+      </c>
+      <c r="V170" t="n">
+        <v>4</v>
+      </c>
+      <c r="W170" t="n">
+        <v>8</v>
+      </c>
+      <c r="X170" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y170" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z170" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA170" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB170" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC170" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD170" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE170" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF170" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG170" t="n">
+        <v>7</v>
+      </c>
+      <c r="AH170" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI170" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ170" t="n">
+        <v>1</v>
       </c>
       <c r="AK170" t="inlineStr"/>
       <c r="AL170" t="inlineStr"/>
       <c r="AM170" t="inlineStr"/>
       <c r="AN170" t="inlineStr"/>
-      <c r="AO170" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="AP170" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
-      </c>
-      <c r="AQ170" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="AR170" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
+      <c r="AO170" t="n">
+        <v>66</v>
+      </c>
+      <c r="AP170" t="n">
+        <v>163</v>
+      </c>
+      <c r="AQ170" t="n">
+        <v>37</v>
+      </c>
+      <c r="AR170" t="n">
+        <v>59</v>
       </c>
       <c r="AS170" t="inlineStr"/>
       <c r="AT170" t="inlineStr"/>
@@ -34999,15 +34947,11 @@
       </c>
       <c r="BC170" t="inlineStr"/>
       <c r="BD170" t="inlineStr"/>
-      <c r="BE170" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF170" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="BE170" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF170" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="171">
@@ -35039,15 +34983,11 @@
         </is>
       </c>
       <c r="F171" t="inlineStr"/>
-      <c r="G171" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="G171" t="n">
+        <v>1</v>
+      </c>
+      <c r="H171" t="n">
+        <v>3</v>
       </c>
       <c r="I171" t="inlineStr">
         <is>
@@ -35082,129 +35022,81 @@
           <t>61%</t>
         </is>
       </c>
-      <c r="Q171" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="R171" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="S171" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="T171" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="U171" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="V171" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="W171" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="X171" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="Y171" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Z171" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AA171" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB171" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AC171" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AD171" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="AE171" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AF171" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AG171" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AH171" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AI171" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AJ171" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="Q171" t="n">
+        <v>8</v>
+      </c>
+      <c r="R171" t="n">
+        <v>18</v>
+      </c>
+      <c r="S171" t="n">
+        <v>3</v>
+      </c>
+      <c r="T171" t="n">
+        <v>9</v>
+      </c>
+      <c r="U171" t="n">
+        <v>4</v>
+      </c>
+      <c r="V171" t="n">
+        <v>6</v>
+      </c>
+      <c r="W171" t="n">
+        <v>16</v>
+      </c>
+      <c r="X171" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y171" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z171" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA171" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB171" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC171" t="n">
+        <v>21</v>
+      </c>
+      <c r="AD171" t="n">
+        <v>34</v>
+      </c>
+      <c r="AE171" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF171" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG171" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH171" t="n">
+        <v>9</v>
+      </c>
+      <c r="AI171" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ171" t="n">
+        <v>2</v>
       </c>
       <c r="AK171" t="inlineStr"/>
       <c r="AL171" t="inlineStr"/>
       <c r="AM171" t="inlineStr"/>
       <c r="AN171" t="inlineStr"/>
-      <c r="AO171" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="AP171" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
-      </c>
-      <c r="AQ171" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="AR171" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
+      <c r="AO171" t="n">
+        <v>122</v>
+      </c>
+      <c r="AP171" t="n">
+        <v>170</v>
+      </c>
+      <c r="AQ171" t="n">
+        <v>74</v>
+      </c>
+      <c r="AR171" t="n">
+        <v>139</v>
       </c>
       <c r="AS171" t="inlineStr"/>
       <c r="AT171" t="inlineStr"/>
@@ -35242,25 +35134,17 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="BC171" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BD171" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE171" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF171" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="BC171" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD171" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE171" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF171" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="172">
@@ -35292,15 +35176,11 @@
         </is>
       </c>
       <c r="F172" t="inlineStr"/>
-      <c r="G172" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G172" t="n">
+        <v>2</v>
+      </c>
+      <c r="H172" t="n">
+        <v>1</v>
       </c>
       <c r="I172" t="inlineStr">
         <is>
@@ -35335,129 +35215,81 @@
           <t>74%</t>
         </is>
       </c>
-      <c r="Q172" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="R172" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="S172" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="T172" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="U172" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="V172" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="W172" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="X172" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="Y172" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Z172" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA172" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB172" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AC172" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AD172" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="AE172" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AF172" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AG172" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AH172" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AI172" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AJ172" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="Q172" t="n">
+        <v>8</v>
+      </c>
+      <c r="R172" t="n">
+        <v>15</v>
+      </c>
+      <c r="S172" t="n">
+        <v>3</v>
+      </c>
+      <c r="T172" t="n">
+        <v>9</v>
+      </c>
+      <c r="U172" t="n">
+        <v>3</v>
+      </c>
+      <c r="V172" t="n">
+        <v>3</v>
+      </c>
+      <c r="W172" t="n">
+        <v>20</v>
+      </c>
+      <c r="X172" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y172" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z172" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA172" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB172" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC172" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD172" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE172" t="n">
+        <v>8</v>
+      </c>
+      <c r="AF172" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG172" t="n">
+        <v>20</v>
+      </c>
+      <c r="AH172" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI172" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ172" t="n">
+        <v>7</v>
       </c>
       <c r="AK172" t="inlineStr"/>
       <c r="AL172" t="inlineStr"/>
       <c r="AM172" t="inlineStr"/>
       <c r="AN172" t="inlineStr"/>
-      <c r="AO172" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="AP172" t="inlineStr">
-        <is>
-          <t>133</t>
-        </is>
-      </c>
-      <c r="AQ172" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="AR172" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
+      <c r="AO172" t="n">
+        <v>77</v>
+      </c>
+      <c r="AP172" t="n">
+        <v>133</v>
+      </c>
+      <c r="AQ172" t="n">
+        <v>27</v>
+      </c>
+      <c r="AR172" t="n">
+        <v>74</v>
       </c>
       <c r="AS172" t="inlineStr"/>
       <c r="AT172" t="inlineStr"/>
@@ -35497,15 +35329,11 @@
       </c>
       <c r="BC172" t="inlineStr"/>
       <c r="BD172" t="inlineStr"/>
-      <c r="BE172" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="BF172" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="BE172" t="n">
+        <v>2</v>
+      </c>
+      <c r="BF172" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="173">
@@ -35537,15 +35365,11 @@
         </is>
       </c>
       <c r="F173" t="inlineStr"/>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G173" t="n">
+        <v>0</v>
+      </c>
+      <c r="H173" t="n">
+        <v>1</v>
       </c>
       <c r="I173" t="inlineStr">
         <is>
@@ -35580,129 +35404,81 @@
           <t>76%</t>
         </is>
       </c>
-      <c r="Q173" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="R173" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="S173" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="T173" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U173" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="V173" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="W173" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="X173" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="Y173" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Z173" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA173" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB173" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC173" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AD173" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="AE173" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AF173" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AG173" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AH173" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AI173" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AJ173" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="Q173" t="n">
+        <v>6</v>
+      </c>
+      <c r="R173" t="n">
+        <v>18</v>
+      </c>
+      <c r="S173" t="n">
+        <v>1</v>
+      </c>
+      <c r="T173" t="n">
+        <v>2</v>
+      </c>
+      <c r="U173" t="n">
+        <v>4</v>
+      </c>
+      <c r="V173" t="n">
+        <v>13</v>
+      </c>
+      <c r="W173" t="n">
+        <v>10</v>
+      </c>
+      <c r="X173" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y173" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z173" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA173" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB173" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC173" t="n">
+        <v>21</v>
+      </c>
+      <c r="AD173" t="n">
+        <v>32</v>
+      </c>
+      <c r="AE173" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF173" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG173" t="n">
+        <v>19</v>
+      </c>
+      <c r="AH173" t="n">
+        <v>9</v>
+      </c>
+      <c r="AI173" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ173" t="n">
+        <v>2</v>
       </c>
       <c r="AK173" t="inlineStr"/>
       <c r="AL173" t="inlineStr"/>
       <c r="AM173" t="inlineStr"/>
       <c r="AN173" t="inlineStr"/>
-      <c r="AO173" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="AP173" t="inlineStr">
-        <is>
-          <t>186</t>
-        </is>
-      </c>
-      <c r="AQ173" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="AR173" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
+      <c r="AO173" t="n">
+        <v>65</v>
+      </c>
+      <c r="AP173" t="n">
+        <v>186</v>
+      </c>
+      <c r="AQ173" t="n">
+        <v>39</v>
+      </c>
+      <c r="AR173" t="n">
+        <v>165</v>
       </c>
       <c r="AS173" t="inlineStr"/>
       <c r="AT173" t="inlineStr"/>
@@ -35740,26 +35516,3314 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="BC173" t="inlineStr">
+      <c r="BC173" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD173" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE173" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF173" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="1" t="inlineStr">
+        <is>
+          <t>SxFxJ44k</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>24.08.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Zwayer F.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Signal Iduna Park
+ (Dortmund)</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>81 365</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>81 365</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>Dortmund</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>Eintracht Frankfurt</t>
+        </is>
+      </c>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="N174" t="inlineStr">
+        <is>
+          <t>1.19</t>
+        </is>
+      </c>
+      <c r="O174" t="inlineStr">
+        <is>
+          <t>67%</t>
+        </is>
+      </c>
+      <c r="P174" t="inlineStr">
+        <is>
+          <t>33%</t>
+        </is>
+      </c>
+      <c r="Q174" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="R174" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="S174" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T174" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U174" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="V174" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="W174" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X174" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y174" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Z174" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA174" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB174" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="BD173" t="inlineStr">
+      <c r="AC174" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AD174" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AE174" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AF174" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AG174" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AH174" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI174" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="BE173" t="inlineStr">
+      <c r="AJ174" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="BF173" t="inlineStr">
+      <c r="AK174" t="inlineStr">
+        <is>
+          <t>697</t>
+        </is>
+      </c>
+      <c r="AL174" t="inlineStr">
+        <is>
+          <t>293</t>
+        </is>
+      </c>
+      <c r="AM174" t="inlineStr">
+        <is>
+          <t>648</t>
+        </is>
+      </c>
+      <c r="AN174" t="inlineStr">
+        <is>
+          <t>266</t>
+        </is>
+      </c>
+      <c r="AO174" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="AP174" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="AQ174" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="AR174" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="AS174" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="AT174" t="inlineStr">
+        <is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="AU174" t="inlineStr">
+        <is>
+          <t>IkCftsQm</t>
+        </is>
+      </c>
+      <c r="AV174" t="inlineStr">
+        <is>
+          <t>sahin nuri</t>
+        </is>
+      </c>
+      <c r="AW174" t="inlineStr">
+        <is>
+          <t>UgdQz0fK</t>
+        </is>
+      </c>
+      <c r="AX174" t="inlineStr">
+        <is>
+          <t>toppmoller dino</t>
+        </is>
+      </c>
+      <c r="AY174" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ174" t="n">
+        <v>591</v>
+      </c>
+      <c r="BA174" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB174" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC174" t="inlineStr"/>
+      <c r="BD174" t="inlineStr"/>
+      <c r="BE174" t="inlineStr"/>
+      <c r="BF174" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="1" t="inlineStr">
+        <is>
+          <t>YZZcMwBs</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>24.08.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Stegemann S.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>WWK Arena
+ (Augsburg)</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>30 660</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>30 660</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>fTVNku3I</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>Augsburg</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Ig1f1fy3</t>
+        </is>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>Werder Bremen</t>
+        </is>
+      </c>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>1.12</t>
+        </is>
+      </c>
+      <c r="N175" t="inlineStr">
+        <is>
+          <t>1.86</t>
+        </is>
+      </c>
+      <c r="O175" t="inlineStr">
+        <is>
+          <t>45%</t>
+        </is>
+      </c>
+      <c r="P175" t="inlineStr">
+        <is>
+          <t>55%</t>
+        </is>
+      </c>
+      <c r="Q175" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R175" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="S175" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
+      <c r="T175" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="U175" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V175" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W175" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="X175" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="Y175" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Z175" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA175" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB175" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC175" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AD175" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AE175" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AF175" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AG175" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AH175" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AI175" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AJ175" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AK175" t="inlineStr">
+        <is>
+          <t>355</t>
+        </is>
+      </c>
+      <c r="AL175" t="inlineStr">
+        <is>
+          <t>443</t>
+        </is>
+      </c>
+      <c r="AM175" t="inlineStr">
+        <is>
+          <t>302</t>
+        </is>
+      </c>
+      <c r="AN175" t="inlineStr">
+        <is>
+          <t>381</t>
+        </is>
+      </c>
+      <c r="AO175" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="AP175" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="AQ175" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="AR175" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="AS175" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="AT175" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="AU175" t="inlineStr">
+        <is>
+          <t>2VSFgl3c</t>
+        </is>
+      </c>
+      <c r="AV175" t="inlineStr">
+        <is>
+          <t>thorup jess</t>
+        </is>
+      </c>
+      <c r="AW175" t="inlineStr">
+        <is>
+          <t>4fuCGs9P</t>
+        </is>
+      </c>
+      <c r="AX175" t="inlineStr">
+        <is>
+          <t>werner ole</t>
+        </is>
+      </c>
+      <c r="AY175" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ175" t="n">
+        <v>591</v>
+      </c>
+      <c r="BA175" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB175" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC175" t="inlineStr"/>
+      <c r="BD175" t="inlineStr"/>
+      <c r="BE175" t="inlineStr"/>
+      <c r="BF175" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="1" t="inlineStr">
+        <is>
+          <t>GbeXvnR8</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>24.08.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Welz T.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Europa-Park Stadion
+ (Freiburg)</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>34 700</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>34 700</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>Freiburg</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>Stuttgart</t>
+        </is>
+      </c>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>2.66</t>
+        </is>
+      </c>
+      <c r="N176" t="inlineStr">
+        <is>
+          <t>0.46</t>
+        </is>
+      </c>
+      <c r="O176" t="inlineStr">
+        <is>
+          <t>36%</t>
+        </is>
+      </c>
+      <c r="P176" t="inlineStr">
+        <is>
+          <t>64%</t>
+        </is>
+      </c>
+      <c r="Q176" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="R176" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="S176" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T176" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U176" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="V176" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="W176" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="X176" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y176" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Z176" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA176" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB176" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC176" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AD176" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AE176" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AF176" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AG176" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AH176" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AI176" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AJ176" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AK176" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="AL176" t="inlineStr">
+        <is>
+          <t>644</t>
+        </is>
+      </c>
+      <c r="AM176" t="inlineStr">
+        <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="AN176" t="inlineStr">
+        <is>
+          <t>573</t>
+        </is>
+      </c>
+      <c r="AO176" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="AP176" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="AQ176" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="AR176" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="AS176" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="AT176" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="AU176" t="inlineStr">
+        <is>
+          <t>YZPE6Sx7</t>
+        </is>
+      </c>
+      <c r="AV176" t="inlineStr">
+        <is>
+          <t>schuster julian</t>
+        </is>
+      </c>
+      <c r="AW176" t="inlineStr">
+        <is>
+          <t>GzfvcwRj</t>
+        </is>
+      </c>
+      <c r="AX176" t="inlineStr">
+        <is>
+          <t>hoeness sebastian</t>
+        </is>
+      </c>
+      <c r="AY176" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ176" t="n">
+        <v>591</v>
+      </c>
+      <c r="BA176" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB176" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC176" t="inlineStr"/>
+      <c r="BD176" t="inlineStr"/>
+      <c r="BE176" t="inlineStr"/>
+      <c r="BF176" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="1" t="inlineStr">
+        <is>
+          <t>O48oHrZ1</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>24.08.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Stieler T.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>PreZero Arena
+ (Sinsheim)</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>30 150</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>18 503</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>hQAtP9Sl</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>Hoffenheim</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>63WsD2ei</t>
+        </is>
+      </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>Holstein Kiel</t>
+        </is>
+      </c>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>3.01</t>
+        </is>
+      </c>
+      <c r="N177" t="inlineStr">
+        <is>
+          <t>2.11</t>
+        </is>
+      </c>
+      <c r="O177" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
+      </c>
+      <c r="P177" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="Q177" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="R177" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="S177" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="T177" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="U177" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="V177" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="W177" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="X177" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Y177" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Z177" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA177" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB177" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC177" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AD177" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AE177" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AF177" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AG177" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AH177" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AI177" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AJ177" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AK177" t="inlineStr">
+        <is>
+          <t>478</t>
+        </is>
+      </c>
+      <c r="AL177" t="inlineStr">
+        <is>
+          <t>384</t>
+        </is>
+      </c>
+      <c r="AM177" t="inlineStr">
+        <is>
+          <t>405</t>
+        </is>
+      </c>
+      <c r="AN177" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="AO177" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="AP177" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="AQ177" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="AR177" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="AS177" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="AT177" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="AU177" t="inlineStr">
+        <is>
+          <t>KUx4Q7x1</t>
+        </is>
+      </c>
+      <c r="AV177" t="inlineStr">
+        <is>
+          <t>matarazzo pellegrino</t>
+        </is>
+      </c>
+      <c r="AW177" t="inlineStr">
+        <is>
+          <t>A15eUM4C</t>
+        </is>
+      </c>
+      <c r="AX177" t="inlineStr">
+        <is>
+          <t>rapp marcel</t>
+        </is>
+      </c>
+      <c r="AY177" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ177" t="n">
+        <v>591</v>
+      </c>
+      <c r="BA177" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB177" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC177" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BD177" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BE177" t="inlineStr"/>
+      <c r="BF177" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="1" t="inlineStr">
+        <is>
+          <t>2FREIeA6</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>24.08.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Osmers H.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Mewa Arena
+ (Mainz)</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>34 000</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>31 500</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>EuakNmc1</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>Mainz</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>pzHW4oaE</t>
+        </is>
+      </c>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>Union Berlin</t>
+        </is>
+      </c>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="N178" t="inlineStr">
+        <is>
+          <t>1.02</t>
+        </is>
+      </c>
+      <c r="O178" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
+      </c>
+      <c r="P178" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="Q178" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="R178" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="S178" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T178" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U178" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="V178" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="W178" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="X178" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Y178" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Z178" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA178" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB178" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC178" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AD178" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AE178" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AF178" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AG178" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AH178" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AI178" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AJ178" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AK178" t="inlineStr">
+        <is>
+          <t>338</t>
+        </is>
+      </c>
+      <c r="AL178" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="AM178" t="inlineStr">
+        <is>
+          <t>274</t>
+        </is>
+      </c>
+      <c r="AN178" t="inlineStr">
+        <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="AO178" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="AP178" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="AQ178" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="AR178" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="AS178" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="AT178" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="AU178" t="inlineStr">
+        <is>
+          <t>vZA6VYpf</t>
+        </is>
+      </c>
+      <c r="AV178" t="inlineStr">
+        <is>
+          <t>henriksen bo</t>
+        </is>
+      </c>
+      <c r="AW178" t="inlineStr">
+        <is>
+          <t>hpYJ6izc</t>
+        </is>
+      </c>
+      <c r="AX178" t="inlineStr">
+        <is>
+          <t>svensson bo</t>
+        </is>
+      </c>
+      <c r="AY178" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ178" t="n">
+        <v>591</v>
+      </c>
+      <c r="BA178" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB178" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC178" t="inlineStr"/>
+      <c r="BD178" t="inlineStr"/>
+      <c r="BE178" t="inlineStr"/>
+      <c r="BF178" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="1" t="inlineStr">
+        <is>
+          <t>dfO6OQtS</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>24.08.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Brand B.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Red Bull Arena
+ (Leipzig)</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>47 069</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>44 611</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>KbS1suSm</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>RB Leipzig</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>8Y2m6ADe</t>
+        </is>
+      </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>Bochum</t>
+        </is>
+      </c>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="N179" t="inlineStr">
+        <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="O179" t="inlineStr">
+        <is>
+          <t>59%</t>
+        </is>
+      </c>
+      <c r="P179" t="inlineStr">
+        <is>
+          <t>41%</t>
+        </is>
+      </c>
+      <c r="Q179" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R179" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S179" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T179" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U179" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="V179" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W179" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="X179" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="Y179" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Z179" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA179" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB179" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC179" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AD179" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AE179" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AF179" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AG179" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AH179" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AI179" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AJ179" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AK179" t="inlineStr">
+        <is>
+          <t>486</t>
+        </is>
+      </c>
+      <c r="AL179" t="inlineStr">
+        <is>
+          <t>290</t>
+        </is>
+      </c>
+      <c r="AM179" t="inlineStr">
+        <is>
+          <t>408</t>
+        </is>
+      </c>
+      <c r="AN179" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="AO179" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="AP179" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="AQ179" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="AR179" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AS179" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="AT179" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="AU179" t="inlineStr">
+        <is>
+          <t>pfoInmcq</t>
+        </is>
+      </c>
+      <c r="AV179" t="inlineStr">
+        <is>
+          <t>rose marko</t>
+        </is>
+      </c>
+      <c r="AW179" t="inlineStr">
+        <is>
+          <t>8f6APkLc</t>
+        </is>
+      </c>
+      <c r="AX179" t="inlineStr">
+        <is>
+          <t>zeidler peter</t>
+        </is>
+      </c>
+      <c r="AY179" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ179" t="n">
+        <v>591</v>
+      </c>
+      <c r="BA179" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB179" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC179" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BD179" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE179" t="inlineStr"/>
+      <c r="BF179" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="1" t="inlineStr">
+        <is>
+          <t>zuzbQnCF</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>23.08.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Schroder R.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Borussia-Park
+ (Mönchengladbach)</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>54 042</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>54 042</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>88HSzjDr</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>B. Monchengladbach</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>4jcj2zMd</t>
+        </is>
+      </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>Bayer Leverkusen</t>
+        </is>
+      </c>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>2.19</t>
+        </is>
+      </c>
+      <c r="N180" t="inlineStr">
+        <is>
+          <t>4.01</t>
+        </is>
+      </c>
+      <c r="O180" t="inlineStr">
+        <is>
+          <t>46%</t>
+        </is>
+      </c>
+      <c r="P180" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="Q180" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R180" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="S180" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T180" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="U180" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V180" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="W180" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="X180" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="Y180" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Z180" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA180" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB180" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC180" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AD180" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AE180" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AF180" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AG180" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AH180" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AI180" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AJ180" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK180" t="inlineStr">
+        <is>
+          <t>446</t>
+        </is>
+      </c>
+      <c r="AL180" t="inlineStr">
+        <is>
+          <t>605</t>
+        </is>
+      </c>
+      <c r="AM180" t="inlineStr">
+        <is>
+          <t>370</t>
+        </is>
+      </c>
+      <c r="AN180" t="inlineStr">
+        <is>
+          <t>526</t>
+        </is>
+      </c>
+      <c r="AO180" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="AP180" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="AQ180" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="AR180" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="AS180" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="AT180" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="AU180" t="inlineStr">
+        <is>
+          <t>M5BRZDsC</t>
+        </is>
+      </c>
+      <c r="AV180" t="inlineStr">
+        <is>
+          <t>seoane gerardo</t>
+        </is>
+      </c>
+      <c r="AW180" t="inlineStr">
+        <is>
+          <t>hAcTWKKN</t>
+        </is>
+      </c>
+      <c r="AX180" t="inlineStr">
+        <is>
+          <t>alonso xabi</t>
+        </is>
+      </c>
+      <c r="AY180" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ180" t="n">
+        <v>591</v>
+      </c>
+      <c r="BA180" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB180" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC180" t="inlineStr"/>
+      <c r="BD180" t="inlineStr"/>
+      <c r="BE180" t="inlineStr"/>
+      <c r="BF180" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="1" t="inlineStr">
+        <is>
+          <t>S2GROGyP</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>24.08.2024 08:00</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Braun R.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Sportpark Ronhof Thomas Sommer
+ (Fürth)</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>16 626</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>10 261</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>CCQGbik8</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>Greuther Furth</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>G2Op923t</t>
+        </is>
+      </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>Paderborn</t>
+        </is>
+      </c>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>0.95</t>
+        </is>
+      </c>
+      <c r="N181" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="O181" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="P181" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="Q181" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R181" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="S181" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T181" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U181" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="V181" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="W181" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="X181" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="Y181" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Z181" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA181" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB181" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC181" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AD181" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AE181" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AF181" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AG181" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AH181" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AI181" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AJ181" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AK181" t="inlineStr">
+        <is>
+          <t>513</t>
+        </is>
+      </c>
+      <c r="AL181" t="inlineStr">
+        <is>
+          <t>481</t>
+        </is>
+      </c>
+      <c r="AM181" t="inlineStr">
+        <is>
+          <t>430</t>
+        </is>
+      </c>
+      <c r="AN181" t="inlineStr">
+        <is>
+          <t>409</t>
+        </is>
+      </c>
+      <c r="AO181" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="AP181" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="AQ181" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="AR181" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="AS181" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="AT181" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="AU181" t="inlineStr">
+        <is>
+          <t>8E86CPuD</t>
+        </is>
+      </c>
+      <c r="AV181" t="inlineStr">
+        <is>
+          <t>zorniger alexander</t>
+        </is>
+      </c>
+      <c r="AW181" t="inlineStr">
+        <is>
+          <t>0AI1QUJH</t>
+        </is>
+      </c>
+      <c r="AX181" t="inlineStr">
+        <is>
+          <t>kwasniok lukas</t>
+        </is>
+      </c>
+      <c r="AY181" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ181" t="n">
+        <v>592</v>
+      </c>
+      <c r="BA181" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB181" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC181" t="inlineStr"/>
+      <c r="BD181" t="inlineStr"/>
+      <c r="BE181" t="inlineStr"/>
+      <c r="BF181" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="1" t="inlineStr">
+        <is>
+          <t>IReyqKMt</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>24.08.2024 08:00</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Hempel R.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Olympiastadion
+ (Berlin)</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>74 667</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>42 355</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>2y0u8Wrq</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>Hertha Berlin</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>UiCmEP56</t>
+        </is>
+      </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>Regensburg</t>
+        </is>
+      </c>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>0.51</t>
+        </is>
+      </c>
+      <c r="N182" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="O182" t="inlineStr">
+        <is>
+          <t>67%</t>
+        </is>
+      </c>
+      <c r="P182" t="inlineStr">
+        <is>
+          <t>33%</t>
+        </is>
+      </c>
+      <c r="Q182" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R182" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="S182" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T182" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U182" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="V182" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="W182" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="X182" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="Y182" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Z182" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA182" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB182" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC182" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AD182" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="AE182" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AF182" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AG182" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AH182" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AI182" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AJ182" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AK182" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="AL182" t="inlineStr">
+        <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="AM182" t="inlineStr">
+        <is>
+          <t>439</t>
+        </is>
+      </c>
+      <c r="AN182" t="inlineStr">
+        <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="AO182" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="AP182" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="AQ182" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="AR182" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AS182" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="AT182" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="AU182" t="inlineStr">
+        <is>
+          <t>YmfcAeCo</t>
+        </is>
+      </c>
+      <c r="AV182" t="inlineStr">
+        <is>
+          <t>fiel cristian</t>
+        </is>
+      </c>
+      <c r="AW182" t="inlineStr">
+        <is>
+          <t>zyLSrbZQ</t>
+        </is>
+      </c>
+      <c r="AX182" t="inlineStr">
+        <is>
+          <t>enochs joe</t>
+        </is>
+      </c>
+      <c r="AY182" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ182" t="n">
+        <v>592</v>
+      </c>
+      <c r="BA182" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB182" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC182" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BD182" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BE182" t="inlineStr"/>
+      <c r="BF182" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="1" t="inlineStr">
+        <is>
+          <t>lGJRqVt2</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>24.08.2024 08:00</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Bacher M.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Preussenstadion
+ (Munster)</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>12 794</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>12 422</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>zedZaSL7</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>Preussen Munster</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>naWckLmC</t>
+        </is>
+      </c>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>Kaiserslautern</t>
+        </is>
+      </c>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>1.13</t>
+        </is>
+      </c>
+      <c r="N183" t="inlineStr">
+        <is>
+          <t>0.83</t>
+        </is>
+      </c>
+      <c r="O183" t="inlineStr">
+        <is>
+          <t>43%</t>
+        </is>
+      </c>
+      <c r="P183" t="inlineStr">
+        <is>
+          <t>57%</t>
+        </is>
+      </c>
+      <c r="Q183" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R183" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="S183" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T183" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U183" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V183" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W183" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="X183" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="Y183" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Z183" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA183" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB183" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC183" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="AD183" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AE183" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AF183" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AG183" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AH183" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AI183" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AJ183" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AK183" t="inlineStr">
+        <is>
+          <t>292</t>
+        </is>
+      </c>
+      <c r="AL183" t="inlineStr">
+        <is>
+          <t>402</t>
+        </is>
+      </c>
+      <c r="AM183" t="inlineStr">
+        <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="AN183" t="inlineStr">
+        <is>
+          <t>338</t>
+        </is>
+      </c>
+      <c r="AO183" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="AP183" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="AQ183" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="AR183" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AS183" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="AT183" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="AU183" t="inlineStr">
+        <is>
+          <t>pdPRS0me</t>
+        </is>
+      </c>
+      <c r="AV183" t="inlineStr">
+        <is>
+          <t>hildmann sascha</t>
+        </is>
+      </c>
+      <c r="AW183" t="inlineStr">
+        <is>
+          <t>4bJLk19p</t>
+        </is>
+      </c>
+      <c r="AX183" t="inlineStr">
+        <is>
+          <t>anfang marcus</t>
+        </is>
+      </c>
+      <c r="AY183" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ183" t="n">
+        <v>592</v>
+      </c>
+      <c r="BA183" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB183" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC183" t="inlineStr"/>
+      <c r="BD183" t="inlineStr"/>
+      <c r="BE183" t="inlineStr"/>
+      <c r="BF183" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="1" t="inlineStr">
+        <is>
+          <t>800QQx7C</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>23.08.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Alt P.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Heinz-von-Heiden-Arena
+ (Hannover)</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>49 200</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>49 000</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>dfNCCCzS</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>Hannover</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>v9k3aY5F</t>
+        </is>
+      </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>Hamburger SV</t>
+        </is>
+      </c>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>1.12</t>
+        </is>
+      </c>
+      <c r="N184" t="inlineStr">
+        <is>
+          <t>0.74</t>
+        </is>
+      </c>
+      <c r="O184" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="P184" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="Q184" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R184" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="S184" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T184" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U184" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V184" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="W184" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="X184" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="Y184" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Z184" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA184" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB184" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC184" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AD184" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AE184" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AF184" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AG184" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AH184" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AI184" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AJ184" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AK184" t="inlineStr">
+        <is>
+          <t>395</t>
+        </is>
+      </c>
+      <c r="AL184" t="inlineStr">
+        <is>
+          <t>434</t>
+        </is>
+      </c>
+      <c r="AM184" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="AN184" t="inlineStr">
+        <is>
+          <t>365</t>
+        </is>
+      </c>
+      <c r="AO184" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="AP184" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="AQ184" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="AR184" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="AS184" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="AT184" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="AU184" t="inlineStr">
+        <is>
+          <t>t0ZPdkUl</t>
+        </is>
+      </c>
+      <c r="AV184" t="inlineStr">
+        <is>
+          <t>leitl stefan</t>
+        </is>
+      </c>
+      <c r="AW184" t="inlineStr">
+        <is>
+          <t>EDRZkDzS</t>
+        </is>
+      </c>
+      <c r="AX184" t="inlineStr">
+        <is>
+          <t>baumgart steffen</t>
+        </is>
+      </c>
+      <c r="AY184" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ184" t="n">
+        <v>592</v>
+      </c>
+      <c r="BA184" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB184" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC184" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BD184" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BE184" t="inlineStr"/>
+      <c r="BF184" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="1" t="inlineStr">
+        <is>
+          <t>zm2ISbx0</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>23.08.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Prigan F.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>BBBank Wildpark
+ (Karlsruhe)</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>34 302</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>26 838</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>EB3q7jbk</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>Karlsruher SC</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>6in2Eknb</t>
+        </is>
+      </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>Elversberg</t>
+        </is>
+      </c>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="N185" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="O185" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="P185" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="Q185" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R185" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="S185" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="T185" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U185" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V185" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="W185" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="X185" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y185" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Z185" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA185" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB185" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC185" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AD185" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AE185" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AF185" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AG185" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AH185" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AI185" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AJ185" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK185" t="inlineStr">
+        <is>
+          <t>539</t>
+        </is>
+      </c>
+      <c r="AL185" t="inlineStr">
+        <is>
+          <t>452</t>
+        </is>
+      </c>
+      <c r="AM185" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="AN185" t="inlineStr">
+        <is>
+          <t>362</t>
+        </is>
+      </c>
+      <c r="AO185" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="AP185" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="AQ185" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="AR185" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AS185" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="AT185" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="AU185" t="inlineStr">
+        <is>
+          <t>OzPMRhK3</t>
+        </is>
+      </c>
+      <c r="AV185" t="inlineStr">
+        <is>
+          <t>eichner christian</t>
+        </is>
+      </c>
+      <c r="AW185" t="inlineStr">
+        <is>
+          <t>8E8qmw3d</t>
+        </is>
+      </c>
+      <c r="AX185" t="inlineStr">
+        <is>
+          <t>steffen horst</t>
+        </is>
+      </c>
+      <c r="AY185" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ185" t="n">
+        <v>592</v>
+      </c>
+      <c r="BA185" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB185" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC185" t="inlineStr"/>
+      <c r="BD185" t="inlineStr"/>
+      <c r="BE185" t="inlineStr"/>
+      <c r="BF185" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/germany/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
+++ b/data/germany/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BF185"/>
+  <dimension ref="A1:BF191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35562,15 +35562,11 @@
           <t>81 365</t>
         </is>
       </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G174" t="n">
+        <v>2</v>
+      </c>
+      <c r="H174" t="n">
+        <v>0</v>
       </c>
       <c r="I174" t="inlineStr">
         <is>
@@ -35592,15 +35588,11 @@
           <t>Eintracht Frankfurt</t>
         </is>
       </c>
-      <c r="M174" t="inlineStr">
-        <is>
-          <t>1.41</t>
-        </is>
-      </c>
-      <c r="N174" t="inlineStr">
-        <is>
-          <t>1.19</t>
-        </is>
+      <c r="M174" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="N174" t="n">
+        <v>1.19</v>
       </c>
       <c r="O174" t="inlineStr">
         <is>
@@ -35612,155 +35604,95 @@
           <t>33%</t>
         </is>
       </c>
-      <c r="Q174" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="R174" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="S174" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="T174" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="U174" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="V174" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="W174" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="X174" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y174" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Z174" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA174" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB174" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC174" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="AD174" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="AE174" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AF174" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AG174" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AH174" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AI174" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ174" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AK174" t="inlineStr">
-        <is>
-          <t>697</t>
-        </is>
-      </c>
-      <c r="AL174" t="inlineStr">
-        <is>
-          <t>293</t>
-        </is>
-      </c>
-      <c r="AM174" t="inlineStr">
-        <is>
-          <t>648</t>
-        </is>
-      </c>
-      <c r="AN174" t="inlineStr">
-        <is>
-          <t>266</t>
-        </is>
-      </c>
-      <c r="AO174" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="AP174" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="AQ174" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="AR174" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="AS174" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="AT174" t="inlineStr">
-        <is>
-          <t>246</t>
-        </is>
+      <c r="Q174" t="n">
+        <v>18</v>
+      </c>
+      <c r="R174" t="n">
+        <v>8</v>
+      </c>
+      <c r="S174" t="n">
+        <v>5</v>
+      </c>
+      <c r="T174" t="n">
+        <v>3</v>
+      </c>
+      <c r="U174" t="n">
+        <v>13</v>
+      </c>
+      <c r="V174" t="n">
+        <v>5</v>
+      </c>
+      <c r="W174" t="n">
+        <v>4</v>
+      </c>
+      <c r="X174" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y174" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z174" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA174" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB174" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC174" t="n">
+        <v>23</v>
+      </c>
+      <c r="AD174" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE174" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF174" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG174" t="n">
+        <v>6</v>
+      </c>
+      <c r="AH174" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI174" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ174" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK174" t="n">
+        <v>697</v>
+      </c>
+      <c r="AL174" t="n">
+        <v>293</v>
+      </c>
+      <c r="AM174" t="n">
+        <v>648</v>
+      </c>
+      <c r="AN174" t="n">
+        <v>266</v>
+      </c>
+      <c r="AO174" t="n">
+        <v>120</v>
+      </c>
+      <c r="AP174" t="n">
+        <v>59</v>
+      </c>
+      <c r="AQ174" t="n">
+        <v>90</v>
+      </c>
+      <c r="AR174" t="n">
+        <v>47</v>
+      </c>
+      <c r="AS174" t="n">
+        <v>116</v>
+      </c>
+      <c r="AT174" t="n">
+        <v>246</v>
       </c>
       <c r="AU174" t="inlineStr">
         <is>
@@ -35834,15 +35766,11 @@
           <t>30 660</t>
         </is>
       </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G175" t="n">
+        <v>2</v>
+      </c>
+      <c r="H175" t="n">
+        <v>2</v>
       </c>
       <c r="I175" t="inlineStr">
         <is>
@@ -35864,15 +35792,11 @@
           <t>Werder Bremen</t>
         </is>
       </c>
-      <c r="M175" t="inlineStr">
-        <is>
-          <t>1.12</t>
-        </is>
-      </c>
-      <c r="N175" t="inlineStr">
-        <is>
-          <t>1.86</t>
-        </is>
+      <c r="M175" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N175" t="n">
+        <v>1.86</v>
       </c>
       <c r="O175" t="inlineStr">
         <is>
@@ -35884,155 +35808,95 @@
           <t>55%</t>
         </is>
       </c>
-      <c r="Q175" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="R175" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="S175" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="T175" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="U175" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V175" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="W175" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="X175" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="Y175" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Z175" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA175" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB175" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC175" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AD175" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AE175" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AF175" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AG175" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AH175" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AI175" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AJ175" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AK175" t="inlineStr">
-        <is>
-          <t>355</t>
-        </is>
-      </c>
-      <c r="AL175" t="inlineStr">
-        <is>
-          <t>443</t>
-        </is>
-      </c>
-      <c r="AM175" t="inlineStr">
-        <is>
-          <t>302</t>
-        </is>
-      </c>
-      <c r="AN175" t="inlineStr">
-        <is>
-          <t>381</t>
-        </is>
-      </c>
-      <c r="AO175" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="AP175" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="AQ175" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="AR175" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="AS175" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="AT175" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
+      <c r="Q175" t="n">
+        <v>10</v>
+      </c>
+      <c r="R175" t="n">
+        <v>12</v>
+      </c>
+      <c r="S175" t="n">
+        <v>3</v>
+      </c>
+      <c r="T175" t="n">
+        <v>6</v>
+      </c>
+      <c r="U175" t="n">
+        <v>7</v>
+      </c>
+      <c r="V175" t="n">
+        <v>6</v>
+      </c>
+      <c r="W175" t="n">
+        <v>14</v>
+      </c>
+      <c r="X175" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y175" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z175" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA175" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB175" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC175" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD175" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE175" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF175" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG175" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH175" t="n">
+        <v>10</v>
+      </c>
+      <c r="AI175" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ175" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK175" t="n">
+        <v>355</v>
+      </c>
+      <c r="AL175" t="n">
+        <v>443</v>
+      </c>
+      <c r="AM175" t="n">
+        <v>302</v>
+      </c>
+      <c r="AN175" t="n">
+        <v>381</v>
+      </c>
+      <c r="AO175" t="n">
+        <v>87</v>
+      </c>
+      <c r="AP175" t="n">
+        <v>106</v>
+      </c>
+      <c r="AQ175" t="n">
+        <v>49</v>
+      </c>
+      <c r="AR175" t="n">
+        <v>37</v>
+      </c>
+      <c r="AS175" t="n">
+        <v>112</v>
+      </c>
+      <c r="AT175" t="n">
+        <v>108</v>
       </c>
       <c r="AU175" t="inlineStr">
         <is>
@@ -36106,15 +35970,11 @@
           <t>34 700</t>
         </is>
       </c>
-      <c r="G176" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H176" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G176" t="n">
+        <v>3</v>
+      </c>
+      <c r="H176" t="n">
+        <v>1</v>
       </c>
       <c r="I176" t="inlineStr">
         <is>
@@ -36136,15 +35996,11 @@
           <t>Stuttgart</t>
         </is>
       </c>
-      <c r="M176" t="inlineStr">
-        <is>
-          <t>2.66</t>
-        </is>
-      </c>
-      <c r="N176" t="inlineStr">
-        <is>
-          <t>0.46</t>
-        </is>
+      <c r="M176" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="N176" t="n">
+        <v>0.46</v>
       </c>
       <c r="O176" t="inlineStr">
         <is>
@@ -36156,155 +36012,95 @@
           <t>64%</t>
         </is>
       </c>
-      <c r="Q176" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="R176" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="S176" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="T176" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U176" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="V176" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="W176" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="X176" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y176" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Z176" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA176" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AB176" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC176" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AD176" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AE176" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AF176" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AG176" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AH176" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AI176" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AJ176" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AK176" t="inlineStr">
-        <is>
-          <t>303</t>
-        </is>
-      </c>
-      <c r="AL176" t="inlineStr">
-        <is>
-          <t>644</t>
-        </is>
-      </c>
-      <c r="AM176" t="inlineStr">
-        <is>
-          <t>236</t>
-        </is>
-      </c>
-      <c r="AN176" t="inlineStr">
-        <is>
-          <t>573</t>
-        </is>
-      </c>
-      <c r="AO176" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="AP176" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
-      <c r="AQ176" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="AR176" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="AS176" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="AT176" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
+      <c r="Q176" t="n">
+        <v>15</v>
+      </c>
+      <c r="R176" t="n">
+        <v>9</v>
+      </c>
+      <c r="S176" t="n">
+        <v>4</v>
+      </c>
+      <c r="T176" t="n">
+        <v>2</v>
+      </c>
+      <c r="U176" t="n">
+        <v>11</v>
+      </c>
+      <c r="V176" t="n">
+        <v>7</v>
+      </c>
+      <c r="W176" t="n">
+        <v>10</v>
+      </c>
+      <c r="X176" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y176" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z176" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA176" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB176" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC176" t="n">
+        <v>16</v>
+      </c>
+      <c r="AD176" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE176" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF176" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG176" t="n">
+        <v>7</v>
+      </c>
+      <c r="AH176" t="n">
+        <v>10</v>
+      </c>
+      <c r="AI176" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ176" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK176" t="n">
+        <v>303</v>
+      </c>
+      <c r="AL176" t="n">
+        <v>644</v>
+      </c>
+      <c r="AM176" t="n">
+        <v>236</v>
+      </c>
+      <c r="AN176" t="n">
+        <v>573</v>
+      </c>
+      <c r="AO176" t="n">
+        <v>91</v>
+      </c>
+      <c r="AP176" t="n">
+        <v>103</v>
+      </c>
+      <c r="AQ176" t="n">
+        <v>34</v>
+      </c>
+      <c r="AR176" t="n">
+        <v>42</v>
+      </c>
+      <c r="AS176" t="n">
+        <v>114</v>
+      </c>
+      <c r="AT176" t="n">
+        <v>109</v>
       </c>
       <c r="AU176" t="inlineStr">
         <is>
@@ -36378,15 +36174,11 @@
           <t>18 503</t>
         </is>
       </c>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H177" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G177" t="n">
+        <v>3</v>
+      </c>
+      <c r="H177" t="n">
+        <v>2</v>
       </c>
       <c r="I177" t="inlineStr">
         <is>
@@ -36408,15 +36200,11 @@
           <t>Holstein Kiel</t>
         </is>
       </c>
-      <c r="M177" t="inlineStr">
-        <is>
-          <t>3.01</t>
-        </is>
-      </c>
-      <c r="N177" t="inlineStr">
-        <is>
-          <t>2.11</t>
-        </is>
+      <c r="M177" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="N177" t="n">
+        <v>2.11</v>
       </c>
       <c r="O177" t="inlineStr">
         <is>
@@ -36428,155 +36216,95 @@
           <t>47%</t>
         </is>
       </c>
-      <c r="Q177" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="R177" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="S177" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="T177" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="U177" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="V177" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="W177" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="X177" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="Y177" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Z177" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA177" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB177" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC177" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AD177" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AE177" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AF177" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AG177" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AH177" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AI177" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AJ177" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AK177" t="inlineStr">
-        <is>
-          <t>478</t>
-        </is>
-      </c>
-      <c r="AL177" t="inlineStr">
-        <is>
-          <t>384</t>
-        </is>
-      </c>
-      <c r="AM177" t="inlineStr">
-        <is>
-          <t>405</t>
-        </is>
-      </c>
-      <c r="AN177" t="inlineStr">
-        <is>
-          <t>303</t>
-        </is>
-      </c>
-      <c r="AO177" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="AP177" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="AQ177" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="AR177" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="AS177" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
-      <c r="AT177" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
+      <c r="Q177" t="n">
+        <v>20</v>
+      </c>
+      <c r="R177" t="n">
+        <v>15</v>
+      </c>
+      <c r="S177" t="n">
+        <v>8</v>
+      </c>
+      <c r="T177" t="n">
+        <v>6</v>
+      </c>
+      <c r="U177" t="n">
+        <v>12</v>
+      </c>
+      <c r="V177" t="n">
+        <v>9</v>
+      </c>
+      <c r="W177" t="n">
+        <v>14</v>
+      </c>
+      <c r="X177" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y177" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z177" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA177" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB177" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC177" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD177" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE177" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF177" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG177" t="n">
+        <v>8</v>
+      </c>
+      <c r="AH177" t="n">
+        <v>14</v>
+      </c>
+      <c r="AI177" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ177" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK177" t="n">
+        <v>478</v>
+      </c>
+      <c r="AL177" t="n">
+        <v>384</v>
+      </c>
+      <c r="AM177" t="n">
+        <v>405</v>
+      </c>
+      <c r="AN177" t="n">
+        <v>303</v>
+      </c>
+      <c r="AO177" t="n">
+        <v>99</v>
+      </c>
+      <c r="AP177" t="n">
+        <v>78</v>
+      </c>
+      <c r="AQ177" t="n">
+        <v>69</v>
+      </c>
+      <c r="AR177" t="n">
+        <v>32</v>
+      </c>
+      <c r="AS177" t="n">
+        <v>119</v>
+      </c>
+      <c r="AT177" t="n">
+        <v>119</v>
       </c>
       <c r="AU177" t="inlineStr">
         <is>
@@ -36612,15 +36340,11 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="BC177" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BD177" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="BC177" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD177" t="n">
+        <v>1</v>
       </c>
       <c r="BE177" t="inlineStr"/>
       <c r="BF177" t="inlineStr"/>
@@ -36658,15 +36382,11 @@
           <t>31 500</t>
         </is>
       </c>
-      <c r="G178" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H178" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G178" t="n">
+        <v>1</v>
+      </c>
+      <c r="H178" t="n">
+        <v>1</v>
       </c>
       <c r="I178" t="inlineStr">
         <is>
@@ -36688,15 +36408,11 @@
           <t>Union Berlin</t>
         </is>
       </c>
-      <c r="M178" t="inlineStr">
-        <is>
-          <t>1.33</t>
-        </is>
-      </c>
-      <c r="N178" t="inlineStr">
-        <is>
-          <t>1.02</t>
-        </is>
+      <c r="M178" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="N178" t="n">
+        <v>1.02</v>
       </c>
       <c r="O178" t="inlineStr">
         <is>
@@ -36708,155 +36424,95 @@
           <t>47%</t>
         </is>
       </c>
-      <c r="Q178" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="R178" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="S178" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="T178" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U178" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="V178" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="W178" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="X178" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="Y178" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Z178" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA178" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB178" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC178" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AD178" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AE178" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AF178" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AG178" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AH178" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI178" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AJ178" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AK178" t="inlineStr">
-        <is>
-          <t>338</t>
-        </is>
-      </c>
-      <c r="AL178" t="inlineStr">
-        <is>
-          <t>270</t>
-        </is>
-      </c>
-      <c r="AM178" t="inlineStr">
-        <is>
-          <t>274</t>
-        </is>
-      </c>
-      <c r="AN178" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
-      </c>
-      <c r="AO178" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="AP178" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="AQ178" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="AR178" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="AS178" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="AT178" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
+      <c r="Q178" t="n">
+        <v>15</v>
+      </c>
+      <c r="R178" t="n">
+        <v>15</v>
+      </c>
+      <c r="S178" t="n">
+        <v>3</v>
+      </c>
+      <c r="T178" t="n">
+        <v>4</v>
+      </c>
+      <c r="U178" t="n">
+        <v>12</v>
+      </c>
+      <c r="V178" t="n">
+        <v>11</v>
+      </c>
+      <c r="W178" t="n">
+        <v>16</v>
+      </c>
+      <c r="X178" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y178" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z178" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA178" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB178" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC178" t="n">
+        <v>17</v>
+      </c>
+      <c r="AD178" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE178" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF178" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG178" t="n">
+        <v>9</v>
+      </c>
+      <c r="AH178" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI178" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ178" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK178" t="n">
+        <v>338</v>
+      </c>
+      <c r="AL178" t="n">
+        <v>270</v>
+      </c>
+      <c r="AM178" t="n">
+        <v>274</v>
+      </c>
+      <c r="AN178" t="n">
+        <v>208</v>
+      </c>
+      <c r="AO178" t="n">
+        <v>92</v>
+      </c>
+      <c r="AP178" t="n">
+        <v>90</v>
+      </c>
+      <c r="AQ178" t="n">
+        <v>26</v>
+      </c>
+      <c r="AR178" t="n">
+        <v>50</v>
+      </c>
+      <c r="AS178" t="n">
+        <v>109</v>
+      </c>
+      <c r="AT178" t="n">
+        <v>114</v>
       </c>
       <c r="AU178" t="inlineStr">
         <is>
@@ -36930,15 +36586,11 @@
           <t>44 611</t>
         </is>
       </c>
-      <c r="G179" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H179" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G179" t="n">
+        <v>1</v>
+      </c>
+      <c r="H179" t="n">
+        <v>0</v>
       </c>
       <c r="I179" t="inlineStr">
         <is>
@@ -36960,15 +36612,11 @@
           <t>Bochum</t>
         </is>
       </c>
-      <c r="M179" t="inlineStr">
-        <is>
-          <t>1.39</t>
-        </is>
-      </c>
-      <c r="N179" t="inlineStr">
-        <is>
-          <t>1.29</t>
-        </is>
+      <c r="M179" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="N179" t="n">
+        <v>1.29</v>
       </c>
       <c r="O179" t="inlineStr">
         <is>
@@ -36980,155 +36628,95 @@
           <t>41%</t>
         </is>
       </c>
-      <c r="Q179" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="R179" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="S179" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="T179" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U179" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="V179" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="W179" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="X179" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="Y179" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Z179" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA179" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AB179" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC179" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AD179" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AE179" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AF179" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AG179" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AH179" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AI179" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AJ179" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AK179" t="inlineStr">
-        <is>
-          <t>486</t>
-        </is>
-      </c>
-      <c r="AL179" t="inlineStr">
-        <is>
-          <t>290</t>
-        </is>
-      </c>
-      <c r="AM179" t="inlineStr">
-        <is>
-          <t>408</t>
-        </is>
-      </c>
-      <c r="AN179" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
-      <c r="AO179" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="AP179" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="AQ179" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="AR179" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="AS179" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="AT179" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
+      <c r="Q179" t="n">
+        <v>12</v>
+      </c>
+      <c r="R179" t="n">
+        <v>10</v>
+      </c>
+      <c r="S179" t="n">
+        <v>3</v>
+      </c>
+      <c r="T179" t="n">
+        <v>4</v>
+      </c>
+      <c r="U179" t="n">
+        <v>9</v>
+      </c>
+      <c r="V179" t="n">
+        <v>6</v>
+      </c>
+      <c r="W179" t="n">
+        <v>15</v>
+      </c>
+      <c r="X179" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y179" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z179" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA179" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB179" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC179" t="n">
+        <v>20</v>
+      </c>
+      <c r="AD179" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE179" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF179" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG179" t="n">
+        <v>9</v>
+      </c>
+      <c r="AH179" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI179" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ179" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK179" t="n">
+        <v>486</v>
+      </c>
+      <c r="AL179" t="n">
+        <v>290</v>
+      </c>
+      <c r="AM179" t="n">
+        <v>408</v>
+      </c>
+      <c r="AN179" t="n">
+        <v>220</v>
+      </c>
+      <c r="AO179" t="n">
+        <v>83</v>
+      </c>
+      <c r="AP179" t="n">
+        <v>106</v>
+      </c>
+      <c r="AQ179" t="n">
+        <v>43</v>
+      </c>
+      <c r="AR179" t="n">
+        <v>25</v>
+      </c>
+      <c r="AS179" t="n">
+        <v>110</v>
+      </c>
+      <c r="AT179" t="n">
+        <v>110</v>
       </c>
       <c r="AU179" t="inlineStr">
         <is>
@@ -37164,15 +36752,11 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="BC179" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BD179" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="BC179" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD179" t="n">
+        <v>0</v>
       </c>
       <c r="BE179" t="inlineStr"/>
       <c r="BF179" t="inlineStr"/>
@@ -37210,15 +36794,11 @@
           <t>54 042</t>
         </is>
       </c>
-      <c r="G180" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H180" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="G180" t="n">
+        <v>2</v>
+      </c>
+      <c r="H180" t="n">
+        <v>3</v>
       </c>
       <c r="I180" t="inlineStr">
         <is>
@@ -37240,15 +36820,11 @@
           <t>Bayer Leverkusen</t>
         </is>
       </c>
-      <c r="M180" t="inlineStr">
-        <is>
-          <t>2.19</t>
-        </is>
-      </c>
-      <c r="N180" t="inlineStr">
-        <is>
-          <t>4.01</t>
-        </is>
+      <c r="M180" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="N180" t="n">
+        <v>4.01</v>
       </c>
       <c r="O180" t="inlineStr">
         <is>
@@ -37260,155 +36836,95 @@
           <t>54%</t>
         </is>
       </c>
-      <c r="Q180" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="R180" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="S180" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="T180" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="U180" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V180" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="W180" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="X180" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="Y180" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Z180" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA180" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB180" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC180" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AD180" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AE180" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AF180" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AG180" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AH180" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AI180" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AJ180" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK180" t="inlineStr">
-        <is>
-          <t>446</t>
-        </is>
-      </c>
-      <c r="AL180" t="inlineStr">
-        <is>
-          <t>605</t>
-        </is>
-      </c>
-      <c r="AM180" t="inlineStr">
-        <is>
-          <t>370</t>
-        </is>
-      </c>
-      <c r="AN180" t="inlineStr">
-        <is>
-          <t>526</t>
-        </is>
-      </c>
-      <c r="AO180" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="AP180" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
-      <c r="AQ180" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="AR180" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="AS180" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="AT180" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
+      <c r="Q180" t="n">
+        <v>14</v>
+      </c>
+      <c r="R180" t="n">
+        <v>25</v>
+      </c>
+      <c r="S180" t="n">
+        <v>7</v>
+      </c>
+      <c r="T180" t="n">
+        <v>9</v>
+      </c>
+      <c r="U180" t="n">
+        <v>7</v>
+      </c>
+      <c r="V180" t="n">
+        <v>16</v>
+      </c>
+      <c r="W180" t="n">
+        <v>6</v>
+      </c>
+      <c r="X180" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y180" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z180" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA180" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB180" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC180" t="n">
+        <v>18</v>
+      </c>
+      <c r="AD180" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE180" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF180" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG180" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH180" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI180" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ180" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK180" t="n">
+        <v>446</v>
+      </c>
+      <c r="AL180" t="n">
+        <v>605</v>
+      </c>
+      <c r="AM180" t="n">
+        <v>370</v>
+      </c>
+      <c r="AN180" t="n">
+        <v>526</v>
+      </c>
+      <c r="AO180" t="n">
+        <v>81</v>
+      </c>
+      <c r="AP180" t="n">
+        <v>126</v>
+      </c>
+      <c r="AQ180" t="n">
+        <v>28</v>
+      </c>
+      <c r="AR180" t="n">
+        <v>64</v>
+      </c>
+      <c r="AS180" t="n">
+        <v>121</v>
+      </c>
+      <c r="AT180" t="n">
+        <v>119</v>
       </c>
       <c r="AU180" t="inlineStr">
         <is>
@@ -37482,15 +36998,11 @@
           <t>10 261</t>
         </is>
       </c>
-      <c r="G181" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H181" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G181" t="n">
+        <v>1</v>
+      </c>
+      <c r="H181" t="n">
+        <v>1</v>
       </c>
       <c r="I181" t="inlineStr">
         <is>
@@ -37512,15 +37024,11 @@
           <t>Paderborn</t>
         </is>
       </c>
-      <c r="M181" t="inlineStr">
-        <is>
-          <t>0.95</t>
-        </is>
-      </c>
-      <c r="N181" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
+      <c r="M181" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="N181" t="n">
+        <v>1.95</v>
       </c>
       <c r="O181" t="inlineStr">
         <is>
@@ -37532,155 +37040,95 @@
           <t>48%</t>
         </is>
       </c>
-      <c r="Q181" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="R181" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="S181" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="T181" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U181" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="V181" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="W181" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="X181" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="Y181" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Z181" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA181" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB181" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC181" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AD181" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AE181" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AF181" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AG181" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AH181" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AI181" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AJ181" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AK181" t="inlineStr">
-        <is>
-          <t>513</t>
-        </is>
-      </c>
-      <c r="AL181" t="inlineStr">
-        <is>
-          <t>481</t>
-        </is>
-      </c>
-      <c r="AM181" t="inlineStr">
-        <is>
-          <t>430</t>
-        </is>
-      </c>
-      <c r="AN181" t="inlineStr">
-        <is>
-          <t>409</t>
-        </is>
-      </c>
-      <c r="AO181" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="AP181" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="AQ181" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="AR181" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="AS181" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="AT181" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
+      <c r="Q181" t="n">
+        <v>14</v>
+      </c>
+      <c r="R181" t="n">
+        <v>13</v>
+      </c>
+      <c r="S181" t="n">
+        <v>3</v>
+      </c>
+      <c r="T181" t="n">
+        <v>4</v>
+      </c>
+      <c r="U181" t="n">
+        <v>11</v>
+      </c>
+      <c r="V181" t="n">
+        <v>9</v>
+      </c>
+      <c r="W181" t="n">
+        <v>18</v>
+      </c>
+      <c r="X181" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y181" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z181" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA181" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB181" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC181" t="n">
+        <v>19</v>
+      </c>
+      <c r="AD181" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE181" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF181" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG181" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH181" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI181" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ181" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK181" t="n">
+        <v>513</v>
+      </c>
+      <c r="AL181" t="n">
+        <v>481</v>
+      </c>
+      <c r="AM181" t="n">
+        <v>430</v>
+      </c>
+      <c r="AN181" t="n">
+        <v>409</v>
+      </c>
+      <c r="AO181" t="n">
+        <v>117</v>
+      </c>
+      <c r="AP181" t="n">
+        <v>86</v>
+      </c>
+      <c r="AQ181" t="n">
+        <v>53</v>
+      </c>
+      <c r="AR181" t="n">
+        <v>40</v>
+      </c>
+      <c r="AS181" t="n">
+        <v>96</v>
+      </c>
+      <c r="AT181" t="n">
+        <v>100</v>
       </c>
       <c r="AU181" t="inlineStr">
         <is>
@@ -37754,15 +37202,11 @@
           <t>42 355</t>
         </is>
       </c>
-      <c r="G182" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H182" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G182" t="n">
+        <v>2</v>
+      </c>
+      <c r="H182" t="n">
+        <v>0</v>
       </c>
       <c r="I182" t="inlineStr">
         <is>
@@ -37784,15 +37228,11 @@
           <t>Regensburg</t>
         </is>
       </c>
-      <c r="M182" t="inlineStr">
-        <is>
-          <t>0.51</t>
-        </is>
-      </c>
-      <c r="N182" t="inlineStr">
-        <is>
-          <t>1.39</t>
-        </is>
+      <c r="M182" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="N182" t="n">
+        <v>1.39</v>
       </c>
       <c r="O182" t="inlineStr">
         <is>
@@ -37804,155 +37244,95 @@
           <t>33%</t>
         </is>
       </c>
-      <c r="Q182" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="R182" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="S182" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="T182" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U182" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="V182" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="W182" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="X182" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="Y182" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Z182" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA182" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AB182" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC182" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AD182" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="AE182" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AF182" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AG182" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AH182" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AI182" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AJ182" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AK182" t="inlineStr">
-        <is>
-          <t>499</t>
-        </is>
-      </c>
-      <c r="AL182" t="inlineStr">
-        <is>
-          <t>268</t>
-        </is>
-      </c>
-      <c r="AM182" t="inlineStr">
-        <is>
-          <t>439</t>
-        </is>
-      </c>
-      <c r="AN182" t="inlineStr">
-        <is>
-          <t>204</t>
-        </is>
-      </c>
-      <c r="AO182" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
-      <c r="AP182" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="AQ182" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="AR182" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="AS182" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="AT182" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
+      <c r="Q182" t="n">
+        <v>11</v>
+      </c>
+      <c r="R182" t="n">
+        <v>13</v>
+      </c>
+      <c r="S182" t="n">
+        <v>2</v>
+      </c>
+      <c r="T182" t="n">
+        <v>2</v>
+      </c>
+      <c r="U182" t="n">
+        <v>9</v>
+      </c>
+      <c r="V182" t="n">
+        <v>11</v>
+      </c>
+      <c r="W182" t="n">
+        <v>9</v>
+      </c>
+      <c r="X182" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y182" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z182" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA182" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB182" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC182" t="n">
+        <v>21</v>
+      </c>
+      <c r="AD182" t="n">
+        <v>28</v>
+      </c>
+      <c r="AE182" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF182" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG182" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH182" t="n">
+        <v>9</v>
+      </c>
+      <c r="AI182" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ182" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK182" t="n">
+        <v>499</v>
+      </c>
+      <c r="AL182" t="n">
+        <v>268</v>
+      </c>
+      <c r="AM182" t="n">
+        <v>439</v>
+      </c>
+      <c r="AN182" t="n">
+        <v>204</v>
+      </c>
+      <c r="AO182" t="n">
+        <v>119</v>
+      </c>
+      <c r="AP182" t="n">
+        <v>98</v>
+      </c>
+      <c r="AQ182" t="n">
+        <v>66</v>
+      </c>
+      <c r="AR182" t="n">
+        <v>30</v>
+      </c>
+      <c r="AS182" t="n">
+        <v>48</v>
+      </c>
+      <c r="AT182" t="n">
+        <v>110</v>
       </c>
       <c r="AU182" t="inlineStr">
         <is>
@@ -37988,15 +37368,11 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="BC182" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BD182" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="BC182" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD182" t="n">
+        <v>1</v>
       </c>
       <c r="BE182" t="inlineStr"/>
       <c r="BF182" t="inlineStr"/>
@@ -38034,15 +37410,11 @@
           <t>12 422</t>
         </is>
       </c>
-      <c r="G183" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H183" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G183" t="n">
+        <v>0</v>
+      </c>
+      <c r="H183" t="n">
+        <v>1</v>
       </c>
       <c r="I183" t="inlineStr">
         <is>
@@ -38064,15 +37436,11 @@
           <t>Kaiserslautern</t>
         </is>
       </c>
-      <c r="M183" t="inlineStr">
-        <is>
-          <t>1.13</t>
-        </is>
-      </c>
-      <c r="N183" t="inlineStr">
-        <is>
-          <t>0.83</t>
-        </is>
+      <c r="M183" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="N183" t="n">
+        <v>0.83</v>
       </c>
       <c r="O183" t="inlineStr">
         <is>
@@ -38084,155 +37452,95 @@
           <t>57%</t>
         </is>
       </c>
-      <c r="Q183" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="R183" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="S183" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="T183" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="U183" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V183" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="W183" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="X183" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="Y183" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Z183" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA183" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AB183" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC183" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="AD183" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AE183" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AF183" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AG183" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AH183" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AI183" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AJ183" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AK183" t="inlineStr">
-        <is>
-          <t>292</t>
-        </is>
-      </c>
-      <c r="AL183" t="inlineStr">
-        <is>
-          <t>402</t>
-        </is>
-      </c>
-      <c r="AM183" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
-      <c r="AN183" t="inlineStr">
-        <is>
-          <t>338</t>
-        </is>
-      </c>
-      <c r="AO183" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="AP183" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="AQ183" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="AR183" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="AS183" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="AT183" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
+      <c r="Q183" t="n">
+        <v>14</v>
+      </c>
+      <c r="R183" t="n">
+        <v>8</v>
+      </c>
+      <c r="S183" t="n">
+        <v>7</v>
+      </c>
+      <c r="T183" t="n">
+        <v>5</v>
+      </c>
+      <c r="U183" t="n">
+        <v>7</v>
+      </c>
+      <c r="V183" t="n">
+        <v>3</v>
+      </c>
+      <c r="W183" t="n">
+        <v>19</v>
+      </c>
+      <c r="X183" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y183" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z183" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA183" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB183" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC183" t="n">
+        <v>31</v>
+      </c>
+      <c r="AD183" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE183" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF183" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG183" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH183" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI183" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ183" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK183" t="n">
+        <v>292</v>
+      </c>
+      <c r="AL183" t="n">
+        <v>402</v>
+      </c>
+      <c r="AM183" t="n">
+        <v>207</v>
+      </c>
+      <c r="AN183" t="n">
+        <v>338</v>
+      </c>
+      <c r="AO183" t="n">
+        <v>83</v>
+      </c>
+      <c r="AP183" t="n">
+        <v>112</v>
+      </c>
+      <c r="AQ183" t="n">
+        <v>52</v>
+      </c>
+      <c r="AR183" t="n">
+        <v>30</v>
+      </c>
+      <c r="AS183" t="n">
+        <v>118</v>
+      </c>
+      <c r="AT183" t="n">
+        <v>107</v>
       </c>
       <c r="AU183" t="inlineStr">
         <is>
@@ -38306,15 +37614,11 @@
           <t>49 000</t>
         </is>
       </c>
-      <c r="G184" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H184" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G184" t="n">
+        <v>1</v>
+      </c>
+      <c r="H184" t="n">
+        <v>0</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -38336,15 +37640,11 @@
           <t>Hamburger SV</t>
         </is>
       </c>
-      <c r="M184" t="inlineStr">
-        <is>
-          <t>1.12</t>
-        </is>
-      </c>
-      <c r="N184" t="inlineStr">
-        <is>
-          <t>0.74</t>
-        </is>
+      <c r="M184" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N184" t="n">
+        <v>0.74</v>
       </c>
       <c r="O184" t="inlineStr">
         <is>
@@ -38356,155 +37656,95 @@
           <t>48%</t>
         </is>
       </c>
-      <c r="Q184" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R184" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="S184" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="T184" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="U184" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="V184" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="W184" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="X184" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="Y184" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Z184" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA184" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB184" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC184" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AD184" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AE184" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AF184" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AG184" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AH184" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AI184" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AJ184" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AK184" t="inlineStr">
-        <is>
-          <t>395</t>
-        </is>
-      </c>
-      <c r="AL184" t="inlineStr">
-        <is>
-          <t>434</t>
-        </is>
-      </c>
-      <c r="AM184" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="AN184" t="inlineStr">
-        <is>
-          <t>365</t>
-        </is>
-      </c>
-      <c r="AO184" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="AP184" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="AQ184" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="AR184" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="AS184" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="AT184" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
+      <c r="Q184" t="n">
+        <v>9</v>
+      </c>
+      <c r="R184" t="n">
+        <v>8</v>
+      </c>
+      <c r="S184" t="n">
+        <v>3</v>
+      </c>
+      <c r="T184" t="n">
+        <v>1</v>
+      </c>
+      <c r="U184" t="n">
+        <v>6</v>
+      </c>
+      <c r="V184" t="n">
+        <v>7</v>
+      </c>
+      <c r="W184" t="n">
+        <v>17</v>
+      </c>
+      <c r="X184" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y184" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z184" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA184" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB184" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC184" t="n">
+        <v>17</v>
+      </c>
+      <c r="AD184" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE184" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF184" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG184" t="n">
+        <v>20</v>
+      </c>
+      <c r="AH184" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI184" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ184" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK184" t="n">
+        <v>395</v>
+      </c>
+      <c r="AL184" t="n">
+        <v>434</v>
+      </c>
+      <c r="AM184" t="n">
+        <v>336</v>
+      </c>
+      <c r="AN184" t="n">
+        <v>365</v>
+      </c>
+      <c r="AO184" t="n">
+        <v>114</v>
+      </c>
+      <c r="AP184" t="n">
+        <v>78</v>
+      </c>
+      <c r="AQ184" t="n">
+        <v>43</v>
+      </c>
+      <c r="AR184" t="n">
+        <v>50</v>
+      </c>
+      <c r="AS184" t="n">
+        <v>113</v>
+      </c>
+      <c r="AT184" t="n">
+        <v>111</v>
       </c>
       <c r="AU184" t="inlineStr">
         <is>
@@ -38540,15 +37780,11 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="BC184" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BD184" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="BC184" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD184" t="n">
+        <v>1</v>
       </c>
       <c r="BE184" t="inlineStr"/>
       <c r="BF184" t="inlineStr"/>
@@ -38586,15 +37822,11 @@
           <t>26 838</t>
         </is>
       </c>
-      <c r="G185" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H185" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G185" t="n">
+        <v>3</v>
+      </c>
+      <c r="H185" t="n">
+        <v>2</v>
       </c>
       <c r="I185" t="inlineStr">
         <is>
@@ -38616,15 +37848,11 @@
           <t>Elversberg</t>
         </is>
       </c>
-      <c r="M185" t="inlineStr">
-        <is>
-          <t>1.22</t>
-        </is>
-      </c>
-      <c r="N185" t="inlineStr">
-        <is>
-          <t>1.30</t>
-        </is>
+      <c r="M185" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="N185" t="n">
+        <v>1.3</v>
       </c>
       <c r="O185" t="inlineStr">
         <is>
@@ -38636,155 +37864,95 @@
           <t>50%</t>
         </is>
       </c>
-      <c r="Q185" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="R185" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="S185" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="T185" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="U185" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="V185" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="W185" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="X185" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y185" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Z185" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA185" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB185" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC185" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AD185" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AE185" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AF185" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AG185" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AH185" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AI185" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AJ185" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK185" t="inlineStr">
-        <is>
-          <t>539</t>
-        </is>
-      </c>
-      <c r="AL185" t="inlineStr">
-        <is>
-          <t>452</t>
-        </is>
-      </c>
-      <c r="AM185" t="inlineStr">
-        <is>
-          <t>480</t>
-        </is>
-      </c>
-      <c r="AN185" t="inlineStr">
-        <is>
-          <t>362</t>
-        </is>
-      </c>
-      <c r="AO185" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="AP185" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="AQ185" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="AR185" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="AS185" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="AT185" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
+      <c r="Q185" t="n">
+        <v>11</v>
+      </c>
+      <c r="R185" t="n">
+        <v>11</v>
+      </c>
+      <c r="S185" t="n">
+        <v>8</v>
+      </c>
+      <c r="T185" t="n">
+        <v>3</v>
+      </c>
+      <c r="U185" t="n">
+        <v>3</v>
+      </c>
+      <c r="V185" t="n">
+        <v>8</v>
+      </c>
+      <c r="W185" t="n">
+        <v>6</v>
+      </c>
+      <c r="X185" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y185" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z185" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA185" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB185" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC185" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD185" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE185" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF185" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG185" t="n">
+        <v>8</v>
+      </c>
+      <c r="AH185" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI185" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ185" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK185" t="n">
+        <v>539</v>
+      </c>
+      <c r="AL185" t="n">
+        <v>452</v>
+      </c>
+      <c r="AM185" t="n">
+        <v>480</v>
+      </c>
+      <c r="AN185" t="n">
+        <v>362</v>
+      </c>
+      <c r="AO185" t="n">
+        <v>83</v>
+      </c>
+      <c r="AP185" t="n">
+        <v>85</v>
+      </c>
+      <c r="AQ185" t="n">
+        <v>45</v>
+      </c>
+      <c r="AR185" t="n">
+        <v>30</v>
+      </c>
+      <c r="AS185" t="n">
+        <v>118</v>
+      </c>
+      <c r="AT185" t="n">
+        <v>120</v>
       </c>
       <c r="AU185" t="inlineStr">
         <is>
@@ -38825,6 +37993,1638 @@
       <c r="BE185" t="inlineStr"/>
       <c r="BF185" t="inlineStr"/>
     </row>
+    <row r="186">
+      <c r="A186" s="1" t="inlineStr">
+        <is>
+          <t>AuVMGZvJ</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>25.08.2024 12:30</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Jablonski S.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Millerntor-Stadion
+ (Hamburg)</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>29 546</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>29 157</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>St. Pauli</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>KWixEVWi</t>
+        </is>
+      </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>Heidenheim</t>
+        </is>
+      </c>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>1.59</t>
+        </is>
+      </c>
+      <c r="N186" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="O186" t="inlineStr">
+        <is>
+          <t>58%</t>
+        </is>
+      </c>
+      <c r="P186" t="inlineStr">
+        <is>
+          <t>42%</t>
+        </is>
+      </c>
+      <c r="Q186" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R186" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="S186" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T186" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U186" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V186" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W186" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="X186" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Y186" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Z186" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA186" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB186" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC186" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AD186" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AE186" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AF186" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AG186" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AH186" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AI186" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AJ186" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AK186" t="inlineStr">
+        <is>
+          <t>548</t>
+        </is>
+      </c>
+      <c r="AL186" t="inlineStr">
+        <is>
+          <t>341</t>
+        </is>
+      </c>
+      <c r="AM186" t="inlineStr">
+        <is>
+          <t>444</t>
+        </is>
+      </c>
+      <c r="AN186" t="inlineStr">
+        <is>
+          <t>245</t>
+        </is>
+      </c>
+      <c r="AO186" t="inlineStr">
+        <is>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="AP186" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="AQ186" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="AR186" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AS186" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="AT186" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="AU186" t="inlineStr">
+        <is>
+          <t>0jdIgO6t</t>
+        </is>
+      </c>
+      <c r="AV186" t="inlineStr">
+        <is>
+          <t>blessin alexander</t>
+        </is>
+      </c>
+      <c r="AW186" t="inlineStr">
+        <is>
+          <t>4ljanukM</t>
+        </is>
+      </c>
+      <c r="AX186" t="inlineStr">
+        <is>
+          <t>schmidt frank</t>
+        </is>
+      </c>
+      <c r="AY186" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ186" t="n">
+        <v>591</v>
+      </c>
+      <c r="BA186" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB186" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC186" t="inlineStr"/>
+      <c r="BD186" t="inlineStr"/>
+      <c r="BE186" t="inlineStr"/>
+      <c r="BF186" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="1" t="inlineStr">
+        <is>
+          <t>t0w6KHuf</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>25.08.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Siebert D.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Volkswagen Arena
+ (Wolfsburg)</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>28 917</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>28 917</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>nwkTahLL</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>Wolfsburg</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>nVp0wiqd</t>
+        </is>
+      </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>Bayern Munich</t>
+        </is>
+      </c>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>2.34</t>
+        </is>
+      </c>
+      <c r="N187" t="inlineStr">
+        <is>
+          <t>2.85</t>
+        </is>
+      </c>
+      <c r="O187" t="inlineStr">
+        <is>
+          <t>36%</t>
+        </is>
+      </c>
+      <c r="P187" t="inlineStr">
+        <is>
+          <t>64%</t>
+        </is>
+      </c>
+      <c r="Q187" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R187" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="S187" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T187" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="U187" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="V187" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W187" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="X187" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="Y187" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Z187" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA187" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB187" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC187" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AD187" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AE187" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AF187" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG187" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AH187" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AI187" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AJ187" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AK187" t="inlineStr">
+        <is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="AL187" t="inlineStr">
+        <is>
+          <t>593</t>
+        </is>
+      </c>
+      <c r="AM187" t="inlineStr">
+        <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="AN187" t="inlineStr">
+        <is>
+          <t>515</t>
+        </is>
+      </c>
+      <c r="AO187" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="AP187" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="AQ187" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="AR187" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="AS187" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="AT187" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="AU187" t="inlineStr">
+        <is>
+          <t>f3ddUIXs</t>
+        </is>
+      </c>
+      <c r="AV187" t="inlineStr">
+        <is>
+          <t>hasenhuttl ralph</t>
+        </is>
+      </c>
+      <c r="AW187" t="inlineStr">
+        <is>
+          <t>K6A2elS9</t>
+        </is>
+      </c>
+      <c r="AX187" t="inlineStr">
+        <is>
+          <t>kompany vincent</t>
+        </is>
+      </c>
+      <c r="AY187" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ187" t="n">
+        <v>591</v>
+      </c>
+      <c r="BA187" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB187" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC187" t="inlineStr"/>
+      <c r="BD187" t="inlineStr"/>
+      <c r="BE187" t="inlineStr"/>
+      <c r="BF187" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="1" t="inlineStr">
+        <is>
+          <t>vL89UK7m</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>25.08.2024 08:30</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Burda M.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Merck-Stadion am Bollenfalltor
+ (Darmstadt)</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>17 810</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>17 600</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>S0hPB9rA</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>Darmstadt</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>6FDqshzF</t>
+        </is>
+      </c>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>Nurnberg</t>
+        </is>
+      </c>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>1.31</t>
+        </is>
+      </c>
+      <c r="N188" t="inlineStr">
+        <is>
+          <t>0.37</t>
+        </is>
+      </c>
+      <c r="O188" t="inlineStr">
+        <is>
+          <t>59%</t>
+        </is>
+      </c>
+      <c r="P188" t="inlineStr">
+        <is>
+          <t>41%</t>
+        </is>
+      </c>
+      <c r="Q188" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="R188" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="S188" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T188" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U188" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="V188" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W188" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="X188" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Y188" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="Z188" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA188" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB188" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC188" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AD188" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AE188" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AF188" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AG188" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AH188" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AI188" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AJ188" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AK188" t="inlineStr">
+        <is>
+          <t>506</t>
+        </is>
+      </c>
+      <c r="AL188" t="inlineStr">
+        <is>
+          <t>348</t>
+        </is>
+      </c>
+      <c r="AM188" t="inlineStr">
+        <is>
+          <t>420</t>
+        </is>
+      </c>
+      <c r="AN188" t="inlineStr">
+        <is>
+          <t>257</t>
+        </is>
+      </c>
+      <c r="AO188" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="AP188" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="AQ188" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="AR188" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AS188" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="AT188" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="AU188" t="inlineStr">
+        <is>
+          <t>MDhPV0RQ</t>
+        </is>
+      </c>
+      <c r="AV188" t="inlineStr">
+        <is>
+          <t>lieberknecht torsten</t>
+        </is>
+      </c>
+      <c r="AW188" t="inlineStr">
+        <is>
+          <t>tO31cZrF</t>
+        </is>
+      </c>
+      <c r="AX188" t="inlineStr">
+        <is>
+          <t>klose miroslav</t>
+        </is>
+      </c>
+      <c r="AY188" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ188" t="n">
+        <v>592</v>
+      </c>
+      <c r="BA188" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB188" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC188" t="inlineStr"/>
+      <c r="BD188" t="inlineStr"/>
+      <c r="BE188" t="inlineStr"/>
+      <c r="BF188" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="1" t="inlineStr">
+        <is>
+          <t>vsppsbig</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>25.08.2024 08:30</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Gerach T.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>MDCC-Arena
+ (Magdeburg)</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>30 098</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>27 146</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>YFuz2RLm</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>Magdeburg</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>0Ija0Ej9</t>
+        </is>
+      </c>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>Schalke</t>
+        </is>
+      </c>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="N189" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="O189" t="inlineStr">
+        <is>
+          <t>57%</t>
+        </is>
+      </c>
+      <c r="P189" t="inlineStr">
+        <is>
+          <t>43%</t>
+        </is>
+      </c>
+      <c r="Q189" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R189" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="S189" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="T189" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="U189" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V189" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W189" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="X189" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y189" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Z189" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA189" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB189" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC189" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AD189" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AE189" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AF189" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AG189" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AH189" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AI189" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AJ189" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AK189" t="inlineStr">
+        <is>
+          <t>453</t>
+        </is>
+      </c>
+      <c r="AL189" t="inlineStr">
+        <is>
+          <t>337</t>
+        </is>
+      </c>
+      <c r="AM189" t="inlineStr">
+        <is>
+          <t>371</t>
+        </is>
+      </c>
+      <c r="AN189" t="inlineStr">
+        <is>
+          <t>256</t>
+        </is>
+      </c>
+      <c r="AO189" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="AP189" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="AQ189" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="AR189" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="AS189" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="AT189" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="AU189" t="inlineStr">
+        <is>
+          <t>IgZoGKFn</t>
+        </is>
+      </c>
+      <c r="AV189" t="inlineStr">
+        <is>
+          <t>titz christian</t>
+        </is>
+      </c>
+      <c r="AW189" t="inlineStr">
+        <is>
+          <t>txZLBQVC</t>
+        </is>
+      </c>
+      <c r="AX189" t="inlineStr">
+        <is>
+          <t>geraerts karel</t>
+        </is>
+      </c>
+      <c r="AY189" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ189" t="n">
+        <v>592</v>
+      </c>
+      <c r="BA189" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB189" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC189" t="inlineStr"/>
+      <c r="BD189" t="inlineStr"/>
+      <c r="BE189" t="inlineStr"/>
+      <c r="BF189" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="1" t="inlineStr">
+        <is>
+          <t>n7mhuxM5</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>25.08.2024 08:30</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Weisbach E.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Donaustadion
+ (Ulm)</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>19 500</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>13 226</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>tbC3EcQn</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>Ulm</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>ne1oL3y7</t>
+        </is>
+      </c>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>Dusseldorf</t>
+        </is>
+      </c>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="N190" t="inlineStr">
+        <is>
+          <t>3.87</t>
+        </is>
+      </c>
+      <c r="O190" t="inlineStr">
+        <is>
+          <t>46%</t>
+        </is>
+      </c>
+      <c r="P190" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="Q190" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="R190" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="S190" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="T190" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U190" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="V190" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="W190" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="X190" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y190" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Z190" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA190" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB190" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC190" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AD190" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AE190" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AF190" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AG190" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AH190" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AI190" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AJ190" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AK190" t="inlineStr">
+        <is>
+          <t>340</t>
+        </is>
+      </c>
+      <c r="AL190" t="inlineStr">
+        <is>
+          <t>427</t>
+        </is>
+      </c>
+      <c r="AM190" t="inlineStr">
+        <is>
+          <t>272</t>
+        </is>
+      </c>
+      <c r="AN190" t="inlineStr">
+        <is>
+          <t>341</t>
+        </is>
+      </c>
+      <c r="AO190" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="AP190" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="AQ190" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="AR190" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="AS190" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="AT190" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="AU190" t="inlineStr">
+        <is>
+          <t>QevvB2nf</t>
+        </is>
+      </c>
+      <c r="AV190" t="inlineStr">
+        <is>
+          <t>worle thomas</t>
+        </is>
+      </c>
+      <c r="AW190" t="inlineStr">
+        <is>
+          <t>AoL97rX8</t>
+        </is>
+      </c>
+      <c r="AX190" t="inlineStr">
+        <is>
+          <t>thioune daniel</t>
+        </is>
+      </c>
+      <c r="AY190" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ190" t="n">
+        <v>592</v>
+      </c>
+      <c r="BA190" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB190" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC190" t="inlineStr"/>
+      <c r="BD190" t="inlineStr"/>
+      <c r="BE190" t="inlineStr"/>
+      <c r="BF190" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="1" t="inlineStr">
+        <is>
+          <t>8xIwzspQ</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>24.08.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Jollenbeck M.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>RheinEnergieStadion
+ (Cologne)</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>50 000</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>50 000</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>WG9pOTse</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>FC Koln</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>QqLCC3il</t>
+        </is>
+      </c>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>Braunschweig</t>
+        </is>
+      </c>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>3.34</t>
+        </is>
+      </c>
+      <c r="N191" t="inlineStr">
+        <is>
+          <t>0.33</t>
+        </is>
+      </c>
+      <c r="O191" t="inlineStr">
+        <is>
+          <t>29%</t>
+        </is>
+      </c>
+      <c r="P191" t="inlineStr">
+        <is>
+          <t>71%</t>
+        </is>
+      </c>
+      <c r="Q191" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="R191" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="S191" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="T191" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U191" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="V191" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W191" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="X191" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="Y191" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Z191" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA191" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB191" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC191" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AD191" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AE191" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AF191" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AG191" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AH191" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AI191" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AJ191" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AK191" t="inlineStr">
+        <is>
+          <t>586</t>
+        </is>
+      </c>
+      <c r="AL191" t="inlineStr">
+        <is>
+          <t>369</t>
+        </is>
+      </c>
+      <c r="AM191" t="inlineStr">
+        <is>
+          <t>522</t>
+        </is>
+      </c>
+      <c r="AN191" t="inlineStr">
+        <is>
+          <t>292</t>
+        </is>
+      </c>
+      <c r="AO191" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="AP191" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="AQ191" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="AR191" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AS191" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="AT191" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="AU191" t="inlineStr">
+        <is>
+          <t>4fX0k7gg</t>
+        </is>
+      </c>
+      <c r="AV191" t="inlineStr">
+        <is>
+          <t>struber gerhard</t>
+        </is>
+      </c>
+      <c r="AW191" t="inlineStr">
+        <is>
+          <t>SQrxFAMl</t>
+        </is>
+      </c>
+      <c r="AX191" t="inlineStr">
+        <is>
+          <t>scherning daniel</t>
+        </is>
+      </c>
+      <c r="AY191" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ191" t="n">
+        <v>592</v>
+      </c>
+      <c r="BA191" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB191" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC191" t="inlineStr"/>
+      <c r="BD191" t="inlineStr"/>
+      <c r="BE191" t="inlineStr"/>
+      <c r="BF191" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/germany/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
+++ b/data/germany/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BF191"/>
+  <dimension ref="A1:BF196"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38026,15 +38026,11 @@
           <t>29 157</t>
         </is>
       </c>
-      <c r="G186" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H186" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G186" t="n">
+        <v>0</v>
+      </c>
+      <c r="H186" t="n">
+        <v>2</v>
       </c>
       <c r="I186" t="inlineStr">
         <is>
@@ -38056,15 +38052,11 @@
           <t>Heidenheim</t>
         </is>
       </c>
-      <c r="M186" t="inlineStr">
-        <is>
-          <t>1.59</t>
-        </is>
-      </c>
-      <c r="N186" t="inlineStr">
-        <is>
-          <t>1.45</t>
-        </is>
+      <c r="M186" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="N186" t="n">
+        <v>1.45</v>
       </c>
       <c r="O186" t="inlineStr">
         <is>
@@ -38076,155 +38068,95 @@
           <t>42%</t>
         </is>
       </c>
-      <c r="Q186" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="R186" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="S186" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="T186" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="U186" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="V186" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="W186" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="X186" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="Y186" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Z186" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA186" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB186" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC186" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="AD186" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="AE186" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AF186" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AG186" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AH186" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI186" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AJ186" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AK186" t="inlineStr">
-        <is>
-          <t>548</t>
-        </is>
-      </c>
-      <c r="AL186" t="inlineStr">
-        <is>
-          <t>341</t>
-        </is>
-      </c>
-      <c r="AM186" t="inlineStr">
-        <is>
-          <t>444</t>
-        </is>
-      </c>
-      <c r="AN186" t="inlineStr">
-        <is>
-          <t>245</t>
-        </is>
-      </c>
-      <c r="AO186" t="inlineStr">
-        <is>
-          <t>133</t>
-        </is>
-      </c>
-      <c r="AP186" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="AQ186" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="AR186" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="AS186" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="AT186" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
+      <c r="Q186" t="n">
+        <v>11</v>
+      </c>
+      <c r="R186" t="n">
+        <v>6</v>
+      </c>
+      <c r="S186" t="n">
+        <v>3</v>
+      </c>
+      <c r="T186" t="n">
+        <v>3</v>
+      </c>
+      <c r="U186" t="n">
+        <v>8</v>
+      </c>
+      <c r="V186" t="n">
+        <v>3</v>
+      </c>
+      <c r="W186" t="n">
+        <v>15</v>
+      </c>
+      <c r="X186" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y186" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z186" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA186" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB186" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC186" t="n">
+        <v>25</v>
+      </c>
+      <c r="AD186" t="n">
+        <v>27</v>
+      </c>
+      <c r="AE186" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF186" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG186" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH186" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI186" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ186" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK186" t="n">
+        <v>548</v>
+      </c>
+      <c r="AL186" t="n">
+        <v>341</v>
+      </c>
+      <c r="AM186" t="n">
+        <v>444</v>
+      </c>
+      <c r="AN186" t="n">
+        <v>245</v>
+      </c>
+      <c r="AO186" t="n">
+        <v>133</v>
+      </c>
+      <c r="AP186" t="n">
+        <v>88</v>
+      </c>
+      <c r="AQ186" t="n">
+        <v>39</v>
+      </c>
+      <c r="AR186" t="n">
+        <v>27</v>
+      </c>
+      <c r="AS186" t="n">
+        <v>118</v>
+      </c>
+      <c r="AT186" t="n">
+        <v>116</v>
       </c>
       <c r="AU186" t="inlineStr">
         <is>
@@ -38298,15 +38230,11 @@
           <t>28 917</t>
         </is>
       </c>
-      <c r="G187" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H187" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="G187" t="n">
+        <v>2</v>
+      </c>
+      <c r="H187" t="n">
+        <v>3</v>
       </c>
       <c r="I187" t="inlineStr">
         <is>
@@ -38328,15 +38256,11 @@
           <t>Bayern Munich</t>
         </is>
       </c>
-      <c r="M187" t="inlineStr">
-        <is>
-          <t>2.34</t>
-        </is>
-      </c>
-      <c r="N187" t="inlineStr">
-        <is>
-          <t>2.85</t>
-        </is>
+      <c r="M187" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="N187" t="n">
+        <v>2.85</v>
       </c>
       <c r="O187" t="inlineStr">
         <is>
@@ -38348,155 +38272,95 @@
           <t>64%</t>
         </is>
       </c>
-      <c r="Q187" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="R187" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="S187" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="T187" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="U187" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="V187" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="W187" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="X187" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="Y187" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Z187" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA187" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AB187" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC187" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AD187" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="AE187" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AF187" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG187" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AH187" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AI187" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AJ187" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AK187" t="inlineStr">
-        <is>
-          <t>246</t>
-        </is>
-      </c>
-      <c r="AL187" t="inlineStr">
-        <is>
-          <t>593</t>
-        </is>
-      </c>
-      <c r="AM187" t="inlineStr">
-        <is>
-          <t>169</t>
-        </is>
-      </c>
-      <c r="AN187" t="inlineStr">
-        <is>
-          <t>515</t>
-        </is>
-      </c>
-      <c r="AO187" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="AP187" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="AQ187" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="AR187" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="AS187" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="AT187" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
+      <c r="Q187" t="n">
+        <v>11</v>
+      </c>
+      <c r="R187" t="n">
+        <v>14</v>
+      </c>
+      <c r="S187" t="n">
+        <v>2</v>
+      </c>
+      <c r="T187" t="n">
+        <v>8</v>
+      </c>
+      <c r="U187" t="n">
+        <v>9</v>
+      </c>
+      <c r="V187" t="n">
+        <v>6</v>
+      </c>
+      <c r="W187" t="n">
+        <v>12</v>
+      </c>
+      <c r="X187" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y187" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z187" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA187" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB187" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC187" t="n">
+        <v>16</v>
+      </c>
+      <c r="AD187" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE187" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF187" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG187" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH187" t="n">
+        <v>11</v>
+      </c>
+      <c r="AI187" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ187" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK187" t="n">
+        <v>246</v>
+      </c>
+      <c r="AL187" t="n">
+        <v>593</v>
+      </c>
+      <c r="AM187" t="n">
+        <v>169</v>
+      </c>
+      <c r="AN187" t="n">
+        <v>515</v>
+      </c>
+      <c r="AO187" t="n">
+        <v>85</v>
+      </c>
+      <c r="AP187" t="n">
+        <v>95</v>
+      </c>
+      <c r="AQ187" t="n">
+        <v>26</v>
+      </c>
+      <c r="AR187" t="n">
+        <v>62</v>
+      </c>
+      <c r="AS187" t="n">
+        <v>113</v>
+      </c>
+      <c r="AT187" t="n">
+        <v>116</v>
       </c>
       <c r="AU187" t="inlineStr">
         <is>
@@ -38570,15 +38434,11 @@
           <t>17 600</t>
         </is>
       </c>
-      <c r="G188" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H188" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G188" t="n">
+        <v>1</v>
+      </c>
+      <c r="H188" t="n">
+        <v>1</v>
       </c>
       <c r="I188" t="inlineStr">
         <is>
@@ -38600,15 +38460,11 @@
           <t>Nurnberg</t>
         </is>
       </c>
-      <c r="M188" t="inlineStr">
-        <is>
-          <t>1.31</t>
-        </is>
-      </c>
-      <c r="N188" t="inlineStr">
-        <is>
-          <t>0.37</t>
-        </is>
+      <c r="M188" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="N188" t="n">
+        <v>0.37</v>
       </c>
       <c r="O188" t="inlineStr">
         <is>
@@ -38620,155 +38476,95 @@
           <t>41%</t>
         </is>
       </c>
-      <c r="Q188" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="R188" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="S188" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="T188" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U188" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="V188" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="W188" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="X188" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="Y188" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="Z188" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA188" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB188" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC188" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AD188" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AE188" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AF188" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AG188" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AH188" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AI188" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AJ188" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AK188" t="inlineStr">
-        <is>
-          <t>506</t>
-        </is>
-      </c>
-      <c r="AL188" t="inlineStr">
-        <is>
-          <t>348</t>
-        </is>
-      </c>
-      <c r="AM188" t="inlineStr">
-        <is>
-          <t>420</t>
-        </is>
-      </c>
-      <c r="AN188" t="inlineStr">
-        <is>
-          <t>257</t>
-        </is>
-      </c>
-      <c r="AO188" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
-      <c r="AP188" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="AQ188" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="AR188" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AS188" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="AT188" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
+      <c r="Q188" t="n">
+        <v>19</v>
+      </c>
+      <c r="R188" t="n">
+        <v>5</v>
+      </c>
+      <c r="S188" t="n">
+        <v>7</v>
+      </c>
+      <c r="T188" t="n">
+        <v>4</v>
+      </c>
+      <c r="U188" t="n">
+        <v>12</v>
+      </c>
+      <c r="V188" t="n">
+        <v>1</v>
+      </c>
+      <c r="W188" t="n">
+        <v>11</v>
+      </c>
+      <c r="X188" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y188" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z188" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA188" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB188" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC188" t="n">
+        <v>17</v>
+      </c>
+      <c r="AD188" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE188" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF188" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG188" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH188" t="n">
+        <v>11</v>
+      </c>
+      <c r="AI188" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ188" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK188" t="n">
+        <v>506</v>
+      </c>
+      <c r="AL188" t="n">
+        <v>348</v>
+      </c>
+      <c r="AM188" t="n">
+        <v>420</v>
+      </c>
+      <c r="AN188" t="n">
+        <v>257</v>
+      </c>
+      <c r="AO188" t="n">
+        <v>119</v>
+      </c>
+      <c r="AP188" t="n">
+        <v>57</v>
+      </c>
+      <c r="AQ188" t="n">
+        <v>60</v>
+      </c>
+      <c r="AR188" t="n">
+        <v>17</v>
+      </c>
+      <c r="AS188" t="n">
+        <v>113</v>
+      </c>
+      <c r="AT188" t="n">
+        <v>112</v>
       </c>
       <c r="AU188" t="inlineStr">
         <is>
@@ -38842,15 +38638,11 @@
           <t>27 146</t>
         </is>
       </c>
-      <c r="G189" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H189" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G189" t="n">
+        <v>2</v>
+      </c>
+      <c r="H189" t="n">
+        <v>2</v>
       </c>
       <c r="I189" t="inlineStr">
         <is>
@@ -38872,15 +38664,11 @@
           <t>Schalke</t>
         </is>
       </c>
-      <c r="M189" t="inlineStr">
-        <is>
-          <t>1.55</t>
-        </is>
-      </c>
-      <c r="N189" t="inlineStr">
-        <is>
-          <t>1.22</t>
-        </is>
+      <c r="M189" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="N189" t="n">
+        <v>1.22</v>
       </c>
       <c r="O189" t="inlineStr">
         <is>
@@ -38892,155 +38680,95 @@
           <t>43%</t>
         </is>
       </c>
-      <c r="Q189" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="R189" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="S189" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="T189" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="U189" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="V189" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="W189" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="X189" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y189" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Z189" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA189" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB189" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC189" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AD189" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="AE189" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AF189" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AG189" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AH189" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AI189" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AJ189" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AK189" t="inlineStr">
-        <is>
-          <t>453</t>
-        </is>
-      </c>
-      <c r="AL189" t="inlineStr">
-        <is>
-          <t>337</t>
-        </is>
-      </c>
-      <c r="AM189" t="inlineStr">
-        <is>
-          <t>371</t>
-        </is>
-      </c>
-      <c r="AN189" t="inlineStr">
-        <is>
-          <t>256</t>
-        </is>
-      </c>
-      <c r="AO189" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
-      <c r="AP189" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="AQ189" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="AR189" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="AS189" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="AT189" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
+      <c r="Q189" t="n">
+        <v>14</v>
+      </c>
+      <c r="R189" t="n">
+        <v>13</v>
+      </c>
+      <c r="S189" t="n">
+        <v>8</v>
+      </c>
+      <c r="T189" t="n">
+        <v>7</v>
+      </c>
+      <c r="U189" t="n">
+        <v>6</v>
+      </c>
+      <c r="V189" t="n">
+        <v>6</v>
+      </c>
+      <c r="W189" t="n">
+        <v>13</v>
+      </c>
+      <c r="X189" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y189" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z189" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA189" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB189" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC189" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD189" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE189" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF189" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG189" t="n">
+        <v>9</v>
+      </c>
+      <c r="AH189" t="n">
+        <v>12</v>
+      </c>
+      <c r="AI189" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ189" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK189" t="n">
+        <v>453</v>
+      </c>
+      <c r="AL189" t="n">
+        <v>337</v>
+      </c>
+      <c r="AM189" t="n">
+        <v>371</v>
+      </c>
+      <c r="AN189" t="n">
+        <v>256</v>
+      </c>
+      <c r="AO189" t="n">
+        <v>103</v>
+      </c>
+      <c r="AP189" t="n">
+        <v>67</v>
+      </c>
+      <c r="AQ189" t="n">
+        <v>45</v>
+      </c>
+      <c r="AR189" t="n">
+        <v>34</v>
+      </c>
+      <c r="AS189" t="n">
+        <v>116</v>
+      </c>
+      <c r="AT189" t="n">
+        <v>113</v>
       </c>
       <c r="AU189" t="inlineStr">
         <is>
@@ -39114,15 +38842,11 @@
           <t>13 226</t>
         </is>
       </c>
-      <c r="G190" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G190" t="n">
+        <v>1</v>
+      </c>
+      <c r="H190" t="n">
+        <v>2</v>
       </c>
       <c r="I190" t="inlineStr">
         <is>
@@ -39144,15 +38868,11 @@
           <t>Dusseldorf</t>
         </is>
       </c>
-      <c r="M190" t="inlineStr">
-        <is>
-          <t>1.66</t>
-        </is>
-      </c>
-      <c r="N190" t="inlineStr">
-        <is>
-          <t>3.87</t>
-        </is>
+      <c r="M190" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="N190" t="n">
+        <v>3.87</v>
       </c>
       <c r="O190" t="inlineStr">
         <is>
@@ -39164,155 +38884,95 @@
           <t>54%</t>
         </is>
       </c>
-      <c r="Q190" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="R190" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="S190" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="T190" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="U190" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="V190" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="W190" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="X190" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y190" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Z190" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA190" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB190" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC190" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="AD190" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="AE190" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AF190" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AG190" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AH190" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AI190" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AJ190" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AK190" t="inlineStr">
-        <is>
-          <t>340</t>
-        </is>
-      </c>
-      <c r="AL190" t="inlineStr">
-        <is>
-          <t>427</t>
-        </is>
-      </c>
-      <c r="AM190" t="inlineStr">
-        <is>
-          <t>272</t>
-        </is>
-      </c>
-      <c r="AN190" t="inlineStr">
-        <is>
-          <t>341</t>
-        </is>
-      </c>
-      <c r="AO190" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="AP190" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="AQ190" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="AR190" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="AS190" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="AT190" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
+      <c r="Q190" t="n">
+        <v>21</v>
+      </c>
+      <c r="R190" t="n">
+        <v>12</v>
+      </c>
+      <c r="S190" t="n">
+        <v>8</v>
+      </c>
+      <c r="T190" t="n">
+        <v>5</v>
+      </c>
+      <c r="U190" t="n">
+        <v>13</v>
+      </c>
+      <c r="V190" t="n">
+        <v>7</v>
+      </c>
+      <c r="W190" t="n">
+        <v>13</v>
+      </c>
+      <c r="X190" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y190" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z190" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA190" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB190" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC190" t="n">
+        <v>22</v>
+      </c>
+      <c r="AD190" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE190" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF190" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG190" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH190" t="n">
+        <v>13</v>
+      </c>
+      <c r="AI190" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ190" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK190" t="n">
+        <v>340</v>
+      </c>
+      <c r="AL190" t="n">
+        <v>427</v>
+      </c>
+      <c r="AM190" t="n">
+        <v>272</v>
+      </c>
+      <c r="AN190" t="n">
+        <v>341</v>
+      </c>
+      <c r="AO190" t="n">
+        <v>106</v>
+      </c>
+      <c r="AP190" t="n">
+        <v>90</v>
+      </c>
+      <c r="AQ190" t="n">
+        <v>42</v>
+      </c>
+      <c r="AR190" t="n">
+        <v>33</v>
+      </c>
+      <c r="AS190" t="n">
+        <v>121</v>
+      </c>
+      <c r="AT190" t="n">
+        <v>116</v>
       </c>
       <c r="AU190" t="inlineStr">
         <is>
@@ -39386,15 +39046,11 @@
           <t>50 000</t>
         </is>
       </c>
-      <c r="G191" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H191" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G191" t="n">
+        <v>5</v>
+      </c>
+      <c r="H191" t="n">
+        <v>0</v>
       </c>
       <c r="I191" t="inlineStr">
         <is>
@@ -39416,15 +39072,11 @@
           <t>Braunschweig</t>
         </is>
       </c>
-      <c r="M191" t="inlineStr">
-        <is>
-          <t>3.34</t>
-        </is>
-      </c>
-      <c r="N191" t="inlineStr">
-        <is>
-          <t>0.33</t>
-        </is>
+      <c r="M191" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="N191" t="n">
+        <v>0.33</v>
       </c>
       <c r="O191" t="inlineStr">
         <is>
@@ -39436,155 +39088,95 @@
           <t>71%</t>
         </is>
       </c>
-      <c r="Q191" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="R191" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="S191" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="T191" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="U191" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="V191" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="W191" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="X191" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="Y191" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Z191" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA191" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AB191" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC191" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AD191" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AE191" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AF191" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AG191" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AH191" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AI191" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AJ191" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AK191" t="inlineStr">
-        <is>
-          <t>586</t>
-        </is>
-      </c>
-      <c r="AL191" t="inlineStr">
-        <is>
-          <t>369</t>
-        </is>
-      </c>
-      <c r="AM191" t="inlineStr">
-        <is>
-          <t>522</t>
-        </is>
-      </c>
-      <c r="AN191" t="inlineStr">
-        <is>
-          <t>292</t>
-        </is>
-      </c>
-      <c r="AO191" t="inlineStr">
-        <is>
-          <t>135</t>
-        </is>
-      </c>
-      <c r="AP191" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="AQ191" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="AR191" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="AS191" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="AT191" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
+      <c r="Q191" t="n">
+        <v>22</v>
+      </c>
+      <c r="R191" t="n">
+        <v>6</v>
+      </c>
+      <c r="S191" t="n">
+        <v>13</v>
+      </c>
+      <c r="T191" t="n">
+        <v>3</v>
+      </c>
+      <c r="U191" t="n">
+        <v>9</v>
+      </c>
+      <c r="V191" t="n">
+        <v>3</v>
+      </c>
+      <c r="W191" t="n">
+        <v>9</v>
+      </c>
+      <c r="X191" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y191" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z191" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA191" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB191" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC191" t="n">
+        <v>21</v>
+      </c>
+      <c r="AD191" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE191" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF191" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG191" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH191" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI191" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ191" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK191" t="n">
+        <v>586</v>
+      </c>
+      <c r="AL191" t="n">
+        <v>369</v>
+      </c>
+      <c r="AM191" t="n">
+        <v>522</v>
+      </c>
+      <c r="AN191" t="n">
+        <v>292</v>
+      </c>
+      <c r="AO191" t="n">
+        <v>135</v>
+      </c>
+      <c r="AP191" t="n">
+        <v>61</v>
+      </c>
+      <c r="AQ191" t="n">
+        <v>40</v>
+      </c>
+      <c r="AR191" t="n">
+        <v>24</v>
+      </c>
+      <c r="AS191" t="n">
+        <v>118</v>
+      </c>
+      <c r="AT191" t="n">
+        <v>110</v>
       </c>
       <c r="AU191" t="inlineStr">
         <is>
@@ -39625,6 +39217,1300 @@
       <c r="BE191" t="inlineStr"/>
       <c r="BF191" t="inlineStr"/>
     </row>
+    <row r="192">
+      <c r="A192" s="1" t="inlineStr">
+        <is>
+          <t>djSMofvg</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>30.08.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Dankert B.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Stadion An der Alten Försterei
+ (Berlin)</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>22 012</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr"/>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>pzHW4oaE</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>Union Berlin</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>St. Pauli</t>
+        </is>
+      </c>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>0.80</t>
+        </is>
+      </c>
+      <c r="N192" t="inlineStr">
+        <is>
+          <t>0.50</t>
+        </is>
+      </c>
+      <c r="O192" t="inlineStr">
+        <is>
+          <t>43%</t>
+        </is>
+      </c>
+      <c r="P192" t="inlineStr">
+        <is>
+          <t>57%</t>
+        </is>
+      </c>
+      <c r="Q192" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R192" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="S192" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T192" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U192" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V192" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W192" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="X192" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="Y192" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Z192" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA192" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB192" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC192" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AD192" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AE192" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AF192" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AG192" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AH192" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AI192" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AJ192" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AK192" t="inlineStr">
+        <is>
+          <t>340</t>
+        </is>
+      </c>
+      <c r="AL192" t="inlineStr">
+        <is>
+          <t>567</t>
+        </is>
+      </c>
+      <c r="AM192" t="inlineStr">
+        <is>
+          <t>285</t>
+        </is>
+      </c>
+      <c r="AN192" t="inlineStr">
+        <is>
+          <t>508</t>
+        </is>
+      </c>
+      <c r="AO192" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="AP192" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="AQ192" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="AR192" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="AS192" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="AT192" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="AU192" t="inlineStr">
+        <is>
+          <t>hpYJ6izc</t>
+        </is>
+      </c>
+      <c r="AV192" t="inlineStr">
+        <is>
+          <t>svensson bo</t>
+        </is>
+      </c>
+      <c r="AW192" t="inlineStr">
+        <is>
+          <t>0jdIgO6t</t>
+        </is>
+      </c>
+      <c r="AX192" t="inlineStr">
+        <is>
+          <t>blessin alexander</t>
+        </is>
+      </c>
+      <c r="AY192" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ192" t="n">
+        <v>591</v>
+      </c>
+      <c r="BA192" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB192" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC192" t="inlineStr"/>
+      <c r="BD192" t="inlineStr"/>
+      <c r="BE192" t="inlineStr"/>
+      <c r="BF192" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="1" t="inlineStr">
+        <is>
+          <t>SGe0wGjI</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>30.08.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Heft F.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Merkur Spiel-Arena
+ (Düsseldorf)</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>54 600</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr"/>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>ne1oL3y7</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>Dusseldorf</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>dfNCCCzS</t>
+        </is>
+      </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>Hannover</t>
+        </is>
+      </c>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>2.07</t>
+        </is>
+      </c>
+      <c r="N193" t="inlineStr">
+        <is>
+          <t>0.70</t>
+        </is>
+      </c>
+      <c r="O193" t="inlineStr">
+        <is>
+          <t>46%</t>
+        </is>
+      </c>
+      <c r="P193" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="Q193" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="R193" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="S193" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T193" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U193" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="V193" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="W193" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="X193" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="Y193" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Z193" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA193" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB193" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC193" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AD193" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AE193" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AF193" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AG193" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AH193" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AI193" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AJ193" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AK193" t="inlineStr">
+        <is>
+          <t>419</t>
+        </is>
+      </c>
+      <c r="AL193" t="inlineStr">
+        <is>
+          <t>447</t>
+        </is>
+      </c>
+      <c r="AM193" t="inlineStr">
+        <is>
+          <t>383</t>
+        </is>
+      </c>
+      <c r="AN193" t="inlineStr">
+        <is>
+          <t>420</t>
+        </is>
+      </c>
+      <c r="AO193" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="AP193" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="AQ193" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="AR193" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="AS193" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="AT193" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="AU193" t="inlineStr">
+        <is>
+          <t>AoL97rX8</t>
+        </is>
+      </c>
+      <c r="AV193" t="inlineStr">
+        <is>
+          <t>thioune daniel</t>
+        </is>
+      </c>
+      <c r="AW193" t="inlineStr">
+        <is>
+          <t>t0ZPdkUl</t>
+        </is>
+      </c>
+      <c r="AX193" t="inlineStr">
+        <is>
+          <t>leitl stefan</t>
+        </is>
+      </c>
+      <c r="AY193" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ193" t="n">
+        <v>592</v>
+      </c>
+      <c r="BA193" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB193" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC193" t="inlineStr"/>
+      <c r="BD193" t="inlineStr"/>
+      <c r="BE193" t="inlineStr"/>
+      <c r="BF193" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" s="1" t="inlineStr">
+        <is>
+          <t>vs08wy8F</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>30.08.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Schwengers P.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Jahnstadion Regensburg
+ (Regensburg)</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>15 210</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr"/>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>UiCmEP56</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>Regensburg</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>CCQGbik8</t>
+        </is>
+      </c>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>Greuther Furth</t>
+        </is>
+      </c>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="N194" t="inlineStr">
+        <is>
+          <t>2.23</t>
+        </is>
+      </c>
+      <c r="O194" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
+      </c>
+      <c r="P194" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="Q194" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="R194" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="S194" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T194" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="U194" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V194" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="W194" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="X194" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="Y194" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Z194" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA194" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB194" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC194" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AD194" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AE194" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AF194" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AG194" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AH194" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AI194" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AJ194" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AK194" t="inlineStr">
+        <is>
+          <t>426</t>
+        </is>
+      </c>
+      <c r="AL194" t="inlineStr">
+        <is>
+          <t>355</t>
+        </is>
+      </c>
+      <c r="AM194" t="inlineStr">
+        <is>
+          <t>375</t>
+        </is>
+      </c>
+      <c r="AN194" t="inlineStr">
+        <is>
+          <t>296</t>
+        </is>
+      </c>
+      <c r="AO194" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="AP194" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="AQ194" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="AR194" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="AS194" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="AT194" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="AU194" t="inlineStr">
+        <is>
+          <t>zyLSrbZQ</t>
+        </is>
+      </c>
+      <c r="AV194" t="inlineStr">
+        <is>
+          <t>enochs joe</t>
+        </is>
+      </c>
+      <c r="AW194" t="inlineStr">
+        <is>
+          <t>8E86CPuD</t>
+        </is>
+      </c>
+      <c r="AX194" t="inlineStr">
+        <is>
+          <t>zorniger alexander</t>
+        </is>
+      </c>
+      <c r="AY194" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ194" t="n">
+        <v>592</v>
+      </c>
+      <c r="BA194" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB194" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC194" t="inlineStr"/>
+      <c r="BD194" t="inlineStr"/>
+      <c r="BE194" t="inlineStr"/>
+      <c r="BF194" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" s="1" t="inlineStr">
+        <is>
+          <t>6u6i5pie</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>28.08.2024 13:00</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Welz T.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Ernst Abbe Sportfeld
+ (Jena)</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>10 445</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>APNl8MIn</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>Jena</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>4jcj2zMd</t>
+        </is>
+      </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>Bayer Leverkusen
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M195" t="inlineStr"/>
+      <c r="N195" t="inlineStr"/>
+      <c r="O195" t="inlineStr">
+        <is>
+          <t>27%</t>
+        </is>
+      </c>
+      <c r="P195" t="inlineStr">
+        <is>
+          <t>73%</t>
+        </is>
+      </c>
+      <c r="Q195" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R195" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="S195" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T195" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="U195" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V195" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="W195" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X195" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="Y195" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Z195" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA195" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB195" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC195" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AD195" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="AE195" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AF195" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AG195" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AH195" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI195" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AJ195" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AK195" t="inlineStr"/>
+      <c r="AL195" t="inlineStr"/>
+      <c r="AM195" t="inlineStr"/>
+      <c r="AN195" t="inlineStr"/>
+      <c r="AO195" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="AP195" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="AQ195" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="AR195" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="AS195" t="inlineStr"/>
+      <c r="AT195" t="inlineStr"/>
+      <c r="AU195" t="inlineStr">
+        <is>
+          <t>WzqXh8OL</t>
+        </is>
+      </c>
+      <c r="AV195" t="inlineStr">
+        <is>
+          <t>burger henning</t>
+        </is>
+      </c>
+      <c r="AW195" t="inlineStr">
+        <is>
+          <t>hAcTWKKN</t>
+        </is>
+      </c>
+      <c r="AX195" t="inlineStr">
+        <is>
+          <t>alonso xabi</t>
+        </is>
+      </c>
+      <c r="AY195" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ195" t="n">
+        <v>593</v>
+      </c>
+      <c r="BA195" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB195" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC195" t="inlineStr"/>
+      <c r="BD195" t="inlineStr"/>
+      <c r="BE195" t="inlineStr"/>
+      <c r="BF195" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" s="1" t="inlineStr">
+        <is>
+          <t>W67CmLPh</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>27.08.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Jollenbeck M.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Preussenstadion
+ (Munster)</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>12 794</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>12 672</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>zedZaSL7</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>Preussen Munster</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>Stuttgart
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M196" t="inlineStr"/>
+      <c r="N196" t="inlineStr"/>
+      <c r="O196" t="inlineStr">
+        <is>
+          <t>22%</t>
+        </is>
+      </c>
+      <c r="P196" t="inlineStr">
+        <is>
+          <t>78%</t>
+        </is>
+      </c>
+      <c r="Q196" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R196" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="S196" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T196" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="U196" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V196" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W196" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="X196" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="Y196" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Z196" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA196" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB196" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC196" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AD196" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AE196" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AF196" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG196" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AH196" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AI196" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AJ196" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AK196" t="inlineStr"/>
+      <c r="AL196" t="inlineStr"/>
+      <c r="AM196" t="inlineStr"/>
+      <c r="AN196" t="inlineStr"/>
+      <c r="AO196" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="AP196" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="AQ196" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="AR196" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="AS196" t="inlineStr"/>
+      <c r="AT196" t="inlineStr"/>
+      <c r="AU196" t="inlineStr">
+        <is>
+          <t>pdPRS0me</t>
+        </is>
+      </c>
+      <c r="AV196" t="inlineStr">
+        <is>
+          <t>hildmann sascha</t>
+        </is>
+      </c>
+      <c r="AW196" t="inlineStr">
+        <is>
+          <t>GzfvcwRj</t>
+        </is>
+      </c>
+      <c r="AX196" t="inlineStr">
+        <is>
+          <t>hoeness sebastian</t>
+        </is>
+      </c>
+      <c r="AY196" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ196" t="n">
+        <v>593</v>
+      </c>
+      <c r="BA196" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB196" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC196" t="inlineStr"/>
+      <c r="BD196" t="inlineStr"/>
+      <c r="BE196" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF196" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/germany/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
+++ b/data/germany/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BF196"/>
+  <dimension ref="A1:BF206"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39246,15 +39246,11 @@
         </is>
       </c>
       <c r="F192" t="inlineStr"/>
-      <c r="G192" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H192" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G192" t="n">
+        <v>1</v>
+      </c>
+      <c r="H192" t="n">
+        <v>0</v>
       </c>
       <c r="I192" t="inlineStr">
         <is>
@@ -39276,15 +39272,11 @@
           <t>St. Pauli</t>
         </is>
       </c>
-      <c r="M192" t="inlineStr">
-        <is>
-          <t>0.80</t>
-        </is>
-      </c>
-      <c r="N192" t="inlineStr">
-        <is>
-          <t>0.50</t>
-        </is>
+      <c r="M192" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="N192" t="n">
+        <v>0.5</v>
       </c>
       <c r="O192" t="inlineStr">
         <is>
@@ -39296,155 +39288,95 @@
           <t>57%</t>
         </is>
       </c>
-      <c r="Q192" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="R192" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="S192" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="T192" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U192" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="V192" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="W192" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="X192" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="Y192" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Z192" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA192" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB192" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AC192" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AD192" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="AE192" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AF192" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AG192" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AH192" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AI192" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AJ192" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AK192" t="inlineStr">
-        <is>
-          <t>340</t>
-        </is>
-      </c>
-      <c r="AL192" t="inlineStr">
-        <is>
-          <t>567</t>
-        </is>
-      </c>
-      <c r="AM192" t="inlineStr">
-        <is>
-          <t>285</t>
-        </is>
-      </c>
-      <c r="AN192" t="inlineStr">
-        <is>
-          <t>508</t>
-        </is>
-      </c>
-      <c r="AO192" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="AP192" t="inlineStr">
-        <is>
-          <t>137</t>
-        </is>
-      </c>
-      <c r="AQ192" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="AR192" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="AS192" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="AT192" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
+      <c r="Q192" t="n">
+        <v>10</v>
+      </c>
+      <c r="R192" t="n">
+        <v>8</v>
+      </c>
+      <c r="S192" t="n">
+        <v>5</v>
+      </c>
+      <c r="T192" t="n">
+        <v>2</v>
+      </c>
+      <c r="U192" t="n">
+        <v>5</v>
+      </c>
+      <c r="V192" t="n">
+        <v>6</v>
+      </c>
+      <c r="W192" t="n">
+        <v>12</v>
+      </c>
+      <c r="X192" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y192" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z192" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA192" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB192" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC192" t="n">
+        <v>18</v>
+      </c>
+      <c r="AD192" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE192" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF192" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG192" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH192" t="n">
+        <v>11</v>
+      </c>
+      <c r="AI192" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ192" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK192" t="n">
+        <v>340</v>
+      </c>
+      <c r="AL192" t="n">
+        <v>567</v>
+      </c>
+      <c r="AM192" t="n">
+        <v>285</v>
+      </c>
+      <c r="AN192" t="n">
+        <v>508</v>
+      </c>
+      <c r="AO192" t="n">
+        <v>90</v>
+      </c>
+      <c r="AP192" t="n">
+        <v>137</v>
+      </c>
+      <c r="AQ192" t="n">
+        <v>33</v>
+      </c>
+      <c r="AR192" t="n">
+        <v>36</v>
+      </c>
+      <c r="AS192" t="n">
+        <v>125</v>
+      </c>
+      <c r="AT192" t="n">
+        <v>125</v>
       </c>
       <c r="AU192" t="inlineStr">
         <is>
@@ -39514,15 +39446,11 @@
         </is>
       </c>
       <c r="F193" t="inlineStr"/>
-      <c r="G193" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H193" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G193" t="n">
+        <v>1</v>
+      </c>
+      <c r="H193" t="n">
+        <v>0</v>
       </c>
       <c r="I193" t="inlineStr">
         <is>
@@ -39544,15 +39472,11 @@
           <t>Hannover</t>
         </is>
       </c>
-      <c r="M193" t="inlineStr">
-        <is>
-          <t>2.07</t>
-        </is>
-      </c>
-      <c r="N193" t="inlineStr">
-        <is>
-          <t>0.70</t>
-        </is>
+      <c r="M193" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="N193" t="n">
+        <v>0.7</v>
       </c>
       <c r="O193" t="inlineStr">
         <is>
@@ -39564,155 +39488,95 @@
           <t>54%</t>
         </is>
       </c>
-      <c r="Q193" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="R193" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="S193" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="T193" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U193" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="V193" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="W193" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="X193" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="Y193" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Z193" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA193" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB193" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC193" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AD193" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AE193" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AF193" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AG193" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AH193" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AI193" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AJ193" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AK193" t="inlineStr">
-        <is>
-          <t>419</t>
-        </is>
-      </c>
-      <c r="AL193" t="inlineStr">
-        <is>
-          <t>447</t>
-        </is>
-      </c>
-      <c r="AM193" t="inlineStr">
-        <is>
-          <t>383</t>
-        </is>
-      </c>
-      <c r="AN193" t="inlineStr">
-        <is>
-          <t>420</t>
-        </is>
-      </c>
-      <c r="AO193" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="AP193" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="AQ193" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="AR193" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="AS193" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="AT193" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
+      <c r="Q193" t="n">
+        <v>23</v>
+      </c>
+      <c r="R193" t="n">
+        <v>14</v>
+      </c>
+      <c r="S193" t="n">
+        <v>5</v>
+      </c>
+      <c r="T193" t="n">
+        <v>2</v>
+      </c>
+      <c r="U193" t="n">
+        <v>18</v>
+      </c>
+      <c r="V193" t="n">
+        <v>12</v>
+      </c>
+      <c r="W193" t="n">
+        <v>13</v>
+      </c>
+      <c r="X193" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y193" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z193" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA193" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB193" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC193" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD193" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE193" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF193" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG193" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH193" t="n">
+        <v>11</v>
+      </c>
+      <c r="AI193" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ193" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK193" t="n">
+        <v>419</v>
+      </c>
+      <c r="AL193" t="n">
+        <v>447</v>
+      </c>
+      <c r="AM193" t="n">
+        <v>383</v>
+      </c>
+      <c r="AN193" t="n">
+        <v>420</v>
+      </c>
+      <c r="AO193" t="n">
+        <v>79</v>
+      </c>
+      <c r="AP193" t="n">
+        <v>128</v>
+      </c>
+      <c r="AQ193" t="n">
+        <v>51</v>
+      </c>
+      <c r="AR193" t="n">
+        <v>44</v>
+      </c>
+      <c r="AS193" t="n">
+        <v>117</v>
+      </c>
+      <c r="AT193" t="n">
+        <v>115</v>
       </c>
       <c r="AU193" t="inlineStr">
         <is>
@@ -39782,15 +39646,11 @@
         </is>
       </c>
       <c r="F194" t="inlineStr"/>
-      <c r="G194" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H194" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="G194" t="n">
+        <v>0</v>
+      </c>
+      <c r="H194" t="n">
+        <v>4</v>
       </c>
       <c r="I194" t="inlineStr">
         <is>
@@ -39812,15 +39672,11 @@
           <t>Greuther Furth</t>
         </is>
       </c>
-      <c r="M194" t="inlineStr">
-        <is>
-          <t>1.98</t>
-        </is>
-      </c>
-      <c r="N194" t="inlineStr">
-        <is>
-          <t>2.23</t>
-        </is>
+      <c r="M194" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="N194" t="n">
+        <v>2.23</v>
       </c>
       <c r="O194" t="inlineStr">
         <is>
@@ -39832,155 +39688,95 @@
           <t>47%</t>
         </is>
       </c>
-      <c r="Q194" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="R194" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="S194" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="T194" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="U194" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="V194" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="W194" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="X194" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Y194" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Z194" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA194" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AB194" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC194" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AD194" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AE194" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AF194" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AG194" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AH194" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AI194" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AJ194" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AK194" t="inlineStr">
-        <is>
-          <t>426</t>
-        </is>
-      </c>
-      <c r="AL194" t="inlineStr">
-        <is>
-          <t>355</t>
-        </is>
-      </c>
-      <c r="AM194" t="inlineStr">
-        <is>
-          <t>375</t>
-        </is>
-      </c>
-      <c r="AN194" t="inlineStr">
-        <is>
-          <t>296</t>
-        </is>
-      </c>
-      <c r="AO194" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="AP194" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="AQ194" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="AR194" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="AS194" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="AT194" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
+      <c r="Q194" t="n">
+        <v>17</v>
+      </c>
+      <c r="R194" t="n">
+        <v>21</v>
+      </c>
+      <c r="S194" t="n">
+        <v>7</v>
+      </c>
+      <c r="T194" t="n">
+        <v>9</v>
+      </c>
+      <c r="U194" t="n">
+        <v>10</v>
+      </c>
+      <c r="V194" t="n">
+        <v>12</v>
+      </c>
+      <c r="W194" t="n">
+        <v>5</v>
+      </c>
+      <c r="X194" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y194" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z194" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA194" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB194" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC194" t="n">
+        <v>16</v>
+      </c>
+      <c r="AD194" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE194" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF194" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG194" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH194" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI194" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ194" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK194" t="n">
+        <v>426</v>
+      </c>
+      <c r="AL194" t="n">
+        <v>355</v>
+      </c>
+      <c r="AM194" t="n">
+        <v>375</v>
+      </c>
+      <c r="AN194" t="n">
+        <v>296</v>
+      </c>
+      <c r="AO194" t="n">
+        <v>112</v>
+      </c>
+      <c r="AP194" t="n">
+        <v>65</v>
+      </c>
+      <c r="AQ194" t="n">
+        <v>58</v>
+      </c>
+      <c r="AR194" t="n">
+        <v>36</v>
+      </c>
+      <c r="AS194" t="n">
+        <v>114</v>
+      </c>
+      <c r="AT194" t="n">
+        <v>118</v>
       </c>
       <c r="AU194" t="inlineStr">
         <is>
@@ -40054,15 +39850,11 @@
           <t>15 000</t>
         </is>
       </c>
-      <c r="G195" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H195" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G195" t="n">
+        <v>0</v>
+      </c>
+      <c r="H195" t="n">
+        <v>1</v>
       </c>
       <c r="I195" t="inlineStr">
         <is>
@@ -40097,129 +39889,81 @@
           <t>73%</t>
         </is>
       </c>
-      <c r="Q195" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R195" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="S195" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="T195" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="U195" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="V195" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="W195" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="X195" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="Y195" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Z195" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA195" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB195" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC195" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="AD195" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="AE195" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AF195" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AG195" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AH195" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AI195" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AJ195" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="Q195" t="n">
+        <v>4</v>
+      </c>
+      <c r="R195" t="n">
+        <v>14</v>
+      </c>
+      <c r="S195" t="n">
+        <v>1</v>
+      </c>
+      <c r="T195" t="n">
+        <v>7</v>
+      </c>
+      <c r="U195" t="n">
+        <v>3</v>
+      </c>
+      <c r="V195" t="n">
+        <v>7</v>
+      </c>
+      <c r="W195" t="n">
+        <v>4</v>
+      </c>
+      <c r="X195" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y195" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z195" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA195" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB195" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC195" t="n">
+        <v>22</v>
+      </c>
+      <c r="AD195" t="n">
+        <v>31</v>
+      </c>
+      <c r="AE195" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF195" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG195" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH195" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI195" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ195" t="n">
+        <v>1</v>
       </c>
       <c r="AK195" t="inlineStr"/>
       <c r="AL195" t="inlineStr"/>
       <c r="AM195" t="inlineStr"/>
       <c r="AN195" t="inlineStr"/>
-      <c r="AO195" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="AP195" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="AQ195" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="AR195" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
+      <c r="AO195" t="n">
+        <v>78</v>
+      </c>
+      <c r="AP195" t="n">
+        <v>102</v>
+      </c>
+      <c r="AQ195" t="n">
+        <v>59</v>
+      </c>
+      <c r="AR195" t="n">
+        <v>90</v>
       </c>
       <c r="AS195" t="inlineStr"/>
       <c r="AT195" t="inlineStr"/>
@@ -40295,15 +40039,11 @@
           <t>12 672</t>
         </is>
       </c>
-      <c r="G196" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H196" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="G196" t="n">
+        <v>0</v>
+      </c>
+      <c r="H196" t="n">
+        <v>5</v>
       </c>
       <c r="I196" t="inlineStr">
         <is>
@@ -40338,129 +40078,81 @@
           <t>78%</t>
         </is>
       </c>
-      <c r="Q196" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R196" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="S196" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T196" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="U196" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="V196" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="W196" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="X196" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="Y196" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Z196" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA196" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB196" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC196" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AD196" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AE196" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AF196" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG196" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AH196" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AI196" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AJ196" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="Q196" t="n">
+        <v>5</v>
+      </c>
+      <c r="R196" t="n">
+        <v>13</v>
+      </c>
+      <c r="S196" t="n">
+        <v>0</v>
+      </c>
+      <c r="T196" t="n">
+        <v>7</v>
+      </c>
+      <c r="U196" t="n">
+        <v>4</v>
+      </c>
+      <c r="V196" t="n">
+        <v>2</v>
+      </c>
+      <c r="W196" t="n">
+        <v>12</v>
+      </c>
+      <c r="X196" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y196" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z196" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA196" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB196" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC196" t="n">
+        <v>21</v>
+      </c>
+      <c r="AD196" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE196" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF196" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG196" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH196" t="n">
+        <v>12</v>
+      </c>
+      <c r="AI196" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ196" t="n">
+        <v>1</v>
       </c>
       <c r="AK196" t="inlineStr"/>
       <c r="AL196" t="inlineStr"/>
       <c r="AM196" t="inlineStr"/>
       <c r="AN196" t="inlineStr"/>
-      <c r="AO196" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="AP196" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="AQ196" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="AR196" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
+      <c r="AO196" t="n">
+        <v>58</v>
+      </c>
+      <c r="AP196" t="n">
+        <v>90</v>
+      </c>
+      <c r="AQ196" t="n">
+        <v>28</v>
+      </c>
+      <c r="AR196" t="n">
+        <v>69</v>
       </c>
       <c r="AS196" t="inlineStr"/>
       <c r="AT196" t="inlineStr"/>
@@ -40500,16 +40192,2736 @@
       </c>
       <c r="BC196" t="inlineStr"/>
       <c r="BD196" t="inlineStr"/>
-      <c r="BE196" t="inlineStr">
+      <c r="BE196" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF196" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="1" t="inlineStr">
+        <is>
+          <t>AVR8vwXP</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>31.08.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Jollenbeck M.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>BayArena
+ (Leverkusen)</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>30 210</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>28 000</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>4jcj2zMd</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>Bayer Leverkusen</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>KbS1suSm</t>
+        </is>
+      </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>RB Leipzig</t>
+        </is>
+      </c>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>2.93</t>
+        </is>
+      </c>
+      <c r="N197" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="O197" t="inlineStr">
+        <is>
+          <t>56%</t>
+        </is>
+      </c>
+      <c r="P197" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
+      <c r="Q197" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="R197" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S197" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T197" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U197" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="V197" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W197" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="X197" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y197" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="Z197" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA197" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB197" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC197" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AD197" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AE197" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="BF196" t="inlineStr">
+      <c r="AF197" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AG197" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AH197" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AI197" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AJ197" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AK197" t="inlineStr">
+        <is>
+          <t>578</t>
+        </is>
+      </c>
+      <c r="AL197" t="inlineStr">
+        <is>
+          <t>352</t>
+        </is>
+      </c>
+      <c r="AM197" t="inlineStr">
+        <is>
+          <t>533</t>
+        </is>
+      </c>
+      <c r="AN197" t="inlineStr">
+        <is>
+          <t>313</t>
+        </is>
+      </c>
+      <c r="AO197" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="AP197" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="AQ197" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="AR197" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="AS197" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="AT197" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="AU197" t="inlineStr">
+        <is>
+          <t>hAcTWKKN</t>
+        </is>
+      </c>
+      <c r="AV197" t="inlineStr">
+        <is>
+          <t>alonso xabi</t>
+        </is>
+      </c>
+      <c r="AW197" t="inlineStr">
+        <is>
+          <t>pfoInmcq</t>
+        </is>
+      </c>
+      <c r="AX197" t="inlineStr">
+        <is>
+          <t>rose marko</t>
+        </is>
+      </c>
+      <c r="AY197" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ197" t="n">
+        <v>591</v>
+      </c>
+      <c r="BA197" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB197" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC197" t="inlineStr"/>
+      <c r="BD197" t="inlineStr"/>
+      <c r="BE197" t="inlineStr"/>
+      <c r="BF197" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" s="1" t="inlineStr">
+        <is>
+          <t>U3QUqY85</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>31.08.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Storks S.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Vonovia Ruhrstadion
+ (Bochum)</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>26 000</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>26 000</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>8Y2m6ADe</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>Bochum</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>88HSzjDr</t>
+        </is>
+      </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>B. Monchengladbach</t>
+        </is>
+      </c>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>1.07</t>
+        </is>
+      </c>
+      <c r="N198" t="inlineStr">
+        <is>
+          <t>2.84</t>
+        </is>
+      </c>
+      <c r="O198" t="inlineStr">
+        <is>
+          <t>43%</t>
+        </is>
+      </c>
+      <c r="P198" t="inlineStr">
+        <is>
+          <t>57%</t>
+        </is>
+      </c>
+      <c r="Q198" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R198" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="S198" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
+      <c r="T198" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="U198" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="V198" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="W198" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="X198" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Y198" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Z198" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA198" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB198" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC198" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AD198" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AE198" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AF198" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AG198" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AH198" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AI198" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AJ198" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK198" t="inlineStr">
+        <is>
+          <t>348</t>
+        </is>
+      </c>
+      <c r="AL198" t="inlineStr">
+        <is>
+          <t>557</t>
+        </is>
+      </c>
+      <c r="AM198" t="inlineStr">
+        <is>
+          <t>294</t>
+        </is>
+      </c>
+      <c r="AN198" t="inlineStr">
+        <is>
+          <t>528</t>
+        </is>
+      </c>
+      <c r="AO198" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="AP198" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="AQ198" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="AR198" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="AS198" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="AT198" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="AU198" t="inlineStr">
+        <is>
+          <t>8f6APkLc</t>
+        </is>
+      </c>
+      <c r="AV198" t="inlineStr">
+        <is>
+          <t>zeidler peter</t>
+        </is>
+      </c>
+      <c r="AW198" t="inlineStr">
+        <is>
+          <t>M5BRZDsC</t>
+        </is>
+      </c>
+      <c r="AX198" t="inlineStr">
+        <is>
+          <t>seoane gerardo</t>
+        </is>
+      </c>
+      <c r="AY198" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ198" t="n">
+        <v>591</v>
+      </c>
+      <c r="BA198" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB198" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC198" t="inlineStr"/>
+      <c r="BD198" t="inlineStr"/>
+      <c r="BE198" t="inlineStr"/>
+      <c r="BF198" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" s="1" t="inlineStr">
+        <is>
+          <t>AgAeVYgC</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>31.08.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Badstubner F.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>Deutsche Bank Park
+ (Frankfurt)</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>58 000</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>57 100</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>Eintracht Frankfurt</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>hQAtP9Sl</t>
+        </is>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>Hoffenheim</t>
+        </is>
+      </c>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="N199" t="inlineStr">
+        <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="O199" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="P199" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="Q199" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="R199" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S199" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T199" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U199" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V199" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="W199" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="X199" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="Y199" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Z199" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA199" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB199" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC199" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AD199" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AE199" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AF199" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AG199" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AH199" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AI199" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AJ199" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AK199" t="inlineStr">
+        <is>
+          <t>460</t>
+        </is>
+      </c>
+      <c r="AL199" t="inlineStr">
+        <is>
+          <t>450</t>
+        </is>
+      </c>
+      <c r="AM199" t="inlineStr">
+        <is>
+          <t>415</t>
+        </is>
+      </c>
+      <c r="AN199" t="inlineStr">
+        <is>
+          <t>421</t>
+        </is>
+      </c>
+      <c r="AO199" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="AP199" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="AQ199" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="AR199" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="AS199" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="AT199" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="AU199" t="inlineStr">
+        <is>
+          <t>UgdQz0fK</t>
+        </is>
+      </c>
+      <c r="AV199" t="inlineStr">
+        <is>
+          <t>toppmoller dino</t>
+        </is>
+      </c>
+      <c r="AW199" t="inlineStr">
+        <is>
+          <t>KUx4Q7x1</t>
+        </is>
+      </c>
+      <c r="AX199" t="inlineStr">
+        <is>
+          <t>matarazzo pellegrino</t>
+        </is>
+      </c>
+      <c r="AY199" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ199" t="n">
+        <v>591</v>
+      </c>
+      <c r="BA199" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB199" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC199" t="inlineStr"/>
+      <c r="BD199" t="inlineStr"/>
+      <c r="BE199" t="inlineStr"/>
+      <c r="BF199" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" s="1" t="inlineStr">
+        <is>
+          <t>QVJwrCwI</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>31.08.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Exner F.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Holstein-Stadion
+ (Kiel)</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>15 034</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>15 034</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>63WsD2ei</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>Holstein Kiel</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>nwkTahLL</t>
+        </is>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>Wolfsburg</t>
+        </is>
+      </c>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>1.06</t>
+        </is>
+      </c>
+      <c r="N200" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="O200" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="P200" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="Q200" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R200" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="S200" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T200" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U200" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V200" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="W200" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="X200" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="Y200" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Z200" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA200" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB200" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC200" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AD200" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AE200" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AF200" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AG200" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AH200" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AI200" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AJ200" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AK200" t="inlineStr">
+        <is>
+          <t>420</t>
+        </is>
+      </c>
+      <c r="AL200" t="inlineStr">
+        <is>
+          <t>335</t>
+        </is>
+      </c>
+      <c r="AM200" t="inlineStr">
+        <is>
+          <t>370</t>
+        </is>
+      </c>
+      <c r="AN200" t="inlineStr">
+        <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="AO200" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="AP200" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="AQ200" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="AR200" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="AS200" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="AT200" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="AU200" t="inlineStr">
+        <is>
+          <t>A15eUM4C</t>
+        </is>
+      </c>
+      <c r="AV200" t="inlineStr">
+        <is>
+          <t>rapp marcel</t>
+        </is>
+      </c>
+      <c r="AW200" t="inlineStr">
+        <is>
+          <t>f3ddUIXs</t>
+        </is>
+      </c>
+      <c r="AX200" t="inlineStr">
+        <is>
+          <t>hasenhuttl ralph</t>
+        </is>
+      </c>
+      <c r="AY200" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ200" t="n">
+        <v>591</v>
+      </c>
+      <c r="BA200" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB200" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC200" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BD200" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE200" t="inlineStr"/>
+      <c r="BF200" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" s="1" t="inlineStr">
+        <is>
+          <t>61DvZGfm</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>31.08.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Gerach T.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>MHPArena
+ (Stuttgart)</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>60 449</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>59 000</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>Stuttgart</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>EuakNmc1</t>
+        </is>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>Mainz</t>
+        </is>
+      </c>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>5.21</t>
+        </is>
+      </c>
+      <c r="N201" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="O201" t="inlineStr">
+        <is>
+          <t>62%</t>
+        </is>
+      </c>
+      <c r="P201" t="inlineStr">
+        <is>
+          <t>38%</t>
+        </is>
+      </c>
+      <c r="Q201" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="R201" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="S201" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="T201" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="U201" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="V201" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W201" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="X201" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y201" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="Z201" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA201" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB201" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC201" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AD201" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AE201" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AF201" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AG201" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AH201" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AI201" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AJ201" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AK201" t="inlineStr">
+        <is>
+          <t>529</t>
+        </is>
+      </c>
+      <c r="AL201" t="inlineStr">
+        <is>
+          <t>301</t>
+        </is>
+      </c>
+      <c r="AM201" t="inlineStr">
+        <is>
+          <t>501</t>
+        </is>
+      </c>
+      <c r="AN201" t="inlineStr">
+        <is>
+          <t>259</t>
+        </is>
+      </c>
+      <c r="AO201" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="AP201" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="AQ201" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="AR201" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AS201" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="AT201" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="AU201" t="inlineStr">
+        <is>
+          <t>GzfvcwRj</t>
+        </is>
+      </c>
+      <c r="AV201" t="inlineStr">
+        <is>
+          <t>hoeness sebastian</t>
+        </is>
+      </c>
+      <c r="AW201" t="inlineStr">
+        <is>
+          <t>vZA6VYpf</t>
+        </is>
+      </c>
+      <c r="AX201" t="inlineStr">
+        <is>
+          <t>henriksen bo</t>
+        </is>
+      </c>
+      <c r="AY201" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ201" t="n">
+        <v>591</v>
+      </c>
+      <c r="BA201" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB201" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC201" t="inlineStr"/>
+      <c r="BD201" t="inlineStr"/>
+      <c r="BE201" t="inlineStr"/>
+      <c r="BF201" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" s="1" t="inlineStr">
+        <is>
+          <t>0OYDmG9t</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>31.08.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Hartmann R.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>Weserstadion
+ (Bremen)</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>42 100</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>42 100</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>Ig1f1fy3</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>Werder Bremen</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>Dortmund</t>
+        </is>
+      </c>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>0.33</t>
+        </is>
+      </c>
+      <c r="N202" t="inlineStr">
+        <is>
+          <t>0.76</t>
+        </is>
+      </c>
+      <c r="O202" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="P202" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="Q202" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R202" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="S202" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T202" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U202" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V202" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="W202" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="X202" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="Y202" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Z202" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA202" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AB202" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC202" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AD202" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AE202" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AF202" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AG202" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AH202" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AI202" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AJ202" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AK202" t="inlineStr">
+        <is>
+          <t>449</t>
+        </is>
+      </c>
+      <c r="AL202" t="inlineStr">
+        <is>
+          <t>526</t>
+        </is>
+      </c>
+      <c r="AM202" t="inlineStr">
+        <is>
+          <t>409</t>
+        </is>
+      </c>
+      <c r="AN202" t="inlineStr">
+        <is>
+          <t>506</t>
+        </is>
+      </c>
+      <c r="AO202" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="AP202" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="AQ202" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="AR202" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="AS202" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="AT202" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="AU202" t="inlineStr">
+        <is>
+          <t>4fuCGs9P</t>
+        </is>
+      </c>
+      <c r="AV202" t="inlineStr">
+        <is>
+          <t>werner ole</t>
+        </is>
+      </c>
+      <c r="AW202" t="inlineStr">
+        <is>
+          <t>IkCftsQm</t>
+        </is>
+      </c>
+      <c r="AX202" t="inlineStr">
+        <is>
+          <t>sahin nuri</t>
+        </is>
+      </c>
+      <c r="AY202" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ202" t="n">
+        <v>591</v>
+      </c>
+      <c r="BA202" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB202" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC202" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BD202" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BE202" t="inlineStr"/>
+      <c r="BF202" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" s="1" t="inlineStr">
+        <is>
+          <t>jLJDHgod</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>31.08.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Brand B.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>Fritz Walter Stadion
+ (Kaiserslautern)</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>49 500</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr"/>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>naWckLmC</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>Kaiserslautern</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>2y0u8Wrq</t>
+        </is>
+      </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>Hertha Berlin</t>
+        </is>
+      </c>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>2.85</t>
+        </is>
+      </c>
+      <c r="N203" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="O203" t="inlineStr">
+        <is>
+          <t>39%</t>
+        </is>
+      </c>
+      <c r="P203" t="inlineStr">
+        <is>
+          <t>61%</t>
+        </is>
+      </c>
+      <c r="Q203" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="R203" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="S203" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="T203" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="U203" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="V203" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="W203" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="X203" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y203" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="Z203" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA203" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB203" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC203" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AD203" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AE203" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AF203" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AG203" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AH203" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AI203" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AJ203" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AK203" t="inlineStr">
+        <is>
+          <t>249</t>
+        </is>
+      </c>
+      <c r="AL203" t="inlineStr">
+        <is>
+          <t>462</t>
+        </is>
+      </c>
+      <c r="AM203" t="inlineStr">
+        <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="AN203" t="inlineStr">
+        <is>
+          <t>416</t>
+        </is>
+      </c>
+      <c r="AO203" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="AP203" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="AQ203" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="AR203" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="AS203" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="AT203" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="AU203" t="inlineStr">
+        <is>
+          <t>4bJLk19p</t>
+        </is>
+      </c>
+      <c r="AV203" t="inlineStr">
+        <is>
+          <t>anfang marcus</t>
+        </is>
+      </c>
+      <c r="AW203" t="inlineStr">
+        <is>
+          <t>YmfcAeCo</t>
+        </is>
+      </c>
+      <c r="AX203" t="inlineStr">
+        <is>
+          <t>fiel cristian</t>
+        </is>
+      </c>
+      <c r="AY203" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ203" t="n">
+        <v>592</v>
+      </c>
+      <c r="BA203" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB203" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC203" t="inlineStr"/>
+      <c r="BD203" t="inlineStr"/>
+      <c r="BE203" t="inlineStr"/>
+      <c r="BF203" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" s="1" t="inlineStr">
+        <is>
+          <t>A33XyOWA</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>31.08.2024 08:00</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Benen L.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>Waldstadion Kaiserlinde
+ (Spiesen-Elversberg)</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>9 970</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>9 443</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>6in2Eknb</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>Elversberg</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>S0hPB9rA</t>
+        </is>
+      </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>Darmstadt</t>
+        </is>
+      </c>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>2.31</t>
+        </is>
+      </c>
+      <c r="N204" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="O204" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="P204" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="Q204" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="R204" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="S204" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T204" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U204" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="V204" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="W204" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="X204" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y204" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Z204" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AA204" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB204" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC204" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AD204" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AE204" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AF204" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG204" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AH204" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AI204" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AJ204" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AK204" t="inlineStr">
+        <is>
+          <t>423</t>
+        </is>
+      </c>
+      <c r="AL204" t="inlineStr">
+        <is>
+          <t>429</t>
+        </is>
+      </c>
+      <c r="AM204" t="inlineStr">
+        <is>
+          <t>383</t>
+        </is>
+      </c>
+      <c r="AN204" t="inlineStr">
+        <is>
+          <t>397</t>
+        </is>
+      </c>
+      <c r="AO204" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="AP204" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="AQ204" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="AR204" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="AS204" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="AT204" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="AU204" t="inlineStr">
+        <is>
+          <t>8E8qmw3d</t>
+        </is>
+      </c>
+      <c r="AV204" t="inlineStr">
+        <is>
+          <t>steffen horst</t>
+        </is>
+      </c>
+      <c r="AW204" t="inlineStr">
+        <is>
+          <t>MDhPV0RQ</t>
+        </is>
+      </c>
+      <c r="AX204" t="inlineStr">
+        <is>
+          <t>lieberknecht torsten</t>
+        </is>
+      </c>
+      <c r="AY204" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ204" t="n">
+        <v>592</v>
+      </c>
+      <c r="BA204" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB204" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC204" t="inlineStr"/>
+      <c r="BD204" t="inlineStr"/>
+      <c r="BE204" t="inlineStr"/>
+      <c r="BF204" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" s="1" t="inlineStr">
+        <is>
+          <t>0Ug8yfLU</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>31.08.2024 08:00</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Siebert D.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>Volksparkstadion
+ (Hamburg)</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>57 274</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>57 000</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>v9k3aY5F</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>Hamburger SV</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>zedZaSL7</t>
+        </is>
+      </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>Preussen Munster</t>
+        </is>
+      </c>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="N205" t="inlineStr">
+        <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="O205" t="inlineStr">
+        <is>
+          <t>63%</t>
+        </is>
+      </c>
+      <c r="P205" t="inlineStr">
+        <is>
+          <t>37%</t>
+        </is>
+      </c>
+      <c r="Q205" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R205" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="S205" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T205" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="U205" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V205" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="W205" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="X205" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Y205" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Z205" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AA205" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB205" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC205" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AD205" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AE205" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AF205" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AG205" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AH205" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AI205" t="inlineStr"/>
+      <c r="AJ205" t="inlineStr"/>
+      <c r="AK205" t="inlineStr">
+        <is>
+          <t>538</t>
+        </is>
+      </c>
+      <c r="AL205" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="AM205" t="inlineStr">
+        <is>
+          <t>529</t>
+        </is>
+      </c>
+      <c r="AN205" t="inlineStr">
+        <is>
+          <t>261</t>
+        </is>
+      </c>
+      <c r="AO205" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="AP205" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="AQ205" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="AR205" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="AS205" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="AT205" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="AU205" t="inlineStr">
+        <is>
+          <t>EDRZkDzS</t>
+        </is>
+      </c>
+      <c r="AV205" t="inlineStr">
+        <is>
+          <t>baumgart steffen</t>
+        </is>
+      </c>
+      <c r="AW205" t="inlineStr">
+        <is>
+          <t>pdPRS0me</t>
+        </is>
+      </c>
+      <c r="AX205" t="inlineStr">
+        <is>
+          <t>hildmann sascha</t>
+        </is>
+      </c>
+      <c r="AY205" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ205" t="n">
+        <v>592</v>
+      </c>
+      <c r="BA205" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB205" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC205" t="inlineStr"/>
+      <c r="BD205" t="inlineStr"/>
+      <c r="BE205" t="inlineStr"/>
+      <c r="BF205" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" s="1" t="inlineStr">
+        <is>
+          <t>fgQ4JFGq</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>31.08.2024 08:00</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Brych D. F.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>Max-Morlock-Stadion
+ (Nuremberg)</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>50 000</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>31 581</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>6FDqshzF</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>Nurnberg</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>YFuz2RLm</t>
+        </is>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>Magdeburg</t>
+        </is>
+      </c>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="N206" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+      <c r="O206" t="inlineStr">
+        <is>
+          <t>42%</t>
+        </is>
+      </c>
+      <c r="P206" t="inlineStr">
+        <is>
+          <t>58%</t>
+        </is>
+      </c>
+      <c r="Q206" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R206" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="S206" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T206" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="U206" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V206" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="W206" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="X206" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y206" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Z206" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA206" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB206" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC206" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AD206" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AE206" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AF206" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AG206" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AH206" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AI206" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AJ206" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AK206" t="inlineStr">
+        <is>
+          <t>323</t>
+        </is>
+      </c>
+      <c r="AL206" t="inlineStr">
+        <is>
+          <t>478</t>
+        </is>
+      </c>
+      <c r="AM206" t="inlineStr">
+        <is>
+          <t>290</t>
+        </is>
+      </c>
+      <c r="AN206" t="inlineStr">
+        <is>
+          <t>454</t>
+        </is>
+      </c>
+      <c r="AO206" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="AP206" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="AQ206" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AR206" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="AS206" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="AT206" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="AU206" t="inlineStr">
+        <is>
+          <t>tO31cZrF</t>
+        </is>
+      </c>
+      <c r="AV206" t="inlineStr">
+        <is>
+          <t>klose miroslav</t>
+        </is>
+      </c>
+      <c r="AW206" t="inlineStr">
+        <is>
+          <t>IgZoGKFn</t>
+        </is>
+      </c>
+      <c r="AX206" t="inlineStr">
+        <is>
+          <t>titz christian</t>
+        </is>
+      </c>
+      <c r="AY206" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ206" t="n">
+        <v>592</v>
+      </c>
+      <c r="BA206" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB206" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC206" t="inlineStr"/>
+      <c r="BD206" t="inlineStr"/>
+      <c r="BE206" t="inlineStr"/>
+      <c r="BF206" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/germany/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
+++ b/data/germany/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BF206"/>
+  <dimension ref="A1:BF211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40232,15 +40232,11 @@
           <t>28 000</t>
         </is>
       </c>
-      <c r="G197" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H197" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="G197" t="n">
+        <v>2</v>
+      </c>
+      <c r="H197" t="n">
+        <v>3</v>
       </c>
       <c r="I197" t="inlineStr">
         <is>
@@ -40262,15 +40258,11 @@
           <t>RB Leipzig</t>
         </is>
       </c>
-      <c r="M197" t="inlineStr">
-        <is>
-          <t>2.93</t>
-        </is>
-      </c>
-      <c r="N197" t="inlineStr">
-        <is>
-          <t>1.39</t>
-        </is>
+      <c r="M197" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="N197" t="n">
+        <v>1.39</v>
       </c>
       <c r="O197" t="inlineStr">
         <is>
@@ -40282,155 +40274,95 @@
           <t>44%</t>
         </is>
       </c>
-      <c r="Q197" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="R197" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="S197" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="T197" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U197" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="V197" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="W197" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="X197" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y197" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="Z197" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA197" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB197" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AC197" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AD197" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AE197" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AF197" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AG197" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AH197" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AI197" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AJ197" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AK197" t="inlineStr">
-        <is>
-          <t>578</t>
-        </is>
-      </c>
-      <c r="AL197" t="inlineStr">
-        <is>
-          <t>352</t>
-        </is>
-      </c>
-      <c r="AM197" t="inlineStr">
-        <is>
-          <t>533</t>
-        </is>
-      </c>
-      <c r="AN197" t="inlineStr">
-        <is>
-          <t>313</t>
-        </is>
-      </c>
-      <c r="AO197" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="AP197" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="AQ197" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="AR197" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="AS197" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="AT197" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
+      <c r="Q197" t="n">
+        <v>27</v>
+      </c>
+      <c r="R197" t="n">
+        <v>10</v>
+      </c>
+      <c r="S197" t="n">
+        <v>10</v>
+      </c>
+      <c r="T197" t="n">
+        <v>4</v>
+      </c>
+      <c r="U197" t="n">
+        <v>17</v>
+      </c>
+      <c r="V197" t="n">
+        <v>6</v>
+      </c>
+      <c r="W197" t="n">
+        <v>14</v>
+      </c>
+      <c r="X197" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y197" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z197" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA197" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB197" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC197" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD197" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE197" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF197" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG197" t="n">
+        <v>7</v>
+      </c>
+      <c r="AH197" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI197" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ197" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK197" t="n">
+        <v>578</v>
+      </c>
+      <c r="AL197" t="n">
+        <v>352</v>
+      </c>
+      <c r="AM197" t="n">
+        <v>533</v>
+      </c>
+      <c r="AN197" t="n">
+        <v>313</v>
+      </c>
+      <c r="AO197" t="n">
+        <v>114</v>
+      </c>
+      <c r="AP197" t="n">
+        <v>68</v>
+      </c>
+      <c r="AQ197" t="n">
+        <v>77</v>
+      </c>
+      <c r="AR197" t="n">
+        <v>28</v>
+      </c>
+      <c r="AS197" t="n">
+        <v>117</v>
+      </c>
+      <c r="AT197" t="n">
+        <v>118</v>
       </c>
       <c r="AU197" t="inlineStr">
         <is>
@@ -40504,15 +40436,11 @@
           <t>26 000</t>
         </is>
       </c>
-      <c r="G198" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H198" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G198" t="n">
+        <v>0</v>
+      </c>
+      <c r="H198" t="n">
+        <v>2</v>
       </c>
       <c r="I198" t="inlineStr">
         <is>
@@ -40534,15 +40462,11 @@
           <t>B. Monchengladbach</t>
         </is>
       </c>
-      <c r="M198" t="inlineStr">
-        <is>
-          <t>1.07</t>
-        </is>
-      </c>
-      <c r="N198" t="inlineStr">
-        <is>
-          <t>2.84</t>
-        </is>
+      <c r="M198" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N198" t="n">
+        <v>2.84</v>
       </c>
       <c r="O198" t="inlineStr">
         <is>
@@ -40554,155 +40478,95 @@
           <t>57%</t>
         </is>
       </c>
-      <c r="Q198" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="R198" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="S198" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="T198" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="U198" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="V198" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="W198" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="X198" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="Y198" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Z198" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA198" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB198" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC198" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="AD198" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="AE198" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AF198" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AG198" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AH198" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AI198" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AJ198" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK198" t="inlineStr">
-        <is>
-          <t>348</t>
-        </is>
-      </c>
-      <c r="AL198" t="inlineStr">
-        <is>
-          <t>557</t>
-        </is>
-      </c>
-      <c r="AM198" t="inlineStr">
-        <is>
-          <t>294</t>
-        </is>
-      </c>
-      <c r="AN198" t="inlineStr">
-        <is>
-          <t>528</t>
-        </is>
-      </c>
-      <c r="AO198" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="AP198" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="AQ198" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="AR198" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="AS198" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="AT198" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
+      <c r="Q198" t="n">
+        <v>16</v>
+      </c>
+      <c r="R198" t="n">
+        <v>15</v>
+      </c>
+      <c r="S198" t="n">
+        <v>4</v>
+      </c>
+      <c r="T198" t="n">
+        <v>6</v>
+      </c>
+      <c r="U198" t="n">
+        <v>12</v>
+      </c>
+      <c r="V198" t="n">
+        <v>9</v>
+      </c>
+      <c r="W198" t="n">
+        <v>12</v>
+      </c>
+      <c r="X198" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y198" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z198" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA198" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB198" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC198" t="n">
+        <v>23</v>
+      </c>
+      <c r="AD198" t="n">
+        <v>27</v>
+      </c>
+      <c r="AE198" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF198" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG198" t="n">
+        <v>9</v>
+      </c>
+      <c r="AH198" t="n">
+        <v>10</v>
+      </c>
+      <c r="AI198" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ198" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK198" t="n">
+        <v>348</v>
+      </c>
+      <c r="AL198" t="n">
+        <v>557</v>
+      </c>
+      <c r="AM198" t="n">
+        <v>294</v>
+      </c>
+      <c r="AN198" t="n">
+        <v>528</v>
+      </c>
+      <c r="AO198" t="n">
+        <v>114</v>
+      </c>
+      <c r="AP198" t="n">
+        <v>77</v>
+      </c>
+      <c r="AQ198" t="n">
+        <v>45</v>
+      </c>
+      <c r="AR198" t="n">
+        <v>48</v>
+      </c>
+      <c r="AS198" t="n">
+        <v>114</v>
+      </c>
+      <c r="AT198" t="n">
+        <v>111</v>
       </c>
       <c r="AU198" t="inlineStr">
         <is>
@@ -40776,15 +40640,11 @@
           <t>57 100</t>
         </is>
       </c>
-      <c r="G199" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H199" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G199" t="n">
+        <v>3</v>
+      </c>
+      <c r="H199" t="n">
+        <v>1</v>
       </c>
       <c r="I199" t="inlineStr">
         <is>
@@ -40806,15 +40666,11 @@
           <t>Hoffenheim</t>
         </is>
       </c>
-      <c r="M199" t="inlineStr">
-        <is>
-          <t>2.60</t>
-        </is>
-      </c>
-      <c r="N199" t="inlineStr">
-        <is>
-          <t>1.29</t>
-        </is>
+      <c r="M199" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="N199" t="n">
+        <v>1.29</v>
       </c>
       <c r="O199" t="inlineStr">
         <is>
@@ -40826,155 +40682,95 @@
           <t>50%</t>
         </is>
       </c>
-      <c r="Q199" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="R199" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="S199" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="T199" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="U199" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="V199" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="W199" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="X199" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="Y199" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Z199" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA199" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB199" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC199" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AD199" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AE199" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AF199" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AG199" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AH199" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AI199" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ199" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AK199" t="inlineStr">
-        <is>
-          <t>460</t>
-        </is>
-      </c>
-      <c r="AL199" t="inlineStr">
-        <is>
-          <t>450</t>
-        </is>
-      </c>
-      <c r="AM199" t="inlineStr">
-        <is>
-          <t>415</t>
-        </is>
-      </c>
-      <c r="AN199" t="inlineStr">
-        <is>
-          <t>421</t>
-        </is>
-      </c>
-      <c r="AO199" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="AP199" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="AQ199" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="AR199" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="AS199" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="AT199" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
+      <c r="Q199" t="n">
+        <v>17</v>
+      </c>
+      <c r="R199" t="n">
+        <v>10</v>
+      </c>
+      <c r="S199" t="n">
+        <v>7</v>
+      </c>
+      <c r="T199" t="n">
+        <v>3</v>
+      </c>
+      <c r="U199" t="n">
+        <v>10</v>
+      </c>
+      <c r="V199" t="n">
+        <v>7</v>
+      </c>
+      <c r="W199" t="n">
+        <v>11</v>
+      </c>
+      <c r="X199" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y199" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z199" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA199" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB199" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC199" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD199" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE199" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF199" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG199" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH199" t="n">
+        <v>10</v>
+      </c>
+      <c r="AI199" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ199" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK199" t="n">
+        <v>460</v>
+      </c>
+      <c r="AL199" t="n">
+        <v>450</v>
+      </c>
+      <c r="AM199" t="n">
+        <v>415</v>
+      </c>
+      <c r="AN199" t="n">
+        <v>421</v>
+      </c>
+      <c r="AO199" t="n">
+        <v>102</v>
+      </c>
+      <c r="AP199" t="n">
+        <v>94</v>
+      </c>
+      <c r="AQ199" t="n">
+        <v>40</v>
+      </c>
+      <c r="AR199" t="n">
+        <v>39</v>
+      </c>
+      <c r="AS199" t="n">
+        <v>116</v>
+      </c>
+      <c r="AT199" t="n">
+        <v>117</v>
       </c>
       <c r="AU199" t="inlineStr">
         <is>
@@ -41048,15 +40844,11 @@
           <t>15 034</t>
         </is>
       </c>
-      <c r="G200" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H200" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G200" t="n">
+        <v>0</v>
+      </c>
+      <c r="H200" t="n">
+        <v>2</v>
       </c>
       <c r="I200" t="inlineStr">
         <is>
@@ -41078,15 +40870,11 @@
           <t>Wolfsburg</t>
         </is>
       </c>
-      <c r="M200" t="inlineStr">
-        <is>
-          <t>1.06</t>
-        </is>
-      </c>
-      <c r="N200" t="inlineStr">
-        <is>
-          <t>1.38</t>
-        </is>
+      <c r="M200" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N200" t="n">
+        <v>1.38</v>
       </c>
       <c r="O200" t="inlineStr">
         <is>
@@ -41098,155 +40886,95 @@
           <t>48%</t>
         </is>
       </c>
-      <c r="Q200" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="R200" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="S200" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="T200" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U200" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V200" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="W200" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="X200" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="Y200" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Z200" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA200" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB200" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC200" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="AD200" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AE200" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AF200" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AG200" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AH200" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AI200" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AJ200" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AK200" t="inlineStr">
-        <is>
-          <t>420</t>
-        </is>
-      </c>
-      <c r="AL200" t="inlineStr">
-        <is>
-          <t>335</t>
-        </is>
-      </c>
-      <c r="AM200" t="inlineStr">
-        <is>
-          <t>370</t>
-        </is>
-      </c>
-      <c r="AN200" t="inlineStr">
-        <is>
-          <t>265</t>
-        </is>
-      </c>
-      <c r="AO200" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="AP200" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="AQ200" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="AR200" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="AS200" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="AT200" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
+      <c r="Q200" t="n">
+        <v>12</v>
+      </c>
+      <c r="R200" t="n">
+        <v>12</v>
+      </c>
+      <c r="S200" t="n">
+        <v>5</v>
+      </c>
+      <c r="T200" t="n">
+        <v>4</v>
+      </c>
+      <c r="U200" t="n">
+        <v>7</v>
+      </c>
+      <c r="V200" t="n">
+        <v>8</v>
+      </c>
+      <c r="W200" t="n">
+        <v>15</v>
+      </c>
+      <c r="X200" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y200" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z200" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA200" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB200" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC200" t="n">
+        <v>23</v>
+      </c>
+      <c r="AD200" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE200" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF200" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG200" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH200" t="n">
+        <v>14</v>
+      </c>
+      <c r="AI200" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ200" t="n">
+        <v>7</v>
+      </c>
+      <c r="AK200" t="n">
+        <v>420</v>
+      </c>
+      <c r="AL200" t="n">
+        <v>335</v>
+      </c>
+      <c r="AM200" t="n">
+        <v>370</v>
+      </c>
+      <c r="AN200" t="n">
+        <v>265</v>
+      </c>
+      <c r="AO200" t="n">
+        <v>63</v>
+      </c>
+      <c r="AP200" t="n">
+        <v>113</v>
+      </c>
+      <c r="AQ200" t="n">
+        <v>31</v>
+      </c>
+      <c r="AR200" t="n">
+        <v>55</v>
+      </c>
+      <c r="AS200" t="n">
+        <v>114</v>
+      </c>
+      <c r="AT200" t="n">
+        <v>111</v>
       </c>
       <c r="AU200" t="inlineStr">
         <is>
@@ -41282,15 +41010,11 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="BC200" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BD200" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="BC200" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD200" t="n">
+        <v>0</v>
       </c>
       <c r="BE200" t="inlineStr"/>
       <c r="BF200" t="inlineStr"/>
@@ -41328,15 +41052,11 @@
           <t>59 000</t>
         </is>
       </c>
-      <c r="G201" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H201" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="G201" t="n">
+        <v>3</v>
+      </c>
+      <c r="H201" t="n">
+        <v>3</v>
       </c>
       <c r="I201" t="inlineStr">
         <is>
@@ -41358,15 +41078,11 @@
           <t>Mainz</t>
         </is>
       </c>
-      <c r="M201" t="inlineStr">
-        <is>
-          <t>5.21</t>
-        </is>
-      </c>
-      <c r="N201" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
+      <c r="M201" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="N201" t="n">
+        <v>2.25</v>
       </c>
       <c r="O201" t="inlineStr">
         <is>
@@ -41378,155 +41094,95 @@
           <t>38%</t>
         </is>
       </c>
-      <c r="Q201" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="R201" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="S201" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="T201" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="U201" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="V201" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="W201" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="X201" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y201" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="Z201" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA201" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB201" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC201" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AD201" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AE201" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AF201" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AG201" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AH201" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AI201" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AJ201" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AK201" t="inlineStr">
-        <is>
-          <t>529</t>
-        </is>
-      </c>
-      <c r="AL201" t="inlineStr">
-        <is>
-          <t>301</t>
-        </is>
-      </c>
-      <c r="AM201" t="inlineStr">
-        <is>
-          <t>501</t>
-        </is>
-      </c>
-      <c r="AN201" t="inlineStr">
-        <is>
-          <t>259</t>
-        </is>
-      </c>
-      <c r="AO201" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="AP201" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="AQ201" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="AR201" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AS201" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="AT201" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
+      <c r="Q201" t="n">
+        <v>28</v>
+      </c>
+      <c r="R201" t="n">
+        <v>9</v>
+      </c>
+      <c r="S201" t="n">
+        <v>13</v>
+      </c>
+      <c r="T201" t="n">
+        <v>7</v>
+      </c>
+      <c r="U201" t="n">
+        <v>15</v>
+      </c>
+      <c r="V201" t="n">
+        <v>2</v>
+      </c>
+      <c r="W201" t="n">
+        <v>14</v>
+      </c>
+      <c r="X201" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y201" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z201" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA201" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB201" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC201" t="n">
+        <v>17</v>
+      </c>
+      <c r="AD201" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE201" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF201" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG201" t="n">
+        <v>6</v>
+      </c>
+      <c r="AH201" t="n">
+        <v>12</v>
+      </c>
+      <c r="AI201" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ201" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK201" t="n">
+        <v>529</v>
+      </c>
+      <c r="AL201" t="n">
+        <v>301</v>
+      </c>
+      <c r="AM201" t="n">
+        <v>501</v>
+      </c>
+      <c r="AN201" t="n">
+        <v>259</v>
+      </c>
+      <c r="AO201" t="n">
+        <v>89</v>
+      </c>
+      <c r="AP201" t="n">
+        <v>55</v>
+      </c>
+      <c r="AQ201" t="n">
+        <v>54</v>
+      </c>
+      <c r="AR201" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS201" t="n">
+        <v>109</v>
+      </c>
+      <c r="AT201" t="n">
+        <v>111</v>
       </c>
       <c r="AU201" t="inlineStr">
         <is>
@@ -41600,15 +41256,11 @@
           <t>42 100</t>
         </is>
       </c>
-      <c r="G202" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H202" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G202" t="n">
+        <v>0</v>
+      </c>
+      <c r="H202" t="n">
+        <v>0</v>
       </c>
       <c r="I202" t="inlineStr">
         <is>
@@ -41630,15 +41282,11 @@
           <t>Dortmund</t>
         </is>
       </c>
-      <c r="M202" t="inlineStr">
-        <is>
-          <t>0.33</t>
-        </is>
-      </c>
-      <c r="N202" t="inlineStr">
-        <is>
-          <t>0.76</t>
-        </is>
+      <c r="M202" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="N202" t="n">
+        <v>0.76</v>
       </c>
       <c r="O202" t="inlineStr">
         <is>
@@ -41650,155 +41298,95 @@
           <t>52%</t>
         </is>
       </c>
-      <c r="Q202" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R202" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="S202" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="T202" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U202" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="V202" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="W202" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="X202" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="Y202" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Z202" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA202" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AB202" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AC202" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AD202" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AE202" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AF202" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AG202" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AH202" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AI202" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AJ202" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AK202" t="inlineStr">
-        <is>
-          <t>449</t>
-        </is>
-      </c>
-      <c r="AL202" t="inlineStr">
-        <is>
-          <t>526</t>
-        </is>
-      </c>
-      <c r="AM202" t="inlineStr">
-        <is>
-          <t>409</t>
-        </is>
-      </c>
-      <c r="AN202" t="inlineStr">
-        <is>
-          <t>506</t>
-        </is>
-      </c>
-      <c r="AO202" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="AP202" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="AQ202" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="AR202" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="AS202" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="AT202" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
+      <c r="Q202" t="n">
+        <v>5</v>
+      </c>
+      <c r="R202" t="n">
+        <v>9</v>
+      </c>
+      <c r="S202" t="n">
+        <v>1</v>
+      </c>
+      <c r="T202" t="n">
+        <v>4</v>
+      </c>
+      <c r="U202" t="n">
+        <v>4</v>
+      </c>
+      <c r="V202" t="n">
+        <v>5</v>
+      </c>
+      <c r="W202" t="n">
+        <v>18</v>
+      </c>
+      <c r="X202" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y202" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z202" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA202" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB202" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC202" t="n">
+        <v>16</v>
+      </c>
+      <c r="AD202" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE202" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF202" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG202" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH202" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI202" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ202" t="n">
+        <v>7</v>
+      </c>
+      <c r="AK202" t="n">
+        <v>449</v>
+      </c>
+      <c r="AL202" t="n">
+        <v>526</v>
+      </c>
+      <c r="AM202" t="n">
+        <v>409</v>
+      </c>
+      <c r="AN202" t="n">
+        <v>506</v>
+      </c>
+      <c r="AO202" t="n">
+        <v>88</v>
+      </c>
+      <c r="AP202" t="n">
+        <v>91</v>
+      </c>
+      <c r="AQ202" t="n">
+        <v>52</v>
+      </c>
+      <c r="AR202" t="n">
+        <v>29</v>
+      </c>
+      <c r="AS202" t="n">
+        <v>111</v>
+      </c>
+      <c r="AT202" t="n">
+        <v>113</v>
       </c>
       <c r="AU202" t="inlineStr">
         <is>
@@ -41834,15 +41422,11 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="BC202" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BD202" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="BC202" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD202" t="n">
+        <v>1</v>
       </c>
       <c r="BE202" t="inlineStr"/>
       <c r="BF202" t="inlineStr"/>
@@ -41876,15 +41460,11 @@
         </is>
       </c>
       <c r="F203" t="inlineStr"/>
-      <c r="G203" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H203" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="G203" t="n">
+        <v>3</v>
+      </c>
+      <c r="H203" t="n">
+        <v>4</v>
       </c>
       <c r="I203" t="inlineStr">
         <is>
@@ -41906,15 +41486,11 @@
           <t>Hertha Berlin</t>
         </is>
       </c>
-      <c r="M203" t="inlineStr">
-        <is>
-          <t>2.85</t>
-        </is>
-      </c>
-      <c r="N203" t="inlineStr">
-        <is>
-          <t>2.35</t>
-        </is>
+      <c r="M203" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="N203" t="n">
+        <v>2.35</v>
       </c>
       <c r="O203" t="inlineStr">
         <is>
@@ -41926,155 +41502,95 @@
           <t>61%</t>
         </is>
       </c>
-      <c r="Q203" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="R203" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="S203" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="T203" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="U203" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="V203" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="W203" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="X203" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y203" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="Z203" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA203" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB203" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC203" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="AD203" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="AE203" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AF203" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AG203" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AH203" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AI203" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AJ203" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AK203" t="inlineStr">
-        <is>
-          <t>249</t>
-        </is>
-      </c>
-      <c r="AL203" t="inlineStr">
-        <is>
-          <t>462</t>
-        </is>
-      </c>
-      <c r="AM203" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
-      </c>
-      <c r="AN203" t="inlineStr">
-        <is>
-          <t>416</t>
-        </is>
-      </c>
-      <c r="AO203" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="AP203" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="AQ203" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="AR203" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="AS203" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="AT203" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
+      <c r="Q203" t="n">
+        <v>24</v>
+      </c>
+      <c r="R203" t="n">
+        <v>17</v>
+      </c>
+      <c r="S203" t="n">
+        <v>9</v>
+      </c>
+      <c r="T203" t="n">
+        <v>8</v>
+      </c>
+      <c r="U203" t="n">
+        <v>15</v>
+      </c>
+      <c r="V203" t="n">
+        <v>9</v>
+      </c>
+      <c r="W203" t="n">
+        <v>14</v>
+      </c>
+      <c r="X203" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y203" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z203" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA203" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB203" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC203" t="n">
+        <v>22</v>
+      </c>
+      <c r="AD203" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE203" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF203" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG203" t="n">
+        <v>6</v>
+      </c>
+      <c r="AH203" t="n">
+        <v>10</v>
+      </c>
+      <c r="AI203" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ203" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK203" t="n">
+        <v>249</v>
+      </c>
+      <c r="AL203" t="n">
+        <v>462</v>
+      </c>
+      <c r="AM203" t="n">
+        <v>182</v>
+      </c>
+      <c r="AN203" t="n">
+        <v>416</v>
+      </c>
+      <c r="AO203" t="n">
+        <v>78</v>
+      </c>
+      <c r="AP203" t="n">
+        <v>79</v>
+      </c>
+      <c r="AQ203" t="n">
+        <v>38</v>
+      </c>
+      <c r="AR203" t="n">
+        <v>58</v>
+      </c>
+      <c r="AS203" t="n">
+        <v>113</v>
+      </c>
+      <c r="AT203" t="n">
+        <v>115</v>
       </c>
       <c r="AU203" t="inlineStr">
         <is>
@@ -42148,15 +41664,11 @@
           <t>9 443</t>
         </is>
       </c>
-      <c r="G204" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H204" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G204" t="n">
+        <v>4</v>
+      </c>
+      <c r="H204" t="n">
+        <v>0</v>
       </c>
       <c r="I204" t="inlineStr">
         <is>
@@ -42178,15 +41690,11 @@
           <t>Darmstadt</t>
         </is>
       </c>
-      <c r="M204" t="inlineStr">
-        <is>
-          <t>2.31</t>
-        </is>
-      </c>
-      <c r="N204" t="inlineStr">
-        <is>
-          <t>1.56</t>
-        </is>
+      <c r="M204" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="N204" t="n">
+        <v>1.56</v>
       </c>
       <c r="O204" t="inlineStr">
         <is>
@@ -42198,155 +41706,95 @@
           <t>50%</t>
         </is>
       </c>
-      <c r="Q204" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="R204" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="S204" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="T204" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="U204" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="V204" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="W204" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="X204" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y204" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Z204" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AA204" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB204" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC204" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AD204" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AE204" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AF204" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG204" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AH204" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AI204" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AJ204" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AK204" t="inlineStr">
-        <is>
-          <t>423</t>
-        </is>
-      </c>
-      <c r="AL204" t="inlineStr">
-        <is>
-          <t>429</t>
-        </is>
-      </c>
-      <c r="AM204" t="inlineStr">
-        <is>
-          <t>383</t>
-        </is>
-      </c>
-      <c r="AN204" t="inlineStr">
-        <is>
-          <t>397</t>
-        </is>
-      </c>
-      <c r="AO204" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="AP204" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="AQ204" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="AR204" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="AS204" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="AT204" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
+      <c r="Q204" t="n">
+        <v>17</v>
+      </c>
+      <c r="R204" t="n">
+        <v>13</v>
+      </c>
+      <c r="S204" t="n">
+        <v>4</v>
+      </c>
+      <c r="T204" t="n">
+        <v>5</v>
+      </c>
+      <c r="U204" t="n">
+        <v>13</v>
+      </c>
+      <c r="V204" t="n">
+        <v>8</v>
+      </c>
+      <c r="W204" t="n">
+        <v>13</v>
+      </c>
+      <c r="X204" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y204" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z204" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA204" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB204" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC204" t="n">
+        <v>16</v>
+      </c>
+      <c r="AD204" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE204" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF204" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG204" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH204" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI204" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ204" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK204" t="n">
+        <v>423</v>
+      </c>
+      <c r="AL204" t="n">
+        <v>429</v>
+      </c>
+      <c r="AM204" t="n">
+        <v>383</v>
+      </c>
+      <c r="AN204" t="n">
+        <v>397</v>
+      </c>
+      <c r="AO204" t="n">
+        <v>76</v>
+      </c>
+      <c r="AP204" t="n">
+        <v>82</v>
+      </c>
+      <c r="AQ204" t="n">
+        <v>44</v>
+      </c>
+      <c r="AR204" t="n">
+        <v>50</v>
+      </c>
+      <c r="AS204" t="n">
+        <v>124</v>
+      </c>
+      <c r="AT204" t="n">
+        <v>119</v>
       </c>
       <c r="AU204" t="inlineStr">
         <is>
@@ -42420,15 +41868,11 @@
           <t>57 000</t>
         </is>
       </c>
-      <c r="G205" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H205" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G205" t="n">
+        <v>4</v>
+      </c>
+      <c r="H205" t="n">
+        <v>1</v>
       </c>
       <c r="I205" t="inlineStr">
         <is>
@@ -42450,15 +41894,11 @@
           <t>Preussen Munster</t>
         </is>
       </c>
-      <c r="M205" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
-      </c>
-      <c r="N205" t="inlineStr">
-        <is>
-          <t>1.14</t>
-        </is>
+      <c r="M205" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="N205" t="n">
+        <v>1.14</v>
       </c>
       <c r="O205" t="inlineStr">
         <is>
@@ -42470,147 +41910,91 @@
           <t>37%</t>
         </is>
       </c>
-      <c r="Q205" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="R205" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="S205" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="T205" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="U205" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="V205" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="W205" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="X205" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="Y205" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Z205" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AA205" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AB205" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC205" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AD205" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AE205" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AF205" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AG205" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AH205" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="Q205" t="n">
+        <v>10</v>
+      </c>
+      <c r="R205" t="n">
+        <v>15</v>
+      </c>
+      <c r="S205" t="n">
+        <v>7</v>
+      </c>
+      <c r="T205" t="n">
+        <v>7</v>
+      </c>
+      <c r="U205" t="n">
+        <v>3</v>
+      </c>
+      <c r="V205" t="n">
+        <v>8</v>
+      </c>
+      <c r="W205" t="n">
+        <v>8</v>
+      </c>
+      <c r="X205" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y205" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z205" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA205" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB205" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC205" t="n">
+        <v>13</v>
+      </c>
+      <c r="AD205" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE205" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF205" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG205" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH205" t="n">
+        <v>8</v>
       </c>
       <c r="AI205" t="inlineStr"/>
       <c r="AJ205" t="inlineStr"/>
-      <c r="AK205" t="inlineStr">
-        <is>
-          <t>538</t>
-        </is>
-      </c>
-      <c r="AL205" t="inlineStr">
-        <is>
-          <t>303</t>
-        </is>
-      </c>
-      <c r="AM205" t="inlineStr">
-        <is>
-          <t>529</t>
-        </is>
-      </c>
-      <c r="AN205" t="inlineStr">
-        <is>
-          <t>261</t>
-        </is>
-      </c>
-      <c r="AO205" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="AP205" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="AQ205" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="AR205" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="AS205" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="AT205" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
+      <c r="AK205" t="n">
+        <v>538</v>
+      </c>
+      <c r="AL205" t="n">
+        <v>303</v>
+      </c>
+      <c r="AM205" t="n">
+        <v>529</v>
+      </c>
+      <c r="AN205" t="n">
+        <v>261</v>
+      </c>
+      <c r="AO205" t="n">
+        <v>59</v>
+      </c>
+      <c r="AP205" t="n">
+        <v>62</v>
+      </c>
+      <c r="AQ205" t="n">
+        <v>32</v>
+      </c>
+      <c r="AR205" t="n">
+        <v>40</v>
+      </c>
+      <c r="AS205" t="n">
+        <v>113</v>
+      </c>
+      <c r="AT205" t="n">
+        <v>113</v>
       </c>
       <c r="AU205" t="inlineStr">
         <is>
@@ -42684,15 +42068,11 @@
           <t>31 581</t>
         </is>
       </c>
-      <c r="G206" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H206" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="G206" t="n">
+        <v>0</v>
+      </c>
+      <c r="H206" t="n">
+        <v>4</v>
       </c>
       <c r="I206" t="inlineStr">
         <is>
@@ -42714,15 +42094,11 @@
           <t>Magdeburg</t>
         </is>
       </c>
-      <c r="M206" t="inlineStr">
-        <is>
-          <t>1.42</t>
-        </is>
-      </c>
-      <c r="N206" t="inlineStr">
-        <is>
-          <t>2.63</t>
-        </is>
+      <c r="M206" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="N206" t="n">
+        <v>2.63</v>
       </c>
       <c r="O206" t="inlineStr">
         <is>
@@ -42734,155 +42110,95 @@
           <t>58%</t>
         </is>
       </c>
-      <c r="Q206" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="R206" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="S206" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="T206" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="U206" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="V206" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="W206" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="X206" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y206" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Z206" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA206" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB206" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC206" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AD206" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AE206" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AF206" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AG206" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AH206" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AI206" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ206" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AK206" t="inlineStr">
-        <is>
-          <t>323</t>
-        </is>
-      </c>
-      <c r="AL206" t="inlineStr">
-        <is>
-          <t>478</t>
-        </is>
-      </c>
-      <c r="AM206" t="inlineStr">
-        <is>
-          <t>290</t>
-        </is>
-      </c>
-      <c r="AN206" t="inlineStr">
-        <is>
-          <t>454</t>
-        </is>
-      </c>
-      <c r="AO206" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="AP206" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="AQ206" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AR206" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="AS206" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="AT206" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
+      <c r="Q206" t="n">
+        <v>7</v>
+      </c>
+      <c r="R206" t="n">
+        <v>14</v>
+      </c>
+      <c r="S206" t="n">
+        <v>3</v>
+      </c>
+      <c r="T206" t="n">
+        <v>7</v>
+      </c>
+      <c r="U206" t="n">
+        <v>4</v>
+      </c>
+      <c r="V206" t="n">
+        <v>7</v>
+      </c>
+      <c r="W206" t="n">
+        <v>10</v>
+      </c>
+      <c r="X206" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y206" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z206" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA206" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB206" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC206" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD206" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE206" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF206" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG206" t="n">
+        <v>7</v>
+      </c>
+      <c r="AH206" t="n">
+        <v>12</v>
+      </c>
+      <c r="AI206" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ206" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK206" t="n">
+        <v>323</v>
+      </c>
+      <c r="AL206" t="n">
+        <v>478</v>
+      </c>
+      <c r="AM206" t="n">
+        <v>290</v>
+      </c>
+      <c r="AN206" t="n">
+        <v>454</v>
+      </c>
+      <c r="AO206" t="n">
+        <v>40</v>
+      </c>
+      <c r="AP206" t="n">
+        <v>52</v>
+      </c>
+      <c r="AQ206" t="n">
+        <v>16</v>
+      </c>
+      <c r="AR206" t="n">
+        <v>38</v>
+      </c>
+      <c r="AS206" t="n">
+        <v>106</v>
+      </c>
+      <c r="AT206" t="n">
+        <v>112</v>
       </c>
       <c r="AU206" t="inlineStr">
         <is>
@@ -42923,6 +42239,1366 @@
       <c r="BE206" t="inlineStr"/>
       <c r="BF206" t="inlineStr"/>
     </row>
+    <row r="207">
+      <c r="A207" s="1" t="inlineStr">
+        <is>
+          <t>2T6mXfPa</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>01.09.2024 12:30</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Dingert C.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>Allianz Arena
+ (Munich)</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>75 024</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>75 000</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>nVp0wiqd</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>Bayern Munich</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>Freiburg</t>
+        </is>
+      </c>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="N207" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="O207" t="inlineStr">
+        <is>
+          <t>62%</t>
+        </is>
+      </c>
+      <c r="P207" t="inlineStr">
+        <is>
+          <t>38%</t>
+        </is>
+      </c>
+      <c r="Q207" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R207" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="S207" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T207" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U207" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V207" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W207" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="X207" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="Y207" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Z207" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA207" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB207" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC207" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AD207" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AE207" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AF207" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AG207" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AH207" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AI207" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AJ207" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK207" t="inlineStr">
+        <is>
+          <t>764</t>
+        </is>
+      </c>
+      <c r="AL207" t="inlineStr">
+        <is>
+          <t>425</t>
+        </is>
+      </c>
+      <c r="AM207" t="inlineStr">
+        <is>
+          <t>668</t>
+        </is>
+      </c>
+      <c r="AN207" t="inlineStr">
+        <is>
+          <t>332</t>
+        </is>
+      </c>
+      <c r="AO207" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="AP207" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="AQ207" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="AR207" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="AS207" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="AT207" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="AU207" t="inlineStr">
+        <is>
+          <t>K6A2elS9</t>
+        </is>
+      </c>
+      <c r="AV207" t="inlineStr">
+        <is>
+          <t>kompany vincent</t>
+        </is>
+      </c>
+      <c r="AW207" t="inlineStr">
+        <is>
+          <t>YZPE6Sx7</t>
+        </is>
+      </c>
+      <c r="AX207" t="inlineStr">
+        <is>
+          <t>schuster julian</t>
+        </is>
+      </c>
+      <c r="AY207" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ207" t="n">
+        <v>591</v>
+      </c>
+      <c r="BA207" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB207" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC207" t="inlineStr"/>
+      <c r="BD207" t="inlineStr"/>
+      <c r="BE207" t="inlineStr"/>
+      <c r="BF207" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" s="1" t="inlineStr">
+        <is>
+          <t>W8b4TCOO</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>01.09.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Petersen M.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>Voith-Arena
+ (Heidenheim)</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>KWixEVWi</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>Heidenheim</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>fTVNku3I</t>
+        </is>
+      </c>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>Augsburg</t>
+        </is>
+      </c>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>2.89</t>
+        </is>
+      </c>
+      <c r="N208" t="inlineStr">
+        <is>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="O208" t="inlineStr">
+        <is>
+          <t>41%</t>
+        </is>
+      </c>
+      <c r="P208" t="inlineStr">
+        <is>
+          <t>59%</t>
+        </is>
+      </c>
+      <c r="Q208" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="R208" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="S208" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="T208" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U208" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V208" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="W208" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="X208" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="Y208" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Z208" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA208" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB208" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC208" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AD208" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AE208" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AF208" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AG208" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AH208" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AI208" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AJ208" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AK208" t="inlineStr">
+        <is>
+          <t>371</t>
+        </is>
+      </c>
+      <c r="AL208" t="inlineStr">
+        <is>
+          <t>604</t>
+        </is>
+      </c>
+      <c r="AM208" t="inlineStr">
+        <is>
+          <t>286</t>
+        </is>
+      </c>
+      <c r="AN208" t="inlineStr">
+        <is>
+          <t>520</t>
+        </is>
+      </c>
+      <c r="AO208" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="AP208" t="inlineStr">
+        <is>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="AQ208" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AR208" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="AS208" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="AT208" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="AU208" t="inlineStr">
+        <is>
+          <t>4ljanukM</t>
+        </is>
+      </c>
+      <c r="AV208" t="inlineStr">
+        <is>
+          <t>schmidt frank</t>
+        </is>
+      </c>
+      <c r="AW208" t="inlineStr">
+        <is>
+          <t>2VSFgl3c</t>
+        </is>
+      </c>
+      <c r="AX208" t="inlineStr">
+        <is>
+          <t>thorup jess</t>
+        </is>
+      </c>
+      <c r="AY208" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ208" t="n">
+        <v>591</v>
+      </c>
+      <c r="BA208" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB208" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC208" t="inlineStr"/>
+      <c r="BD208" t="inlineStr"/>
+      <c r="BE208" t="inlineStr"/>
+      <c r="BF208" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" s="1" t="inlineStr">
+        <is>
+          <t>rF6aucw3</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>01.09.2024 08:30</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Bauer T.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Eintracht-Stadion
+ (Braunschweig)</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>23 325</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>19 908</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>QqLCC3il</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>Braunschweig</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>EB3q7jbk</t>
+        </is>
+      </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>Karlsruher SC</t>
+        </is>
+      </c>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>0.68</t>
+        </is>
+      </c>
+      <c r="N209" t="inlineStr">
+        <is>
+          <t>1.23</t>
+        </is>
+      </c>
+      <c r="O209" t="inlineStr">
+        <is>
+          <t>39%</t>
+        </is>
+      </c>
+      <c r="P209" t="inlineStr">
+        <is>
+          <t>61%</t>
+        </is>
+      </c>
+      <c r="Q209" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R209" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="S209" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T209" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U209" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V209" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="W209" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="X209" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="Y209" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Z209" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA209" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB209" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC209" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AD209" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="AE209" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AF209" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG209" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AH209" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AI209" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AJ209" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AK209" t="inlineStr">
+        <is>
+          <t>340</t>
+        </is>
+      </c>
+      <c r="AL209" t="inlineStr">
+        <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="AM209" t="inlineStr">
+        <is>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="AN209" t="inlineStr">
+        <is>
+          <t>559</t>
+        </is>
+      </c>
+      <c r="AO209" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="AP209" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="AQ209" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AR209" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="AS209" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="AT209" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="AU209" t="inlineStr">
+        <is>
+          <t>SQrxFAMl</t>
+        </is>
+      </c>
+      <c r="AV209" t="inlineStr">
+        <is>
+          <t>scherning daniel</t>
+        </is>
+      </c>
+      <c r="AW209" t="inlineStr">
+        <is>
+          <t>OzPMRhK3</t>
+        </is>
+      </c>
+      <c r="AX209" t="inlineStr">
+        <is>
+          <t>eichner christian</t>
+        </is>
+      </c>
+      <c r="AY209" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ209" t="n">
+        <v>592</v>
+      </c>
+      <c r="BA209" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB209" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC209" t="inlineStr"/>
+      <c r="BD209" t="inlineStr"/>
+      <c r="BE209" t="inlineStr"/>
+      <c r="BF209" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" s="1" t="inlineStr">
+        <is>
+          <t>tOBGu6Xo</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>01.09.2024 08:30</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Lechner F.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>Home Deluxe Arena
+ (Paderborn)</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>11 985</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>G2Op923t</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>Paderborn</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>tbC3EcQn</t>
+        </is>
+      </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>Ulm</t>
+        </is>
+      </c>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="N210" t="inlineStr">
+        <is>
+          <t>0.64</t>
+        </is>
+      </c>
+      <c r="O210" t="inlineStr">
+        <is>
+          <t>58%</t>
+        </is>
+      </c>
+      <c r="P210" t="inlineStr">
+        <is>
+          <t>42%</t>
+        </is>
+      </c>
+      <c r="Q210" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="R210" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="S210" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T210" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U210" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="V210" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="W210" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="X210" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="Y210" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Z210" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA210" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB210" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC210" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AD210" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AE210" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AF210" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AG210" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AH210" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AI210" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AJ210" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AK210" t="inlineStr">
+        <is>
+          <t>486</t>
+        </is>
+      </c>
+      <c r="AL210" t="inlineStr">
+        <is>
+          <t>357</t>
+        </is>
+      </c>
+      <c r="AM210" t="inlineStr">
+        <is>
+          <t>405</t>
+        </is>
+      </c>
+      <c r="AN210" t="inlineStr">
+        <is>
+          <t>279</t>
+        </is>
+      </c>
+      <c r="AO210" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="AP210" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="AQ210" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="AR210" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="AS210" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="AT210" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="AU210" t="inlineStr">
+        <is>
+          <t>0AI1QUJH</t>
+        </is>
+      </c>
+      <c r="AV210" t="inlineStr">
+        <is>
+          <t>kwasniok lukas</t>
+        </is>
+      </c>
+      <c r="AW210" t="inlineStr">
+        <is>
+          <t>QevvB2nf</t>
+        </is>
+      </c>
+      <c r="AX210" t="inlineStr">
+        <is>
+          <t>worle thomas</t>
+        </is>
+      </c>
+      <c r="AY210" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ210" t="n">
+        <v>592</v>
+      </c>
+      <c r="BA210" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB210" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC210" t="inlineStr"/>
+      <c r="BD210" t="inlineStr"/>
+      <c r="BE210" t="inlineStr"/>
+      <c r="BF210" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" s="1" t="inlineStr">
+        <is>
+          <t>llFOwp2b</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>01.09.2024 08:30</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Jablonski S.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Veltins Arena
+ (Gelsenkirchen)</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>62 271</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>61 624</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>0Ija0Ej9</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>Schalke</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>WG9pOTse</t>
+        </is>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>FC Koln</t>
+        </is>
+      </c>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="N211" t="inlineStr">
+        <is>
+          <t>3.13</t>
+        </is>
+      </c>
+      <c r="O211" t="inlineStr">
+        <is>
+          <t>57%</t>
+        </is>
+      </c>
+      <c r="P211" t="inlineStr">
+        <is>
+          <t>43%</t>
+        </is>
+      </c>
+      <c r="Q211" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="R211" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="S211" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T211" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="U211" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V211" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="W211" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="X211" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y211" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Z211" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA211" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB211" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC211" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="AD211" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AE211" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AF211" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AG211" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AH211" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AI211" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AJ211" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AK211" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="AL211" t="inlineStr">
+        <is>
+          <t>328</t>
+        </is>
+      </c>
+      <c r="AM211" t="inlineStr">
+        <is>
+          <t>405</t>
+        </is>
+      </c>
+      <c r="AN211" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="AO211" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="AP211" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="AQ211" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="AR211" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="AS211" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="AT211" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="AU211" t="inlineStr">
+        <is>
+          <t>txZLBQVC</t>
+        </is>
+      </c>
+      <c r="AV211" t="inlineStr">
+        <is>
+          <t>geraerts karel</t>
+        </is>
+      </c>
+      <c r="AW211" t="inlineStr">
+        <is>
+          <t>4fX0k7gg</t>
+        </is>
+      </c>
+      <c r="AX211" t="inlineStr">
+        <is>
+          <t>struber gerhard</t>
+        </is>
+      </c>
+      <c r="AY211" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ211" t="n">
+        <v>592</v>
+      </c>
+      <c r="BA211" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB211" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC211" t="inlineStr"/>
+      <c r="BD211" t="inlineStr"/>
+      <c r="BE211" t="inlineStr"/>
+      <c r="BF211" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/germany/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
+++ b/data/germany/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BF223"/>
+  <dimension ref="A1:BH229"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -714,6 +714,16 @@
           <t>blocked_shots_away</t>
         </is>
       </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>tackles_home</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>tackles_away</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -918,6 +928,8 @@
       <c r="BD2" t="inlineStr"/>
       <c r="BE2" t="inlineStr"/>
       <c r="BF2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr"/>
+      <c r="BH2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -1122,6 +1134,8 @@
       <c r="BD3" t="inlineStr"/>
       <c r="BE3" t="inlineStr"/>
       <c r="BF3" t="inlineStr"/>
+      <c r="BG3" t="inlineStr"/>
+      <c r="BH3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -1326,6 +1340,8 @@
       <c r="BD4" t="inlineStr"/>
       <c r="BE4" t="inlineStr"/>
       <c r="BF4" t="inlineStr"/>
+      <c r="BG4" t="inlineStr"/>
+      <c r="BH4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -1530,6 +1546,8 @@
       <c r="BD5" t="inlineStr"/>
       <c r="BE5" t="inlineStr"/>
       <c r="BF5" t="inlineStr"/>
+      <c r="BG5" t="inlineStr"/>
+      <c r="BH5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -1734,6 +1752,8 @@
       <c r="BD6" t="inlineStr"/>
       <c r="BE6" t="inlineStr"/>
       <c r="BF6" t="inlineStr"/>
+      <c r="BG6" t="inlineStr"/>
+      <c r="BH6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -1938,6 +1958,8 @@
       <c r="BD7" t="inlineStr"/>
       <c r="BE7" t="inlineStr"/>
       <c r="BF7" t="inlineStr"/>
+      <c r="BG7" t="inlineStr"/>
+      <c r="BH7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -2142,6 +2164,8 @@
       <c r="BD8" t="inlineStr"/>
       <c r="BE8" t="inlineStr"/>
       <c r="BF8" t="inlineStr"/>
+      <c r="BG8" t="inlineStr"/>
+      <c r="BH8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -2350,6 +2374,8 @@
       </c>
       <c r="BE9" t="inlineStr"/>
       <c r="BF9" t="inlineStr"/>
+      <c r="BG9" t="inlineStr"/>
+      <c r="BH9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -2554,6 +2580,8 @@
       <c r="BD10" t="inlineStr"/>
       <c r="BE10" t="inlineStr"/>
       <c r="BF10" t="inlineStr"/>
+      <c r="BG10" t="inlineStr"/>
+      <c r="BH10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -2758,6 +2786,8 @@
       <c r="BD11" t="inlineStr"/>
       <c r="BE11" t="inlineStr"/>
       <c r="BF11" t="inlineStr"/>
+      <c r="BG11" t="inlineStr"/>
+      <c r="BH11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -2962,6 +2992,8 @@
       <c r="BD12" t="inlineStr"/>
       <c r="BE12" t="inlineStr"/>
       <c r="BF12" t="inlineStr"/>
+      <c r="BG12" t="inlineStr"/>
+      <c r="BH12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -3166,6 +3198,8 @@
       <c r="BD13" t="inlineStr"/>
       <c r="BE13" t="inlineStr"/>
       <c r="BF13" t="inlineStr"/>
+      <c r="BG13" t="inlineStr"/>
+      <c r="BH13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -3370,6 +3404,8 @@
       <c r="BD14" t="inlineStr"/>
       <c r="BE14" t="inlineStr"/>
       <c r="BF14" t="inlineStr"/>
+      <c r="BG14" t="inlineStr"/>
+      <c r="BH14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -3574,6 +3610,8 @@
       <c r="BD15" t="inlineStr"/>
       <c r="BE15" t="inlineStr"/>
       <c r="BF15" t="inlineStr"/>
+      <c r="BG15" t="inlineStr"/>
+      <c r="BH15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -3782,6 +3820,8 @@
       </c>
       <c r="BE16" t="inlineStr"/>
       <c r="BF16" t="inlineStr"/>
+      <c r="BG16" t="inlineStr"/>
+      <c r="BH16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -3986,6 +4026,8 @@
       <c r="BD17" t="inlineStr"/>
       <c r="BE17" t="inlineStr"/>
       <c r="BF17" t="inlineStr"/>
+      <c r="BG17" t="inlineStr"/>
+      <c r="BH17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
@@ -4194,6 +4236,8 @@
       </c>
       <c r="BE18" t="inlineStr"/>
       <c r="BF18" t="inlineStr"/>
+      <c r="BG18" t="inlineStr"/>
+      <c r="BH18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
@@ -4398,6 +4442,8 @@
       <c r="BD19" t="inlineStr"/>
       <c r="BE19" t="inlineStr"/>
       <c r="BF19" t="inlineStr"/>
+      <c r="BG19" t="inlineStr"/>
+      <c r="BH19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
@@ -4603,6 +4649,8 @@
       <c r="BD20" t="inlineStr"/>
       <c r="BE20" t="inlineStr"/>
       <c r="BF20" t="inlineStr"/>
+      <c r="BG20" t="inlineStr"/>
+      <c r="BH20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
@@ -4807,6 +4855,8 @@
       <c r="BD21" t="inlineStr"/>
       <c r="BE21" t="inlineStr"/>
       <c r="BF21" t="inlineStr"/>
+      <c r="BG21" t="inlineStr"/>
+      <c r="BH21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -5011,6 +5061,8 @@
       <c r="BD22" t="inlineStr"/>
       <c r="BE22" t="inlineStr"/>
       <c r="BF22" t="inlineStr"/>
+      <c r="BG22" t="inlineStr"/>
+      <c r="BH22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
@@ -5215,6 +5267,8 @@
       <c r="BD23" t="inlineStr"/>
       <c r="BE23" t="inlineStr"/>
       <c r="BF23" t="inlineStr"/>
+      <c r="BG23" t="inlineStr"/>
+      <c r="BH23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
@@ -5419,6 +5473,8 @@
       <c r="BD24" t="inlineStr"/>
       <c r="BE24" t="inlineStr"/>
       <c r="BF24" t="inlineStr"/>
+      <c r="BG24" t="inlineStr"/>
+      <c r="BH24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -5623,6 +5679,8 @@
       <c r="BD25" t="inlineStr"/>
       <c r="BE25" t="inlineStr"/>
       <c r="BF25" t="inlineStr"/>
+      <c r="BG25" t="inlineStr"/>
+      <c r="BH25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
@@ -5827,6 +5885,8 @@
       <c r="BD26" t="inlineStr"/>
       <c r="BE26" t="inlineStr"/>
       <c r="BF26" t="inlineStr"/>
+      <c r="BG26" t="inlineStr"/>
+      <c r="BH26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
@@ -6031,6 +6091,8 @@
       <c r="BD27" t="inlineStr"/>
       <c r="BE27" t="inlineStr"/>
       <c r="BF27" t="inlineStr"/>
+      <c r="BG27" t="inlineStr"/>
+      <c r="BH27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -6235,6 +6297,8 @@
       <c r="BD28" t="inlineStr"/>
       <c r="BE28" t="inlineStr"/>
       <c r="BF28" t="inlineStr"/>
+      <c r="BG28" t="inlineStr"/>
+      <c r="BH28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
@@ -6439,6 +6503,8 @@
       <c r="BD29" t="inlineStr"/>
       <c r="BE29" t="inlineStr"/>
       <c r="BF29" t="inlineStr"/>
+      <c r="BG29" t="inlineStr"/>
+      <c r="BH29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
@@ -6643,6 +6709,8 @@
       <c r="BD30" t="inlineStr"/>
       <c r="BE30" t="inlineStr"/>
       <c r="BF30" t="inlineStr"/>
+      <c r="BG30" t="inlineStr"/>
+      <c r="BH30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
@@ -6851,6 +6919,8 @@
       </c>
       <c r="BE31" t="inlineStr"/>
       <c r="BF31" t="inlineStr"/>
+      <c r="BG31" t="inlineStr"/>
+      <c r="BH31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
@@ -7055,6 +7125,8 @@
       <c r="BD32" t="inlineStr"/>
       <c r="BE32" t="inlineStr"/>
       <c r="BF32" t="inlineStr"/>
+      <c r="BG32" t="inlineStr"/>
+      <c r="BH32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
@@ -7259,6 +7331,8 @@
       <c r="BD33" t="inlineStr"/>
       <c r="BE33" t="inlineStr"/>
       <c r="BF33" t="inlineStr"/>
+      <c r="BG33" t="inlineStr"/>
+      <c r="BH33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
@@ -7463,6 +7537,8 @@
       <c r="BD34" t="inlineStr"/>
       <c r="BE34" t="inlineStr"/>
       <c r="BF34" t="inlineStr"/>
+      <c r="BG34" t="inlineStr"/>
+      <c r="BH34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
@@ -7667,6 +7743,8 @@
       <c r="BD35" t="inlineStr"/>
       <c r="BE35" t="inlineStr"/>
       <c r="BF35" t="inlineStr"/>
+      <c r="BG35" t="inlineStr"/>
+      <c r="BH35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
@@ -7871,6 +7949,8 @@
       <c r="BD36" t="inlineStr"/>
       <c r="BE36" t="inlineStr"/>
       <c r="BF36" t="inlineStr"/>
+      <c r="BG36" t="inlineStr"/>
+      <c r="BH36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
@@ -8075,6 +8155,8 @@
       <c r="BD37" t="inlineStr"/>
       <c r="BE37" t="inlineStr"/>
       <c r="BF37" t="inlineStr"/>
+      <c r="BG37" t="inlineStr"/>
+      <c r="BH37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
@@ -8279,6 +8361,8 @@
       <c r="BD38" t="inlineStr"/>
       <c r="BE38" t="inlineStr"/>
       <c r="BF38" t="inlineStr"/>
+      <c r="BG38" t="inlineStr"/>
+      <c r="BH38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
@@ -8483,6 +8567,8 @@
       <c r="BD39" t="inlineStr"/>
       <c r="BE39" t="inlineStr"/>
       <c r="BF39" t="inlineStr"/>
+      <c r="BG39" t="inlineStr"/>
+      <c r="BH39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
@@ -8687,6 +8773,8 @@
       <c r="BD40" t="inlineStr"/>
       <c r="BE40" t="inlineStr"/>
       <c r="BF40" t="inlineStr"/>
+      <c r="BG40" t="inlineStr"/>
+      <c r="BH40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
@@ -8887,6 +8975,8 @@
       <c r="BD41" t="inlineStr"/>
       <c r="BE41" t="inlineStr"/>
       <c r="BF41" t="inlineStr"/>
+      <c r="BG41" t="inlineStr"/>
+      <c r="BH41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
@@ -9091,6 +9181,8 @@
       <c r="BD42" t="inlineStr"/>
       <c r="BE42" t="inlineStr"/>
       <c r="BF42" t="inlineStr"/>
+      <c r="BG42" t="inlineStr"/>
+      <c r="BH42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
@@ -9295,6 +9387,8 @@
       <c r="BD43" t="inlineStr"/>
       <c r="BE43" t="inlineStr"/>
       <c r="BF43" t="inlineStr"/>
+      <c r="BG43" t="inlineStr"/>
+      <c r="BH43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
@@ -9499,6 +9593,8 @@
       <c r="BD44" t="inlineStr"/>
       <c r="BE44" t="inlineStr"/>
       <c r="BF44" t="inlineStr"/>
+      <c r="BG44" t="inlineStr"/>
+      <c r="BH44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
@@ -9703,6 +9799,8 @@
       <c r="BD45" t="inlineStr"/>
       <c r="BE45" t="inlineStr"/>
       <c r="BF45" t="inlineStr"/>
+      <c r="BG45" t="inlineStr"/>
+      <c r="BH45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
@@ -9903,6 +10001,8 @@
       <c r="BD46" t="inlineStr"/>
       <c r="BE46" t="inlineStr"/>
       <c r="BF46" t="inlineStr"/>
+      <c r="BG46" t="inlineStr"/>
+      <c r="BH46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
@@ -10107,6 +10207,8 @@
       <c r="BD47" t="inlineStr"/>
       <c r="BE47" t="inlineStr"/>
       <c r="BF47" t="inlineStr"/>
+      <c r="BG47" t="inlineStr"/>
+      <c r="BH47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
@@ -10315,6 +10417,8 @@
       </c>
       <c r="BE48" t="inlineStr"/>
       <c r="BF48" t="inlineStr"/>
+      <c r="BG48" t="inlineStr"/>
+      <c r="BH48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
@@ -10519,6 +10623,8 @@
       <c r="BD49" t="inlineStr"/>
       <c r="BE49" t="inlineStr"/>
       <c r="BF49" t="inlineStr"/>
+      <c r="BG49" t="inlineStr"/>
+      <c r="BH49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
@@ -10727,6 +10833,8 @@
       </c>
       <c r="BE50" t="inlineStr"/>
       <c r="BF50" t="inlineStr"/>
+      <c r="BG50" t="inlineStr"/>
+      <c r="BH50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
@@ -10931,6 +11039,8 @@
       <c r="BD51" t="inlineStr"/>
       <c r="BE51" t="inlineStr"/>
       <c r="BF51" t="inlineStr"/>
+      <c r="BG51" t="inlineStr"/>
+      <c r="BH51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
@@ -11135,6 +11245,8 @@
       <c r="BD52" t="inlineStr"/>
       <c r="BE52" t="inlineStr"/>
       <c r="BF52" t="inlineStr"/>
+      <c r="BG52" t="inlineStr"/>
+      <c r="BH52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
@@ -11339,6 +11451,8 @@
       <c r="BD53" t="inlineStr"/>
       <c r="BE53" t="inlineStr"/>
       <c r="BF53" t="inlineStr"/>
+      <c r="BG53" t="inlineStr"/>
+      <c r="BH53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
@@ -11543,6 +11657,8 @@
       <c r="BD54" t="inlineStr"/>
       <c r="BE54" t="inlineStr"/>
       <c r="BF54" t="inlineStr"/>
+      <c r="BG54" t="inlineStr"/>
+      <c r="BH54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
@@ -11751,6 +11867,8 @@
       </c>
       <c r="BE55" t="inlineStr"/>
       <c r="BF55" t="inlineStr"/>
+      <c r="BG55" t="inlineStr"/>
+      <c r="BH55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
@@ -11955,6 +12073,8 @@
       <c r="BD56" t="inlineStr"/>
       <c r="BE56" t="inlineStr"/>
       <c r="BF56" t="inlineStr"/>
+      <c r="BG56" t="inlineStr"/>
+      <c r="BH56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
@@ -12159,6 +12279,8 @@
       <c r="BD57" t="inlineStr"/>
       <c r="BE57" t="inlineStr"/>
       <c r="BF57" t="inlineStr"/>
+      <c r="BG57" t="inlineStr"/>
+      <c r="BH57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
@@ -12363,6 +12485,8 @@
       <c r="BD58" t="inlineStr"/>
       <c r="BE58" t="inlineStr"/>
       <c r="BF58" t="inlineStr"/>
+      <c r="BG58" t="inlineStr"/>
+      <c r="BH58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
@@ -12567,6 +12691,8 @@
       <c r="BD59" t="inlineStr"/>
       <c r="BE59" t="inlineStr"/>
       <c r="BF59" t="inlineStr"/>
+      <c r="BG59" t="inlineStr"/>
+      <c r="BH59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
@@ -12771,6 +12897,8 @@
       <c r="BD60" t="inlineStr"/>
       <c r="BE60" t="inlineStr"/>
       <c r="BF60" t="inlineStr"/>
+      <c r="BG60" t="inlineStr"/>
+      <c r="BH60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
@@ -12971,6 +13099,8 @@
       <c r="BD61" t="inlineStr"/>
       <c r="BE61" t="inlineStr"/>
       <c r="BF61" t="inlineStr"/>
+      <c r="BG61" t="inlineStr"/>
+      <c r="BH61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
@@ -13175,6 +13305,8 @@
       <c r="BD62" t="inlineStr"/>
       <c r="BE62" t="inlineStr"/>
       <c r="BF62" t="inlineStr"/>
+      <c r="BG62" t="inlineStr"/>
+      <c r="BH62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
@@ -13379,6 +13511,8 @@
       <c r="BD63" t="inlineStr"/>
       <c r="BE63" t="inlineStr"/>
       <c r="BF63" t="inlineStr"/>
+      <c r="BG63" t="inlineStr"/>
+      <c r="BH63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
@@ -13583,6 +13717,8 @@
       <c r="BD64" t="inlineStr"/>
       <c r="BE64" t="inlineStr"/>
       <c r="BF64" t="inlineStr"/>
+      <c r="BG64" t="inlineStr"/>
+      <c r="BH64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
@@ -13787,6 +13923,8 @@
       <c r="BD65" t="inlineStr"/>
       <c r="BE65" t="inlineStr"/>
       <c r="BF65" t="inlineStr"/>
+      <c r="BG65" t="inlineStr"/>
+      <c r="BH65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
@@ -13991,6 +14129,8 @@
       <c r="BD66" t="inlineStr"/>
       <c r="BE66" t="inlineStr"/>
       <c r="BF66" t="inlineStr"/>
+      <c r="BG66" t="inlineStr"/>
+      <c r="BH66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
@@ -14195,6 +14335,8 @@
       <c r="BD67" t="inlineStr"/>
       <c r="BE67" t="inlineStr"/>
       <c r="BF67" t="inlineStr"/>
+      <c r="BG67" t="inlineStr"/>
+      <c r="BH67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
@@ -14399,6 +14541,8 @@
       <c r="BD68" t="inlineStr"/>
       <c r="BE68" t="inlineStr"/>
       <c r="BF68" t="inlineStr"/>
+      <c r="BG68" t="inlineStr"/>
+      <c r="BH68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
@@ -14603,6 +14747,8 @@
       <c r="BD69" t="inlineStr"/>
       <c r="BE69" t="inlineStr"/>
       <c r="BF69" t="inlineStr"/>
+      <c r="BG69" t="inlineStr"/>
+      <c r="BH69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
@@ -14811,6 +14957,8 @@
       </c>
       <c r="BE70" t="inlineStr"/>
       <c r="BF70" t="inlineStr"/>
+      <c r="BG70" t="inlineStr"/>
+      <c r="BH70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
@@ -15015,6 +15163,8 @@
       <c r="BD71" t="inlineStr"/>
       <c r="BE71" t="inlineStr"/>
       <c r="BF71" t="inlineStr"/>
+      <c r="BG71" t="inlineStr"/>
+      <c r="BH71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
@@ -15219,6 +15369,8 @@
       <c r="BD72" t="inlineStr"/>
       <c r="BE72" t="inlineStr"/>
       <c r="BF72" t="inlineStr"/>
+      <c r="BG72" t="inlineStr"/>
+      <c r="BH72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
@@ -15423,6 +15575,8 @@
       <c r="BD73" t="inlineStr"/>
       <c r="BE73" t="inlineStr"/>
       <c r="BF73" t="inlineStr"/>
+      <c r="BG73" t="inlineStr"/>
+      <c r="BH73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
@@ -15627,6 +15781,8 @@
       <c r="BD74" t="inlineStr"/>
       <c r="BE74" t="inlineStr"/>
       <c r="BF74" t="inlineStr"/>
+      <c r="BG74" t="inlineStr"/>
+      <c r="BH74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
@@ -15831,6 +15987,8 @@
       <c r="BD75" t="inlineStr"/>
       <c r="BE75" t="inlineStr"/>
       <c r="BF75" t="inlineStr"/>
+      <c r="BG75" t="inlineStr"/>
+      <c r="BH75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
@@ -16035,6 +16193,8 @@
       <c r="BD76" t="inlineStr"/>
       <c r="BE76" t="inlineStr"/>
       <c r="BF76" t="inlineStr"/>
+      <c r="BG76" t="inlineStr"/>
+      <c r="BH76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
@@ -16239,6 +16399,8 @@
       <c r="BD77" t="inlineStr"/>
       <c r="BE77" t="inlineStr"/>
       <c r="BF77" t="inlineStr"/>
+      <c r="BG77" t="inlineStr"/>
+      <c r="BH77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
@@ -16443,6 +16605,8 @@
       <c r="BD78" t="inlineStr"/>
       <c r="BE78" t="inlineStr"/>
       <c r="BF78" t="inlineStr"/>
+      <c r="BG78" t="inlineStr"/>
+      <c r="BH78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
@@ -16647,6 +16811,8 @@
       <c r="BD79" t="inlineStr"/>
       <c r="BE79" t="inlineStr"/>
       <c r="BF79" t="inlineStr"/>
+      <c r="BG79" t="inlineStr"/>
+      <c r="BH79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
@@ -16851,6 +17017,8 @@
       <c r="BD80" t="inlineStr"/>
       <c r="BE80" t="inlineStr"/>
       <c r="BF80" t="inlineStr"/>
+      <c r="BG80" t="inlineStr"/>
+      <c r="BH80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
@@ -17055,6 +17223,8 @@
       <c r="BD81" t="inlineStr"/>
       <c r="BE81" t="inlineStr"/>
       <c r="BF81" t="inlineStr"/>
+      <c r="BG81" t="inlineStr"/>
+      <c r="BH81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
@@ -17259,6 +17429,8 @@
       <c r="BD82" t="inlineStr"/>
       <c r="BE82" t="inlineStr"/>
       <c r="BF82" t="inlineStr"/>
+      <c r="BG82" t="inlineStr"/>
+      <c r="BH82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
@@ -17467,6 +17639,8 @@
       </c>
       <c r="BE83" t="inlineStr"/>
       <c r="BF83" t="inlineStr"/>
+      <c r="BG83" t="inlineStr"/>
+      <c r="BH83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
@@ -17675,6 +17849,8 @@
       </c>
       <c r="BE84" t="inlineStr"/>
       <c r="BF84" t="inlineStr"/>
+      <c r="BG84" t="inlineStr"/>
+      <c r="BH84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
@@ -17879,6 +18055,8 @@
       <c r="BD85" t="inlineStr"/>
       <c r="BE85" t="inlineStr"/>
       <c r="BF85" t="inlineStr"/>
+      <c r="BG85" t="inlineStr"/>
+      <c r="BH85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
@@ -18087,6 +18265,8 @@
       </c>
       <c r="BE86" t="inlineStr"/>
       <c r="BF86" t="inlineStr"/>
+      <c r="BG86" t="inlineStr"/>
+      <c r="BH86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
@@ -18291,6 +18471,8 @@
       <c r="BD87" t="inlineStr"/>
       <c r="BE87" t="inlineStr"/>
       <c r="BF87" t="inlineStr"/>
+      <c r="BG87" t="inlineStr"/>
+      <c r="BH87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
@@ -18491,6 +18673,8 @@
       <c r="BD88" t="inlineStr"/>
       <c r="BE88" t="inlineStr"/>
       <c r="BF88" t="inlineStr"/>
+      <c r="BG88" t="inlineStr"/>
+      <c r="BH88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
@@ -18695,6 +18879,8 @@
       <c r="BD89" t="inlineStr"/>
       <c r="BE89" t="inlineStr"/>
       <c r="BF89" t="inlineStr"/>
+      <c r="BG89" t="inlineStr"/>
+      <c r="BH89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
@@ -18899,6 +19085,8 @@
       <c r="BD90" t="inlineStr"/>
       <c r="BE90" t="inlineStr"/>
       <c r="BF90" t="inlineStr"/>
+      <c r="BG90" t="inlineStr"/>
+      <c r="BH90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
@@ -19103,6 +19291,8 @@
       <c r="BD91" t="inlineStr"/>
       <c r="BE91" t="inlineStr"/>
       <c r="BF91" t="inlineStr"/>
+      <c r="BG91" t="inlineStr"/>
+      <c r="BH91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
@@ -19307,6 +19497,8 @@
       <c r="BD92" t="inlineStr"/>
       <c r="BE92" t="inlineStr"/>
       <c r="BF92" t="inlineStr"/>
+      <c r="BG92" t="inlineStr"/>
+      <c r="BH92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
@@ -19515,6 +19707,8 @@
       </c>
       <c r="BE93" t="inlineStr"/>
       <c r="BF93" t="inlineStr"/>
+      <c r="BG93" t="inlineStr"/>
+      <c r="BH93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
@@ -19719,6 +19913,8 @@
       <c r="BD94" t="inlineStr"/>
       <c r="BE94" t="inlineStr"/>
       <c r="BF94" t="inlineStr"/>
+      <c r="BG94" t="inlineStr"/>
+      <c r="BH94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
@@ -19923,6 +20119,8 @@
       <c r="BD95" t="inlineStr"/>
       <c r="BE95" t="inlineStr"/>
       <c r="BF95" t="inlineStr"/>
+      <c r="BG95" t="inlineStr"/>
+      <c r="BH95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
@@ -20127,6 +20325,8 @@
       <c r="BD96" t="inlineStr"/>
       <c r="BE96" t="inlineStr"/>
       <c r="BF96" t="inlineStr"/>
+      <c r="BG96" t="inlineStr"/>
+      <c r="BH96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
@@ -20331,6 +20531,8 @@
       <c r="BD97" t="inlineStr"/>
       <c r="BE97" t="inlineStr"/>
       <c r="BF97" t="inlineStr"/>
+      <c r="BG97" t="inlineStr"/>
+      <c r="BH97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
@@ -20535,6 +20737,8 @@
       <c r="BD98" t="inlineStr"/>
       <c r="BE98" t="inlineStr"/>
       <c r="BF98" t="inlineStr"/>
+      <c r="BG98" t="inlineStr"/>
+      <c r="BH98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
@@ -20739,6 +20943,8 @@
       <c r="BD99" t="inlineStr"/>
       <c r="BE99" t="inlineStr"/>
       <c r="BF99" t="inlineStr"/>
+      <c r="BG99" t="inlineStr"/>
+      <c r="BH99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
@@ -20943,6 +21149,8 @@
       <c r="BD100" t="inlineStr"/>
       <c r="BE100" t="inlineStr"/>
       <c r="BF100" t="inlineStr"/>
+      <c r="BG100" t="inlineStr"/>
+      <c r="BH100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
@@ -21151,6 +21359,8 @@
       </c>
       <c r="BE101" t="inlineStr"/>
       <c r="BF101" t="inlineStr"/>
+      <c r="BG101" t="inlineStr"/>
+      <c r="BH101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
@@ -21351,6 +21561,8 @@
       <c r="BD102" t="inlineStr"/>
       <c r="BE102" t="inlineStr"/>
       <c r="BF102" t="inlineStr"/>
+      <c r="BG102" t="inlineStr"/>
+      <c r="BH102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
@@ -21559,6 +21771,8 @@
       </c>
       <c r="BE103" t="inlineStr"/>
       <c r="BF103" t="inlineStr"/>
+      <c r="BG103" t="inlineStr"/>
+      <c r="BH103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
@@ -21767,6 +21981,8 @@
       </c>
       <c r="BE104" t="inlineStr"/>
       <c r="BF104" t="inlineStr"/>
+      <c r="BG104" t="inlineStr"/>
+      <c r="BH104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
@@ -21971,6 +22187,8 @@
       <c r="BD105" t="inlineStr"/>
       <c r="BE105" t="inlineStr"/>
       <c r="BF105" t="inlineStr"/>
+      <c r="BG105" t="inlineStr"/>
+      <c r="BH105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
@@ -22179,6 +22397,8 @@
       </c>
       <c r="BE106" t="inlineStr"/>
       <c r="BF106" t="inlineStr"/>
+      <c r="BG106" t="inlineStr"/>
+      <c r="BH106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
@@ -22383,6 +22603,8 @@
       <c r="BD107" t="inlineStr"/>
       <c r="BE107" t="inlineStr"/>
       <c r="BF107" t="inlineStr"/>
+      <c r="BG107" t="inlineStr"/>
+      <c r="BH107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
@@ -22587,6 +22809,8 @@
       <c r="BD108" t="inlineStr"/>
       <c r="BE108" t="inlineStr"/>
       <c r="BF108" t="inlineStr"/>
+      <c r="BG108" t="inlineStr"/>
+      <c r="BH108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
@@ -22791,6 +23015,8 @@
       <c r="BD109" t="inlineStr"/>
       <c r="BE109" t="inlineStr"/>
       <c r="BF109" t="inlineStr"/>
+      <c r="BG109" t="inlineStr"/>
+      <c r="BH109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
@@ -22995,6 +23221,8 @@
       <c r="BD110" t="inlineStr"/>
       <c r="BE110" t="inlineStr"/>
       <c r="BF110" t="inlineStr"/>
+      <c r="BG110" t="inlineStr"/>
+      <c r="BH110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
@@ -23203,6 +23431,8 @@
       </c>
       <c r="BE111" t="inlineStr"/>
       <c r="BF111" t="inlineStr"/>
+      <c r="BG111" t="inlineStr"/>
+      <c r="BH111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
@@ -23411,6 +23641,8 @@
       </c>
       <c r="BE112" t="inlineStr"/>
       <c r="BF112" t="inlineStr"/>
+      <c r="BG112" t="inlineStr"/>
+      <c r="BH112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
@@ -23619,6 +23851,8 @@
       </c>
       <c r="BE113" t="inlineStr"/>
       <c r="BF113" t="inlineStr"/>
+      <c r="BG113" t="inlineStr"/>
+      <c r="BH113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
@@ -23823,6 +24057,8 @@
       <c r="BD114" t="inlineStr"/>
       <c r="BE114" t="inlineStr"/>
       <c r="BF114" t="inlineStr"/>
+      <c r="BG114" t="inlineStr"/>
+      <c r="BH114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
@@ -24031,6 +24267,8 @@
       </c>
       <c r="BE115" t="inlineStr"/>
       <c r="BF115" t="inlineStr"/>
+      <c r="BG115" t="inlineStr"/>
+      <c r="BH115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
@@ -24235,6 +24473,8 @@
       <c r="BD116" t="inlineStr"/>
       <c r="BE116" t="inlineStr"/>
       <c r="BF116" t="inlineStr"/>
+      <c r="BG116" t="inlineStr"/>
+      <c r="BH116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
@@ -24439,6 +24679,8 @@
       <c r="BD117" t="inlineStr"/>
       <c r="BE117" t="inlineStr"/>
       <c r="BF117" t="inlineStr"/>
+      <c r="BG117" t="inlineStr"/>
+      <c r="BH117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
@@ -24647,6 +24889,8 @@
       </c>
       <c r="BE118" t="inlineStr"/>
       <c r="BF118" t="inlineStr"/>
+      <c r="BG118" t="inlineStr"/>
+      <c r="BH118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
@@ -24851,6 +25095,8 @@
       <c r="BD119" t="inlineStr"/>
       <c r="BE119" t="inlineStr"/>
       <c r="BF119" t="inlineStr"/>
+      <c r="BG119" t="inlineStr"/>
+      <c r="BH119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
@@ -25055,6 +25301,8 @@
       <c r="BD120" t="inlineStr"/>
       <c r="BE120" t="inlineStr"/>
       <c r="BF120" t="inlineStr"/>
+      <c r="BG120" t="inlineStr"/>
+      <c r="BH120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
@@ -25259,6 +25507,8 @@
       <c r="BD121" t="inlineStr"/>
       <c r="BE121" t="inlineStr"/>
       <c r="BF121" t="inlineStr"/>
+      <c r="BG121" t="inlineStr"/>
+      <c r="BH121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
@@ -25463,6 +25713,8 @@
       <c r="BD122" t="inlineStr"/>
       <c r="BE122" t="inlineStr"/>
       <c r="BF122" t="inlineStr"/>
+      <c r="BG122" t="inlineStr"/>
+      <c r="BH122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
@@ -25667,6 +25919,8 @@
       <c r="BD123" t="inlineStr"/>
       <c r="BE123" t="inlineStr"/>
       <c r="BF123" t="inlineStr"/>
+      <c r="BG123" t="inlineStr"/>
+      <c r="BH123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
@@ -25871,6 +26125,8 @@
       <c r="BD124" t="inlineStr"/>
       <c r="BE124" t="inlineStr"/>
       <c r="BF124" t="inlineStr"/>
+      <c r="BG124" t="inlineStr"/>
+      <c r="BH124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
@@ -26075,6 +26331,8 @@
       <c r="BD125" t="inlineStr"/>
       <c r="BE125" t="inlineStr"/>
       <c r="BF125" t="inlineStr"/>
+      <c r="BG125" t="inlineStr"/>
+      <c r="BH125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
@@ -26275,6 +26533,8 @@
       <c r="BD126" t="inlineStr"/>
       <c r="BE126" t="inlineStr"/>
       <c r="BF126" t="inlineStr"/>
+      <c r="BG126" t="inlineStr"/>
+      <c r="BH126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
@@ -26479,6 +26739,8 @@
       <c r="BD127" t="inlineStr"/>
       <c r="BE127" t="inlineStr"/>
       <c r="BF127" t="inlineStr"/>
+      <c r="BG127" t="inlineStr"/>
+      <c r="BH127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
@@ -26683,6 +26945,8 @@
       <c r="BD128" t="inlineStr"/>
       <c r="BE128" t="inlineStr"/>
       <c r="BF128" t="inlineStr"/>
+      <c r="BG128" t="inlineStr"/>
+      <c r="BH128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
@@ -26887,6 +27151,8 @@
       <c r="BD129" t="inlineStr"/>
       <c r="BE129" t="inlineStr"/>
       <c r="BF129" t="inlineStr"/>
+      <c r="BG129" t="inlineStr"/>
+      <c r="BH129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
@@ -27091,6 +27357,8 @@
       <c r="BD130" t="inlineStr"/>
       <c r="BE130" t="inlineStr"/>
       <c r="BF130" t="inlineStr"/>
+      <c r="BG130" t="inlineStr"/>
+      <c r="BH130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
@@ -27295,6 +27563,8 @@
       <c r="BD131" t="inlineStr"/>
       <c r="BE131" t="inlineStr"/>
       <c r="BF131" t="inlineStr"/>
+      <c r="BG131" t="inlineStr"/>
+      <c r="BH131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
@@ -27499,6 +27769,8 @@
       <c r="BD132" t="inlineStr"/>
       <c r="BE132" t="inlineStr"/>
       <c r="BF132" t="inlineStr"/>
+      <c r="BG132" t="inlineStr"/>
+      <c r="BH132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
@@ -27703,6 +27975,8 @@
       <c r="BD133" t="inlineStr"/>
       <c r="BE133" t="inlineStr"/>
       <c r="BF133" t="inlineStr"/>
+      <c r="BG133" t="inlineStr"/>
+      <c r="BH133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
@@ -27907,6 +28181,8 @@
       <c r="BD134" t="inlineStr"/>
       <c r="BE134" t="inlineStr"/>
       <c r="BF134" t="inlineStr"/>
+      <c r="BG134" t="inlineStr"/>
+      <c r="BH134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
@@ -28115,6 +28391,8 @@
       </c>
       <c r="BE135" t="inlineStr"/>
       <c r="BF135" t="inlineStr"/>
+      <c r="BG135" t="inlineStr"/>
+      <c r="BH135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
@@ -28319,6 +28597,8 @@
       <c r="BD136" t="inlineStr"/>
       <c r="BE136" t="inlineStr"/>
       <c r="BF136" t="inlineStr"/>
+      <c r="BG136" t="inlineStr"/>
+      <c r="BH136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
@@ -28519,6 +28799,8 @@
       <c r="BD137" t="inlineStr"/>
       <c r="BE137" t="inlineStr"/>
       <c r="BF137" t="inlineStr"/>
+      <c r="BG137" t="inlineStr"/>
+      <c r="BH137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
@@ -28723,6 +29005,8 @@
       <c r="BD138" t="inlineStr"/>
       <c r="BE138" t="inlineStr"/>
       <c r="BF138" t="inlineStr"/>
+      <c r="BG138" t="inlineStr"/>
+      <c r="BH138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
@@ -28927,6 +29211,8 @@
       <c r="BD139" t="inlineStr"/>
       <c r="BE139" t="inlineStr"/>
       <c r="BF139" t="inlineStr"/>
+      <c r="BG139" t="inlineStr"/>
+      <c r="BH139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
@@ -29131,6 +29417,8 @@
       <c r="BD140" t="inlineStr"/>
       <c r="BE140" t="inlineStr"/>
       <c r="BF140" t="inlineStr"/>
+      <c r="BG140" t="inlineStr"/>
+      <c r="BH140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
@@ -29335,6 +29623,8 @@
       <c r="BD141" t="inlineStr"/>
       <c r="BE141" t="inlineStr"/>
       <c r="BF141" t="inlineStr"/>
+      <c r="BG141" t="inlineStr"/>
+      <c r="BH141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
@@ -29539,6 +29829,8 @@
       <c r="BD142" t="inlineStr"/>
       <c r="BE142" t="inlineStr"/>
       <c r="BF142" t="inlineStr"/>
+      <c r="BG142" t="inlineStr"/>
+      <c r="BH142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
@@ -29743,6 +30035,8 @@
       <c r="BD143" t="inlineStr"/>
       <c r="BE143" t="inlineStr"/>
       <c r="BF143" t="inlineStr"/>
+      <c r="BG143" t="inlineStr"/>
+      <c r="BH143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
@@ -29947,6 +30241,8 @@
       <c r="BD144" t="inlineStr"/>
       <c r="BE144" t="inlineStr"/>
       <c r="BF144" t="inlineStr"/>
+      <c r="BG144" t="inlineStr"/>
+      <c r="BH144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
@@ -30155,6 +30451,8 @@
       </c>
       <c r="BE145" t="inlineStr"/>
       <c r="BF145" t="inlineStr"/>
+      <c r="BG145" t="inlineStr"/>
+      <c r="BH145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
@@ -30359,6 +30657,8 @@
       <c r="BD146" t="inlineStr"/>
       <c r="BE146" t="inlineStr"/>
       <c r="BF146" t="inlineStr"/>
+      <c r="BG146" t="inlineStr"/>
+      <c r="BH146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
@@ -30563,6 +30863,8 @@
       <c r="BD147" t="inlineStr"/>
       <c r="BE147" t="inlineStr"/>
       <c r="BF147" t="inlineStr"/>
+      <c r="BG147" t="inlineStr"/>
+      <c r="BH147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
@@ -30771,6 +31073,8 @@
       </c>
       <c r="BE148" t="inlineStr"/>
       <c r="BF148" t="inlineStr"/>
+      <c r="BG148" t="inlineStr"/>
+      <c r="BH148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
@@ -30975,6 +31279,8 @@
       <c r="BD149" t="inlineStr"/>
       <c r="BE149" t="inlineStr"/>
       <c r="BF149" t="inlineStr"/>
+      <c r="BG149" t="inlineStr"/>
+      <c r="BH149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
@@ -31179,6 +31485,8 @@
       <c r="BD150" t="inlineStr"/>
       <c r="BE150" t="inlineStr"/>
       <c r="BF150" t="inlineStr"/>
+      <c r="BG150" t="inlineStr"/>
+      <c r="BH150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
@@ -31383,6 +31691,8 @@
       <c r="BD151" t="inlineStr"/>
       <c r="BE151" t="inlineStr"/>
       <c r="BF151" t="inlineStr"/>
+      <c r="BG151" t="inlineStr"/>
+      <c r="BH151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
@@ -31587,6 +31897,8 @@
       <c r="BD152" t="inlineStr"/>
       <c r="BE152" t="inlineStr"/>
       <c r="BF152" t="inlineStr"/>
+      <c r="BG152" t="inlineStr"/>
+      <c r="BH152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
@@ -31791,6 +32103,8 @@
       <c r="BD153" t="inlineStr"/>
       <c r="BE153" t="inlineStr"/>
       <c r="BF153" t="inlineStr"/>
+      <c r="BG153" t="inlineStr"/>
+      <c r="BH153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
@@ -31995,6 +32309,8 @@
       <c r="BD154" t="inlineStr"/>
       <c r="BE154" t="inlineStr"/>
       <c r="BF154" t="inlineStr"/>
+      <c r="BG154" t="inlineStr"/>
+      <c r="BH154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
@@ -32199,6 +32515,8 @@
       <c r="BD155" t="inlineStr"/>
       <c r="BE155" t="inlineStr"/>
       <c r="BF155" t="inlineStr"/>
+      <c r="BG155" t="inlineStr"/>
+      <c r="BH155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
@@ -32403,6 +32721,8 @@
       <c r="BD156" t="inlineStr"/>
       <c r="BE156" t="inlineStr"/>
       <c r="BF156" t="inlineStr"/>
+      <c r="BG156" t="inlineStr"/>
+      <c r="BH156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" s="1" t="inlineStr">
@@ -32608,6 +32928,8 @@
       <c r="BD157" t="inlineStr"/>
       <c r="BE157" t="inlineStr"/>
       <c r="BF157" t="inlineStr"/>
+      <c r="BG157" t="inlineStr"/>
+      <c r="BH157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" s="1" t="inlineStr">
@@ -32812,6 +33134,8 @@
       <c r="BD158" t="inlineStr"/>
       <c r="BE158" t="inlineStr"/>
       <c r="BF158" t="inlineStr"/>
+      <c r="BG158" t="inlineStr"/>
+      <c r="BH158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" s="1" t="inlineStr">
@@ -33020,6 +33344,8 @@
       </c>
       <c r="BE159" t="inlineStr"/>
       <c r="BF159" t="inlineStr"/>
+      <c r="BG159" t="inlineStr"/>
+      <c r="BH159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" s="1" t="inlineStr">
@@ -33224,6 +33550,8 @@
       <c r="BD160" t="inlineStr"/>
       <c r="BE160" t="inlineStr"/>
       <c r="BF160" t="inlineStr"/>
+      <c r="BG160" t="inlineStr"/>
+      <c r="BH160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" s="1" t="inlineStr">
@@ -33428,6 +33756,8 @@
       <c r="BD161" t="inlineStr"/>
       <c r="BE161" t="inlineStr"/>
       <c r="BF161" t="inlineStr"/>
+      <c r="BG161" t="inlineStr"/>
+      <c r="BH161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" s="1" t="inlineStr">
@@ -33632,6 +33962,8 @@
       <c r="BD162" t="inlineStr"/>
       <c r="BE162" t="inlineStr"/>
       <c r="BF162" t="inlineStr"/>
+      <c r="BG162" t="inlineStr"/>
+      <c r="BH162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" s="1" t="inlineStr">
@@ -33836,6 +34168,8 @@
       <c r="BD163" t="inlineStr"/>
       <c r="BE163" t="inlineStr"/>
       <c r="BF163" t="inlineStr"/>
+      <c r="BG163" t="inlineStr"/>
+      <c r="BH163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" s="1" t="inlineStr">
@@ -34040,6 +34374,8 @@
       <c r="BD164" t="inlineStr"/>
       <c r="BE164" t="inlineStr"/>
       <c r="BF164" t="inlineStr"/>
+      <c r="BG164" t="inlineStr"/>
+      <c r="BH164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" s="1" t="inlineStr">
@@ -34248,6 +34584,8 @@
       </c>
       <c r="BE165" t="inlineStr"/>
       <c r="BF165" t="inlineStr"/>
+      <c r="BG165" t="inlineStr"/>
+      <c r="BH165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" s="1" t="inlineStr">
@@ -34452,6 +34790,8 @@
       <c r="BD166" t="inlineStr"/>
       <c r="BE166" t="inlineStr"/>
       <c r="BF166" t="inlineStr"/>
+      <c r="BG166" t="inlineStr"/>
+      <c r="BH166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" s="1" t="inlineStr">
@@ -34656,6 +34996,8 @@
       <c r="BD167" t="inlineStr"/>
       <c r="BE167" t="inlineStr"/>
       <c r="BF167" t="inlineStr"/>
+      <c r="BG167" t="inlineStr"/>
+      <c r="BH167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" s="1" t="inlineStr">
@@ -34860,6 +35202,8 @@
       <c r="BD168" t="inlineStr"/>
       <c r="BE168" t="inlineStr"/>
       <c r="BF168" t="inlineStr"/>
+      <c r="BG168" t="inlineStr"/>
+      <c r="BH168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" s="1" t="inlineStr">
@@ -35064,6 +35408,8 @@
       <c r="BD169" t="inlineStr"/>
       <c r="BE169" t="inlineStr"/>
       <c r="BF169" t="inlineStr"/>
+      <c r="BG169" t="inlineStr"/>
+      <c r="BH169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" s="1" t="inlineStr">
@@ -35268,6 +35614,8 @@
       <c r="BD170" t="inlineStr"/>
       <c r="BE170" t="inlineStr"/>
       <c r="BF170" t="inlineStr"/>
+      <c r="BG170" t="inlineStr"/>
+      <c r="BH170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" s="1" t="inlineStr">
@@ -35472,6 +35820,8 @@
       <c r="BD171" t="inlineStr"/>
       <c r="BE171" t="inlineStr"/>
       <c r="BF171" t="inlineStr"/>
+      <c r="BG171" t="inlineStr"/>
+      <c r="BH171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" s="1" t="inlineStr">
@@ -35676,6 +36026,8 @@
       <c r="BD172" t="inlineStr"/>
       <c r="BE172" t="inlineStr"/>
       <c r="BF172" t="inlineStr"/>
+      <c r="BG172" t="inlineStr"/>
+      <c r="BH172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" s="1" t="inlineStr">
@@ -35880,6 +36232,8 @@
       <c r="BD173" t="inlineStr"/>
       <c r="BE173" t="inlineStr"/>
       <c r="BF173" t="inlineStr"/>
+      <c r="BG173" t="inlineStr"/>
+      <c r="BH173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" s="1" t="inlineStr">
@@ -36088,6 +36442,8 @@
       </c>
       <c r="BE174" t="inlineStr"/>
       <c r="BF174" t="inlineStr"/>
+      <c r="BG174" t="inlineStr"/>
+      <c r="BH174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" s="1" t="inlineStr">
@@ -36292,6 +36648,8 @@
       <c r="BD175" t="inlineStr"/>
       <c r="BE175" t="inlineStr"/>
       <c r="BF175" t="inlineStr"/>
+      <c r="BG175" t="inlineStr"/>
+      <c r="BH175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" s="1" t="inlineStr">
@@ -36496,6 +36854,8 @@
       <c r="BD176" t="inlineStr"/>
       <c r="BE176" t="inlineStr"/>
       <c r="BF176" t="inlineStr"/>
+      <c r="BG176" t="inlineStr"/>
+      <c r="BH176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" s="1" t="inlineStr">
@@ -36696,6 +37056,8 @@
       <c r="BD177" t="inlineStr"/>
       <c r="BE177" t="inlineStr"/>
       <c r="BF177" t="inlineStr"/>
+      <c r="BG177" t="inlineStr"/>
+      <c r="BH177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" s="1" t="inlineStr">
@@ -36885,6 +37247,8 @@
       <c r="BD178" t="inlineStr"/>
       <c r="BE178" t="inlineStr"/>
       <c r="BF178" t="inlineStr"/>
+      <c r="BG178" t="inlineStr"/>
+      <c r="BH178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" s="1" t="inlineStr">
@@ -37078,6 +37442,8 @@
       <c r="BF179" t="n">
         <v>4</v>
       </c>
+      <c r="BG179" t="inlineStr"/>
+      <c r="BH179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" s="1" t="inlineStr">
@@ -37271,6 +37637,8 @@
       <c r="BF180" t="n">
         <v>0</v>
       </c>
+      <c r="BG180" t="inlineStr"/>
+      <c r="BH180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" s="1" t="inlineStr">
@@ -37468,6 +37836,8 @@
       <c r="BF181" t="n">
         <v>3</v>
       </c>
+      <c r="BG181" t="inlineStr"/>
+      <c r="BH181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" s="1" t="inlineStr">
@@ -37661,6 +38031,8 @@
       <c r="BF182" t="n">
         <v>3</v>
       </c>
+      <c r="BG182" t="inlineStr"/>
+      <c r="BH182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" s="1" t="inlineStr">
@@ -37858,6 +38230,8 @@
       <c r="BF183" t="n">
         <v>3</v>
       </c>
+      <c r="BG183" t="inlineStr"/>
+      <c r="BH183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" s="1" t="inlineStr">
@@ -38051,6 +38425,8 @@
       <c r="BF184" t="n">
         <v>4</v>
       </c>
+      <c r="BG184" t="inlineStr"/>
+      <c r="BH184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" s="1" t="inlineStr">
@@ -38244,6 +38620,8 @@
       <c r="BF185" t="n">
         <v>0</v>
       </c>
+      <c r="BG185" t="inlineStr"/>
+      <c r="BH185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" s="1" t="inlineStr">
@@ -38437,6 +38815,8 @@
       <c r="BF186" t="n">
         <v>1</v>
       </c>
+      <c r="BG186" t="inlineStr"/>
+      <c r="BH186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" s="1" t="inlineStr">
@@ -38630,6 +39010,8 @@
       <c r="BF187" t="n">
         <v>3</v>
       </c>
+      <c r="BG187" t="inlineStr"/>
+      <c r="BH187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" s="1" t="inlineStr">
@@ -38823,6 +39205,8 @@
       <c r="BF188" t="n">
         <v>5</v>
       </c>
+      <c r="BG188" t="inlineStr"/>
+      <c r="BH188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" s="1" t="inlineStr">
@@ -39016,6 +39400,8 @@
       <c r="BF189" t="n">
         <v>3</v>
       </c>
+      <c r="BG189" t="inlineStr"/>
+      <c r="BH189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" s="1" t="inlineStr">
@@ -39209,6 +39595,8 @@
       <c r="BF190" t="n">
         <v>2</v>
       </c>
+      <c r="BG190" t="inlineStr"/>
+      <c r="BH190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" s="1" t="inlineStr">
@@ -39402,6 +39790,8 @@
       <c r="BF191" t="n">
         <v>2</v>
       </c>
+      <c r="BG191" t="inlineStr"/>
+      <c r="BH191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" s="1" t="inlineStr">
@@ -39595,6 +39985,8 @@
       <c r="BF192" t="n">
         <v>1</v>
       </c>
+      <c r="BG192" t="inlineStr"/>
+      <c r="BH192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" s="1" t="inlineStr">
@@ -39784,6 +40176,8 @@
       <c r="BD193" t="inlineStr"/>
       <c r="BE193" t="inlineStr"/>
       <c r="BF193" t="inlineStr"/>
+      <c r="BG193" t="inlineStr"/>
+      <c r="BH193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" s="1" t="inlineStr">
@@ -39977,6 +40371,8 @@
       <c r="BF194" t="n">
         <v>3</v>
       </c>
+      <c r="BG194" t="inlineStr"/>
+      <c r="BH194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" s="1" t="inlineStr">
@@ -40170,6 +40566,8 @@
       <c r="BF195" t="n">
         <v>0</v>
       </c>
+      <c r="BG195" t="inlineStr"/>
+      <c r="BH195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" s="1" t="inlineStr">
@@ -40363,6 +40761,8 @@
       <c r="BF196" t="n">
         <v>5</v>
       </c>
+      <c r="BG196" t="inlineStr"/>
+      <c r="BH196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" s="1" t="inlineStr">
@@ -40556,6 +40956,8 @@
       <c r="BF197" t="n">
         <v>2</v>
       </c>
+      <c r="BG197" t="inlineStr"/>
+      <c r="BH197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" s="1" t="inlineStr">
@@ -40749,6 +41151,8 @@
       <c r="BF198" t="n">
         <v>4</v>
       </c>
+      <c r="BG198" t="inlineStr"/>
+      <c r="BH198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" s="1" t="inlineStr">
@@ -40942,6 +41346,8 @@
       <c r="BF199" t="n">
         <v>6</v>
       </c>
+      <c r="BG199" t="inlineStr"/>
+      <c r="BH199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" s="1" t="inlineStr">
@@ -41139,6 +41545,8 @@
       <c r="BF200" t="n">
         <v>1</v>
       </c>
+      <c r="BG200" t="inlineStr"/>
+      <c r="BH200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" s="1" t="inlineStr">
@@ -41332,6 +41740,8 @@
       <c r="BF201" t="n">
         <v>0</v>
       </c>
+      <c r="BG201" t="inlineStr"/>
+      <c r="BH201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" s="1" t="inlineStr">
@@ -41525,6 +41935,8 @@
       <c r="BF202" t="n">
         <v>0</v>
       </c>
+      <c r="BG202" t="inlineStr"/>
+      <c r="BH202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" s="1" t="inlineStr">
@@ -41718,6 +42130,8 @@
       <c r="BF203" t="n">
         <v>2</v>
       </c>
+      <c r="BG203" t="inlineStr"/>
+      <c r="BH203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" s="1" t="inlineStr">
@@ -41911,6 +42325,8 @@
       <c r="BF204" t="n">
         <v>2</v>
       </c>
+      <c r="BG204" t="inlineStr"/>
+      <c r="BH204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" s="1" t="inlineStr">
@@ -42104,6 +42520,8 @@
       <c r="BF205" t="n">
         <v>2</v>
       </c>
+      <c r="BG205" t="inlineStr"/>
+      <c r="BH205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" s="1" t="inlineStr">
@@ -42297,6 +42715,8 @@
       <c r="BF206" t="n">
         <v>6</v>
       </c>
+      <c r="BG206" t="inlineStr"/>
+      <c r="BH206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" s="1" t="inlineStr">
@@ -42490,6 +42910,8 @@
       <c r="BF207" t="n">
         <v>2</v>
       </c>
+      <c r="BG207" t="inlineStr"/>
+      <c r="BH207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" s="1" t="inlineStr">
@@ -42683,6 +43105,8 @@
       <c r="BF208" t="n">
         <v>8</v>
       </c>
+      <c r="BG208" t="inlineStr"/>
+      <c r="BH208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" s="1" t="inlineStr">
@@ -42876,6 +43300,8 @@
       <c r="BF209" t="n">
         <v>3</v>
       </c>
+      <c r="BG209" t="inlineStr"/>
+      <c r="BH209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" s="1" t="inlineStr">
@@ -43077,6 +43503,8 @@
       <c r="BF210" t="n">
         <v>3</v>
       </c>
+      <c r="BG210" t="inlineStr"/>
+      <c r="BH210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" s="1" t="inlineStr">
@@ -43278,6 +43706,8 @@
       </c>
       <c r="BE211" t="inlineStr"/>
       <c r="BF211" t="inlineStr"/>
+      <c r="BG211" t="inlineStr"/>
+      <c r="BH211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" s="1" t="inlineStr">
@@ -43312,15 +43742,11 @@
           <t>15 034</t>
         </is>
       </c>
-      <c r="G212" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H212" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="G212" t="n">
+        <v>1</v>
+      </c>
+      <c r="H212" t="n">
+        <v>6</v>
       </c>
       <c r="I212" t="inlineStr">
         <is>
@@ -43342,15 +43768,11 @@
           <t>Bayern Munich</t>
         </is>
       </c>
-      <c r="M212" t="inlineStr">
-        <is>
-          <t>0.38</t>
-        </is>
-      </c>
-      <c r="N212" t="inlineStr">
-        <is>
-          <t>4.14</t>
-        </is>
+      <c r="M212" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="N212" t="n">
+        <v>4.14</v>
       </c>
       <c r="O212" t="inlineStr">
         <is>
@@ -43362,155 +43784,95 @@
           <t>64%</t>
         </is>
       </c>
-      <c r="Q212" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R212" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="S212" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="T212" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="U212" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="V212" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="W212" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="X212" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="Y212" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Z212" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AA212" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB212" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC212" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AD212" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AE212" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AF212" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG212" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AH212" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AI212" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ212" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AK212" t="inlineStr">
-        <is>
-          <t>338</t>
-        </is>
-      </c>
-      <c r="AL212" t="inlineStr">
-        <is>
-          <t>812</t>
-        </is>
-      </c>
-      <c r="AM212" t="inlineStr">
-        <is>
-          <t>264</t>
-        </is>
-      </c>
-      <c r="AN212" t="inlineStr">
-        <is>
-          <t>747</t>
-        </is>
-      </c>
-      <c r="AO212" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="AP212" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="AQ212" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AR212" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="AS212" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="AT212" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
+      <c r="Q212" t="n">
+        <v>5</v>
+      </c>
+      <c r="R212" t="n">
+        <v>23</v>
+      </c>
+      <c r="S212" t="n">
+        <v>1</v>
+      </c>
+      <c r="T212" t="n">
+        <v>13</v>
+      </c>
+      <c r="U212" t="n">
+        <v>4</v>
+      </c>
+      <c r="V212" t="n">
+        <v>10</v>
+      </c>
+      <c r="W212" t="n">
+        <v>11</v>
+      </c>
+      <c r="X212" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y212" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z212" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA212" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB212" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC212" t="n">
+        <v>16</v>
+      </c>
+      <c r="AD212" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE212" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF212" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG212" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH212" t="n">
+        <v>11</v>
+      </c>
+      <c r="AI212" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ212" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK212" t="n">
+        <v>338</v>
+      </c>
+      <c r="AL212" t="n">
+        <v>812</v>
+      </c>
+      <c r="AM212" t="n">
+        <v>264</v>
+      </c>
+      <c r="AN212" t="n">
+        <v>747</v>
+      </c>
+      <c r="AO212" t="n">
+        <v>54</v>
+      </c>
+      <c r="AP212" t="n">
+        <v>145</v>
+      </c>
+      <c r="AQ212" t="n">
+        <v>19</v>
+      </c>
+      <c r="AR212" t="n">
+        <v>73</v>
+      </c>
+      <c r="AS212" t="n">
+        <v>123</v>
+      </c>
+      <c r="AT212" t="n">
+        <v>122</v>
       </c>
       <c r="AU212" t="inlineStr">
         <is>
@@ -43550,6 +43912,8 @@
       <c r="BD212" t="inlineStr"/>
       <c r="BE212" t="inlineStr"/>
       <c r="BF212" t="inlineStr"/>
+      <c r="BG212" t="inlineStr"/>
+      <c r="BH212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" s="1" t="inlineStr">
@@ -43584,15 +43948,11 @@
           <t>53 756</t>
         </is>
       </c>
-      <c r="G213" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H213" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="G213" t="n">
+        <v>1</v>
+      </c>
+      <c r="H213" t="n">
+        <v>3</v>
       </c>
       <c r="I213" t="inlineStr">
         <is>
@@ -43614,15 +43974,11 @@
           <t>Stuttgart</t>
         </is>
       </c>
-      <c r="M213" t="inlineStr">
-        <is>
-          <t>2.12</t>
-        </is>
-      </c>
-      <c r="N213" t="inlineStr">
-        <is>
-          <t>2.11</t>
-        </is>
+      <c r="M213" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="N213" t="n">
+        <v>2.11</v>
       </c>
       <c r="O213" t="inlineStr">
         <is>
@@ -43634,155 +43990,95 @@
           <t>48%</t>
         </is>
       </c>
-      <c r="Q213" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="R213" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="S213" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="T213" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="U213" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="V213" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="W213" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="X213" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="Y213" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Z213" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA213" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AB213" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC213" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AD213" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="AE213" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AF213" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AG213" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AH213" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AI213" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AJ213" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AK213" t="inlineStr">
-        <is>
-          <t>401</t>
-        </is>
-      </c>
-      <c r="AL213" t="inlineStr">
-        <is>
-          <t>533</t>
-        </is>
-      </c>
-      <c r="AM213" t="inlineStr">
-        <is>
-          <t>321</t>
-        </is>
-      </c>
-      <c r="AN213" t="inlineStr">
-        <is>
-          <t>448</t>
-        </is>
-      </c>
-      <c r="AO213" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="AP213" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
-      </c>
-      <c r="AQ213" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="AR213" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="AS213" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="AT213" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
+      <c r="Q213" t="n">
+        <v>15</v>
+      </c>
+      <c r="R213" t="n">
+        <v>12</v>
+      </c>
+      <c r="S213" t="n">
+        <v>7</v>
+      </c>
+      <c r="T213" t="n">
+        <v>7</v>
+      </c>
+      <c r="U213" t="n">
+        <v>8</v>
+      </c>
+      <c r="V213" t="n">
+        <v>5</v>
+      </c>
+      <c r="W213" t="n">
+        <v>16</v>
+      </c>
+      <c r="X213" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y213" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z213" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA213" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB213" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC213" t="n">
+        <v>18</v>
+      </c>
+      <c r="AD213" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE213" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF213" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG213" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH213" t="n">
+        <v>12</v>
+      </c>
+      <c r="AI213" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ213" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK213" t="n">
+        <v>401</v>
+      </c>
+      <c r="AL213" t="n">
+        <v>533</v>
+      </c>
+      <c r="AM213" t="n">
+        <v>321</v>
+      </c>
+      <c r="AN213" t="n">
+        <v>448</v>
+      </c>
+      <c r="AO213" t="n">
+        <v>96</v>
+      </c>
+      <c r="AP213" t="n">
+        <v>108</v>
+      </c>
+      <c r="AQ213" t="n">
+        <v>45</v>
+      </c>
+      <c r="AR213" t="n">
+        <v>37</v>
+      </c>
+      <c r="AS213" t="n">
+        <v>114</v>
+      </c>
+      <c r="AT213" t="n">
+        <v>116</v>
       </c>
       <c r="AU213" t="inlineStr">
         <is>
@@ -43822,6 +44118,8 @@
       <c r="BD213" t="inlineStr"/>
       <c r="BE213" t="inlineStr"/>
       <c r="BF213" t="inlineStr"/>
+      <c r="BG213" t="inlineStr"/>
+      <c r="BH213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" s="1" t="inlineStr">
@@ -43856,15 +44154,11 @@
           <t>34 100</t>
         </is>
       </c>
-      <c r="G214" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H214" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G214" t="n">
+        <v>2</v>
+      </c>
+      <c r="H214" t="n">
+        <v>1</v>
       </c>
       <c r="I214" t="inlineStr">
         <is>
@@ -43886,15 +44180,11 @@
           <t>Bochum</t>
         </is>
       </c>
-      <c r="M214" t="inlineStr">
-        <is>
-          <t>4.26</t>
-        </is>
-      </c>
-      <c r="N214" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
+      <c r="M214" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="N214" t="n">
+        <v>1.65</v>
       </c>
       <c r="O214" t="inlineStr">
         <is>
@@ -43906,155 +44196,95 @@
           <t>36%</t>
         </is>
       </c>
-      <c r="Q214" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="R214" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="S214" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="T214" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U214" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="V214" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="W214" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="X214" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="Y214" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Z214" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA214" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AB214" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC214" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AD214" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="AE214" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AF214" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AG214" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AH214" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AI214" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ214" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AK214" t="inlineStr">
-        <is>
-          <t>440</t>
-        </is>
-      </c>
-      <c r="AL214" t="inlineStr">
-        <is>
-          <t>366</t>
-        </is>
-      </c>
-      <c r="AM214" t="inlineStr">
-        <is>
-          <t>348</t>
-        </is>
-      </c>
-      <c r="AN214" t="inlineStr">
-        <is>
-          <t>264</t>
-        </is>
-      </c>
-      <c r="AO214" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="AP214" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="AQ214" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="AR214" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="AS214" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="AT214" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
+      <c r="Q214" t="n">
+        <v>27</v>
+      </c>
+      <c r="R214" t="n">
+        <v>13</v>
+      </c>
+      <c r="S214" t="n">
+        <v>9</v>
+      </c>
+      <c r="T214" t="n">
+        <v>2</v>
+      </c>
+      <c r="U214" t="n">
+        <v>18</v>
+      </c>
+      <c r="V214" t="n">
+        <v>11</v>
+      </c>
+      <c r="W214" t="n">
+        <v>20</v>
+      </c>
+      <c r="X214" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y214" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z214" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA214" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB214" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC214" t="n">
+        <v>21</v>
+      </c>
+      <c r="AD214" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE214" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF214" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG214" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH214" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI214" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ214" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK214" t="n">
+        <v>440</v>
+      </c>
+      <c r="AL214" t="n">
+        <v>366</v>
+      </c>
+      <c r="AM214" t="n">
+        <v>348</v>
+      </c>
+      <c r="AN214" t="n">
+        <v>264</v>
+      </c>
+      <c r="AO214" t="n">
+        <v>92</v>
+      </c>
+      <c r="AP214" t="n">
+        <v>116</v>
+      </c>
+      <c r="AQ214" t="n">
+        <v>43</v>
+      </c>
+      <c r="AR214" t="n">
+        <v>36</v>
+      </c>
+      <c r="AS214" t="n">
+        <v>120</v>
+      </c>
+      <c r="AT214" t="n">
+        <v>116</v>
       </c>
       <c r="AU214" t="inlineStr">
         <is>
@@ -44094,6 +44324,8 @@
       <c r="BD214" t="inlineStr"/>
       <c r="BE214" t="inlineStr"/>
       <c r="BF214" t="inlineStr"/>
+      <c r="BG214" t="inlineStr"/>
+      <c r="BH214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" s="1" t="inlineStr">
@@ -44128,15 +44360,11 @@
           <t>30 000</t>
         </is>
       </c>
-      <c r="G215" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H215" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="G215" t="n">
+        <v>1</v>
+      </c>
+      <c r="H215" t="n">
+        <v>4</v>
       </c>
       <c r="I215" t="inlineStr">
         <is>
@@ -44158,15 +44386,11 @@
           <t>Bayer Leverkusen</t>
         </is>
       </c>
-      <c r="M215" t="inlineStr">
-        <is>
-          <t>1.08</t>
-        </is>
-      </c>
-      <c r="N215" t="inlineStr">
-        <is>
-          <t>3.65</t>
-        </is>
+      <c r="M215" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N215" t="n">
+        <v>3.65</v>
       </c>
       <c r="O215" t="inlineStr">
         <is>
@@ -44178,155 +44402,95 @@
           <t>48%</t>
         </is>
       </c>
-      <c r="Q215" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="R215" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="S215" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="T215" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="U215" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="V215" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="W215" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="X215" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="Y215" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Z215" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AA215" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB215" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC215" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AD215" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AE215" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AF215" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AG215" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AH215" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AI215" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AJ215" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AK215" t="inlineStr">
-        <is>
-          <t>403</t>
-        </is>
-      </c>
-      <c r="AL215" t="inlineStr">
-        <is>
-          <t>609</t>
-        </is>
-      </c>
-      <c r="AM215" t="inlineStr">
-        <is>
-          <t>343</t>
-        </is>
-      </c>
-      <c r="AN215" t="inlineStr">
-        <is>
-          <t>566</t>
-        </is>
-      </c>
-      <c r="AO215" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="AP215" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="AQ215" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="AR215" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="AS215" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="AT215" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
+      <c r="Q215" t="n">
+        <v>14</v>
+      </c>
+      <c r="R215" t="n">
+        <v>20</v>
+      </c>
+      <c r="S215" t="n">
+        <v>5</v>
+      </c>
+      <c r="T215" t="n">
+        <v>8</v>
+      </c>
+      <c r="U215" t="n">
+        <v>9</v>
+      </c>
+      <c r="V215" t="n">
+        <v>12</v>
+      </c>
+      <c r="W215" t="n">
+        <v>12</v>
+      </c>
+      <c r="X215" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y215" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z215" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA215" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB215" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC215" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD215" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE215" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF215" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG215" t="n">
+        <v>9</v>
+      </c>
+      <c r="AH215" t="n">
+        <v>10</v>
+      </c>
+      <c r="AI215" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ215" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK215" t="n">
+        <v>403</v>
+      </c>
+      <c r="AL215" t="n">
+        <v>609</v>
+      </c>
+      <c r="AM215" t="n">
+        <v>343</v>
+      </c>
+      <c r="AN215" t="n">
+        <v>566</v>
+      </c>
+      <c r="AO215" t="n">
+        <v>74</v>
+      </c>
+      <c r="AP215" t="n">
+        <v>125</v>
+      </c>
+      <c r="AQ215" t="n">
+        <v>47</v>
+      </c>
+      <c r="AR215" t="n">
+        <v>77</v>
+      </c>
+      <c r="AS215" t="n">
+        <v>114</v>
+      </c>
+      <c r="AT215" t="n">
+        <v>116</v>
       </c>
       <c r="AU215" t="inlineStr">
         <is>
@@ -44366,6 +44530,8 @@
       <c r="BD215" t="inlineStr"/>
       <c r="BE215" t="inlineStr"/>
       <c r="BF215" t="inlineStr"/>
+      <c r="BG215" t="inlineStr"/>
+      <c r="BH215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" s="1" t="inlineStr">
@@ -44400,15 +44566,11 @@
           <t>45 000</t>
         </is>
       </c>
-      <c r="G216" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H216" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G216" t="n">
+        <v>0</v>
+      </c>
+      <c r="H216" t="n">
+        <v>0</v>
       </c>
       <c r="I216" t="inlineStr">
         <is>
@@ -44430,15 +44592,11 @@
           <t>Union Berlin</t>
         </is>
       </c>
-      <c r="M216" t="inlineStr">
-        <is>
-          <t>1.43</t>
-        </is>
-      </c>
-      <c r="N216" t="inlineStr">
-        <is>
-          <t>1.13</t>
-        </is>
+      <c r="M216" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N216" t="n">
+        <v>1.13</v>
       </c>
       <c r="O216" t="inlineStr">
         <is>
@@ -44450,155 +44608,95 @@
           <t>30%</t>
         </is>
       </c>
-      <c r="Q216" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="R216" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="S216" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="T216" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="U216" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="V216" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="W216" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="X216" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="Y216" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Z216" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA216" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB216" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC216" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AD216" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AE216" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AF216" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AG216" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AH216" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AI216" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AJ216" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AK216" t="inlineStr">
-        <is>
-          <t>754</t>
-        </is>
-      </c>
-      <c r="AL216" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="AM216" t="inlineStr">
-        <is>
-          <t>678</t>
-        </is>
-      </c>
-      <c r="AN216" t="inlineStr">
-        <is>
-          <t>262</t>
-        </is>
-      </c>
-      <c r="AO216" t="inlineStr">
-        <is>
-          <t>172</t>
-        </is>
-      </c>
-      <c r="AP216" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="AQ216" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="AR216" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="AS216" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="AT216" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
+      <c r="Q216" t="n">
+        <v>16</v>
+      </c>
+      <c r="R216" t="n">
+        <v>11</v>
+      </c>
+      <c r="S216" t="n">
+        <v>3</v>
+      </c>
+      <c r="T216" t="n">
+        <v>3</v>
+      </c>
+      <c r="U216" t="n">
+        <v>13</v>
+      </c>
+      <c r="V216" t="n">
+        <v>8</v>
+      </c>
+      <c r="W216" t="n">
+        <v>22</v>
+      </c>
+      <c r="X216" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y216" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z216" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA216" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB216" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC216" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD216" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE216" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF216" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG216" t="n">
+        <v>9</v>
+      </c>
+      <c r="AH216" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI216" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ216" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK216" t="n">
+        <v>754</v>
+      </c>
+      <c r="AL216" t="n">
+        <v>336</v>
+      </c>
+      <c r="AM216" t="n">
+        <v>678</v>
+      </c>
+      <c r="AN216" t="n">
+        <v>262</v>
+      </c>
+      <c r="AO216" t="n">
+        <v>172</v>
+      </c>
+      <c r="AP216" t="n">
+        <v>77</v>
+      </c>
+      <c r="AQ216" t="n">
+        <v>33</v>
+      </c>
+      <c r="AR216" t="n">
+        <v>26</v>
+      </c>
+      <c r="AS216" t="n">
+        <v>109</v>
+      </c>
+      <c r="AT216" t="n">
+        <v>117</v>
       </c>
       <c r="AU216" t="inlineStr">
         <is>
@@ -44638,6 +44736,8 @@
       <c r="BD216" t="inlineStr"/>
       <c r="BE216" t="inlineStr"/>
       <c r="BF216" t="inlineStr"/>
+      <c r="BG216" t="inlineStr"/>
+      <c r="BH216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" s="1" t="inlineStr">
@@ -44672,15 +44772,11 @@
           <t>20 000</t>
         </is>
       </c>
-      <c r="G217" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H217" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G217" t="n">
+        <v>1</v>
+      </c>
+      <c r="H217" t="n">
+        <v>2</v>
       </c>
       <c r="I217" t="inlineStr">
         <is>
@@ -44702,15 +44798,11 @@
           <t>Eintracht Frankfurt</t>
         </is>
       </c>
-      <c r="M217" t="inlineStr">
-        <is>
-          <t>1.31</t>
-        </is>
-      </c>
-      <c r="N217" t="inlineStr">
-        <is>
-          <t>3.08</t>
-        </is>
+      <c r="M217" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="N217" t="n">
+        <v>3.08</v>
       </c>
       <c r="O217" t="inlineStr">
         <is>
@@ -44722,155 +44814,95 @@
           <t>34%</t>
         </is>
       </c>
-      <c r="Q217" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="R217" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="S217" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="T217" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="U217" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="V217" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="W217" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="X217" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y217" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Z217" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA217" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB217" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AC217" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="AD217" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AE217" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AF217" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AG217" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AH217" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AI217" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AJ217" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AK217" t="inlineStr">
-        <is>
-          <t>478</t>
-        </is>
-      </c>
-      <c r="AL217" t="inlineStr">
-        <is>
-          <t>315</t>
-        </is>
-      </c>
-      <c r="AM217" t="inlineStr">
-        <is>
-          <t>402</t>
-        </is>
-      </c>
-      <c r="AN217" t="inlineStr">
-        <is>
-          <t>255</t>
-        </is>
-      </c>
-      <c r="AO217" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="AP217" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="AQ217" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="AR217" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="AS217" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="AT217" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
+      <c r="Q217" t="n">
+        <v>17</v>
+      </c>
+      <c r="R217" t="n">
+        <v>15</v>
+      </c>
+      <c r="S217" t="n">
+        <v>4</v>
+      </c>
+      <c r="T217" t="n">
+        <v>7</v>
+      </c>
+      <c r="U217" t="n">
+        <v>13</v>
+      </c>
+      <c r="V217" t="n">
+        <v>8</v>
+      </c>
+      <c r="W217" t="n">
+        <v>22</v>
+      </c>
+      <c r="X217" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y217" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z217" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA217" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB217" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC217" t="n">
+        <v>29</v>
+      </c>
+      <c r="AD217" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE217" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF217" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG217" t="n">
+        <v>7</v>
+      </c>
+      <c r="AH217" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI217" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ217" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK217" t="n">
+        <v>478</v>
+      </c>
+      <c r="AL217" t="n">
+        <v>315</v>
+      </c>
+      <c r="AM217" t="n">
+        <v>402</v>
+      </c>
+      <c r="AN217" t="n">
+        <v>255</v>
+      </c>
+      <c r="AO217" t="n">
+        <v>122</v>
+      </c>
+      <c r="AP217" t="n">
+        <v>70</v>
+      </c>
+      <c r="AQ217" t="n">
+        <v>67</v>
+      </c>
+      <c r="AR217" t="n">
+        <v>34</v>
+      </c>
+      <c r="AS217" t="n">
+        <v>114</v>
+      </c>
+      <c r="AT217" t="n">
+        <v>115</v>
       </c>
       <c r="AU217" t="inlineStr">
         <is>
@@ -44910,6 +44942,8 @@
       <c r="BD217" t="inlineStr"/>
       <c r="BE217" t="inlineStr"/>
       <c r="BF217" t="inlineStr"/>
+      <c r="BG217" t="inlineStr"/>
+      <c r="BH217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" s="1" t="inlineStr">
@@ -44944,15 +44978,11 @@
           <t>81 365</t>
         </is>
       </c>
-      <c r="G218" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H218" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G218" t="n">
+        <v>4</v>
+      </c>
+      <c r="H218" t="n">
+        <v>2</v>
       </c>
       <c r="I218" t="inlineStr">
         <is>
@@ -44974,15 +45004,11 @@
           <t>Heidenheim</t>
         </is>
       </c>
-      <c r="M218" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
-      </c>
-      <c r="N218" t="inlineStr">
-        <is>
-          <t>1.99</t>
-        </is>
+      <c r="M218" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="N218" t="n">
+        <v>1.99</v>
       </c>
       <c r="O218" t="inlineStr">
         <is>
@@ -44994,155 +45020,95 @@
           <t>42%</t>
         </is>
       </c>
-      <c r="Q218" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="R218" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="S218" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="T218" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U218" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="V218" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="W218" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="X218" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="Y218" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Z218" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA218" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB218" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC218" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AD218" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="AE218" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AF218" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AG218" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AH218" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AI218" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AJ218" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AK218" t="inlineStr">
-        <is>
-          <t>559</t>
-        </is>
-      </c>
-      <c r="AL218" t="inlineStr">
-        <is>
-          <t>340</t>
-        </is>
-      </c>
-      <c r="AM218" t="inlineStr">
-        <is>
-          <t>498</t>
-        </is>
-      </c>
-      <c r="AN218" t="inlineStr">
-        <is>
-          <t>275</t>
-        </is>
-      </c>
-      <c r="AO218" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="AP218" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="AQ218" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="AR218" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="AS218" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="AT218" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
+      <c r="Q218" t="n">
+        <v>13</v>
+      </c>
+      <c r="R218" t="n">
+        <v>11</v>
+      </c>
+      <c r="S218" t="n">
+        <v>7</v>
+      </c>
+      <c r="T218" t="n">
+        <v>4</v>
+      </c>
+      <c r="U218" t="n">
+        <v>6</v>
+      </c>
+      <c r="V218" t="n">
+        <v>7</v>
+      </c>
+      <c r="W218" t="n">
+        <v>20</v>
+      </c>
+      <c r="X218" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y218" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z218" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA218" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB218" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC218" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD218" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE218" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF218" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG218" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH218" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI218" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ218" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK218" t="n">
+        <v>559</v>
+      </c>
+      <c r="AL218" t="n">
+        <v>340</v>
+      </c>
+      <c r="AM218" t="n">
+        <v>498</v>
+      </c>
+      <c r="AN218" t="n">
+        <v>275</v>
+      </c>
+      <c r="AO218" t="n">
+        <v>124</v>
+      </c>
+      <c r="AP218" t="n">
+        <v>89</v>
+      </c>
+      <c r="AQ218" t="n">
+        <v>52</v>
+      </c>
+      <c r="AR218" t="n">
+        <v>35</v>
+      </c>
+      <c r="AS218" t="n">
+        <v>122</v>
+      </c>
+      <c r="AT218" t="n">
+        <v>121</v>
       </c>
       <c r="AU218" t="inlineStr">
         <is>
@@ -45182,6 +45148,8 @@
       <c r="BD218" t="inlineStr"/>
       <c r="BE218" t="inlineStr"/>
       <c r="BF218" t="inlineStr"/>
+      <c r="BG218" t="inlineStr"/>
+      <c r="BH218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" s="1" t="inlineStr">
@@ -45216,15 +45184,11 @@
           <t>17 076</t>
         </is>
       </c>
-      <c r="G219" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H219" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G219" t="n">
+        <v>1</v>
+      </c>
+      <c r="H219" t="n">
+        <v>1</v>
       </c>
       <c r="I219" t="inlineStr">
         <is>
@@ -45246,15 +45210,11 @@
           <t>Braunschweig</t>
         </is>
       </c>
-      <c r="M219" t="inlineStr">
-        <is>
-          <t>1.04</t>
-        </is>
-      </c>
-      <c r="N219" t="inlineStr">
-        <is>
-          <t>0.85</t>
-        </is>
+      <c r="M219" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N219" t="n">
+        <v>0.85</v>
       </c>
       <c r="O219" t="inlineStr">
         <is>
@@ -45266,155 +45226,95 @@
           <t>52%</t>
         </is>
       </c>
-      <c r="Q219" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="R219" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="S219" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="T219" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="U219" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="V219" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="W219" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="X219" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="Y219" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Z219" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AA219" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB219" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC219" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="AD219" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="AE219" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AF219" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AG219" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AH219" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AI219" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AJ219" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AK219" t="inlineStr">
-        <is>
-          <t>383</t>
-        </is>
-      </c>
-      <c r="AL219" t="inlineStr">
-        <is>
-          <t>484</t>
-        </is>
-      </c>
-      <c r="AM219" t="inlineStr">
-        <is>
-          <t>313</t>
-        </is>
-      </c>
-      <c r="AN219" t="inlineStr">
-        <is>
-          <t>432</t>
-        </is>
-      </c>
-      <c r="AO219" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="AP219" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="AQ219" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="AR219" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="AS219" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="AT219" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
+      <c r="Q219" t="n">
+        <v>15</v>
+      </c>
+      <c r="R219" t="n">
+        <v>14</v>
+      </c>
+      <c r="S219" t="n">
+        <v>3</v>
+      </c>
+      <c r="T219" t="n">
+        <v>3</v>
+      </c>
+      <c r="U219" t="n">
+        <v>12</v>
+      </c>
+      <c r="V219" t="n">
+        <v>11</v>
+      </c>
+      <c r="W219" t="n">
+        <v>14</v>
+      </c>
+      <c r="X219" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y219" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z219" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA219" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB219" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC219" t="n">
+        <v>22</v>
+      </c>
+      <c r="AD219" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE219" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF219" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG219" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH219" t="n">
+        <v>13</v>
+      </c>
+      <c r="AI219" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ219" t="n">
+        <v>7</v>
+      </c>
+      <c r="AK219" t="n">
+        <v>383</v>
+      </c>
+      <c r="AL219" t="n">
+        <v>484</v>
+      </c>
+      <c r="AM219" t="n">
+        <v>313</v>
+      </c>
+      <c r="AN219" t="n">
+        <v>432</v>
+      </c>
+      <c r="AO219" t="n">
+        <v>77</v>
+      </c>
+      <c r="AP219" t="n">
+        <v>115</v>
+      </c>
+      <c r="AQ219" t="n">
+        <v>41</v>
+      </c>
+      <c r="AR219" t="n">
+        <v>73</v>
+      </c>
+      <c r="AS219" t="n">
+        <v>113</v>
+      </c>
+      <c r="AT219" t="n">
+        <v>117</v>
       </c>
       <c r="AU219" t="inlineStr">
         <is>
@@ -45454,6 +45354,8 @@
       <c r="BD219" t="inlineStr"/>
       <c r="BE219" t="inlineStr"/>
       <c r="BF219" t="inlineStr"/>
+      <c r="BG219" t="inlineStr"/>
+      <c r="BH219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" s="1" t="inlineStr">
@@ -45488,15 +45390,11 @@
           <t>38 100</t>
         </is>
       </c>
-      <c r="G220" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H220" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G220" t="n">
+        <v>3</v>
+      </c>
+      <c r="H220" t="n">
+        <v>1</v>
       </c>
       <c r="I220" t="inlineStr">
         <is>
@@ -45518,15 +45416,11 @@
           <t>Kaiserslautern</t>
         </is>
       </c>
-      <c r="M220" t="inlineStr">
-        <is>
-          <t>3.06</t>
-        </is>
-      </c>
-      <c r="N220" t="inlineStr">
-        <is>
-          <t>2.16</t>
-        </is>
+      <c r="M220" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="N220" t="n">
+        <v>2.16</v>
       </c>
       <c r="O220" t="inlineStr">
         <is>
@@ -45538,155 +45432,95 @@
           <t>47%</t>
         </is>
       </c>
-      <c r="Q220" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="R220" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="S220" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="T220" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U220" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="V220" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="W220" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="X220" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="Y220" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="Z220" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA220" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AB220" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AC220" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="AD220" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="AE220" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AF220" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AG220" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AH220" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AI220" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AJ220" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AK220" t="inlineStr">
-        <is>
-          <t>339</t>
-        </is>
-      </c>
-      <c r="AL220" t="inlineStr">
-        <is>
-          <t>354</t>
-        </is>
-      </c>
-      <c r="AM220" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="AN220" t="inlineStr">
-        <is>
-          <t>297</t>
-        </is>
-      </c>
-      <c r="AO220" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="AP220" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="AQ220" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="AR220" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="AS220" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="AT220" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
+      <c r="Q220" t="n">
+        <v>18</v>
+      </c>
+      <c r="R220" t="n">
+        <v>14</v>
+      </c>
+      <c r="S220" t="n">
+        <v>9</v>
+      </c>
+      <c r="T220" t="n">
+        <v>4</v>
+      </c>
+      <c r="U220" t="n">
+        <v>9</v>
+      </c>
+      <c r="V220" t="n">
+        <v>10</v>
+      </c>
+      <c r="W220" t="n">
+        <v>12</v>
+      </c>
+      <c r="X220" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y220" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z220" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA220" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB220" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC220" t="n">
+        <v>29</v>
+      </c>
+      <c r="AD220" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE220" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF220" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG220" t="n">
+        <v>20</v>
+      </c>
+      <c r="AH220" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI220" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ220" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK220" t="n">
+        <v>339</v>
+      </c>
+      <c r="AL220" t="n">
+        <v>354</v>
+      </c>
+      <c r="AM220" t="n">
+        <v>300</v>
+      </c>
+      <c r="AN220" t="n">
+        <v>297</v>
+      </c>
+      <c r="AO220" t="n">
+        <v>104</v>
+      </c>
+      <c r="AP220" t="n">
+        <v>66</v>
+      </c>
+      <c r="AQ220" t="n">
+        <v>67</v>
+      </c>
+      <c r="AR220" t="n">
+        <v>38</v>
+      </c>
+      <c r="AS220" t="n">
+        <v>115</v>
+      </c>
+      <c r="AT220" t="n">
+        <v>114</v>
       </c>
       <c r="AU220" t="inlineStr">
         <is>
@@ -45726,6 +45560,8 @@
       <c r="BD220" t="inlineStr"/>
       <c r="BE220" t="inlineStr"/>
       <c r="BF220" t="inlineStr"/>
+      <c r="BG220" t="inlineStr"/>
+      <c r="BH220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" s="1" t="inlineStr">
@@ -45760,15 +45596,11 @@
           <t>17 400</t>
         </is>
       </c>
-      <c r="G221" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H221" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G221" t="n">
+        <v>1</v>
+      </c>
+      <c r="H221" t="n">
+        <v>2</v>
       </c>
       <c r="I221" t="inlineStr">
         <is>
@@ -45790,15 +45622,11 @@
           <t>Nurnberg</t>
         </is>
       </c>
-      <c r="M221" t="inlineStr">
-        <is>
-          <t>0.99</t>
-        </is>
-      </c>
-      <c r="N221" t="inlineStr">
-        <is>
-          <t>2.17</t>
-        </is>
+      <c r="M221" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="N221" t="n">
+        <v>2.17</v>
       </c>
       <c r="O221" t="inlineStr">
         <is>
@@ -45810,155 +45638,95 @@
           <t>54%</t>
         </is>
       </c>
-      <c r="Q221" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="R221" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="S221" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="T221" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="U221" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="V221" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="W221" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="X221" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="Y221" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Z221" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA221" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB221" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC221" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="AD221" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AE221" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AF221" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AG221" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AH221" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AI221" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AJ221" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AK221" t="inlineStr">
-        <is>
-          <t>345</t>
-        </is>
-      </c>
-      <c r="AL221" t="inlineStr">
-        <is>
-          <t>459</t>
-        </is>
-      </c>
-      <c r="AM221" t="inlineStr">
-        <is>
-          <t>306</t>
-        </is>
-      </c>
-      <c r="AN221" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="AO221" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="AP221" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="AQ221" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="AR221" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="AS221" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="AT221" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
+      <c r="Q221" t="n">
+        <v>12</v>
+      </c>
+      <c r="R221" t="n">
+        <v>15</v>
+      </c>
+      <c r="S221" t="n">
+        <v>3</v>
+      </c>
+      <c r="T221" t="n">
+        <v>8</v>
+      </c>
+      <c r="U221" t="n">
+        <v>9</v>
+      </c>
+      <c r="V221" t="n">
+        <v>7</v>
+      </c>
+      <c r="W221" t="n">
+        <v>16</v>
+      </c>
+      <c r="X221" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y221" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z221" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA221" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB221" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC221" t="n">
+        <v>25</v>
+      </c>
+      <c r="AD221" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE221" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF221" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG221" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH221" t="n">
+        <v>13</v>
+      </c>
+      <c r="AI221" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ221" t="n">
+        <v>6</v>
+      </c>
+      <c r="AK221" t="n">
+        <v>345</v>
+      </c>
+      <c r="AL221" t="n">
+        <v>459</v>
+      </c>
+      <c r="AM221" t="n">
+        <v>306</v>
+      </c>
+      <c r="AN221" t="n">
+        <v>414</v>
+      </c>
+      <c r="AO221" t="n">
+        <v>88</v>
+      </c>
+      <c r="AP221" t="n">
+        <v>93</v>
+      </c>
+      <c r="AQ221" t="n">
+        <v>39</v>
+      </c>
+      <c r="AR221" t="n">
+        <v>39</v>
+      </c>
+      <c r="AS221" t="n">
+        <v>124</v>
+      </c>
+      <c r="AT221" t="n">
+        <v>116</v>
       </c>
       <c r="AU221" t="inlineStr">
         <is>
@@ -45994,18 +45762,16 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="BC221" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BD221" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="BC221" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD221" t="n">
+        <v>1</v>
       </c>
       <c r="BE221" t="inlineStr"/>
       <c r="BF221" t="inlineStr"/>
+      <c r="BG221" t="inlineStr"/>
+      <c r="BH221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" s="1" t="inlineStr">
@@ -46040,15 +45806,11 @@
           <t>31 845</t>
         </is>
       </c>
-      <c r="G222" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H222" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G222" t="n">
+        <v>2</v>
+      </c>
+      <c r="H222" t="n">
+        <v>0</v>
       </c>
       <c r="I222" t="inlineStr">
         <is>
@@ -46070,15 +45832,11 @@
           <t>Schalke</t>
         </is>
       </c>
-      <c r="M222" t="inlineStr">
-        <is>
-          <t>2.12</t>
-        </is>
-      </c>
-      <c r="N222" t="inlineStr">
-        <is>
-          <t>0.58</t>
-        </is>
+      <c r="M222" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="N222" t="n">
+        <v>0.58</v>
       </c>
       <c r="O222" t="inlineStr">
         <is>
@@ -46090,155 +45848,95 @@
           <t>52%</t>
         </is>
       </c>
-      <c r="Q222" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="R222" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="S222" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="T222" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U222" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="V222" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="W222" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="X222" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="Y222" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Z222" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA222" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB222" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC222" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="AD222" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="AE222" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AF222" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AG222" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AH222" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AI222" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AJ222" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AK222" t="inlineStr">
-        <is>
-          <t>432</t>
-        </is>
-      </c>
-      <c r="AL222" t="inlineStr">
-        <is>
-          <t>466</t>
-        </is>
-      </c>
-      <c r="AM222" t="inlineStr">
-        <is>
-          <t>332</t>
-        </is>
-      </c>
-      <c r="AN222" t="inlineStr">
-        <is>
-          <t>391</t>
-        </is>
-      </c>
-      <c r="AO222" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="AP222" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="AQ222" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="AR222" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="AS222" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="AT222" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
+      <c r="Q222" t="n">
+        <v>14</v>
+      </c>
+      <c r="R222" t="n">
+        <v>8</v>
+      </c>
+      <c r="S222" t="n">
+        <v>4</v>
+      </c>
+      <c r="T222" t="n">
+        <v>2</v>
+      </c>
+      <c r="U222" t="n">
+        <v>10</v>
+      </c>
+      <c r="V222" t="n">
+        <v>6</v>
+      </c>
+      <c r="W222" t="n">
+        <v>13</v>
+      </c>
+      <c r="X222" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y222" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z222" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA222" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB222" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC222" t="n">
+        <v>33</v>
+      </c>
+      <c r="AD222" t="n">
+        <v>32</v>
+      </c>
+      <c r="AE222" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF222" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG222" t="n">
+        <v>8</v>
+      </c>
+      <c r="AH222" t="n">
+        <v>14</v>
+      </c>
+      <c r="AI222" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ222" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK222" t="n">
+        <v>432</v>
+      </c>
+      <c r="AL222" t="n">
+        <v>466</v>
+      </c>
+      <c r="AM222" t="n">
+        <v>332</v>
+      </c>
+      <c r="AN222" t="n">
+        <v>391</v>
+      </c>
+      <c r="AO222" t="n">
+        <v>102</v>
+      </c>
+      <c r="AP222" t="n">
+        <v>104</v>
+      </c>
+      <c r="AQ222" t="n">
+        <v>39</v>
+      </c>
+      <c r="AR222" t="n">
+        <v>37</v>
+      </c>
+      <c r="AS222" t="n">
+        <v>120</v>
+      </c>
+      <c r="AT222" t="n">
+        <v>119</v>
       </c>
       <c r="AU222" t="inlineStr">
         <is>
@@ -46278,6 +45976,8 @@
       <c r="BD222" t="inlineStr"/>
       <c r="BE222" t="inlineStr"/>
       <c r="BF222" t="inlineStr"/>
+      <c r="BG222" t="inlineStr"/>
+      <c r="BH222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" s="1" t="inlineStr">
@@ -46312,15 +46012,11 @@
           <t>12 422</t>
         </is>
       </c>
-      <c r="G223" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H223" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="G223" t="n">
+        <v>3</v>
+      </c>
+      <c r="H223" t="n">
+        <v>3</v>
       </c>
       <c r="I223" t="inlineStr">
         <is>
@@ -46342,15 +46038,11 @@
           <t>Paderborn</t>
         </is>
       </c>
-      <c r="M223" t="inlineStr">
-        <is>
-          <t>1.36</t>
-        </is>
-      </c>
-      <c r="N223" t="inlineStr">
-        <is>
-          <t>2.35</t>
-        </is>
+      <c r="M223" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="N223" t="n">
+        <v>2.35</v>
       </c>
       <c r="O223" t="inlineStr">
         <is>
@@ -46362,155 +46054,95 @@
           <t>58%</t>
         </is>
       </c>
-      <c r="Q223" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="R223" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="S223" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="T223" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="U223" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V223" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="W223" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="X223" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y223" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Z223" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA223" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB223" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AC223" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AD223" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="AE223" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AF223" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AG223" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AH223" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AI223" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AJ223" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AK223" t="inlineStr">
-        <is>
-          <t>309</t>
-        </is>
-      </c>
-      <c r="AL223" t="inlineStr">
-        <is>
-          <t>515</t>
-        </is>
-      </c>
-      <c r="AM223" t="inlineStr">
-        <is>
-          <t>231</t>
-        </is>
-      </c>
-      <c r="AN223" t="inlineStr">
-        <is>
-          <t>442</t>
-        </is>
-      </c>
-      <c r="AO223" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="AP223" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="AQ223" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="AR223" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="AS223" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="AT223" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
+      <c r="Q223" t="n">
+        <v>11</v>
+      </c>
+      <c r="R223" t="n">
+        <v>20</v>
+      </c>
+      <c r="S223" t="n">
+        <v>4</v>
+      </c>
+      <c r="T223" t="n">
+        <v>9</v>
+      </c>
+      <c r="U223" t="n">
+        <v>7</v>
+      </c>
+      <c r="V223" t="n">
+        <v>11</v>
+      </c>
+      <c r="W223" t="n">
+        <v>14</v>
+      </c>
+      <c r="X223" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y223" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z223" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA223" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB223" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC223" t="n">
+        <v>21</v>
+      </c>
+      <c r="AD223" t="n">
+        <v>29</v>
+      </c>
+      <c r="AE223" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF223" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG223" t="n">
+        <v>6</v>
+      </c>
+      <c r="AH223" t="n">
+        <v>10</v>
+      </c>
+      <c r="AI223" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ223" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK223" t="n">
+        <v>309</v>
+      </c>
+      <c r="AL223" t="n">
+        <v>515</v>
+      </c>
+      <c r="AM223" t="n">
+        <v>231</v>
+      </c>
+      <c r="AN223" t="n">
+        <v>442</v>
+      </c>
+      <c r="AO223" t="n">
+        <v>82</v>
+      </c>
+      <c r="AP223" t="n">
+        <v>94</v>
+      </c>
+      <c r="AQ223" t="n">
+        <v>51</v>
+      </c>
+      <c r="AR223" t="n">
+        <v>42</v>
+      </c>
+      <c r="AS223" t="n">
+        <v>121</v>
+      </c>
+      <c r="AT223" t="n">
+        <v>123</v>
       </c>
       <c r="AU223" t="inlineStr">
         <is>
@@ -46550,6 +46182,1676 @@
       <c r="BD223" t="inlineStr"/>
       <c r="BE223" t="inlineStr"/>
       <c r="BF223" t="inlineStr"/>
+      <c r="BG223" t="inlineStr"/>
+      <c r="BH223" t="inlineStr"/>
+    </row>
+    <row r="224">
+      <c r="A224" s="1" t="inlineStr">
+        <is>
+          <t>8OhVCWxh</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>15.09.2024 12:30</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Brand B.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>Mewa Arena
+ (Mainz)</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>34 000</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>32 000</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>EuakNmc1</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>Mainz</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Ig1f1fy3</t>
+        </is>
+      </c>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t>Werder Bremen</t>
+        </is>
+      </c>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="N224" t="inlineStr">
+        <is>
+          <t>2.32</t>
+        </is>
+      </c>
+      <c r="O224" t="inlineStr">
+        <is>
+          <t>55%</t>
+        </is>
+      </c>
+      <c r="P224" t="inlineStr">
+        <is>
+          <t>45%</t>
+        </is>
+      </c>
+      <c r="Q224" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R224" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="S224" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T224" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U224" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V224" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W224" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="X224" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="Y224" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Z224" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA224" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB224" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC224" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AD224" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AE224" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AF224" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AG224" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AH224" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AI224" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AJ224" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AK224" t="inlineStr">
+        <is>
+          <t>481</t>
+        </is>
+      </c>
+      <c r="AL224" t="inlineStr">
+        <is>
+          <t>347</t>
+        </is>
+      </c>
+      <c r="AM224" t="inlineStr">
+        <is>
+          <t>390</t>
+        </is>
+      </c>
+      <c r="AN224" t="inlineStr">
+        <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="AO224" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="AP224" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="AQ224" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="AR224" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AS224" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="AT224" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="AU224" t="inlineStr">
+        <is>
+          <t>vZA6VYpf</t>
+        </is>
+      </c>
+      <c r="AV224" t="inlineStr">
+        <is>
+          <t>henriksen bo</t>
+        </is>
+      </c>
+      <c r="AW224" t="inlineStr">
+        <is>
+          <t>4fuCGs9P</t>
+        </is>
+      </c>
+      <c r="AX224" t="inlineStr">
+        <is>
+          <t>werner ole</t>
+        </is>
+      </c>
+      <c r="AY224" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ224" t="n">
+        <v>591</v>
+      </c>
+      <c r="BA224" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB224" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC224" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BD224" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BE224" t="inlineStr"/>
+      <c r="BF224" t="inlineStr"/>
+      <c r="BG224" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="BH224" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="1" t="inlineStr">
+        <is>
+          <t>CnrLfkNN</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>15.09.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Zwayer F.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>WWK Arena
+ (Augsburg)</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>30 660</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>30 660</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>fTVNku3I</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>Augsburg</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t>St. Pauli</t>
+        </is>
+      </c>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>2.48</t>
+        </is>
+      </c>
+      <c r="N225" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="O225" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
+      <c r="P225" t="inlineStr">
+        <is>
+          <t>56%</t>
+        </is>
+      </c>
+      <c r="Q225" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="R225" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="S225" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T225" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U225" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V225" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="W225" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="X225" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="Y225" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Z225" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA225" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB225" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC225" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AD225" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AE225" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AF225" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AG225" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AH225" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AI225" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AJ225" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AK225" t="inlineStr">
+        <is>
+          <t>317</t>
+        </is>
+      </c>
+      <c r="AL225" t="inlineStr">
+        <is>
+          <t>424</t>
+        </is>
+      </c>
+      <c r="AM225" t="inlineStr">
+        <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="AN225" t="inlineStr">
+        <is>
+          <t>335</t>
+        </is>
+      </c>
+      <c r="AO225" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="AP225" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="AQ225" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="AR225" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="AS225" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="AT225" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="AU225" t="inlineStr">
+        <is>
+          <t>2VSFgl3c</t>
+        </is>
+      </c>
+      <c r="AV225" t="inlineStr">
+        <is>
+          <t>thorup jess</t>
+        </is>
+      </c>
+      <c r="AW225" t="inlineStr">
+        <is>
+          <t>0jdIgO6t</t>
+        </is>
+      </c>
+      <c r="AX225" t="inlineStr">
+        <is>
+          <t>blessin alexander</t>
+        </is>
+      </c>
+      <c r="AY225" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ225" t="n">
+        <v>591</v>
+      </c>
+      <c r="BA225" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB225" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC225" t="inlineStr"/>
+      <c r="BD225" t="inlineStr"/>
+      <c r="BE225" t="inlineStr"/>
+      <c r="BF225" t="inlineStr"/>
+      <c r="BG225" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="BH225" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="1" t="inlineStr">
+        <is>
+          <t>fTtEphFr</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>15.09.2024 08:30</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Weisbach E.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>Sportpark Ronhof Thomas Sommer
+ (Fürth)</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>16 626</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>10 877</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>CCQGbik8</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>Greuther Furth</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>6in2Eknb</t>
+        </is>
+      </c>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>Elversberg</t>
+        </is>
+      </c>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>0.67</t>
+        </is>
+      </c>
+      <c r="N226" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="O226" t="inlineStr">
+        <is>
+          <t>55%</t>
+        </is>
+      </c>
+      <c r="P226" t="inlineStr">
+        <is>
+          <t>45%</t>
+        </is>
+      </c>
+      <c r="Q226" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R226" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="S226" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T226" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="U226" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V226" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="W226" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="X226" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="Y226" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Z226" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA226" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB226" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC226" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AD226" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AE226" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AF226" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AG226" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AH226" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AI226" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AJ226" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AK226" t="inlineStr">
+        <is>
+          <t>417</t>
+        </is>
+      </c>
+      <c r="AL226" t="inlineStr">
+        <is>
+          <t>368</t>
+        </is>
+      </c>
+      <c r="AM226" t="inlineStr">
+        <is>
+          <t>380</t>
+        </is>
+      </c>
+      <c r="AN226" t="inlineStr">
+        <is>
+          <t>317</t>
+        </is>
+      </c>
+      <c r="AO226" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="AP226" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="AQ226" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="AR226" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="AS226" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="AT226" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="AU226" t="inlineStr">
+        <is>
+          <t>8E86CPuD</t>
+        </is>
+      </c>
+      <c r="AV226" t="inlineStr">
+        <is>
+          <t>zorniger alexander</t>
+        </is>
+      </c>
+      <c r="AW226" t="inlineStr">
+        <is>
+          <t>8E8qmw3d</t>
+        </is>
+      </c>
+      <c r="AX226" t="inlineStr">
+        <is>
+          <t>steffen horst</t>
+        </is>
+      </c>
+      <c r="AY226" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ226" t="n">
+        <v>592</v>
+      </c>
+      <c r="BA226" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB226" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC226" t="inlineStr"/>
+      <c r="BD226" t="inlineStr"/>
+      <c r="BE226" t="inlineStr"/>
+      <c r="BF226" t="inlineStr"/>
+      <c r="BG226" t="inlineStr"/>
+      <c r="BH226" t="inlineStr"/>
+    </row>
+    <row r="227">
+      <c r="A227" s="1" t="inlineStr">
+        <is>
+          <t>xxreUWU1</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>15.09.2024 08:30</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Braun R.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>Volksparkstadion
+ (Hamburg)</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>57 274</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>53 779</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>v9k3aY5F</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>Hamburger SV</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>UiCmEP56</t>
+        </is>
+      </c>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>Regensburg</t>
+        </is>
+      </c>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="N227" t="inlineStr">
+        <is>
+          <t>0.30</t>
+        </is>
+      </c>
+      <c r="O227" t="inlineStr">
+        <is>
+          <t>63%</t>
+        </is>
+      </c>
+      <c r="P227" t="inlineStr">
+        <is>
+          <t>37%</t>
+        </is>
+      </c>
+      <c r="Q227" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R227" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="S227" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="T227" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U227" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V227" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W227" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="X227" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="Y227" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Z227" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA227" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB227" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC227" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AD227" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="AE227" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AF227" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AG227" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AH227" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AI227" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AJ227" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AK227" t="inlineStr">
+        <is>
+          <t>610</t>
+        </is>
+      </c>
+      <c r="AL227" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="AM227" t="inlineStr">
+        <is>
+          <t>559</t>
+        </is>
+      </c>
+      <c r="AN227" t="inlineStr">
+        <is>
+          <t>324</t>
+        </is>
+      </c>
+      <c r="AO227" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="AP227" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="AQ227" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="AR227" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="AS227" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="AT227" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="AU227" t="inlineStr">
+        <is>
+          <t>EDRZkDzS</t>
+        </is>
+      </c>
+      <c r="AV227" t="inlineStr">
+        <is>
+          <t>baumgart steffen</t>
+        </is>
+      </c>
+      <c r="AW227" t="inlineStr">
+        <is>
+          <t>zyLSrbZQ</t>
+        </is>
+      </c>
+      <c r="AX227" t="inlineStr">
+        <is>
+          <t>enochs joe</t>
+        </is>
+      </c>
+      <c r="AY227" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ227" t="n">
+        <v>592</v>
+      </c>
+      <c r="BA227" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB227" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC227" t="inlineStr"/>
+      <c r="BD227" t="inlineStr"/>
+      <c r="BE227" t="inlineStr"/>
+      <c r="BF227" t="inlineStr"/>
+      <c r="BG227" t="inlineStr"/>
+      <c r="BH227" t="inlineStr"/>
+    </row>
+    <row r="228">
+      <c r="A228" s="1" t="inlineStr">
+        <is>
+          <t>2gpMrWqe</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>15.09.2024 08:30</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Bacher M.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>Olympiastadion
+ (Berlin)</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>74 667</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>50 135</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>2y0u8Wrq</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>Hertha Berlin</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>ne1oL3y7</t>
+        </is>
+      </c>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>Dusseldorf</t>
+        </is>
+      </c>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="N228" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="O228" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="P228" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="Q228" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R228" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="S228" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T228" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="U228" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V228" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W228" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="X228" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="Y228" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Z228" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA228" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB228" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC228" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AD228" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AE228" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AF228" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AG228" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AH228" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AI228" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AJ228" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AK228" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
+      <c r="AL228" t="inlineStr">
+        <is>
+          <t>301</t>
+        </is>
+      </c>
+      <c r="AM228" t="inlineStr">
+        <is>
+          <t>516</t>
+        </is>
+      </c>
+      <c r="AN228" t="inlineStr">
+        <is>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="AO228" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="AP228" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="AQ228" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="AR228" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AS228" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="AT228" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="AU228" t="inlineStr">
+        <is>
+          <t>YmfcAeCo</t>
+        </is>
+      </c>
+      <c r="AV228" t="inlineStr">
+        <is>
+          <t>fiel cristian</t>
+        </is>
+      </c>
+      <c r="AW228" t="inlineStr">
+        <is>
+          <t>AoL97rX8</t>
+        </is>
+      </c>
+      <c r="AX228" t="inlineStr">
+        <is>
+          <t>thioune daniel</t>
+        </is>
+      </c>
+      <c r="AY228" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ228" t="n">
+        <v>592</v>
+      </c>
+      <c r="BA228" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB228" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC228" t="inlineStr"/>
+      <c r="BD228" t="inlineStr"/>
+      <c r="BE228" t="inlineStr"/>
+      <c r="BF228" t="inlineStr"/>
+      <c r="BG228" t="inlineStr"/>
+      <c r="BH228" t="inlineStr"/>
+    </row>
+    <row r="229">
+      <c r="A229" s="1" t="inlineStr">
+        <is>
+          <t>pv3GyFxS</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>14.09.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Hempel R.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>RheinEnergieStadion
+ (Cologne)</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>50 000</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>50 000</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>WG9pOTse</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>FC Koln</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>YFuz2RLm</t>
+        </is>
+      </c>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>Magdeburg</t>
+        </is>
+      </c>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>4.64</t>
+        </is>
+      </c>
+      <c r="N229" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="O229" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="P229" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="Q229" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="R229" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="S229" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="T229" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U229" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="V229" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="W229" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="X229" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="Y229" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Z229" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA229" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB229" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC229" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AD229" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AE229" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AF229" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AG229" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AH229" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AI229" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AJ229" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AK229" t="inlineStr">
+        <is>
+          <t>436</t>
+        </is>
+      </c>
+      <c r="AL229" t="inlineStr">
+        <is>
+          <t>483</t>
+        </is>
+      </c>
+      <c r="AM229" t="inlineStr">
+        <is>
+          <t>358</t>
+        </is>
+      </c>
+      <c r="AN229" t="inlineStr">
+        <is>
+          <t>406</t>
+        </is>
+      </c>
+      <c r="AO229" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="AP229" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="AQ229" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="AR229" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="AS229" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="AT229" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="AU229" t="inlineStr">
+        <is>
+          <t>4fX0k7gg</t>
+        </is>
+      </c>
+      <c r="AV229" t="inlineStr">
+        <is>
+          <t>struber gerhard</t>
+        </is>
+      </c>
+      <c r="AW229" t="inlineStr">
+        <is>
+          <t>IgZoGKFn</t>
+        </is>
+      </c>
+      <c r="AX229" t="inlineStr">
+        <is>
+          <t>titz christian</t>
+        </is>
+      </c>
+      <c r="AY229" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ229" t="n">
+        <v>592</v>
+      </c>
+      <c r="BA229" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB229" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC229" t="inlineStr"/>
+      <c r="BD229" t="inlineStr"/>
+      <c r="BE229" t="inlineStr"/>
+      <c r="BF229" t="inlineStr"/>
+      <c r="BG229" t="inlineStr"/>
+      <c r="BH229" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/germany/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
+++ b/data/germany/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH260"/>
+  <dimension ref="A1:BH265"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -51102,15 +51102,11 @@
           <t>75 000</t>
         </is>
       </c>
-      <c r="G248" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H248" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G248" t="n">
+        <v>1</v>
+      </c>
+      <c r="H248" t="n">
+        <v>1</v>
       </c>
       <c r="I248" t="inlineStr">
         <is>
@@ -51132,15 +51128,11 @@
           <t>Bayer Leverkusen</t>
         </is>
       </c>
-      <c r="M248" t="inlineStr">
-        <is>
-          <t>1.16</t>
-        </is>
-      </c>
-      <c r="N248" t="inlineStr">
-        <is>
-          <t>0.14</t>
-        </is>
+      <c r="M248" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="N248" t="n">
+        <v>0.14</v>
       </c>
       <c r="O248" t="inlineStr">
         <is>
@@ -51152,139 +51144,87 @@
           <t>31%</t>
         </is>
       </c>
-      <c r="Q248" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="R248" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="S248" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="T248" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="U248" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="V248" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W248" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="X248" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="Y248" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Z248" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA248" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB248" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC248" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AD248" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AE248" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AF248" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AG248" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AH248" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI248" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AJ248" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AK248" t="inlineStr">
-        <is>
-          <t>710</t>
-        </is>
-      </c>
-      <c r="AL248" t="inlineStr">
-        <is>
-          <t>312</t>
-        </is>
-      </c>
-      <c r="AM248" t="inlineStr">
-        <is>
-          <t>646</t>
-        </is>
-      </c>
-      <c r="AN248" t="inlineStr">
-        <is>
-          <t>237</t>
-        </is>
+      <c r="Q248" t="n">
+        <v>18</v>
+      </c>
+      <c r="R248" t="n">
+        <v>3</v>
+      </c>
+      <c r="S248" t="n">
+        <v>3</v>
+      </c>
+      <c r="T248" t="n">
+        <v>3</v>
+      </c>
+      <c r="U248" t="n">
+        <v>15</v>
+      </c>
+      <c r="V248" t="n">
+        <v>0</v>
+      </c>
+      <c r="W248" t="n">
+        <v>16</v>
+      </c>
+      <c r="X248" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y248" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z248" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA248" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB248" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC248" t="n">
+        <v>18</v>
+      </c>
+      <c r="AD248" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE248" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF248" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG248" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH248" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI248" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ248" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK248" t="n">
+        <v>710</v>
+      </c>
+      <c r="AL248" t="n">
+        <v>312</v>
+      </c>
+      <c r="AM248" t="n">
+        <v>646</v>
+      </c>
+      <c r="AN248" t="n">
+        <v>237</v>
       </c>
       <c r="AO248" t="inlineStr"/>
       <c r="AP248" t="inlineStr"/>
       <c r="AQ248" t="inlineStr"/>
       <c r="AR248" t="inlineStr"/>
-      <c r="AS248" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
-      <c r="AT248" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
+      <c r="AS248" t="n">
+        <v>119</v>
+      </c>
+      <c r="AT248" t="n">
+        <v>118</v>
       </c>
       <c r="AU248" t="inlineStr">
         <is>
@@ -51360,15 +51300,11 @@
           <t>53 056</t>
         </is>
       </c>
-      <c r="G249" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H249" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G249" t="n">
+        <v>1</v>
+      </c>
+      <c r="H249" t="n">
+        <v>0</v>
       </c>
       <c r="I249" t="inlineStr">
         <is>
@@ -51390,15 +51326,11 @@
           <t>Union Berlin</t>
         </is>
       </c>
-      <c r="M249" t="inlineStr">
-        <is>
-          <t>0.98</t>
-        </is>
-      </c>
-      <c r="N249" t="inlineStr">
-        <is>
-          <t>0.73</t>
-        </is>
+      <c r="M249" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="N249" t="n">
+        <v>0.73</v>
       </c>
       <c r="O249" t="inlineStr">
         <is>
@@ -51410,139 +51342,87 @@
           <t>39%</t>
         </is>
       </c>
-      <c r="Q249" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="R249" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="S249" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="T249" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="U249" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="V249" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="W249" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="X249" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="Y249" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Z249" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA249" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AB249" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC249" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="AD249" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="AE249" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AF249" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AG249" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AH249" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AI249" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AJ249" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AK249" t="inlineStr">
-        <is>
-          <t>606</t>
-        </is>
-      </c>
-      <c r="AL249" t="inlineStr">
-        <is>
-          <t>334</t>
-        </is>
-      </c>
-      <c r="AM249" t="inlineStr">
-        <is>
-          <t>521</t>
-        </is>
-      </c>
-      <c r="AN249" t="inlineStr">
-        <is>
-          <t>237</t>
-        </is>
+      <c r="Q249" t="n">
+        <v>8</v>
+      </c>
+      <c r="R249" t="n">
+        <v>9</v>
+      </c>
+      <c r="S249" t="n">
+        <v>3</v>
+      </c>
+      <c r="T249" t="n">
+        <v>3</v>
+      </c>
+      <c r="U249" t="n">
+        <v>5</v>
+      </c>
+      <c r="V249" t="n">
+        <v>6</v>
+      </c>
+      <c r="W249" t="n">
+        <v>15</v>
+      </c>
+      <c r="X249" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y249" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z249" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA249" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB249" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC249" t="n">
+        <v>31</v>
+      </c>
+      <c r="AD249" t="n">
+        <v>47</v>
+      </c>
+      <c r="AE249" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF249" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG249" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH249" t="n">
+        <v>12</v>
+      </c>
+      <c r="AI249" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ249" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK249" t="n">
+        <v>606</v>
+      </c>
+      <c r="AL249" t="n">
+        <v>334</v>
+      </c>
+      <c r="AM249" t="n">
+        <v>521</v>
+      </c>
+      <c r="AN249" t="n">
+        <v>237</v>
       </c>
       <c r="AO249" t="inlineStr"/>
       <c r="AP249" t="inlineStr"/>
       <c r="AQ249" t="inlineStr"/>
       <c r="AR249" t="inlineStr"/>
-      <c r="AS249" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="AT249" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
+      <c r="AS249" t="n">
+        <v>116</v>
+      </c>
+      <c r="AT249" t="n">
+        <v>122</v>
       </c>
       <c r="AU249" t="inlineStr">
         <is>
@@ -51618,15 +51498,11 @@
           <t>34 700</t>
         </is>
       </c>
-      <c r="G250" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H250" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="G250" t="n">
+        <v>0</v>
+      </c>
+      <c r="H250" t="n">
+        <v>3</v>
       </c>
       <c r="I250" t="inlineStr">
         <is>
@@ -51648,15 +51524,11 @@
           <t>St. Pauli</t>
         </is>
       </c>
-      <c r="M250" t="inlineStr">
-        <is>
-          <t>1.12</t>
-        </is>
-      </c>
-      <c r="N250" t="inlineStr">
-        <is>
-          <t>1.50</t>
-        </is>
+      <c r="M250" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N250" t="n">
+        <v>1.5</v>
       </c>
       <c r="O250" t="inlineStr">
         <is>
@@ -51668,139 +51540,87 @@
           <t>33%</t>
         </is>
       </c>
-      <c r="Q250" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="R250" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="S250" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="T250" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U250" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="V250" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="W250" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="X250" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Y250" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Z250" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA250" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AB250" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC250" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="AD250" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AE250" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AF250" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AG250" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AH250" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AI250" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AJ250" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AK250" t="inlineStr">
-        <is>
-          <t>647</t>
-        </is>
-      </c>
-      <c r="AL250" t="inlineStr">
-        <is>
-          <t>263</t>
-        </is>
-      </c>
-      <c r="AM250" t="inlineStr">
-        <is>
-          <t>549</t>
-        </is>
-      </c>
-      <c r="AN250" t="inlineStr">
-        <is>
-          <t>171</t>
-        </is>
+      <c r="Q250" t="n">
+        <v>6</v>
+      </c>
+      <c r="R250" t="n">
+        <v>10</v>
+      </c>
+      <c r="S250" t="n">
+        <v>2</v>
+      </c>
+      <c r="T250" t="n">
+        <v>4</v>
+      </c>
+      <c r="U250" t="n">
+        <v>4</v>
+      </c>
+      <c r="V250" t="n">
+        <v>6</v>
+      </c>
+      <c r="W250" t="n">
+        <v>21</v>
+      </c>
+      <c r="X250" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y250" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z250" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA250" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB250" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC250" t="n">
+        <v>25</v>
+      </c>
+      <c r="AD250" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE250" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF250" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG250" t="n">
+        <v>7</v>
+      </c>
+      <c r="AH250" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI250" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ250" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK250" t="n">
+        <v>647</v>
+      </c>
+      <c r="AL250" t="n">
+        <v>263</v>
+      </c>
+      <c r="AM250" t="n">
+        <v>549</v>
+      </c>
+      <c r="AN250" t="n">
+        <v>171</v>
       </c>
       <c r="AO250" t="inlineStr"/>
       <c r="AP250" t="inlineStr"/>
       <c r="AQ250" t="inlineStr"/>
       <c r="AR250" t="inlineStr"/>
-      <c r="AS250" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="AT250" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
+      <c r="AS250" t="n">
+        <v>122</v>
+      </c>
+      <c r="AT250" t="n">
+        <v>124</v>
       </c>
       <c r="AU250" t="inlineStr">
         <is>
@@ -51876,15 +51696,11 @@
           <t>31 500</t>
         </is>
       </c>
-      <c r="G251" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H251" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G251" t="n">
+        <v>0</v>
+      </c>
+      <c r="H251" t="n">
+        <v>2</v>
       </c>
       <c r="I251" t="inlineStr">
         <is>
@@ -51906,15 +51722,11 @@
           <t>Heidenheim</t>
         </is>
       </c>
-      <c r="M251" t="inlineStr">
-        <is>
-          <t>0.50</t>
-        </is>
-      </c>
-      <c r="N251" t="inlineStr">
-        <is>
-          <t>1.50</t>
-        </is>
+      <c r="M251" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N251" t="n">
+        <v>1.5</v>
       </c>
       <c r="O251" t="inlineStr">
         <is>
@@ -51926,139 +51738,87 @@
           <t>48%</t>
         </is>
       </c>
-      <c r="Q251" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="R251" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="S251" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="T251" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="U251" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="V251" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="W251" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="X251" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="Y251" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Z251" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA251" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB251" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC251" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="AD251" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="AE251" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AF251" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AG251" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AH251" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AI251" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AJ251" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AK251" t="inlineStr">
-        <is>
-          <t>433</t>
-        </is>
-      </c>
-      <c r="AL251" t="inlineStr">
-        <is>
-          <t>406</t>
-        </is>
-      </c>
-      <c r="AM251" t="inlineStr">
-        <is>
-          <t>325</t>
-        </is>
-      </c>
-      <c r="AN251" t="inlineStr">
-        <is>
-          <t>305</t>
-        </is>
+      <c r="Q251" t="n">
+        <v>7</v>
+      </c>
+      <c r="R251" t="n">
+        <v>14</v>
+      </c>
+      <c r="S251" t="n">
+        <v>2</v>
+      </c>
+      <c r="T251" t="n">
+        <v>7</v>
+      </c>
+      <c r="U251" t="n">
+        <v>5</v>
+      </c>
+      <c r="V251" t="n">
+        <v>7</v>
+      </c>
+      <c r="W251" t="n">
+        <v>12</v>
+      </c>
+      <c r="X251" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y251" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z251" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA251" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB251" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC251" t="n">
+        <v>31</v>
+      </c>
+      <c r="AD251" t="n">
+        <v>32</v>
+      </c>
+      <c r="AE251" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF251" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG251" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH251" t="n">
+        <v>10</v>
+      </c>
+      <c r="AI251" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ251" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK251" t="n">
+        <v>433</v>
+      </c>
+      <c r="AL251" t="n">
+        <v>406</v>
+      </c>
+      <c r="AM251" t="n">
+        <v>325</v>
+      </c>
+      <c r="AN251" t="n">
+        <v>305</v>
       </c>
       <c r="AO251" t="inlineStr"/>
       <c r="AP251" t="inlineStr"/>
       <c r="AQ251" t="inlineStr"/>
       <c r="AR251" t="inlineStr"/>
-      <c r="AS251" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="AT251" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
+      <c r="AS251" t="n">
+        <v>110</v>
+      </c>
+      <c r="AT251" t="n">
+        <v>112</v>
       </c>
       <c r="AU251" t="inlineStr">
         <is>
@@ -52094,15 +51854,11 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="BC251" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BD251" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="BC251" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD251" t="n">
+        <v>1</v>
       </c>
       <c r="BE251" t="inlineStr"/>
       <c r="BF251" t="inlineStr"/>
@@ -52142,15 +51898,11 @@
           <t>44 407</t>
         </is>
       </c>
-      <c r="G252" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H252" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G252" t="n">
+        <v>4</v>
+      </c>
+      <c r="H252" t="n">
+        <v>0</v>
       </c>
       <c r="I252" t="inlineStr">
         <is>
@@ -52172,15 +51924,11 @@
           <t>Augsburg</t>
         </is>
       </c>
-      <c r="M252" t="inlineStr">
-        <is>
-          <t>2.79</t>
-        </is>
-      </c>
-      <c r="N252" t="inlineStr">
-        <is>
-          <t>1.12</t>
-        </is>
+      <c r="M252" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="N252" t="n">
+        <v>1.12</v>
       </c>
       <c r="O252" t="inlineStr">
         <is>
@@ -52192,139 +51940,87 @@
           <t>43%</t>
         </is>
       </c>
-      <c r="Q252" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="R252" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="S252" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="T252" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="U252" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V252" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="W252" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="X252" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="Y252" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Z252" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA252" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB252" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC252" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="AD252" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AE252" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AF252" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AG252" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AH252" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AI252" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AJ252" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AK252" t="inlineStr">
-        <is>
-          <t>550</t>
-        </is>
-      </c>
-      <c r="AL252" t="inlineStr">
-        <is>
-          <t>367</t>
-        </is>
-      </c>
-      <c r="AM252" t="inlineStr">
-        <is>
-          <t>473</t>
-        </is>
-      </c>
-      <c r="AN252" t="inlineStr">
-        <is>
-          <t>301</t>
-        </is>
+      <c r="Q252" t="n">
+        <v>14</v>
+      </c>
+      <c r="R252" t="n">
+        <v>7</v>
+      </c>
+      <c r="S252" t="n">
+        <v>7</v>
+      </c>
+      <c r="T252" t="n">
+        <v>1</v>
+      </c>
+      <c r="U252" t="n">
+        <v>7</v>
+      </c>
+      <c r="V252" t="n">
+        <v>6</v>
+      </c>
+      <c r="W252" t="n">
+        <v>16</v>
+      </c>
+      <c r="X252" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y252" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z252" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA252" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB252" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC252" t="n">
+        <v>30</v>
+      </c>
+      <c r="AD252" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE252" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF252" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG252" t="n">
+        <v>9</v>
+      </c>
+      <c r="AH252" t="n">
+        <v>13</v>
+      </c>
+      <c r="AI252" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ252" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK252" t="n">
+        <v>550</v>
+      </c>
+      <c r="AL252" t="n">
+        <v>367</v>
+      </c>
+      <c r="AM252" t="n">
+        <v>473</v>
+      </c>
+      <c r="AN252" t="n">
+        <v>301</v>
       </c>
       <c r="AO252" t="inlineStr"/>
       <c r="AP252" t="inlineStr"/>
       <c r="AQ252" t="inlineStr"/>
       <c r="AR252" t="inlineStr"/>
-      <c r="AS252" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="AT252" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
+      <c r="AS252" t="n">
+        <v>114</v>
+      </c>
+      <c r="AT252" t="n">
+        <v>112</v>
       </c>
       <c r="AU252" t="inlineStr">
         <is>
@@ -52400,15 +52096,11 @@
           <t>27 135</t>
         </is>
       </c>
-      <c r="G253" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H253" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G253" t="n">
+        <v>2</v>
+      </c>
+      <c r="H253" t="n">
+        <v>2</v>
       </c>
       <c r="I253" t="inlineStr">
         <is>
@@ -52430,15 +52122,11 @@
           <t>Stuttgart</t>
         </is>
       </c>
-      <c r="M253" t="inlineStr">
-        <is>
-          <t>1.15</t>
-        </is>
-      </c>
-      <c r="N253" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
+      <c r="M253" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="N253" t="n">
+        <v>3</v>
       </c>
       <c r="O253" t="inlineStr">
         <is>
@@ -52450,139 +52138,87 @@
           <t>66%</t>
         </is>
       </c>
-      <c r="Q253" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R253" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="S253" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="T253" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="U253" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="V253" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="W253" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="X253" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="Y253" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Z253" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA253" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB253" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AC253" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="AD253" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="AE253" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AF253" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG253" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AH253" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AI253" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AJ253" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AK253" t="inlineStr">
-        <is>
-          <t>248</t>
-        </is>
-      </c>
-      <c r="AL253" t="inlineStr">
-        <is>
-          <t>583</t>
-        </is>
-      </c>
-      <c r="AM253" t="inlineStr">
-        <is>
-          <t>159</t>
-        </is>
-      </c>
-      <c r="AN253" t="inlineStr">
-        <is>
-          <t>496</t>
-        </is>
+      <c r="Q253" t="n">
+        <v>5</v>
+      </c>
+      <c r="R253" t="n">
+        <v>17</v>
+      </c>
+      <c r="S253" t="n">
+        <v>2</v>
+      </c>
+      <c r="T253" t="n">
+        <v>5</v>
+      </c>
+      <c r="U253" t="n">
+        <v>3</v>
+      </c>
+      <c r="V253" t="n">
+        <v>12</v>
+      </c>
+      <c r="W253" t="n">
+        <v>14</v>
+      </c>
+      <c r="X253" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y253" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z253" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA253" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB253" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC253" t="n">
+        <v>26</v>
+      </c>
+      <c r="AD253" t="n">
+        <v>32</v>
+      </c>
+      <c r="AE253" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF253" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG253" t="n">
+        <v>20</v>
+      </c>
+      <c r="AH253" t="n">
+        <v>10</v>
+      </c>
+      <c r="AI253" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ253" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK253" t="n">
+        <v>248</v>
+      </c>
+      <c r="AL253" t="n">
+        <v>583</v>
+      </c>
+      <c r="AM253" t="n">
+        <v>159</v>
+      </c>
+      <c r="AN253" t="n">
+        <v>496</v>
       </c>
       <c r="AO253" t="inlineStr"/>
       <c r="AP253" t="inlineStr"/>
       <c r="AQ253" t="inlineStr"/>
       <c r="AR253" t="inlineStr"/>
-      <c r="AS253" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
-      </c>
-      <c r="AT253" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
+      <c r="AS253" t="n">
+        <v>108</v>
+      </c>
+      <c r="AT253" t="n">
+        <v>109</v>
       </c>
       <c r="AU253" t="inlineStr">
         <is>
@@ -52618,15 +52254,11 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="BC253" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BD253" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="BC253" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD253" t="n">
+        <v>1</v>
       </c>
       <c r="BE253" t="inlineStr"/>
       <c r="BF253" t="inlineStr"/>
@@ -52666,15 +52298,11 @@
           <t>80 000</t>
         </is>
       </c>
-      <c r="G254" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H254" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G254" t="n">
+        <v>4</v>
+      </c>
+      <c r="H254" t="n">
+        <v>2</v>
       </c>
       <c r="I254" t="inlineStr">
         <is>
@@ -52696,15 +52324,11 @@
           <t>Bochum</t>
         </is>
       </c>
-      <c r="M254" t="inlineStr">
-        <is>
-          <t>3.24</t>
-        </is>
-      </c>
-      <c r="N254" t="inlineStr">
-        <is>
-          <t>1.49</t>
-        </is>
+      <c r="M254" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="N254" t="n">
+        <v>1.49</v>
       </c>
       <c r="O254" t="inlineStr">
         <is>
@@ -52716,139 +52340,87 @@
           <t>36%</t>
         </is>
       </c>
-      <c r="Q254" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="R254" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="S254" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="T254" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="U254" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="V254" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="W254" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="X254" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="Y254" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="Z254" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AA254" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AB254" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AC254" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AD254" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AE254" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AF254" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AG254" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AH254" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AI254" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AJ254" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK254" t="inlineStr">
-        <is>
-          <t>538</t>
-        </is>
-      </c>
-      <c r="AL254" t="inlineStr">
-        <is>
-          <t>272</t>
-        </is>
-      </c>
-      <c r="AM254" t="inlineStr">
-        <is>
-          <t>491</t>
-        </is>
-      </c>
-      <c r="AN254" t="inlineStr">
-        <is>
-          <t>205</t>
-        </is>
+      <c r="Q254" t="n">
+        <v>22</v>
+      </c>
+      <c r="R254" t="n">
+        <v>10</v>
+      </c>
+      <c r="S254" t="n">
+        <v>7</v>
+      </c>
+      <c r="T254" t="n">
+        <v>6</v>
+      </c>
+      <c r="U254" t="n">
+        <v>15</v>
+      </c>
+      <c r="V254" t="n">
+        <v>4</v>
+      </c>
+      <c r="W254" t="n">
+        <v>12</v>
+      </c>
+      <c r="X254" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y254" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z254" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA254" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB254" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC254" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD254" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE254" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF254" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG254" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH254" t="n">
+        <v>9</v>
+      </c>
+      <c r="AI254" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ254" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK254" t="n">
+        <v>538</v>
+      </c>
+      <c r="AL254" t="n">
+        <v>272</v>
+      </c>
+      <c r="AM254" t="n">
+        <v>491</v>
+      </c>
+      <c r="AN254" t="n">
+        <v>205</v>
       </c>
       <c r="AO254" t="inlineStr"/>
       <c r="AP254" t="inlineStr"/>
       <c r="AQ254" t="inlineStr"/>
       <c r="AR254" t="inlineStr"/>
-      <c r="AS254" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="AT254" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
+      <c r="AS254" t="n">
+        <v>114</v>
+      </c>
+      <c r="AT254" t="n">
+        <v>114</v>
       </c>
       <c r="AU254" t="inlineStr">
         <is>
@@ -52924,15 +52496,11 @@
           <t>12 422</t>
         </is>
       </c>
-      <c r="G255" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H255" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G255" t="n">
+        <v>1</v>
+      </c>
+      <c r="H255" t="n">
+        <v>2</v>
       </c>
       <c r="I255" t="inlineStr">
         <is>
@@ -52954,15 +52522,11 @@
           <t>Schalke</t>
         </is>
       </c>
-      <c r="M255" t="inlineStr">
-        <is>
-          <t>2.33</t>
-        </is>
-      </c>
-      <c r="N255" t="inlineStr">
-        <is>
-          <t>1.18</t>
-        </is>
+      <c r="M255" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="N255" t="n">
+        <v>1.18</v>
       </c>
       <c r="O255" t="inlineStr">
         <is>
@@ -52974,139 +52538,87 @@
           <t>57%</t>
         </is>
       </c>
-      <c r="Q255" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="R255" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="S255" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="T255" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U255" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="V255" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="W255" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="X255" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="Y255" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Z255" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA255" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB255" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC255" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="AD255" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AE255" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AF255" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AG255" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AH255" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AI255" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AJ255" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AK255" t="inlineStr">
-        <is>
-          <t>324</t>
-        </is>
-      </c>
-      <c r="AL255" t="inlineStr">
-        <is>
-          <t>521</t>
-        </is>
-      </c>
-      <c r="AM255" t="inlineStr">
-        <is>
-          <t>260</t>
-        </is>
-      </c>
-      <c r="AN255" t="inlineStr">
-        <is>
-          <t>459</t>
-        </is>
+      <c r="Q255" t="n">
+        <v>19</v>
+      </c>
+      <c r="R255" t="n">
+        <v>14</v>
+      </c>
+      <c r="S255" t="n">
+        <v>4</v>
+      </c>
+      <c r="T255" t="n">
+        <v>4</v>
+      </c>
+      <c r="U255" t="n">
+        <v>15</v>
+      </c>
+      <c r="V255" t="n">
+        <v>10</v>
+      </c>
+      <c r="W255" t="n">
+        <v>10</v>
+      </c>
+      <c r="X255" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y255" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z255" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA255" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB255" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC255" t="n">
+        <v>26</v>
+      </c>
+      <c r="AD255" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE255" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF255" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG255" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH255" t="n">
+        <v>9</v>
+      </c>
+      <c r="AI255" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ255" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK255" t="n">
+        <v>324</v>
+      </c>
+      <c r="AL255" t="n">
+        <v>521</v>
+      </c>
+      <c r="AM255" t="n">
+        <v>260</v>
+      </c>
+      <c r="AN255" t="n">
+        <v>459</v>
       </c>
       <c r="AO255" t="inlineStr"/>
       <c r="AP255" t="inlineStr"/>
       <c r="AQ255" t="inlineStr"/>
       <c r="AR255" t="inlineStr"/>
-      <c r="AS255" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="AT255" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
+      <c r="AS255" t="n">
+        <v>116</v>
+      </c>
+      <c r="AT255" t="n">
+        <v>121</v>
       </c>
       <c r="AU255" t="inlineStr">
         <is>
@@ -53182,15 +52694,11 @@
           <t>17 311</t>
         </is>
       </c>
-      <c r="G256" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H256" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G256" t="n">
+        <v>1</v>
+      </c>
+      <c r="H256" t="n">
+        <v>2</v>
       </c>
       <c r="I256" t="inlineStr">
         <is>
@@ -53212,15 +52720,11 @@
           <t>Magdeburg</t>
         </is>
       </c>
-      <c r="M256" t="inlineStr">
-        <is>
-          <t>2.62</t>
-        </is>
-      </c>
-      <c r="N256" t="inlineStr">
-        <is>
-          <t>1.06</t>
-        </is>
+      <c r="M256" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="N256" t="n">
+        <v>1.06</v>
       </c>
       <c r="O256" t="inlineStr">
         <is>
@@ -53232,139 +52736,87 @@
           <t>58%</t>
         </is>
       </c>
-      <c r="Q256" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="R256" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="S256" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="T256" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="U256" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="V256" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="W256" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="X256" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="Y256" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Z256" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA256" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB256" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC256" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AD256" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AE256" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AF256" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AG256" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AH256" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AI256" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AJ256" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AK256" t="inlineStr">
-        <is>
-          <t>389</t>
-        </is>
-      </c>
-      <c r="AL256" t="inlineStr">
-        <is>
-          <t>556</t>
-        </is>
-      </c>
-      <c r="AM256" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
-      </c>
-      <c r="AN256" t="inlineStr">
-        <is>
-          <t>518</t>
-        </is>
+      <c r="Q256" t="n">
+        <v>17</v>
+      </c>
+      <c r="R256" t="n">
+        <v>11</v>
+      </c>
+      <c r="S256" t="n">
+        <v>7</v>
+      </c>
+      <c r="T256" t="n">
+        <v>3</v>
+      </c>
+      <c r="U256" t="n">
+        <v>10</v>
+      </c>
+      <c r="V256" t="n">
+        <v>8</v>
+      </c>
+      <c r="W256" t="n">
+        <v>17</v>
+      </c>
+      <c r="X256" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y256" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z256" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA256" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB256" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC256" t="n">
+        <v>17</v>
+      </c>
+      <c r="AD256" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE256" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF256" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG256" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH256" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI256" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ256" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK256" t="n">
+        <v>389</v>
+      </c>
+      <c r="AL256" t="n">
+        <v>556</v>
+      </c>
+      <c r="AM256" t="n">
+        <v>328</v>
+      </c>
+      <c r="AN256" t="n">
+        <v>518</v>
       </c>
       <c r="AO256" t="inlineStr"/>
       <c r="AP256" t="inlineStr"/>
       <c r="AQ256" t="inlineStr"/>
       <c r="AR256" t="inlineStr"/>
-      <c r="AS256" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
-      </c>
-      <c r="AT256" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
+      <c r="AS256" t="n">
+        <v>127</v>
+      </c>
+      <c r="AT256" t="n">
+        <v>125</v>
       </c>
       <c r="AU256" t="inlineStr">
         <is>
@@ -53400,15 +52852,11 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="BC256" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BD256" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="BC256" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD256" t="n">
+        <v>1</v>
       </c>
       <c r="BE256" t="inlineStr"/>
       <c r="BF256" t="inlineStr"/>
@@ -53448,15 +52896,11 @@
           <t>57 000</t>
         </is>
       </c>
-      <c r="G257" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H257" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G257" t="n">
+        <v>2</v>
+      </c>
+      <c r="H257" t="n">
+        <v>2</v>
       </c>
       <c r="I257" t="inlineStr">
         <is>
@@ -53478,15 +52922,11 @@
           <t>Paderborn</t>
         </is>
       </c>
-      <c r="M257" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
-      <c r="N257" t="inlineStr">
-        <is>
-          <t>1.27</t>
-        </is>
+      <c r="M257" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="N257" t="n">
+        <v>1.27</v>
       </c>
       <c r="O257" t="inlineStr">
         <is>
@@ -53498,139 +52938,87 @@
           <t>44%</t>
         </is>
       </c>
-      <c r="Q257" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="R257" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="S257" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="T257" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="U257" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="V257" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="W257" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="X257" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="Y257" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Z257" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA257" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB257" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC257" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="AD257" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AE257" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AF257" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AG257" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AH257" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AI257" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AJ257" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AK257" t="inlineStr">
-        <is>
-          <t>525</t>
-        </is>
-      </c>
-      <c r="AL257" t="inlineStr">
-        <is>
-          <t>324</t>
-        </is>
-      </c>
-      <c r="AM257" t="inlineStr">
-        <is>
-          <t>483</t>
-        </is>
-      </c>
-      <c r="AN257" t="inlineStr">
-        <is>
-          <t>273</t>
-        </is>
+      <c r="Q257" t="n">
+        <v>17</v>
+      </c>
+      <c r="R257" t="n">
+        <v>12</v>
+      </c>
+      <c r="S257" t="n">
+        <v>7</v>
+      </c>
+      <c r="T257" t="n">
+        <v>6</v>
+      </c>
+      <c r="U257" t="n">
+        <v>10</v>
+      </c>
+      <c r="V257" t="n">
+        <v>6</v>
+      </c>
+      <c r="W257" t="n">
+        <v>15</v>
+      </c>
+      <c r="X257" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y257" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z257" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA257" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB257" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC257" t="n">
+        <v>23</v>
+      </c>
+      <c r="AD257" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE257" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF257" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG257" t="n">
+        <v>18</v>
+      </c>
+      <c r="AH257" t="n">
+        <v>12</v>
+      </c>
+      <c r="AI257" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ257" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK257" t="n">
+        <v>525</v>
+      </c>
+      <c r="AL257" t="n">
+        <v>324</v>
+      </c>
+      <c r="AM257" t="n">
+        <v>483</v>
+      </c>
+      <c r="AN257" t="n">
+        <v>273</v>
       </c>
       <c r="AO257" t="inlineStr"/>
       <c r="AP257" t="inlineStr"/>
       <c r="AQ257" t="inlineStr"/>
       <c r="AR257" t="inlineStr"/>
-      <c r="AS257" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="AT257" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
+      <c r="AS257" t="n">
+        <v>121</v>
+      </c>
+      <c r="AT257" t="n">
+        <v>128</v>
       </c>
       <c r="AU257" t="inlineStr">
         <is>
@@ -53706,15 +53094,11 @@
           <t>14 431</t>
         </is>
       </c>
-      <c r="G258" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H258" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G258" t="n">
+        <v>0</v>
+      </c>
+      <c r="H258" t="n">
+        <v>0</v>
       </c>
       <c r="I258" t="inlineStr">
         <is>
@@ -53736,15 +53120,11 @@
           <t>Kaiserslautern</t>
         </is>
       </c>
-      <c r="M258" t="inlineStr">
-        <is>
-          <t>0.40</t>
-        </is>
-      </c>
-      <c r="N258" t="inlineStr">
-        <is>
-          <t>1.19</t>
-        </is>
+      <c r="M258" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N258" t="n">
+        <v>1.19</v>
       </c>
       <c r="O258" t="inlineStr">
         <is>
@@ -53756,139 +53136,87 @@
           <t>69%</t>
         </is>
       </c>
-      <c r="Q258" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="R258" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="S258" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="T258" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U258" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="V258" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="W258" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="X258" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="Y258" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Z258" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA258" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB258" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AC258" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AD258" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="AE258" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AF258" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AG258" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AH258" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AI258" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AJ258" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AK258" t="inlineStr">
-        <is>
-          <t>189</t>
-        </is>
-      </c>
-      <c r="AL258" t="inlineStr">
-        <is>
-          <t>677</t>
-        </is>
-      </c>
-      <c r="AM258" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="AN258" t="inlineStr">
-        <is>
-          <t>669</t>
-        </is>
+      <c r="Q258" t="n">
+        <v>7</v>
+      </c>
+      <c r="R258" t="n">
+        <v>9</v>
+      </c>
+      <c r="S258" t="n">
+        <v>2</v>
+      </c>
+      <c r="T258" t="n">
+        <v>4</v>
+      </c>
+      <c r="U258" t="n">
+        <v>5</v>
+      </c>
+      <c r="V258" t="n">
+        <v>5</v>
+      </c>
+      <c r="W258" t="n">
+        <v>19</v>
+      </c>
+      <c r="X258" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y258" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z258" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA258" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB258" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC258" t="n">
+        <v>17</v>
+      </c>
+      <c r="AD258" t="n">
+        <v>29</v>
+      </c>
+      <c r="AE258" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF258" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG258" t="n">
+        <v>9</v>
+      </c>
+      <c r="AH258" t="n">
+        <v>14</v>
+      </c>
+      <c r="AI258" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ258" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK258" t="n">
+        <v>189</v>
+      </c>
+      <c r="AL258" t="n">
+        <v>677</v>
+      </c>
+      <c r="AM258" t="n">
+        <v>151</v>
+      </c>
+      <c r="AN258" t="n">
+        <v>669</v>
       </c>
       <c r="AO258" t="inlineStr"/>
       <c r="AP258" t="inlineStr"/>
       <c r="AQ258" t="inlineStr"/>
       <c r="AR258" t="inlineStr"/>
-      <c r="AS258" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="AT258" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
+      <c r="AS258" t="n">
+        <v>118</v>
+      </c>
+      <c r="AT258" t="n">
+        <v>115</v>
       </c>
       <c r="AU258" t="inlineStr">
         <is>
@@ -53964,15 +53292,11 @@
           <t>12 405</t>
         </is>
       </c>
-      <c r="G259" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H259" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G259" t="n">
+        <v>1</v>
+      </c>
+      <c r="H259" t="n">
+        <v>2</v>
       </c>
       <c r="I259" t="inlineStr">
         <is>
@@ -53994,15 +53318,11 @@
           <t>Dusseldorf</t>
         </is>
       </c>
-      <c r="M259" t="inlineStr">
-        <is>
-          <t>2.66</t>
-        </is>
-      </c>
-      <c r="N259" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
+      <c r="M259" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="N259" t="n">
+        <v>2.55</v>
       </c>
       <c r="O259" t="inlineStr">
         <is>
@@ -54014,139 +53334,87 @@
           <t>44%</t>
         </is>
       </c>
-      <c r="Q259" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="R259" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="S259" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="T259" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="U259" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="V259" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="W259" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="X259" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="Y259" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Z259" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AA259" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB259" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AC259" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="AD259" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AE259" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AF259" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG259" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AH259" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AI259" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AJ259" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AK259" t="inlineStr">
-        <is>
-          <t>514</t>
-        </is>
-      </c>
-      <c r="AL259" t="inlineStr">
-        <is>
-          <t>433</t>
-        </is>
-      </c>
-      <c r="AM259" t="inlineStr">
-        <is>
-          <t>442</t>
-        </is>
-      </c>
-      <c r="AN259" t="inlineStr">
-        <is>
-          <t>368</t>
-        </is>
+      <c r="Q259" t="n">
+        <v>15</v>
+      </c>
+      <c r="R259" t="n">
+        <v>12</v>
+      </c>
+      <c r="S259" t="n">
+        <v>1</v>
+      </c>
+      <c r="T259" t="n">
+        <v>3</v>
+      </c>
+      <c r="U259" t="n">
+        <v>14</v>
+      </c>
+      <c r="V259" t="n">
+        <v>9</v>
+      </c>
+      <c r="W259" t="n">
+        <v>14</v>
+      </c>
+      <c r="X259" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y259" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z259" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA259" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB259" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC259" t="n">
+        <v>27</v>
+      </c>
+      <c r="AD259" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE259" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF259" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG259" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH259" t="n">
+        <v>10</v>
+      </c>
+      <c r="AI259" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ259" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK259" t="n">
+        <v>514</v>
+      </c>
+      <c r="AL259" t="n">
+        <v>433</v>
+      </c>
+      <c r="AM259" t="n">
+        <v>442</v>
+      </c>
+      <c r="AN259" t="n">
+        <v>368</v>
       </c>
       <c r="AO259" t="inlineStr"/>
       <c r="AP259" t="inlineStr"/>
       <c r="AQ259" t="inlineStr"/>
       <c r="AR259" t="inlineStr"/>
-      <c r="AS259" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="AT259" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
+      <c r="AS259" t="n">
+        <v>120</v>
+      </c>
+      <c r="AT259" t="n">
+        <v>118</v>
       </c>
       <c r="AU259" t="inlineStr">
         <is>
@@ -54222,15 +53490,11 @@
           <t>13 607</t>
         </is>
       </c>
-      <c r="G260" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H260" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G260" t="n">
+        <v>3</v>
+      </c>
+      <c r="H260" t="n">
+        <v>1</v>
       </c>
       <c r="I260" t="inlineStr">
         <is>
@@ -54252,15 +53516,11 @@
           <t>Braunschweig</t>
         </is>
       </c>
-      <c r="M260" t="inlineStr">
-        <is>
-          <t>2.91</t>
-        </is>
-      </c>
-      <c r="N260" t="inlineStr">
-        <is>
-          <t>0.68</t>
-        </is>
+      <c r="M260" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="N260" t="n">
+        <v>0.68</v>
       </c>
       <c r="O260" t="inlineStr">
         <is>
@@ -54272,139 +53532,87 @@
           <t>53%</t>
         </is>
       </c>
-      <c r="Q260" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="R260" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="S260" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="T260" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="U260" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="V260" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="W260" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="X260" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="Y260" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Z260" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA260" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AB260" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC260" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="AD260" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="AE260" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AF260" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AG260" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AH260" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI260" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AJ260" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AK260" t="inlineStr">
-        <is>
-          <t>327</t>
-        </is>
-      </c>
-      <c r="AL260" t="inlineStr">
-        <is>
-          <t>402</t>
-        </is>
-      </c>
-      <c r="AM260" t="inlineStr">
-        <is>
-          <t>265</t>
-        </is>
-      </c>
-      <c r="AN260" t="inlineStr">
-        <is>
-          <t>334</t>
-        </is>
+      <c r="Q260" t="n">
+        <v>18</v>
+      </c>
+      <c r="R260" t="n">
+        <v>9</v>
+      </c>
+      <c r="S260" t="n">
+        <v>6</v>
+      </c>
+      <c r="T260" t="n">
+        <v>1</v>
+      </c>
+      <c r="U260" t="n">
+        <v>12</v>
+      </c>
+      <c r="V260" t="n">
+        <v>8</v>
+      </c>
+      <c r="W260" t="n">
+        <v>14</v>
+      </c>
+      <c r="X260" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y260" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z260" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA260" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB260" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC260" t="n">
+        <v>29</v>
+      </c>
+      <c r="AD260" t="n">
+        <v>29</v>
+      </c>
+      <c r="AE260" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF260" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG260" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH260" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI260" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ260" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK260" t="n">
+        <v>327</v>
+      </c>
+      <c r="AL260" t="n">
+        <v>402</v>
+      </c>
+      <c r="AM260" t="n">
+        <v>265</v>
+      </c>
+      <c r="AN260" t="n">
+        <v>334</v>
       </c>
       <c r="AO260" t="inlineStr"/>
       <c r="AP260" t="inlineStr"/>
       <c r="AQ260" t="inlineStr"/>
       <c r="AR260" t="inlineStr"/>
-      <c r="AS260" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="AT260" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
+      <c r="AS260" t="n">
+        <v>125</v>
+      </c>
+      <c r="AT260" t="n">
+        <v>117</v>
       </c>
       <c r="AU260" t="inlineStr">
         <is>
@@ -54440,21 +53648,1315 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="BC260" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BD260" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="BC260" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD260" t="n">
+        <v>1</v>
       </c>
       <c r="BE260" t="inlineStr"/>
       <c r="BF260" t="inlineStr"/>
       <c r="BG260" t="inlineStr"/>
       <c r="BH260" t="inlineStr"/>
     </row>
+    <row r="261">
+      <c r="A261" s="1" t="inlineStr">
+        <is>
+          <t>bFO8E4Vg</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>29.09.2024 12:30</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Reichel T.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>PreZero Arena
+ (Sinsheim)</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>30 150</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>26 018</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>hQAtP9Sl</t>
+        </is>
+      </c>
+      <c r="J261" t="inlineStr">
+        <is>
+          <t>Hoffenheim</t>
+        </is>
+      </c>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>Ig1f1fy3</t>
+        </is>
+      </c>
+      <c r="L261" t="inlineStr">
+        <is>
+          <t>Werder Bremen</t>
+        </is>
+      </c>
+      <c r="M261" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="N261" t="inlineStr">
+        <is>
+          <t>2.42</t>
+        </is>
+      </c>
+      <c r="O261" t="inlineStr">
+        <is>
+          <t>43%</t>
+        </is>
+      </c>
+      <c r="P261" t="inlineStr">
+        <is>
+          <t>57%</t>
+        </is>
+      </c>
+      <c r="Q261" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R261" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="S261" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T261" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="U261" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V261" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="W261" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="X261" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="Y261" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Z261" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA261" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB261" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC261" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AD261" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AE261" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AF261" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AG261" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AH261" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AI261" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AJ261" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AK261" t="inlineStr">
+        <is>
+          <t>325</t>
+        </is>
+      </c>
+      <c r="AL261" t="inlineStr">
+        <is>
+          <t>601</t>
+        </is>
+      </c>
+      <c r="AM261" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="AN261" t="inlineStr">
+        <is>
+          <t>594</t>
+        </is>
+      </c>
+      <c r="AO261" t="inlineStr"/>
+      <c r="AP261" t="inlineStr"/>
+      <c r="AQ261" t="inlineStr"/>
+      <c r="AR261" t="inlineStr"/>
+      <c r="AS261" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="AT261" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="AU261" t="inlineStr">
+        <is>
+          <t>KUx4Q7x1</t>
+        </is>
+      </c>
+      <c r="AV261" t="inlineStr">
+        <is>
+          <t>matarazzo pellegrino</t>
+        </is>
+      </c>
+      <c r="AW261" t="inlineStr">
+        <is>
+          <t>4fuCGs9P</t>
+        </is>
+      </c>
+      <c r="AX261" t="inlineStr">
+        <is>
+          <t>werner ole</t>
+        </is>
+      </c>
+      <c r="AY261" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ261" t="n">
+        <v>591</v>
+      </c>
+      <c r="BA261" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB261" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC261" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BD261" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE261" t="inlineStr"/>
+      <c r="BF261" t="inlineStr"/>
+      <c r="BG261" t="inlineStr"/>
+      <c r="BH261" t="inlineStr"/>
+    </row>
+    <row r="262">
+      <c r="A262" s="1" t="inlineStr">
+        <is>
+          <t>pWnjRsFa</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>29.09.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>Stieler T.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>Holstein-Stadion
+ (Kiel)</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>15 034</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>15 034</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>63WsD2ei</t>
+        </is>
+      </c>
+      <c r="J262" t="inlineStr">
+        <is>
+          <t>Holstein Kiel</t>
+        </is>
+      </c>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="L262" t="inlineStr">
+        <is>
+          <t>Eintracht Frankfurt</t>
+        </is>
+      </c>
+      <c r="M262" t="inlineStr">
+        <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="N262" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="O262" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="P262" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
+      </c>
+      <c r="Q262" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R262" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="S262" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T262" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="U262" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V262" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="W262" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="X262" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="Y262" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Z262" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA262" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB262" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC262" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AD262" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AE262" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AF262" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AG262" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AH262" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AI262" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AJ262" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AK262" t="inlineStr">
+        <is>
+          <t>406</t>
+        </is>
+      </c>
+      <c r="AL262" t="inlineStr">
+        <is>
+          <t>446</t>
+        </is>
+      </c>
+      <c r="AM262" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="AN262" t="inlineStr">
+        <is>
+          <t>369</t>
+        </is>
+      </c>
+      <c r="AO262" t="inlineStr"/>
+      <c r="AP262" t="inlineStr"/>
+      <c r="AQ262" t="inlineStr"/>
+      <c r="AR262" t="inlineStr"/>
+      <c r="AS262" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="AT262" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="AU262" t="inlineStr">
+        <is>
+          <t>A15eUM4C</t>
+        </is>
+      </c>
+      <c r="AV262" t="inlineStr">
+        <is>
+          <t>rapp marcel</t>
+        </is>
+      </c>
+      <c r="AW262" t="inlineStr">
+        <is>
+          <t>UgdQz0fK</t>
+        </is>
+      </c>
+      <c r="AX262" t="inlineStr">
+        <is>
+          <t>toppmoller dino</t>
+        </is>
+      </c>
+      <c r="AY262" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ262" t="n">
+        <v>591</v>
+      </c>
+      <c r="BA262" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB262" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC262" t="inlineStr"/>
+      <c r="BD262" t="inlineStr"/>
+      <c r="BE262" t="inlineStr"/>
+      <c r="BF262" t="inlineStr"/>
+      <c r="BG262" t="inlineStr"/>
+      <c r="BH262" t="inlineStr"/>
+    </row>
+    <row r="263">
+      <c r="A263" s="1" t="inlineStr">
+        <is>
+          <t>Ays5Dskn</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>29.09.2024 08:30</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Brand B.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>RheinEnergieStadion
+ (Cologne)</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>50 000</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>50 000</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>WG9pOTse</t>
+        </is>
+      </c>
+      <c r="J263" t="inlineStr">
+        <is>
+          <t>FC Koln</t>
+        </is>
+      </c>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>EB3q7jbk</t>
+        </is>
+      </c>
+      <c r="L263" t="inlineStr">
+        <is>
+          <t>Karlsruher SC</t>
+        </is>
+      </c>
+      <c r="M263" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="N263" t="inlineStr">
+        <is>
+          <t>2.32</t>
+        </is>
+      </c>
+      <c r="O263" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
+      </c>
+      <c r="P263" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="Q263" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R263" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="S263" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T263" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="U263" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="V263" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="W263" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="X263" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="Y263" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Z263" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA263" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB263" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC263" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AD263" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AE263" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AF263" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AG263" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AH263" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AI263" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AJ263" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AK263" t="inlineStr">
+        <is>
+          <t>470</t>
+        </is>
+      </c>
+      <c r="AL263" t="inlineStr">
+        <is>
+          <t>434</t>
+        </is>
+      </c>
+      <c r="AM263" t="inlineStr">
+        <is>
+          <t>395</t>
+        </is>
+      </c>
+      <c r="AN263" t="inlineStr">
+        <is>
+          <t>356</t>
+        </is>
+      </c>
+      <c r="AO263" t="inlineStr"/>
+      <c r="AP263" t="inlineStr"/>
+      <c r="AQ263" t="inlineStr"/>
+      <c r="AR263" t="inlineStr"/>
+      <c r="AS263" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="AT263" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="AU263" t="inlineStr">
+        <is>
+          <t>4fX0k7gg</t>
+        </is>
+      </c>
+      <c r="AV263" t="inlineStr">
+        <is>
+          <t>struber gerhard</t>
+        </is>
+      </c>
+      <c r="AW263" t="inlineStr">
+        <is>
+          <t>OzPMRhK3</t>
+        </is>
+      </c>
+      <c r="AX263" t="inlineStr">
+        <is>
+          <t>eichner christian</t>
+        </is>
+      </c>
+      <c r="AY263" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ263" t="n">
+        <v>592</v>
+      </c>
+      <c r="BA263" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB263" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC263" t="inlineStr"/>
+      <c r="BD263" t="inlineStr"/>
+      <c r="BE263" t="inlineStr"/>
+      <c r="BF263" t="inlineStr"/>
+      <c r="BG263" t="inlineStr"/>
+      <c r="BH263" t="inlineStr"/>
+    </row>
+    <row r="264">
+      <c r="A264" s="1" t="inlineStr">
+        <is>
+          <t>zqSU7wJN</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>29.09.2024 08:30</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>Weisbach E.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>Heinz-von-Heiden-Arena
+ (Hannover)</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>49 200</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>36 500</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>dfNCCCzS</t>
+        </is>
+      </c>
+      <c r="J264" t="inlineStr">
+        <is>
+          <t>Hannover</t>
+        </is>
+      </c>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>6FDqshzF</t>
+        </is>
+      </c>
+      <c r="L264" t="inlineStr">
+        <is>
+          <t>Nurnberg</t>
+        </is>
+      </c>
+      <c r="M264" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="N264" t="inlineStr">
+        <is>
+          <t>0.67</t>
+        </is>
+      </c>
+      <c r="O264" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
+      </c>
+      <c r="P264" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="Q264" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="R264" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S264" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T264" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U264" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V264" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W264" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="X264" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="Y264" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Z264" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA264" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB264" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC264" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AD264" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AE264" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AF264" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AG264" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AH264" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AI264" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AJ264" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AK264" t="inlineStr">
+        <is>
+          <t>465</t>
+        </is>
+      </c>
+      <c r="AL264" t="inlineStr">
+        <is>
+          <t>428</t>
+        </is>
+      </c>
+      <c r="AM264" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="AN264" t="inlineStr">
+        <is>
+          <t>335</t>
+        </is>
+      </c>
+      <c r="AO264" t="inlineStr"/>
+      <c r="AP264" t="inlineStr"/>
+      <c r="AQ264" t="inlineStr"/>
+      <c r="AR264" t="inlineStr"/>
+      <c r="AS264" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="AT264" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="AU264" t="inlineStr">
+        <is>
+          <t>t0ZPdkUl</t>
+        </is>
+      </c>
+      <c r="AV264" t="inlineStr">
+        <is>
+          <t>leitl stefan</t>
+        </is>
+      </c>
+      <c r="AW264" t="inlineStr">
+        <is>
+          <t>tO31cZrF</t>
+        </is>
+      </c>
+      <c r="AX264" t="inlineStr">
+        <is>
+          <t>klose miroslav</t>
+        </is>
+      </c>
+      <c r="AY264" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ264" t="n">
+        <v>592</v>
+      </c>
+      <c r="BA264" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB264" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC264" t="inlineStr"/>
+      <c r="BD264" t="inlineStr"/>
+      <c r="BE264" t="inlineStr"/>
+      <c r="BF264" t="inlineStr"/>
+      <c r="BG264" t="inlineStr"/>
+      <c r="BH264" t="inlineStr"/>
+    </row>
+    <row r="265">
+      <c r="A265" s="1" t="inlineStr">
+        <is>
+          <t>AcIuQKYi</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>29.09.2024 08:30</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Winter N.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>Olympiastadion
+ (Berlin)</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>74 667</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>43 123</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>2y0u8Wrq</t>
+        </is>
+      </c>
+      <c r="J265" t="inlineStr">
+        <is>
+          <t>Hertha Berlin</t>
+        </is>
+      </c>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>6in2Eknb</t>
+        </is>
+      </c>
+      <c r="L265" t="inlineStr">
+        <is>
+          <t>Elversberg</t>
+        </is>
+      </c>
+      <c r="M265" t="inlineStr">
+        <is>
+          <t>0.93</t>
+        </is>
+      </c>
+      <c r="N265" t="inlineStr">
+        <is>
+          <t>2.51</t>
+        </is>
+      </c>
+      <c r="O265" t="inlineStr">
+        <is>
+          <t>57%</t>
+        </is>
+      </c>
+      <c r="P265" t="inlineStr">
+        <is>
+          <t>43%</t>
+        </is>
+      </c>
+      <c r="Q265" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R265" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="S265" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T265" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="U265" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V265" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W265" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="X265" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="Y265" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Z265" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA265" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB265" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC265" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AD265" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="AE265" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AF265" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AG265" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AH265" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AI265" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AJ265" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AK265" t="inlineStr">
+        <is>
+          <t>407</t>
+        </is>
+      </c>
+      <c r="AL265" t="inlineStr">
+        <is>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="AM265" t="inlineStr">
+        <is>
+          <t>346</t>
+        </is>
+      </c>
+      <c r="AN265" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="AO265" t="inlineStr"/>
+      <c r="AP265" t="inlineStr"/>
+      <c r="AQ265" t="inlineStr"/>
+      <c r="AR265" t="inlineStr"/>
+      <c r="AS265" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="AT265" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="AU265" t="inlineStr">
+        <is>
+          <t>YmfcAeCo</t>
+        </is>
+      </c>
+      <c r="AV265" t="inlineStr">
+        <is>
+          <t>fiel cristian</t>
+        </is>
+      </c>
+      <c r="AW265" t="inlineStr">
+        <is>
+          <t>8E8qmw3d</t>
+        </is>
+      </c>
+      <c r="AX265" t="inlineStr">
+        <is>
+          <t>steffen horst</t>
+        </is>
+      </c>
+      <c r="AY265" t="n">
+        <v>59</v>
+      </c>
+      <c r="AZ265" t="n">
+        <v>592</v>
+      </c>
+      <c r="BA265" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB265" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BC265" t="inlineStr"/>
+      <c r="BD265" t="inlineStr"/>
+      <c r="BE265" t="inlineStr"/>
+      <c r="BF265" t="inlineStr"/>
+      <c r="BG265" t="inlineStr"/>
+      <c r="BH265" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/germany/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
+++ b/data/germany/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH276"/>
+  <dimension ref="A1:BH283"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54714,15 +54714,11 @@
           <t>29 546</t>
         </is>
       </c>
-      <c r="G266" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H266" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="G266" t="n">
+        <v>0</v>
+      </c>
+      <c r="H266" t="n">
+        <v>3</v>
       </c>
       <c r="I266" t="inlineStr">
         <is>
@@ -54744,15 +54740,11 @@
           <t>Mainz</t>
         </is>
       </c>
-      <c r="M266" t="inlineStr">
-        <is>
-          <t>1.05</t>
-        </is>
-      </c>
-      <c r="N266" t="inlineStr">
-        <is>
-          <t>0.74</t>
-        </is>
+      <c r="M266" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N266" t="n">
+        <v>0.74</v>
       </c>
       <c r="O266" t="inlineStr">
         <is>
@@ -54764,137 +54756,85 @@
           <t>44%</t>
         </is>
       </c>
-      <c r="Q266" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="R266" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="S266" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="T266" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U266" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="V266" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="W266" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="X266" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Y266" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Z266" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA266" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB266" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC266" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="AD266" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AE266" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AF266" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AG266" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AH266" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+      <c r="Q266" t="n">
+        <v>17</v>
+      </c>
+      <c r="R266" t="n">
+        <v>8</v>
+      </c>
+      <c r="S266" t="n">
+        <v>4</v>
+      </c>
+      <c r="T266" t="n">
+        <v>4</v>
+      </c>
+      <c r="U266" t="n">
+        <v>13</v>
+      </c>
+      <c r="V266" t="n">
+        <v>4</v>
+      </c>
+      <c r="W266" t="n">
+        <v>20</v>
+      </c>
+      <c r="X266" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y266" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z266" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA266" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB266" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC266" t="n">
+        <v>48</v>
+      </c>
+      <c r="AD266" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE266" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF266" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG266" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH266" t="n">
+        <v>16</v>
       </c>
       <c r="AI266" t="inlineStr"/>
       <c r="AJ266" t="inlineStr"/>
-      <c r="AK266" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AL266" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AM266" t="inlineStr">
-        <is>
-          <t>488</t>
-        </is>
-      </c>
-      <c r="AN266" t="inlineStr">
-        <is>
-          <t>408</t>
-        </is>
-      </c>
-      <c r="AO266" t="inlineStr">
-        <is>
-          <t>386</t>
-        </is>
-      </c>
-      <c r="AP266" t="inlineStr">
-        <is>
-          <t>318</t>
-        </is>
-      </c>
-      <c r="AQ266" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
-      <c r="AR266" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
+      <c r="AK266" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL266" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM266" t="n">
+        <v>488</v>
+      </c>
+      <c r="AN266" t="n">
+        <v>408</v>
+      </c>
+      <c r="AO266" t="n">
+        <v>386</v>
+      </c>
+      <c r="AP266" t="n">
+        <v>318</v>
+      </c>
+      <c r="AQ266" t="n">
+        <v>126</v>
+      </c>
+      <c r="AR266" t="n">
+        <v>123</v>
       </c>
       <c r="AS266" t="inlineStr">
         <is>
@@ -54972,15 +54912,11 @@
           <t>30 210</t>
         </is>
       </c>
-      <c r="G267" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H267" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G267" t="n">
+        <v>2</v>
+      </c>
+      <c r="H267" t="n">
+        <v>2</v>
       </c>
       <c r="I267" t="inlineStr">
         <is>
@@ -55002,15 +54938,11 @@
           <t>Holstein Kiel</t>
         </is>
       </c>
-      <c r="M267" t="inlineStr">
-        <is>
-          <t>2.13</t>
-        </is>
-      </c>
-      <c r="N267" t="inlineStr">
-        <is>
-          <t>1.71</t>
-        </is>
+      <c r="M267" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="N267" t="n">
+        <v>1.71</v>
       </c>
       <c r="O267" t="inlineStr">
         <is>
@@ -55022,137 +54954,85 @@
           <t>33%</t>
         </is>
       </c>
-      <c r="Q267" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="R267" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="S267" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="T267" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U267" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="V267" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="W267" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="X267" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y267" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="Z267" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA267" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AB267" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC267" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AD267" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AE267" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AF267" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AG267" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AH267" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="Q267" t="n">
+        <v>24</v>
+      </c>
+      <c r="R267" t="n">
+        <v>8</v>
+      </c>
+      <c r="S267" t="n">
+        <v>7</v>
+      </c>
+      <c r="T267" t="n">
+        <v>4</v>
+      </c>
+      <c r="U267" t="n">
+        <v>17</v>
+      </c>
+      <c r="V267" t="n">
+        <v>4</v>
+      </c>
+      <c r="W267" t="n">
+        <v>11</v>
+      </c>
+      <c r="X267" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y267" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z267" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA267" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB267" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC267" t="n">
+        <v>21</v>
+      </c>
+      <c r="AD267" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE267" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF267" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG267" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH267" t="n">
+        <v>9</v>
       </c>
       <c r="AI267" t="inlineStr"/>
       <c r="AJ267" t="inlineStr"/>
-      <c r="AK267" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL267" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AM267" t="inlineStr">
-        <is>
-          <t>814</t>
-        </is>
-      </c>
-      <c r="AN267" t="inlineStr">
-        <is>
-          <t>277</t>
-        </is>
-      </c>
-      <c r="AO267" t="inlineStr">
-        <is>
-          <t>749</t>
-        </is>
-      </c>
-      <c r="AP267" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
-      </c>
-      <c r="AQ267" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="AR267" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
+      <c r="AK267" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL267" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM267" t="n">
+        <v>814</v>
+      </c>
+      <c r="AN267" t="n">
+        <v>277</v>
+      </c>
+      <c r="AO267" t="n">
+        <v>749</v>
+      </c>
+      <c r="AP267" t="n">
+        <v>208</v>
+      </c>
+      <c r="AQ267" t="n">
+        <v>120</v>
+      </c>
+      <c r="AR267" t="n">
+        <v>123</v>
       </c>
       <c r="AS267" t="inlineStr">
         <is>
@@ -55230,15 +55110,11 @@
           <t>24 630</t>
         </is>
       </c>
-      <c r="G268" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H268" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="G268" t="n">
+        <v>1</v>
+      </c>
+      <c r="H268" t="n">
+        <v>3</v>
       </c>
       <c r="I268" t="inlineStr">
         <is>
@@ -55260,15 +55136,11 @@
           <t>Wolfsburg</t>
         </is>
       </c>
-      <c r="M268" t="inlineStr">
-        <is>
-          <t>2.01</t>
-        </is>
-      </c>
-      <c r="N268" t="inlineStr">
-        <is>
-          <t>3.41</t>
-        </is>
+      <c r="M268" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="N268" t="n">
+        <v>3.41</v>
       </c>
       <c r="O268" t="inlineStr">
         <is>
@@ -55280,137 +55152,85 @@
           <t>44%</t>
         </is>
       </c>
-      <c r="Q268" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="R268" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="S268" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="T268" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="U268" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="V268" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="W268" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="X268" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="Y268" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Z268" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA268" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AB268" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC268" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AD268" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AE268" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AF268" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AG268" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AH268" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="Q268" t="n">
+        <v>17</v>
+      </c>
+      <c r="R268" t="n">
+        <v>15</v>
+      </c>
+      <c r="S268" t="n">
+        <v>5</v>
+      </c>
+      <c r="T268" t="n">
+        <v>5</v>
+      </c>
+      <c r="U268" t="n">
+        <v>12</v>
+      </c>
+      <c r="V268" t="n">
+        <v>10</v>
+      </c>
+      <c r="W268" t="n">
+        <v>13</v>
+      </c>
+      <c r="X268" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y268" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z268" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA268" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB268" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC268" t="n">
+        <v>21</v>
+      </c>
+      <c r="AD268" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE268" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF268" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG268" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH268" t="n">
+        <v>12</v>
       </c>
       <c r="AI268" t="inlineStr"/>
       <c r="AJ268" t="inlineStr"/>
-      <c r="AK268" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL268" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AM268" t="inlineStr">
-        <is>
-          <t>391</t>
-        </is>
-      </c>
-      <c r="AN268" t="inlineStr">
-        <is>
-          <t>286</t>
-        </is>
-      </c>
-      <c r="AO268" t="inlineStr">
-        <is>
-          <t>301</t>
-        </is>
-      </c>
-      <c r="AP268" t="inlineStr">
-        <is>
-          <t>206</t>
-        </is>
-      </c>
-      <c r="AQ268" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="AR268" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
+      <c r="AK268" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL268" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM268" t="n">
+        <v>391</v>
+      </c>
+      <c r="AN268" t="n">
+        <v>286</v>
+      </c>
+      <c r="AO268" t="n">
+        <v>301</v>
+      </c>
+      <c r="AP268" t="n">
+        <v>206</v>
+      </c>
+      <c r="AQ268" t="n">
+        <v>111</v>
+      </c>
+      <c r="AR268" t="n">
+        <v>106</v>
       </c>
       <c r="AS268" t="inlineStr">
         <is>
@@ -55488,15 +55308,11 @@
           <t>22 012</t>
         </is>
       </c>
-      <c r="G269" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H269" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G269" t="n">
+        <v>2</v>
+      </c>
+      <c r="H269" t="n">
+        <v>1</v>
       </c>
       <c r="I269" t="inlineStr">
         <is>
@@ -55518,15 +55334,11 @@
           <t>Dortmund</t>
         </is>
       </c>
-      <c r="M269" t="inlineStr">
-        <is>
-          <t>1.57</t>
-        </is>
-      </c>
-      <c r="N269" t="inlineStr">
-        <is>
-          <t>0.95</t>
-        </is>
+      <c r="M269" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="N269" t="n">
+        <v>0.95</v>
       </c>
       <c r="O269" t="inlineStr">
         <is>
@@ -55538,137 +55350,85 @@
           <t>64%</t>
         </is>
       </c>
-      <c r="Q269" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="R269" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="S269" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="T269" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="U269" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="V269" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="W269" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="X269" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="Y269" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Z269" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA269" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AB269" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC269" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AD269" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="AE269" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AF269" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AG269" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AH269" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
+      <c r="Q269" t="n">
+        <v>13</v>
+      </c>
+      <c r="R269" t="n">
+        <v>9</v>
+      </c>
+      <c r="S269" t="n">
+        <v>5</v>
+      </c>
+      <c r="T269" t="n">
+        <v>5</v>
+      </c>
+      <c r="U269" t="n">
+        <v>8</v>
+      </c>
+      <c r="V269" t="n">
+        <v>4</v>
+      </c>
+      <c r="W269" t="n">
+        <v>16</v>
+      </c>
+      <c r="X269" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y269" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z269" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA269" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB269" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC269" t="n">
+        <v>18</v>
+      </c>
+      <c r="AD269" t="n">
+        <v>28</v>
+      </c>
+      <c r="AE269" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF269" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG269" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH269" t="n">
+        <v>17</v>
       </c>
       <c r="AI269" t="inlineStr"/>
       <c r="AJ269" t="inlineStr"/>
-      <c r="AK269" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AL269" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AM269" t="inlineStr">
-        <is>
-          <t>271</t>
-        </is>
-      </c>
-      <c r="AN269" t="inlineStr">
-        <is>
-          <t>602</t>
-        </is>
-      </c>
-      <c r="AO269" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
-      </c>
-      <c r="AP269" t="inlineStr">
-        <is>
-          <t>512</t>
-        </is>
-      </c>
-      <c r="AQ269" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
-      <c r="AR269" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
+      <c r="AK269" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL269" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM269" t="n">
+        <v>271</v>
+      </c>
+      <c r="AN269" t="n">
+        <v>602</v>
+      </c>
+      <c r="AO269" t="n">
+        <v>198</v>
+      </c>
+      <c r="AP269" t="n">
+        <v>512</v>
+      </c>
+      <c r="AQ269" t="n">
+        <v>126</v>
+      </c>
+      <c r="AR269" t="n">
+        <v>117</v>
       </c>
       <c r="AS269" t="inlineStr">
         <is>
@@ -55746,15 +55506,11 @@
           <t>41 200</t>
         </is>
       </c>
-      <c r="G270" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H270" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G270" t="n">
+        <v>0</v>
+      </c>
+      <c r="H270" t="n">
+        <v>1</v>
       </c>
       <c r="I270" t="inlineStr">
         <is>
@@ -55776,15 +55532,11 @@
           <t>Freiburg</t>
         </is>
       </c>
-      <c r="M270" t="inlineStr">
-        <is>
-          <t>0.84</t>
-        </is>
-      </c>
-      <c r="N270" t="inlineStr">
-        <is>
-          <t>1.12</t>
-        </is>
+      <c r="M270" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="N270" t="n">
+        <v>1.12</v>
       </c>
       <c r="O270" t="inlineStr">
         <is>
@@ -55796,137 +55548,85 @@
           <t>44%</t>
         </is>
       </c>
-      <c r="Q270" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="R270" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="S270" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="T270" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="U270" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="V270" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="W270" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="X270" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y270" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Z270" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA270" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB270" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC270" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="AD270" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AE270" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AF270" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AG270" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AH270" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="Q270" t="n">
+        <v>11</v>
+      </c>
+      <c r="R270" t="n">
+        <v>13</v>
+      </c>
+      <c r="S270" t="n">
+        <v>3</v>
+      </c>
+      <c r="T270" t="n">
+        <v>3</v>
+      </c>
+      <c r="U270" t="n">
+        <v>8</v>
+      </c>
+      <c r="V270" t="n">
+        <v>10</v>
+      </c>
+      <c r="W270" t="n">
+        <v>11</v>
+      </c>
+      <c r="X270" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y270" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z270" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA270" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB270" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC270" t="n">
+        <v>24</v>
+      </c>
+      <c r="AD270" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE270" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF270" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG270" t="n">
+        <v>7</v>
+      </c>
+      <c r="AH270" t="n">
+        <v>9</v>
       </c>
       <c r="AI270" t="inlineStr"/>
       <c r="AJ270" t="inlineStr"/>
-      <c r="AK270" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL270" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AM270" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="AN270" t="inlineStr">
-        <is>
-          <t>419</t>
-        </is>
-      </c>
-      <c r="AO270" t="inlineStr">
-        <is>
-          <t>539</t>
-        </is>
-      </c>
-      <c r="AP270" t="inlineStr">
-        <is>
-          <t>360</t>
-        </is>
-      </c>
-      <c r="AQ270" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="AR270" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
+      <c r="AK270" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL270" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM270" t="n">
+        <v>612</v>
+      </c>
+      <c r="AN270" t="n">
+        <v>419</v>
+      </c>
+      <c r="AO270" t="n">
+        <v>539</v>
+      </c>
+      <c r="AP270" t="n">
+        <v>360</v>
+      </c>
+      <c r="AQ270" t="n">
+        <v>116</v>
+      </c>
+      <c r="AR270" t="n">
+        <v>122</v>
       </c>
       <c r="AS270" t="inlineStr">
         <is>
@@ -56004,15 +55704,11 @@
           <t>30 660</t>
         </is>
       </c>
-      <c r="G271" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H271" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G271" t="n">
+        <v>2</v>
+      </c>
+      <c r="H271" t="n">
+        <v>1</v>
       </c>
       <c r="I271" t="inlineStr">
         <is>
@@ -56034,15 +55730,11 @@
           <t>B. Monchengladbach</t>
         </is>
       </c>
-      <c r="M271" t="inlineStr">
-        <is>
-          <t>1.30</t>
-        </is>
-      </c>
-      <c r="N271" t="inlineStr">
-        <is>
-          <t>0.65</t>
-        </is>
+      <c r="M271" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="N271" t="n">
+        <v>0.65</v>
       </c>
       <c r="O271" t="inlineStr">
         <is>
@@ -56054,137 +55746,85 @@
           <t>61%</t>
         </is>
       </c>
-      <c r="Q271" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="R271" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="S271" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="T271" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="U271" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="V271" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="W271" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="X271" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="Y271" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Z271" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA271" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AB271" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC271" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AD271" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="AE271" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AF271" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AG271" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AH271" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
+      <c r="Q271" t="n">
+        <v>14</v>
+      </c>
+      <c r="R271" t="n">
+        <v>11</v>
+      </c>
+      <c r="S271" t="n">
+        <v>5</v>
+      </c>
+      <c r="T271" t="n">
+        <v>5</v>
+      </c>
+      <c r="U271" t="n">
+        <v>9</v>
+      </c>
+      <c r="V271" t="n">
+        <v>6</v>
+      </c>
+      <c r="W271" t="n">
+        <v>18</v>
+      </c>
+      <c r="X271" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y271" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z271" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA271" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB271" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC271" t="n">
+        <v>20</v>
+      </c>
+      <c r="AD271" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE271" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF271" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG271" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH271" t="n">
+        <v>15</v>
       </c>
       <c r="AI271" t="inlineStr"/>
       <c r="AJ271" t="inlineStr"/>
-      <c r="AK271" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL271" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AM271" t="inlineStr">
-        <is>
-          <t>398</t>
-        </is>
-      </c>
-      <c r="AN271" t="inlineStr">
-        <is>
-          <t>735</t>
-        </is>
-      </c>
-      <c r="AO271" t="inlineStr">
-        <is>
-          <t>291</t>
-        </is>
-      </c>
-      <c r="AP271" t="inlineStr">
-        <is>
-          <t>610</t>
-        </is>
-      </c>
-      <c r="AQ271" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="AR271" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
+      <c r="AK271" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL271" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM271" t="n">
+        <v>398</v>
+      </c>
+      <c r="AN271" t="n">
+        <v>735</v>
+      </c>
+      <c r="AO271" t="n">
+        <v>291</v>
+      </c>
+      <c r="AP271" t="n">
+        <v>610</v>
+      </c>
+      <c r="AQ271" t="n">
+        <v>118</v>
+      </c>
+      <c r="AR271" t="n">
+        <v>116</v>
       </c>
       <c r="AS271" t="inlineStr">
         <is>
@@ -56262,15 +55902,11 @@
           <t>9 502</t>
         </is>
       </c>
-      <c r="G272" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H272" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G272" t="n">
+        <v>1</v>
+      </c>
+      <c r="H272" t="n">
+        <v>0</v>
       </c>
       <c r="I272" t="inlineStr">
         <is>
@@ -56292,15 +55928,11 @@
           <t>Kaiserslautern</t>
         </is>
       </c>
-      <c r="M272" t="inlineStr">
-        <is>
-          <t>1.36</t>
-        </is>
-      </c>
-      <c r="N272" t="inlineStr">
-        <is>
-          <t>1.40</t>
-        </is>
+      <c r="M272" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="N272" t="n">
+        <v>1.4</v>
       </c>
       <c r="O272" t="inlineStr">
         <is>
@@ -56312,137 +55944,85 @@
           <t>52%</t>
         </is>
       </c>
-      <c r="Q272" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="R272" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="S272" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="T272" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="U272" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="V272" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="W272" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="X272" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="Y272" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Z272" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA272" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB272" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC272" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AD272" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AE272" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AF272" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AG272" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AH272" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
+      <c r="Q272" t="n">
+        <v>13</v>
+      </c>
+      <c r="R272" t="n">
+        <v>16</v>
+      </c>
+      <c r="S272" t="n">
+        <v>3</v>
+      </c>
+      <c r="T272" t="n">
+        <v>3</v>
+      </c>
+      <c r="U272" t="n">
+        <v>10</v>
+      </c>
+      <c r="V272" t="n">
+        <v>13</v>
+      </c>
+      <c r="W272" t="n">
+        <v>18</v>
+      </c>
+      <c r="X272" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y272" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z272" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA272" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB272" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC272" t="n">
+        <v>19</v>
+      </c>
+      <c r="AD272" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE272" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF272" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG272" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH272" t="n">
+        <v>18</v>
       </c>
       <c r="AI272" t="inlineStr"/>
       <c r="AJ272" t="inlineStr"/>
-      <c r="AK272" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AL272" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AM272" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
-      </c>
-      <c r="AN272" t="inlineStr">
-        <is>
-          <t>394</t>
-        </is>
-      </c>
-      <c r="AO272" t="inlineStr">
-        <is>
-          <t>249</t>
-        </is>
-      </c>
-      <c r="AP272" t="inlineStr">
-        <is>
-          <t>307</t>
-        </is>
-      </c>
-      <c r="AQ272" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="AR272" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
+      <c r="AK272" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL272" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM272" t="n">
+        <v>328</v>
+      </c>
+      <c r="AN272" t="n">
+        <v>394</v>
+      </c>
+      <c r="AO272" t="n">
+        <v>249</v>
+      </c>
+      <c r="AP272" t="n">
+        <v>307</v>
+      </c>
+      <c r="AQ272" t="n">
+        <v>113</v>
+      </c>
+      <c r="AR272" t="n">
+        <v>110</v>
       </c>
       <c r="AS272" t="inlineStr">
         <is>
@@ -56520,15 +56100,11 @@
           <t>49 900</t>
         </is>
       </c>
-      <c r="G273" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H273" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G273" t="n">
+        <v>2</v>
+      </c>
+      <c r="H273" t="n">
+        <v>0</v>
       </c>
       <c r="I273" t="inlineStr">
         <is>
@@ -56550,15 +56126,11 @@
           <t>Ulm</t>
         </is>
       </c>
-      <c r="M273" t="inlineStr">
-        <is>
-          <t>2.27</t>
-        </is>
-      </c>
-      <c r="N273" t="inlineStr">
-        <is>
-          <t>0.11</t>
-        </is>
+      <c r="M273" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="N273" t="n">
+        <v>0.11</v>
       </c>
       <c r="O273" t="inlineStr">
         <is>
@@ -56570,145 +56142,89 @@
           <t>45%</t>
         </is>
       </c>
-      <c r="Q273" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="R273" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="S273" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="T273" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U273" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="V273" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="W273" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="X273" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="Y273" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Z273" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA273" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AB273" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC273" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="AD273" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="AE273" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AF273" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AG273" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AH273" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AI273" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ273" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AK273" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AL273" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AM273" t="inlineStr">
-        <is>
-          <t>545</t>
-        </is>
-      </c>
-      <c r="AN273" t="inlineStr">
-        <is>
-          <t>379</t>
-        </is>
-      </c>
-      <c r="AO273" t="inlineStr">
-        <is>
-          <t>480</t>
-        </is>
-      </c>
-      <c r="AP273" t="inlineStr">
-        <is>
-          <t>303</t>
-        </is>
-      </c>
-      <c r="AQ273" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="AR273" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
+      <c r="Q273" t="n">
+        <v>21</v>
+      </c>
+      <c r="R273" t="n">
+        <v>3</v>
+      </c>
+      <c r="S273" t="n">
+        <v>4</v>
+      </c>
+      <c r="T273" t="n">
+        <v>0</v>
+      </c>
+      <c r="U273" t="n">
+        <v>17</v>
+      </c>
+      <c r="V273" t="n">
+        <v>3</v>
+      </c>
+      <c r="W273" t="n">
+        <v>7</v>
+      </c>
+      <c r="X273" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y273" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z273" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA273" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB273" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC273" t="n">
+        <v>25</v>
+      </c>
+      <c r="AD273" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE273" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF273" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG273" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH273" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI273" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ273" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK273" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL273" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM273" t="n">
+        <v>545</v>
+      </c>
+      <c r="AN273" t="n">
+        <v>379</v>
+      </c>
+      <c r="AO273" t="n">
+        <v>480</v>
+      </c>
+      <c r="AP273" t="n">
+        <v>303</v>
+      </c>
+      <c r="AQ273" t="n">
+        <v>113</v>
+      </c>
+      <c r="AR273" t="n">
+        <v>109</v>
       </c>
       <c r="AS273" t="inlineStr">
         <is>
@@ -56786,15 +56302,11 @@
           <t>27 312</t>
         </is>
       </c>
-      <c r="G274" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H274" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G274" t="n">
+        <v>3</v>
+      </c>
+      <c r="H274" t="n">
+        <v>2</v>
       </c>
       <c r="I274" t="inlineStr">
         <is>
@@ -56816,15 +56328,11 @@
           <t>Preussen Munster</t>
         </is>
       </c>
-      <c r="M274" t="inlineStr">
-        <is>
-          <t>1.45</t>
-        </is>
-      </c>
-      <c r="N274" t="inlineStr">
-        <is>
-          <t>1.42</t>
-        </is>
+      <c r="M274" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="N274" t="n">
+        <v>1.42</v>
       </c>
       <c r="O274" t="inlineStr">
         <is>
@@ -56836,137 +56344,85 @@
           <t>39%</t>
         </is>
       </c>
-      <c r="Q274" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="R274" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="S274" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="T274" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U274" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="V274" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="W274" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="X274" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Y274" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Z274" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA274" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB274" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC274" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="AD274" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AE274" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AF274" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AG274" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AH274" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
+      <c r="Q274" t="n">
+        <v>17</v>
+      </c>
+      <c r="R274" t="n">
+        <v>15</v>
+      </c>
+      <c r="S274" t="n">
+        <v>7</v>
+      </c>
+      <c r="T274" t="n">
+        <v>4</v>
+      </c>
+      <c r="U274" t="n">
+        <v>10</v>
+      </c>
+      <c r="V274" t="n">
+        <v>11</v>
+      </c>
+      <c r="W274" t="n">
+        <v>22</v>
+      </c>
+      <c r="X274" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y274" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z274" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA274" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB274" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC274" t="n">
+        <v>30</v>
+      </c>
+      <c r="AD274" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE274" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF274" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG274" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH274" t="n">
+        <v>19</v>
       </c>
       <c r="AI274" t="inlineStr"/>
       <c r="AJ274" t="inlineStr"/>
-      <c r="AK274" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL274" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AM274" t="inlineStr">
-        <is>
-          <t>415</t>
-        </is>
-      </c>
-      <c r="AN274" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
-      <c r="AO274" t="inlineStr">
-        <is>
-          <t>344</t>
-        </is>
-      </c>
-      <c r="AP274" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
-      </c>
-      <c r="AQ274" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="AR274" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
+      <c r="AK274" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL274" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM274" t="n">
+        <v>415</v>
+      </c>
+      <c r="AN274" t="n">
+        <v>243</v>
+      </c>
+      <c r="AO274" t="n">
+        <v>344</v>
+      </c>
+      <c r="AP274" t="n">
+        <v>182</v>
+      </c>
+      <c r="AQ274" t="n">
+        <v>112</v>
+      </c>
+      <c r="AR274" t="n">
+        <v>111</v>
       </c>
       <c r="AS274" t="inlineStr">
         <is>
@@ -57044,15 +56500,11 @@
           <t>31 034</t>
         </is>
       </c>
-      <c r="G275" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H275" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="G275" t="n">
+        <v>3</v>
+      </c>
+      <c r="H275" t="n">
+        <v>3</v>
       </c>
       <c r="I275" t="inlineStr">
         <is>
@@ -57074,15 +56526,11 @@
           <t>Darmstadt</t>
         </is>
       </c>
-      <c r="M275" t="inlineStr">
-        <is>
-          <t>1.27</t>
-        </is>
-      </c>
-      <c r="N275" t="inlineStr">
-        <is>
-          <t>2.84</t>
-        </is>
+      <c r="M275" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="N275" t="n">
+        <v>2.84</v>
       </c>
       <c r="O275" t="inlineStr">
         <is>
@@ -57094,137 +56542,85 @@
           <t>53%</t>
         </is>
       </c>
-      <c r="Q275" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="R275" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="S275" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="T275" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="U275" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="V275" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="W275" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="X275" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="Y275" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Z275" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA275" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB275" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC275" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="AD275" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="AE275" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AF275" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AG275" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AH275" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="Q275" t="n">
+        <v>13</v>
+      </c>
+      <c r="R275" t="n">
+        <v>18</v>
+      </c>
+      <c r="S275" t="n">
+        <v>5</v>
+      </c>
+      <c r="T275" t="n">
+        <v>9</v>
+      </c>
+      <c r="U275" t="n">
+        <v>8</v>
+      </c>
+      <c r="V275" t="n">
+        <v>9</v>
+      </c>
+      <c r="W275" t="n">
+        <v>8</v>
+      </c>
+      <c r="X275" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y275" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z275" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA275" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB275" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC275" t="n">
+        <v>23</v>
+      </c>
+      <c r="AD275" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE275" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF275" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG275" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH275" t="n">
+        <v>6</v>
       </c>
       <c r="AI275" t="inlineStr"/>
       <c r="AJ275" t="inlineStr"/>
-      <c r="AK275" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AL275" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AM275" t="inlineStr">
-        <is>
-          <t>468</t>
-        </is>
-      </c>
-      <c r="AN275" t="inlineStr">
-        <is>
-          <t>585</t>
-        </is>
-      </c>
-      <c r="AO275" t="inlineStr">
-        <is>
-          <t>389</t>
-        </is>
-      </c>
-      <c r="AP275" t="inlineStr">
-        <is>
-          <t>515</t>
-        </is>
-      </c>
-      <c r="AQ275" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="AR275" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
+      <c r="AK275" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL275" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM275" t="n">
+        <v>468</v>
+      </c>
+      <c r="AN275" t="n">
+        <v>585</v>
+      </c>
+      <c r="AO275" t="n">
+        <v>389</v>
+      </c>
+      <c r="AP275" t="n">
+        <v>515</v>
+      </c>
+      <c r="AQ275" t="n">
+        <v>113</v>
+      </c>
+      <c r="AR275" t="n">
+        <v>115</v>
       </c>
       <c r="AS275" t="inlineStr">
         <is>
@@ -57302,15 +56698,11 @@
           <t>12 615</t>
         </is>
       </c>
-      <c r="G276" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H276" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G276" t="n">
+        <v>3</v>
+      </c>
+      <c r="H276" t="n">
+        <v>0</v>
       </c>
       <c r="I276" t="inlineStr">
         <is>
@@ -57332,15 +56724,11 @@
           <t>Regensburg</t>
         </is>
       </c>
-      <c r="M276" t="inlineStr">
-        <is>
-          <t>2.69</t>
-        </is>
-      </c>
-      <c r="N276" t="inlineStr">
-        <is>
-          <t>0.68</t>
-        </is>
+      <c r="M276" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="N276" t="n">
+        <v>0.68</v>
       </c>
       <c r="O276" t="inlineStr">
         <is>
@@ -57352,129 +56740,81 @@
           <t>32%</t>
         </is>
       </c>
-      <c r="Q276" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="R276" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="S276" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="T276" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="U276" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="V276" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="W276" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="X276" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="Y276" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Z276" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA276" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB276" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC276" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="AD276" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="AE276" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AF276" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AG276" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AH276" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="Q276" t="n">
+        <v>22</v>
+      </c>
+      <c r="R276" t="n">
+        <v>10</v>
+      </c>
+      <c r="S276" t="n">
+        <v>9</v>
+      </c>
+      <c r="T276" t="n">
+        <v>1</v>
+      </c>
+      <c r="U276" t="n">
+        <v>13</v>
+      </c>
+      <c r="V276" t="n">
+        <v>9</v>
+      </c>
+      <c r="W276" t="n">
+        <v>9</v>
+      </c>
+      <c r="X276" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y276" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z276" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA276" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB276" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC276" t="n">
+        <v>34</v>
+      </c>
+      <c r="AD276" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE276" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF276" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG276" t="n">
+        <v>9</v>
+      </c>
+      <c r="AH276" t="n">
+        <v>8</v>
       </c>
       <c r="AI276" t="inlineStr"/>
       <c r="AJ276" t="inlineStr"/>
       <c r="AK276" t="inlineStr"/>
       <c r="AL276" t="inlineStr"/>
-      <c r="AM276" t="inlineStr">
-        <is>
-          <t>724</t>
-        </is>
-      </c>
-      <c r="AN276" t="inlineStr">
-        <is>
-          <t>306</t>
-        </is>
-      </c>
-      <c r="AO276" t="inlineStr">
-        <is>
-          <t>652</t>
-        </is>
-      </c>
-      <c r="AP276" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="AQ276" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="AR276" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
+      <c r="AM276" t="n">
+        <v>724</v>
+      </c>
+      <c r="AN276" t="n">
+        <v>306</v>
+      </c>
+      <c r="AO276" t="n">
+        <v>652</v>
+      </c>
+      <c r="AP276" t="n">
+        <v>230</v>
+      </c>
+      <c r="AQ276" t="n">
+        <v>118</v>
+      </c>
+      <c r="AR276" t="n">
+        <v>116</v>
       </c>
       <c r="AS276" t="inlineStr">
         <is>
@@ -57519,6 +56859,1820 @@
       <c r="BG276" t="inlineStr"/>
       <c r="BH276" t="inlineStr"/>
     </row>
+    <row r="277">
+      <c r="A277" s="1" t="inlineStr">
+        <is>
+          <t>nc8W6DTp</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>06.10.2024 14:30</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>Osmers H.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>MHPArena
+ (Stuttgart)</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>60 449</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>58 000</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="J277" t="inlineStr">
+        <is>
+          <t>Stuttgart</t>
+        </is>
+      </c>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>hQAtP9Sl</t>
+        </is>
+      </c>
+      <c r="L277" t="inlineStr">
+        <is>
+          <t>Hoffenheim</t>
+        </is>
+      </c>
+      <c r="M277" t="inlineStr">
+        <is>
+          <t>3.12</t>
+        </is>
+      </c>
+      <c r="N277" t="inlineStr">
+        <is>
+          <t>0.86</t>
+        </is>
+      </c>
+      <c r="O277" t="inlineStr">
+        <is>
+          <t>62%</t>
+        </is>
+      </c>
+      <c r="P277" t="inlineStr">
+        <is>
+          <t>38%</t>
+        </is>
+      </c>
+      <c r="Q277" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="R277" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="S277" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T277" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U277" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="V277" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W277" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="X277" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Y277" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Z277" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA277" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB277" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC277" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AD277" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AE277" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AF277" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AG277" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AH277" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AI277" t="inlineStr"/>
+      <c r="AJ277" t="inlineStr"/>
+      <c r="AK277" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL277" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AM277" t="inlineStr">
+        <is>
+          <t>712</t>
+        </is>
+      </c>
+      <c r="AN277" t="inlineStr">
+        <is>
+          <t>319</t>
+        </is>
+      </c>
+      <c r="AO277" t="inlineStr">
+        <is>
+          <t>655</t>
+        </is>
+      </c>
+      <c r="AP277" t="inlineStr">
+        <is>
+          <t>296</t>
+        </is>
+      </c>
+      <c r="AQ277" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="AR277" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="AS277" t="inlineStr">
+        <is>
+          <t>GzfvcwRj</t>
+        </is>
+      </c>
+      <c r="AT277" t="inlineStr">
+        <is>
+          <t>hoeness sebastian</t>
+        </is>
+      </c>
+      <c r="AU277" t="inlineStr">
+        <is>
+          <t>KUx4Q7x1</t>
+        </is>
+      </c>
+      <c r="AV277" t="inlineStr">
+        <is>
+          <t>matarazzo pellegrino</t>
+        </is>
+      </c>
+      <c r="AW277" t="n">
+        <v>59</v>
+      </c>
+      <c r="AX277" t="n">
+        <v>591</v>
+      </c>
+      <c r="AY277" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ277" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BA277" t="inlineStr"/>
+      <c r="BB277" t="inlineStr"/>
+      <c r="BC277" t="inlineStr"/>
+      <c r="BD277" t="inlineStr"/>
+      <c r="BE277" t="inlineStr"/>
+      <c r="BF277" t="inlineStr"/>
+      <c r="BG277" t="inlineStr"/>
+      <c r="BH277" t="inlineStr"/>
+    </row>
+    <row r="278">
+      <c r="A278" s="1" t="inlineStr">
+        <is>
+          <t>ShoJUGLi</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>06.10.2024 12:30</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>Brand B.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>Deutsche Bank Park
+ (Frankfurt)</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>58 000</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>58 000</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="J278" t="inlineStr">
+        <is>
+          <t>Eintracht Frankfurt</t>
+        </is>
+      </c>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>nVp0wiqd</t>
+        </is>
+      </c>
+      <c r="L278" t="inlineStr">
+        <is>
+          <t>Bayern Munich</t>
+        </is>
+      </c>
+      <c r="M278" t="inlineStr">
+        <is>
+          <t>0.89</t>
+        </is>
+      </c>
+      <c r="N278" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="O278" t="inlineStr">
+        <is>
+          <t>33%</t>
+        </is>
+      </c>
+      <c r="P278" t="inlineStr">
+        <is>
+          <t>67%</t>
+        </is>
+      </c>
+      <c r="Q278" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R278" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="S278" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T278" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="U278" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V278" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="W278" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="X278" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="Y278" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z278" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AA278" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB278" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC278" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AD278" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AE278" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AF278" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AG278" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AH278" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AI278" t="inlineStr"/>
+      <c r="AJ278" t="inlineStr"/>
+      <c r="AK278" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL278" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM278" t="inlineStr">
+        <is>
+          <t>305</t>
+        </is>
+      </c>
+      <c r="AN278" t="inlineStr">
+        <is>
+          <t>863</t>
+        </is>
+      </c>
+      <c r="AO278" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="AP278" t="inlineStr">
+        <is>
+          <t>768</t>
+        </is>
+      </c>
+      <c r="AQ278" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="AR278" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="AS278" t="inlineStr">
+        <is>
+          <t>UgdQz0fK</t>
+        </is>
+      </c>
+      <c r="AT278" t="inlineStr">
+        <is>
+          <t>toppmoller dino</t>
+        </is>
+      </c>
+      <c r="AU278" t="inlineStr">
+        <is>
+          <t>K6A2elS9</t>
+        </is>
+      </c>
+      <c r="AV278" t="inlineStr">
+        <is>
+          <t>kompany vincent</t>
+        </is>
+      </c>
+      <c r="AW278" t="n">
+        <v>59</v>
+      </c>
+      <c r="AX278" t="n">
+        <v>591</v>
+      </c>
+      <c r="AY278" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ278" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BA278" t="inlineStr"/>
+      <c r="BB278" t="inlineStr"/>
+      <c r="BC278" t="inlineStr"/>
+      <c r="BD278" t="inlineStr"/>
+      <c r="BE278" t="inlineStr"/>
+      <c r="BF278" t="inlineStr"/>
+      <c r="BG278" t="inlineStr"/>
+      <c r="BH278" t="inlineStr"/>
+    </row>
+    <row r="279">
+      <c r="A279" s="1" t="inlineStr">
+        <is>
+          <t>0KbQSfj4</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>06.10.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>Stegemann S.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>Voith-Arena
+ (Heidenheim)</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>KWixEVWi</t>
+        </is>
+      </c>
+      <c r="J279" t="inlineStr">
+        <is>
+          <t>Heidenheim</t>
+        </is>
+      </c>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>KbS1suSm</t>
+        </is>
+      </c>
+      <c r="L279" t="inlineStr">
+        <is>
+          <t>RB Leipzig</t>
+        </is>
+      </c>
+      <c r="M279" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="N279" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="O279" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="P279" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
+      </c>
+      <c r="Q279" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="R279" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="S279" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T279" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U279" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="V279" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="W279" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="X279" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="Y279" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Z279" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA279" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB279" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC279" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AD279" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AE279" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AF279" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AG279" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AH279" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AI279" t="inlineStr"/>
+      <c r="AJ279" t="inlineStr"/>
+      <c r="AK279" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL279" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM279" t="inlineStr">
+        <is>
+          <t>408</t>
+        </is>
+      </c>
+      <c r="AN279" t="inlineStr">
+        <is>
+          <t>491</t>
+        </is>
+      </c>
+      <c r="AO279" t="inlineStr">
+        <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="AP279" t="inlineStr">
+        <is>
+          <t>393</t>
+        </is>
+      </c>
+      <c r="AQ279" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="AR279" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="AS279" t="inlineStr">
+        <is>
+          <t>4ljanukM</t>
+        </is>
+      </c>
+      <c r="AT279" t="inlineStr">
+        <is>
+          <t>schmidt frank</t>
+        </is>
+      </c>
+      <c r="AU279" t="inlineStr">
+        <is>
+          <t>pfoInmcq</t>
+        </is>
+      </c>
+      <c r="AV279" t="inlineStr">
+        <is>
+          <t>rose marko</t>
+        </is>
+      </c>
+      <c r="AW279" t="n">
+        <v>59</v>
+      </c>
+      <c r="AX279" t="n">
+        <v>591</v>
+      </c>
+      <c r="AY279" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ279" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BA279" t="inlineStr"/>
+      <c r="BB279" t="inlineStr"/>
+      <c r="BC279" t="inlineStr"/>
+      <c r="BD279" t="inlineStr"/>
+      <c r="BE279" t="inlineStr"/>
+      <c r="BF279" t="inlineStr"/>
+      <c r="BG279" t="inlineStr"/>
+      <c r="BH279" t="inlineStr"/>
+    </row>
+    <row r="280">
+      <c r="A280" s="1" t="inlineStr">
+        <is>
+          <t>2g2Log1S</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>06.10.2024 08:30</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>Schlager D.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>Eintracht-Stadion
+ (Braunschweig)</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>23 325</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>19 919</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>QqLCC3il</t>
+        </is>
+      </c>
+      <c r="J280" t="inlineStr">
+        <is>
+          <t>Braunschweig</t>
+        </is>
+      </c>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>dfNCCCzS</t>
+        </is>
+      </c>
+      <c r="L280" t="inlineStr">
+        <is>
+          <t>Hannover</t>
+        </is>
+      </c>
+      <c r="M280" t="inlineStr">
+        <is>
+          <t>4.24</t>
+        </is>
+      </c>
+      <c r="N280" t="inlineStr">
+        <is>
+          <t>1.59</t>
+        </is>
+      </c>
+      <c r="O280" t="inlineStr">
+        <is>
+          <t>37%</t>
+        </is>
+      </c>
+      <c r="P280" t="inlineStr">
+        <is>
+          <t>63%</t>
+        </is>
+      </c>
+      <c r="Q280" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="R280" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="S280" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="T280" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U280" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V280" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="W280" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="X280" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="Y280" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Z280" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA280" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB280" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC280" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AD280" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AE280" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AF280" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AG280" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AH280" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AI280" t="inlineStr"/>
+      <c r="AJ280" t="inlineStr"/>
+      <c r="AK280" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL280" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AM280" t="inlineStr">
+        <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="AN280" t="inlineStr">
+        <is>
+          <t>486</t>
+        </is>
+      </c>
+      <c r="AO280" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="AP280" t="inlineStr">
+        <is>
+          <t>379</t>
+        </is>
+      </c>
+      <c r="AQ280" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="AR280" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="AS280" t="inlineStr">
+        <is>
+          <t>SQrxFAMl</t>
+        </is>
+      </c>
+      <c r="AT280" t="inlineStr">
+        <is>
+          <t>scherning daniel</t>
+        </is>
+      </c>
+      <c r="AU280" t="inlineStr">
+        <is>
+          <t>t0ZPdkUl</t>
+        </is>
+      </c>
+      <c r="AV280" t="inlineStr">
+        <is>
+          <t>leitl stefan</t>
+        </is>
+      </c>
+      <c r="AW280" t="n">
+        <v>59</v>
+      </c>
+      <c r="AX280" t="n">
+        <v>592</v>
+      </c>
+      <c r="AY280" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ280" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BA280" t="inlineStr"/>
+      <c r="BB280" t="inlineStr"/>
+      <c r="BC280" t="inlineStr"/>
+      <c r="BD280" t="inlineStr"/>
+      <c r="BE280" t="inlineStr"/>
+      <c r="BF280" t="inlineStr"/>
+      <c r="BG280" t="inlineStr"/>
+      <c r="BH280" t="inlineStr"/>
+    </row>
+    <row r="281">
+      <c r="A281" s="1" t="inlineStr">
+        <is>
+          <t>dEtNxbIc</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>06.10.2024 08:30</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>Petersen M.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>Merkur Spiel-Arena
+ (Düsseldorf)</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>54 600</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>51 500</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>ne1oL3y7</t>
+        </is>
+      </c>
+      <c r="J281" t="inlineStr">
+        <is>
+          <t>Dusseldorf</t>
+        </is>
+      </c>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>v9k3aY5F</t>
+        </is>
+      </c>
+      <c r="L281" t="inlineStr">
+        <is>
+          <t>Hamburger SV</t>
+        </is>
+      </c>
+      <c r="M281" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="N281" t="inlineStr">
+        <is>
+          <t>2.54</t>
+        </is>
+      </c>
+      <c r="O281" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="P281" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="Q281" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="R281" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="S281" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T281" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U281" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="V281" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="W281" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="X281" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y281" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Z281" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA281" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB281" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC281" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AD281" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AE281" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AF281" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AG281" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AH281" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AI281" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AJ281" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK281" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL281" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM281" t="inlineStr">
+        <is>
+          <t>465</t>
+        </is>
+      </c>
+      <c r="AN281" t="inlineStr">
+        <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="AO281" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="AP281" t="inlineStr">
+        <is>
+          <t>460</t>
+        </is>
+      </c>
+      <c r="AQ281" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="AR281" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="AS281" t="inlineStr">
+        <is>
+          <t>AoL97rX8</t>
+        </is>
+      </c>
+      <c r="AT281" t="inlineStr">
+        <is>
+          <t>thioune daniel</t>
+        </is>
+      </c>
+      <c r="AU281" t="inlineStr">
+        <is>
+          <t>EDRZkDzS</t>
+        </is>
+      </c>
+      <c r="AV281" t="inlineStr">
+        <is>
+          <t>baumgart steffen</t>
+        </is>
+      </c>
+      <c r="AW281" t="n">
+        <v>59</v>
+      </c>
+      <c r="AX281" t="n">
+        <v>592</v>
+      </c>
+      <c r="AY281" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ281" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BA281" t="inlineStr"/>
+      <c r="BB281" t="inlineStr"/>
+      <c r="BC281" t="inlineStr"/>
+      <c r="BD281" t="inlineStr"/>
+      <c r="BE281" t="inlineStr"/>
+      <c r="BF281" t="inlineStr"/>
+      <c r="BG281" t="inlineStr"/>
+      <c r="BH281" t="inlineStr"/>
+    </row>
+    <row r="282">
+      <c r="A282" s="1" t="inlineStr">
+        <is>
+          <t>6R8CmFWF</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>06.10.2024 08:30</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>Dankert B.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>Avnet-Arena
+ (Magdeburg)</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>25 910</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>22 615</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>YFuz2RLm</t>
+        </is>
+      </c>
+      <c r="J282" t="inlineStr">
+        <is>
+          <t>Magdeburg</t>
+        </is>
+      </c>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>CCQGbik8</t>
+        </is>
+      </c>
+      <c r="L282" t="inlineStr">
+        <is>
+          <t>Greuther Furth</t>
+        </is>
+      </c>
+      <c r="M282" t="inlineStr">
+        <is>
+          <t>3.64</t>
+        </is>
+      </c>
+      <c r="N282" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="O282" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
+      <c r="P282" t="inlineStr">
+        <is>
+          <t>35%</t>
+        </is>
+      </c>
+      <c r="Q282" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="R282" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="S282" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T282" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U282" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="V282" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="W282" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="X282" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="Y282" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Z282" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA282" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB282" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC282" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AD282" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="AE282" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AF282" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AG282" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AH282" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AI282" t="inlineStr"/>
+      <c r="AJ282" t="inlineStr"/>
+      <c r="AK282" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AL282" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AM282" t="inlineStr">
+        <is>
+          <t>534</t>
+        </is>
+      </c>
+      <c r="AN282" t="inlineStr">
+        <is>
+          <t>331</t>
+        </is>
+      </c>
+      <c r="AO282" t="inlineStr">
+        <is>
+          <t>481</t>
+        </is>
+      </c>
+      <c r="AP282" t="inlineStr">
+        <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="AQ282" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="AR282" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="AS282" t="inlineStr">
+        <is>
+          <t>IgZoGKFn</t>
+        </is>
+      </c>
+      <c r="AT282" t="inlineStr">
+        <is>
+          <t>titz christian</t>
+        </is>
+      </c>
+      <c r="AU282" t="inlineStr">
+        <is>
+          <t>8E86CPuD</t>
+        </is>
+      </c>
+      <c r="AV282" t="inlineStr">
+        <is>
+          <t>zorniger alexander</t>
+        </is>
+      </c>
+      <c r="AW282" t="n">
+        <v>59</v>
+      </c>
+      <c r="AX282" t="n">
+        <v>592</v>
+      </c>
+      <c r="AY282" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ282" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BA282" t="inlineStr"/>
+      <c r="BB282" t="inlineStr"/>
+      <c r="BC282" t="inlineStr"/>
+      <c r="BD282" t="inlineStr"/>
+      <c r="BE282" t="inlineStr"/>
+      <c r="BF282" t="inlineStr"/>
+      <c r="BG282" t="inlineStr"/>
+      <c r="BH282" t="inlineStr"/>
+    </row>
+    <row r="283">
+      <c r="A283" s="1" t="inlineStr">
+        <is>
+          <t>pvFATgup</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>05.10.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>Bauer T.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>Veltins Arena
+ (Gelsenkirchen)</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>62 271</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>61 939</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>0Ija0Ej9</t>
+        </is>
+      </c>
+      <c r="J283" t="inlineStr">
+        <is>
+          <t>Schalke</t>
+        </is>
+      </c>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>2y0u8Wrq</t>
+        </is>
+      </c>
+      <c r="L283" t="inlineStr">
+        <is>
+          <t>Hertha Berlin</t>
+        </is>
+      </c>
+      <c r="M283" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="N283" t="inlineStr">
+        <is>
+          <t>2.23</t>
+        </is>
+      </c>
+      <c r="O283" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="P283" t="inlineStr">
+        <is>
+          <t>46%</t>
+        </is>
+      </c>
+      <c r="Q283" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R283" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="S283" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T283" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U283" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="V283" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="W283" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="X283" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y283" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Z283" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA283" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB283" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC283" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AD283" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AE283" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AF283" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AG283" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AH283" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AI283" t="inlineStr"/>
+      <c r="AJ283" t="inlineStr"/>
+      <c r="AK283" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AL283" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AM283" t="inlineStr">
+        <is>
+          <t>455</t>
+        </is>
+      </c>
+      <c r="AN283" t="inlineStr">
+        <is>
+          <t>354</t>
+        </is>
+      </c>
+      <c r="AO283" t="inlineStr">
+        <is>
+          <t>373</t>
+        </is>
+      </c>
+      <c r="AP283" t="inlineStr">
+        <is>
+          <t>297</t>
+        </is>
+      </c>
+      <c r="AQ283" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="AR283" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="AS283" t="inlineStr">
+        <is>
+          <t>rPmNFwq1</t>
+        </is>
+      </c>
+      <c r="AT283" t="inlineStr">
+        <is>
+          <t>fimpel jakob</t>
+        </is>
+      </c>
+      <c r="AU283" t="inlineStr">
+        <is>
+          <t>YmfcAeCo</t>
+        </is>
+      </c>
+      <c r="AV283" t="inlineStr">
+        <is>
+          <t>fiel cristian</t>
+        </is>
+      </c>
+      <c r="AW283" t="n">
+        <v>59</v>
+      </c>
+      <c r="AX283" t="n">
+        <v>592</v>
+      </c>
+      <c r="AY283" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ283" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BA283" t="inlineStr"/>
+      <c r="BB283" t="inlineStr"/>
+      <c r="BC283" t="inlineStr"/>
+      <c r="BD283" t="inlineStr"/>
+      <c r="BE283" t="inlineStr"/>
+      <c r="BF283" t="inlineStr"/>
+      <c r="BG283" t="inlineStr"/>
+      <c r="BH283" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/germany/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
+++ b/data/germany/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH283"/>
+  <dimension ref="A1:BL295"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -722,6 +722,26 @@
       <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>blocked_shots_away</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>crosses_completed_home</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>crosses_completed_away</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>interceptions_home</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>interceptions_away</t>
         </is>
       </c>
     </row>
@@ -926,6 +946,10 @@
       <c r="BF2" t="inlineStr"/>
       <c r="BG2" t="inlineStr"/>
       <c r="BH2" t="inlineStr"/>
+      <c r="BI2" t="inlineStr"/>
+      <c r="BJ2" t="inlineStr"/>
+      <c r="BK2" t="inlineStr"/>
+      <c r="BL2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -1124,6 +1148,10 @@
       <c r="BF3" t="inlineStr"/>
       <c r="BG3" t="inlineStr"/>
       <c r="BH3" t="inlineStr"/>
+      <c r="BI3" t="inlineStr"/>
+      <c r="BJ3" t="inlineStr"/>
+      <c r="BK3" t="inlineStr"/>
+      <c r="BL3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -1322,6 +1350,10 @@
       <c r="BF4" t="inlineStr"/>
       <c r="BG4" t="inlineStr"/>
       <c r="BH4" t="inlineStr"/>
+      <c r="BI4" t="inlineStr"/>
+      <c r="BJ4" t="inlineStr"/>
+      <c r="BK4" t="inlineStr"/>
+      <c r="BL4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -1520,6 +1552,10 @@
       <c r="BF5" t="inlineStr"/>
       <c r="BG5" t="inlineStr"/>
       <c r="BH5" t="inlineStr"/>
+      <c r="BI5" t="inlineStr"/>
+      <c r="BJ5" t="inlineStr"/>
+      <c r="BK5" t="inlineStr"/>
+      <c r="BL5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -1718,6 +1754,10 @@
       <c r="BF6" t="inlineStr"/>
       <c r="BG6" t="inlineStr"/>
       <c r="BH6" t="inlineStr"/>
+      <c r="BI6" t="inlineStr"/>
+      <c r="BJ6" t="inlineStr"/>
+      <c r="BK6" t="inlineStr"/>
+      <c r="BL6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -1920,6 +1960,10 @@
       <c r="BF7" t="inlineStr"/>
       <c r="BG7" t="inlineStr"/>
       <c r="BH7" t="inlineStr"/>
+      <c r="BI7" t="inlineStr"/>
+      <c r="BJ7" t="inlineStr"/>
+      <c r="BK7" t="inlineStr"/>
+      <c r="BL7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -2118,6 +2162,10 @@
       <c r="BF8" t="inlineStr"/>
       <c r="BG8" t="inlineStr"/>
       <c r="BH8" t="inlineStr"/>
+      <c r="BI8" t="inlineStr"/>
+      <c r="BJ8" t="inlineStr"/>
+      <c r="BK8" t="inlineStr"/>
+      <c r="BL8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -2320,6 +2368,10 @@
       <c r="BF9" t="inlineStr"/>
       <c r="BG9" t="inlineStr"/>
       <c r="BH9" t="inlineStr"/>
+      <c r="BI9" t="inlineStr"/>
+      <c r="BJ9" t="inlineStr"/>
+      <c r="BK9" t="inlineStr"/>
+      <c r="BL9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -2518,6 +2570,10 @@
       <c r="BF10" t="inlineStr"/>
       <c r="BG10" t="inlineStr"/>
       <c r="BH10" t="inlineStr"/>
+      <c r="BI10" t="inlineStr"/>
+      <c r="BJ10" t="inlineStr"/>
+      <c r="BK10" t="inlineStr"/>
+      <c r="BL10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -2712,6 +2768,10 @@
       <c r="BF11" t="inlineStr"/>
       <c r="BG11" t="inlineStr"/>
       <c r="BH11" t="inlineStr"/>
+      <c r="BI11" t="inlineStr"/>
+      <c r="BJ11" t="inlineStr"/>
+      <c r="BK11" t="inlineStr"/>
+      <c r="BL11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -2910,6 +2970,10 @@
       <c r="BF12" t="inlineStr"/>
       <c r="BG12" t="inlineStr"/>
       <c r="BH12" t="inlineStr"/>
+      <c r="BI12" t="inlineStr"/>
+      <c r="BJ12" t="inlineStr"/>
+      <c r="BK12" t="inlineStr"/>
+      <c r="BL12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -3112,6 +3176,10 @@
       <c r="BF13" t="inlineStr"/>
       <c r="BG13" t="inlineStr"/>
       <c r="BH13" t="inlineStr"/>
+      <c r="BI13" t="inlineStr"/>
+      <c r="BJ13" t="inlineStr"/>
+      <c r="BK13" t="inlineStr"/>
+      <c r="BL13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -3310,6 +3378,10 @@
       <c r="BF14" t="inlineStr"/>
       <c r="BG14" t="inlineStr"/>
       <c r="BH14" t="inlineStr"/>
+      <c r="BI14" t="inlineStr"/>
+      <c r="BJ14" t="inlineStr"/>
+      <c r="BK14" t="inlineStr"/>
+      <c r="BL14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -3508,6 +3580,10 @@
       <c r="BF15" t="inlineStr"/>
       <c r="BG15" t="inlineStr"/>
       <c r="BH15" t="inlineStr"/>
+      <c r="BI15" t="inlineStr"/>
+      <c r="BJ15" t="inlineStr"/>
+      <c r="BK15" t="inlineStr"/>
+      <c r="BL15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -3706,6 +3782,10 @@
       <c r="BF16" t="inlineStr"/>
       <c r="BG16" t="inlineStr"/>
       <c r="BH16" t="inlineStr"/>
+      <c r="BI16" t="inlineStr"/>
+      <c r="BJ16" t="inlineStr"/>
+      <c r="BK16" t="inlineStr"/>
+      <c r="BL16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -3904,6 +3984,10 @@
       <c r="BF17" t="inlineStr"/>
       <c r="BG17" t="inlineStr"/>
       <c r="BH17" t="inlineStr"/>
+      <c r="BI17" t="inlineStr"/>
+      <c r="BJ17" t="inlineStr"/>
+      <c r="BK17" t="inlineStr"/>
+      <c r="BL17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
@@ -4102,6 +4186,10 @@
       <c r="BF18" t="inlineStr"/>
       <c r="BG18" t="inlineStr"/>
       <c r="BH18" t="inlineStr"/>
+      <c r="BI18" t="inlineStr"/>
+      <c r="BJ18" t="inlineStr"/>
+      <c r="BK18" t="inlineStr"/>
+      <c r="BL18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
@@ -4304,6 +4392,10 @@
       <c r="BF19" t="inlineStr"/>
       <c r="BG19" t="inlineStr"/>
       <c r="BH19" t="inlineStr"/>
+      <c r="BI19" t="inlineStr"/>
+      <c r="BJ19" t="inlineStr"/>
+      <c r="BK19" t="inlineStr"/>
+      <c r="BL19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
@@ -4518,6 +4610,10 @@
       </c>
       <c r="BG20" t="inlineStr"/>
       <c r="BH20" t="inlineStr"/>
+      <c r="BI20" t="inlineStr"/>
+      <c r="BJ20" t="inlineStr"/>
+      <c r="BK20" t="inlineStr"/>
+      <c r="BL20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
@@ -4728,6 +4824,10 @@
       </c>
       <c r="BG21" t="inlineStr"/>
       <c r="BH21" t="inlineStr"/>
+      <c r="BI21" t="inlineStr"/>
+      <c r="BJ21" t="inlineStr"/>
+      <c r="BK21" t="inlineStr"/>
+      <c r="BL21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -4938,6 +5038,10 @@
       </c>
       <c r="BG22" t="inlineStr"/>
       <c r="BH22" t="inlineStr"/>
+      <c r="BI22" t="inlineStr"/>
+      <c r="BJ22" t="inlineStr"/>
+      <c r="BK22" t="inlineStr"/>
+      <c r="BL22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
@@ -5148,6 +5252,10 @@
       </c>
       <c r="BG23" t="inlineStr"/>
       <c r="BH23" t="inlineStr"/>
+      <c r="BI23" t="inlineStr"/>
+      <c r="BJ23" t="inlineStr"/>
+      <c r="BK23" t="inlineStr"/>
+      <c r="BL23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
@@ -5358,6 +5466,10 @@
       </c>
       <c r="BG24" t="inlineStr"/>
       <c r="BH24" t="inlineStr"/>
+      <c r="BI24" t="inlineStr"/>
+      <c r="BJ24" t="inlineStr"/>
+      <c r="BK24" t="inlineStr"/>
+      <c r="BL24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -5568,6 +5680,10 @@
       </c>
       <c r="BG25" t="inlineStr"/>
       <c r="BH25" t="inlineStr"/>
+      <c r="BI25" t="inlineStr"/>
+      <c r="BJ25" t="inlineStr"/>
+      <c r="BK25" t="inlineStr"/>
+      <c r="BL25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
@@ -5778,6 +5894,10 @@
       </c>
       <c r="BG26" t="inlineStr"/>
       <c r="BH26" t="inlineStr"/>
+      <c r="BI26" t="inlineStr"/>
+      <c r="BJ26" t="inlineStr"/>
+      <c r="BK26" t="inlineStr"/>
+      <c r="BL26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
@@ -5988,6 +6108,10 @@
       </c>
       <c r="BG27" t="inlineStr"/>
       <c r="BH27" t="inlineStr"/>
+      <c r="BI27" t="inlineStr"/>
+      <c r="BJ27" t="inlineStr"/>
+      <c r="BK27" t="inlineStr"/>
+      <c r="BL27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -6198,6 +6322,10 @@
       </c>
       <c r="BG28" t="inlineStr"/>
       <c r="BH28" t="inlineStr"/>
+      <c r="BI28" t="inlineStr"/>
+      <c r="BJ28" t="inlineStr"/>
+      <c r="BK28" t="inlineStr"/>
+      <c r="BL28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
@@ -6404,6 +6532,10 @@
       </c>
       <c r="BG29" t="inlineStr"/>
       <c r="BH29" t="inlineStr"/>
+      <c r="BI29" t="inlineStr"/>
+      <c r="BJ29" t="inlineStr"/>
+      <c r="BK29" t="inlineStr"/>
+      <c r="BL29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
@@ -6610,6 +6742,10 @@
       </c>
       <c r="BG30" t="inlineStr"/>
       <c r="BH30" t="inlineStr"/>
+      <c r="BI30" t="inlineStr"/>
+      <c r="BJ30" t="inlineStr"/>
+      <c r="BK30" t="inlineStr"/>
+      <c r="BL30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
@@ -6816,6 +6952,10 @@
       </c>
       <c r="BG31" t="inlineStr"/>
       <c r="BH31" t="inlineStr"/>
+      <c r="BI31" t="inlineStr"/>
+      <c r="BJ31" t="inlineStr"/>
+      <c r="BK31" t="inlineStr"/>
+      <c r="BL31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
@@ -7022,6 +7162,10 @@
       </c>
       <c r="BG32" t="inlineStr"/>
       <c r="BH32" t="inlineStr"/>
+      <c r="BI32" t="inlineStr"/>
+      <c r="BJ32" t="inlineStr"/>
+      <c r="BK32" t="inlineStr"/>
+      <c r="BL32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
@@ -7228,6 +7372,10 @@
       </c>
       <c r="BG33" t="inlineStr"/>
       <c r="BH33" t="inlineStr"/>
+      <c r="BI33" t="inlineStr"/>
+      <c r="BJ33" t="inlineStr"/>
+      <c r="BK33" t="inlineStr"/>
+      <c r="BL33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
@@ -7434,6 +7582,10 @@
       </c>
       <c r="BG34" t="inlineStr"/>
       <c r="BH34" t="inlineStr"/>
+      <c r="BI34" t="inlineStr"/>
+      <c r="BJ34" t="inlineStr"/>
+      <c r="BK34" t="inlineStr"/>
+      <c r="BL34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
@@ -7640,6 +7792,10 @@
       </c>
       <c r="BG35" t="inlineStr"/>
       <c r="BH35" t="inlineStr"/>
+      <c r="BI35" t="inlineStr"/>
+      <c r="BJ35" t="inlineStr"/>
+      <c r="BK35" t="inlineStr"/>
+      <c r="BL35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
@@ -7850,6 +8006,10 @@
       </c>
       <c r="BG36" t="inlineStr"/>
       <c r="BH36" t="inlineStr"/>
+      <c r="BI36" t="inlineStr"/>
+      <c r="BJ36" t="inlineStr"/>
+      <c r="BK36" t="inlineStr"/>
+      <c r="BL36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
@@ -8056,6 +8216,10 @@
       </c>
       <c r="BG37" t="inlineStr"/>
       <c r="BH37" t="inlineStr"/>
+      <c r="BI37" t="inlineStr"/>
+      <c r="BJ37" t="inlineStr"/>
+      <c r="BK37" t="inlineStr"/>
+      <c r="BL37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
@@ -8262,6 +8426,10 @@
       </c>
       <c r="BG38" t="inlineStr"/>
       <c r="BH38" t="inlineStr"/>
+      <c r="BI38" t="inlineStr"/>
+      <c r="BJ38" t="inlineStr"/>
+      <c r="BK38" t="inlineStr"/>
+      <c r="BL38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
@@ -8468,6 +8636,10 @@
       </c>
       <c r="BG39" t="inlineStr"/>
       <c r="BH39" t="inlineStr"/>
+      <c r="BI39" t="inlineStr"/>
+      <c r="BJ39" t="inlineStr"/>
+      <c r="BK39" t="inlineStr"/>
+      <c r="BL39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
@@ -8674,6 +8846,10 @@
       </c>
       <c r="BG40" t="inlineStr"/>
       <c r="BH40" t="inlineStr"/>
+      <c r="BI40" t="inlineStr"/>
+      <c r="BJ40" t="inlineStr"/>
+      <c r="BK40" t="inlineStr"/>
+      <c r="BL40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
@@ -8880,6 +9056,10 @@
       </c>
       <c r="BG41" t="inlineStr"/>
       <c r="BH41" t="inlineStr"/>
+      <c r="BI41" t="inlineStr"/>
+      <c r="BJ41" t="inlineStr"/>
+      <c r="BK41" t="inlineStr"/>
+      <c r="BL41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
@@ -9086,6 +9266,10 @@
       </c>
       <c r="BG42" t="inlineStr"/>
       <c r="BH42" t="inlineStr"/>
+      <c r="BI42" t="inlineStr"/>
+      <c r="BJ42" t="inlineStr"/>
+      <c r="BK42" t="inlineStr"/>
+      <c r="BL42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
@@ -9296,6 +9480,10 @@
       </c>
       <c r="BG43" t="inlineStr"/>
       <c r="BH43" t="inlineStr"/>
+      <c r="BI43" t="inlineStr"/>
+      <c r="BJ43" t="inlineStr"/>
+      <c r="BK43" t="inlineStr"/>
+      <c r="BL43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
@@ -9502,6 +9690,10 @@
       </c>
       <c r="BG44" t="inlineStr"/>
       <c r="BH44" t="inlineStr"/>
+      <c r="BI44" t="inlineStr"/>
+      <c r="BJ44" t="inlineStr"/>
+      <c r="BK44" t="inlineStr"/>
+      <c r="BL44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
@@ -9712,6 +9904,10 @@
       </c>
       <c r="BG45" t="inlineStr"/>
       <c r="BH45" t="inlineStr"/>
+      <c r="BI45" t="inlineStr"/>
+      <c r="BJ45" t="inlineStr"/>
+      <c r="BK45" t="inlineStr"/>
+      <c r="BL45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
@@ -9918,6 +10114,10 @@
       </c>
       <c r="BG46" t="inlineStr"/>
       <c r="BH46" t="inlineStr"/>
+      <c r="BI46" t="inlineStr"/>
+      <c r="BJ46" t="inlineStr"/>
+      <c r="BK46" t="inlineStr"/>
+      <c r="BL46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
@@ -10125,6 +10325,10 @@
       </c>
       <c r="BG47" t="inlineStr"/>
       <c r="BH47" t="inlineStr"/>
+      <c r="BI47" t="inlineStr"/>
+      <c r="BJ47" t="inlineStr"/>
+      <c r="BK47" t="inlineStr"/>
+      <c r="BL47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
@@ -10331,6 +10535,10 @@
       </c>
       <c r="BG48" t="inlineStr"/>
       <c r="BH48" t="inlineStr"/>
+      <c r="BI48" t="inlineStr"/>
+      <c r="BJ48" t="inlineStr"/>
+      <c r="BK48" t="inlineStr"/>
+      <c r="BL48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
@@ -10537,6 +10745,10 @@
       </c>
       <c r="BG49" t="inlineStr"/>
       <c r="BH49" t="inlineStr"/>
+      <c r="BI49" t="inlineStr"/>
+      <c r="BJ49" t="inlineStr"/>
+      <c r="BK49" t="inlineStr"/>
+      <c r="BL49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
@@ -10743,6 +10955,10 @@
       </c>
       <c r="BG50" t="inlineStr"/>
       <c r="BH50" t="inlineStr"/>
+      <c r="BI50" t="inlineStr"/>
+      <c r="BJ50" t="inlineStr"/>
+      <c r="BK50" t="inlineStr"/>
+      <c r="BL50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
@@ -10949,6 +11165,10 @@
       </c>
       <c r="BG51" t="inlineStr"/>
       <c r="BH51" t="inlineStr"/>
+      <c r="BI51" t="inlineStr"/>
+      <c r="BJ51" t="inlineStr"/>
+      <c r="BK51" t="inlineStr"/>
+      <c r="BL51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
@@ -11155,6 +11375,10 @@
       </c>
       <c r="BG52" t="inlineStr"/>
       <c r="BH52" t="inlineStr"/>
+      <c r="BI52" t="inlineStr"/>
+      <c r="BJ52" t="inlineStr"/>
+      <c r="BK52" t="inlineStr"/>
+      <c r="BL52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
@@ -11361,6 +11585,10 @@
       </c>
       <c r="BG53" t="inlineStr"/>
       <c r="BH53" t="inlineStr"/>
+      <c r="BI53" t="inlineStr"/>
+      <c r="BJ53" t="inlineStr"/>
+      <c r="BK53" t="inlineStr"/>
+      <c r="BL53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
@@ -11567,6 +11795,10 @@
       </c>
       <c r="BG54" t="inlineStr"/>
       <c r="BH54" t="inlineStr"/>
+      <c r="BI54" t="inlineStr"/>
+      <c r="BJ54" t="inlineStr"/>
+      <c r="BK54" t="inlineStr"/>
+      <c r="BL54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
@@ -11773,6 +12005,10 @@
       </c>
       <c r="BG55" t="inlineStr"/>
       <c r="BH55" t="inlineStr"/>
+      <c r="BI55" t="inlineStr"/>
+      <c r="BJ55" t="inlineStr"/>
+      <c r="BK55" t="inlineStr"/>
+      <c r="BL55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
@@ -11979,6 +12215,10 @@
       </c>
       <c r="BG56" t="inlineStr"/>
       <c r="BH56" t="inlineStr"/>
+      <c r="BI56" t="inlineStr"/>
+      <c r="BJ56" t="inlineStr"/>
+      <c r="BK56" t="inlineStr"/>
+      <c r="BL56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
@@ -12185,6 +12425,10 @@
       </c>
       <c r="BG57" t="inlineStr"/>
       <c r="BH57" t="inlineStr"/>
+      <c r="BI57" t="inlineStr"/>
+      <c r="BJ57" t="inlineStr"/>
+      <c r="BK57" t="inlineStr"/>
+      <c r="BL57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
@@ -12395,6 +12639,10 @@
       </c>
       <c r="BG58" t="inlineStr"/>
       <c r="BH58" t="inlineStr"/>
+      <c r="BI58" t="inlineStr"/>
+      <c r="BJ58" t="inlineStr"/>
+      <c r="BK58" t="inlineStr"/>
+      <c r="BL58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
@@ -12601,6 +12849,10 @@
       </c>
       <c r="BG59" t="inlineStr"/>
       <c r="BH59" t="inlineStr"/>
+      <c r="BI59" t="inlineStr"/>
+      <c r="BJ59" t="inlineStr"/>
+      <c r="BK59" t="inlineStr"/>
+      <c r="BL59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
@@ -12807,6 +13059,10 @@
       </c>
       <c r="BG60" t="inlineStr"/>
       <c r="BH60" t="inlineStr"/>
+      <c r="BI60" t="inlineStr"/>
+      <c r="BJ60" t="inlineStr"/>
+      <c r="BK60" t="inlineStr"/>
+      <c r="BL60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
@@ -13013,6 +13269,10 @@
       </c>
       <c r="BG61" t="inlineStr"/>
       <c r="BH61" t="inlineStr"/>
+      <c r="BI61" t="inlineStr"/>
+      <c r="BJ61" t="inlineStr"/>
+      <c r="BK61" t="inlineStr"/>
+      <c r="BL61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
@@ -13219,6 +13479,10 @@
       </c>
       <c r="BG62" t="inlineStr"/>
       <c r="BH62" t="inlineStr"/>
+      <c r="BI62" t="inlineStr"/>
+      <c r="BJ62" t="inlineStr"/>
+      <c r="BK62" t="inlineStr"/>
+      <c r="BL62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
@@ -13425,6 +13689,10 @@
       </c>
       <c r="BG63" t="inlineStr"/>
       <c r="BH63" t="inlineStr"/>
+      <c r="BI63" t="inlineStr"/>
+      <c r="BJ63" t="inlineStr"/>
+      <c r="BK63" t="inlineStr"/>
+      <c r="BL63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
@@ -13631,6 +13899,10 @@
       </c>
       <c r="BG64" t="inlineStr"/>
       <c r="BH64" t="inlineStr"/>
+      <c r="BI64" t="inlineStr"/>
+      <c r="BJ64" t="inlineStr"/>
+      <c r="BK64" t="inlineStr"/>
+      <c r="BL64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
@@ -13837,6 +14109,10 @@
       </c>
       <c r="BG65" t="inlineStr"/>
       <c r="BH65" t="inlineStr"/>
+      <c r="BI65" t="inlineStr"/>
+      <c r="BJ65" t="inlineStr"/>
+      <c r="BK65" t="inlineStr"/>
+      <c r="BL65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
@@ -14043,6 +14319,10 @@
       </c>
       <c r="BG66" t="inlineStr"/>
       <c r="BH66" t="inlineStr"/>
+      <c r="BI66" t="inlineStr"/>
+      <c r="BJ66" t="inlineStr"/>
+      <c r="BK66" t="inlineStr"/>
+      <c r="BL66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
@@ -14249,6 +14529,10 @@
       </c>
       <c r="BG67" t="inlineStr"/>
       <c r="BH67" t="inlineStr"/>
+      <c r="BI67" t="inlineStr"/>
+      <c r="BJ67" t="inlineStr"/>
+      <c r="BK67" t="inlineStr"/>
+      <c r="BL67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
@@ -14451,6 +14735,10 @@
       </c>
       <c r="BG68" t="inlineStr"/>
       <c r="BH68" t="inlineStr"/>
+      <c r="BI68" t="inlineStr"/>
+      <c r="BJ68" t="inlineStr"/>
+      <c r="BK68" t="inlineStr"/>
+      <c r="BL68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
@@ -14657,6 +14945,10 @@
       </c>
       <c r="BG69" t="inlineStr"/>
       <c r="BH69" t="inlineStr"/>
+      <c r="BI69" t="inlineStr"/>
+      <c r="BJ69" t="inlineStr"/>
+      <c r="BK69" t="inlineStr"/>
+      <c r="BL69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
@@ -14863,6 +15155,10 @@
       </c>
       <c r="BG70" t="inlineStr"/>
       <c r="BH70" t="inlineStr"/>
+      <c r="BI70" t="inlineStr"/>
+      <c r="BJ70" t="inlineStr"/>
+      <c r="BK70" t="inlineStr"/>
+      <c r="BL70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
@@ -15069,6 +15365,10 @@
       </c>
       <c r="BG71" t="inlineStr"/>
       <c r="BH71" t="inlineStr"/>
+      <c r="BI71" t="inlineStr"/>
+      <c r="BJ71" t="inlineStr"/>
+      <c r="BK71" t="inlineStr"/>
+      <c r="BL71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
@@ -15275,6 +15575,10 @@
       </c>
       <c r="BG72" t="inlineStr"/>
       <c r="BH72" t="inlineStr"/>
+      <c r="BI72" t="inlineStr"/>
+      <c r="BJ72" t="inlineStr"/>
+      <c r="BK72" t="inlineStr"/>
+      <c r="BL72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
@@ -15477,6 +15781,10 @@
       </c>
       <c r="BG73" t="inlineStr"/>
       <c r="BH73" t="inlineStr"/>
+      <c r="BI73" t="inlineStr"/>
+      <c r="BJ73" t="inlineStr"/>
+      <c r="BK73" t="inlineStr"/>
+      <c r="BL73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
@@ -15683,6 +15991,10 @@
       </c>
       <c r="BG74" t="inlineStr"/>
       <c r="BH74" t="inlineStr"/>
+      <c r="BI74" t="inlineStr"/>
+      <c r="BJ74" t="inlineStr"/>
+      <c r="BK74" t="inlineStr"/>
+      <c r="BL74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
@@ -15893,6 +16205,10 @@
       </c>
       <c r="BG75" t="inlineStr"/>
       <c r="BH75" t="inlineStr"/>
+      <c r="BI75" t="inlineStr"/>
+      <c r="BJ75" t="inlineStr"/>
+      <c r="BK75" t="inlineStr"/>
+      <c r="BL75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
@@ -16099,6 +16415,10 @@
       </c>
       <c r="BG76" t="inlineStr"/>
       <c r="BH76" t="inlineStr"/>
+      <c r="BI76" t="inlineStr"/>
+      <c r="BJ76" t="inlineStr"/>
+      <c r="BK76" t="inlineStr"/>
+      <c r="BL76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
@@ -16309,6 +16629,10 @@
       </c>
       <c r="BG77" t="inlineStr"/>
       <c r="BH77" t="inlineStr"/>
+      <c r="BI77" t="inlineStr"/>
+      <c r="BJ77" t="inlineStr"/>
+      <c r="BK77" t="inlineStr"/>
+      <c r="BL77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
@@ -16515,6 +16839,10 @@
       </c>
       <c r="BG78" t="inlineStr"/>
       <c r="BH78" t="inlineStr"/>
+      <c r="BI78" t="inlineStr"/>
+      <c r="BJ78" t="inlineStr"/>
+      <c r="BK78" t="inlineStr"/>
+      <c r="BL78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
@@ -16721,6 +17049,10 @@
       </c>
       <c r="BG79" t="inlineStr"/>
       <c r="BH79" t="inlineStr"/>
+      <c r="BI79" t="inlineStr"/>
+      <c r="BJ79" t="inlineStr"/>
+      <c r="BK79" t="inlineStr"/>
+      <c r="BL79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
@@ -16927,6 +17259,10 @@
       </c>
       <c r="BG80" t="inlineStr"/>
       <c r="BH80" t="inlineStr"/>
+      <c r="BI80" t="inlineStr"/>
+      <c r="BJ80" t="inlineStr"/>
+      <c r="BK80" t="inlineStr"/>
+      <c r="BL80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
@@ -17133,6 +17469,10 @@
       </c>
       <c r="BG81" t="inlineStr"/>
       <c r="BH81" t="inlineStr"/>
+      <c r="BI81" t="inlineStr"/>
+      <c r="BJ81" t="inlineStr"/>
+      <c r="BK81" t="inlineStr"/>
+      <c r="BL81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
@@ -17343,6 +17683,10 @@
       </c>
       <c r="BG82" t="inlineStr"/>
       <c r="BH82" t="inlineStr"/>
+      <c r="BI82" t="inlineStr"/>
+      <c r="BJ82" t="inlineStr"/>
+      <c r="BK82" t="inlineStr"/>
+      <c r="BL82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
@@ -17549,6 +17893,10 @@
       </c>
       <c r="BG83" t="inlineStr"/>
       <c r="BH83" t="inlineStr"/>
+      <c r="BI83" t="inlineStr"/>
+      <c r="BJ83" t="inlineStr"/>
+      <c r="BK83" t="inlineStr"/>
+      <c r="BL83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
@@ -17755,6 +18103,10 @@
       </c>
       <c r="BG84" t="inlineStr"/>
       <c r="BH84" t="inlineStr"/>
+      <c r="BI84" t="inlineStr"/>
+      <c r="BJ84" t="inlineStr"/>
+      <c r="BK84" t="inlineStr"/>
+      <c r="BL84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
@@ -17961,6 +18313,10 @@
       </c>
       <c r="BG85" t="inlineStr"/>
       <c r="BH85" t="inlineStr"/>
+      <c r="BI85" t="inlineStr"/>
+      <c r="BJ85" t="inlineStr"/>
+      <c r="BK85" t="inlineStr"/>
+      <c r="BL85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
@@ -18167,6 +18523,10 @@
       </c>
       <c r="BG86" t="inlineStr"/>
       <c r="BH86" t="inlineStr"/>
+      <c r="BI86" t="inlineStr"/>
+      <c r="BJ86" t="inlineStr"/>
+      <c r="BK86" t="inlineStr"/>
+      <c r="BL86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
@@ -18373,6 +18733,10 @@
       </c>
       <c r="BG87" t="inlineStr"/>
       <c r="BH87" t="inlineStr"/>
+      <c r="BI87" t="inlineStr"/>
+      <c r="BJ87" t="inlineStr"/>
+      <c r="BK87" t="inlineStr"/>
+      <c r="BL87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
@@ -18575,6 +18939,10 @@
       </c>
       <c r="BG88" t="inlineStr"/>
       <c r="BH88" t="inlineStr"/>
+      <c r="BI88" t="inlineStr"/>
+      <c r="BJ88" t="inlineStr"/>
+      <c r="BK88" t="inlineStr"/>
+      <c r="BL88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
@@ -18781,6 +19149,10 @@
       </c>
       <c r="BG89" t="inlineStr"/>
       <c r="BH89" t="inlineStr"/>
+      <c r="BI89" t="inlineStr"/>
+      <c r="BJ89" t="inlineStr"/>
+      <c r="BK89" t="inlineStr"/>
+      <c r="BL89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
@@ -18987,6 +19359,10 @@
       </c>
       <c r="BG90" t="inlineStr"/>
       <c r="BH90" t="inlineStr"/>
+      <c r="BI90" t="inlineStr"/>
+      <c r="BJ90" t="inlineStr"/>
+      <c r="BK90" t="inlineStr"/>
+      <c r="BL90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
@@ -19193,6 +19569,10 @@
       </c>
       <c r="BG91" t="inlineStr"/>
       <c r="BH91" t="inlineStr"/>
+      <c r="BI91" t="inlineStr"/>
+      <c r="BJ91" t="inlineStr"/>
+      <c r="BK91" t="inlineStr"/>
+      <c r="BL91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
@@ -19399,6 +19779,10 @@
       </c>
       <c r="BG92" t="inlineStr"/>
       <c r="BH92" t="inlineStr"/>
+      <c r="BI92" t="inlineStr"/>
+      <c r="BJ92" t="inlineStr"/>
+      <c r="BK92" t="inlineStr"/>
+      <c r="BL92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
@@ -19605,6 +19989,10 @@
       </c>
       <c r="BG93" t="inlineStr"/>
       <c r="BH93" t="inlineStr"/>
+      <c r="BI93" t="inlineStr"/>
+      <c r="BJ93" t="inlineStr"/>
+      <c r="BK93" t="inlineStr"/>
+      <c r="BL93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
@@ -19811,6 +20199,10 @@
       </c>
       <c r="BG94" t="inlineStr"/>
       <c r="BH94" t="inlineStr"/>
+      <c r="BI94" t="inlineStr"/>
+      <c r="BJ94" t="inlineStr"/>
+      <c r="BK94" t="inlineStr"/>
+      <c r="BL94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
@@ -20017,6 +20409,10 @@
       </c>
       <c r="BG95" t="inlineStr"/>
       <c r="BH95" t="inlineStr"/>
+      <c r="BI95" t="inlineStr"/>
+      <c r="BJ95" t="inlineStr"/>
+      <c r="BK95" t="inlineStr"/>
+      <c r="BL95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
@@ -20223,6 +20619,10 @@
       </c>
       <c r="BG96" t="inlineStr"/>
       <c r="BH96" t="inlineStr"/>
+      <c r="BI96" t="inlineStr"/>
+      <c r="BJ96" t="inlineStr"/>
+      <c r="BK96" t="inlineStr"/>
+      <c r="BL96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
@@ -20433,6 +20833,10 @@
       </c>
       <c r="BG97" t="inlineStr"/>
       <c r="BH97" t="inlineStr"/>
+      <c r="BI97" t="inlineStr"/>
+      <c r="BJ97" t="inlineStr"/>
+      <c r="BK97" t="inlineStr"/>
+      <c r="BL97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
@@ -20639,6 +21043,10 @@
       </c>
       <c r="BG98" t="inlineStr"/>
       <c r="BH98" t="inlineStr"/>
+      <c r="BI98" t="inlineStr"/>
+      <c r="BJ98" t="inlineStr"/>
+      <c r="BK98" t="inlineStr"/>
+      <c r="BL98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
@@ -20845,6 +21253,10 @@
       </c>
       <c r="BG99" t="inlineStr"/>
       <c r="BH99" t="inlineStr"/>
+      <c r="BI99" t="inlineStr"/>
+      <c r="BJ99" t="inlineStr"/>
+      <c r="BK99" t="inlineStr"/>
+      <c r="BL99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
@@ -21051,6 +21463,10 @@
       </c>
       <c r="BG100" t="inlineStr"/>
       <c r="BH100" t="inlineStr"/>
+      <c r="BI100" t="inlineStr"/>
+      <c r="BJ100" t="inlineStr"/>
+      <c r="BK100" t="inlineStr"/>
+      <c r="BL100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
@@ -21257,6 +21673,10 @@
       </c>
       <c r="BG101" t="inlineStr"/>
       <c r="BH101" t="inlineStr"/>
+      <c r="BI101" t="inlineStr"/>
+      <c r="BJ101" t="inlineStr"/>
+      <c r="BK101" t="inlineStr"/>
+      <c r="BL101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
@@ -21463,6 +21883,10 @@
       </c>
       <c r="BG102" t="inlineStr"/>
       <c r="BH102" t="inlineStr"/>
+      <c r="BI102" t="inlineStr"/>
+      <c r="BJ102" t="inlineStr"/>
+      <c r="BK102" t="inlineStr"/>
+      <c r="BL102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
@@ -21669,6 +22093,10 @@
       </c>
       <c r="BG103" t="inlineStr"/>
       <c r="BH103" t="inlineStr"/>
+      <c r="BI103" t="inlineStr"/>
+      <c r="BJ103" t="inlineStr"/>
+      <c r="BK103" t="inlineStr"/>
+      <c r="BL103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
@@ -21875,6 +22303,10 @@
       </c>
       <c r="BG104" t="inlineStr"/>
       <c r="BH104" t="inlineStr"/>
+      <c r="BI104" t="inlineStr"/>
+      <c r="BJ104" t="inlineStr"/>
+      <c r="BK104" t="inlineStr"/>
+      <c r="BL104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
@@ -22081,6 +22513,10 @@
       </c>
       <c r="BG105" t="inlineStr"/>
       <c r="BH105" t="inlineStr"/>
+      <c r="BI105" t="inlineStr"/>
+      <c r="BJ105" t="inlineStr"/>
+      <c r="BK105" t="inlineStr"/>
+      <c r="BL105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
@@ -22287,6 +22723,10 @@
       </c>
       <c r="BG106" t="inlineStr"/>
       <c r="BH106" t="inlineStr"/>
+      <c r="BI106" t="inlineStr"/>
+      <c r="BJ106" t="inlineStr"/>
+      <c r="BK106" t="inlineStr"/>
+      <c r="BL106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
@@ -22493,6 +22933,10 @@
       </c>
       <c r="BG107" t="inlineStr"/>
       <c r="BH107" t="inlineStr"/>
+      <c r="BI107" t="inlineStr"/>
+      <c r="BJ107" t="inlineStr"/>
+      <c r="BK107" t="inlineStr"/>
+      <c r="BL107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
@@ -22699,6 +23143,10 @@
       </c>
       <c r="BG108" t="inlineStr"/>
       <c r="BH108" t="inlineStr"/>
+      <c r="BI108" t="inlineStr"/>
+      <c r="BJ108" t="inlineStr"/>
+      <c r="BK108" t="inlineStr"/>
+      <c r="BL108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
@@ -22905,6 +23353,10 @@
       </c>
       <c r="BG109" t="inlineStr"/>
       <c r="BH109" t="inlineStr"/>
+      <c r="BI109" t="inlineStr"/>
+      <c r="BJ109" t="inlineStr"/>
+      <c r="BK109" t="inlineStr"/>
+      <c r="BL109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
@@ -23115,6 +23567,10 @@
       </c>
       <c r="BG110" t="inlineStr"/>
       <c r="BH110" t="inlineStr"/>
+      <c r="BI110" t="inlineStr"/>
+      <c r="BJ110" t="inlineStr"/>
+      <c r="BK110" t="inlineStr"/>
+      <c r="BL110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
@@ -23325,6 +23781,10 @@
       </c>
       <c r="BG111" t="inlineStr"/>
       <c r="BH111" t="inlineStr"/>
+      <c r="BI111" t="inlineStr"/>
+      <c r="BJ111" t="inlineStr"/>
+      <c r="BK111" t="inlineStr"/>
+      <c r="BL111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
@@ -23531,6 +23991,10 @@
       </c>
       <c r="BG112" t="inlineStr"/>
       <c r="BH112" t="inlineStr"/>
+      <c r="BI112" t="inlineStr"/>
+      <c r="BJ112" t="inlineStr"/>
+      <c r="BK112" t="inlineStr"/>
+      <c r="BL112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
@@ -23741,6 +24205,10 @@
       </c>
       <c r="BG113" t="inlineStr"/>
       <c r="BH113" t="inlineStr"/>
+      <c r="BI113" t="inlineStr"/>
+      <c r="BJ113" t="inlineStr"/>
+      <c r="BK113" t="inlineStr"/>
+      <c r="BL113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
@@ -23947,6 +24415,10 @@
       </c>
       <c r="BG114" t="inlineStr"/>
       <c r="BH114" t="inlineStr"/>
+      <c r="BI114" t="inlineStr"/>
+      <c r="BJ114" t="inlineStr"/>
+      <c r="BK114" t="inlineStr"/>
+      <c r="BL114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
@@ -24149,6 +24621,10 @@
       </c>
       <c r="BG115" t="inlineStr"/>
       <c r="BH115" t="inlineStr"/>
+      <c r="BI115" t="inlineStr"/>
+      <c r="BJ115" t="inlineStr"/>
+      <c r="BK115" t="inlineStr"/>
+      <c r="BL115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
@@ -24355,6 +24831,10 @@
       </c>
       <c r="BG116" t="inlineStr"/>
       <c r="BH116" t="inlineStr"/>
+      <c r="BI116" t="inlineStr"/>
+      <c r="BJ116" t="inlineStr"/>
+      <c r="BK116" t="inlineStr"/>
+      <c r="BL116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
@@ -24561,6 +25041,10 @@
       </c>
       <c r="BG117" t="inlineStr"/>
       <c r="BH117" t="inlineStr"/>
+      <c r="BI117" t="inlineStr"/>
+      <c r="BJ117" t="inlineStr"/>
+      <c r="BK117" t="inlineStr"/>
+      <c r="BL117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
@@ -24767,6 +25251,10 @@
       </c>
       <c r="BG118" t="inlineStr"/>
       <c r="BH118" t="inlineStr"/>
+      <c r="BI118" t="inlineStr"/>
+      <c r="BJ118" t="inlineStr"/>
+      <c r="BK118" t="inlineStr"/>
+      <c r="BL118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
@@ -24973,6 +25461,10 @@
       </c>
       <c r="BG119" t="inlineStr"/>
       <c r="BH119" t="inlineStr"/>
+      <c r="BI119" t="inlineStr"/>
+      <c r="BJ119" t="inlineStr"/>
+      <c r="BK119" t="inlineStr"/>
+      <c r="BL119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
@@ -25183,6 +25675,10 @@
       </c>
       <c r="BG120" t="inlineStr"/>
       <c r="BH120" t="inlineStr"/>
+      <c r="BI120" t="inlineStr"/>
+      <c r="BJ120" t="inlineStr"/>
+      <c r="BK120" t="inlineStr"/>
+      <c r="BL120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
@@ -25389,6 +25885,10 @@
       </c>
       <c r="BG121" t="inlineStr"/>
       <c r="BH121" t="inlineStr"/>
+      <c r="BI121" t="inlineStr"/>
+      <c r="BJ121" t="inlineStr"/>
+      <c r="BK121" t="inlineStr"/>
+      <c r="BL121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
@@ -25595,6 +26095,10 @@
       </c>
       <c r="BG122" t="inlineStr"/>
       <c r="BH122" t="inlineStr"/>
+      <c r="BI122" t="inlineStr"/>
+      <c r="BJ122" t="inlineStr"/>
+      <c r="BK122" t="inlineStr"/>
+      <c r="BL122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
@@ -25801,6 +26305,10 @@
       </c>
       <c r="BG123" t="inlineStr"/>
       <c r="BH123" t="inlineStr"/>
+      <c r="BI123" t="inlineStr"/>
+      <c r="BJ123" t="inlineStr"/>
+      <c r="BK123" t="inlineStr"/>
+      <c r="BL123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
@@ -26007,6 +26515,10 @@
       </c>
       <c r="BG124" t="inlineStr"/>
       <c r="BH124" t="inlineStr"/>
+      <c r="BI124" t="inlineStr"/>
+      <c r="BJ124" t="inlineStr"/>
+      <c r="BK124" t="inlineStr"/>
+      <c r="BL124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
@@ -26213,6 +26725,10 @@
       </c>
       <c r="BG125" t="inlineStr"/>
       <c r="BH125" t="inlineStr"/>
+      <c r="BI125" t="inlineStr"/>
+      <c r="BJ125" t="inlineStr"/>
+      <c r="BK125" t="inlineStr"/>
+      <c r="BL125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
@@ -26419,6 +26935,10 @@
       </c>
       <c r="BG126" t="inlineStr"/>
       <c r="BH126" t="inlineStr"/>
+      <c r="BI126" t="inlineStr"/>
+      <c r="BJ126" t="inlineStr"/>
+      <c r="BK126" t="inlineStr"/>
+      <c r="BL126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
@@ -26625,6 +27145,10 @@
       </c>
       <c r="BG127" t="inlineStr"/>
       <c r="BH127" t="inlineStr"/>
+      <c r="BI127" t="inlineStr"/>
+      <c r="BJ127" t="inlineStr"/>
+      <c r="BK127" t="inlineStr"/>
+      <c r="BL127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
@@ -26835,6 +27359,10 @@
       </c>
       <c r="BG128" t="inlineStr"/>
       <c r="BH128" t="inlineStr"/>
+      <c r="BI128" t="inlineStr"/>
+      <c r="BJ128" t="inlineStr"/>
+      <c r="BK128" t="inlineStr"/>
+      <c r="BL128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
@@ -27037,6 +27565,10 @@
       </c>
       <c r="BG129" t="inlineStr"/>
       <c r="BH129" t="inlineStr"/>
+      <c r="BI129" t="inlineStr"/>
+      <c r="BJ129" t="inlineStr"/>
+      <c r="BK129" t="inlineStr"/>
+      <c r="BL129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
@@ -27247,6 +27779,10 @@
       </c>
       <c r="BG130" t="inlineStr"/>
       <c r="BH130" t="inlineStr"/>
+      <c r="BI130" t="inlineStr"/>
+      <c r="BJ130" t="inlineStr"/>
+      <c r="BK130" t="inlineStr"/>
+      <c r="BL130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
@@ -27457,6 +27993,10 @@
       </c>
       <c r="BG131" t="inlineStr"/>
       <c r="BH131" t="inlineStr"/>
+      <c r="BI131" t="inlineStr"/>
+      <c r="BJ131" t="inlineStr"/>
+      <c r="BK131" t="inlineStr"/>
+      <c r="BL131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
@@ -27663,6 +28203,10 @@
       </c>
       <c r="BG132" t="inlineStr"/>
       <c r="BH132" t="inlineStr"/>
+      <c r="BI132" t="inlineStr"/>
+      <c r="BJ132" t="inlineStr"/>
+      <c r="BK132" t="inlineStr"/>
+      <c r="BL132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
@@ -27873,6 +28417,10 @@
       </c>
       <c r="BG133" t="inlineStr"/>
       <c r="BH133" t="inlineStr"/>
+      <c r="BI133" t="inlineStr"/>
+      <c r="BJ133" t="inlineStr"/>
+      <c r="BK133" t="inlineStr"/>
+      <c r="BL133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
@@ -28079,6 +28627,10 @@
       </c>
       <c r="BG134" t="inlineStr"/>
       <c r="BH134" t="inlineStr"/>
+      <c r="BI134" t="inlineStr"/>
+      <c r="BJ134" t="inlineStr"/>
+      <c r="BK134" t="inlineStr"/>
+      <c r="BL134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
@@ -28285,6 +28837,10 @@
       </c>
       <c r="BG135" t="inlineStr"/>
       <c r="BH135" t="inlineStr"/>
+      <c r="BI135" t="inlineStr"/>
+      <c r="BJ135" t="inlineStr"/>
+      <c r="BK135" t="inlineStr"/>
+      <c r="BL135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
@@ -28491,6 +29047,10 @@
       </c>
       <c r="BG136" t="inlineStr"/>
       <c r="BH136" t="inlineStr"/>
+      <c r="BI136" t="inlineStr"/>
+      <c r="BJ136" t="inlineStr"/>
+      <c r="BK136" t="inlineStr"/>
+      <c r="BL136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
@@ -28697,6 +29257,10 @@
       </c>
       <c r="BG137" t="inlineStr"/>
       <c r="BH137" t="inlineStr"/>
+      <c r="BI137" t="inlineStr"/>
+      <c r="BJ137" t="inlineStr"/>
+      <c r="BK137" t="inlineStr"/>
+      <c r="BL137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
@@ -28907,6 +29471,10 @@
       </c>
       <c r="BG138" t="inlineStr"/>
       <c r="BH138" t="inlineStr"/>
+      <c r="BI138" t="inlineStr"/>
+      <c r="BJ138" t="inlineStr"/>
+      <c r="BK138" t="inlineStr"/>
+      <c r="BL138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
@@ -29117,6 +29685,10 @@
       </c>
       <c r="BG139" t="inlineStr"/>
       <c r="BH139" t="inlineStr"/>
+      <c r="BI139" t="inlineStr"/>
+      <c r="BJ139" t="inlineStr"/>
+      <c r="BK139" t="inlineStr"/>
+      <c r="BL139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
@@ -29327,6 +29899,10 @@
       </c>
       <c r="BG140" t="inlineStr"/>
       <c r="BH140" t="inlineStr"/>
+      <c r="BI140" t="inlineStr"/>
+      <c r="BJ140" t="inlineStr"/>
+      <c r="BK140" t="inlineStr"/>
+      <c r="BL140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
@@ -29533,6 +30109,10 @@
       </c>
       <c r="BG141" t="inlineStr"/>
       <c r="BH141" t="inlineStr"/>
+      <c r="BI141" t="inlineStr"/>
+      <c r="BJ141" t="inlineStr"/>
+      <c r="BK141" t="inlineStr"/>
+      <c r="BL141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
@@ -29743,6 +30323,10 @@
       </c>
       <c r="BG142" t="inlineStr"/>
       <c r="BH142" t="inlineStr"/>
+      <c r="BI142" t="inlineStr"/>
+      <c r="BJ142" t="inlineStr"/>
+      <c r="BK142" t="inlineStr"/>
+      <c r="BL142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
@@ -29949,6 +30533,10 @@
       </c>
       <c r="BG143" t="inlineStr"/>
       <c r="BH143" t="inlineStr"/>
+      <c r="BI143" t="inlineStr"/>
+      <c r="BJ143" t="inlineStr"/>
+      <c r="BK143" t="inlineStr"/>
+      <c r="BL143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
@@ -30155,6 +30743,10 @@
       </c>
       <c r="BG144" t="inlineStr"/>
       <c r="BH144" t="inlineStr"/>
+      <c r="BI144" t="inlineStr"/>
+      <c r="BJ144" t="inlineStr"/>
+      <c r="BK144" t="inlineStr"/>
+      <c r="BL144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
@@ -30365,6 +30957,10 @@
       </c>
       <c r="BG145" t="inlineStr"/>
       <c r="BH145" t="inlineStr"/>
+      <c r="BI145" t="inlineStr"/>
+      <c r="BJ145" t="inlineStr"/>
+      <c r="BK145" t="inlineStr"/>
+      <c r="BL145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
@@ -30571,6 +31167,10 @@
       </c>
       <c r="BG146" t="inlineStr"/>
       <c r="BH146" t="inlineStr"/>
+      <c r="BI146" t="inlineStr"/>
+      <c r="BJ146" t="inlineStr"/>
+      <c r="BK146" t="inlineStr"/>
+      <c r="BL146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
@@ -30777,6 +31377,10 @@
       </c>
       <c r="BG147" t="inlineStr"/>
       <c r="BH147" t="inlineStr"/>
+      <c r="BI147" t="inlineStr"/>
+      <c r="BJ147" t="inlineStr"/>
+      <c r="BK147" t="inlineStr"/>
+      <c r="BL147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
@@ -30975,6 +31579,10 @@
       <c r="BF148" t="inlineStr"/>
       <c r="BG148" t="inlineStr"/>
       <c r="BH148" t="inlineStr"/>
+      <c r="BI148" t="inlineStr"/>
+      <c r="BJ148" t="inlineStr"/>
+      <c r="BK148" t="inlineStr"/>
+      <c r="BL148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
@@ -31173,6 +31781,10 @@
       <c r="BF149" t="inlineStr"/>
       <c r="BG149" t="inlineStr"/>
       <c r="BH149" t="inlineStr"/>
+      <c r="BI149" t="inlineStr"/>
+      <c r="BJ149" t="inlineStr"/>
+      <c r="BK149" t="inlineStr"/>
+      <c r="BL149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
@@ -31371,6 +31983,10 @@
       <c r="BF150" t="inlineStr"/>
       <c r="BG150" t="inlineStr"/>
       <c r="BH150" t="inlineStr"/>
+      <c r="BI150" t="inlineStr"/>
+      <c r="BJ150" t="inlineStr"/>
+      <c r="BK150" t="inlineStr"/>
+      <c r="BL150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
@@ -31569,6 +32185,10 @@
       <c r="BF151" t="inlineStr"/>
       <c r="BG151" t="inlineStr"/>
       <c r="BH151" t="inlineStr"/>
+      <c r="BI151" t="inlineStr"/>
+      <c r="BJ151" t="inlineStr"/>
+      <c r="BK151" t="inlineStr"/>
+      <c r="BL151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
@@ -31771,6 +32391,10 @@
       <c r="BF152" t="inlineStr"/>
       <c r="BG152" t="inlineStr"/>
       <c r="BH152" t="inlineStr"/>
+      <c r="BI152" t="inlineStr"/>
+      <c r="BJ152" t="inlineStr"/>
+      <c r="BK152" t="inlineStr"/>
+      <c r="BL152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
@@ -31969,6 +32593,10 @@
       <c r="BF153" t="inlineStr"/>
       <c r="BG153" t="inlineStr"/>
       <c r="BH153" t="inlineStr"/>
+      <c r="BI153" t="inlineStr"/>
+      <c r="BJ153" t="inlineStr"/>
+      <c r="BK153" t="inlineStr"/>
+      <c r="BL153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
@@ -32167,6 +32795,10 @@
       <c r="BF154" t="inlineStr"/>
       <c r="BG154" t="inlineStr"/>
       <c r="BH154" t="inlineStr"/>
+      <c r="BI154" t="inlineStr"/>
+      <c r="BJ154" t="inlineStr"/>
+      <c r="BK154" t="inlineStr"/>
+      <c r="BL154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
@@ -32365,6 +32997,10 @@
       <c r="BF155" t="inlineStr"/>
       <c r="BG155" t="inlineStr"/>
       <c r="BH155" t="inlineStr"/>
+      <c r="BI155" t="inlineStr"/>
+      <c r="BJ155" t="inlineStr"/>
+      <c r="BK155" t="inlineStr"/>
+      <c r="BL155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
@@ -32567,6 +33203,10 @@
       <c r="BF156" t="inlineStr"/>
       <c r="BG156" t="inlineStr"/>
       <c r="BH156" t="inlineStr"/>
+      <c r="BI156" t="inlineStr"/>
+      <c r="BJ156" t="inlineStr"/>
+      <c r="BK156" t="inlineStr"/>
+      <c r="BL156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" s="1" t="inlineStr">
@@ -32773,6 +33413,10 @@
       </c>
       <c r="BG157" t="inlineStr"/>
       <c r="BH157" t="inlineStr"/>
+      <c r="BI157" t="inlineStr"/>
+      <c r="BJ157" t="inlineStr"/>
+      <c r="BK157" t="inlineStr"/>
+      <c r="BL157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" s="1" t="inlineStr">
@@ -32979,6 +33623,10 @@
       </c>
       <c r="BG158" t="inlineStr"/>
       <c r="BH158" t="inlineStr"/>
+      <c r="BI158" t="inlineStr"/>
+      <c r="BJ158" t="inlineStr"/>
+      <c r="BK158" t="inlineStr"/>
+      <c r="BL158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" s="1" t="inlineStr">
@@ -33185,6 +33833,10 @@
       </c>
       <c r="BG159" t="inlineStr"/>
       <c r="BH159" t="inlineStr"/>
+      <c r="BI159" t="inlineStr"/>
+      <c r="BJ159" t="inlineStr"/>
+      <c r="BK159" t="inlineStr"/>
+      <c r="BL159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" s="1" t="inlineStr">
@@ -33391,6 +34043,10 @@
       </c>
       <c r="BG160" t="inlineStr"/>
       <c r="BH160" t="inlineStr"/>
+      <c r="BI160" t="inlineStr"/>
+      <c r="BJ160" t="inlineStr"/>
+      <c r="BK160" t="inlineStr"/>
+      <c r="BL160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" s="1" t="inlineStr">
@@ -33597,6 +34253,10 @@
       </c>
       <c r="BG161" t="inlineStr"/>
       <c r="BH161" t="inlineStr"/>
+      <c r="BI161" t="inlineStr"/>
+      <c r="BJ161" t="inlineStr"/>
+      <c r="BK161" t="inlineStr"/>
+      <c r="BL161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" s="1" t="inlineStr">
@@ -33803,6 +34463,10 @@
       </c>
       <c r="BG162" t="inlineStr"/>
       <c r="BH162" t="inlineStr"/>
+      <c r="BI162" t="inlineStr"/>
+      <c r="BJ162" t="inlineStr"/>
+      <c r="BK162" t="inlineStr"/>
+      <c r="BL162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" s="1" t="inlineStr">
@@ -34009,6 +34673,10 @@
       </c>
       <c r="BG163" t="inlineStr"/>
       <c r="BH163" t="inlineStr"/>
+      <c r="BI163" t="inlineStr"/>
+      <c r="BJ163" t="inlineStr"/>
+      <c r="BK163" t="inlineStr"/>
+      <c r="BL163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" s="1" t="inlineStr">
@@ -34215,6 +34883,10 @@
       </c>
       <c r="BG164" t="inlineStr"/>
       <c r="BH164" t="inlineStr"/>
+      <c r="BI164" t="inlineStr"/>
+      <c r="BJ164" t="inlineStr"/>
+      <c r="BK164" t="inlineStr"/>
+      <c r="BL164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" s="1" t="inlineStr">
@@ -34417,6 +35089,10 @@
       </c>
       <c r="BG165" t="inlineStr"/>
       <c r="BH165" t="inlineStr"/>
+      <c r="BI165" t="inlineStr"/>
+      <c r="BJ165" t="inlineStr"/>
+      <c r="BK165" t="inlineStr"/>
+      <c r="BL165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" s="1" t="inlineStr">
@@ -34623,6 +35299,10 @@
       </c>
       <c r="BG166" t="inlineStr"/>
       <c r="BH166" t="inlineStr"/>
+      <c r="BI166" t="inlineStr"/>
+      <c r="BJ166" t="inlineStr"/>
+      <c r="BK166" t="inlineStr"/>
+      <c r="BL166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" s="1" t="inlineStr">
@@ -34829,6 +35509,10 @@
       </c>
       <c r="BG167" t="inlineStr"/>
       <c r="BH167" t="inlineStr"/>
+      <c r="BI167" t="inlineStr"/>
+      <c r="BJ167" t="inlineStr"/>
+      <c r="BK167" t="inlineStr"/>
+      <c r="BL167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" s="1" t="inlineStr">
@@ -35035,6 +35719,10 @@
       </c>
       <c r="BG168" t="inlineStr"/>
       <c r="BH168" t="inlineStr"/>
+      <c r="BI168" t="inlineStr"/>
+      <c r="BJ168" t="inlineStr"/>
+      <c r="BK168" t="inlineStr"/>
+      <c r="BL168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" s="1" t="inlineStr">
@@ -35241,6 +35929,10 @@
       </c>
       <c r="BG169" t="inlineStr"/>
       <c r="BH169" t="inlineStr"/>
+      <c r="BI169" t="inlineStr"/>
+      <c r="BJ169" t="inlineStr"/>
+      <c r="BK169" t="inlineStr"/>
+      <c r="BL169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" s="1" t="inlineStr">
@@ -35447,6 +36139,10 @@
       </c>
       <c r="BG170" t="inlineStr"/>
       <c r="BH170" t="inlineStr"/>
+      <c r="BI170" t="inlineStr"/>
+      <c r="BJ170" t="inlineStr"/>
+      <c r="BK170" t="inlineStr"/>
+      <c r="BL170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" s="1" t="inlineStr">
@@ -35653,6 +36349,10 @@
       </c>
       <c r="BG171" t="inlineStr"/>
       <c r="BH171" t="inlineStr"/>
+      <c r="BI171" t="inlineStr"/>
+      <c r="BJ171" t="inlineStr"/>
+      <c r="BK171" t="inlineStr"/>
+      <c r="BL171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" s="1" t="inlineStr">
@@ -35863,6 +36563,10 @@
       </c>
       <c r="BG172" t="inlineStr"/>
       <c r="BH172" t="inlineStr"/>
+      <c r="BI172" t="inlineStr"/>
+      <c r="BJ172" t="inlineStr"/>
+      <c r="BK172" t="inlineStr"/>
+      <c r="BL172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" s="1" t="inlineStr">
@@ -36069,6 +36773,10 @@
       </c>
       <c r="BG173" t="inlineStr"/>
       <c r="BH173" t="inlineStr"/>
+      <c r="BI173" t="inlineStr"/>
+      <c r="BJ173" t="inlineStr"/>
+      <c r="BK173" t="inlineStr"/>
+      <c r="BL173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" s="1" t="inlineStr">
@@ -36275,6 +36983,10 @@
       </c>
       <c r="BG174" t="inlineStr"/>
       <c r="BH174" t="inlineStr"/>
+      <c r="BI174" t="inlineStr"/>
+      <c r="BJ174" t="inlineStr"/>
+      <c r="BK174" t="inlineStr"/>
+      <c r="BL174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" s="1" t="inlineStr">
@@ -36481,6 +37193,10 @@
       </c>
       <c r="BG175" t="inlineStr"/>
       <c r="BH175" t="inlineStr"/>
+      <c r="BI175" t="inlineStr"/>
+      <c r="BJ175" t="inlineStr"/>
+      <c r="BK175" t="inlineStr"/>
+      <c r="BL175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" s="1" t="inlineStr">
@@ -36687,6 +37403,10 @@
       </c>
       <c r="BG176" t="inlineStr"/>
       <c r="BH176" t="inlineStr"/>
+      <c r="BI176" t="inlineStr"/>
+      <c r="BJ176" t="inlineStr"/>
+      <c r="BK176" t="inlineStr"/>
+      <c r="BL176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" s="1" t="inlineStr">
@@ -36893,6 +37613,10 @@
       </c>
       <c r="BG177" t="inlineStr"/>
       <c r="BH177" t="inlineStr"/>
+      <c r="BI177" t="inlineStr"/>
+      <c r="BJ177" t="inlineStr"/>
+      <c r="BK177" t="inlineStr"/>
+      <c r="BL177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" s="1" t="inlineStr">
@@ -37099,6 +37823,10 @@
       </c>
       <c r="BG178" t="inlineStr"/>
       <c r="BH178" t="inlineStr"/>
+      <c r="BI178" t="inlineStr"/>
+      <c r="BJ178" t="inlineStr"/>
+      <c r="BK178" t="inlineStr"/>
+      <c r="BL178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" s="1" t="inlineStr">
@@ -37305,6 +38033,10 @@
       </c>
       <c r="BG179" t="inlineStr"/>
       <c r="BH179" t="inlineStr"/>
+      <c r="BI179" t="inlineStr"/>
+      <c r="BJ179" t="inlineStr"/>
+      <c r="BK179" t="inlineStr"/>
+      <c r="BL179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" s="1" t="inlineStr">
@@ -37507,6 +38239,10 @@
       </c>
       <c r="BG180" t="inlineStr"/>
       <c r="BH180" t="inlineStr"/>
+      <c r="BI180" t="inlineStr"/>
+      <c r="BJ180" t="inlineStr"/>
+      <c r="BK180" t="inlineStr"/>
+      <c r="BL180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" s="1" t="inlineStr">
@@ -37713,6 +38449,10 @@
       </c>
       <c r="BG181" t="inlineStr"/>
       <c r="BH181" t="inlineStr"/>
+      <c r="BI181" t="inlineStr"/>
+      <c r="BJ181" t="inlineStr"/>
+      <c r="BK181" t="inlineStr"/>
+      <c r="BL181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" s="1" t="inlineStr">
@@ -37919,6 +38659,10 @@
       </c>
       <c r="BG182" t="inlineStr"/>
       <c r="BH182" t="inlineStr"/>
+      <c r="BI182" t="inlineStr"/>
+      <c r="BJ182" t="inlineStr"/>
+      <c r="BK182" t="inlineStr"/>
+      <c r="BL182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" s="1" t="inlineStr">
@@ -38125,6 +38869,10 @@
       </c>
       <c r="BG183" t="inlineStr"/>
       <c r="BH183" t="inlineStr"/>
+      <c r="BI183" t="inlineStr"/>
+      <c r="BJ183" t="inlineStr"/>
+      <c r="BK183" t="inlineStr"/>
+      <c r="BL183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" s="1" t="inlineStr">
@@ -38331,6 +39079,10 @@
       </c>
       <c r="BG184" t="inlineStr"/>
       <c r="BH184" t="inlineStr"/>
+      <c r="BI184" t="inlineStr"/>
+      <c r="BJ184" t="inlineStr"/>
+      <c r="BK184" t="inlineStr"/>
+      <c r="BL184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" s="1" t="inlineStr">
@@ -38537,6 +39289,10 @@
       </c>
       <c r="BG185" t="inlineStr"/>
       <c r="BH185" t="inlineStr"/>
+      <c r="BI185" t="inlineStr"/>
+      <c r="BJ185" t="inlineStr"/>
+      <c r="BK185" t="inlineStr"/>
+      <c r="BL185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" s="1" t="inlineStr">
@@ -38743,6 +39499,10 @@
       </c>
       <c r="BG186" t="inlineStr"/>
       <c r="BH186" t="inlineStr"/>
+      <c r="BI186" t="inlineStr"/>
+      <c r="BJ186" t="inlineStr"/>
+      <c r="BK186" t="inlineStr"/>
+      <c r="BL186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" s="1" t="inlineStr">
@@ -38949,6 +39709,10 @@
       </c>
       <c r="BG187" t="inlineStr"/>
       <c r="BH187" t="inlineStr"/>
+      <c r="BI187" t="inlineStr"/>
+      <c r="BJ187" t="inlineStr"/>
+      <c r="BK187" t="inlineStr"/>
+      <c r="BL187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" s="1" t="inlineStr">
@@ -39155,6 +39919,10 @@
       </c>
       <c r="BG188" t="inlineStr"/>
       <c r="BH188" t="inlineStr"/>
+      <c r="BI188" t="inlineStr"/>
+      <c r="BJ188" t="inlineStr"/>
+      <c r="BK188" t="inlineStr"/>
+      <c r="BL188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" s="1" t="inlineStr">
@@ -39365,6 +40133,10 @@
       </c>
       <c r="BG189" t="inlineStr"/>
       <c r="BH189" t="inlineStr"/>
+      <c r="BI189" t="inlineStr"/>
+      <c r="BJ189" t="inlineStr"/>
+      <c r="BK189" t="inlineStr"/>
+      <c r="BL189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" s="1" t="inlineStr">
@@ -39571,6 +40343,10 @@
       </c>
       <c r="BG190" t="inlineStr"/>
       <c r="BH190" t="inlineStr"/>
+      <c r="BI190" t="inlineStr"/>
+      <c r="BJ190" t="inlineStr"/>
+      <c r="BK190" t="inlineStr"/>
+      <c r="BL190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" s="1" t="inlineStr">
@@ -39773,6 +40549,10 @@
       </c>
       <c r="BG191" t="inlineStr"/>
       <c r="BH191" t="inlineStr"/>
+      <c r="BI191" t="inlineStr"/>
+      <c r="BJ191" t="inlineStr"/>
+      <c r="BK191" t="inlineStr"/>
+      <c r="BL191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" s="1" t="inlineStr">
@@ -39979,6 +40759,10 @@
       </c>
       <c r="BG192" t="inlineStr"/>
       <c r="BH192" t="inlineStr"/>
+      <c r="BI192" t="inlineStr"/>
+      <c r="BJ192" t="inlineStr"/>
+      <c r="BK192" t="inlineStr"/>
+      <c r="BL192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" s="1" t="inlineStr">
@@ -40185,6 +40969,10 @@
       </c>
       <c r="BG193" t="inlineStr"/>
       <c r="BH193" t="inlineStr"/>
+      <c r="BI193" t="inlineStr"/>
+      <c r="BJ193" t="inlineStr"/>
+      <c r="BK193" t="inlineStr"/>
+      <c r="BL193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" s="1" t="inlineStr">
@@ -40391,6 +41179,10 @@
       </c>
       <c r="BG194" t="inlineStr"/>
       <c r="BH194" t="inlineStr"/>
+      <c r="BI194" t="inlineStr"/>
+      <c r="BJ194" t="inlineStr"/>
+      <c r="BK194" t="inlineStr"/>
+      <c r="BL194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" s="1" t="inlineStr">
@@ -40597,6 +41389,10 @@
       </c>
       <c r="BG195" t="inlineStr"/>
       <c r="BH195" t="inlineStr"/>
+      <c r="BI195" t="inlineStr"/>
+      <c r="BJ195" t="inlineStr"/>
+      <c r="BK195" t="inlineStr"/>
+      <c r="BL195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" s="1" t="inlineStr">
@@ -40803,6 +41599,10 @@
       </c>
       <c r="BG196" t="inlineStr"/>
       <c r="BH196" t="inlineStr"/>
+      <c r="BI196" t="inlineStr"/>
+      <c r="BJ196" t="inlineStr"/>
+      <c r="BK196" t="inlineStr"/>
+      <c r="BL196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" s="1" t="inlineStr">
@@ -41009,6 +41809,10 @@
       </c>
       <c r="BG197" t="inlineStr"/>
       <c r="BH197" t="inlineStr"/>
+      <c r="BI197" t="inlineStr"/>
+      <c r="BJ197" t="inlineStr"/>
+      <c r="BK197" t="inlineStr"/>
+      <c r="BL197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" s="1" t="inlineStr">
@@ -41215,6 +42019,10 @@
       </c>
       <c r="BG198" t="inlineStr"/>
       <c r="BH198" t="inlineStr"/>
+      <c r="BI198" t="inlineStr"/>
+      <c r="BJ198" t="inlineStr"/>
+      <c r="BK198" t="inlineStr"/>
+      <c r="BL198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" s="1" t="inlineStr">
@@ -41425,6 +42233,10 @@
       </c>
       <c r="BG199" t="inlineStr"/>
       <c r="BH199" t="inlineStr"/>
+      <c r="BI199" t="inlineStr"/>
+      <c r="BJ199" t="inlineStr"/>
+      <c r="BK199" t="inlineStr"/>
+      <c r="BL199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" s="1" t="inlineStr">
@@ -41631,6 +42443,10 @@
       </c>
       <c r="BG200" t="inlineStr"/>
       <c r="BH200" t="inlineStr"/>
+      <c r="BI200" t="inlineStr"/>
+      <c r="BJ200" t="inlineStr"/>
+      <c r="BK200" t="inlineStr"/>
+      <c r="BL200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" s="1" t="inlineStr">
@@ -41837,6 +42653,10 @@
       </c>
       <c r="BG201" t="inlineStr"/>
       <c r="BH201" t="inlineStr"/>
+      <c r="BI201" t="inlineStr"/>
+      <c r="BJ201" t="inlineStr"/>
+      <c r="BK201" t="inlineStr"/>
+      <c r="BL201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" s="1" t="inlineStr">
@@ -42047,6 +42867,10 @@
       </c>
       <c r="BG202" t="inlineStr"/>
       <c r="BH202" t="inlineStr"/>
+      <c r="BI202" t="inlineStr"/>
+      <c r="BJ202" t="inlineStr"/>
+      <c r="BK202" t="inlineStr"/>
+      <c r="BL202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" s="1" t="inlineStr">
@@ -42253,6 +43077,10 @@
       </c>
       <c r="BG203" t="inlineStr"/>
       <c r="BH203" t="inlineStr"/>
+      <c r="BI203" t="inlineStr"/>
+      <c r="BJ203" t="inlineStr"/>
+      <c r="BK203" t="inlineStr"/>
+      <c r="BL203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" s="1" t="inlineStr">
@@ -42459,6 +43287,10 @@
       </c>
       <c r="BG204" t="inlineStr"/>
       <c r="BH204" t="inlineStr"/>
+      <c r="BI204" t="inlineStr"/>
+      <c r="BJ204" t="inlineStr"/>
+      <c r="BK204" t="inlineStr"/>
+      <c r="BL204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" s="1" t="inlineStr">
@@ -42665,6 +43497,10 @@
       </c>
       <c r="BG205" t="inlineStr"/>
       <c r="BH205" t="inlineStr"/>
+      <c r="BI205" t="inlineStr"/>
+      <c r="BJ205" t="inlineStr"/>
+      <c r="BK205" t="inlineStr"/>
+      <c r="BL205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" s="1" t="inlineStr">
@@ -42871,6 +43707,10 @@
       </c>
       <c r="BG206" t="inlineStr"/>
       <c r="BH206" t="inlineStr"/>
+      <c r="BI206" t="inlineStr"/>
+      <c r="BJ206" t="inlineStr"/>
+      <c r="BK206" t="inlineStr"/>
+      <c r="BL206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" s="1" t="inlineStr">
@@ -43077,6 +43917,10 @@
       </c>
       <c r="BG207" t="inlineStr"/>
       <c r="BH207" t="inlineStr"/>
+      <c r="BI207" t="inlineStr"/>
+      <c r="BJ207" t="inlineStr"/>
+      <c r="BK207" t="inlineStr"/>
+      <c r="BL207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" s="1" t="inlineStr">
@@ -43283,6 +44127,10 @@
       </c>
       <c r="BG208" t="inlineStr"/>
       <c r="BH208" t="inlineStr"/>
+      <c r="BI208" t="inlineStr"/>
+      <c r="BJ208" t="inlineStr"/>
+      <c r="BK208" t="inlineStr"/>
+      <c r="BL208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" s="1" t="inlineStr">
@@ -43489,6 +44337,10 @@
       </c>
       <c r="BG209" t="inlineStr"/>
       <c r="BH209" t="inlineStr"/>
+      <c r="BI209" t="inlineStr"/>
+      <c r="BJ209" t="inlineStr"/>
+      <c r="BK209" t="inlineStr"/>
+      <c r="BL209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" s="1" t="inlineStr">
@@ -43695,6 +44547,10 @@
       </c>
       <c r="BG210" t="inlineStr"/>
       <c r="BH210" t="inlineStr"/>
+      <c r="BI210" t="inlineStr"/>
+      <c r="BJ210" t="inlineStr"/>
+      <c r="BK210" t="inlineStr"/>
+      <c r="BL210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" s="1" t="inlineStr">
@@ -43902,6 +44758,10 @@
       </c>
       <c r="BG211" t="inlineStr"/>
       <c r="BH211" t="inlineStr"/>
+      <c r="BI211" t="inlineStr"/>
+      <c r="BJ211" t="inlineStr"/>
+      <c r="BK211" t="inlineStr"/>
+      <c r="BL211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" s="1" t="inlineStr">
@@ -44108,6 +44968,10 @@
       </c>
       <c r="BG212" t="inlineStr"/>
       <c r="BH212" t="inlineStr"/>
+      <c r="BI212" t="inlineStr"/>
+      <c r="BJ212" t="inlineStr"/>
+      <c r="BK212" t="inlineStr"/>
+      <c r="BL212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" s="1" t="inlineStr">
@@ -44318,6 +45182,10 @@
       </c>
       <c r="BG213" t="inlineStr"/>
       <c r="BH213" t="inlineStr"/>
+      <c r="BI213" t="inlineStr"/>
+      <c r="BJ213" t="inlineStr"/>
+      <c r="BK213" t="inlineStr"/>
+      <c r="BL213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" s="1" t="inlineStr">
@@ -44524,6 +45392,10 @@
       </c>
       <c r="BG214" t="inlineStr"/>
       <c r="BH214" t="inlineStr"/>
+      <c r="BI214" t="inlineStr"/>
+      <c r="BJ214" t="inlineStr"/>
+      <c r="BK214" t="inlineStr"/>
+      <c r="BL214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" s="1" t="inlineStr">
@@ -44730,6 +45602,10 @@
       </c>
       <c r="BG215" t="inlineStr"/>
       <c r="BH215" t="inlineStr"/>
+      <c r="BI215" t="inlineStr"/>
+      <c r="BJ215" t="inlineStr"/>
+      <c r="BK215" t="inlineStr"/>
+      <c r="BL215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" s="1" t="inlineStr">
@@ -44936,6 +45812,10 @@
       </c>
       <c r="BG216" t="inlineStr"/>
       <c r="BH216" t="inlineStr"/>
+      <c r="BI216" t="inlineStr"/>
+      <c r="BJ216" t="inlineStr"/>
+      <c r="BK216" t="inlineStr"/>
+      <c r="BL216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" s="1" t="inlineStr">
@@ -45142,6 +46022,10 @@
       </c>
       <c r="BG217" t="inlineStr"/>
       <c r="BH217" t="inlineStr"/>
+      <c r="BI217" t="inlineStr"/>
+      <c r="BJ217" t="inlineStr"/>
+      <c r="BK217" t="inlineStr"/>
+      <c r="BL217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" s="1" t="inlineStr">
@@ -45348,6 +46232,10 @@
       </c>
       <c r="BG218" t="inlineStr"/>
       <c r="BH218" t="inlineStr"/>
+      <c r="BI218" t="inlineStr"/>
+      <c r="BJ218" t="inlineStr"/>
+      <c r="BK218" t="inlineStr"/>
+      <c r="BL218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" s="1" t="inlineStr">
@@ -45558,6 +46446,10 @@
       </c>
       <c r="BG219" t="inlineStr"/>
       <c r="BH219" t="inlineStr"/>
+      <c r="BI219" t="inlineStr"/>
+      <c r="BJ219" t="inlineStr"/>
+      <c r="BK219" t="inlineStr"/>
+      <c r="BL219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" s="1" t="inlineStr">
@@ -45764,6 +46656,10 @@
       </c>
       <c r="BG220" t="inlineStr"/>
       <c r="BH220" t="inlineStr"/>
+      <c r="BI220" t="inlineStr"/>
+      <c r="BJ220" t="inlineStr"/>
+      <c r="BK220" t="inlineStr"/>
+      <c r="BL220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" s="1" t="inlineStr">
@@ -45970,6 +46866,10 @@
       </c>
       <c r="BG221" t="inlineStr"/>
       <c r="BH221" t="inlineStr"/>
+      <c r="BI221" t="inlineStr"/>
+      <c r="BJ221" t="inlineStr"/>
+      <c r="BK221" t="inlineStr"/>
+      <c r="BL221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" s="1" t="inlineStr">
@@ -46176,6 +47076,10 @@
       </c>
       <c r="BG222" t="inlineStr"/>
       <c r="BH222" t="inlineStr"/>
+      <c r="BI222" t="inlineStr"/>
+      <c r="BJ222" t="inlineStr"/>
+      <c r="BK222" t="inlineStr"/>
+      <c r="BL222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" s="1" t="inlineStr">
@@ -46382,6 +47286,10 @@
       </c>
       <c r="BG223" t="inlineStr"/>
       <c r="BH223" t="inlineStr"/>
+      <c r="BI223" t="inlineStr"/>
+      <c r="BJ223" t="inlineStr"/>
+      <c r="BK223" t="inlineStr"/>
+      <c r="BL223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" s="1" t="inlineStr">
@@ -46588,6 +47496,10 @@
       </c>
       <c r="BG224" t="inlineStr"/>
       <c r="BH224" t="inlineStr"/>
+      <c r="BI224" t="inlineStr"/>
+      <c r="BJ224" t="inlineStr"/>
+      <c r="BK224" t="inlineStr"/>
+      <c r="BL224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" s="1" t="inlineStr">
@@ -46794,6 +47706,10 @@
       </c>
       <c r="BG225" t="inlineStr"/>
       <c r="BH225" t="inlineStr"/>
+      <c r="BI225" t="inlineStr"/>
+      <c r="BJ225" t="inlineStr"/>
+      <c r="BK225" t="inlineStr"/>
+      <c r="BL225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" s="1" t="inlineStr">
@@ -47000,6 +47916,10 @@
       </c>
       <c r="BG226" t="inlineStr"/>
       <c r="BH226" t="inlineStr"/>
+      <c r="BI226" t="inlineStr"/>
+      <c r="BJ226" t="inlineStr"/>
+      <c r="BK226" t="inlineStr"/>
+      <c r="BL226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" s="1" t="inlineStr">
@@ -47206,6 +48126,10 @@
       </c>
       <c r="BG227" t="inlineStr"/>
       <c r="BH227" t="inlineStr"/>
+      <c r="BI227" t="inlineStr"/>
+      <c r="BJ227" t="inlineStr"/>
+      <c r="BK227" t="inlineStr"/>
+      <c r="BL227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" s="1" t="inlineStr">
@@ -47416,6 +48340,10 @@
       </c>
       <c r="BG228" t="inlineStr"/>
       <c r="BH228" t="inlineStr"/>
+      <c r="BI228" t="inlineStr"/>
+      <c r="BJ228" t="inlineStr"/>
+      <c r="BK228" t="inlineStr"/>
+      <c r="BL228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" s="1" t="inlineStr">
@@ -47622,6 +48550,10 @@
       </c>
       <c r="BG229" t="inlineStr"/>
       <c r="BH229" t="inlineStr"/>
+      <c r="BI229" t="inlineStr"/>
+      <c r="BJ229" t="inlineStr"/>
+      <c r="BK229" t="inlineStr"/>
+      <c r="BL229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" s="1" t="inlineStr">
@@ -47828,6 +48760,10 @@
       </c>
       <c r="BG230" t="inlineStr"/>
       <c r="BH230" t="inlineStr"/>
+      <c r="BI230" t="inlineStr"/>
+      <c r="BJ230" t="inlineStr"/>
+      <c r="BK230" t="inlineStr"/>
+      <c r="BL230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" s="1" t="inlineStr">
@@ -48030,6 +48966,10 @@
       </c>
       <c r="BG231" t="inlineStr"/>
       <c r="BH231" t="inlineStr"/>
+      <c r="BI231" t="inlineStr"/>
+      <c r="BJ231" t="inlineStr"/>
+      <c r="BK231" t="inlineStr"/>
+      <c r="BL231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" s="1" t="inlineStr">
@@ -48221,6 +49161,10 @@
       </c>
       <c r="BG232" t="inlineStr"/>
       <c r="BH232" t="inlineStr"/>
+      <c r="BI232" t="inlineStr"/>
+      <c r="BJ232" t="inlineStr"/>
+      <c r="BK232" t="inlineStr"/>
+      <c r="BL232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" s="1" t="inlineStr">
@@ -48416,6 +49360,10 @@
       <c r="BH233" t="n">
         <v>4</v>
       </c>
+      <c r="BI233" t="inlineStr"/>
+      <c r="BJ233" t="inlineStr"/>
+      <c r="BK233" t="inlineStr"/>
+      <c r="BL233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" s="1" t="inlineStr">
@@ -48611,6 +49559,10 @@
       <c r="BH234" t="n">
         <v>0</v>
       </c>
+      <c r="BI234" t="inlineStr"/>
+      <c r="BJ234" t="inlineStr"/>
+      <c r="BK234" t="inlineStr"/>
+      <c r="BL234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" s="1" t="inlineStr">
@@ -48810,6 +49762,10 @@
       <c r="BH235" t="n">
         <v>3</v>
       </c>
+      <c r="BI235" t="inlineStr"/>
+      <c r="BJ235" t="inlineStr"/>
+      <c r="BK235" t="inlineStr"/>
+      <c r="BL235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" s="1" t="inlineStr">
@@ -49005,6 +49961,10 @@
       <c r="BH236" t="n">
         <v>3</v>
       </c>
+      <c r="BI236" t="inlineStr"/>
+      <c r="BJ236" t="inlineStr"/>
+      <c r="BK236" t="inlineStr"/>
+      <c r="BL236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" s="1" t="inlineStr">
@@ -49204,6 +50164,10 @@
       <c r="BH237" t="n">
         <v>3</v>
       </c>
+      <c r="BI237" t="inlineStr"/>
+      <c r="BJ237" t="inlineStr"/>
+      <c r="BK237" t="inlineStr"/>
+      <c r="BL237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" s="1" t="inlineStr">
@@ -49399,6 +50363,10 @@
       <c r="BH238" t="n">
         <v>4</v>
       </c>
+      <c r="BI238" t="inlineStr"/>
+      <c r="BJ238" t="inlineStr"/>
+      <c r="BK238" t="inlineStr"/>
+      <c r="BL238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" s="1" t="inlineStr">
@@ -49594,6 +50562,10 @@
       <c r="BH239" t="n">
         <v>0</v>
       </c>
+      <c r="BI239" t="inlineStr"/>
+      <c r="BJ239" t="inlineStr"/>
+      <c r="BK239" t="inlineStr"/>
+      <c r="BL239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" s="1" t="inlineStr">
@@ -49789,6 +50761,10 @@
       <c r="BH240" t="n">
         <v>1</v>
       </c>
+      <c r="BI240" t="inlineStr"/>
+      <c r="BJ240" t="inlineStr"/>
+      <c r="BK240" t="inlineStr"/>
+      <c r="BL240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" s="1" t="inlineStr">
@@ -49984,6 +50960,10 @@
       <c r="BH241" t="n">
         <v>3</v>
       </c>
+      <c r="BI241" t="inlineStr"/>
+      <c r="BJ241" t="inlineStr"/>
+      <c r="BK241" t="inlineStr"/>
+      <c r="BL241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" s="1" t="inlineStr">
@@ -50179,6 +51159,10 @@
       <c r="BH242" t="n">
         <v>5</v>
       </c>
+      <c r="BI242" t="inlineStr"/>
+      <c r="BJ242" t="inlineStr"/>
+      <c r="BK242" t="inlineStr"/>
+      <c r="BL242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" s="1" t="inlineStr">
@@ -50374,6 +51358,10 @@
       <c r="BH243" t="n">
         <v>3</v>
       </c>
+      <c r="BI243" t="inlineStr"/>
+      <c r="BJ243" t="inlineStr"/>
+      <c r="BK243" t="inlineStr"/>
+      <c r="BL243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" s="1" t="inlineStr">
@@ -50569,6 +51557,10 @@
       <c r="BH244" t="n">
         <v>2</v>
       </c>
+      <c r="BI244" t="inlineStr"/>
+      <c r="BJ244" t="inlineStr"/>
+      <c r="BK244" t="inlineStr"/>
+      <c r="BL244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" s="1" t="inlineStr">
@@ -50764,6 +51756,10 @@
       <c r="BH245" t="n">
         <v>2</v>
       </c>
+      <c r="BI245" t="inlineStr"/>
+      <c r="BJ245" t="inlineStr"/>
+      <c r="BK245" t="inlineStr"/>
+      <c r="BL245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" s="1" t="inlineStr">
@@ -50959,6 +51955,10 @@
       <c r="BH246" t="n">
         <v>1</v>
       </c>
+      <c r="BI246" t="inlineStr"/>
+      <c r="BJ246" t="inlineStr"/>
+      <c r="BK246" t="inlineStr"/>
+      <c r="BL246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" s="1" t="inlineStr">
@@ -51150,6 +52150,10 @@
       </c>
       <c r="BG247" t="inlineStr"/>
       <c r="BH247" t="inlineStr"/>
+      <c r="BI247" t="inlineStr"/>
+      <c r="BJ247" t="inlineStr"/>
+      <c r="BK247" t="inlineStr"/>
+      <c r="BL247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" s="1" t="inlineStr">
@@ -51345,6 +52349,10 @@
       <c r="BH248" t="n">
         <v>3</v>
       </c>
+      <c r="BI248" t="inlineStr"/>
+      <c r="BJ248" t="inlineStr"/>
+      <c r="BK248" t="inlineStr"/>
+      <c r="BL248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" s="1" t="inlineStr">
@@ -51540,6 +52548,10 @@
       <c r="BH249" t="n">
         <v>0</v>
       </c>
+      <c r="BI249" t="inlineStr"/>
+      <c r="BJ249" t="inlineStr"/>
+      <c r="BK249" t="inlineStr"/>
+      <c r="BL249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" s="1" t="inlineStr">
@@ -51735,6 +52747,10 @@
       <c r="BH250" t="n">
         <v>5</v>
       </c>
+      <c r="BI250" t="inlineStr"/>
+      <c r="BJ250" t="inlineStr"/>
+      <c r="BK250" t="inlineStr"/>
+      <c r="BL250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" s="1" t="inlineStr">
@@ -51930,6 +52946,10 @@
       <c r="BH251" t="n">
         <v>2</v>
       </c>
+      <c r="BI251" t="inlineStr"/>
+      <c r="BJ251" t="inlineStr"/>
+      <c r="BK251" t="inlineStr"/>
+      <c r="BL251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" s="1" t="inlineStr">
@@ -52125,6 +53145,10 @@
       <c r="BH252" t="n">
         <v>4</v>
       </c>
+      <c r="BI252" t="inlineStr"/>
+      <c r="BJ252" t="inlineStr"/>
+      <c r="BK252" t="inlineStr"/>
+      <c r="BL252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" s="1" t="inlineStr">
@@ -52320,6 +53344,10 @@
       <c r="BH253" t="n">
         <v>6</v>
       </c>
+      <c r="BI253" t="inlineStr"/>
+      <c r="BJ253" t="inlineStr"/>
+      <c r="BK253" t="inlineStr"/>
+      <c r="BL253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" s="1" t="inlineStr">
@@ -52519,6 +53547,10 @@
       <c r="BH254" t="n">
         <v>1</v>
       </c>
+      <c r="BI254" t="inlineStr"/>
+      <c r="BJ254" t="inlineStr"/>
+      <c r="BK254" t="inlineStr"/>
+      <c r="BL254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" s="1" t="inlineStr">
@@ -52714,6 +53746,10 @@
       <c r="BH255" t="n">
         <v>0</v>
       </c>
+      <c r="BI255" t="inlineStr"/>
+      <c r="BJ255" t="inlineStr"/>
+      <c r="BK255" t="inlineStr"/>
+      <c r="BL255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" s="1" t="inlineStr">
@@ -52909,6 +53945,10 @@
       <c r="BH256" t="n">
         <v>0</v>
       </c>
+      <c r="BI256" t="inlineStr"/>
+      <c r="BJ256" t="inlineStr"/>
+      <c r="BK256" t="inlineStr"/>
+      <c r="BL256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" s="1" t="inlineStr">
@@ -53104,6 +54144,10 @@
       <c r="BH257" t="n">
         <v>2</v>
       </c>
+      <c r="BI257" t="inlineStr"/>
+      <c r="BJ257" t="inlineStr"/>
+      <c r="BK257" t="inlineStr"/>
+      <c r="BL257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" s="1" t="inlineStr">
@@ -53299,6 +54343,10 @@
       <c r="BH258" t="n">
         <v>2</v>
       </c>
+      <c r="BI258" t="inlineStr"/>
+      <c r="BJ258" t="inlineStr"/>
+      <c r="BK258" t="inlineStr"/>
+      <c r="BL258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" s="1" t="inlineStr">
@@ -53494,6 +54542,10 @@
       <c r="BH259" t="n">
         <v>2</v>
       </c>
+      <c r="BI259" t="inlineStr"/>
+      <c r="BJ259" t="inlineStr"/>
+      <c r="BK259" t="inlineStr"/>
+      <c r="BL259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" s="1" t="inlineStr">
@@ -53689,6 +54741,10 @@
       <c r="BH260" t="n">
         <v>6</v>
       </c>
+      <c r="BI260" t="inlineStr"/>
+      <c r="BJ260" t="inlineStr"/>
+      <c r="BK260" t="inlineStr"/>
+      <c r="BL260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" s="1" t="inlineStr">
@@ -53884,6 +54940,10 @@
       <c r="BH261" t="n">
         <v>2</v>
       </c>
+      <c r="BI261" t="inlineStr"/>
+      <c r="BJ261" t="inlineStr"/>
+      <c r="BK261" t="inlineStr"/>
+      <c r="BL261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" s="1" t="inlineStr">
@@ -54079,6 +55139,10 @@
       <c r="BH262" t="n">
         <v>8</v>
       </c>
+      <c r="BI262" t="inlineStr"/>
+      <c r="BJ262" t="inlineStr"/>
+      <c r="BK262" t="inlineStr"/>
+      <c r="BL262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" s="1" t="inlineStr">
@@ -54274,6 +55338,10 @@
       <c r="BH263" t="n">
         <v>3</v>
       </c>
+      <c r="BI263" t="inlineStr"/>
+      <c r="BJ263" t="inlineStr"/>
+      <c r="BK263" t="inlineStr"/>
+      <c r="BL263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" s="1" t="inlineStr">
@@ -54477,6 +55545,10 @@
       <c r="BH264" t="n">
         <v>3</v>
       </c>
+      <c r="BI264" t="inlineStr"/>
+      <c r="BJ264" t="inlineStr"/>
+      <c r="BK264" t="inlineStr"/>
+      <c r="BL264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" s="1" t="inlineStr">
@@ -54680,6 +55752,10 @@
       </c>
       <c r="BG265" t="inlineStr"/>
       <c r="BH265" t="inlineStr"/>
+      <c r="BI265" t="inlineStr"/>
+      <c r="BJ265" t="inlineStr"/>
+      <c r="BK265" t="inlineStr"/>
+      <c r="BL265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" s="1" t="inlineStr">
@@ -54878,6 +55954,10 @@
       <c r="BF266" t="inlineStr"/>
       <c r="BG266" t="inlineStr"/>
       <c r="BH266" t="inlineStr"/>
+      <c r="BI266" t="inlineStr"/>
+      <c r="BJ266" t="inlineStr"/>
+      <c r="BK266" t="inlineStr"/>
+      <c r="BL266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" s="1" t="inlineStr">
@@ -55076,6 +56156,10 @@
       <c r="BF267" t="inlineStr"/>
       <c r="BG267" t="inlineStr"/>
       <c r="BH267" t="inlineStr"/>
+      <c r="BI267" t="inlineStr"/>
+      <c r="BJ267" t="inlineStr"/>
+      <c r="BK267" t="inlineStr"/>
+      <c r="BL267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" s="1" t="inlineStr">
@@ -55274,6 +56358,10 @@
       <c r="BF268" t="inlineStr"/>
       <c r="BG268" t="inlineStr"/>
       <c r="BH268" t="inlineStr"/>
+      <c r="BI268" t="inlineStr"/>
+      <c r="BJ268" t="inlineStr"/>
+      <c r="BK268" t="inlineStr"/>
+      <c r="BL268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" s="1" t="inlineStr">
@@ -55472,6 +56560,10 @@
       <c r="BF269" t="inlineStr"/>
       <c r="BG269" t="inlineStr"/>
       <c r="BH269" t="inlineStr"/>
+      <c r="BI269" t="inlineStr"/>
+      <c r="BJ269" t="inlineStr"/>
+      <c r="BK269" t="inlineStr"/>
+      <c r="BL269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" s="1" t="inlineStr">
@@ -55670,6 +56762,10 @@
       <c r="BF270" t="inlineStr"/>
       <c r="BG270" t="inlineStr"/>
       <c r="BH270" t="inlineStr"/>
+      <c r="BI270" t="inlineStr"/>
+      <c r="BJ270" t="inlineStr"/>
+      <c r="BK270" t="inlineStr"/>
+      <c r="BL270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" s="1" t="inlineStr">
@@ -55868,6 +56964,10 @@
       <c r="BF271" t="inlineStr"/>
       <c r="BG271" t="inlineStr"/>
       <c r="BH271" t="inlineStr"/>
+      <c r="BI271" t="inlineStr"/>
+      <c r="BJ271" t="inlineStr"/>
+      <c r="BK271" t="inlineStr"/>
+      <c r="BL271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" s="1" t="inlineStr">
@@ -56066,6 +57166,10 @@
       <c r="BF272" t="inlineStr"/>
       <c r="BG272" t="inlineStr"/>
       <c r="BH272" t="inlineStr"/>
+      <c r="BI272" t="inlineStr"/>
+      <c r="BJ272" t="inlineStr"/>
+      <c r="BK272" t="inlineStr"/>
+      <c r="BL272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" s="1" t="inlineStr">
@@ -56268,6 +57372,10 @@
       <c r="BF273" t="inlineStr"/>
       <c r="BG273" t="inlineStr"/>
       <c r="BH273" t="inlineStr"/>
+      <c r="BI273" t="inlineStr"/>
+      <c r="BJ273" t="inlineStr"/>
+      <c r="BK273" t="inlineStr"/>
+      <c r="BL273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" s="1" t="inlineStr">
@@ -56466,6 +57574,10 @@
       <c r="BF274" t="inlineStr"/>
       <c r="BG274" t="inlineStr"/>
       <c r="BH274" t="inlineStr"/>
+      <c r="BI274" t="inlineStr"/>
+      <c r="BJ274" t="inlineStr"/>
+      <c r="BK274" t="inlineStr"/>
+      <c r="BL274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" s="1" t="inlineStr">
@@ -56664,6 +57776,10 @@
       <c r="BF275" t="inlineStr"/>
       <c r="BG275" t="inlineStr"/>
       <c r="BH275" t="inlineStr"/>
+      <c r="BI275" t="inlineStr"/>
+      <c r="BJ275" t="inlineStr"/>
+      <c r="BK275" t="inlineStr"/>
+      <c r="BL275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" s="1" t="inlineStr">
@@ -56858,6 +57974,10 @@
       <c r="BF276" t="inlineStr"/>
       <c r="BG276" t="inlineStr"/>
       <c r="BH276" t="inlineStr"/>
+      <c r="BI276" t="inlineStr"/>
+      <c r="BJ276" t="inlineStr"/>
+      <c r="BK276" t="inlineStr"/>
+      <c r="BL276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" s="1" t="inlineStr">
@@ -56892,15 +58012,11 @@
           <t>58 000</t>
         </is>
       </c>
-      <c r="G277" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H277" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G277" t="n">
+        <v>1</v>
+      </c>
+      <c r="H277" t="n">
+        <v>1</v>
       </c>
       <c r="I277" t="inlineStr">
         <is>
@@ -56922,15 +58038,11 @@
           <t>Hoffenheim</t>
         </is>
       </c>
-      <c r="M277" t="inlineStr">
-        <is>
-          <t>3.12</t>
-        </is>
-      </c>
-      <c r="N277" t="inlineStr">
-        <is>
-          <t>0.86</t>
-        </is>
+      <c r="M277" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="N277" t="n">
+        <v>0.86</v>
       </c>
       <c r="O277" t="inlineStr">
         <is>
@@ -56942,137 +58054,85 @@
           <t>38%</t>
         </is>
       </c>
-      <c r="Q277" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="R277" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="S277" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="T277" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="U277" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="V277" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="W277" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="X277" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="Y277" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="Z277" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA277" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB277" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC277" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="AD277" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="AE277" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AF277" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AG277" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AH277" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="Q277" t="n">
+        <v>18</v>
+      </c>
+      <c r="R277" t="n">
+        <v>7</v>
+      </c>
+      <c r="S277" t="n">
+        <v>7</v>
+      </c>
+      <c r="T277" t="n">
+        <v>5</v>
+      </c>
+      <c r="U277" t="n">
+        <v>11</v>
+      </c>
+      <c r="V277" t="n">
+        <v>2</v>
+      </c>
+      <c r="W277" t="n">
+        <v>7</v>
+      </c>
+      <c r="X277" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y277" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z277" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA277" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB277" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC277" t="n">
+        <v>25</v>
+      </c>
+      <c r="AD277" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE277" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF277" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG277" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH277" t="n">
+        <v>7</v>
       </c>
       <c r="AI277" t="inlineStr"/>
       <c r="AJ277" t="inlineStr"/>
-      <c r="AK277" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL277" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AM277" t="inlineStr">
-        <is>
-          <t>712</t>
-        </is>
-      </c>
-      <c r="AN277" t="inlineStr">
-        <is>
-          <t>319</t>
-        </is>
-      </c>
-      <c r="AO277" t="inlineStr">
-        <is>
-          <t>655</t>
-        </is>
-      </c>
-      <c r="AP277" t="inlineStr">
-        <is>
-          <t>296</t>
-        </is>
-      </c>
-      <c r="AQ277" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="AR277" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
+      <c r="AK277" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL277" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM277" t="n">
+        <v>712</v>
+      </c>
+      <c r="AN277" t="n">
+        <v>319</v>
+      </c>
+      <c r="AO277" t="n">
+        <v>655</v>
+      </c>
+      <c r="AP277" t="n">
+        <v>296</v>
+      </c>
+      <c r="AQ277" t="n">
+        <v>121</v>
+      </c>
+      <c r="AR277" t="n">
+        <v>124</v>
       </c>
       <c r="AS277" t="inlineStr">
         <is>
@@ -57116,6 +58176,10 @@
       <c r="BF277" t="inlineStr"/>
       <c r="BG277" t="inlineStr"/>
       <c r="BH277" t="inlineStr"/>
+      <c r="BI277" t="inlineStr"/>
+      <c r="BJ277" t="inlineStr"/>
+      <c r="BK277" t="inlineStr"/>
+      <c r="BL277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" s="1" t="inlineStr">
@@ -57150,15 +58214,11 @@
           <t>58 000</t>
         </is>
       </c>
-      <c r="G278" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H278" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="G278" t="n">
+        <v>3</v>
+      </c>
+      <c r="H278" t="n">
+        <v>3</v>
       </c>
       <c r="I278" t="inlineStr">
         <is>
@@ -57180,15 +58240,11 @@
           <t>Bayern Munich</t>
         </is>
       </c>
-      <c r="M278" t="inlineStr">
-        <is>
-          <t>0.89</t>
-        </is>
-      </c>
-      <c r="N278" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
+      <c r="M278" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="N278" t="n">
+        <v>2.25</v>
       </c>
       <c r="O278" t="inlineStr">
         <is>
@@ -57200,137 +58256,85 @@
           <t>67%</t>
         </is>
       </c>
-      <c r="Q278" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R278" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="S278" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="T278" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="U278" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V278" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="W278" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="X278" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="Y278" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z278" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AA278" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AB278" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AC278" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AD278" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AE278" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AF278" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AG278" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AH278" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="Q278" t="n">
+        <v>5</v>
+      </c>
+      <c r="R278" t="n">
+        <v>22</v>
+      </c>
+      <c r="S278" t="n">
+        <v>4</v>
+      </c>
+      <c r="T278" t="n">
+        <v>13</v>
+      </c>
+      <c r="U278" t="n">
+        <v>1</v>
+      </c>
+      <c r="V278" t="n">
+        <v>9</v>
+      </c>
+      <c r="W278" t="n">
+        <v>11</v>
+      </c>
+      <c r="X278" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y278" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z278" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA278" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB278" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC278" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD278" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE278" t="n">
+        <v>10</v>
+      </c>
+      <c r="AF278" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG278" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH278" t="n">
+        <v>6</v>
       </c>
       <c r="AI278" t="inlineStr"/>
       <c r="AJ278" t="inlineStr"/>
-      <c r="AK278" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL278" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AM278" t="inlineStr">
-        <is>
-          <t>305</t>
-        </is>
-      </c>
-      <c r="AN278" t="inlineStr">
-        <is>
-          <t>863</t>
-        </is>
-      </c>
-      <c r="AO278" t="inlineStr">
-        <is>
-          <t>238</t>
-        </is>
-      </c>
-      <c r="AP278" t="inlineStr">
-        <is>
-          <t>768</t>
-        </is>
-      </c>
-      <c r="AQ278" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="AR278" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
+      <c r="AK278" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL278" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM278" t="n">
+        <v>305</v>
+      </c>
+      <c r="AN278" t="n">
+        <v>863</v>
+      </c>
+      <c r="AO278" t="n">
+        <v>238</v>
+      </c>
+      <c r="AP278" t="n">
+        <v>768</v>
+      </c>
+      <c r="AQ278" t="n">
+        <v>118</v>
+      </c>
+      <c r="AR278" t="n">
+        <v>124</v>
       </c>
       <c r="AS278" t="inlineStr">
         <is>
@@ -57374,6 +58378,10 @@
       <c r="BF278" t="inlineStr"/>
       <c r="BG278" t="inlineStr"/>
       <c r="BH278" t="inlineStr"/>
+      <c r="BI278" t="inlineStr"/>
+      <c r="BJ278" t="inlineStr"/>
+      <c r="BK278" t="inlineStr"/>
+      <c r="BL278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" s="1" t="inlineStr">
@@ -57408,15 +58416,11 @@
           <t>15 000</t>
         </is>
       </c>
-      <c r="G279" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H279" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G279" t="n">
+        <v>0</v>
+      </c>
+      <c r="H279" t="n">
+        <v>1</v>
       </c>
       <c r="I279" t="inlineStr">
         <is>
@@ -57438,15 +58442,11 @@
           <t>RB Leipzig</t>
         </is>
       </c>
-      <c r="M279" t="inlineStr">
-        <is>
-          <t>1.46</t>
-        </is>
-      </c>
-      <c r="N279" t="inlineStr">
-        <is>
-          <t>1.62</t>
-        </is>
+      <c r="M279" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="N279" t="n">
+        <v>1.62</v>
       </c>
       <c r="O279" t="inlineStr">
         <is>
@@ -57458,137 +58458,85 @@
           <t>53%</t>
         </is>
       </c>
-      <c r="Q279" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="R279" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="S279" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="T279" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U279" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="V279" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="W279" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="X279" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="Y279" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Z279" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA279" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB279" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC279" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AD279" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="AE279" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AF279" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AG279" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AH279" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
+      <c r="Q279" t="n">
+        <v>15</v>
+      </c>
+      <c r="R279" t="n">
+        <v>12</v>
+      </c>
+      <c r="S279" t="n">
+        <v>4</v>
+      </c>
+      <c r="T279" t="n">
+        <v>2</v>
+      </c>
+      <c r="U279" t="n">
+        <v>11</v>
+      </c>
+      <c r="V279" t="n">
+        <v>10</v>
+      </c>
+      <c r="W279" t="n">
+        <v>18</v>
+      </c>
+      <c r="X279" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y279" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z279" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA279" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB279" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC279" t="n">
+        <v>21</v>
+      </c>
+      <c r="AD279" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE279" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF279" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG279" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH279" t="n">
+        <v>13</v>
       </c>
       <c r="AI279" t="inlineStr"/>
       <c r="AJ279" t="inlineStr"/>
-      <c r="AK279" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL279" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AM279" t="inlineStr">
-        <is>
-          <t>408</t>
-        </is>
-      </c>
-      <c r="AN279" t="inlineStr">
-        <is>
-          <t>491</t>
-        </is>
-      </c>
-      <c r="AO279" t="inlineStr">
-        <is>
-          <t>306</t>
-        </is>
-      </c>
-      <c r="AP279" t="inlineStr">
-        <is>
-          <t>393</t>
-        </is>
-      </c>
-      <c r="AQ279" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="AR279" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
+      <c r="AK279" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL279" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM279" t="n">
+        <v>408</v>
+      </c>
+      <c r="AN279" t="n">
+        <v>491</v>
+      </c>
+      <c r="AO279" t="n">
+        <v>306</v>
+      </c>
+      <c r="AP279" t="n">
+        <v>393</v>
+      </c>
+      <c r="AQ279" t="n">
+        <v>118</v>
+      </c>
+      <c r="AR279" t="n">
+        <v>119</v>
       </c>
       <c r="AS279" t="inlineStr">
         <is>
@@ -57632,6 +58580,10 @@
       <c r="BF279" t="inlineStr"/>
       <c r="BG279" t="inlineStr"/>
       <c r="BH279" t="inlineStr"/>
+      <c r="BI279" t="inlineStr"/>
+      <c r="BJ279" t="inlineStr"/>
+      <c r="BK279" t="inlineStr"/>
+      <c r="BL279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" s="1" t="inlineStr">
@@ -57666,15 +58618,11 @@
           <t>19 919</t>
         </is>
       </c>
-      <c r="G280" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H280" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G280" t="n">
+        <v>2</v>
+      </c>
+      <c r="H280" t="n">
+        <v>0</v>
       </c>
       <c r="I280" t="inlineStr">
         <is>
@@ -57696,15 +58644,11 @@
           <t>Hannover</t>
         </is>
       </c>
-      <c r="M280" t="inlineStr">
-        <is>
-          <t>4.24</t>
-        </is>
-      </c>
-      <c r="N280" t="inlineStr">
-        <is>
-          <t>1.59</t>
-        </is>
+      <c r="M280" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="N280" t="n">
+        <v>1.59</v>
       </c>
       <c r="O280" t="inlineStr">
         <is>
@@ -57716,137 +58660,85 @@
           <t>63%</t>
         </is>
       </c>
-      <c r="Q280" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="R280" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="S280" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="T280" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="U280" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="V280" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="W280" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="X280" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="Y280" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Z280" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA280" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB280" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AC280" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AD280" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="AE280" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AF280" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AG280" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AH280" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
+      <c r="Q280" t="n">
+        <v>22</v>
+      </c>
+      <c r="R280" t="n">
+        <v>17</v>
+      </c>
+      <c r="S280" t="n">
+        <v>12</v>
+      </c>
+      <c r="T280" t="n">
+        <v>1</v>
+      </c>
+      <c r="U280" t="n">
+        <v>10</v>
+      </c>
+      <c r="V280" t="n">
+        <v>16</v>
+      </c>
+      <c r="W280" t="n">
+        <v>18</v>
+      </c>
+      <c r="X280" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y280" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z280" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA280" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB280" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC280" t="n">
+        <v>20</v>
+      </c>
+      <c r="AD280" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE280" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF280" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG280" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH280" t="n">
+        <v>13</v>
       </c>
       <c r="AI280" t="inlineStr"/>
       <c r="AJ280" t="inlineStr"/>
-      <c r="AK280" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL280" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AM280" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
-      </c>
-      <c r="AN280" t="inlineStr">
-        <is>
-          <t>486</t>
-        </is>
-      </c>
-      <c r="AO280" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
-      </c>
-      <c r="AP280" t="inlineStr">
-        <is>
-          <t>379</t>
-        </is>
-      </c>
-      <c r="AQ280" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="AR280" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
+      <c r="AK280" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL280" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM280" t="n">
+        <v>208</v>
+      </c>
+      <c r="AN280" t="n">
+        <v>486</v>
+      </c>
+      <c r="AO280" t="n">
+        <v>138</v>
+      </c>
+      <c r="AP280" t="n">
+        <v>379</v>
+      </c>
+      <c r="AQ280" t="n">
+        <v>115</v>
+      </c>
+      <c r="AR280" t="n">
+        <v>110</v>
       </c>
       <c r="AS280" t="inlineStr">
         <is>
@@ -57890,6 +58782,10 @@
       <c r="BF280" t="inlineStr"/>
       <c r="BG280" t="inlineStr"/>
       <c r="BH280" t="inlineStr"/>
+      <c r="BI280" t="inlineStr"/>
+      <c r="BJ280" t="inlineStr"/>
+      <c r="BK280" t="inlineStr"/>
+      <c r="BL280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" s="1" t="inlineStr">
@@ -57924,15 +58820,11 @@
           <t>51 500</t>
         </is>
       </c>
-      <c r="G281" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H281" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="G281" t="n">
+        <v>0</v>
+      </c>
+      <c r="H281" t="n">
+        <v>3</v>
       </c>
       <c r="I281" t="inlineStr">
         <is>
@@ -57954,15 +58846,11 @@
           <t>Hamburger SV</t>
         </is>
       </c>
-      <c r="M281" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
-      </c>
-      <c r="N281" t="inlineStr">
-        <is>
-          <t>2.54</t>
-        </is>
+      <c r="M281" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="N281" t="n">
+        <v>2.54</v>
       </c>
       <c r="O281" t="inlineStr">
         <is>
@@ -57974,145 +58862,89 @@
           <t>52%</t>
         </is>
       </c>
-      <c r="Q281" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="R281" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="S281" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="T281" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="U281" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="V281" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="W281" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="X281" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y281" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="Z281" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA281" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB281" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC281" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AD281" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AE281" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AF281" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AG281" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AH281" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AI281" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AJ281" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK281" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL281" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AM281" t="inlineStr">
-        <is>
-          <t>465</t>
-        </is>
-      </c>
-      <c r="AN281" t="inlineStr">
-        <is>
-          <t>511</t>
-        </is>
-      </c>
-      <c r="AO281" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="AP281" t="inlineStr">
-        <is>
-          <t>460</t>
-        </is>
-      </c>
-      <c r="AQ281" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="AR281" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
+      <c r="Q281" t="n">
+        <v>22</v>
+      </c>
+      <c r="R281" t="n">
+        <v>18</v>
+      </c>
+      <c r="S281" t="n">
+        <v>7</v>
+      </c>
+      <c r="T281" t="n">
+        <v>5</v>
+      </c>
+      <c r="U281" t="n">
+        <v>15</v>
+      </c>
+      <c r="V281" t="n">
+        <v>13</v>
+      </c>
+      <c r="W281" t="n">
+        <v>11</v>
+      </c>
+      <c r="X281" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y281" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z281" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA281" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB281" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC281" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD281" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE281" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF281" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG281" t="n">
+        <v>8</v>
+      </c>
+      <c r="AH281" t="n">
+        <v>9</v>
+      </c>
+      <c r="AI281" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ281" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK281" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL281" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM281" t="n">
+        <v>465</v>
+      </c>
+      <c r="AN281" t="n">
+        <v>511</v>
+      </c>
+      <c r="AO281" t="n">
+        <v>414</v>
+      </c>
+      <c r="AP281" t="n">
+        <v>460</v>
+      </c>
+      <c r="AQ281" t="n">
+        <v>115</v>
+      </c>
+      <c r="AR281" t="n">
+        <v>116</v>
       </c>
       <c r="AS281" t="inlineStr">
         <is>
@@ -58156,6 +58988,10 @@
       <c r="BF281" t="inlineStr"/>
       <c r="BG281" t="inlineStr"/>
       <c r="BH281" t="inlineStr"/>
+      <c r="BI281" t="inlineStr"/>
+      <c r="BJ281" t="inlineStr"/>
+      <c r="BK281" t="inlineStr"/>
+      <c r="BL281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" s="1" t="inlineStr">
@@ -58190,15 +59026,11 @@
           <t>22 615</t>
         </is>
       </c>
-      <c r="G282" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H282" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G282" t="n">
+        <v>2</v>
+      </c>
+      <c r="H282" t="n">
+        <v>2</v>
       </c>
       <c r="I282" t="inlineStr">
         <is>
@@ -58220,15 +59052,11 @@
           <t>Greuther Furth</t>
         </is>
       </c>
-      <c r="M282" t="inlineStr">
-        <is>
-          <t>3.64</t>
-        </is>
-      </c>
-      <c r="N282" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
+      <c r="M282" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="N282" t="n">
+        <v>2</v>
       </c>
       <c r="O282" t="inlineStr">
         <is>
@@ -58240,137 +59068,85 @@
           <t>35%</t>
         </is>
       </c>
-      <c r="Q282" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="R282" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="S282" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="T282" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="U282" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="V282" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="W282" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="X282" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="Y282" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Z282" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA282" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB282" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC282" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AD282" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="AE282" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AF282" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AG282" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AH282" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+      <c r="Q282" t="n">
+        <v>15</v>
+      </c>
+      <c r="R282" t="n">
+        <v>18</v>
+      </c>
+      <c r="S282" t="n">
+        <v>6</v>
+      </c>
+      <c r="T282" t="n">
+        <v>3</v>
+      </c>
+      <c r="U282" t="n">
+        <v>9</v>
+      </c>
+      <c r="V282" t="n">
+        <v>15</v>
+      </c>
+      <c r="W282" t="n">
+        <v>17</v>
+      </c>
+      <c r="X282" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y282" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z282" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA282" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB282" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC282" t="n">
+        <v>17</v>
+      </c>
+      <c r="AD282" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE282" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF282" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG282" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH282" t="n">
+        <v>16</v>
       </c>
       <c r="AI282" t="inlineStr"/>
       <c r="AJ282" t="inlineStr"/>
-      <c r="AK282" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AL282" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AM282" t="inlineStr">
-        <is>
-          <t>534</t>
-        </is>
-      </c>
-      <c r="AN282" t="inlineStr">
-        <is>
-          <t>331</t>
-        </is>
-      </c>
-      <c r="AO282" t="inlineStr">
-        <is>
-          <t>481</t>
-        </is>
-      </c>
-      <c r="AP282" t="inlineStr">
-        <is>
-          <t>275</t>
-        </is>
-      </c>
-      <c r="AQ282" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
-      <c r="AR282" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
+      <c r="AK282" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL282" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM282" t="n">
+        <v>534</v>
+      </c>
+      <c r="AN282" t="n">
+        <v>331</v>
+      </c>
+      <c r="AO282" t="n">
+        <v>481</v>
+      </c>
+      <c r="AP282" t="n">
+        <v>275</v>
+      </c>
+      <c r="AQ282" t="n">
+        <v>119</v>
+      </c>
+      <c r="AR282" t="n">
+        <v>122</v>
       </c>
       <c r="AS282" t="inlineStr">
         <is>
@@ -58414,6 +59190,10 @@
       <c r="BF282" t="inlineStr"/>
       <c r="BG282" t="inlineStr"/>
       <c r="BH282" t="inlineStr"/>
+      <c r="BI282" t="inlineStr"/>
+      <c r="BJ282" t="inlineStr"/>
+      <c r="BK282" t="inlineStr"/>
+      <c r="BL282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" s="1" t="inlineStr">
@@ -58448,15 +59228,11 @@
           <t>61 939</t>
         </is>
       </c>
-      <c r="G283" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H283" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G283" t="n">
+        <v>2</v>
+      </c>
+      <c r="H283" t="n">
+        <v>2</v>
       </c>
       <c r="I283" t="inlineStr">
         <is>
@@ -58478,15 +59254,11 @@
           <t>Hertha Berlin</t>
         </is>
       </c>
-      <c r="M283" t="inlineStr">
-        <is>
-          <t>1.21</t>
-        </is>
-      </c>
-      <c r="N283" t="inlineStr">
-        <is>
-          <t>2.23</t>
-        </is>
+      <c r="M283" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="N283" t="n">
+        <v>2.23</v>
       </c>
       <c r="O283" t="inlineStr">
         <is>
@@ -58498,137 +59270,85 @@
           <t>46%</t>
         </is>
       </c>
-      <c r="Q283" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="R283" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="S283" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="T283" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="U283" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="V283" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="W283" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="X283" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y283" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Z283" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA283" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB283" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AC283" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AD283" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AE283" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AF283" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AG283" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AH283" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+      <c r="Q283" t="n">
+        <v>14</v>
+      </c>
+      <c r="R283" t="n">
+        <v>17</v>
+      </c>
+      <c r="S283" t="n">
+        <v>3</v>
+      </c>
+      <c r="T283" t="n">
+        <v>5</v>
+      </c>
+      <c r="U283" t="n">
+        <v>11</v>
+      </c>
+      <c r="V283" t="n">
+        <v>12</v>
+      </c>
+      <c r="W283" t="n">
+        <v>21</v>
+      </c>
+      <c r="X283" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y283" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z283" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA283" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB283" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC283" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD283" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE283" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF283" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG283" t="n">
+        <v>8</v>
+      </c>
+      <c r="AH283" t="n">
+        <v>16</v>
       </c>
       <c r="AI283" t="inlineStr"/>
       <c r="AJ283" t="inlineStr"/>
-      <c r="AK283" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AL283" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AM283" t="inlineStr">
-        <is>
-          <t>455</t>
-        </is>
-      </c>
-      <c r="AN283" t="inlineStr">
-        <is>
-          <t>354</t>
-        </is>
-      </c>
-      <c r="AO283" t="inlineStr">
-        <is>
-          <t>373</t>
-        </is>
-      </c>
-      <c r="AP283" t="inlineStr">
-        <is>
-          <t>297</t>
-        </is>
-      </c>
-      <c r="AQ283" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="AR283" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
+      <c r="AK283" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL283" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM283" t="n">
+        <v>455</v>
+      </c>
+      <c r="AN283" t="n">
+        <v>354</v>
+      </c>
+      <c r="AO283" t="n">
+        <v>373</v>
+      </c>
+      <c r="AP283" t="n">
+        <v>297</v>
+      </c>
+      <c r="AQ283" t="n">
+        <v>115</v>
+      </c>
+      <c r="AR283" t="n">
+        <v>116</v>
       </c>
       <c r="AS283" t="inlineStr">
         <is>
@@ -58672,6 +59392,3278 @@
       <c r="BF283" t="inlineStr"/>
       <c r="BG283" t="inlineStr"/>
       <c r="BH283" t="inlineStr"/>
+      <c r="BI283" t="inlineStr"/>
+      <c r="BJ283" t="inlineStr"/>
+      <c r="BK283" t="inlineStr"/>
+      <c r="BL283" t="inlineStr"/>
+    </row>
+    <row r="284">
+      <c r="A284" s="1" t="inlineStr">
+        <is>
+          <t>2mcmYkSq</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>19.10.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>Stieler T.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>Allianz Arena
+ (Munich)</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>75 024</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr"/>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>nVp0wiqd</t>
+        </is>
+      </c>
+      <c r="J284" t="inlineStr">
+        <is>
+          <t>Bayern Munich</t>
+        </is>
+      </c>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="L284" t="inlineStr">
+        <is>
+          <t>Stuttgart</t>
+        </is>
+      </c>
+      <c r="M284" t="inlineStr">
+        <is>
+          <t>3.27</t>
+        </is>
+      </c>
+      <c r="N284" t="inlineStr">
+        <is>
+          <t>0.40</t>
+        </is>
+      </c>
+      <c r="O284" t="inlineStr">
+        <is>
+          <t>66%</t>
+        </is>
+      </c>
+      <c r="P284" t="inlineStr">
+        <is>
+          <t>34%</t>
+        </is>
+      </c>
+      <c r="Q284" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="R284" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="S284" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T284" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U284" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V284" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W284" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="X284" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y284" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Z284" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA284" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB284" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC284" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AD284" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AE284" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AF284" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AG284" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AH284" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AI284" t="inlineStr"/>
+      <c r="AJ284" t="inlineStr"/>
+      <c r="AK284" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AL284" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM284" t="inlineStr">
+        <is>
+          <t>698</t>
+        </is>
+      </c>
+      <c r="AN284" t="inlineStr">
+        <is>
+          <t>362</t>
+        </is>
+      </c>
+      <c r="AO284" t="inlineStr">
+        <is>
+          <t>627</t>
+        </is>
+      </c>
+      <c r="AP284" t="inlineStr">
+        <is>
+          <t>281</t>
+        </is>
+      </c>
+      <c r="AQ284" t="inlineStr"/>
+      <c r="AR284" t="inlineStr"/>
+      <c r="AS284" t="inlineStr">
+        <is>
+          <t>K6A2elS9</t>
+        </is>
+      </c>
+      <c r="AT284" t="inlineStr">
+        <is>
+          <t>kompany vincent</t>
+        </is>
+      </c>
+      <c r="AU284" t="inlineStr">
+        <is>
+          <t>GzfvcwRj</t>
+        </is>
+      </c>
+      <c r="AV284" t="inlineStr">
+        <is>
+          <t>hoeness sebastian</t>
+        </is>
+      </c>
+      <c r="AW284" t="n">
+        <v>59</v>
+      </c>
+      <c r="AX284" t="n">
+        <v>591</v>
+      </c>
+      <c r="AY284" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ284" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BA284" t="inlineStr"/>
+      <c r="BB284" t="inlineStr"/>
+      <c r="BC284" t="inlineStr"/>
+      <c r="BD284" t="inlineStr"/>
+      <c r="BE284" t="inlineStr"/>
+      <c r="BF284" t="inlineStr"/>
+      <c r="BG284" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="BH284" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BI284" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="BJ284" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="BK284" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="BL284" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="1" t="inlineStr">
+        <is>
+          <t>fHjVr7t2</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>19.10.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>Siebert D.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>Borussia-Park
+ (Mönchengladbach)</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>54 042</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>50 000</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>88HSzjDr</t>
+        </is>
+      </c>
+      <c r="J285" t="inlineStr">
+        <is>
+          <t>B. Monchengladbach</t>
+        </is>
+      </c>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>KWixEVWi</t>
+        </is>
+      </c>
+      <c r="L285" t="inlineStr">
+        <is>
+          <t>Heidenheim</t>
+        </is>
+      </c>
+      <c r="M285" t="inlineStr">
+        <is>
+          <t>3.13</t>
+        </is>
+      </c>
+      <c r="N285" t="inlineStr">
+        <is>
+          <t>1.69</t>
+        </is>
+      </c>
+      <c r="O285" t="inlineStr">
+        <is>
+          <t>66%</t>
+        </is>
+      </c>
+      <c r="P285" t="inlineStr">
+        <is>
+          <t>34%</t>
+        </is>
+      </c>
+      <c r="Q285" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="R285" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="S285" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T285" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="U285" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V285" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W285" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="X285" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="Y285" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Z285" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA285" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB285" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC285" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="AD285" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AE285" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AF285" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AG285" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AH285" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AI285" t="inlineStr"/>
+      <c r="AJ285" t="inlineStr"/>
+      <c r="AK285" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AL285" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM285" t="inlineStr">
+        <is>
+          <t>524</t>
+        </is>
+      </c>
+      <c r="AN285" t="inlineStr">
+        <is>
+          <t>257</t>
+        </is>
+      </c>
+      <c r="AO285" t="inlineStr">
+        <is>
+          <t>428</t>
+        </is>
+      </c>
+      <c r="AP285" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="AQ285" t="inlineStr"/>
+      <c r="AR285" t="inlineStr"/>
+      <c r="AS285" t="inlineStr">
+        <is>
+          <t>M5BRZDsC</t>
+        </is>
+      </c>
+      <c r="AT285" t="inlineStr">
+        <is>
+          <t>seoane gerardo</t>
+        </is>
+      </c>
+      <c r="AU285" t="inlineStr">
+        <is>
+          <t>4ljanukM</t>
+        </is>
+      </c>
+      <c r="AV285" t="inlineStr">
+        <is>
+          <t>schmidt frank</t>
+        </is>
+      </c>
+      <c r="AW285" t="n">
+        <v>59</v>
+      </c>
+      <c r="AX285" t="n">
+        <v>591</v>
+      </c>
+      <c r="AY285" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ285" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BA285" t="inlineStr"/>
+      <c r="BB285" t="inlineStr"/>
+      <c r="BC285" t="inlineStr"/>
+      <c r="BD285" t="inlineStr"/>
+      <c r="BE285" t="inlineStr"/>
+      <c r="BF285" t="inlineStr"/>
+      <c r="BG285" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BH285" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="BI285" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BJ285" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="BK285" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BL285" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="1" t="inlineStr">
+        <is>
+          <t>r3GGwC4M</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>19.10.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>Brych F.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>BayArena
+ (Leverkusen)</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>30 210</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>30 000</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>4jcj2zMd</t>
+        </is>
+      </c>
+      <c r="J286" t="inlineStr">
+        <is>
+          <t>Bayer Leverkusen</t>
+        </is>
+      </c>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="L286" t="inlineStr">
+        <is>
+          <t>Eintracht Frankfurt</t>
+        </is>
+      </c>
+      <c r="M286" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="N286" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="O286" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="P286" t="inlineStr">
+        <is>
+          <t>46%</t>
+        </is>
+      </c>
+      <c r="Q286" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="R286" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="S286" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="T286" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U286" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V286" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W286" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="X286" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y286" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Z286" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA286" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB286" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC286" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AD286" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AE286" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AF286" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AG286" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AH286" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AI286" t="inlineStr"/>
+      <c r="AJ286" t="inlineStr"/>
+      <c r="AK286" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL286" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM286" t="inlineStr">
+        <is>
+          <t>542</t>
+        </is>
+      </c>
+      <c r="AN286" t="inlineStr">
+        <is>
+          <t>470</t>
+        </is>
+      </c>
+      <c r="AO286" t="inlineStr">
+        <is>
+          <t>497</t>
+        </is>
+      </c>
+      <c r="AP286" t="inlineStr">
+        <is>
+          <t>412</t>
+        </is>
+      </c>
+      <c r="AQ286" t="inlineStr"/>
+      <c r="AR286" t="inlineStr"/>
+      <c r="AS286" t="inlineStr">
+        <is>
+          <t>hAcTWKKN</t>
+        </is>
+      </c>
+      <c r="AT286" t="inlineStr">
+        <is>
+          <t>alonso xabi</t>
+        </is>
+      </c>
+      <c r="AU286" t="inlineStr">
+        <is>
+          <t>UgdQz0fK</t>
+        </is>
+      </c>
+      <c r="AV286" t="inlineStr">
+        <is>
+          <t>toppmoller dino</t>
+        </is>
+      </c>
+      <c r="AW286" t="n">
+        <v>59</v>
+      </c>
+      <c r="AX286" t="n">
+        <v>591</v>
+      </c>
+      <c r="AY286" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ286" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BA286" t="inlineStr"/>
+      <c r="BB286" t="inlineStr"/>
+      <c r="BC286" t="inlineStr"/>
+      <c r="BD286" t="inlineStr"/>
+      <c r="BE286" t="inlineStr"/>
+      <c r="BF286" t="inlineStr"/>
+      <c r="BG286" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="BH286" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BI286" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="BJ286" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BK286" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BL286" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="1" t="inlineStr">
+        <is>
+          <t>M93rhBJF</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>19.10.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>Dankert B.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>Europa-Park Stadion
+ (Freiburg)</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>34 700</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>33 500</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
+      <c r="J287" t="inlineStr">
+        <is>
+          <t>Freiburg</t>
+        </is>
+      </c>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>fTVNku3I</t>
+        </is>
+      </c>
+      <c r="L287" t="inlineStr">
+        <is>
+          <t>Augsburg</t>
+        </is>
+      </c>
+      <c r="M287" t="inlineStr">
+        <is>
+          <t>0.73</t>
+        </is>
+      </c>
+      <c r="N287" t="inlineStr">
+        <is>
+          <t>0.56</t>
+        </is>
+      </c>
+      <c r="O287" t="inlineStr">
+        <is>
+          <t>57%</t>
+        </is>
+      </c>
+      <c r="P287" t="inlineStr">
+        <is>
+          <t>43%</t>
+        </is>
+      </c>
+      <c r="Q287" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="R287" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="S287" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T287" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U287" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V287" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W287" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="X287" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="Y287" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Z287" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA287" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB287" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC287" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AD287" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AE287" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AF287" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AG287" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AH287" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AI287" t="inlineStr"/>
+      <c r="AJ287" t="inlineStr"/>
+      <c r="AK287" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL287" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM287" t="inlineStr">
+        <is>
+          <t>578</t>
+        </is>
+      </c>
+      <c r="AN287" t="inlineStr">
+        <is>
+          <t>429</t>
+        </is>
+      </c>
+      <c r="AO287" t="inlineStr">
+        <is>
+          <t>478</t>
+        </is>
+      </c>
+      <c r="AP287" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="AQ287" t="inlineStr"/>
+      <c r="AR287" t="inlineStr"/>
+      <c r="AS287" t="inlineStr">
+        <is>
+          <t>YZPE6Sx7</t>
+        </is>
+      </c>
+      <c r="AT287" t="inlineStr">
+        <is>
+          <t>schuster julian</t>
+        </is>
+      </c>
+      <c r="AU287" t="inlineStr">
+        <is>
+          <t>2VSFgl3c</t>
+        </is>
+      </c>
+      <c r="AV287" t="inlineStr">
+        <is>
+          <t>thorup jess</t>
+        </is>
+      </c>
+      <c r="AW287" t="n">
+        <v>59</v>
+      </c>
+      <c r="AX287" t="n">
+        <v>591</v>
+      </c>
+      <c r="AY287" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ287" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BA287" t="inlineStr"/>
+      <c r="BB287" t="inlineStr"/>
+      <c r="BC287" t="inlineStr"/>
+      <c r="BD287" t="inlineStr"/>
+      <c r="BE287" t="inlineStr"/>
+      <c r="BF287" t="inlineStr"/>
+      <c r="BG287" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BH287" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BI287" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="BJ287" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BK287" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="BL287" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="1" t="inlineStr">
+        <is>
+          <t>Eq0zfXl3</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>19.10.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>Storks S.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>PreZero Arena
+ (Sinsheim)</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>30 150</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>19 281</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>hQAtP9Sl</t>
+        </is>
+      </c>
+      <c r="J288" t="inlineStr">
+        <is>
+          <t>Hoffenheim</t>
+        </is>
+      </c>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>8Y2m6ADe</t>
+        </is>
+      </c>
+      <c r="L288" t="inlineStr">
+        <is>
+          <t>Bochum</t>
+        </is>
+      </c>
+      <c r="M288" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="N288" t="inlineStr">
+        <is>
+          <t>2.32</t>
+        </is>
+      </c>
+      <c r="O288" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="P288" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="Q288" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R288" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="S288" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T288" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U288" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V288" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="W288" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="X288" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Y288" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Z288" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA288" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB288" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC288" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AD288" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="AE288" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AF288" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AG288" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AH288" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AI288" t="inlineStr"/>
+      <c r="AJ288" t="inlineStr"/>
+      <c r="AK288" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL288" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM288" t="inlineStr">
+        <is>
+          <t>411</t>
+        </is>
+      </c>
+      <c r="AN288" t="inlineStr">
+        <is>
+          <t>418</t>
+        </is>
+      </c>
+      <c r="AO288" t="inlineStr">
+        <is>
+          <t>319</t>
+        </is>
+      </c>
+      <c r="AP288" t="inlineStr">
+        <is>
+          <t>326</t>
+        </is>
+      </c>
+      <c r="AQ288" t="inlineStr"/>
+      <c r="AR288" t="inlineStr"/>
+      <c r="AS288" t="inlineStr">
+        <is>
+          <t>KUx4Q7x1</t>
+        </is>
+      </c>
+      <c r="AT288" t="inlineStr">
+        <is>
+          <t>matarazzo pellegrino</t>
+        </is>
+      </c>
+      <c r="AU288" t="inlineStr">
+        <is>
+          <t>8f6APkLc</t>
+        </is>
+      </c>
+      <c r="AV288" t="inlineStr">
+        <is>
+          <t>zeidler peter</t>
+        </is>
+      </c>
+      <c r="AW288" t="n">
+        <v>59</v>
+      </c>
+      <c r="AX288" t="n">
+        <v>591</v>
+      </c>
+      <c r="AY288" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ288" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BA288" t="inlineStr"/>
+      <c r="BB288" t="inlineStr"/>
+      <c r="BC288" t="inlineStr"/>
+      <c r="BD288" t="inlineStr"/>
+      <c r="BE288" t="inlineStr"/>
+      <c r="BF288" t="inlineStr"/>
+      <c r="BG288" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BH288" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="BI288" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BJ288" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BK288" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="BL288" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="1" t="inlineStr">
+        <is>
+          <t>E7rNpTBk</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>19.10.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>Zwayer F.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>Mewa Arena
+ (Mainz)</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>34 000</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>30 100</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>EuakNmc1</t>
+        </is>
+      </c>
+      <c r="J289" t="inlineStr">
+        <is>
+          <t>Mainz</t>
+        </is>
+      </c>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>KbS1suSm</t>
+        </is>
+      </c>
+      <c r="L289" t="inlineStr">
+        <is>
+          <t>RB Leipzig</t>
+        </is>
+      </c>
+      <c r="M289" t="inlineStr">
+        <is>
+          <t>0.47</t>
+        </is>
+      </c>
+      <c r="N289" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="O289" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
+      </c>
+      <c r="P289" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="Q289" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R289" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="S289" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T289" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U289" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V289" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W289" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="X289" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="Y289" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Z289" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA289" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB289" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC289" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AD289" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AE289" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AF289" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AG289" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AH289" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AI289" t="inlineStr"/>
+      <c r="AJ289" t="inlineStr"/>
+      <c r="AK289" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL289" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM289" t="inlineStr">
+        <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="AN289" t="inlineStr">
+        <is>
+          <t>457</t>
+        </is>
+      </c>
+      <c r="AO289" t="inlineStr">
+        <is>
+          <t>402</t>
+        </is>
+      </c>
+      <c r="AP289" t="inlineStr">
+        <is>
+          <t>346</t>
+        </is>
+      </c>
+      <c r="AQ289" t="inlineStr"/>
+      <c r="AR289" t="inlineStr"/>
+      <c r="AS289" t="inlineStr">
+        <is>
+          <t>vZA6VYpf</t>
+        </is>
+      </c>
+      <c r="AT289" t="inlineStr">
+        <is>
+          <t>henriksen bo</t>
+        </is>
+      </c>
+      <c r="AU289" t="inlineStr">
+        <is>
+          <t>pfoInmcq</t>
+        </is>
+      </c>
+      <c r="AV289" t="inlineStr">
+        <is>
+          <t>rose marko</t>
+        </is>
+      </c>
+      <c r="AW289" t="n">
+        <v>59</v>
+      </c>
+      <c r="AX289" t="n">
+        <v>591</v>
+      </c>
+      <c r="AY289" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ289" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BA289" t="inlineStr"/>
+      <c r="BB289" t="inlineStr"/>
+      <c r="BC289" t="inlineStr"/>
+      <c r="BD289" t="inlineStr"/>
+      <c r="BE289" t="inlineStr"/>
+      <c r="BF289" t="inlineStr"/>
+      <c r="BG289" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="BH289" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BI289" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BJ289" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="BK289" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="BL289" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="1" t="inlineStr">
+        <is>
+          <t>z1eeWTdd</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>18.10.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>Jollenbeck M.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>Signal Iduna Park
+ (Dortmund)</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>81 365</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>81 365</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="J290" t="inlineStr">
+        <is>
+          <t>Dortmund</t>
+        </is>
+      </c>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="L290" t="inlineStr">
+        <is>
+          <t>St. Pauli</t>
+        </is>
+      </c>
+      <c r="M290" t="inlineStr">
+        <is>
+          <t>3.46</t>
+        </is>
+      </c>
+      <c r="N290" t="inlineStr">
+        <is>
+          <t>0.58</t>
+        </is>
+      </c>
+      <c r="O290" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="P290" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="Q290" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="R290" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S290" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T290" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U290" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="V290" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W290" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="X290" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y290" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Z290" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA290" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB290" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC290" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AD290" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AE290" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AF290" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AG290" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AH290" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AI290" t="inlineStr"/>
+      <c r="AJ290" t="inlineStr"/>
+      <c r="AK290" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL290" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM290" t="inlineStr">
+        <is>
+          <t>767</t>
+        </is>
+      </c>
+      <c r="AN290" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="AO290" t="inlineStr">
+        <is>
+          <t>713</t>
+        </is>
+      </c>
+      <c r="AP290" t="inlineStr">
+        <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="AQ290" t="inlineStr"/>
+      <c r="AR290" t="inlineStr"/>
+      <c r="AS290" t="inlineStr">
+        <is>
+          <t>IkCftsQm</t>
+        </is>
+      </c>
+      <c r="AT290" t="inlineStr">
+        <is>
+          <t>sahin nuri</t>
+        </is>
+      </c>
+      <c r="AU290" t="inlineStr">
+        <is>
+          <t>0jdIgO6t</t>
+        </is>
+      </c>
+      <c r="AV290" t="inlineStr">
+        <is>
+          <t>blessin alexander</t>
+        </is>
+      </c>
+      <c r="AW290" t="n">
+        <v>59</v>
+      </c>
+      <c r="AX290" t="n">
+        <v>591</v>
+      </c>
+      <c r="AY290" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ290" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BA290" t="inlineStr"/>
+      <c r="BB290" t="inlineStr"/>
+      <c r="BC290" t="inlineStr"/>
+      <c r="BD290" t="inlineStr"/>
+      <c r="BE290" t="inlineStr"/>
+      <c r="BF290" t="inlineStr"/>
+      <c r="BG290" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="BH290" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BI290" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="BJ290" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="BK290" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BL290" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="1" t="inlineStr">
+        <is>
+          <t>KUYo2Eo9</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>19.10.2024 08:00</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>Weisbach E.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>Heinz-von-Heiden-Arena
+ (Hannover)</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>49 200</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>49 000</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>dfNCCCzS</t>
+        </is>
+      </c>
+      <c r="J291" t="inlineStr">
+        <is>
+          <t>Hannover</t>
+        </is>
+      </c>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>0Ija0Ej9</t>
+        </is>
+      </c>
+      <c r="L291" t="inlineStr">
+        <is>
+          <t>Schalke</t>
+        </is>
+      </c>
+      <c r="M291" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="N291" t="inlineStr">
+        <is>
+          <t>0.26</t>
+        </is>
+      </c>
+      <c r="O291" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="P291" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="Q291" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="R291" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="S291" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T291" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U291" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="V291" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="W291" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="X291" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="Y291" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Z291" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA291" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB291" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC291" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AD291" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="AE291" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AF291" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AG291" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AH291" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AI291" t="inlineStr"/>
+      <c r="AJ291" t="inlineStr"/>
+      <c r="AK291" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AL291" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AM291" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="AN291" t="inlineStr">
+        <is>
+          <t>436</t>
+        </is>
+      </c>
+      <c r="AO291" t="inlineStr">
+        <is>
+          <t>324</t>
+        </is>
+      </c>
+      <c r="AP291" t="inlineStr">
+        <is>
+          <t>353</t>
+        </is>
+      </c>
+      <c r="AQ291" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="AR291" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="AS291" t="inlineStr">
+        <is>
+          <t>t0ZPdkUl</t>
+        </is>
+      </c>
+      <c r="AT291" t="inlineStr">
+        <is>
+          <t>leitl stefan</t>
+        </is>
+      </c>
+      <c r="AU291" t="inlineStr">
+        <is>
+          <t>SMaB5LKo</t>
+        </is>
+      </c>
+      <c r="AV291" t="inlineStr">
+        <is>
+          <t>van wonderen kees</t>
+        </is>
+      </c>
+      <c r="AW291" t="n">
+        <v>59</v>
+      </c>
+      <c r="AX291" t="n">
+        <v>592</v>
+      </c>
+      <c r="AY291" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ291" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BA291" t="inlineStr"/>
+      <c r="BB291" t="inlineStr"/>
+      <c r="BC291" t="inlineStr"/>
+      <c r="BD291" t="inlineStr"/>
+      <c r="BE291" t="inlineStr"/>
+      <c r="BF291" t="inlineStr"/>
+      <c r="BG291" t="inlineStr"/>
+      <c r="BH291" t="inlineStr"/>
+      <c r="BI291" t="inlineStr"/>
+      <c r="BJ291" t="inlineStr"/>
+      <c r="BK291" t="inlineStr"/>
+      <c r="BL291" t="inlineStr"/>
+    </row>
+    <row r="292">
+      <c r="A292" s="1" t="inlineStr">
+        <is>
+          <t>r9D87Uvn</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>19.10.2024 08:00</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>Haslberger W.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>Preussenstadion
+ (Munster)</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>12 794</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>11 500</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>zedZaSL7</t>
+        </is>
+      </c>
+      <c r="J292" t="inlineStr">
+        <is>
+          <t>Preussen Munster</t>
+        </is>
+      </c>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>6in2Eknb</t>
+        </is>
+      </c>
+      <c r="L292" t="inlineStr">
+        <is>
+          <t>Elversberg</t>
+        </is>
+      </c>
+      <c r="M292" t="inlineStr">
+        <is>
+          <t>0.56</t>
+        </is>
+      </c>
+      <c r="N292" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="O292" t="inlineStr">
+        <is>
+          <t>35%</t>
+        </is>
+      </c>
+      <c r="P292" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
+      <c r="Q292" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R292" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="S292" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T292" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U292" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V292" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="W292" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="X292" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="Y292" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Z292" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA292" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB292" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC292" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AD292" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="AE292" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AF292" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG292" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AH292" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AI292" t="inlineStr"/>
+      <c r="AJ292" t="inlineStr"/>
+      <c r="AK292" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AL292" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM292" t="inlineStr">
+        <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="AN292" t="inlineStr">
+        <is>
+          <t>581</t>
+        </is>
+      </c>
+      <c r="AO292" t="inlineStr">
+        <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="AP292" t="inlineStr">
+        <is>
+          <t>535</t>
+        </is>
+      </c>
+      <c r="AQ292" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="AR292" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="AS292" t="inlineStr">
+        <is>
+          <t>pdPRS0me</t>
+        </is>
+      </c>
+      <c r="AT292" t="inlineStr">
+        <is>
+          <t>hildmann sascha</t>
+        </is>
+      </c>
+      <c r="AU292" t="inlineStr">
+        <is>
+          <t>8E8qmw3d</t>
+        </is>
+      </c>
+      <c r="AV292" t="inlineStr">
+        <is>
+          <t>steffen horst</t>
+        </is>
+      </c>
+      <c r="AW292" t="n">
+        <v>59</v>
+      </c>
+      <c r="AX292" t="n">
+        <v>592</v>
+      </c>
+      <c r="AY292" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ292" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BA292" t="inlineStr"/>
+      <c r="BB292" t="inlineStr"/>
+      <c r="BC292" t="inlineStr"/>
+      <c r="BD292" t="inlineStr"/>
+      <c r="BE292" t="inlineStr"/>
+      <c r="BF292" t="inlineStr"/>
+      <c r="BG292" t="inlineStr"/>
+      <c r="BH292" t="inlineStr"/>
+      <c r="BI292" t="inlineStr"/>
+      <c r="BJ292" t="inlineStr"/>
+      <c r="BK292" t="inlineStr"/>
+      <c r="BL292" t="inlineStr"/>
+    </row>
+    <row r="293">
+      <c r="A293" s="1" t="inlineStr">
+        <is>
+          <t>l6GG589b</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>19.10.2024 08:00</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>Benen L.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>Jahnstadion Regensburg
+ (Regensburg)</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>15 210</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>12 310</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t>UiCmEP56</t>
+        </is>
+      </c>
+      <c r="J293" t="inlineStr">
+        <is>
+          <t>Regensburg</t>
+        </is>
+      </c>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>ne1oL3y7</t>
+        </is>
+      </c>
+      <c r="L293" t="inlineStr">
+        <is>
+          <t>Dusseldorf</t>
+        </is>
+      </c>
+      <c r="M293" t="inlineStr">
+        <is>
+          <t>0.71</t>
+        </is>
+      </c>
+      <c r="N293" t="inlineStr">
+        <is>
+          <t>2.82</t>
+        </is>
+      </c>
+      <c r="O293" t="inlineStr">
+        <is>
+          <t>49%</t>
+        </is>
+      </c>
+      <c r="P293" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="Q293" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R293" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="S293" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T293" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U293" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V293" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="W293" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="X293" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="Y293" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Z293" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA293" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB293" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC293" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AD293" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AE293" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AF293" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AG293" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AH293" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AI293" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AJ293" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK293" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AL293" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM293" t="inlineStr">
+        <is>
+          <t>331</t>
+        </is>
+      </c>
+      <c r="AN293" t="inlineStr">
+        <is>
+          <t>380</t>
+        </is>
+      </c>
+      <c r="AO293" t="inlineStr">
+        <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="AP293" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="AQ293" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="AR293" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="AS293" t="inlineStr">
+        <is>
+          <t>zyLSrbZQ</t>
+        </is>
+      </c>
+      <c r="AT293" t="inlineStr">
+        <is>
+          <t>enochs joe</t>
+        </is>
+      </c>
+      <c r="AU293" t="inlineStr">
+        <is>
+          <t>AoL97rX8</t>
+        </is>
+      </c>
+      <c r="AV293" t="inlineStr">
+        <is>
+          <t>thioune daniel</t>
+        </is>
+      </c>
+      <c r="AW293" t="n">
+        <v>59</v>
+      </c>
+      <c r="AX293" t="n">
+        <v>592</v>
+      </c>
+      <c r="AY293" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ293" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BA293" t="inlineStr"/>
+      <c r="BB293" t="inlineStr"/>
+      <c r="BC293" t="inlineStr"/>
+      <c r="BD293" t="inlineStr"/>
+      <c r="BE293" t="inlineStr"/>
+      <c r="BF293" t="inlineStr"/>
+      <c r="BG293" t="inlineStr"/>
+      <c r="BH293" t="inlineStr"/>
+      <c r="BI293" t="inlineStr"/>
+      <c r="BJ293" t="inlineStr"/>
+      <c r="BK293" t="inlineStr"/>
+      <c r="BL293" t="inlineStr"/>
+    </row>
+    <row r="294">
+      <c r="A294" s="1" t="inlineStr">
+        <is>
+          <t>W8hitXOk</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>18.10.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>Willenborg F.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>Merck-Stadion am Bollenfalltor
+ (Darmstadt)</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>17 810</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>17 810</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>S0hPB9rA</t>
+        </is>
+      </c>
+      <c r="J294" t="inlineStr">
+        <is>
+          <t>Darmstadt</t>
+        </is>
+      </c>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>WG9pOTse</t>
+        </is>
+      </c>
+      <c r="L294" t="inlineStr">
+        <is>
+          <t>FC Koln</t>
+        </is>
+      </c>
+      <c r="M294" t="inlineStr">
+        <is>
+          <t>2.56</t>
+        </is>
+      </c>
+      <c r="N294" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="O294" t="inlineStr">
+        <is>
+          <t>41%</t>
+        </is>
+      </c>
+      <c r="P294" t="inlineStr">
+        <is>
+          <t>59%</t>
+        </is>
+      </c>
+      <c r="Q294" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R294" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="S294" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T294" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="U294" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V294" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="W294" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="X294" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="Y294" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Z294" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA294" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB294" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC294" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AD294" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="AE294" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AF294" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AG294" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AH294" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AI294" t="inlineStr"/>
+      <c r="AJ294" t="inlineStr"/>
+      <c r="AK294" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL294" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM294" t="inlineStr">
+        <is>
+          <t>417</t>
+        </is>
+      </c>
+      <c r="AN294" t="inlineStr">
+        <is>
+          <t>647</t>
+        </is>
+      </c>
+      <c r="AO294" t="inlineStr">
+        <is>
+          <t>312</t>
+        </is>
+      </c>
+      <c r="AP294" t="inlineStr">
+        <is>
+          <t>579</t>
+        </is>
+      </c>
+      <c r="AQ294" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="AR294" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="AS294" t="inlineStr">
+        <is>
+          <t>4dKVOnA1</t>
+        </is>
+      </c>
+      <c r="AT294" t="inlineStr">
+        <is>
+          <t>kohfeldt florian</t>
+        </is>
+      </c>
+      <c r="AU294" t="inlineStr">
+        <is>
+          <t>4fX0k7gg</t>
+        </is>
+      </c>
+      <c r="AV294" t="inlineStr">
+        <is>
+          <t>struber gerhard</t>
+        </is>
+      </c>
+      <c r="AW294" t="n">
+        <v>59</v>
+      </c>
+      <c r="AX294" t="n">
+        <v>592</v>
+      </c>
+      <c r="AY294" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ294" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BA294" t="inlineStr"/>
+      <c r="BB294" t="inlineStr"/>
+      <c r="BC294" t="inlineStr"/>
+      <c r="BD294" t="inlineStr"/>
+      <c r="BE294" t="inlineStr"/>
+      <c r="BF294" t="inlineStr"/>
+      <c r="BG294" t="inlineStr"/>
+      <c r="BH294" t="inlineStr"/>
+      <c r="BI294" t="inlineStr"/>
+      <c r="BJ294" t="inlineStr"/>
+      <c r="BK294" t="inlineStr"/>
+      <c r="BL294" t="inlineStr"/>
+    </row>
+    <row r="295">
+      <c r="A295" s="1" t="inlineStr">
+        <is>
+          <t>nqkSsp0f</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>18.10.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>Braun R.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>Olympiastadion
+ (Berlin)</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>74 667</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>45 457</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I295" t="inlineStr">
+        <is>
+          <t>2y0u8Wrq</t>
+        </is>
+      </c>
+      <c r="J295" t="inlineStr">
+        <is>
+          <t>Hertha Berlin</t>
+        </is>
+      </c>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>QqLCC3il</t>
+        </is>
+      </c>
+      <c r="L295" t="inlineStr">
+        <is>
+          <t>Braunschweig</t>
+        </is>
+      </c>
+      <c r="M295" t="inlineStr">
+        <is>
+          <t>2.28</t>
+        </is>
+      </c>
+      <c r="N295" t="inlineStr">
+        <is>
+          <t>0.27</t>
+        </is>
+      </c>
+      <c r="O295" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="P295" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="Q295" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R295" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="S295" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T295" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U295" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="V295" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W295" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="X295" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="Y295" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Z295" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA295" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB295" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC295" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AD295" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AE295" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AF295" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AG295" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AH295" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AI295" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AJ295" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AK295" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AL295" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM295" t="inlineStr">
+        <is>
+          <t>526</t>
+        </is>
+      </c>
+      <c r="AN295" t="inlineStr">
+        <is>
+          <t>294</t>
+        </is>
+      </c>
+      <c r="AO295" t="inlineStr">
+        <is>
+          <t>468</t>
+        </is>
+      </c>
+      <c r="AP295" t="inlineStr">
+        <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="AQ295" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="AR295" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="AS295" t="inlineStr">
+        <is>
+          <t>YmfcAeCo</t>
+        </is>
+      </c>
+      <c r="AT295" t="inlineStr">
+        <is>
+          <t>fiel cristian</t>
+        </is>
+      </c>
+      <c r="AU295" t="inlineStr">
+        <is>
+          <t>SQrxFAMl</t>
+        </is>
+      </c>
+      <c r="AV295" t="inlineStr">
+        <is>
+          <t>scherning daniel</t>
+        </is>
+      </c>
+      <c r="AW295" t="n">
+        <v>59</v>
+      </c>
+      <c r="AX295" t="n">
+        <v>592</v>
+      </c>
+      <c r="AY295" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ295" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BA295" t="inlineStr"/>
+      <c r="BB295" t="inlineStr"/>
+      <c r="BC295" t="inlineStr"/>
+      <c r="BD295" t="inlineStr"/>
+      <c r="BE295" t="inlineStr"/>
+      <c r="BF295" t="inlineStr"/>
+      <c r="BG295" t="inlineStr"/>
+      <c r="BH295" t="inlineStr"/>
+      <c r="BI295" t="inlineStr"/>
+      <c r="BJ295" t="inlineStr"/>
+      <c r="BK295" t="inlineStr"/>
+      <c r="BL295" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/germany/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
+++ b/data/germany/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL295"/>
+  <dimension ref="A1:BL301"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -59426,15 +59426,11 @@
         </is>
       </c>
       <c r="F284" t="inlineStr"/>
-      <c r="G284" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H284" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G284" t="n">
+        <v>4</v>
+      </c>
+      <c r="H284" t="n">
+        <v>0</v>
       </c>
       <c r="I284" t="inlineStr">
         <is>
@@ -59456,15 +59452,11 @@
           <t>Stuttgart</t>
         </is>
       </c>
-      <c r="M284" t="inlineStr">
-        <is>
-          <t>3.27</t>
-        </is>
-      </c>
-      <c r="N284" t="inlineStr">
-        <is>
-          <t>0.40</t>
-        </is>
+      <c r="M284" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="N284" t="n">
+        <v>0.4</v>
       </c>
       <c r="O284" t="inlineStr">
         <is>
@@ -59476,127 +59468,79 @@
           <t>34%</t>
         </is>
       </c>
-      <c r="Q284" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="R284" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="S284" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="T284" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="U284" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="V284" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="W284" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="X284" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y284" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Z284" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA284" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB284" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC284" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AD284" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="AE284" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AF284" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AG284" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AH284" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="Q284" t="n">
+        <v>22</v>
+      </c>
+      <c r="R284" t="n">
+        <v>4</v>
+      </c>
+      <c r="S284" t="n">
+        <v>10</v>
+      </c>
+      <c r="T284" t="n">
+        <v>1</v>
+      </c>
+      <c r="U284" t="n">
+        <v>8</v>
+      </c>
+      <c r="V284" t="n">
+        <v>2</v>
+      </c>
+      <c r="W284" t="n">
+        <v>10</v>
+      </c>
+      <c r="X284" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y284" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z284" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA284" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB284" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC284" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD284" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE284" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF284" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG284" t="n">
+        <v>6</v>
+      </c>
+      <c r="AH284" t="n">
+        <v>10</v>
       </c>
       <c r="AI284" t="inlineStr"/>
       <c r="AJ284" t="inlineStr"/>
-      <c r="AK284" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AL284" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AM284" t="inlineStr">
-        <is>
-          <t>698</t>
-        </is>
-      </c>
-      <c r="AN284" t="inlineStr">
-        <is>
-          <t>362</t>
-        </is>
-      </c>
-      <c r="AO284" t="inlineStr">
-        <is>
-          <t>627</t>
-        </is>
-      </c>
-      <c r="AP284" t="inlineStr">
-        <is>
-          <t>281</t>
-        </is>
+      <c r="AK284" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL284" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM284" t="n">
+        <v>698</v>
+      </c>
+      <c r="AN284" t="n">
+        <v>362</v>
+      </c>
+      <c r="AO284" t="n">
+        <v>627</v>
+      </c>
+      <c r="AP284" t="n">
+        <v>281</v>
       </c>
       <c r="AQ284" t="inlineStr"/>
       <c r="AR284" t="inlineStr"/>
@@ -59640,35 +59584,23 @@
       <c r="BD284" t="inlineStr"/>
       <c r="BE284" t="inlineStr"/>
       <c r="BF284" t="inlineStr"/>
-      <c r="BG284" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="BH284" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BI284" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="BJ284" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="BK284" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="BL284" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
+      <c r="BG284" t="n">
+        <v>4</v>
+      </c>
+      <c r="BH284" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI284" t="n">
+        <v>6</v>
+      </c>
+      <c r="BJ284" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK284" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL284" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="285">
@@ -59704,15 +59636,11 @@
           <t>50 000</t>
         </is>
       </c>
-      <c r="G285" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H285" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G285" t="n">
+        <v>3</v>
+      </c>
+      <c r="H285" t="n">
+        <v>2</v>
       </c>
       <c r="I285" t="inlineStr">
         <is>
@@ -59734,15 +59662,11 @@
           <t>Heidenheim</t>
         </is>
       </c>
-      <c r="M285" t="inlineStr">
-        <is>
-          <t>3.13</t>
-        </is>
-      </c>
-      <c r="N285" t="inlineStr">
-        <is>
-          <t>1.69</t>
-        </is>
+      <c r="M285" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="N285" t="n">
+        <v>1.69</v>
       </c>
       <c r="O285" t="inlineStr">
         <is>
@@ -59754,127 +59678,79 @@
           <t>34%</t>
         </is>
       </c>
-      <c r="Q285" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="R285" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="S285" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="T285" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="U285" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V285" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="W285" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="X285" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Y285" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Z285" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA285" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB285" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC285" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="AD285" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AE285" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AF285" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AG285" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AH285" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="Q285" t="n">
+        <v>20</v>
+      </c>
+      <c r="R285" t="n">
+        <v>19</v>
+      </c>
+      <c r="S285" t="n">
+        <v>10</v>
+      </c>
+      <c r="T285" t="n">
+        <v>6</v>
+      </c>
+      <c r="U285" t="n">
+        <v>7</v>
+      </c>
+      <c r="V285" t="n">
+        <v>6</v>
+      </c>
+      <c r="W285" t="n">
+        <v>9</v>
+      </c>
+      <c r="X285" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y285" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z285" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA285" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB285" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC285" t="n">
+        <v>32</v>
+      </c>
+      <c r="AD285" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE285" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF285" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG285" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH285" t="n">
+        <v>9</v>
       </c>
       <c r="AI285" t="inlineStr"/>
       <c r="AJ285" t="inlineStr"/>
-      <c r="AK285" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AL285" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AM285" t="inlineStr">
-        <is>
-          <t>524</t>
-        </is>
-      </c>
-      <c r="AN285" t="inlineStr">
-        <is>
-          <t>257</t>
-        </is>
-      </c>
-      <c r="AO285" t="inlineStr">
-        <is>
-          <t>428</t>
-        </is>
-      </c>
-      <c r="AP285" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
+      <c r="AK285" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL285" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM285" t="n">
+        <v>524</v>
+      </c>
+      <c r="AN285" t="n">
+        <v>257</v>
+      </c>
+      <c r="AO285" t="n">
+        <v>428</v>
+      </c>
+      <c r="AP285" t="n">
+        <v>176</v>
       </c>
       <c r="AQ285" t="inlineStr"/>
       <c r="AR285" t="inlineStr"/>
@@ -59918,35 +59794,23 @@
       <c r="BD285" t="inlineStr"/>
       <c r="BE285" t="inlineStr"/>
       <c r="BF285" t="inlineStr"/>
-      <c r="BG285" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="BH285" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="BI285" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="BJ285" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="BK285" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="BL285" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="BG285" t="n">
+        <v>3</v>
+      </c>
+      <c r="BH285" t="n">
+        <v>7</v>
+      </c>
+      <c r="BI285" t="n">
+        <v>5</v>
+      </c>
+      <c r="BJ285" t="n">
+        <v>7</v>
+      </c>
+      <c r="BK285" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL285" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="286">
@@ -59982,15 +59846,11 @@
           <t>30 000</t>
         </is>
       </c>
-      <c r="G286" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H286" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G286" t="n">
+        <v>2</v>
+      </c>
+      <c r="H286" t="n">
+        <v>1</v>
       </c>
       <c r="I286" t="inlineStr">
         <is>
@@ -60012,15 +59872,11 @@
           <t>Eintracht Frankfurt</t>
         </is>
       </c>
-      <c r="M286" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
-      </c>
-      <c r="N286" t="inlineStr">
-        <is>
-          <t>1.78</t>
-        </is>
+      <c r="M286" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="N286" t="n">
+        <v>1.78</v>
       </c>
       <c r="O286" t="inlineStr">
         <is>
@@ -60032,127 +59888,79 @@
           <t>46%</t>
         </is>
       </c>
-      <c r="Q286" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="R286" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="S286" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="T286" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U286" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="V286" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="W286" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="X286" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y286" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Z286" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA286" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB286" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC286" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AD286" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AE286" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AF286" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AG286" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AH286" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="Q286" t="n">
+        <v>27</v>
+      </c>
+      <c r="R286" t="n">
+        <v>9</v>
+      </c>
+      <c r="S286" t="n">
+        <v>9</v>
+      </c>
+      <c r="T286" t="n">
+        <v>2</v>
+      </c>
+      <c r="U286" t="n">
+        <v>10</v>
+      </c>
+      <c r="V286" t="n">
+        <v>4</v>
+      </c>
+      <c r="W286" t="n">
+        <v>5</v>
+      </c>
+      <c r="X286" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y286" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z286" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA286" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB286" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC286" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD286" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE286" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF286" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG286" t="n">
+        <v>9</v>
+      </c>
+      <c r="AH286" t="n">
+        <v>5</v>
       </c>
       <c r="AI286" t="inlineStr"/>
       <c r="AJ286" t="inlineStr"/>
-      <c r="AK286" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL286" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AM286" t="inlineStr">
-        <is>
-          <t>542</t>
-        </is>
-      </c>
-      <c r="AN286" t="inlineStr">
-        <is>
-          <t>470</t>
-        </is>
-      </c>
-      <c r="AO286" t="inlineStr">
-        <is>
-          <t>497</t>
-        </is>
-      </c>
-      <c r="AP286" t="inlineStr">
-        <is>
-          <t>412</t>
-        </is>
+      <c r="AK286" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL286" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM286" t="n">
+        <v>542</v>
+      </c>
+      <c r="AN286" t="n">
+        <v>470</v>
+      </c>
+      <c r="AO286" t="n">
+        <v>497</v>
+      </c>
+      <c r="AP286" t="n">
+        <v>412</v>
       </c>
       <c r="AQ286" t="inlineStr"/>
       <c r="AR286" t="inlineStr"/>
@@ -60196,35 +60004,23 @@
       <c r="BD286" t="inlineStr"/>
       <c r="BE286" t="inlineStr"/>
       <c r="BF286" t="inlineStr"/>
-      <c r="BG286" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="BH286" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="BI286" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="BJ286" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BK286" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="BL286" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="BG286" t="n">
+        <v>8</v>
+      </c>
+      <c r="BH286" t="n">
+        <v>3</v>
+      </c>
+      <c r="BI286" t="n">
+        <v>12</v>
+      </c>
+      <c r="BJ286" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK286" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL286" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="287">
@@ -60260,15 +60056,11 @@
           <t>33 500</t>
         </is>
       </c>
-      <c r="G287" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H287" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G287" t="n">
+        <v>3</v>
+      </c>
+      <c r="H287" t="n">
+        <v>1</v>
       </c>
       <c r="I287" t="inlineStr">
         <is>
@@ -60290,15 +60082,11 @@
           <t>Augsburg</t>
         </is>
       </c>
-      <c r="M287" t="inlineStr">
-        <is>
-          <t>0.73</t>
-        </is>
-      </c>
-      <c r="N287" t="inlineStr">
-        <is>
-          <t>0.56</t>
-        </is>
+      <c r="M287" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="N287" t="n">
+        <v>0.5600000000000001</v>
       </c>
       <c r="O287" t="inlineStr">
         <is>
@@ -60310,127 +60098,79 @@
           <t>43%</t>
         </is>
       </c>
-      <c r="Q287" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="R287" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="S287" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="T287" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="U287" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="V287" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="W287" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="X287" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="Y287" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Z287" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA287" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB287" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC287" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AD287" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AE287" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AF287" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AG287" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AH287" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="Q287" t="n">
+        <v>15</v>
+      </c>
+      <c r="R287" t="n">
+        <v>9</v>
+      </c>
+      <c r="S287" t="n">
+        <v>6</v>
+      </c>
+      <c r="T287" t="n">
+        <v>3</v>
+      </c>
+      <c r="U287" t="n">
+        <v>4</v>
+      </c>
+      <c r="V287" t="n">
+        <v>6</v>
+      </c>
+      <c r="W287" t="n">
+        <v>7</v>
+      </c>
+      <c r="X287" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y287" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z287" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA287" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB287" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC287" t="n">
+        <v>18</v>
+      </c>
+      <c r="AD287" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE287" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF287" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG287" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH287" t="n">
+        <v>7</v>
       </c>
       <c r="AI287" t="inlineStr"/>
       <c r="AJ287" t="inlineStr"/>
-      <c r="AK287" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL287" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AM287" t="inlineStr">
-        <is>
-          <t>578</t>
-        </is>
-      </c>
-      <c r="AN287" t="inlineStr">
-        <is>
-          <t>429</t>
-        </is>
-      </c>
-      <c r="AO287" t="inlineStr">
-        <is>
-          <t>478</t>
-        </is>
-      </c>
-      <c r="AP287" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
+      <c r="AK287" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL287" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM287" t="n">
+        <v>578</v>
+      </c>
+      <c r="AN287" t="n">
+        <v>429</v>
+      </c>
+      <c r="AO287" t="n">
+        <v>478</v>
+      </c>
+      <c r="AP287" t="n">
+        <v>350</v>
       </c>
       <c r="AQ287" t="inlineStr"/>
       <c r="AR287" t="inlineStr"/>
@@ -60474,35 +60214,23 @@
       <c r="BD287" t="inlineStr"/>
       <c r="BE287" t="inlineStr"/>
       <c r="BF287" t="inlineStr"/>
-      <c r="BG287" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="BH287" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BI287" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="BJ287" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="BK287" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="BL287" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="BG287" t="n">
+        <v>5</v>
+      </c>
+      <c r="BH287" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI287" t="n">
+        <v>8</v>
+      </c>
+      <c r="BJ287" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK287" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL287" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="288">
@@ -60538,15 +60266,11 @@
           <t>19 281</t>
         </is>
       </c>
-      <c r="G288" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H288" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G288" t="n">
+        <v>3</v>
+      </c>
+      <c r="H288" t="n">
+        <v>1</v>
       </c>
       <c r="I288" t="inlineStr">
         <is>
@@ -60568,15 +60292,11 @@
           <t>Bochum</t>
         </is>
       </c>
-      <c r="M288" t="inlineStr">
-        <is>
-          <t>2.40</t>
-        </is>
-      </c>
-      <c r="N288" t="inlineStr">
-        <is>
-          <t>2.32</t>
-        </is>
+      <c r="M288" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="N288" t="n">
+        <v>2.32</v>
       </c>
       <c r="O288" t="inlineStr">
         <is>
@@ -60588,127 +60308,79 @@
           <t>50%</t>
         </is>
       </c>
-      <c r="Q288" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="R288" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="S288" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="T288" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U288" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="V288" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="W288" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="X288" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="Y288" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Z288" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA288" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AB288" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC288" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AD288" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="AE288" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AF288" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AG288" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AH288" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="Q288" t="n">
+        <v>12</v>
+      </c>
+      <c r="R288" t="n">
+        <v>13</v>
+      </c>
+      <c r="S288" t="n">
+        <v>7</v>
+      </c>
+      <c r="T288" t="n">
+        <v>4</v>
+      </c>
+      <c r="U288" t="n">
+        <v>4</v>
+      </c>
+      <c r="V288" t="n">
+        <v>5</v>
+      </c>
+      <c r="W288" t="n">
+        <v>12</v>
+      </c>
+      <c r="X288" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y288" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z288" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA288" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB288" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC288" t="n">
+        <v>20</v>
+      </c>
+      <c r="AD288" t="n">
+        <v>28</v>
+      </c>
+      <c r="AE288" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF288" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG288" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH288" t="n">
+        <v>12</v>
       </c>
       <c r="AI288" t="inlineStr"/>
       <c r="AJ288" t="inlineStr"/>
-      <c r="AK288" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL288" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AM288" t="inlineStr">
-        <is>
-          <t>411</t>
-        </is>
-      </c>
-      <c r="AN288" t="inlineStr">
-        <is>
-          <t>418</t>
-        </is>
-      </c>
-      <c r="AO288" t="inlineStr">
-        <is>
-          <t>319</t>
-        </is>
-      </c>
-      <c r="AP288" t="inlineStr">
-        <is>
-          <t>326</t>
-        </is>
+      <c r="AK288" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL288" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM288" t="n">
+        <v>411</v>
+      </c>
+      <c r="AN288" t="n">
+        <v>418</v>
+      </c>
+      <c r="AO288" t="n">
+        <v>319</v>
+      </c>
+      <c r="AP288" t="n">
+        <v>326</v>
       </c>
       <c r="AQ288" t="inlineStr"/>
       <c r="AR288" t="inlineStr"/>
@@ -60752,35 +60424,23 @@
       <c r="BD288" t="inlineStr"/>
       <c r="BE288" t="inlineStr"/>
       <c r="BF288" t="inlineStr"/>
-      <c r="BG288" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BH288" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="BI288" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="BJ288" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="BK288" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="BL288" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="BG288" t="n">
+        <v>1</v>
+      </c>
+      <c r="BH288" t="n">
+        <v>4</v>
+      </c>
+      <c r="BI288" t="n">
+        <v>5</v>
+      </c>
+      <c r="BJ288" t="n">
+        <v>5</v>
+      </c>
+      <c r="BK288" t="n">
+        <v>12</v>
+      </c>
+      <c r="BL288" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="289">
@@ -60816,15 +60476,11 @@
           <t>30 100</t>
         </is>
       </c>
-      <c r="G289" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H289" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G289" t="n">
+        <v>0</v>
+      </c>
+      <c r="H289" t="n">
+        <v>2</v>
       </c>
       <c r="I289" t="inlineStr">
         <is>
@@ -60846,15 +60502,11 @@
           <t>RB Leipzig</t>
         </is>
       </c>
-      <c r="M289" t="inlineStr">
-        <is>
-          <t>0.47</t>
-        </is>
-      </c>
-      <c r="N289" t="inlineStr">
-        <is>
-          <t>1.98</t>
-        </is>
+      <c r="M289" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="N289" t="n">
+        <v>1.98</v>
       </c>
       <c r="O289" t="inlineStr">
         <is>
@@ -60866,127 +60518,79 @@
           <t>47%</t>
         </is>
       </c>
-      <c r="Q289" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="R289" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="S289" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="T289" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="U289" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="V289" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="W289" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="X289" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="Y289" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Z289" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA289" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB289" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC289" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AD289" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AE289" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AF289" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AG289" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AH289" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
+      <c r="Q289" t="n">
+        <v>16</v>
+      </c>
+      <c r="R289" t="n">
+        <v>11</v>
+      </c>
+      <c r="S289" t="n">
+        <v>2</v>
+      </c>
+      <c r="T289" t="n">
+        <v>5</v>
+      </c>
+      <c r="U289" t="n">
+        <v>4</v>
+      </c>
+      <c r="V289" t="n">
+        <v>3</v>
+      </c>
+      <c r="W289" t="n">
+        <v>15</v>
+      </c>
+      <c r="X289" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y289" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z289" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA289" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB289" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC289" t="n">
+        <v>17</v>
+      </c>
+      <c r="AD289" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE289" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF289" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG289" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH289" t="n">
+        <v>15</v>
       </c>
       <c r="AI289" t="inlineStr"/>
       <c r="AJ289" t="inlineStr"/>
-      <c r="AK289" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL289" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AM289" t="inlineStr">
-        <is>
-          <t>511</t>
-        </is>
-      </c>
-      <c r="AN289" t="inlineStr">
-        <is>
-          <t>457</t>
-        </is>
-      </c>
-      <c r="AO289" t="inlineStr">
-        <is>
-          <t>402</t>
-        </is>
-      </c>
-      <c r="AP289" t="inlineStr">
-        <is>
-          <t>346</t>
-        </is>
+      <c r="AK289" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL289" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM289" t="n">
+        <v>511</v>
+      </c>
+      <c r="AN289" t="n">
+        <v>457</v>
+      </c>
+      <c r="AO289" t="n">
+        <v>402</v>
+      </c>
+      <c r="AP289" t="n">
+        <v>346</v>
       </c>
       <c r="AQ289" t="inlineStr"/>
       <c r="AR289" t="inlineStr"/>
@@ -61030,35 +60634,23 @@
       <c r="BD289" t="inlineStr"/>
       <c r="BE289" t="inlineStr"/>
       <c r="BF289" t="inlineStr"/>
-      <c r="BG289" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="BH289" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="BI289" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="BJ289" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="BK289" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="BL289" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="BG289" t="n">
+        <v>10</v>
+      </c>
+      <c r="BH289" t="n">
+        <v>3</v>
+      </c>
+      <c r="BI289" t="n">
+        <v>5</v>
+      </c>
+      <c r="BJ289" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK289" t="n">
+        <v>14</v>
+      </c>
+      <c r="BL289" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="290">
@@ -61094,15 +60686,11 @@
           <t>81 365</t>
         </is>
       </c>
-      <c r="G290" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H290" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G290" t="n">
+        <v>2</v>
+      </c>
+      <c r="H290" t="n">
+        <v>1</v>
       </c>
       <c r="I290" t="inlineStr">
         <is>
@@ -61124,15 +60712,11 @@
           <t>St. Pauli</t>
         </is>
       </c>
-      <c r="M290" t="inlineStr">
-        <is>
-          <t>3.46</t>
-        </is>
-      </c>
-      <c r="N290" t="inlineStr">
-        <is>
-          <t>0.58</t>
-        </is>
+      <c r="M290" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="N290" t="n">
+        <v>0.58</v>
       </c>
       <c r="O290" t="inlineStr">
         <is>
@@ -61144,127 +60728,79 @@
           <t>25%</t>
         </is>
       </c>
-      <c r="Q290" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="R290" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="S290" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="T290" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="U290" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="V290" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="W290" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="X290" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y290" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Z290" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA290" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB290" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC290" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AD290" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AE290" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AF290" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AG290" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AH290" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="Q290" t="n">
+        <v>20</v>
+      </c>
+      <c r="R290" t="n">
+        <v>10</v>
+      </c>
+      <c r="S290" t="n">
+        <v>7</v>
+      </c>
+      <c r="T290" t="n">
+        <v>3</v>
+      </c>
+      <c r="U290" t="n">
+        <v>9</v>
+      </c>
+      <c r="V290" t="n">
+        <v>2</v>
+      </c>
+      <c r="W290" t="n">
+        <v>7</v>
+      </c>
+      <c r="X290" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y290" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z290" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA290" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB290" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC290" t="n">
+        <v>21</v>
+      </c>
+      <c r="AD290" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE290" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF290" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG290" t="n">
+        <v>8</v>
+      </c>
+      <c r="AH290" t="n">
+        <v>7</v>
       </c>
       <c r="AI290" t="inlineStr"/>
       <c r="AJ290" t="inlineStr"/>
-      <c r="AK290" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL290" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AM290" t="inlineStr">
-        <is>
-          <t>767</t>
-        </is>
-      </c>
-      <c r="AN290" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="AO290" t="inlineStr">
-        <is>
-          <t>713</t>
-        </is>
-      </c>
-      <c r="AP290" t="inlineStr">
-        <is>
-          <t>189</t>
-        </is>
+      <c r="AK290" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL290" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM290" t="n">
+        <v>767</v>
+      </c>
+      <c r="AN290" t="n">
+        <v>250</v>
+      </c>
+      <c r="AO290" t="n">
+        <v>713</v>
+      </c>
+      <c r="AP290" t="n">
+        <v>189</v>
       </c>
       <c r="AQ290" t="inlineStr"/>
       <c r="AR290" t="inlineStr"/>
@@ -61308,35 +60844,23 @@
       <c r="BD290" t="inlineStr"/>
       <c r="BE290" t="inlineStr"/>
       <c r="BF290" t="inlineStr"/>
-      <c r="BG290" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="BH290" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="BI290" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="BJ290" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="BK290" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="BL290" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="BG290" t="n">
+        <v>4</v>
+      </c>
+      <c r="BH290" t="n">
+        <v>5</v>
+      </c>
+      <c r="BI290" t="n">
+        <v>10</v>
+      </c>
+      <c r="BJ290" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK290" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL290" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="291">
@@ -61372,15 +60896,11 @@
           <t>49 000</t>
         </is>
       </c>
-      <c r="G291" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H291" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G291" t="n">
+        <v>1</v>
+      </c>
+      <c r="H291" t="n">
+        <v>0</v>
       </c>
       <c r="I291" t="inlineStr">
         <is>
@@ -61402,15 +60922,11 @@
           <t>Schalke</t>
         </is>
       </c>
-      <c r="M291" t="inlineStr">
-        <is>
-          <t>1.17</t>
-        </is>
-      </c>
-      <c r="N291" t="inlineStr">
-        <is>
-          <t>0.26</t>
-        </is>
+      <c r="M291" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="N291" t="n">
+        <v>0.26</v>
       </c>
       <c r="O291" t="inlineStr">
         <is>
@@ -61422,137 +60938,85 @@
           <t>48%</t>
         </is>
       </c>
-      <c r="Q291" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="R291" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="S291" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="T291" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U291" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="V291" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="W291" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="X291" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="Y291" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Z291" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA291" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AB291" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AC291" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AD291" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="AE291" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AF291" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AG291" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AH291" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
+      <c r="Q291" t="n">
+        <v>15</v>
+      </c>
+      <c r="R291" t="n">
+        <v>7</v>
+      </c>
+      <c r="S291" t="n">
+        <v>3</v>
+      </c>
+      <c r="T291" t="n">
+        <v>2</v>
+      </c>
+      <c r="U291" t="n">
+        <v>12</v>
+      </c>
+      <c r="V291" t="n">
+        <v>5</v>
+      </c>
+      <c r="W291" t="n">
+        <v>19</v>
+      </c>
+      <c r="X291" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y291" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z291" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA291" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB291" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC291" t="n">
+        <v>21</v>
+      </c>
+      <c r="AD291" t="n">
+        <v>29</v>
+      </c>
+      <c r="AE291" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF291" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG291" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH291" t="n">
+        <v>14</v>
       </c>
       <c r="AI291" t="inlineStr"/>
       <c r="AJ291" t="inlineStr"/>
-      <c r="AK291" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AL291" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AM291" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="AN291" t="inlineStr">
-        <is>
-          <t>436</t>
-        </is>
-      </c>
-      <c r="AO291" t="inlineStr">
-        <is>
-          <t>324</t>
-        </is>
-      </c>
-      <c r="AP291" t="inlineStr">
-        <is>
-          <t>353</t>
-        </is>
-      </c>
-      <c r="AQ291" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="AR291" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
+      <c r="AK291" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL291" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM291" t="n">
+        <v>400</v>
+      </c>
+      <c r="AN291" t="n">
+        <v>436</v>
+      </c>
+      <c r="AO291" t="n">
+        <v>324</v>
+      </c>
+      <c r="AP291" t="n">
+        <v>353</v>
+      </c>
+      <c r="AQ291" t="n">
+        <v>109</v>
+      </c>
+      <c r="AR291" t="n">
+        <v>111</v>
       </c>
       <c r="AS291" t="inlineStr">
         <is>
@@ -61634,15 +61098,11 @@
           <t>11 500</t>
         </is>
       </c>
-      <c r="G292" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H292" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G292" t="n">
+        <v>1</v>
+      </c>
+      <c r="H292" t="n">
+        <v>1</v>
       </c>
       <c r="I292" t="inlineStr">
         <is>
@@ -61664,15 +61124,11 @@
           <t>Elversberg</t>
         </is>
       </c>
-      <c r="M292" t="inlineStr">
-        <is>
-          <t>0.56</t>
-        </is>
-      </c>
-      <c r="N292" t="inlineStr">
-        <is>
-          <t>1.44</t>
-        </is>
+      <c r="M292" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="N292" t="n">
+        <v>1.44</v>
       </c>
       <c r="O292" t="inlineStr">
         <is>
@@ -61684,137 +61140,85 @@
           <t>65%</t>
         </is>
       </c>
-      <c r="Q292" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R292" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="S292" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="T292" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U292" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="V292" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="W292" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="X292" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="Y292" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Z292" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA292" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB292" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC292" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AD292" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="AE292" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AF292" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG292" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AH292" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="Q292" t="n">
+        <v>5</v>
+      </c>
+      <c r="R292" t="n">
+        <v>17</v>
+      </c>
+      <c r="S292" t="n">
+        <v>1</v>
+      </c>
+      <c r="T292" t="n">
+        <v>4</v>
+      </c>
+      <c r="U292" t="n">
+        <v>4</v>
+      </c>
+      <c r="V292" t="n">
+        <v>13</v>
+      </c>
+      <c r="W292" t="n">
+        <v>8</v>
+      </c>
+      <c r="X292" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y292" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z292" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA292" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB292" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC292" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD292" t="n">
+        <v>33</v>
+      </c>
+      <c r="AE292" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF292" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG292" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH292" t="n">
+        <v>7</v>
       </c>
       <c r="AI292" t="inlineStr"/>
       <c r="AJ292" t="inlineStr"/>
-      <c r="AK292" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AL292" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AM292" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
-      </c>
-      <c r="AN292" t="inlineStr">
-        <is>
-          <t>581</t>
-        </is>
-      </c>
-      <c r="AO292" t="inlineStr">
-        <is>
-          <t>169</t>
-        </is>
-      </c>
-      <c r="AP292" t="inlineStr">
-        <is>
-          <t>535</t>
-        </is>
-      </c>
-      <c r="AQ292" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
-      <c r="AR292" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
+      <c r="AK292" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL292" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM292" t="n">
+        <v>232</v>
+      </c>
+      <c r="AN292" t="n">
+        <v>581</v>
+      </c>
+      <c r="AO292" t="n">
+        <v>169</v>
+      </c>
+      <c r="AP292" t="n">
+        <v>535</v>
+      </c>
+      <c r="AQ292" t="n">
+        <v>119</v>
+      </c>
+      <c r="AR292" t="n">
+        <v>117</v>
       </c>
       <c r="AS292" t="inlineStr">
         <is>
@@ -61896,15 +61300,11 @@
           <t>12 310</t>
         </is>
       </c>
-      <c r="G293" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H293" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="G293" t="n">
+        <v>0</v>
+      </c>
+      <c r="H293" t="n">
+        <v>3</v>
       </c>
       <c r="I293" t="inlineStr">
         <is>
@@ -61926,15 +61326,11 @@
           <t>Dusseldorf</t>
         </is>
       </c>
-      <c r="M293" t="inlineStr">
-        <is>
-          <t>0.71</t>
-        </is>
-      </c>
-      <c r="N293" t="inlineStr">
-        <is>
-          <t>2.82</t>
-        </is>
+      <c r="M293" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="N293" t="n">
+        <v>2.82</v>
       </c>
       <c r="O293" t="inlineStr">
         <is>
@@ -61946,145 +61342,89 @@
           <t>51%</t>
         </is>
       </c>
-      <c r="Q293" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="R293" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="S293" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="T293" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U293" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="V293" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="W293" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="X293" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="Y293" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Z293" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA293" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB293" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC293" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AD293" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AE293" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AF293" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AG293" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AH293" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AI293" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AJ293" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK293" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AL293" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AM293" t="inlineStr">
-        <is>
-          <t>331</t>
-        </is>
-      </c>
-      <c r="AN293" t="inlineStr">
-        <is>
-          <t>380</t>
-        </is>
-      </c>
-      <c r="AO293" t="inlineStr">
-        <is>
-          <t>265</t>
-        </is>
-      </c>
-      <c r="AP293" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="AQ293" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="AR293" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
+      <c r="Q293" t="n">
+        <v>10</v>
+      </c>
+      <c r="R293" t="n">
+        <v>15</v>
+      </c>
+      <c r="S293" t="n">
+        <v>5</v>
+      </c>
+      <c r="T293" t="n">
+        <v>4</v>
+      </c>
+      <c r="U293" t="n">
+        <v>5</v>
+      </c>
+      <c r="V293" t="n">
+        <v>11</v>
+      </c>
+      <c r="W293" t="n">
+        <v>13</v>
+      </c>
+      <c r="X293" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y293" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z293" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA293" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB293" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC293" t="n">
+        <v>20</v>
+      </c>
+      <c r="AD293" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE293" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF293" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG293" t="n">
+        <v>19</v>
+      </c>
+      <c r="AH293" t="n">
+        <v>11</v>
+      </c>
+      <c r="AI293" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ293" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK293" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL293" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM293" t="n">
+        <v>331</v>
+      </c>
+      <c r="AN293" t="n">
+        <v>380</v>
+      </c>
+      <c r="AO293" t="n">
+        <v>265</v>
+      </c>
+      <c r="AP293" t="n">
+        <v>300</v>
+      </c>
+      <c r="AQ293" t="n">
+        <v>113</v>
+      </c>
+      <c r="AR293" t="n">
+        <v>115</v>
       </c>
       <c r="AS293" t="inlineStr">
         <is>
@@ -62166,15 +61506,11 @@
           <t>17 810</t>
         </is>
       </c>
-      <c r="G294" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H294" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G294" t="n">
+        <v>5</v>
+      </c>
+      <c r="H294" t="n">
+        <v>1</v>
       </c>
       <c r="I294" t="inlineStr">
         <is>
@@ -62196,15 +61532,11 @@
           <t>FC Koln</t>
         </is>
       </c>
-      <c r="M294" t="inlineStr">
-        <is>
-          <t>2.56</t>
-        </is>
-      </c>
-      <c r="N294" t="inlineStr">
-        <is>
-          <t>1.55</t>
-        </is>
+      <c r="M294" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="N294" t="n">
+        <v>1.55</v>
       </c>
       <c r="O294" t="inlineStr">
         <is>
@@ -62216,137 +61548,85 @@
           <t>59%</t>
         </is>
       </c>
-      <c r="Q294" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="R294" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="S294" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="T294" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="U294" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="V294" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="W294" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="X294" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="Y294" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Z294" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA294" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB294" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AC294" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AD294" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="AE294" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AF294" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AG294" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AH294" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="Q294" t="n">
+        <v>11</v>
+      </c>
+      <c r="R294" t="n">
+        <v>15</v>
+      </c>
+      <c r="S294" t="n">
+        <v>6</v>
+      </c>
+      <c r="T294" t="n">
+        <v>6</v>
+      </c>
+      <c r="U294" t="n">
+        <v>5</v>
+      </c>
+      <c r="V294" t="n">
+        <v>9</v>
+      </c>
+      <c r="W294" t="n">
+        <v>13</v>
+      </c>
+      <c r="X294" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y294" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z294" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA294" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB294" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC294" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD294" t="n">
+        <v>28</v>
+      </c>
+      <c r="AE294" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF294" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG294" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH294" t="n">
+        <v>10</v>
       </c>
       <c r="AI294" t="inlineStr"/>
       <c r="AJ294" t="inlineStr"/>
-      <c r="AK294" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL294" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AM294" t="inlineStr">
-        <is>
-          <t>417</t>
-        </is>
-      </c>
-      <c r="AN294" t="inlineStr">
-        <is>
-          <t>647</t>
-        </is>
-      </c>
-      <c r="AO294" t="inlineStr">
-        <is>
-          <t>312</t>
-        </is>
-      </c>
-      <c r="AP294" t="inlineStr">
-        <is>
-          <t>579</t>
-        </is>
-      </c>
-      <c r="AQ294" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="AR294" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
+      <c r="AK294" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL294" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM294" t="n">
+        <v>417</v>
+      </c>
+      <c r="AN294" t="n">
+        <v>647</v>
+      </c>
+      <c r="AO294" t="n">
+        <v>312</v>
+      </c>
+      <c r="AP294" t="n">
+        <v>579</v>
+      </c>
+      <c r="AQ294" t="n">
+        <v>125</v>
+      </c>
+      <c r="AR294" t="n">
+        <v>116</v>
       </c>
       <c r="AS294" t="inlineStr">
         <is>
@@ -62428,15 +61708,11 @@
           <t>45 457</t>
         </is>
       </c>
-      <c r="G295" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H295" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G295" t="n">
+        <v>3</v>
+      </c>
+      <c r="H295" t="n">
+        <v>1</v>
       </c>
       <c r="I295" t="inlineStr">
         <is>
@@ -62458,15 +61734,11 @@
           <t>Braunschweig</t>
         </is>
       </c>
-      <c r="M295" t="inlineStr">
-        <is>
-          <t>2.28</t>
-        </is>
-      </c>
-      <c r="N295" t="inlineStr">
-        <is>
-          <t>0.27</t>
-        </is>
+      <c r="M295" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="N295" t="n">
+        <v>0.27</v>
       </c>
       <c r="O295" t="inlineStr">
         <is>
@@ -62478,145 +61750,89 @@
           <t>40%</t>
         </is>
       </c>
-      <c r="Q295" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="R295" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="S295" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="T295" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U295" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="V295" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="W295" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="X295" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="Y295" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Z295" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA295" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB295" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC295" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AD295" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="AE295" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AF295" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AG295" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AH295" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AI295" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ295" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AK295" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AL295" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AM295" t="inlineStr">
-        <is>
-          <t>526</t>
-        </is>
-      </c>
-      <c r="AN295" t="inlineStr">
-        <is>
-          <t>294</t>
-        </is>
-      </c>
-      <c r="AO295" t="inlineStr">
-        <is>
-          <t>468</t>
-        </is>
-      </c>
-      <c r="AP295" t="inlineStr">
-        <is>
-          <t>226</t>
-        </is>
-      </c>
-      <c r="AQ295" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="AR295" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
+      <c r="Q295" t="n">
+        <v>16</v>
+      </c>
+      <c r="R295" t="n">
+        <v>5</v>
+      </c>
+      <c r="S295" t="n">
+        <v>7</v>
+      </c>
+      <c r="T295" t="n">
+        <v>2</v>
+      </c>
+      <c r="U295" t="n">
+        <v>9</v>
+      </c>
+      <c r="V295" t="n">
+        <v>3</v>
+      </c>
+      <c r="W295" t="n">
+        <v>6</v>
+      </c>
+      <c r="X295" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y295" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z295" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA295" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB295" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC295" t="n">
+        <v>17</v>
+      </c>
+      <c r="AD295" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE295" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF295" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG295" t="n">
+        <v>9</v>
+      </c>
+      <c r="AH295" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI295" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ295" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK295" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL295" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM295" t="n">
+        <v>526</v>
+      </c>
+      <c r="AN295" t="n">
+        <v>294</v>
+      </c>
+      <c r="AO295" t="n">
+        <v>468</v>
+      </c>
+      <c r="AP295" t="n">
+        <v>226</v>
+      </c>
+      <c r="AQ295" t="n">
+        <v>116</v>
+      </c>
+      <c r="AR295" t="n">
+        <v>112</v>
       </c>
       <c r="AS295" t="inlineStr">
         <is>
@@ -62665,6 +61881,1634 @@
       <c r="BK295" t="inlineStr"/>
       <c r="BL295" t="inlineStr"/>
     </row>
+    <row r="296">
+      <c r="A296" s="1" t="inlineStr">
+        <is>
+          <t>rPiijklS</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>20.10.2024 12:30</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>Schlager D.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>Volkswagen Arena
+ (Wolfsburg)</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>28 917</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>28 917</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I296" t="inlineStr">
+        <is>
+          <t>nwkTahLL</t>
+        </is>
+      </c>
+      <c r="J296" t="inlineStr">
+        <is>
+          <t>Wolfsburg</t>
+        </is>
+      </c>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>Ig1f1fy3</t>
+        </is>
+      </c>
+      <c r="L296" t="inlineStr">
+        <is>
+          <t>Werder Bremen</t>
+        </is>
+      </c>
+      <c r="M296" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="N296" t="inlineStr">
+        <is>
+          <t>2.08</t>
+        </is>
+      </c>
+      <c r="O296" t="inlineStr">
+        <is>
+          <t>43%</t>
+        </is>
+      </c>
+      <c r="P296" t="inlineStr">
+        <is>
+          <t>57%</t>
+        </is>
+      </c>
+      <c r="Q296" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R296" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="S296" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T296" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="U296" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V296" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W296" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="X296" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="Y296" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Z296" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA296" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB296" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC296" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AD296" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AE296" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AF296" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AG296" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AH296" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AI296" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AJ296" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK296" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL296" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM296" t="inlineStr">
+        <is>
+          <t>390</t>
+        </is>
+      </c>
+      <c r="AN296" t="inlineStr">
+        <is>
+          <t>533</t>
+        </is>
+      </c>
+      <c r="AO296" t="inlineStr">
+        <is>
+          <t>302</t>
+        </is>
+      </c>
+      <c r="AP296" t="inlineStr">
+        <is>
+          <t>436</t>
+        </is>
+      </c>
+      <c r="AQ296" t="inlineStr"/>
+      <c r="AR296" t="inlineStr"/>
+      <c r="AS296" t="inlineStr">
+        <is>
+          <t>f3ddUIXs</t>
+        </is>
+      </c>
+      <c r="AT296" t="inlineStr">
+        <is>
+          <t>hasenhuttl ralph</t>
+        </is>
+      </c>
+      <c r="AU296" t="inlineStr">
+        <is>
+          <t>4fuCGs9P</t>
+        </is>
+      </c>
+      <c r="AV296" t="inlineStr">
+        <is>
+          <t>werner ole</t>
+        </is>
+      </c>
+      <c r="AW296" t="n">
+        <v>59</v>
+      </c>
+      <c r="AX296" t="n">
+        <v>591</v>
+      </c>
+      <c r="AY296" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ296" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BA296" t="inlineStr"/>
+      <c r="BB296" t="inlineStr"/>
+      <c r="BC296" t="inlineStr"/>
+      <c r="BD296" t="inlineStr"/>
+      <c r="BE296" t="inlineStr"/>
+      <c r="BF296" t="inlineStr"/>
+      <c r="BG296" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BH296" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="BI296" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="BJ296" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BK296" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="BL296" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="1" t="inlineStr">
+        <is>
+          <t>nBwH6AY8</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>20.10.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>Gerach T.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>Holstein-Stadion
+ (Kiel)</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>15 034</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>15 034</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t>63WsD2ei</t>
+        </is>
+      </c>
+      <c r="J297" t="inlineStr">
+        <is>
+          <t>Holstein Kiel</t>
+        </is>
+      </c>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>pzHW4oaE</t>
+        </is>
+      </c>
+      <c r="L297" t="inlineStr">
+        <is>
+          <t>Union Berlin</t>
+        </is>
+      </c>
+      <c r="M297" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="N297" t="inlineStr">
+        <is>
+          <t>1.10</t>
+        </is>
+      </c>
+      <c r="O297" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="P297" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
+      </c>
+      <c r="Q297" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R297" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="S297" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T297" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U297" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V297" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W297" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="X297" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y297" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Z297" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA297" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB297" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC297" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="AD297" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AE297" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AF297" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AG297" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AH297" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AI297" t="inlineStr"/>
+      <c r="AJ297" t="inlineStr"/>
+      <c r="AK297" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL297" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM297" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
+      <c r="AN297" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="AO297" t="inlineStr">
+        <is>
+          <t>344</t>
+        </is>
+      </c>
+      <c r="AP297" t="inlineStr">
+        <is>
+          <t>392</t>
+        </is>
+      </c>
+      <c r="AQ297" t="inlineStr"/>
+      <c r="AR297" t="inlineStr"/>
+      <c r="AS297" t="inlineStr">
+        <is>
+          <t>A15eUM4C</t>
+        </is>
+      </c>
+      <c r="AT297" t="inlineStr">
+        <is>
+          <t>rapp marcel</t>
+        </is>
+      </c>
+      <c r="AU297" t="inlineStr">
+        <is>
+          <t>hpYJ6izc</t>
+        </is>
+      </c>
+      <c r="AV297" t="inlineStr">
+        <is>
+          <t>svensson bo</t>
+        </is>
+      </c>
+      <c r="AW297" t="n">
+        <v>59</v>
+      </c>
+      <c r="AX297" t="n">
+        <v>591</v>
+      </c>
+      <c r="AY297" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ297" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BA297" t="inlineStr"/>
+      <c r="BB297" t="inlineStr"/>
+      <c r="BC297" t="inlineStr"/>
+      <c r="BD297" t="inlineStr"/>
+      <c r="BE297" t="inlineStr"/>
+      <c r="BF297" t="inlineStr"/>
+      <c r="BG297" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BH297" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="BI297" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="BJ297" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="BK297" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="BL297" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="1" t="inlineStr">
+        <is>
+          <t>EVjKq6Vs</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>20.10.2024 08:30</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>Exner F.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>Sportpark Ronhof Thomas Sommer
+ (Fürth)</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>16 626</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>16 126</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I298" t="inlineStr">
+        <is>
+          <t>CCQGbik8</t>
+        </is>
+      </c>
+      <c r="J298" t="inlineStr">
+        <is>
+          <t>Greuther Furth</t>
+        </is>
+      </c>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>6FDqshzF</t>
+        </is>
+      </c>
+      <c r="L298" t="inlineStr">
+        <is>
+          <t>Nurnberg</t>
+        </is>
+      </c>
+      <c r="M298" t="inlineStr">
+        <is>
+          <t>0.53</t>
+        </is>
+      </c>
+      <c r="N298" t="inlineStr">
+        <is>
+          <t>3.38</t>
+        </is>
+      </c>
+      <c r="O298" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="P298" t="inlineStr">
+        <is>
+          <t>46%</t>
+        </is>
+      </c>
+      <c r="Q298" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R298" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="S298" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T298" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="U298" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V298" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W298" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="X298" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="Y298" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Z298" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA298" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB298" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AC298" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AD298" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AE298" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AF298" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AG298" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AH298" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AI298" t="inlineStr"/>
+      <c r="AJ298" t="inlineStr"/>
+      <c r="AK298" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AL298" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM298" t="inlineStr">
+        <is>
+          <t>496</t>
+        </is>
+      </c>
+      <c r="AN298" t="inlineStr">
+        <is>
+          <t>379</t>
+        </is>
+      </c>
+      <c r="AO298" t="inlineStr">
+        <is>
+          <t>422</t>
+        </is>
+      </c>
+      <c r="AP298" t="inlineStr">
+        <is>
+          <t>296</t>
+        </is>
+      </c>
+      <c r="AQ298" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="AR298" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="AS298" t="inlineStr">
+        <is>
+          <t>8E86CPuD</t>
+        </is>
+      </c>
+      <c r="AT298" t="inlineStr">
+        <is>
+          <t>zorniger alexander</t>
+        </is>
+      </c>
+      <c r="AU298" t="inlineStr">
+        <is>
+          <t>tO31cZrF</t>
+        </is>
+      </c>
+      <c r="AV298" t="inlineStr">
+        <is>
+          <t>klose miroslav</t>
+        </is>
+      </c>
+      <c r="AW298" t="n">
+        <v>59</v>
+      </c>
+      <c r="AX298" t="n">
+        <v>592</v>
+      </c>
+      <c r="AY298" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ298" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BA298" t="inlineStr"/>
+      <c r="BB298" t="inlineStr"/>
+      <c r="BC298" t="inlineStr"/>
+      <c r="BD298" t="inlineStr"/>
+      <c r="BE298" t="inlineStr"/>
+      <c r="BF298" t="inlineStr"/>
+      <c r="BG298" t="inlineStr"/>
+      <c r="BH298" t="inlineStr"/>
+      <c r="BI298" t="inlineStr"/>
+      <c r="BJ298" t="inlineStr"/>
+      <c r="BK298" t="inlineStr"/>
+      <c r="BL298" t="inlineStr"/>
+    </row>
+    <row r="299">
+      <c r="A299" s="1" t="inlineStr">
+        <is>
+          <t>hOt0vBg2</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>20.10.2024 08:30</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>Jablonski S.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>Volksparkstadion
+ (Hamburg)</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>57 274</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>57 000</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I299" t="inlineStr">
+        <is>
+          <t>v9k3aY5F</t>
+        </is>
+      </c>
+      <c r="J299" t="inlineStr">
+        <is>
+          <t>Hamburger SV</t>
+        </is>
+      </c>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>YFuz2RLm</t>
+        </is>
+      </c>
+      <c r="L299" t="inlineStr">
+        <is>
+          <t>Magdeburg</t>
+        </is>
+      </c>
+      <c r="M299" t="inlineStr">
+        <is>
+          <t>2.32</t>
+        </is>
+      </c>
+      <c r="N299" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="O299" t="inlineStr">
+        <is>
+          <t>42%</t>
+        </is>
+      </c>
+      <c r="P299" t="inlineStr">
+        <is>
+          <t>58%</t>
+        </is>
+      </c>
+      <c r="Q299" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="R299" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="S299" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T299" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U299" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V299" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="W299" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="X299" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y299" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Z299" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA299" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB299" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC299" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AD299" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AE299" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AF299" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AG299" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AH299" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AI299" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AJ299" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK299" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL299" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM299" t="inlineStr">
+        <is>
+          <t>348</t>
+        </is>
+      </c>
+      <c r="AN299" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AO299" t="inlineStr">
+        <is>
+          <t>278</t>
+        </is>
+      </c>
+      <c r="AP299" t="inlineStr">
+        <is>
+          <t>519</t>
+        </is>
+      </c>
+      <c r="AQ299" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="AR299" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="AS299" t="inlineStr">
+        <is>
+          <t>EDRZkDzS</t>
+        </is>
+      </c>
+      <c r="AT299" t="inlineStr">
+        <is>
+          <t>baumgart steffen</t>
+        </is>
+      </c>
+      <c r="AU299" t="inlineStr">
+        <is>
+          <t>IgZoGKFn</t>
+        </is>
+      </c>
+      <c r="AV299" t="inlineStr">
+        <is>
+          <t>titz christian</t>
+        </is>
+      </c>
+      <c r="AW299" t="n">
+        <v>59</v>
+      </c>
+      <c r="AX299" t="n">
+        <v>592</v>
+      </c>
+      <c r="AY299" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ299" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BA299" t="inlineStr"/>
+      <c r="BB299" t="inlineStr"/>
+      <c r="BC299" t="inlineStr"/>
+      <c r="BD299" t="inlineStr"/>
+      <c r="BE299" t="inlineStr"/>
+      <c r="BF299" t="inlineStr"/>
+      <c r="BG299" t="inlineStr"/>
+      <c r="BH299" t="inlineStr"/>
+      <c r="BI299" t="inlineStr"/>
+      <c r="BJ299" t="inlineStr"/>
+      <c r="BK299" t="inlineStr"/>
+      <c r="BL299" t="inlineStr"/>
+    </row>
+    <row r="300">
+      <c r="A300" s="1" t="inlineStr">
+        <is>
+          <t>4rrbmRgU</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>20.10.2024 08:30</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>Bacher M.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>Donaustadion
+ (Ulm)</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>19 500</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>17 400</t>
+        </is>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I300" t="inlineStr">
+        <is>
+          <t>tbC3EcQn</t>
+        </is>
+      </c>
+      <c r="J300" t="inlineStr">
+        <is>
+          <t>Ulm</t>
+        </is>
+      </c>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>EB3q7jbk</t>
+        </is>
+      </c>
+      <c r="L300" t="inlineStr">
+        <is>
+          <t>Karlsruher SC</t>
+        </is>
+      </c>
+      <c r="M300" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="N300" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="O300" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="P300" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="Q300" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R300" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="S300" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T300" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U300" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="V300" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="W300" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="X300" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y300" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Z300" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AA300" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB300" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC300" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="AD300" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AE300" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AF300" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AG300" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AH300" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AI300" t="inlineStr"/>
+      <c r="AJ300" t="inlineStr"/>
+      <c r="AK300" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AL300" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM300" t="inlineStr">
+        <is>
+          <t>420</t>
+        </is>
+      </c>
+      <c r="AN300" t="inlineStr">
+        <is>
+          <t>474</t>
+        </is>
+      </c>
+      <c r="AO300" t="inlineStr">
+        <is>
+          <t>349</t>
+        </is>
+      </c>
+      <c r="AP300" t="inlineStr">
+        <is>
+          <t>408</t>
+        </is>
+      </c>
+      <c r="AQ300" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="AR300" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="AS300" t="inlineStr">
+        <is>
+          <t>QevvB2nf</t>
+        </is>
+      </c>
+      <c r="AT300" t="inlineStr">
+        <is>
+          <t>worle thomas</t>
+        </is>
+      </c>
+      <c r="AU300" t="inlineStr">
+        <is>
+          <t>OzPMRhK3</t>
+        </is>
+      </c>
+      <c r="AV300" t="inlineStr">
+        <is>
+          <t>eichner christian</t>
+        </is>
+      </c>
+      <c r="AW300" t="n">
+        <v>59</v>
+      </c>
+      <c r="AX300" t="n">
+        <v>592</v>
+      </c>
+      <c r="AY300" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ300" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BA300" t="inlineStr"/>
+      <c r="BB300" t="inlineStr"/>
+      <c r="BC300" t="inlineStr"/>
+      <c r="BD300" t="inlineStr"/>
+      <c r="BE300" t="inlineStr"/>
+      <c r="BF300" t="inlineStr"/>
+      <c r="BG300" t="inlineStr"/>
+      <c r="BH300" t="inlineStr"/>
+      <c r="BI300" t="inlineStr"/>
+      <c r="BJ300" t="inlineStr"/>
+      <c r="BK300" t="inlineStr"/>
+      <c r="BL300" t="inlineStr"/>
+    </row>
+    <row r="301">
+      <c r="A301" s="1" t="inlineStr">
+        <is>
+          <t>6o5TuOU6</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>19.10.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>Hempel R.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>Fritz Walter Stadion
+ (Kaiserslautern)</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>49 500</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>41 500</t>
+        </is>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I301" t="inlineStr">
+        <is>
+          <t>naWckLmC</t>
+        </is>
+      </c>
+      <c r="J301" t="inlineStr">
+        <is>
+          <t>Kaiserslautern</t>
+        </is>
+      </c>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>G2Op923t</t>
+        </is>
+      </c>
+      <c r="L301" t="inlineStr">
+        <is>
+          <t>Paderborn</t>
+        </is>
+      </c>
+      <c r="M301" t="inlineStr">
+        <is>
+          <t>2.16</t>
+        </is>
+      </c>
+      <c r="N301" t="inlineStr">
+        <is>
+          <t>1.76</t>
+        </is>
+      </c>
+      <c r="O301" t="inlineStr">
+        <is>
+          <t>36%</t>
+        </is>
+      </c>
+      <c r="P301" t="inlineStr">
+        <is>
+          <t>64%</t>
+        </is>
+      </c>
+      <c r="Q301" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="R301" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="S301" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="T301" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U301" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V301" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="W301" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="X301" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="Y301" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Z301" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA301" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB301" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC301" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AD301" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="AE301" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AF301" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AG301" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AH301" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AI301" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AJ301" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AK301" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AL301" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM301" t="inlineStr">
+        <is>
+          <t>289</t>
+        </is>
+      </c>
+      <c r="AN301" t="inlineStr">
+        <is>
+          <t>559</t>
+        </is>
+      </c>
+      <c r="AO301" t="inlineStr">
+        <is>
+          <t>216</t>
+        </is>
+      </c>
+      <c r="AP301" t="inlineStr">
+        <is>
+          <t>479</t>
+        </is>
+      </c>
+      <c r="AQ301" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="AR301" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="AS301" t="inlineStr">
+        <is>
+          <t>4bJLk19p</t>
+        </is>
+      </c>
+      <c r="AT301" t="inlineStr">
+        <is>
+          <t>anfang marcus</t>
+        </is>
+      </c>
+      <c r="AU301" t="inlineStr">
+        <is>
+          <t>0AI1QUJH</t>
+        </is>
+      </c>
+      <c r="AV301" t="inlineStr">
+        <is>
+          <t>kwasniok lukas</t>
+        </is>
+      </c>
+      <c r="AW301" t="n">
+        <v>59</v>
+      </c>
+      <c r="AX301" t="n">
+        <v>592</v>
+      </c>
+      <c r="AY301" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ301" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BA301" t="inlineStr"/>
+      <c r="BB301" t="inlineStr"/>
+      <c r="BC301" t="inlineStr"/>
+      <c r="BD301" t="inlineStr"/>
+      <c r="BE301" t="inlineStr"/>
+      <c r="BF301" t="inlineStr"/>
+      <c r="BG301" t="inlineStr"/>
+      <c r="BH301" t="inlineStr"/>
+      <c r="BI301" t="inlineStr"/>
+      <c r="BJ301" t="inlineStr"/>
+      <c r="BK301" t="inlineStr"/>
+      <c r="BL301" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/germany/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
+++ b/data/germany/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL301"/>
+  <dimension ref="A1:BL319"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -61914,15 +61914,11 @@
           <t>28 917</t>
         </is>
       </c>
-      <c r="G296" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H296" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="G296" t="n">
+        <v>2</v>
+      </c>
+      <c r="H296" t="n">
+        <v>4</v>
       </c>
       <c r="I296" t="inlineStr">
         <is>
@@ -61944,15 +61940,11 @@
           <t>Werder Bremen</t>
         </is>
       </c>
-      <c r="M296" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
-      </c>
-      <c r="N296" t="inlineStr">
-        <is>
-          <t>2.08</t>
-        </is>
+      <c r="M296" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="N296" t="n">
+        <v>2.08</v>
       </c>
       <c r="O296" t="inlineStr">
         <is>
@@ -61964,135 +61956,83 @@
           <t>57%</t>
         </is>
       </c>
-      <c r="Q296" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="R296" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="S296" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="T296" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="U296" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V296" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="W296" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="X296" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Y296" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Z296" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA296" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AB296" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC296" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AD296" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AE296" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AF296" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AG296" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AH296" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AI296" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AJ296" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK296" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL296" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AM296" t="inlineStr">
-        <is>
-          <t>390</t>
-        </is>
-      </c>
-      <c r="AN296" t="inlineStr">
-        <is>
-          <t>533</t>
-        </is>
-      </c>
-      <c r="AO296" t="inlineStr">
-        <is>
-          <t>302</t>
-        </is>
-      </c>
-      <c r="AP296" t="inlineStr">
-        <is>
-          <t>436</t>
-        </is>
+      <c r="Q296" t="n">
+        <v>14</v>
+      </c>
+      <c r="R296" t="n">
+        <v>15</v>
+      </c>
+      <c r="S296" t="n">
+        <v>6</v>
+      </c>
+      <c r="T296" t="n">
+        <v>7</v>
+      </c>
+      <c r="U296" t="n">
+        <v>7</v>
+      </c>
+      <c r="V296" t="n">
+        <v>4</v>
+      </c>
+      <c r="W296" t="n">
+        <v>9</v>
+      </c>
+      <c r="X296" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y296" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z296" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA296" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB296" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC296" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD296" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE296" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF296" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG296" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH296" t="n">
+        <v>9</v>
+      </c>
+      <c r="AI296" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ296" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK296" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL296" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM296" t="n">
+        <v>390</v>
+      </c>
+      <c r="AN296" t="n">
+        <v>533</v>
+      </c>
+      <c r="AO296" t="n">
+        <v>302</v>
+      </c>
+      <c r="AP296" t="n">
+        <v>436</v>
       </c>
       <c r="AQ296" t="inlineStr"/>
       <c r="AR296" t="inlineStr"/>
@@ -62136,35 +62076,23 @@
       <c r="BD296" t="inlineStr"/>
       <c r="BE296" t="inlineStr"/>
       <c r="BF296" t="inlineStr"/>
-      <c r="BG296" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BH296" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="BI296" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="BJ296" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="BK296" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="BL296" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
+      <c r="BG296" t="n">
+        <v>1</v>
+      </c>
+      <c r="BH296" t="n">
+        <v>4</v>
+      </c>
+      <c r="BI296" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ296" t="n">
+        <v>5</v>
+      </c>
+      <c r="BK296" t="n">
+        <v>12</v>
+      </c>
+      <c r="BL296" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="297">
@@ -62200,15 +62128,11 @@
           <t>15 034</t>
         </is>
       </c>
-      <c r="G297" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H297" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G297" t="n">
+        <v>0</v>
+      </c>
+      <c r="H297" t="n">
+        <v>2</v>
       </c>
       <c r="I297" t="inlineStr">
         <is>
@@ -62230,15 +62154,11 @@
           <t>Union Berlin</t>
         </is>
       </c>
-      <c r="M297" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
-      <c r="N297" t="inlineStr">
-        <is>
-          <t>1.10</t>
-        </is>
+      <c r="M297" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="N297" t="n">
+        <v>1.1</v>
       </c>
       <c r="O297" t="inlineStr">
         <is>
@@ -62250,127 +62170,79 @@
           <t>53%</t>
         </is>
       </c>
-      <c r="Q297" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="R297" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="S297" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="T297" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U297" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="V297" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="W297" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="X297" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y297" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Z297" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA297" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB297" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AC297" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="AD297" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AE297" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AF297" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AG297" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AH297" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="Q297" t="n">
+        <v>12</v>
+      </c>
+      <c r="R297" t="n">
+        <v>14</v>
+      </c>
+      <c r="S297" t="n">
+        <v>5</v>
+      </c>
+      <c r="T297" t="n">
+        <v>4</v>
+      </c>
+      <c r="U297" t="n">
+        <v>6</v>
+      </c>
+      <c r="V297" t="n">
+        <v>6</v>
+      </c>
+      <c r="W297" t="n">
+        <v>11</v>
+      </c>
+      <c r="X297" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y297" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z297" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA297" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB297" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC297" t="n">
+        <v>26</v>
+      </c>
+      <c r="AD297" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE297" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF297" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG297" t="n">
+        <v>8</v>
+      </c>
+      <c r="AH297" t="n">
+        <v>11</v>
       </c>
       <c r="AI297" t="inlineStr"/>
       <c r="AJ297" t="inlineStr"/>
-      <c r="AK297" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL297" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AM297" t="inlineStr">
-        <is>
-          <t>433</t>
-        </is>
-      </c>
-      <c r="AN297" t="inlineStr">
-        <is>
-          <t>480</t>
-        </is>
-      </c>
-      <c r="AO297" t="inlineStr">
-        <is>
-          <t>344</t>
-        </is>
-      </c>
-      <c r="AP297" t="inlineStr">
-        <is>
-          <t>392</t>
-        </is>
+      <c r="AK297" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL297" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM297" t="n">
+        <v>433</v>
+      </c>
+      <c r="AN297" t="n">
+        <v>480</v>
+      </c>
+      <c r="AO297" t="n">
+        <v>344</v>
+      </c>
+      <c r="AP297" t="n">
+        <v>392</v>
       </c>
       <c r="AQ297" t="inlineStr"/>
       <c r="AR297" t="inlineStr"/>
@@ -62414,35 +62286,23 @@
       <c r="BD297" t="inlineStr"/>
       <c r="BE297" t="inlineStr"/>
       <c r="BF297" t="inlineStr"/>
-      <c r="BG297" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BH297" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="BI297" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="BJ297" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="BK297" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="BL297" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="BG297" t="n">
+        <v>1</v>
+      </c>
+      <c r="BH297" t="n">
+        <v>4</v>
+      </c>
+      <c r="BI297" t="n">
+        <v>10</v>
+      </c>
+      <c r="BJ297" t="n">
+        <v>7</v>
+      </c>
+      <c r="BK297" t="n">
+        <v>9</v>
+      </c>
+      <c r="BL297" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="298">
@@ -62478,15 +62338,11 @@
           <t>16 126</t>
         </is>
       </c>
-      <c r="G298" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H298" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="G298" t="n">
+        <v>0</v>
+      </c>
+      <c r="H298" t="n">
+        <v>4</v>
       </c>
       <c r="I298" t="inlineStr">
         <is>
@@ -62508,15 +62364,11 @@
           <t>Nurnberg</t>
         </is>
       </c>
-      <c r="M298" t="inlineStr">
-        <is>
-          <t>0.53</t>
-        </is>
-      </c>
-      <c r="N298" t="inlineStr">
-        <is>
-          <t>3.38</t>
-        </is>
+      <c r="M298" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="N298" t="n">
+        <v>3.38</v>
       </c>
       <c r="O298" t="inlineStr">
         <is>
@@ -62528,137 +62380,85 @@
           <t>46%</t>
         </is>
       </c>
-      <c r="Q298" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R298" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="S298" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="T298" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="U298" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="V298" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="W298" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="X298" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="Y298" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Z298" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA298" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB298" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AC298" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AD298" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AE298" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AF298" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AG298" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AH298" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="Q298" t="n">
+        <v>9</v>
+      </c>
+      <c r="R298" t="n">
+        <v>13</v>
+      </c>
+      <c r="S298" t="n">
+        <v>4</v>
+      </c>
+      <c r="T298" t="n">
+        <v>7</v>
+      </c>
+      <c r="U298" t="n">
+        <v>5</v>
+      </c>
+      <c r="V298" t="n">
+        <v>6</v>
+      </c>
+      <c r="W298" t="n">
+        <v>19</v>
+      </c>
+      <c r="X298" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y298" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z298" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA298" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB298" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC298" t="n">
+        <v>16</v>
+      </c>
+      <c r="AD298" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE298" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF298" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG298" t="n">
+        <v>20</v>
+      </c>
+      <c r="AH298" t="n">
+        <v>10</v>
       </c>
       <c r="AI298" t="inlineStr"/>
       <c r="AJ298" t="inlineStr"/>
-      <c r="AK298" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AL298" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AM298" t="inlineStr">
-        <is>
-          <t>496</t>
-        </is>
-      </c>
-      <c r="AN298" t="inlineStr">
-        <is>
-          <t>379</t>
-        </is>
-      </c>
-      <c r="AO298" t="inlineStr">
-        <is>
-          <t>422</t>
-        </is>
-      </c>
-      <c r="AP298" t="inlineStr">
-        <is>
-          <t>296</t>
-        </is>
-      </c>
-      <c r="AQ298" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="AR298" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
+      <c r="AK298" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL298" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM298" t="n">
+        <v>496</v>
+      </c>
+      <c r="AN298" t="n">
+        <v>379</v>
+      </c>
+      <c r="AO298" t="n">
+        <v>422</v>
+      </c>
+      <c r="AP298" t="n">
+        <v>296</v>
+      </c>
+      <c r="AQ298" t="n">
+        <v>120</v>
+      </c>
+      <c r="AR298" t="n">
+        <v>116</v>
       </c>
       <c r="AS298" t="inlineStr">
         <is>
@@ -62740,15 +62540,11 @@
           <t>57 000</t>
         </is>
       </c>
-      <c r="G299" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H299" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G299" t="n">
+        <v>3</v>
+      </c>
+      <c r="H299" t="n">
+        <v>1</v>
       </c>
       <c r="I299" t="inlineStr">
         <is>
@@ -62770,15 +62566,11 @@
           <t>Magdeburg</t>
         </is>
       </c>
-      <c r="M299" t="inlineStr">
-        <is>
-          <t>2.32</t>
-        </is>
-      </c>
-      <c r="N299" t="inlineStr">
-        <is>
-          <t>1.53</t>
-        </is>
+      <c r="M299" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="N299" t="n">
+        <v>1.53</v>
       </c>
       <c r="O299" t="inlineStr">
         <is>
@@ -62790,145 +62582,89 @@
           <t>58%</t>
         </is>
       </c>
-      <c r="Q299" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="R299" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="S299" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="T299" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="U299" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="V299" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="W299" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="X299" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y299" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Z299" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA299" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB299" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC299" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AD299" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AE299" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AF299" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AG299" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AH299" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AI299" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AJ299" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK299" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL299" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AM299" t="inlineStr">
-        <is>
-          <t>348</t>
-        </is>
-      </c>
-      <c r="AN299" t="inlineStr">
-        <is>
-          <t>549</t>
-        </is>
-      </c>
-      <c r="AO299" t="inlineStr">
-        <is>
-          <t>278</t>
-        </is>
-      </c>
-      <c r="AP299" t="inlineStr">
-        <is>
-          <t>519</t>
-        </is>
-      </c>
-      <c r="AQ299" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="AR299" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
+      <c r="Q299" t="n">
+        <v>13</v>
+      </c>
+      <c r="R299" t="n">
+        <v>14</v>
+      </c>
+      <c r="S299" t="n">
+        <v>5</v>
+      </c>
+      <c r="T299" t="n">
+        <v>3</v>
+      </c>
+      <c r="U299" t="n">
+        <v>8</v>
+      </c>
+      <c r="V299" t="n">
+        <v>11</v>
+      </c>
+      <c r="W299" t="n">
+        <v>12</v>
+      </c>
+      <c r="X299" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y299" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z299" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA299" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB299" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC299" t="n">
+        <v>18</v>
+      </c>
+      <c r="AD299" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE299" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF299" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG299" t="n">
+        <v>7</v>
+      </c>
+      <c r="AH299" t="n">
+        <v>10</v>
+      </c>
+      <c r="AI299" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ299" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK299" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL299" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM299" t="n">
+        <v>348</v>
+      </c>
+      <c r="AN299" t="n">
+        <v>549</v>
+      </c>
+      <c r="AO299" t="n">
+        <v>278</v>
+      </c>
+      <c r="AP299" t="n">
+        <v>519</v>
+      </c>
+      <c r="AQ299" t="n">
+        <v>112</v>
+      </c>
+      <c r="AR299" t="n">
+        <v>116</v>
       </c>
       <c r="AS299" t="inlineStr">
         <is>
@@ -63010,15 +62746,11 @@
           <t>17 400</t>
         </is>
       </c>
-      <c r="G300" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H300" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G300" t="n">
+        <v>0</v>
+      </c>
+      <c r="H300" t="n">
+        <v>1</v>
       </c>
       <c r="I300" t="inlineStr">
         <is>
@@ -63040,15 +62772,11 @@
           <t>Karlsruher SC</t>
         </is>
       </c>
-      <c r="M300" t="inlineStr">
-        <is>
-          <t>0.63</t>
-        </is>
-      </c>
-      <c r="N300" t="inlineStr">
-        <is>
-          <t>1.38</t>
-        </is>
+      <c r="M300" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="N300" t="n">
+        <v>1.38</v>
       </c>
       <c r="O300" t="inlineStr">
         <is>
@@ -63060,137 +62788,85 @@
           <t>50%</t>
         </is>
       </c>
-      <c r="Q300" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="R300" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="S300" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="T300" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="U300" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="V300" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="W300" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="X300" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y300" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Z300" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AA300" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB300" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC300" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="AD300" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="AE300" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AF300" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AG300" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AH300" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="Q300" t="n">
+        <v>11</v>
+      </c>
+      <c r="R300" t="n">
+        <v>16</v>
+      </c>
+      <c r="S300" t="n">
+        <v>2</v>
+      </c>
+      <c r="T300" t="n">
+        <v>3</v>
+      </c>
+      <c r="U300" t="n">
+        <v>9</v>
+      </c>
+      <c r="V300" t="n">
+        <v>13</v>
+      </c>
+      <c r="W300" t="n">
+        <v>7</v>
+      </c>
+      <c r="X300" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y300" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z300" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA300" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB300" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC300" t="n">
+        <v>31</v>
+      </c>
+      <c r="AD300" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE300" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF300" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG300" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH300" t="n">
+        <v>6</v>
       </c>
       <c r="AI300" t="inlineStr"/>
       <c r="AJ300" t="inlineStr"/>
-      <c r="AK300" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AL300" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AM300" t="inlineStr">
-        <is>
-          <t>420</t>
-        </is>
-      </c>
-      <c r="AN300" t="inlineStr">
-        <is>
-          <t>474</t>
-        </is>
-      </c>
-      <c r="AO300" t="inlineStr">
-        <is>
-          <t>349</t>
-        </is>
-      </c>
-      <c r="AP300" t="inlineStr">
-        <is>
-          <t>408</t>
-        </is>
-      </c>
-      <c r="AQ300" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="AR300" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
+      <c r="AK300" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL300" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM300" t="n">
+        <v>420</v>
+      </c>
+      <c r="AN300" t="n">
+        <v>474</v>
+      </c>
+      <c r="AO300" t="n">
+        <v>349</v>
+      </c>
+      <c r="AP300" t="n">
+        <v>408</v>
+      </c>
+      <c r="AQ300" t="n">
+        <v>117</v>
+      </c>
+      <c r="AR300" t="n">
+        <v>112</v>
       </c>
       <c r="AS300" t="inlineStr">
         <is>
@@ -63272,15 +62948,11 @@
           <t>41 500</t>
         </is>
       </c>
-      <c r="G301" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H301" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G301" t="n">
+        <v>3</v>
+      </c>
+      <c r="H301" t="n">
+        <v>0</v>
       </c>
       <c r="I301" t="inlineStr">
         <is>
@@ -63302,15 +62974,11 @@
           <t>Paderborn</t>
         </is>
       </c>
-      <c r="M301" t="inlineStr">
-        <is>
-          <t>2.16</t>
-        </is>
-      </c>
-      <c r="N301" t="inlineStr">
-        <is>
-          <t>1.76</t>
-        </is>
+      <c r="M301" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="N301" t="n">
+        <v>1.76</v>
       </c>
       <c r="O301" t="inlineStr">
         <is>
@@ -63322,145 +62990,89 @@
           <t>64%</t>
         </is>
       </c>
-      <c r="Q301" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="R301" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="S301" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="T301" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U301" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="V301" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="W301" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="X301" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Y301" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Z301" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA301" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AB301" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AC301" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AD301" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="AE301" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AF301" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AG301" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AH301" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI301" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ301" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AK301" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AL301" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AM301" t="inlineStr">
-        <is>
-          <t>289</t>
-        </is>
-      </c>
-      <c r="AN301" t="inlineStr">
-        <is>
-          <t>559</t>
-        </is>
-      </c>
-      <c r="AO301" t="inlineStr">
-        <is>
-          <t>216</t>
-        </is>
-      </c>
-      <c r="AP301" t="inlineStr">
-        <is>
-          <t>479</t>
-        </is>
-      </c>
-      <c r="AQ301" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="AR301" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
+      <c r="Q301" t="n">
+        <v>13</v>
+      </c>
+      <c r="R301" t="n">
+        <v>13</v>
+      </c>
+      <c r="S301" t="n">
+        <v>8</v>
+      </c>
+      <c r="T301" t="n">
+        <v>2</v>
+      </c>
+      <c r="U301" t="n">
+        <v>5</v>
+      </c>
+      <c r="V301" t="n">
+        <v>11</v>
+      </c>
+      <c r="W301" t="n">
+        <v>19</v>
+      </c>
+      <c r="X301" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y301" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z301" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA301" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB301" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC301" t="n">
+        <v>17</v>
+      </c>
+      <c r="AD301" t="n">
+        <v>38</v>
+      </c>
+      <c r="AE301" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF301" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG301" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH301" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI301" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ301" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK301" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL301" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM301" t="n">
+        <v>289</v>
+      </c>
+      <c r="AN301" t="n">
+        <v>559</v>
+      </c>
+      <c r="AO301" t="n">
+        <v>216</v>
+      </c>
+      <c r="AP301" t="n">
+        <v>479</v>
+      </c>
+      <c r="AQ301" t="n">
+        <v>118</v>
+      </c>
+      <c r="AR301" t="n">
+        <v>125</v>
       </c>
       <c r="AS301" t="inlineStr">
         <is>
@@ -63509,6 +63121,4110 @@
       <c r="BK301" t="inlineStr"/>
       <c r="BL301" t="inlineStr"/>
     </row>
+    <row r="302">
+      <c r="A302" s="1" t="inlineStr">
+        <is>
+          <t>MiACepQ7</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>26.10.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>Badstubner F.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>Weserstadion
+ (Bremen)</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>42 100</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>42 100</t>
+        </is>
+      </c>
+      <c r="G302" t="n">
+        <v>2</v>
+      </c>
+      <c r="H302" t="n">
+        <v>2</v>
+      </c>
+      <c r="I302" t="inlineStr">
+        <is>
+          <t>Ig1f1fy3</t>
+        </is>
+      </c>
+      <c r="J302" t="inlineStr">
+        <is>
+          <t>Werder Bremen</t>
+        </is>
+      </c>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>4jcj2zMd</t>
+        </is>
+      </c>
+      <c r="L302" t="inlineStr">
+        <is>
+          <t>Bayer Leverkusen</t>
+        </is>
+      </c>
+      <c r="M302" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="N302" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O302" t="inlineStr">
+        <is>
+          <t>43%</t>
+        </is>
+      </c>
+      <c r="P302" t="inlineStr">
+        <is>
+          <t>57%</t>
+        </is>
+      </c>
+      <c r="Q302" t="n">
+        <v>13</v>
+      </c>
+      <c r="R302" t="n">
+        <v>15</v>
+      </c>
+      <c r="S302" t="n">
+        <v>8</v>
+      </c>
+      <c r="T302" t="n">
+        <v>6</v>
+      </c>
+      <c r="U302" t="n">
+        <v>5</v>
+      </c>
+      <c r="V302" t="n">
+        <v>7</v>
+      </c>
+      <c r="W302" t="n">
+        <v>11</v>
+      </c>
+      <c r="X302" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y302" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z302" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA302" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB302" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC302" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD302" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE302" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF302" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG302" t="n">
+        <v>9</v>
+      </c>
+      <c r="AH302" t="n">
+        <v>11</v>
+      </c>
+      <c r="AI302" t="inlineStr"/>
+      <c r="AJ302" t="inlineStr"/>
+      <c r="AK302" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL302" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM302" t="n">
+        <v>466</v>
+      </c>
+      <c r="AN302" t="n">
+        <v>614</v>
+      </c>
+      <c r="AO302" t="n">
+        <v>375</v>
+      </c>
+      <c r="AP302" t="n">
+        <v>521</v>
+      </c>
+      <c r="AQ302" t="inlineStr"/>
+      <c r="AR302" t="inlineStr"/>
+      <c r="AS302" t="inlineStr">
+        <is>
+          <t>4fuCGs9P</t>
+        </is>
+      </c>
+      <c r="AT302" t="inlineStr">
+        <is>
+          <t>werner ole</t>
+        </is>
+      </c>
+      <c r="AU302" t="inlineStr">
+        <is>
+          <t>hAcTWKKN</t>
+        </is>
+      </c>
+      <c r="AV302" t="inlineStr">
+        <is>
+          <t>alonso xabi</t>
+        </is>
+      </c>
+      <c r="AW302" t="n">
+        <v>59</v>
+      </c>
+      <c r="AX302" t="n">
+        <v>591</v>
+      </c>
+      <c r="AY302" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ302" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BA302" t="inlineStr"/>
+      <c r="BB302" t="inlineStr"/>
+      <c r="BC302" t="inlineStr"/>
+      <c r="BD302" t="inlineStr"/>
+      <c r="BE302" t="inlineStr"/>
+      <c r="BF302" t="inlineStr"/>
+      <c r="BG302" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH302" t="n">
+        <v>2</v>
+      </c>
+      <c r="BI302" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ302" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK302" t="n">
+        <v>11</v>
+      </c>
+      <c r="BL302" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="1" t="inlineStr">
+        <is>
+          <t>x0haJmIE</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>26.10.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>Welz T.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>WWK Arena
+ (Augsburg)</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>30 660</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>30 660</t>
+        </is>
+      </c>
+      <c r="G303" t="n">
+        <v>2</v>
+      </c>
+      <c r="H303" t="n">
+        <v>1</v>
+      </c>
+      <c r="I303" t="inlineStr">
+        <is>
+          <t>fTVNku3I</t>
+        </is>
+      </c>
+      <c r="J303" t="inlineStr">
+        <is>
+          <t>Augsburg</t>
+        </is>
+      </c>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="L303" t="inlineStr">
+        <is>
+          <t>Dortmund</t>
+        </is>
+      </c>
+      <c r="M303" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="N303" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="O303" t="inlineStr">
+        <is>
+          <t>23%</t>
+        </is>
+      </c>
+      <c r="P303" t="inlineStr">
+        <is>
+          <t>77%</t>
+        </is>
+      </c>
+      <c r="Q303" t="n">
+        <v>12</v>
+      </c>
+      <c r="R303" t="n">
+        <v>11</v>
+      </c>
+      <c r="S303" t="n">
+        <v>4</v>
+      </c>
+      <c r="T303" t="n">
+        <v>4</v>
+      </c>
+      <c r="U303" t="n">
+        <v>7</v>
+      </c>
+      <c r="V303" t="n">
+        <v>4</v>
+      </c>
+      <c r="W303" t="n">
+        <v>10</v>
+      </c>
+      <c r="X303" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y303" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z303" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA303" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB303" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC303" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD303" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE303" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF303" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG303" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH303" t="n">
+        <v>10</v>
+      </c>
+      <c r="AI303" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ303" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK303" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL303" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM303" t="n">
+        <v>219</v>
+      </c>
+      <c r="AN303" t="n">
+        <v>724</v>
+      </c>
+      <c r="AO303" t="n">
+        <v>150</v>
+      </c>
+      <c r="AP303" t="n">
+        <v>639</v>
+      </c>
+      <c r="AQ303" t="inlineStr"/>
+      <c r="AR303" t="inlineStr"/>
+      <c r="AS303" t="inlineStr">
+        <is>
+          <t>2VSFgl3c</t>
+        </is>
+      </c>
+      <c r="AT303" t="inlineStr">
+        <is>
+          <t>thorup jess</t>
+        </is>
+      </c>
+      <c r="AU303" t="inlineStr">
+        <is>
+          <t>IkCftsQm</t>
+        </is>
+      </c>
+      <c r="AV303" t="inlineStr">
+        <is>
+          <t>sahin nuri</t>
+        </is>
+      </c>
+      <c r="AW303" t="n">
+        <v>59</v>
+      </c>
+      <c r="AX303" t="n">
+        <v>591</v>
+      </c>
+      <c r="AY303" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ303" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BA303" t="inlineStr"/>
+      <c r="BB303" t="inlineStr"/>
+      <c r="BC303" t="inlineStr"/>
+      <c r="BD303" t="inlineStr"/>
+      <c r="BE303" t="inlineStr"/>
+      <c r="BF303" t="inlineStr"/>
+      <c r="BG303" t="n">
+        <v>1</v>
+      </c>
+      <c r="BH303" t="n">
+        <v>3</v>
+      </c>
+      <c r="BI303" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ303" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK303" t="n">
+        <v>14</v>
+      </c>
+      <c r="BL303" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="1" t="inlineStr">
+        <is>
+          <t>ELNeaSQr</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>26.10.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>Jablonski S.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>Red Bull Arena
+ (Leipzig)</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>47 069</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>45 000</t>
+        </is>
+      </c>
+      <c r="G304" t="n">
+        <v>3</v>
+      </c>
+      <c r="H304" t="n">
+        <v>1</v>
+      </c>
+      <c r="I304" t="inlineStr">
+        <is>
+          <t>KbS1suSm</t>
+        </is>
+      </c>
+      <c r="J304" t="inlineStr">
+        <is>
+          <t>RB Leipzig</t>
+        </is>
+      </c>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
+      <c r="L304" t="inlineStr">
+        <is>
+          <t>Freiburg</t>
+        </is>
+      </c>
+      <c r="M304" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="N304" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="O304" t="inlineStr">
+        <is>
+          <t>42%</t>
+        </is>
+      </c>
+      <c r="P304" t="inlineStr">
+        <is>
+          <t>58%</t>
+        </is>
+      </c>
+      <c r="Q304" t="n">
+        <v>12</v>
+      </c>
+      <c r="R304" t="n">
+        <v>15</v>
+      </c>
+      <c r="S304" t="n">
+        <v>9</v>
+      </c>
+      <c r="T304" t="n">
+        <v>5</v>
+      </c>
+      <c r="U304" t="n">
+        <v>2</v>
+      </c>
+      <c r="V304" t="n">
+        <v>8</v>
+      </c>
+      <c r="W304" t="n">
+        <v>7</v>
+      </c>
+      <c r="X304" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y304" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z304" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA304" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB304" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC304" t="n">
+        <v>20</v>
+      </c>
+      <c r="AD304" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE304" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF304" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG304" t="n">
+        <v>9</v>
+      </c>
+      <c r="AH304" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI304" t="inlineStr"/>
+      <c r="AJ304" t="inlineStr"/>
+      <c r="AK304" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL304" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM304" t="n">
+        <v>417</v>
+      </c>
+      <c r="AN304" t="n">
+        <v>559</v>
+      </c>
+      <c r="AO304" t="n">
+        <v>334</v>
+      </c>
+      <c r="AP304" t="n">
+        <v>473</v>
+      </c>
+      <c r="AQ304" t="inlineStr"/>
+      <c r="AR304" t="inlineStr"/>
+      <c r="AS304" t="inlineStr">
+        <is>
+          <t>pfoInmcq</t>
+        </is>
+      </c>
+      <c r="AT304" t="inlineStr">
+        <is>
+          <t>rose marko</t>
+        </is>
+      </c>
+      <c r="AU304" t="inlineStr">
+        <is>
+          <t>YZPE6Sx7</t>
+        </is>
+      </c>
+      <c r="AV304" t="inlineStr">
+        <is>
+          <t>schuster julian</t>
+        </is>
+      </c>
+      <c r="AW304" t="n">
+        <v>59</v>
+      </c>
+      <c r="AX304" t="n">
+        <v>591</v>
+      </c>
+      <c r="AY304" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ304" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BA304" t="inlineStr"/>
+      <c r="BB304" t="inlineStr"/>
+      <c r="BC304" t="inlineStr"/>
+      <c r="BD304" t="inlineStr"/>
+      <c r="BE304" t="inlineStr"/>
+      <c r="BF304" t="inlineStr"/>
+      <c r="BG304" t="n">
+        <v>1</v>
+      </c>
+      <c r="BH304" t="n">
+        <v>2</v>
+      </c>
+      <c r="BI304" t="n">
+        <v>5</v>
+      </c>
+      <c r="BJ304" t="n">
+        <v>6</v>
+      </c>
+      <c r="BK304" t="n">
+        <v>7</v>
+      </c>
+      <c r="BL304" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="1" t="inlineStr">
+        <is>
+          <t>Mku6FvHt</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>26.10.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>Reichel T.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>Millerntor-Stadion
+ (Hamburg)</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>29 546</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>29 500</t>
+        </is>
+      </c>
+      <c r="G305" t="n">
+        <v>0</v>
+      </c>
+      <c r="H305" t="n">
+        <v>0</v>
+      </c>
+      <c r="I305" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="J305" t="inlineStr">
+        <is>
+          <t>St. Pauli</t>
+        </is>
+      </c>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>nwkTahLL</t>
+        </is>
+      </c>
+      <c r="L305" t="inlineStr">
+        <is>
+          <t>Wolfsburg</t>
+        </is>
+      </c>
+      <c r="M305" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="N305" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="O305" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="P305" t="inlineStr">
+        <is>
+          <t>46%</t>
+        </is>
+      </c>
+      <c r="Q305" t="n">
+        <v>14</v>
+      </c>
+      <c r="R305" t="n">
+        <v>10</v>
+      </c>
+      <c r="S305" t="n">
+        <v>5</v>
+      </c>
+      <c r="T305" t="n">
+        <v>4</v>
+      </c>
+      <c r="U305" t="n">
+        <v>3</v>
+      </c>
+      <c r="V305" t="n">
+        <v>6</v>
+      </c>
+      <c r="W305" t="n">
+        <v>12</v>
+      </c>
+      <c r="X305" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y305" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z305" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA305" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB305" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC305" t="n">
+        <v>19</v>
+      </c>
+      <c r="AD305" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE305" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF305" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG305" t="n">
+        <v>9</v>
+      </c>
+      <c r="AH305" t="n">
+        <v>12</v>
+      </c>
+      <c r="AI305" t="inlineStr"/>
+      <c r="AJ305" t="inlineStr"/>
+      <c r="AK305" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL305" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM305" t="n">
+        <v>497</v>
+      </c>
+      <c r="AN305" t="n">
+        <v>434</v>
+      </c>
+      <c r="AO305" t="n">
+        <v>402</v>
+      </c>
+      <c r="AP305" t="n">
+        <v>343</v>
+      </c>
+      <c r="AQ305" t="inlineStr"/>
+      <c r="AR305" t="inlineStr"/>
+      <c r="AS305" t="inlineStr">
+        <is>
+          <t>0jdIgO6t</t>
+        </is>
+      </c>
+      <c r="AT305" t="inlineStr">
+        <is>
+          <t>blessin alexander</t>
+        </is>
+      </c>
+      <c r="AU305" t="inlineStr">
+        <is>
+          <t>f3ddUIXs</t>
+        </is>
+      </c>
+      <c r="AV305" t="inlineStr">
+        <is>
+          <t>hasenhuttl ralph</t>
+        </is>
+      </c>
+      <c r="AW305" t="n">
+        <v>59</v>
+      </c>
+      <c r="AX305" t="n">
+        <v>591</v>
+      </c>
+      <c r="AY305" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ305" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BA305" t="inlineStr"/>
+      <c r="BB305" t="inlineStr"/>
+      <c r="BC305" t="inlineStr"/>
+      <c r="BD305" t="inlineStr"/>
+      <c r="BE305" t="inlineStr"/>
+      <c r="BF305" t="inlineStr"/>
+      <c r="BG305" t="n">
+        <v>6</v>
+      </c>
+      <c r="BH305" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI305" t="n">
+        <v>6</v>
+      </c>
+      <c r="BJ305" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK305" t="n">
+        <v>9</v>
+      </c>
+      <c r="BL305" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="1" t="inlineStr">
+        <is>
+          <t>rwXP4l3L</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>26.10.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>Hartmann R.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>MHPArena
+ (Stuttgart)</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>60 449</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>59 000</t>
+        </is>
+      </c>
+      <c r="G306" t="n">
+        <v>2</v>
+      </c>
+      <c r="H306" t="n">
+        <v>1</v>
+      </c>
+      <c r="I306" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="J306" t="inlineStr">
+        <is>
+          <t>Stuttgart</t>
+        </is>
+      </c>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>63WsD2ei</t>
+        </is>
+      </c>
+      <c r="L306" t="inlineStr">
+        <is>
+          <t>Holstein Kiel</t>
+        </is>
+      </c>
+      <c r="M306" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="N306" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O306" t="inlineStr">
+        <is>
+          <t>59%</t>
+        </is>
+      </c>
+      <c r="P306" t="inlineStr">
+        <is>
+          <t>41%</t>
+        </is>
+      </c>
+      <c r="Q306" t="n">
+        <v>16</v>
+      </c>
+      <c r="R306" t="n">
+        <v>9</v>
+      </c>
+      <c r="S306" t="n">
+        <v>6</v>
+      </c>
+      <c r="T306" t="n">
+        <v>3</v>
+      </c>
+      <c r="U306" t="n">
+        <v>9</v>
+      </c>
+      <c r="V306" t="n">
+        <v>3</v>
+      </c>
+      <c r="W306" t="n">
+        <v>17</v>
+      </c>
+      <c r="X306" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y306" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z306" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA306" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB306" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC306" t="n">
+        <v>18</v>
+      </c>
+      <c r="AD306" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE306" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF306" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG306" t="n">
+        <v>6</v>
+      </c>
+      <c r="AH306" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI306" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ306" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK306" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL306" t="n">
+        <v>6</v>
+      </c>
+      <c r="AM306" t="n">
+        <v>530</v>
+      </c>
+      <c r="AN306" t="n">
+        <v>363</v>
+      </c>
+      <c r="AO306" t="n">
+        <v>470</v>
+      </c>
+      <c r="AP306" t="n">
+        <v>295</v>
+      </c>
+      <c r="AQ306" t="inlineStr"/>
+      <c r="AR306" t="inlineStr"/>
+      <c r="AS306" t="inlineStr">
+        <is>
+          <t>GzfvcwRj</t>
+        </is>
+      </c>
+      <c r="AT306" t="inlineStr">
+        <is>
+          <t>hoeness sebastian</t>
+        </is>
+      </c>
+      <c r="AU306" t="inlineStr">
+        <is>
+          <t>A15eUM4C</t>
+        </is>
+      </c>
+      <c r="AV306" t="inlineStr">
+        <is>
+          <t>rapp marcel</t>
+        </is>
+      </c>
+      <c r="AW306" t="n">
+        <v>59</v>
+      </c>
+      <c r="AX306" t="n">
+        <v>591</v>
+      </c>
+      <c r="AY306" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ306" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BA306" t="inlineStr"/>
+      <c r="BB306" t="inlineStr"/>
+      <c r="BC306" t="inlineStr"/>
+      <c r="BD306" t="inlineStr"/>
+      <c r="BE306" t="inlineStr"/>
+      <c r="BF306" t="inlineStr"/>
+      <c r="BG306" t="n">
+        <v>1</v>
+      </c>
+      <c r="BH306" t="n">
+        <v>3</v>
+      </c>
+      <c r="BI306" t="n">
+        <v>8</v>
+      </c>
+      <c r="BJ306" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK306" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL306" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="1" t="inlineStr">
+        <is>
+          <t>4E8uaJWa</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>25.10.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>Petersen M.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>Mewa Arena
+ (Mainz)</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>34 000</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>33 000</t>
+        </is>
+      </c>
+      <c r="G307" t="n">
+        <v>1</v>
+      </c>
+      <c r="H307" t="n">
+        <v>1</v>
+      </c>
+      <c r="I307" t="inlineStr">
+        <is>
+          <t>EuakNmc1</t>
+        </is>
+      </c>
+      <c r="J307" t="inlineStr">
+        <is>
+          <t>Mainz</t>
+        </is>
+      </c>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>88HSzjDr</t>
+        </is>
+      </c>
+      <c r="L307" t="inlineStr">
+        <is>
+          <t>B. Monchengladbach</t>
+        </is>
+      </c>
+      <c r="M307" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="N307" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O307" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="P307" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="Q307" t="n">
+        <v>23</v>
+      </c>
+      <c r="R307" t="n">
+        <v>9</v>
+      </c>
+      <c r="S307" t="n">
+        <v>6</v>
+      </c>
+      <c r="T307" t="n">
+        <v>5</v>
+      </c>
+      <c r="U307" t="n">
+        <v>8</v>
+      </c>
+      <c r="V307" t="n">
+        <v>4</v>
+      </c>
+      <c r="W307" t="n">
+        <v>16</v>
+      </c>
+      <c r="X307" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y307" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z307" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA307" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB307" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC307" t="n">
+        <v>16</v>
+      </c>
+      <c r="AD307" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE307" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF307" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG307" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH307" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI307" t="inlineStr"/>
+      <c r="AJ307" t="inlineStr"/>
+      <c r="AK307" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL307" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM307" t="n">
+        <v>472</v>
+      </c>
+      <c r="AN307" t="n">
+        <v>438</v>
+      </c>
+      <c r="AO307" t="n">
+        <v>381</v>
+      </c>
+      <c r="AP307" t="n">
+        <v>341</v>
+      </c>
+      <c r="AQ307" t="inlineStr"/>
+      <c r="AR307" t="inlineStr"/>
+      <c r="AS307" t="inlineStr">
+        <is>
+          <t>vZA6VYpf</t>
+        </is>
+      </c>
+      <c r="AT307" t="inlineStr">
+        <is>
+          <t>henriksen bo</t>
+        </is>
+      </c>
+      <c r="AU307" t="inlineStr">
+        <is>
+          <t>M5BRZDsC</t>
+        </is>
+      </c>
+      <c r="AV307" t="inlineStr">
+        <is>
+          <t>seoane gerardo</t>
+        </is>
+      </c>
+      <c r="AW307" t="n">
+        <v>59</v>
+      </c>
+      <c r="AX307" t="n">
+        <v>591</v>
+      </c>
+      <c r="AY307" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ307" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BA307" t="inlineStr"/>
+      <c r="BB307" t="inlineStr"/>
+      <c r="BC307" t="inlineStr"/>
+      <c r="BD307" t="inlineStr"/>
+      <c r="BE307" t="inlineStr"/>
+      <c r="BF307" t="inlineStr"/>
+      <c r="BG307" t="n">
+        <v>9</v>
+      </c>
+      <c r="BH307" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI307" t="n">
+        <v>9</v>
+      </c>
+      <c r="BJ307" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK307" t="n">
+        <v>9</v>
+      </c>
+      <c r="BL307" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="1" t="inlineStr">
+        <is>
+          <t>xWl4d4Wp</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>26.10.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>Willenborg F.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>Merkur Spiel-Arena
+ (Düsseldorf)</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>54 600</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>44 557</t>
+        </is>
+      </c>
+      <c r="G308" t="n">
+        <v>3</v>
+      </c>
+      <c r="H308" t="n">
+        <v>4</v>
+      </c>
+      <c r="I308" t="inlineStr">
+        <is>
+          <t>ne1oL3y7</t>
+        </is>
+      </c>
+      <c r="J308" t="inlineStr">
+        <is>
+          <t>Dusseldorf</t>
+        </is>
+      </c>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>naWckLmC</t>
+        </is>
+      </c>
+      <c r="L308" t="inlineStr">
+        <is>
+          <t>Kaiserslautern</t>
+        </is>
+      </c>
+      <c r="M308" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="N308" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="O308" t="inlineStr">
+        <is>
+          <t>58%</t>
+        </is>
+      </c>
+      <c r="P308" t="inlineStr">
+        <is>
+          <t>42%</t>
+        </is>
+      </c>
+      <c r="Q308" t="n">
+        <v>14</v>
+      </c>
+      <c r="R308" t="n">
+        <v>12</v>
+      </c>
+      <c r="S308" t="n">
+        <v>7</v>
+      </c>
+      <c r="T308" t="n">
+        <v>6</v>
+      </c>
+      <c r="U308" t="n">
+        <v>7</v>
+      </c>
+      <c r="V308" t="n">
+        <v>6</v>
+      </c>
+      <c r="W308" t="n">
+        <v>7</v>
+      </c>
+      <c r="X308" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y308" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z308" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA308" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB308" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC308" t="n">
+        <v>38</v>
+      </c>
+      <c r="AD308" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE308" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF308" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG308" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH308" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI308" t="inlineStr"/>
+      <c r="AJ308" t="inlineStr"/>
+      <c r="AK308" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL308" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM308" t="n">
+        <v>495</v>
+      </c>
+      <c r="AN308" t="n">
+        <v>374</v>
+      </c>
+      <c r="AO308" t="n">
+        <v>426</v>
+      </c>
+      <c r="AP308" t="n">
+        <v>318</v>
+      </c>
+      <c r="AQ308" t="n">
+        <v>121</v>
+      </c>
+      <c r="AR308" t="n">
+        <v>122</v>
+      </c>
+      <c r="AS308" t="inlineStr">
+        <is>
+          <t>AoL97rX8</t>
+        </is>
+      </c>
+      <c r="AT308" t="inlineStr">
+        <is>
+          <t>thioune daniel</t>
+        </is>
+      </c>
+      <c r="AU308" t="inlineStr">
+        <is>
+          <t>4bJLk19p</t>
+        </is>
+      </c>
+      <c r="AV308" t="inlineStr">
+        <is>
+          <t>anfang marcus</t>
+        </is>
+      </c>
+      <c r="AW308" t="n">
+        <v>59</v>
+      </c>
+      <c r="AX308" t="n">
+        <v>592</v>
+      </c>
+      <c r="AY308" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ308" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BA308" t="inlineStr"/>
+      <c r="BB308" t="inlineStr"/>
+      <c r="BC308" t="inlineStr"/>
+      <c r="BD308" t="inlineStr"/>
+      <c r="BE308" t="inlineStr"/>
+      <c r="BF308" t="inlineStr"/>
+      <c r="BG308" t="inlineStr"/>
+      <c r="BH308" t="inlineStr"/>
+      <c r="BI308" t="inlineStr"/>
+      <c r="BJ308" t="inlineStr"/>
+      <c r="BK308" t="inlineStr"/>
+      <c r="BL308" t="inlineStr"/>
+    </row>
+    <row r="309">
+      <c r="A309" s="1" t="inlineStr">
+        <is>
+          <t>r3AbGPNG</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>26.10.2024 08:00</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>Kampka R.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>Waldstadion Kaiserlinde
+ (Spiesen-Elversberg)</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>9 970</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>9 502</t>
+        </is>
+      </c>
+      <c r="G309" t="n">
+        <v>4</v>
+      </c>
+      <c r="H309" t="n">
+        <v>2</v>
+      </c>
+      <c r="I309" t="inlineStr">
+        <is>
+          <t>6in2Eknb</t>
+        </is>
+      </c>
+      <c r="J309" t="inlineStr">
+        <is>
+          <t>Elversberg</t>
+        </is>
+      </c>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>v9k3aY5F</t>
+        </is>
+      </c>
+      <c r="L309" t="inlineStr">
+        <is>
+          <t>Hamburger SV</t>
+        </is>
+      </c>
+      <c r="M309" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="N309" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="O309" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
+      <c r="P309" t="inlineStr">
+        <is>
+          <t>56%</t>
+        </is>
+      </c>
+      <c r="Q309" t="n">
+        <v>18</v>
+      </c>
+      <c r="R309" t="n">
+        <v>9</v>
+      </c>
+      <c r="S309" t="n">
+        <v>10</v>
+      </c>
+      <c r="T309" t="n">
+        <v>4</v>
+      </c>
+      <c r="U309" t="n">
+        <v>8</v>
+      </c>
+      <c r="V309" t="n">
+        <v>5</v>
+      </c>
+      <c r="W309" t="n">
+        <v>17</v>
+      </c>
+      <c r="X309" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y309" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z309" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA309" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB309" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC309" t="n">
+        <v>17</v>
+      </c>
+      <c r="AD309" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE309" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF309" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG309" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH309" t="n">
+        <v>14</v>
+      </c>
+      <c r="AI309" t="inlineStr"/>
+      <c r="AJ309" t="inlineStr"/>
+      <c r="AK309" t="inlineStr"/>
+      <c r="AL309" t="inlineStr"/>
+      <c r="AM309" t="n">
+        <v>371</v>
+      </c>
+      <c r="AN309" t="n">
+        <v>534</v>
+      </c>
+      <c r="AO309" t="n">
+        <v>340</v>
+      </c>
+      <c r="AP309" t="n">
+        <v>514</v>
+      </c>
+      <c r="AQ309" t="n">
+        <v>121</v>
+      </c>
+      <c r="AR309" t="n">
+        <v>117</v>
+      </c>
+      <c r="AS309" t="inlineStr">
+        <is>
+          <t>8E8qmw3d</t>
+        </is>
+      </c>
+      <c r="AT309" t="inlineStr">
+        <is>
+          <t>steffen horst</t>
+        </is>
+      </c>
+      <c r="AU309" t="inlineStr">
+        <is>
+          <t>EDRZkDzS</t>
+        </is>
+      </c>
+      <c r="AV309" t="inlineStr">
+        <is>
+          <t>baumgart steffen</t>
+        </is>
+      </c>
+      <c r="AW309" t="n">
+        <v>59</v>
+      </c>
+      <c r="AX309" t="n">
+        <v>592</v>
+      </c>
+      <c r="AY309" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ309" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BA309" t="inlineStr"/>
+      <c r="BB309" t="inlineStr"/>
+      <c r="BC309" t="inlineStr"/>
+      <c r="BD309" t="inlineStr"/>
+      <c r="BE309" t="inlineStr"/>
+      <c r="BF309" t="inlineStr"/>
+      <c r="BG309" t="inlineStr"/>
+      <c r="BH309" t="inlineStr"/>
+      <c r="BI309" t="inlineStr"/>
+      <c r="BJ309" t="inlineStr"/>
+      <c r="BK309" t="inlineStr"/>
+      <c r="BL309" t="inlineStr"/>
+    </row>
+    <row r="310">
+      <c r="A310" s="1" t="inlineStr">
+        <is>
+          <t>UPyjK7Oi</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>26.10.2024 08:00</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>Heft F.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>BBBank Wildpark
+ (Karlsruhe)</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>34 302</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>31 845</t>
+        </is>
+      </c>
+      <c r="G310" t="n">
+        <v>1</v>
+      </c>
+      <c r="H310" t="n">
+        <v>3</v>
+      </c>
+      <c r="I310" t="inlineStr">
+        <is>
+          <t>EB3q7jbk</t>
+        </is>
+      </c>
+      <c r="J310" t="inlineStr">
+        <is>
+          <t>Karlsruher SC</t>
+        </is>
+      </c>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>2y0u8Wrq</t>
+        </is>
+      </c>
+      <c r="L310" t="inlineStr">
+        <is>
+          <t>Hertha Berlin</t>
+        </is>
+      </c>
+      <c r="M310" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="N310" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="O310" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="P310" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="Q310" t="n">
+        <v>13</v>
+      </c>
+      <c r="R310" t="n">
+        <v>10</v>
+      </c>
+      <c r="S310" t="n">
+        <v>4</v>
+      </c>
+      <c r="T310" t="n">
+        <v>8</v>
+      </c>
+      <c r="U310" t="n">
+        <v>9</v>
+      </c>
+      <c r="V310" t="n">
+        <v>2</v>
+      </c>
+      <c r="W310" t="n">
+        <v>11</v>
+      </c>
+      <c r="X310" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y310" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z310" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA310" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB310" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC310" t="n">
+        <v>18</v>
+      </c>
+      <c r="AD310" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE310" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF310" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG310" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH310" t="n">
+        <v>13</v>
+      </c>
+      <c r="AI310" t="inlineStr"/>
+      <c r="AJ310" t="inlineStr"/>
+      <c r="AK310" t="n">
+        <v>6</v>
+      </c>
+      <c r="AL310" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM310" t="n">
+        <v>528</v>
+      </c>
+      <c r="AN310" t="n">
+        <v>420</v>
+      </c>
+      <c r="AO310" t="n">
+        <v>478</v>
+      </c>
+      <c r="AP310" t="n">
+        <v>380</v>
+      </c>
+      <c r="AQ310" t="n">
+        <v>115</v>
+      </c>
+      <c r="AR310" t="n">
+        <v>118</v>
+      </c>
+      <c r="AS310" t="inlineStr">
+        <is>
+          <t>OzPMRhK3</t>
+        </is>
+      </c>
+      <c r="AT310" t="inlineStr">
+        <is>
+          <t>eichner christian</t>
+        </is>
+      </c>
+      <c r="AU310" t="inlineStr">
+        <is>
+          <t>YmfcAeCo</t>
+        </is>
+      </c>
+      <c r="AV310" t="inlineStr">
+        <is>
+          <t>fiel cristian</t>
+        </is>
+      </c>
+      <c r="AW310" t="n">
+        <v>59</v>
+      </c>
+      <c r="AX310" t="n">
+        <v>592</v>
+      </c>
+      <c r="AY310" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ310" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BA310" t="inlineStr"/>
+      <c r="BB310" t="inlineStr"/>
+      <c r="BC310" t="inlineStr"/>
+      <c r="BD310" t="inlineStr"/>
+      <c r="BE310" t="inlineStr"/>
+      <c r="BF310" t="inlineStr"/>
+      <c r="BG310" t="inlineStr"/>
+      <c r="BH310" t="inlineStr"/>
+      <c r="BI310" t="inlineStr"/>
+      <c r="BJ310" t="inlineStr"/>
+      <c r="BK310" t="inlineStr"/>
+      <c r="BL310" t="inlineStr"/>
+    </row>
+    <row r="311">
+      <c r="A311" s="1" t="inlineStr">
+        <is>
+          <t>zw7jIog4</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>26.10.2024 08:00</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>Alt P.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>Veltins Arena
+ (Gelsenkirchen)</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>62 271</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>60 000</t>
+        </is>
+      </c>
+      <c r="G311" t="n">
+        <v>3</v>
+      </c>
+      <c r="H311" t="n">
+        <v>4</v>
+      </c>
+      <c r="I311" t="inlineStr">
+        <is>
+          <t>0Ija0Ej9</t>
+        </is>
+      </c>
+      <c r="J311" t="inlineStr">
+        <is>
+          <t>Schalke</t>
+        </is>
+      </c>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>CCQGbik8</t>
+        </is>
+      </c>
+      <c r="L311" t="inlineStr">
+        <is>
+          <t>Greuther Furth</t>
+        </is>
+      </c>
+      <c r="M311" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="N311" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="O311" t="inlineStr">
+        <is>
+          <t>55%</t>
+        </is>
+      </c>
+      <c r="P311" t="inlineStr">
+        <is>
+          <t>45%</t>
+        </is>
+      </c>
+      <c r="Q311" t="n">
+        <v>21</v>
+      </c>
+      <c r="R311" t="n">
+        <v>18</v>
+      </c>
+      <c r="S311" t="n">
+        <v>6</v>
+      </c>
+      <c r="T311" t="n">
+        <v>7</v>
+      </c>
+      <c r="U311" t="n">
+        <v>15</v>
+      </c>
+      <c r="V311" t="n">
+        <v>11</v>
+      </c>
+      <c r="W311" t="n">
+        <v>19</v>
+      </c>
+      <c r="X311" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y311" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z311" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA311" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB311" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC311" t="n">
+        <v>27</v>
+      </c>
+      <c r="AD311" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE311" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF311" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG311" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH311" t="n">
+        <v>13</v>
+      </c>
+      <c r="AI311" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ311" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK311" t="n">
+        <v>6</v>
+      </c>
+      <c r="AL311" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM311" t="n">
+        <v>559</v>
+      </c>
+      <c r="AN311" t="n">
+        <v>448</v>
+      </c>
+      <c r="AO311" t="n">
+        <v>535</v>
+      </c>
+      <c r="AP311" t="n">
+        <v>411</v>
+      </c>
+      <c r="AQ311" t="n">
+        <v>59</v>
+      </c>
+      <c r="AR311" t="n">
+        <v>120</v>
+      </c>
+      <c r="AS311" t="inlineStr">
+        <is>
+          <t>SMaB5LKo</t>
+        </is>
+      </c>
+      <c r="AT311" t="inlineStr">
+        <is>
+          <t>van wonderen kees</t>
+        </is>
+      </c>
+      <c r="AU311" t="inlineStr">
+        <is>
+          <t>S6Oa4cwI</t>
+        </is>
+      </c>
+      <c r="AV311" t="inlineStr">
+        <is>
+          <t>haas leonhard</t>
+        </is>
+      </c>
+      <c r="AW311" t="n">
+        <v>59</v>
+      </c>
+      <c r="AX311" t="n">
+        <v>592</v>
+      </c>
+      <c r="AY311" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ311" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BA311" t="inlineStr"/>
+      <c r="BB311" t="inlineStr"/>
+      <c r="BC311" t="inlineStr"/>
+      <c r="BD311" t="inlineStr"/>
+      <c r="BE311" t="inlineStr"/>
+      <c r="BF311" t="inlineStr"/>
+      <c r="BG311" t="inlineStr"/>
+      <c r="BH311" t="inlineStr"/>
+      <c r="BI311" t="inlineStr"/>
+      <c r="BJ311" t="inlineStr"/>
+      <c r="BK311" t="inlineStr"/>
+      <c r="BL311" t="inlineStr"/>
+    </row>
+    <row r="312">
+      <c r="A312" s="1" t="inlineStr">
+        <is>
+          <t>AL4P3nvB</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>25.10.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>Lechner F.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>RheinEnergieStadion
+ (Cologne)</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>50 000</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>50 000</t>
+        </is>
+      </c>
+      <c r="G312" t="n">
+        <v>1</v>
+      </c>
+      <c r="H312" t="n">
+        <v>2</v>
+      </c>
+      <c r="I312" t="inlineStr">
+        <is>
+          <t>WG9pOTse</t>
+        </is>
+      </c>
+      <c r="J312" t="inlineStr">
+        <is>
+          <t>FC Koln</t>
+        </is>
+      </c>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>G2Op923t</t>
+        </is>
+      </c>
+      <c r="L312" t="inlineStr">
+        <is>
+          <t>Paderborn</t>
+        </is>
+      </c>
+      <c r="M312" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N312" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="O312" t="inlineStr">
+        <is>
+          <t>42%</t>
+        </is>
+      </c>
+      <c r="P312" t="inlineStr">
+        <is>
+          <t>58%</t>
+        </is>
+      </c>
+      <c r="Q312" t="n">
+        <v>12</v>
+      </c>
+      <c r="R312" t="n">
+        <v>9</v>
+      </c>
+      <c r="S312" t="n">
+        <v>3</v>
+      </c>
+      <c r="T312" t="n">
+        <v>4</v>
+      </c>
+      <c r="U312" t="n">
+        <v>9</v>
+      </c>
+      <c r="V312" t="n">
+        <v>5</v>
+      </c>
+      <c r="W312" t="n">
+        <v>13</v>
+      </c>
+      <c r="X312" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y312" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z312" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA312" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB312" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC312" t="n">
+        <v>19</v>
+      </c>
+      <c r="AD312" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE312" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF312" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG312" t="n">
+        <v>6</v>
+      </c>
+      <c r="AH312" t="n">
+        <v>11</v>
+      </c>
+      <c r="AI312" t="inlineStr"/>
+      <c r="AJ312" t="inlineStr"/>
+      <c r="AK312" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL312" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM312" t="n">
+        <v>432</v>
+      </c>
+      <c r="AN312" t="n">
+        <v>607</v>
+      </c>
+      <c r="AO312" t="n">
+        <v>350</v>
+      </c>
+      <c r="AP312" t="n">
+        <v>495</v>
+      </c>
+      <c r="AQ312" t="n">
+        <v>120</v>
+      </c>
+      <c r="AR312" t="n">
+        <v>121</v>
+      </c>
+      <c r="AS312" t="inlineStr">
+        <is>
+          <t>4fX0k7gg</t>
+        </is>
+      </c>
+      <c r="AT312" t="inlineStr">
+        <is>
+          <t>struber gerhard</t>
+        </is>
+      </c>
+      <c r="AU312" t="inlineStr">
+        <is>
+          <t>0AI1QUJH</t>
+        </is>
+      </c>
+      <c r="AV312" t="inlineStr">
+        <is>
+          <t>kwasniok lukas</t>
+        </is>
+      </c>
+      <c r="AW312" t="n">
+        <v>59</v>
+      </c>
+      <c r="AX312" t="n">
+        <v>592</v>
+      </c>
+      <c r="AY312" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ312" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BA312" t="inlineStr"/>
+      <c r="BB312" t="inlineStr"/>
+      <c r="BC312" t="inlineStr"/>
+      <c r="BD312" t="inlineStr"/>
+      <c r="BE312" t="inlineStr"/>
+      <c r="BF312" t="inlineStr"/>
+      <c r="BG312" t="inlineStr"/>
+      <c r="BH312" t="inlineStr"/>
+      <c r="BI312" t="inlineStr"/>
+      <c r="BJ312" t="inlineStr"/>
+      <c r="BK312" t="inlineStr"/>
+      <c r="BL312" t="inlineStr"/>
+    </row>
+    <row r="313">
+      <c r="A313" s="1" t="inlineStr">
+        <is>
+          <t>2iNWcH7k</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>25.10.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>Braun R.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>Max-Morlock-Stadion
+ (Nuremberg)</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>50 000</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>36 152</t>
+        </is>
+      </c>
+      <c r="G313" t="n">
+        <v>8</v>
+      </c>
+      <c r="H313" t="n">
+        <v>3</v>
+      </c>
+      <c r="I313" t="inlineStr">
+        <is>
+          <t>6FDqshzF</t>
+        </is>
+      </c>
+      <c r="J313" t="inlineStr">
+        <is>
+          <t>Nurnberg</t>
+        </is>
+      </c>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>UiCmEP56</t>
+        </is>
+      </c>
+      <c r="L313" t="inlineStr">
+        <is>
+          <t>Regensburg</t>
+        </is>
+      </c>
+      <c r="M313" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="N313" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="O313" t="inlineStr">
+        <is>
+          <t>57%</t>
+        </is>
+      </c>
+      <c r="P313" t="inlineStr">
+        <is>
+          <t>43%</t>
+        </is>
+      </c>
+      <c r="Q313" t="n">
+        <v>20</v>
+      </c>
+      <c r="R313" t="n">
+        <v>16</v>
+      </c>
+      <c r="S313" t="n">
+        <v>12</v>
+      </c>
+      <c r="T313" t="n">
+        <v>7</v>
+      </c>
+      <c r="U313" t="n">
+        <v>8</v>
+      </c>
+      <c r="V313" t="n">
+        <v>9</v>
+      </c>
+      <c r="W313" t="n">
+        <v>15</v>
+      </c>
+      <c r="X313" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y313" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z313" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA313" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB313" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC313" t="n">
+        <v>23</v>
+      </c>
+      <c r="AD313" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE313" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF313" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG313" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH313" t="n">
+        <v>13</v>
+      </c>
+      <c r="AI313" t="inlineStr"/>
+      <c r="AJ313" t="inlineStr"/>
+      <c r="AK313" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL313" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM313" t="n">
+        <v>417</v>
+      </c>
+      <c r="AN313" t="n">
+        <v>333</v>
+      </c>
+      <c r="AO313" t="n">
+        <v>342</v>
+      </c>
+      <c r="AP313" t="n">
+        <v>237</v>
+      </c>
+      <c r="AQ313" t="n">
+        <v>110</v>
+      </c>
+      <c r="AR313" t="n">
+        <v>113</v>
+      </c>
+      <c r="AS313" t="inlineStr">
+        <is>
+          <t>tO31cZrF</t>
+        </is>
+      </c>
+      <c r="AT313" t="inlineStr">
+        <is>
+          <t>klose miroslav</t>
+        </is>
+      </c>
+      <c r="AU313" t="inlineStr">
+        <is>
+          <t>zyLSrbZQ</t>
+        </is>
+      </c>
+      <c r="AV313" t="inlineStr">
+        <is>
+          <t>enochs joe</t>
+        </is>
+      </c>
+      <c r="AW313" t="n">
+        <v>59</v>
+      </c>
+      <c r="AX313" t="n">
+        <v>592</v>
+      </c>
+      <c r="AY313" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ313" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BA313" t="inlineStr"/>
+      <c r="BB313" t="inlineStr"/>
+      <c r="BC313" t="inlineStr"/>
+      <c r="BD313" t="inlineStr"/>
+      <c r="BE313" t="inlineStr"/>
+      <c r="BF313" t="inlineStr"/>
+      <c r="BG313" t="inlineStr"/>
+      <c r="BH313" t="inlineStr"/>
+      <c r="BI313" t="inlineStr"/>
+      <c r="BJ313" t="inlineStr"/>
+      <c r="BK313" t="inlineStr"/>
+      <c r="BL313" t="inlineStr"/>
+    </row>
+    <row r="314">
+      <c r="A314" s="1" t="inlineStr">
+        <is>
+          <t>zyC4c6ee</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>27.10.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>Dingert C.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>Voith-Arena
+ (Heidenheim)</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I314" t="inlineStr">
+        <is>
+          <t>KWixEVWi</t>
+        </is>
+      </c>
+      <c r="J314" t="inlineStr">
+        <is>
+          <t>Heidenheim</t>
+        </is>
+      </c>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>hQAtP9Sl</t>
+        </is>
+      </c>
+      <c r="L314" t="inlineStr">
+        <is>
+          <t>Hoffenheim</t>
+        </is>
+      </c>
+      <c r="M314" t="inlineStr">
+        <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="N314" t="inlineStr">
+        <is>
+          <t>0.56</t>
+        </is>
+      </c>
+      <c r="O314" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="P314" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
+      </c>
+      <c r="Q314" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="R314" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="S314" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T314" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U314" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="V314" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W314" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="X314" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="Y314" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Z314" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA314" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB314" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC314" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AD314" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AE314" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AF314" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AG314" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AH314" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AI314" t="inlineStr"/>
+      <c r="AJ314" t="inlineStr"/>
+      <c r="AK314" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL314" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM314" t="inlineStr">
+        <is>
+          <t>379</t>
+        </is>
+      </c>
+      <c r="AN314" t="inlineStr">
+        <is>
+          <t>445</t>
+        </is>
+      </c>
+      <c r="AO314" t="inlineStr">
+        <is>
+          <t>290</t>
+        </is>
+      </c>
+      <c r="AP314" t="inlineStr">
+        <is>
+          <t>355</t>
+        </is>
+      </c>
+      <c r="AQ314" t="inlineStr"/>
+      <c r="AR314" t="inlineStr"/>
+      <c r="AS314" t="inlineStr">
+        <is>
+          <t>4ljanukM</t>
+        </is>
+      </c>
+      <c r="AT314" t="inlineStr">
+        <is>
+          <t>schmidt frank</t>
+        </is>
+      </c>
+      <c r="AU314" t="inlineStr">
+        <is>
+          <t>KUx4Q7x1</t>
+        </is>
+      </c>
+      <c r="AV314" t="inlineStr">
+        <is>
+          <t>matarazzo pellegrino</t>
+        </is>
+      </c>
+      <c r="AW314" t="n">
+        <v>59</v>
+      </c>
+      <c r="AX314" t="n">
+        <v>591</v>
+      </c>
+      <c r="AY314" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ314" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BA314" t="inlineStr"/>
+      <c r="BB314" t="inlineStr"/>
+      <c r="BC314" t="inlineStr"/>
+      <c r="BD314" t="inlineStr"/>
+      <c r="BE314" t="inlineStr"/>
+      <c r="BF314" t="inlineStr"/>
+      <c r="BG314" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="BH314" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BI314" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="BJ314" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BK314" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BL314" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="1" t="inlineStr">
+        <is>
+          <t>ABBmcc1C</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>27.10.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>Osmers H.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>Stadion An der Alten Försterei
+ (Berlin)</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>22 012</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>22 012</t>
+        </is>
+      </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t>pzHW4oaE</t>
+        </is>
+      </c>
+      <c r="J315" t="inlineStr">
+        <is>
+          <t>Union Berlin</t>
+        </is>
+      </c>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="L315" t="inlineStr">
+        <is>
+          <t>Eintracht Frankfurt</t>
+        </is>
+      </c>
+      <c r="M315" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="N315" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="O315" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="P315" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="Q315" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="R315" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="S315" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T315" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U315" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V315" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W315" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="X315" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="Y315" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Z315" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA315" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB315" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC315" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AD315" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="AE315" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AF315" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AG315" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AH315" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AI315" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AJ315" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AK315" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AL315" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM315" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="AN315" t="inlineStr">
+        <is>
+          <t>492</t>
+        </is>
+      </c>
+      <c r="AO315" t="inlineStr">
+        <is>
+          <t>333</t>
+        </is>
+      </c>
+      <c r="AP315" t="inlineStr">
+        <is>
+          <t>379</t>
+        </is>
+      </c>
+      <c r="AQ315" t="inlineStr"/>
+      <c r="AR315" t="inlineStr"/>
+      <c r="AS315" t="inlineStr">
+        <is>
+          <t>hpYJ6izc</t>
+        </is>
+      </c>
+      <c r="AT315" t="inlineStr">
+        <is>
+          <t>svensson bo</t>
+        </is>
+      </c>
+      <c r="AU315" t="inlineStr">
+        <is>
+          <t>UgdQz0fK</t>
+        </is>
+      </c>
+      <c r="AV315" t="inlineStr">
+        <is>
+          <t>toppmoller dino</t>
+        </is>
+      </c>
+      <c r="AW315" t="n">
+        <v>59</v>
+      </c>
+      <c r="AX315" t="n">
+        <v>591</v>
+      </c>
+      <c r="AY315" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ315" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BA315" t="inlineStr"/>
+      <c r="BB315" t="inlineStr"/>
+      <c r="BC315" t="inlineStr"/>
+      <c r="BD315" t="inlineStr"/>
+      <c r="BE315" t="inlineStr"/>
+      <c r="BF315" t="inlineStr"/>
+      <c r="BG315" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="BH315" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="BI315" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BJ315" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="BK315" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="BL315" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="1" t="inlineStr">
+        <is>
+          <t>WQadeyWO</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>27.10.2024 11:30</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>Exner F.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>Vonovia Ruhrstadion
+ (Bochum)</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>26 000</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>26 000</t>
+        </is>
+      </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I316" t="inlineStr">
+        <is>
+          <t>8Y2m6ADe</t>
+        </is>
+      </c>
+      <c r="J316" t="inlineStr">
+        <is>
+          <t>Bochum</t>
+        </is>
+      </c>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>nVp0wiqd</t>
+        </is>
+      </c>
+      <c r="L316" t="inlineStr">
+        <is>
+          <t>Bayern Munich</t>
+        </is>
+      </c>
+      <c r="M316" t="inlineStr">
+        <is>
+          <t>0.52</t>
+        </is>
+      </c>
+      <c r="N316" t="inlineStr">
+        <is>
+          <t>2.23</t>
+        </is>
+      </c>
+      <c r="O316" t="inlineStr">
+        <is>
+          <t>27%</t>
+        </is>
+      </c>
+      <c r="P316" t="inlineStr">
+        <is>
+          <t>73%</t>
+        </is>
+      </c>
+      <c r="Q316" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="R316" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="S316" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T316" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="U316" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V316" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="W316" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="X316" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="Y316" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Z316" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA316" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB316" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC316" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AD316" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AE316" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AF316" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AG316" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AH316" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AI316" t="inlineStr"/>
+      <c r="AJ316" t="inlineStr"/>
+      <c r="AK316" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL316" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM316" t="inlineStr">
+        <is>
+          <t>247</t>
+        </is>
+      </c>
+      <c r="AN316" t="inlineStr">
+        <is>
+          <t>654</t>
+        </is>
+      </c>
+      <c r="AO316" t="inlineStr">
+        <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="AP316" t="inlineStr">
+        <is>
+          <t>591</t>
+        </is>
+      </c>
+      <c r="AQ316" t="inlineStr"/>
+      <c r="AR316" t="inlineStr"/>
+      <c r="AS316" t="inlineStr">
+        <is>
+          <t>8f6APkLc</t>
+        </is>
+      </c>
+      <c r="AT316" t="inlineStr">
+        <is>
+          <t>zeidler peter</t>
+        </is>
+      </c>
+      <c r="AU316" t="inlineStr">
+        <is>
+          <t>K6A2elS9</t>
+        </is>
+      </c>
+      <c r="AV316" t="inlineStr">
+        <is>
+          <t>kompany vincent</t>
+        </is>
+      </c>
+      <c r="AW316" t="n">
+        <v>59</v>
+      </c>
+      <c r="AX316" t="n">
+        <v>591</v>
+      </c>
+      <c r="AY316" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ316" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BA316" t="inlineStr"/>
+      <c r="BB316" t="inlineStr"/>
+      <c r="BC316" t="inlineStr"/>
+      <c r="BD316" t="inlineStr"/>
+      <c r="BE316" t="inlineStr"/>
+      <c r="BF316" t="inlineStr"/>
+      <c r="BG316" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BH316" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BI316" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BJ316" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="BK316" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="BL316" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="1" t="inlineStr">
+        <is>
+          <t>Od8RJbU8</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>27.10.2024 09:30</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>Schwengers P.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>Eintracht-Stadion
+ (Braunschweig)</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>23 325</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>21 809</t>
+        </is>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I317" t="inlineStr">
+        <is>
+          <t>QqLCC3il</t>
+        </is>
+      </c>
+      <c r="J317" t="inlineStr">
+        <is>
+          <t>Braunschweig</t>
+        </is>
+      </c>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>zedZaSL7</t>
+        </is>
+      </c>
+      <c r="L317" t="inlineStr">
+        <is>
+          <t>Preussen Munster</t>
+        </is>
+      </c>
+      <c r="M317" t="inlineStr">
+        <is>
+          <t>0.68</t>
+        </is>
+      </c>
+      <c r="N317" t="inlineStr">
+        <is>
+          <t>0.30</t>
+        </is>
+      </c>
+      <c r="O317" t="inlineStr">
+        <is>
+          <t>56%</t>
+        </is>
+      </c>
+      <c r="P317" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
+      <c r="Q317" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R317" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="S317" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T317" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U317" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V317" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W317" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="X317" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y317" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Z317" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA317" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB317" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC317" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AD317" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AE317" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AF317" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AG317" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AH317" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AI317" t="inlineStr"/>
+      <c r="AJ317" t="inlineStr"/>
+      <c r="AK317" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL317" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM317" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AN317" t="inlineStr">
+        <is>
+          <t>407</t>
+        </is>
+      </c>
+      <c r="AO317" t="inlineStr">
+        <is>
+          <t>456</t>
+        </is>
+      </c>
+      <c r="AP317" t="inlineStr">
+        <is>
+          <t>317</t>
+        </is>
+      </c>
+      <c r="AQ317" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="AR317" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="AS317" t="inlineStr">
+        <is>
+          <t>SQrxFAMl</t>
+        </is>
+      </c>
+      <c r="AT317" t="inlineStr">
+        <is>
+          <t>scherning daniel</t>
+        </is>
+      </c>
+      <c r="AU317" t="inlineStr">
+        <is>
+          <t>pdPRS0me</t>
+        </is>
+      </c>
+      <c r="AV317" t="inlineStr">
+        <is>
+          <t>hildmann sascha</t>
+        </is>
+      </c>
+      <c r="AW317" t="n">
+        <v>59</v>
+      </c>
+      <c r="AX317" t="n">
+        <v>592</v>
+      </c>
+      <c r="AY317" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ317" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BA317" t="inlineStr"/>
+      <c r="BB317" t="inlineStr"/>
+      <c r="BC317" t="inlineStr"/>
+      <c r="BD317" t="inlineStr"/>
+      <c r="BE317" t="inlineStr"/>
+      <c r="BF317" t="inlineStr"/>
+      <c r="BG317" t="inlineStr"/>
+      <c r="BH317" t="inlineStr"/>
+      <c r="BI317" t="inlineStr"/>
+      <c r="BJ317" t="inlineStr"/>
+      <c r="BK317" t="inlineStr"/>
+      <c r="BL317" t="inlineStr"/>
+    </row>
+    <row r="318">
+      <c r="A318" s="1" t="inlineStr">
+        <is>
+          <t>Io8X1Q8N</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>27.10.2024 09:30</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>Storks S.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>Merck-Stadion am Bollenfalltor
+ (Darmstadt)</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>17 810</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>17 455</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>S0hPB9rA</t>
+        </is>
+      </c>
+      <c r="J318" t="inlineStr">
+        <is>
+          <t>Darmstadt</t>
+        </is>
+      </c>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>tbC3EcQn</t>
+        </is>
+      </c>
+      <c r="L318" t="inlineStr">
+        <is>
+          <t>Ulm</t>
+        </is>
+      </c>
+      <c r="M318" t="inlineStr">
+        <is>
+          <t>1.08</t>
+        </is>
+      </c>
+      <c r="N318" t="inlineStr">
+        <is>
+          <t>0.62</t>
+        </is>
+      </c>
+      <c r="O318" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
+      <c r="P318" t="inlineStr">
+        <is>
+          <t>35%</t>
+        </is>
+      </c>
+      <c r="Q318" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="R318" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="S318" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T318" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U318" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V318" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W318" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="X318" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="Y318" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Z318" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA318" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB318" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC318" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AD318" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AE318" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AF318" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AG318" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AH318" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AI318" t="inlineStr"/>
+      <c r="AJ318" t="inlineStr"/>
+      <c r="AK318" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL318" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM318" t="inlineStr">
+        <is>
+          <t>683</t>
+        </is>
+      </c>
+      <c r="AN318" t="inlineStr">
+        <is>
+          <t>316</t>
+        </is>
+      </c>
+      <c r="AO318" t="inlineStr">
+        <is>
+          <t>594</t>
+        </is>
+      </c>
+      <c r="AP318" t="inlineStr">
+        <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="AQ318" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="AR318" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="AS318" t="inlineStr">
+        <is>
+          <t>4dKVOnA1</t>
+        </is>
+      </c>
+      <c r="AT318" t="inlineStr">
+        <is>
+          <t>kohfeldt florian</t>
+        </is>
+      </c>
+      <c r="AU318" t="inlineStr">
+        <is>
+          <t>QevvB2nf</t>
+        </is>
+      </c>
+      <c r="AV318" t="inlineStr">
+        <is>
+          <t>worle thomas</t>
+        </is>
+      </c>
+      <c r="AW318" t="n">
+        <v>59</v>
+      </c>
+      <c r="AX318" t="n">
+        <v>592</v>
+      </c>
+      <c r="AY318" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ318" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BA318" t="inlineStr"/>
+      <c r="BB318" t="inlineStr"/>
+      <c r="BC318" t="inlineStr"/>
+      <c r="BD318" t="inlineStr"/>
+      <c r="BE318" t="inlineStr"/>
+      <c r="BF318" t="inlineStr"/>
+      <c r="BG318" t="inlineStr"/>
+      <c r="BH318" t="inlineStr"/>
+      <c r="BI318" t="inlineStr"/>
+      <c r="BJ318" t="inlineStr"/>
+      <c r="BK318" t="inlineStr"/>
+      <c r="BL318" t="inlineStr"/>
+    </row>
+    <row r="319">
+      <c r="A319" s="1" t="inlineStr">
+        <is>
+          <t>AHQvdex2</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>27.10.2024 09:30</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>Stieler T.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>Avnet-Arena
+ (Magdeburg)</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>25 910</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr"/>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I319" t="inlineStr">
+        <is>
+          <t>YFuz2RLm</t>
+        </is>
+      </c>
+      <c r="J319" t="inlineStr">
+        <is>
+          <t>Magdeburg</t>
+        </is>
+      </c>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>dfNCCCzS</t>
+        </is>
+      </c>
+      <c r="L319" t="inlineStr">
+        <is>
+          <t>Hannover</t>
+        </is>
+      </c>
+      <c r="M319" t="inlineStr">
+        <is>
+          <t>1.28</t>
+        </is>
+      </c>
+      <c r="N319" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="O319" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
+      <c r="P319" t="inlineStr">
+        <is>
+          <t>35%</t>
+        </is>
+      </c>
+      <c r="Q319" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="R319" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="S319" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T319" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="U319" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="V319" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W319" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="X319" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="Y319" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Z319" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA319" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB319" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC319" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AD319" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AE319" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AF319" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AG319" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AH319" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AI319" t="inlineStr"/>
+      <c r="AJ319" t="inlineStr"/>
+      <c r="AK319" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AL319" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM319" t="inlineStr">
+        <is>
+          <t>587</t>
+        </is>
+      </c>
+      <c r="AN319" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="AO319" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="AP319" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="AQ319" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="AR319" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="AS319" t="inlineStr">
+        <is>
+          <t>IgZoGKFn</t>
+        </is>
+      </c>
+      <c r="AT319" t="inlineStr">
+        <is>
+          <t>titz christian</t>
+        </is>
+      </c>
+      <c r="AU319" t="inlineStr">
+        <is>
+          <t>t0ZPdkUl</t>
+        </is>
+      </c>
+      <c r="AV319" t="inlineStr">
+        <is>
+          <t>leitl stefan</t>
+        </is>
+      </c>
+      <c r="AW319" t="n">
+        <v>59</v>
+      </c>
+      <c r="AX319" t="n">
+        <v>592</v>
+      </c>
+      <c r="AY319" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ319" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BA319" t="inlineStr"/>
+      <c r="BB319" t="inlineStr"/>
+      <c r="BC319" t="inlineStr"/>
+      <c r="BD319" t="inlineStr"/>
+      <c r="BE319" t="inlineStr"/>
+      <c r="BF319" t="inlineStr"/>
+      <c r="BG319" t="inlineStr"/>
+      <c r="BH319" t="inlineStr"/>
+      <c r="BI319" t="inlineStr"/>
+      <c r="BJ319" t="inlineStr"/>
+      <c r="BK319" t="inlineStr"/>
+      <c r="BL319" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/germany/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
+++ b/data/germany/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL319"/>
+  <dimension ref="A1:BL335"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -65634,15 +65634,11 @@
           <t>15 000</t>
         </is>
       </c>
-      <c r="G314" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H314" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G314" t="n">
+        <v>0</v>
+      </c>
+      <c r="H314" t="n">
+        <v>0</v>
       </c>
       <c r="I314" t="inlineStr">
         <is>
@@ -65664,15 +65660,11 @@
           <t>Hoffenheim</t>
         </is>
       </c>
-      <c r="M314" t="inlineStr">
-        <is>
-          <t>1.29</t>
-        </is>
-      </c>
-      <c r="N314" t="inlineStr">
-        <is>
-          <t>0.56</t>
-        </is>
+      <c r="M314" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="N314" t="n">
+        <v>0.5600000000000001</v>
       </c>
       <c r="O314" t="inlineStr">
         <is>
@@ -65684,127 +65676,79 @@
           <t>53%</t>
         </is>
       </c>
-      <c r="Q314" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="R314" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="S314" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="T314" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U314" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="V314" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="W314" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="X314" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="Y314" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Z314" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA314" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB314" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC314" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="AD314" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AE314" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AF314" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AG314" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AH314" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+      <c r="Q314" t="n">
+        <v>17</v>
+      </c>
+      <c r="R314" t="n">
+        <v>12</v>
+      </c>
+      <c r="S314" t="n">
+        <v>3</v>
+      </c>
+      <c r="T314" t="n">
+        <v>4</v>
+      </c>
+      <c r="U314" t="n">
+        <v>12</v>
+      </c>
+      <c r="V314" t="n">
+        <v>3</v>
+      </c>
+      <c r="W314" t="n">
+        <v>16</v>
+      </c>
+      <c r="X314" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y314" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z314" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA314" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB314" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC314" t="n">
+        <v>25</v>
+      </c>
+      <c r="AD314" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE314" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF314" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG314" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH314" t="n">
+        <v>16</v>
       </c>
       <c r="AI314" t="inlineStr"/>
       <c r="AJ314" t="inlineStr"/>
-      <c r="AK314" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL314" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AM314" t="inlineStr">
-        <is>
-          <t>379</t>
-        </is>
-      </c>
-      <c r="AN314" t="inlineStr">
-        <is>
-          <t>445</t>
-        </is>
-      </c>
-      <c r="AO314" t="inlineStr">
-        <is>
-          <t>290</t>
-        </is>
-      </c>
-      <c r="AP314" t="inlineStr">
-        <is>
-          <t>355</t>
-        </is>
+      <c r="AK314" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL314" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM314" t="n">
+        <v>379</v>
+      </c>
+      <c r="AN314" t="n">
+        <v>445</v>
+      </c>
+      <c r="AO314" t="n">
+        <v>290</v>
+      </c>
+      <c r="AP314" t="n">
+        <v>355</v>
       </c>
       <c r="AQ314" t="inlineStr"/>
       <c r="AR314" t="inlineStr"/>
@@ -65848,35 +65792,23 @@
       <c r="BD314" t="inlineStr"/>
       <c r="BE314" t="inlineStr"/>
       <c r="BF314" t="inlineStr"/>
-      <c r="BG314" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="BH314" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="BI314" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="BJ314" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="BK314" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="BL314" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="BG314" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH314" t="n">
+        <v>5</v>
+      </c>
+      <c r="BI314" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ314" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK314" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL314" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="315">
@@ -65912,15 +65844,11 @@
           <t>22 012</t>
         </is>
       </c>
-      <c r="G315" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H315" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G315" t="n">
+        <v>1</v>
+      </c>
+      <c r="H315" t="n">
+        <v>1</v>
       </c>
       <c r="I315" t="inlineStr">
         <is>
@@ -65942,15 +65870,11 @@
           <t>Eintracht Frankfurt</t>
         </is>
       </c>
-      <c r="M315" t="inlineStr">
-        <is>
-          <t>1.44</t>
-        </is>
-      </c>
-      <c r="N315" t="inlineStr">
-        <is>
-          <t>1.81</t>
-        </is>
+      <c r="M315" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="N315" t="n">
+        <v>1.81</v>
       </c>
       <c r="O315" t="inlineStr">
         <is>
@@ -65962,135 +65886,83 @@
           <t>52%</t>
         </is>
       </c>
-      <c r="Q315" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="R315" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="S315" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="T315" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="U315" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V315" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="W315" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="X315" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="Y315" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Z315" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA315" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AB315" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC315" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AD315" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="AE315" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AF315" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AG315" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AH315" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AI315" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ315" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AK315" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AL315" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AM315" t="inlineStr">
-        <is>
-          <t>448</t>
-        </is>
-      </c>
-      <c r="AN315" t="inlineStr">
-        <is>
-          <t>492</t>
-        </is>
-      </c>
-      <c r="AO315" t="inlineStr">
-        <is>
-          <t>333</t>
-        </is>
-      </c>
-      <c r="AP315" t="inlineStr">
-        <is>
-          <t>379</t>
-        </is>
+      <c r="Q315" t="n">
+        <v>13</v>
+      </c>
+      <c r="R315" t="n">
+        <v>17</v>
+      </c>
+      <c r="S315" t="n">
+        <v>4</v>
+      </c>
+      <c r="T315" t="n">
+        <v>5</v>
+      </c>
+      <c r="U315" t="n">
+        <v>7</v>
+      </c>
+      <c r="V315" t="n">
+        <v>6</v>
+      </c>
+      <c r="W315" t="n">
+        <v>7</v>
+      </c>
+      <c r="X315" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y315" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z315" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA315" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB315" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC315" t="n">
+        <v>17</v>
+      </c>
+      <c r="AD315" t="n">
+        <v>28</v>
+      </c>
+      <c r="AE315" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF315" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG315" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH315" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI315" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ315" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK315" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL315" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM315" t="n">
+        <v>448</v>
+      </c>
+      <c r="AN315" t="n">
+        <v>492</v>
+      </c>
+      <c r="AO315" t="n">
+        <v>333</v>
+      </c>
+      <c r="AP315" t="n">
+        <v>379</v>
       </c>
       <c r="AQ315" t="inlineStr"/>
       <c r="AR315" t="inlineStr"/>
@@ -66134,35 +66006,23 @@
       <c r="BD315" t="inlineStr"/>
       <c r="BE315" t="inlineStr"/>
       <c r="BF315" t="inlineStr"/>
-      <c r="BG315" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="BH315" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="BI315" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="BJ315" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="BK315" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="BL315" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
+      <c r="BG315" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH315" t="n">
+        <v>6</v>
+      </c>
+      <c r="BI315" t="n">
+        <v>5</v>
+      </c>
+      <c r="BJ315" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK315" t="n">
+        <v>16</v>
+      </c>
+      <c r="BL315" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="316">
@@ -66198,15 +66058,11 @@
           <t>26 000</t>
         </is>
       </c>
-      <c r="G316" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H316" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="G316" t="n">
+        <v>0</v>
+      </c>
+      <c r="H316" t="n">
+        <v>5</v>
       </c>
       <c r="I316" t="inlineStr">
         <is>
@@ -66228,15 +66084,11 @@
           <t>Bayern Munich</t>
         </is>
       </c>
-      <c r="M316" t="inlineStr">
-        <is>
-          <t>0.52</t>
-        </is>
-      </c>
-      <c r="N316" t="inlineStr">
-        <is>
-          <t>2.23</t>
-        </is>
+      <c r="M316" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="N316" t="n">
+        <v>2.23</v>
       </c>
       <c r="O316" t="inlineStr">
         <is>
@@ -66248,127 +66100,79 @@
           <t>73%</t>
         </is>
       </c>
-      <c r="Q316" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="R316" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="S316" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="T316" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="U316" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="V316" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="W316" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="X316" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Y316" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Z316" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA316" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB316" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC316" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AD316" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AE316" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AF316" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AG316" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AH316" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="Q316" t="n">
+        <v>6</v>
+      </c>
+      <c r="R316" t="n">
+        <v>17</v>
+      </c>
+      <c r="S316" t="n">
+        <v>2</v>
+      </c>
+      <c r="T316" t="n">
+        <v>9</v>
+      </c>
+      <c r="U316" t="n">
+        <v>3</v>
+      </c>
+      <c r="V316" t="n">
+        <v>7</v>
+      </c>
+      <c r="W316" t="n">
+        <v>6</v>
+      </c>
+      <c r="X316" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y316" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z316" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA316" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB316" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC316" t="n">
+        <v>13</v>
+      </c>
+      <c r="AD316" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE316" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF316" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG316" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH316" t="n">
+        <v>6</v>
       </c>
       <c r="AI316" t="inlineStr"/>
       <c r="AJ316" t="inlineStr"/>
-      <c r="AK316" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL316" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AM316" t="inlineStr">
-        <is>
-          <t>247</t>
-        </is>
-      </c>
-      <c r="AN316" t="inlineStr">
-        <is>
-          <t>654</t>
-        </is>
-      </c>
-      <c r="AO316" t="inlineStr">
-        <is>
-          <t>169</t>
-        </is>
-      </c>
-      <c r="AP316" t="inlineStr">
-        <is>
-          <t>591</t>
-        </is>
+      <c r="AK316" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL316" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM316" t="n">
+        <v>247</v>
+      </c>
+      <c r="AN316" t="n">
+        <v>654</v>
+      </c>
+      <c r="AO316" t="n">
+        <v>169</v>
+      </c>
+      <c r="AP316" t="n">
+        <v>591</v>
       </c>
       <c r="AQ316" t="inlineStr"/>
       <c r="AR316" t="inlineStr"/>
@@ -66412,35 +66216,23 @@
       <c r="BD316" t="inlineStr"/>
       <c r="BE316" t="inlineStr"/>
       <c r="BF316" t="inlineStr"/>
-      <c r="BG316" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BH316" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BI316" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BJ316" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="BK316" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="BL316" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="BG316" t="n">
+        <v>1</v>
+      </c>
+      <c r="BH316" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI316" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ316" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK316" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL316" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="317">
@@ -66476,15 +66268,11 @@
           <t>21 809</t>
         </is>
       </c>
-      <c r="G317" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H317" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G317" t="n">
+        <v>1</v>
+      </c>
+      <c r="H317" t="n">
+        <v>1</v>
       </c>
       <c r="I317" t="inlineStr">
         <is>
@@ -66506,15 +66294,11 @@
           <t>Preussen Munster</t>
         </is>
       </c>
-      <c r="M317" t="inlineStr">
-        <is>
-          <t>0.68</t>
-        </is>
-      </c>
-      <c r="N317" t="inlineStr">
-        <is>
-          <t>0.30</t>
-        </is>
+      <c r="M317" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="N317" t="n">
+        <v>0.3</v>
       </c>
       <c r="O317" t="inlineStr">
         <is>
@@ -66526,137 +66310,85 @@
           <t>44%</t>
         </is>
       </c>
-      <c r="Q317" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R317" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="S317" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="T317" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U317" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V317" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="W317" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="X317" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y317" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Z317" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA317" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB317" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC317" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AD317" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="AE317" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AF317" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AG317" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AH317" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+      <c r="Q317" t="n">
+        <v>9</v>
+      </c>
+      <c r="R317" t="n">
+        <v>8</v>
+      </c>
+      <c r="S317" t="n">
+        <v>2</v>
+      </c>
+      <c r="T317" t="n">
+        <v>4</v>
+      </c>
+      <c r="U317" t="n">
+        <v>7</v>
+      </c>
+      <c r="V317" t="n">
+        <v>4</v>
+      </c>
+      <c r="W317" t="n">
+        <v>19</v>
+      </c>
+      <c r="X317" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y317" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z317" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA317" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB317" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC317" t="n">
+        <v>21</v>
+      </c>
+      <c r="AD317" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE317" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF317" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG317" t="n">
+        <v>8</v>
+      </c>
+      <c r="AH317" t="n">
+        <v>16</v>
       </c>
       <c r="AI317" t="inlineStr"/>
       <c r="AJ317" t="inlineStr"/>
-      <c r="AK317" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL317" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AM317" t="inlineStr">
-        <is>
-          <t>549</t>
-        </is>
-      </c>
-      <c r="AN317" t="inlineStr">
-        <is>
-          <t>407</t>
-        </is>
-      </c>
-      <c r="AO317" t="inlineStr">
-        <is>
-          <t>456</t>
-        </is>
-      </c>
-      <c r="AP317" t="inlineStr">
-        <is>
-          <t>317</t>
-        </is>
-      </c>
-      <c r="AQ317" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
-      <c r="AR317" t="inlineStr">
-        <is>
-          <t>134</t>
-        </is>
+      <c r="AK317" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL317" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM317" t="n">
+        <v>549</v>
+      </c>
+      <c r="AN317" t="n">
+        <v>407</v>
+      </c>
+      <c r="AO317" t="n">
+        <v>456</v>
+      </c>
+      <c r="AP317" t="n">
+        <v>317</v>
+      </c>
+      <c r="AQ317" t="n">
+        <v>126</v>
+      </c>
+      <c r="AR317" t="n">
+        <v>134</v>
       </c>
       <c r="AS317" t="inlineStr">
         <is>
@@ -66738,15 +66470,11 @@
           <t>17 455</t>
         </is>
       </c>
-      <c r="G318" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H318" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G318" t="n">
+        <v>1</v>
+      </c>
+      <c r="H318" t="n">
+        <v>1</v>
       </c>
       <c r="I318" t="inlineStr">
         <is>
@@ -66768,15 +66496,11 @@
           <t>Ulm</t>
         </is>
       </c>
-      <c r="M318" t="inlineStr">
-        <is>
-          <t>1.08</t>
-        </is>
-      </c>
-      <c r="N318" t="inlineStr">
-        <is>
-          <t>0.62</t>
-        </is>
+      <c r="M318" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N318" t="n">
+        <v>0.62</v>
       </c>
       <c r="O318" t="inlineStr">
         <is>
@@ -66788,137 +66512,85 @@
           <t>35%</t>
         </is>
       </c>
-      <c r="Q318" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="R318" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="S318" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="T318" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="U318" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="V318" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="W318" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="X318" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="Y318" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Z318" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA318" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB318" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC318" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AD318" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AE318" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AF318" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AG318" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AH318" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
+      <c r="Q318" t="n">
+        <v>15</v>
+      </c>
+      <c r="R318" t="n">
+        <v>5</v>
+      </c>
+      <c r="S318" t="n">
+        <v>5</v>
+      </c>
+      <c r="T318" t="n">
+        <v>3</v>
+      </c>
+      <c r="U318" t="n">
+        <v>10</v>
+      </c>
+      <c r="V318" t="n">
+        <v>2</v>
+      </c>
+      <c r="W318" t="n">
+        <v>14</v>
+      </c>
+      <c r="X318" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y318" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z318" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA318" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB318" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC318" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD318" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE318" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF318" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG318" t="n">
+        <v>9</v>
+      </c>
+      <c r="AH318" t="n">
+        <v>14</v>
       </c>
       <c r="AI318" t="inlineStr"/>
       <c r="AJ318" t="inlineStr"/>
-      <c r="AK318" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL318" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AM318" t="inlineStr">
-        <is>
-          <t>683</t>
-        </is>
-      </c>
-      <c r="AN318" t="inlineStr">
-        <is>
-          <t>316</t>
-        </is>
-      </c>
-      <c r="AO318" t="inlineStr">
-        <is>
-          <t>594</t>
-        </is>
-      </c>
-      <c r="AP318" t="inlineStr">
-        <is>
-          <t>231</t>
-        </is>
-      </c>
-      <c r="AQ318" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="AR318" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
+      <c r="AK318" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL318" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM318" t="n">
+        <v>683</v>
+      </c>
+      <c r="AN318" t="n">
+        <v>316</v>
+      </c>
+      <c r="AO318" t="n">
+        <v>594</v>
+      </c>
+      <c r="AP318" t="n">
+        <v>231</v>
+      </c>
+      <c r="AQ318" t="n">
+        <v>112</v>
+      </c>
+      <c r="AR318" t="n">
+        <v>115</v>
       </c>
       <c r="AS318" t="inlineStr">
         <is>
@@ -66996,15 +66668,11 @@
         </is>
       </c>
       <c r="F319" t="inlineStr"/>
-      <c r="G319" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H319" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="G319" t="n">
+        <v>0</v>
+      </c>
+      <c r="H319" t="n">
+        <v>3</v>
       </c>
       <c r="I319" t="inlineStr">
         <is>
@@ -67026,15 +66694,11 @@
           <t>Hannover</t>
         </is>
       </c>
-      <c r="M319" t="inlineStr">
-        <is>
-          <t>1.28</t>
-        </is>
-      </c>
-      <c r="N319" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
+      <c r="M319" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="N319" t="n">
+        <v>2.05</v>
       </c>
       <c r="O319" t="inlineStr">
         <is>
@@ -67046,137 +66710,85 @@
           <t>35%</t>
         </is>
       </c>
-      <c r="Q319" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="R319" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="S319" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="T319" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="U319" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="V319" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="W319" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="X319" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="Y319" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="Z319" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA319" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB319" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC319" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="AD319" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AE319" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AF319" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AG319" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AH319" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+      <c r="Q319" t="n">
+        <v>20</v>
+      </c>
+      <c r="R319" t="n">
+        <v>12</v>
+      </c>
+      <c r="S319" t="n">
+        <v>5</v>
+      </c>
+      <c r="T319" t="n">
+        <v>6</v>
+      </c>
+      <c r="U319" t="n">
+        <v>15</v>
+      </c>
+      <c r="V319" t="n">
+        <v>6</v>
+      </c>
+      <c r="W319" t="n">
+        <v>19</v>
+      </c>
+      <c r="X319" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y319" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z319" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA319" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB319" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC319" t="n">
+        <v>24</v>
+      </c>
+      <c r="AD319" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE319" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF319" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG319" t="n">
+        <v>9</v>
+      </c>
+      <c r="AH319" t="n">
+        <v>16</v>
       </c>
       <c r="AI319" t="inlineStr"/>
       <c r="AJ319" t="inlineStr"/>
-      <c r="AK319" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AL319" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AM319" t="inlineStr">
-        <is>
-          <t>587</t>
-        </is>
-      </c>
-      <c r="AN319" t="inlineStr">
-        <is>
-          <t>240</t>
-        </is>
-      </c>
-      <c r="AO319" t="inlineStr">
-        <is>
-          <t>499</t>
-        </is>
-      </c>
-      <c r="AP319" t="inlineStr">
-        <is>
-          <t>156</t>
-        </is>
-      </c>
-      <c r="AQ319" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="AR319" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
+      <c r="AK319" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL319" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM319" t="n">
+        <v>587</v>
+      </c>
+      <c r="AN319" t="n">
+        <v>240</v>
+      </c>
+      <c r="AO319" t="n">
+        <v>499</v>
+      </c>
+      <c r="AP319" t="n">
+        <v>156</v>
+      </c>
+      <c r="AQ319" t="n">
+        <v>125</v>
+      </c>
+      <c r="AR319" t="n">
+        <v>123</v>
       </c>
       <c r="AS319" t="inlineStr">
         <is>
@@ -67225,6 +66837,3718 @@
       <c r="BK319" t="inlineStr"/>
       <c r="BL319" t="inlineStr"/>
     </row>
+    <row r="320">
+      <c r="A320" s="1" t="inlineStr">
+        <is>
+          <t>84x8UQRb</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>30.10.2024 16:45</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>Haslberger W.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>Schüco Arena
+ (Bielefeld)</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>27 332</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>26 117</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I320" t="inlineStr">
+        <is>
+          <t>pp38UXK8</t>
+        </is>
+      </c>
+      <c r="J320" t="inlineStr">
+        <is>
+          <t>Advancing to next round
+Arminia Bielefeld</t>
+        </is>
+      </c>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>pzHW4oaE</t>
+        </is>
+      </c>
+      <c r="L320" t="inlineStr">
+        <is>
+          <t>Union Berlin</t>
+        </is>
+      </c>
+      <c r="M320" t="inlineStr"/>
+      <c r="N320" t="inlineStr"/>
+      <c r="O320" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="P320" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="Q320" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R320" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="S320" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T320" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="U320" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V320" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W320" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="X320" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="Y320" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Z320" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA320" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB320" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC320" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AD320" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AE320" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AF320" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AG320" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AH320" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AI320" t="inlineStr"/>
+      <c r="AJ320" t="inlineStr"/>
+      <c r="AK320" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AL320" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM320" t="inlineStr"/>
+      <c r="AN320" t="inlineStr"/>
+      <c r="AO320" t="inlineStr"/>
+      <c r="AP320" t="inlineStr"/>
+      <c r="AQ320" t="inlineStr"/>
+      <c r="AR320" t="inlineStr"/>
+      <c r="AS320" t="inlineStr">
+        <is>
+          <t>KrFXELrR</t>
+        </is>
+      </c>
+      <c r="AT320" t="inlineStr">
+        <is>
+          <t>kniat michel</t>
+        </is>
+      </c>
+      <c r="AU320" t="inlineStr">
+        <is>
+          <t>hpYJ6izc</t>
+        </is>
+      </c>
+      <c r="AV320" t="inlineStr">
+        <is>
+          <t>svensson bo</t>
+        </is>
+      </c>
+      <c r="AW320" t="n">
+        <v>59</v>
+      </c>
+      <c r="AX320" t="n">
+        <v>593</v>
+      </c>
+      <c r="AY320" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ320" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BA320" t="inlineStr"/>
+      <c r="BB320" t="inlineStr"/>
+      <c r="BC320" t="inlineStr"/>
+      <c r="BD320" t="inlineStr"/>
+      <c r="BE320" t="inlineStr"/>
+      <c r="BF320" t="inlineStr"/>
+      <c r="BG320" t="inlineStr"/>
+      <c r="BH320" t="inlineStr"/>
+      <c r="BI320" t="inlineStr"/>
+      <c r="BJ320" t="inlineStr"/>
+      <c r="BK320" t="inlineStr"/>
+      <c r="BL320" t="inlineStr"/>
+    </row>
+    <row r="321">
+      <c r="A321" s="1" t="inlineStr">
+        <is>
+          <t>6yf7a6SO</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>30.10.2024 16:45</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>Gerach T.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>PreZero Arena
+ (Sinsheim)</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>30 150</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>18 001</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I321" t="inlineStr">
+        <is>
+          <t>hQAtP9Sl</t>
+        </is>
+      </c>
+      <c r="J321" t="inlineStr">
+        <is>
+          <t>Advancing to next round
+Hoffenheim</t>
+        </is>
+      </c>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>6FDqshzF</t>
+        </is>
+      </c>
+      <c r="L321" t="inlineStr">
+        <is>
+          <t>Nurnberg</t>
+        </is>
+      </c>
+      <c r="M321" t="inlineStr"/>
+      <c r="N321" t="inlineStr"/>
+      <c r="O321" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="P321" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="Q321" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R321" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="S321" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="T321" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U321" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V321" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W321" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="X321" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="Y321" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Z321" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA321" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB321" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC321" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AD321" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="AE321" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AF321" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AG321" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AH321" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AI321" t="inlineStr"/>
+      <c r="AJ321" t="inlineStr"/>
+      <c r="AK321" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL321" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM321" t="inlineStr"/>
+      <c r="AN321" t="inlineStr"/>
+      <c r="AO321" t="inlineStr"/>
+      <c r="AP321" t="inlineStr"/>
+      <c r="AQ321" t="inlineStr"/>
+      <c r="AR321" t="inlineStr"/>
+      <c r="AS321" t="inlineStr">
+        <is>
+          <t>KUx4Q7x1</t>
+        </is>
+      </c>
+      <c r="AT321" t="inlineStr">
+        <is>
+          <t>matarazzo pellegrino</t>
+        </is>
+      </c>
+      <c r="AU321" t="inlineStr">
+        <is>
+          <t>tO31cZrF</t>
+        </is>
+      </c>
+      <c r="AV321" t="inlineStr">
+        <is>
+          <t>klose miroslav</t>
+        </is>
+      </c>
+      <c r="AW321" t="n">
+        <v>59</v>
+      </c>
+      <c r="AX321" t="n">
+        <v>593</v>
+      </c>
+      <c r="AY321" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ321" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BA321" t="inlineStr"/>
+      <c r="BB321" t="inlineStr"/>
+      <c r="BC321" t="inlineStr"/>
+      <c r="BD321" t="inlineStr"/>
+      <c r="BE321" t="inlineStr"/>
+      <c r="BF321" t="inlineStr"/>
+      <c r="BG321" t="inlineStr"/>
+      <c r="BH321" t="inlineStr"/>
+      <c r="BI321" t="inlineStr"/>
+      <c r="BJ321" t="inlineStr"/>
+      <c r="BK321" t="inlineStr"/>
+      <c r="BL321" t="inlineStr"/>
+    </row>
+    <row r="322">
+      <c r="A322" s="1" t="inlineStr">
+        <is>
+          <t>UyxiUHXF</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>30.10.2024 16:45</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>Stegemann S.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>Mewa Arena
+ (Mainz)</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>34 000</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>33 000</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I322" t="inlineStr">
+        <is>
+          <t>EuakNmc1</t>
+        </is>
+      </c>
+      <c r="J322" t="inlineStr">
+        <is>
+          <t>Mainz</t>
+        </is>
+      </c>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>nVp0wiqd</t>
+        </is>
+      </c>
+      <c r="L322" t="inlineStr">
+        <is>
+          <t>Bayern Munich
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M322" t="inlineStr"/>
+      <c r="N322" t="inlineStr"/>
+      <c r="O322" t="inlineStr">
+        <is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="P322" t="inlineStr">
+        <is>
+          <t>79%</t>
+        </is>
+      </c>
+      <c r="Q322" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="R322" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="S322" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T322" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="U322" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V322" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W322" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="X322" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="Y322" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Z322" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA322" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB322" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC322" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AD322" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AE322" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AF322" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AG322" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH322" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI322" t="inlineStr"/>
+      <c r="AJ322" t="inlineStr"/>
+      <c r="AK322" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AL322" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM322" t="inlineStr"/>
+      <c r="AN322" t="inlineStr"/>
+      <c r="AO322" t="inlineStr"/>
+      <c r="AP322" t="inlineStr"/>
+      <c r="AQ322" t="inlineStr"/>
+      <c r="AR322" t="inlineStr"/>
+      <c r="AS322" t="inlineStr">
+        <is>
+          <t>vZA6VYpf</t>
+        </is>
+      </c>
+      <c r="AT322" t="inlineStr">
+        <is>
+          <t>henriksen bo</t>
+        </is>
+      </c>
+      <c r="AU322" t="inlineStr">
+        <is>
+          <t>K6A2elS9</t>
+        </is>
+      </c>
+      <c r="AV322" t="inlineStr">
+        <is>
+          <t>kompany vincent</t>
+        </is>
+      </c>
+      <c r="AW322" t="n">
+        <v>59</v>
+      </c>
+      <c r="AX322" t="n">
+        <v>593</v>
+      </c>
+      <c r="AY322" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ322" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BA322" t="inlineStr"/>
+      <c r="BB322" t="inlineStr"/>
+      <c r="BC322" t="inlineStr"/>
+      <c r="BD322" t="inlineStr"/>
+      <c r="BE322" t="inlineStr"/>
+      <c r="BF322" t="inlineStr"/>
+      <c r="BG322" t="inlineStr"/>
+      <c r="BH322" t="inlineStr"/>
+      <c r="BI322" t="inlineStr"/>
+      <c r="BJ322" t="inlineStr"/>
+      <c r="BK322" t="inlineStr"/>
+      <c r="BL322" t="inlineStr"/>
+    </row>
+    <row r="323">
+      <c r="A323" s="1" t="inlineStr">
+        <is>
+          <t>YNea1ScC</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>30.10.2024 16:45</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>Stieler T.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>Rudolf-Harbig-Stadion
+ (Dresden)</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>32 249</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>30 070</t>
+        </is>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>zL1YsOi1</t>
+        </is>
+      </c>
+      <c r="J323" t="inlineStr">
+        <is>
+          <t>SG Dynamo Dresden</t>
+        </is>
+      </c>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>S0hPB9rA</t>
+        </is>
+      </c>
+      <c r="L323" t="inlineStr">
+        <is>
+          <t>Darmstadt
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M323" t="inlineStr"/>
+      <c r="N323" t="inlineStr"/>
+      <c r="O323" t="inlineStr">
+        <is>
+          <t>39%</t>
+        </is>
+      </c>
+      <c r="P323" t="inlineStr">
+        <is>
+          <t>61%</t>
+        </is>
+      </c>
+      <c r="Q323" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="R323" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="S323" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="T323" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="U323" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="V323" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W323" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="X323" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="Y323" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="Z323" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA323" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB323" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC323" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="AD323" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="AE323" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AF323" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AG323" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AH323" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AI323" t="inlineStr"/>
+      <c r="AJ323" t="inlineStr"/>
+      <c r="AK323" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL323" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM323" t="inlineStr"/>
+      <c r="AN323" t="inlineStr"/>
+      <c r="AO323" t="inlineStr"/>
+      <c r="AP323" t="inlineStr"/>
+      <c r="AQ323" t="inlineStr"/>
+      <c r="AR323" t="inlineStr"/>
+      <c r="AS323" t="inlineStr">
+        <is>
+          <t>4YhTfKrD</t>
+        </is>
+      </c>
+      <c r="AT323" t="inlineStr">
+        <is>
+          <t>stamm thomas</t>
+        </is>
+      </c>
+      <c r="AU323" t="inlineStr">
+        <is>
+          <t>4dKVOnA1</t>
+        </is>
+      </c>
+      <c r="AV323" t="inlineStr">
+        <is>
+          <t>kohfeldt florian</t>
+        </is>
+      </c>
+      <c r="AW323" t="n">
+        <v>59</v>
+      </c>
+      <c r="AX323" t="n">
+        <v>593</v>
+      </c>
+      <c r="AY323" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ323" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BA323" t="inlineStr"/>
+      <c r="BB323" t="inlineStr"/>
+      <c r="BC323" t="inlineStr"/>
+      <c r="BD323" t="inlineStr"/>
+      <c r="BE323" t="inlineStr"/>
+      <c r="BF323" t="inlineStr"/>
+      <c r="BG323" t="inlineStr"/>
+      <c r="BH323" t="inlineStr"/>
+      <c r="BI323" t="inlineStr"/>
+      <c r="BJ323" t="inlineStr"/>
+      <c r="BK323" t="inlineStr"/>
+      <c r="BL323" t="inlineStr"/>
+    </row>
+    <row r="324">
+      <c r="A324" s="1" t="inlineStr">
+        <is>
+          <t>dQ8kCqCU</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>30.10.2024 14:00</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>Jollenbeck M.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>Deutsche Bank Park
+ (Frankfurt)</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>58 000</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>58 000</t>
+        </is>
+      </c>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H324" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I324" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="J324" t="inlineStr">
+        <is>
+          <t>Advancing to next round
+Eintracht Frankfurt</t>
+        </is>
+      </c>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>88HSzjDr</t>
+        </is>
+      </c>
+      <c r="L324" t="inlineStr">
+        <is>
+          <t>B. Monchengladbach</t>
+        </is>
+      </c>
+      <c r="M324" t="inlineStr"/>
+      <c r="N324" t="inlineStr"/>
+      <c r="O324" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="P324" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="Q324" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R324" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="S324" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T324" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U324" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V324" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="W324" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="X324" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="Y324" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Z324" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA324" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB324" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC324" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AD324" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AE324" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AF324" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AG324" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AH324" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AI324" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AJ324" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK324" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL324" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AM324" t="inlineStr"/>
+      <c r="AN324" t="inlineStr"/>
+      <c r="AO324" t="inlineStr"/>
+      <c r="AP324" t="inlineStr"/>
+      <c r="AQ324" t="inlineStr"/>
+      <c r="AR324" t="inlineStr"/>
+      <c r="AS324" t="inlineStr">
+        <is>
+          <t>UgdQz0fK</t>
+        </is>
+      </c>
+      <c r="AT324" t="inlineStr">
+        <is>
+          <t>toppmoller dino</t>
+        </is>
+      </c>
+      <c r="AU324" t="inlineStr">
+        <is>
+          <t>M5BRZDsC</t>
+        </is>
+      </c>
+      <c r="AV324" t="inlineStr">
+        <is>
+          <t>seoane gerardo</t>
+        </is>
+      </c>
+      <c r="AW324" t="n">
+        <v>59</v>
+      </c>
+      <c r="AX324" t="n">
+        <v>593</v>
+      </c>
+      <c r="AY324" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ324" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BA324" t="inlineStr"/>
+      <c r="BB324" t="inlineStr"/>
+      <c r="BC324" t="inlineStr"/>
+      <c r="BD324" t="inlineStr"/>
+      <c r="BE324" t="inlineStr"/>
+      <c r="BF324" t="inlineStr"/>
+      <c r="BG324" t="inlineStr"/>
+      <c r="BH324" t="inlineStr"/>
+      <c r="BI324" t="inlineStr"/>
+      <c r="BJ324" t="inlineStr"/>
+      <c r="BK324" t="inlineStr"/>
+      <c r="BL324" t="inlineStr"/>
+    </row>
+    <row r="325">
+      <c r="A325" s="1" t="inlineStr">
+        <is>
+          <t>0bFtE5sI</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>30.10.2024 14:00</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>Brych F.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>Europa-Park Stadion
+ (Freiburg)</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>34 700</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>34 500</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I325" t="inlineStr">
+        <is>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
+      <c r="J325" t="inlineStr">
+        <is>
+          <t>Advancing to next round
+Freiburg</t>
+        </is>
+      </c>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>v9k3aY5F</t>
+        </is>
+      </c>
+      <c r="L325" t="inlineStr">
+        <is>
+          <t>Hamburger SV</t>
+        </is>
+      </c>
+      <c r="M325" t="inlineStr"/>
+      <c r="N325" t="inlineStr"/>
+      <c r="O325" t="inlineStr">
+        <is>
+          <t>46%</t>
+        </is>
+      </c>
+      <c r="P325" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="Q325" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R325" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="S325" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T325" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U325" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V325" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W325" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="X325" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="Y325" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Z325" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA325" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB325" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC325" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AD325" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AE325" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AF325" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AG325" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AH325" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AI325" t="inlineStr"/>
+      <c r="AJ325" t="inlineStr"/>
+      <c r="AK325" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AL325" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM325" t="inlineStr"/>
+      <c r="AN325" t="inlineStr"/>
+      <c r="AO325" t="inlineStr"/>
+      <c r="AP325" t="inlineStr"/>
+      <c r="AQ325" t="inlineStr"/>
+      <c r="AR325" t="inlineStr"/>
+      <c r="AS325" t="inlineStr">
+        <is>
+          <t>YZPE6Sx7</t>
+        </is>
+      </c>
+      <c r="AT325" t="inlineStr">
+        <is>
+          <t>schuster julian</t>
+        </is>
+      </c>
+      <c r="AU325" t="inlineStr">
+        <is>
+          <t>EDRZkDzS</t>
+        </is>
+      </c>
+      <c r="AV325" t="inlineStr">
+        <is>
+          <t>baumgart steffen</t>
+        </is>
+      </c>
+      <c r="AW325" t="n">
+        <v>59</v>
+      </c>
+      <c r="AX325" t="n">
+        <v>593</v>
+      </c>
+      <c r="AY325" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ325" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BA325" t="inlineStr"/>
+      <c r="BB325" t="inlineStr"/>
+      <c r="BC325" t="inlineStr"/>
+      <c r="BD325" t="inlineStr"/>
+      <c r="BE325" t="inlineStr"/>
+      <c r="BF325" t="inlineStr"/>
+      <c r="BG325" t="inlineStr"/>
+      <c r="BH325" t="inlineStr"/>
+      <c r="BI325" t="inlineStr"/>
+      <c r="BJ325" t="inlineStr"/>
+      <c r="BK325" t="inlineStr"/>
+      <c r="BL325" t="inlineStr"/>
+    </row>
+    <row r="326">
+      <c r="A326" s="1" t="inlineStr">
+        <is>
+          <t>YkhlAdtp</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>30.10.2024 14:00</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>Kampka R.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>Olympiastadion
+ (Berlin)</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>74 667</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>43 000</t>
+        </is>
+      </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H326" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I326" t="inlineStr">
+        <is>
+          <t>2y0u8Wrq</t>
+        </is>
+      </c>
+      <c r="J326" t="inlineStr">
+        <is>
+          <t>Advancing to next round
+Hertha Berlin</t>
+        </is>
+      </c>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>KWixEVWi</t>
+        </is>
+      </c>
+      <c r="L326" t="inlineStr">
+        <is>
+          <t>Heidenheim</t>
+        </is>
+      </c>
+      <c r="M326" t="inlineStr"/>
+      <c r="N326" t="inlineStr"/>
+      <c r="O326" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="P326" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="Q326" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R326" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="S326" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T326" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U326" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V326" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W326" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="X326" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="Y326" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Z326" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA326" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB326" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC326" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AD326" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="AE326" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AF326" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AG326" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AH326" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AI326" t="inlineStr"/>
+      <c r="AJ326" t="inlineStr"/>
+      <c r="AK326" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AL326" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM326" t="inlineStr"/>
+      <c r="AN326" t="inlineStr"/>
+      <c r="AO326" t="inlineStr"/>
+      <c r="AP326" t="inlineStr"/>
+      <c r="AQ326" t="inlineStr"/>
+      <c r="AR326" t="inlineStr"/>
+      <c r="AS326" t="inlineStr">
+        <is>
+          <t>YmfcAeCo</t>
+        </is>
+      </c>
+      <c r="AT326" t="inlineStr">
+        <is>
+          <t>fiel cristian</t>
+        </is>
+      </c>
+      <c r="AU326" t="inlineStr">
+        <is>
+          <t>4ljanukM</t>
+        </is>
+      </c>
+      <c r="AV326" t="inlineStr">
+        <is>
+          <t>schmidt frank</t>
+        </is>
+      </c>
+      <c r="AW326" t="n">
+        <v>59</v>
+      </c>
+      <c r="AX326" t="n">
+        <v>593</v>
+      </c>
+      <c r="AY326" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ326" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BA326" t="inlineStr"/>
+      <c r="BB326" t="inlineStr"/>
+      <c r="BC326" t="inlineStr"/>
+      <c r="BD326" t="inlineStr"/>
+      <c r="BE326" t="inlineStr"/>
+      <c r="BF326" t="inlineStr"/>
+      <c r="BG326" t="inlineStr"/>
+      <c r="BH326" t="inlineStr"/>
+      <c r="BI326" t="inlineStr"/>
+      <c r="BJ326" t="inlineStr"/>
+      <c r="BK326" t="inlineStr"/>
+      <c r="BL326" t="inlineStr"/>
+    </row>
+    <row r="327">
+      <c r="A327" s="1" t="inlineStr">
+        <is>
+          <t>tGed8zBd</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>30.10.2024 14:00</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>Burda M.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>Home Deluxe Arena
+ (Paderborn)</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H327" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I327" t="inlineStr">
+        <is>
+          <t>G2Op923t</t>
+        </is>
+      </c>
+      <c r="J327" t="inlineStr">
+        <is>
+          <t>Paderborn</t>
+        </is>
+      </c>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>Ig1f1fy3</t>
+        </is>
+      </c>
+      <c r="L327" t="inlineStr">
+        <is>
+          <t>Werder Bremen
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M327" t="inlineStr"/>
+      <c r="N327" t="inlineStr"/>
+      <c r="O327" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="P327" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="Q327" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="R327" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="S327" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="T327" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U327" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V327" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W327" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="X327" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="Y327" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Z327" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA327" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB327" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC327" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AD327" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AE327" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AF327" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AG327" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AH327" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AI327" t="inlineStr"/>
+      <c r="AJ327" t="inlineStr"/>
+      <c r="AK327" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL327" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM327" t="inlineStr"/>
+      <c r="AN327" t="inlineStr"/>
+      <c r="AO327" t="inlineStr"/>
+      <c r="AP327" t="inlineStr"/>
+      <c r="AQ327" t="inlineStr"/>
+      <c r="AR327" t="inlineStr"/>
+      <c r="AS327" t="inlineStr">
+        <is>
+          <t>0AI1QUJH</t>
+        </is>
+      </c>
+      <c r="AT327" t="inlineStr">
+        <is>
+          <t>kwasniok lukas</t>
+        </is>
+      </c>
+      <c r="AU327" t="inlineStr">
+        <is>
+          <t>4fuCGs9P</t>
+        </is>
+      </c>
+      <c r="AV327" t="inlineStr">
+        <is>
+          <t>werner ole</t>
+        </is>
+      </c>
+      <c r="AW327" t="n">
+        <v>59</v>
+      </c>
+      <c r="AX327" t="n">
+        <v>593</v>
+      </c>
+      <c r="AY327" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ327" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BA327" t="inlineStr"/>
+      <c r="BB327" t="inlineStr"/>
+      <c r="BC327" t="inlineStr"/>
+      <c r="BD327" t="inlineStr"/>
+      <c r="BE327" t="inlineStr"/>
+      <c r="BF327" t="inlineStr"/>
+      <c r="BG327" t="inlineStr"/>
+      <c r="BH327" t="inlineStr"/>
+      <c r="BI327" t="inlineStr"/>
+      <c r="BJ327" t="inlineStr"/>
+      <c r="BK327" t="inlineStr"/>
+      <c r="BL327" t="inlineStr"/>
+    </row>
+    <row r="328">
+      <c r="A328" s="1" t="inlineStr">
+        <is>
+          <t>EsHYFRC5</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>29.10.2024 16:45</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>Dankert B.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>RheinEnergieStadion
+ (Cologne)</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>50 000</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>48 000</t>
+        </is>
+      </c>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I328" t="inlineStr">
+        <is>
+          <t>WG9pOTse</t>
+        </is>
+      </c>
+      <c r="J328" t="inlineStr">
+        <is>
+          <t>Advancing to next round
+FC Koln</t>
+        </is>
+      </c>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>63WsD2ei</t>
+        </is>
+      </c>
+      <c r="L328" t="inlineStr">
+        <is>
+          <t>Holstein Kiel</t>
+        </is>
+      </c>
+      <c r="M328" t="inlineStr"/>
+      <c r="N328" t="inlineStr"/>
+      <c r="O328" t="inlineStr">
+        <is>
+          <t>41%</t>
+        </is>
+      </c>
+      <c r="P328" t="inlineStr">
+        <is>
+          <t>59%</t>
+        </is>
+      </c>
+      <c r="Q328" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R328" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="S328" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T328" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U328" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V328" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="W328" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="X328" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="Y328" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Z328" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA328" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB328" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC328" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AD328" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="AE328" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AF328" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AG328" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AH328" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AI328" t="inlineStr"/>
+      <c r="AJ328" t="inlineStr"/>
+      <c r="AK328" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL328" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AM328" t="inlineStr"/>
+      <c r="AN328" t="inlineStr"/>
+      <c r="AO328" t="inlineStr"/>
+      <c r="AP328" t="inlineStr"/>
+      <c r="AQ328" t="inlineStr"/>
+      <c r="AR328" t="inlineStr"/>
+      <c r="AS328" t="inlineStr">
+        <is>
+          <t>4fX0k7gg</t>
+        </is>
+      </c>
+      <c r="AT328" t="inlineStr">
+        <is>
+          <t>struber gerhard</t>
+        </is>
+      </c>
+      <c r="AU328" t="inlineStr">
+        <is>
+          <t>A15eUM4C</t>
+        </is>
+      </c>
+      <c r="AV328" t="inlineStr">
+        <is>
+          <t>rapp marcel</t>
+        </is>
+      </c>
+      <c r="AW328" t="n">
+        <v>59</v>
+      </c>
+      <c r="AX328" t="n">
+        <v>593</v>
+      </c>
+      <c r="AY328" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ328" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BA328" t="inlineStr"/>
+      <c r="BB328" t="inlineStr"/>
+      <c r="BC328" t="inlineStr"/>
+      <c r="BD328" t="inlineStr"/>
+      <c r="BE328" t="inlineStr"/>
+      <c r="BF328" t="inlineStr"/>
+      <c r="BG328" t="inlineStr"/>
+      <c r="BH328" t="inlineStr"/>
+      <c r="BI328" t="inlineStr"/>
+      <c r="BJ328" t="inlineStr"/>
+      <c r="BK328" t="inlineStr"/>
+      <c r="BL328" t="inlineStr"/>
+    </row>
+    <row r="329">
+      <c r="A329" s="1" t="inlineStr">
+        <is>
+          <t>CxqaWncn</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>29.10.2024 16:45</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>Bauer T.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>Jahnstadion Regensburg
+ (Regensburg)</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>15 210</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>11 627</t>
+        </is>
+      </c>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H329" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I329" t="inlineStr">
+        <is>
+          <t>UiCmEP56</t>
+        </is>
+      </c>
+      <c r="J329" t="inlineStr">
+        <is>
+          <t>Advancing to next round
+Regensburg</t>
+        </is>
+      </c>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>CCQGbik8</t>
+        </is>
+      </c>
+      <c r="L329" t="inlineStr">
+        <is>
+          <t>Greuther Furth</t>
+        </is>
+      </c>
+      <c r="M329" t="inlineStr"/>
+      <c r="N329" t="inlineStr"/>
+      <c r="O329" t="inlineStr">
+        <is>
+          <t>31%</t>
+        </is>
+      </c>
+      <c r="P329" t="inlineStr">
+        <is>
+          <t>69%</t>
+        </is>
+      </c>
+      <c r="Q329" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="R329" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="S329" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T329" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U329" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V329" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W329" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="X329" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="Y329" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Z329" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA329" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB329" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC329" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="AD329" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="AE329" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AF329" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AG329" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AH329" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AI329" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AJ329" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK329" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AL329" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM329" t="inlineStr"/>
+      <c r="AN329" t="inlineStr"/>
+      <c r="AO329" t="inlineStr"/>
+      <c r="AP329" t="inlineStr"/>
+      <c r="AQ329" t="inlineStr"/>
+      <c r="AR329" t="inlineStr"/>
+      <c r="AS329" t="inlineStr">
+        <is>
+          <t>zP70fYtq</t>
+        </is>
+      </c>
+      <c r="AT329" t="inlineStr">
+        <is>
+          <t>patz andreas</t>
+        </is>
+      </c>
+      <c r="AU329" t="inlineStr">
+        <is>
+          <t>S6Oa4cwI</t>
+        </is>
+      </c>
+      <c r="AV329" t="inlineStr">
+        <is>
+          <t>haas leonhard</t>
+        </is>
+      </c>
+      <c r="AW329" t="n">
+        <v>59</v>
+      </c>
+      <c r="AX329" t="n">
+        <v>593</v>
+      </c>
+      <c r="AY329" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ329" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BA329" t="inlineStr"/>
+      <c r="BB329" t="inlineStr"/>
+      <c r="BC329" t="inlineStr"/>
+      <c r="BD329" t="inlineStr"/>
+      <c r="BE329" t="inlineStr"/>
+      <c r="BF329" t="inlineStr"/>
+      <c r="BG329" t="inlineStr"/>
+      <c r="BH329" t="inlineStr"/>
+      <c r="BI329" t="inlineStr"/>
+      <c r="BJ329" t="inlineStr"/>
+      <c r="BK329" t="inlineStr"/>
+      <c r="BL329" t="inlineStr"/>
+    </row>
+    <row r="330">
+      <c r="A330" s="1" t="inlineStr">
+        <is>
+          <t>hSSPHmrg</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>29.10.2024 16:45</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>Schlager D.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>MHPArena
+ (Stuttgart)</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>60 449</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>60 000</t>
+        </is>
+      </c>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H330" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I330" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="J330" t="inlineStr">
+        <is>
+          <t>Advancing to next round
+Stuttgart</t>
+        </is>
+      </c>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>naWckLmC</t>
+        </is>
+      </c>
+      <c r="L330" t="inlineStr">
+        <is>
+          <t>Kaiserslautern</t>
+        </is>
+      </c>
+      <c r="M330" t="inlineStr"/>
+      <c r="N330" t="inlineStr"/>
+      <c r="O330" t="inlineStr">
+        <is>
+          <t>71%</t>
+        </is>
+      </c>
+      <c r="P330" t="inlineStr">
+        <is>
+          <t>29%</t>
+        </is>
+      </c>
+      <c r="Q330" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="R330" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="S330" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="T330" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U330" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V330" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="W330" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="X330" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="Y330" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Z330" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA330" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB330" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC330" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AD330" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AE330" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AF330" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AG330" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AH330" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AI330" t="inlineStr"/>
+      <c r="AJ330" t="inlineStr"/>
+      <c r="AK330" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL330" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AM330" t="inlineStr"/>
+      <c r="AN330" t="inlineStr"/>
+      <c r="AO330" t="inlineStr"/>
+      <c r="AP330" t="inlineStr"/>
+      <c r="AQ330" t="inlineStr"/>
+      <c r="AR330" t="inlineStr"/>
+      <c r="AS330" t="inlineStr">
+        <is>
+          <t>GzfvcwRj</t>
+        </is>
+      </c>
+      <c r="AT330" t="inlineStr">
+        <is>
+          <t>hoeness sebastian</t>
+        </is>
+      </c>
+      <c r="AU330" t="inlineStr">
+        <is>
+          <t>4bJLk19p</t>
+        </is>
+      </c>
+      <c r="AV330" t="inlineStr">
+        <is>
+          <t>anfang marcus</t>
+        </is>
+      </c>
+      <c r="AW330" t="n">
+        <v>59</v>
+      </c>
+      <c r="AX330" t="n">
+        <v>593</v>
+      </c>
+      <c r="AY330" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ330" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BA330" t="inlineStr"/>
+      <c r="BB330" t="inlineStr"/>
+      <c r="BC330" t="inlineStr"/>
+      <c r="BD330" t="inlineStr"/>
+      <c r="BE330" t="inlineStr"/>
+      <c r="BF330" t="inlineStr"/>
+      <c r="BG330" t="inlineStr"/>
+      <c r="BH330" t="inlineStr"/>
+      <c r="BI330" t="inlineStr"/>
+      <c r="BJ330" t="inlineStr"/>
+      <c r="BK330" t="inlineStr"/>
+      <c r="BL330" t="inlineStr"/>
+    </row>
+    <row r="331">
+      <c r="A331" s="1" t="inlineStr">
+        <is>
+          <t>E1uGS4dB</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>29.10.2024 16:45</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>Siebert D.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>Volkswagen Arena
+ (Wolfsburg)</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>28 917</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>30 000</t>
+        </is>
+      </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I331" t="inlineStr">
+        <is>
+          <t>nwkTahLL</t>
+        </is>
+      </c>
+      <c r="J331" t="inlineStr">
+        <is>
+          <t>Advancing to next round
+Wolfsburg</t>
+        </is>
+      </c>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="L331" t="inlineStr">
+        <is>
+          <t>Dortmund</t>
+        </is>
+      </c>
+      <c r="M331" t="inlineStr"/>
+      <c r="N331" t="inlineStr"/>
+      <c r="O331" t="inlineStr">
+        <is>
+          <t>42%</t>
+        </is>
+      </c>
+      <c r="P331" t="inlineStr">
+        <is>
+          <t>58%</t>
+        </is>
+      </c>
+      <c r="Q331" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="R331" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S331" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T331" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U331" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="V331" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W331" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="X331" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="Y331" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Z331" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA331" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB331" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC331" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AD331" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AE331" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AF331" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AG331" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AH331" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AI331" t="inlineStr"/>
+      <c r="AJ331" t="inlineStr"/>
+      <c r="AK331" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL331" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AM331" t="inlineStr"/>
+      <c r="AN331" t="inlineStr"/>
+      <c r="AO331" t="inlineStr"/>
+      <c r="AP331" t="inlineStr"/>
+      <c r="AQ331" t="inlineStr"/>
+      <c r="AR331" t="inlineStr"/>
+      <c r="AS331" t="inlineStr">
+        <is>
+          <t>f3ddUIXs</t>
+        </is>
+      </c>
+      <c r="AT331" t="inlineStr">
+        <is>
+          <t>hasenhuttl ralph</t>
+        </is>
+      </c>
+      <c r="AU331" t="inlineStr">
+        <is>
+          <t>IkCftsQm</t>
+        </is>
+      </c>
+      <c r="AV331" t="inlineStr">
+        <is>
+          <t>sahin nuri</t>
+        </is>
+      </c>
+      <c r="AW331" t="n">
+        <v>59</v>
+      </c>
+      <c r="AX331" t="n">
+        <v>593</v>
+      </c>
+      <c r="AY331" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ331" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BA331" t="inlineStr"/>
+      <c r="BB331" t="inlineStr"/>
+      <c r="BC331" t="inlineStr"/>
+      <c r="BD331" t="inlineStr"/>
+      <c r="BE331" t="inlineStr"/>
+      <c r="BF331" t="inlineStr"/>
+      <c r="BG331" t="inlineStr"/>
+      <c r="BH331" t="inlineStr"/>
+      <c r="BI331" t="inlineStr"/>
+      <c r="BJ331" t="inlineStr"/>
+      <c r="BK331" t="inlineStr"/>
+      <c r="BL331" t="inlineStr"/>
+    </row>
+    <row r="332">
+      <c r="A332" s="1" t="inlineStr">
+        <is>
+          <t>6XcNMZPk</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>29.10.2024 14:00</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>Willenborg F.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>WWK Arena
+ (Augsburg)</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>30 660</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>27 511</t>
+        </is>
+      </c>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H332" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I332" t="inlineStr">
+        <is>
+          <t>fTVNku3I</t>
+        </is>
+      </c>
+      <c r="J332" t="inlineStr">
+        <is>
+          <t>Advancing to next round
+Augsburg</t>
+        </is>
+      </c>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>0Ija0Ej9</t>
+        </is>
+      </c>
+      <c r="L332" t="inlineStr">
+        <is>
+          <t>Schalke</t>
+        </is>
+      </c>
+      <c r="M332" t="inlineStr"/>
+      <c r="N332" t="inlineStr"/>
+      <c r="O332" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
+      </c>
+      <c r="P332" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="Q332" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R332" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="S332" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T332" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U332" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V332" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W332" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="X332" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y332" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Z332" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA332" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB332" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC332" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AD332" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="AE332" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AF332" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG332" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AH332" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AI332" t="inlineStr"/>
+      <c r="AJ332" t="inlineStr"/>
+      <c r="AK332" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AL332" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AM332" t="inlineStr"/>
+      <c r="AN332" t="inlineStr"/>
+      <c r="AO332" t="inlineStr"/>
+      <c r="AP332" t="inlineStr"/>
+      <c r="AQ332" t="inlineStr"/>
+      <c r="AR332" t="inlineStr"/>
+      <c r="AS332" t="inlineStr">
+        <is>
+          <t>2VSFgl3c</t>
+        </is>
+      </c>
+      <c r="AT332" t="inlineStr">
+        <is>
+          <t>thorup jess</t>
+        </is>
+      </c>
+      <c r="AU332" t="inlineStr">
+        <is>
+          <t>SMaB5LKo</t>
+        </is>
+      </c>
+      <c r="AV332" t="inlineStr">
+        <is>
+          <t>van wonderen kees</t>
+        </is>
+      </c>
+      <c r="AW332" t="n">
+        <v>59</v>
+      </c>
+      <c r="AX332" t="n">
+        <v>593</v>
+      </c>
+      <c r="AY332" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ332" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BA332" t="inlineStr"/>
+      <c r="BB332" t="inlineStr"/>
+      <c r="BC332" t="inlineStr"/>
+      <c r="BD332" t="inlineStr"/>
+      <c r="BE332" t="inlineStr"/>
+      <c r="BF332" t="inlineStr"/>
+      <c r="BG332" t="inlineStr"/>
+      <c r="BH332" t="inlineStr"/>
+      <c r="BI332" t="inlineStr"/>
+      <c r="BJ332" t="inlineStr"/>
+      <c r="BK332" t="inlineStr"/>
+      <c r="BL332" t="inlineStr"/>
+    </row>
+    <row r="333">
+      <c r="A333" s="1" t="inlineStr">
+        <is>
+          <t>zk7iSe2S</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>29.10.2024 14:00</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>Brand B.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>BayArena
+ (Leverkusen)</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>30 210</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>29 787</t>
+        </is>
+      </c>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H333" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I333" t="inlineStr">
+        <is>
+          <t>4jcj2zMd</t>
+        </is>
+      </c>
+      <c r="J333" t="inlineStr">
+        <is>
+          <t>Advancing to next round
+Bayer Leverkusen</t>
+        </is>
+      </c>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>6in2Eknb</t>
+        </is>
+      </c>
+      <c r="L333" t="inlineStr">
+        <is>
+          <t>Elversberg</t>
+        </is>
+      </c>
+      <c r="M333" t="inlineStr"/>
+      <c r="N333" t="inlineStr"/>
+      <c r="O333" t="inlineStr">
+        <is>
+          <t>63%</t>
+        </is>
+      </c>
+      <c r="P333" t="inlineStr">
+        <is>
+          <t>37%</t>
+        </is>
+      </c>
+      <c r="Q333" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R333" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="S333" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="T333" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U333" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V333" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W333" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="X333" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="Y333" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Z333" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AA333" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB333" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC333" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AD333" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AE333" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AF333" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AG333" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AH333" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AI333" t="inlineStr"/>
+      <c r="AJ333" t="inlineStr"/>
+      <c r="AK333" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL333" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM333" t="inlineStr"/>
+      <c r="AN333" t="inlineStr"/>
+      <c r="AO333" t="inlineStr"/>
+      <c r="AP333" t="inlineStr"/>
+      <c r="AQ333" t="inlineStr"/>
+      <c r="AR333" t="inlineStr"/>
+      <c r="AS333" t="inlineStr">
+        <is>
+          <t>hAcTWKKN</t>
+        </is>
+      </c>
+      <c r="AT333" t="inlineStr">
+        <is>
+          <t>alonso xabi</t>
+        </is>
+      </c>
+      <c r="AU333" t="inlineStr">
+        <is>
+          <t>8E8qmw3d</t>
+        </is>
+      </c>
+      <c r="AV333" t="inlineStr">
+        <is>
+          <t>steffen horst</t>
+        </is>
+      </c>
+      <c r="AW333" t="n">
+        <v>59</v>
+      </c>
+      <c r="AX333" t="n">
+        <v>593</v>
+      </c>
+      <c r="AY333" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ333" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BA333" t="inlineStr"/>
+      <c r="BB333" t="inlineStr"/>
+      <c r="BC333" t="inlineStr"/>
+      <c r="BD333" t="inlineStr"/>
+      <c r="BE333" t="inlineStr"/>
+      <c r="BF333" t="inlineStr"/>
+      <c r="BG333" t="inlineStr"/>
+      <c r="BH333" t="inlineStr"/>
+      <c r="BI333" t="inlineStr"/>
+      <c r="BJ333" t="inlineStr"/>
+      <c r="BK333" t="inlineStr"/>
+      <c r="BL333" t="inlineStr"/>
+    </row>
+    <row r="334">
+      <c r="A334" s="1" t="inlineStr">
+        <is>
+          <t>dOwqWw33</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>29.10.2024 14:00</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>Erbst L.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>Bieberer Berg Stadion
+ (Offenbach am Main)</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>20 500</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>20 071</t>
+        </is>
+      </c>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H334" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I334" t="inlineStr">
+        <is>
+          <t>YJURlaIO</t>
+        </is>
+      </c>
+      <c r="J334" t="inlineStr">
+        <is>
+          <t>Offenbach</t>
+        </is>
+      </c>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>EB3q7jbk</t>
+        </is>
+      </c>
+      <c r="L334" t="inlineStr">
+        <is>
+          <t>Karlsruher SC
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M334" t="inlineStr"/>
+      <c r="N334" t="inlineStr"/>
+      <c r="O334" t="inlineStr">
+        <is>
+          <t>26%</t>
+        </is>
+      </c>
+      <c r="P334" t="inlineStr">
+        <is>
+          <t>74%</t>
+        </is>
+      </c>
+      <c r="Q334" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R334" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="S334" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="T334" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="U334" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V334" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W334" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="X334" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="Y334" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Z334" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA334" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB334" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC334" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="AD334" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AE334" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AF334" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AG334" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH334" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI334" t="inlineStr"/>
+      <c r="AJ334" t="inlineStr"/>
+      <c r="AK334" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL334" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AM334" t="inlineStr"/>
+      <c r="AN334" t="inlineStr"/>
+      <c r="AO334" t="inlineStr"/>
+      <c r="AP334" t="inlineStr"/>
+      <c r="AQ334" t="inlineStr"/>
+      <c r="AR334" t="inlineStr"/>
+      <c r="AS334" t="inlineStr">
+        <is>
+          <t>GWkh67yH</t>
+        </is>
+      </c>
+      <c r="AT334" t="inlineStr">
+        <is>
+          <t>neidhart christian</t>
+        </is>
+      </c>
+      <c r="AU334" t="inlineStr">
+        <is>
+          <t>OzPMRhK3</t>
+        </is>
+      </c>
+      <c r="AV334" t="inlineStr">
+        <is>
+          <t>eichner christian</t>
+        </is>
+      </c>
+      <c r="AW334" t="n">
+        <v>59</v>
+      </c>
+      <c r="AX334" t="n">
+        <v>593</v>
+      </c>
+      <c r="AY334" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ334" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BA334" t="inlineStr"/>
+      <c r="BB334" t="inlineStr"/>
+      <c r="BC334" t="inlineStr"/>
+      <c r="BD334" t="inlineStr"/>
+      <c r="BE334" t="inlineStr"/>
+      <c r="BF334" t="inlineStr"/>
+      <c r="BG334" t="inlineStr"/>
+      <c r="BH334" t="inlineStr"/>
+      <c r="BI334" t="inlineStr"/>
+      <c r="BJ334" t="inlineStr"/>
+      <c r="BK334" t="inlineStr"/>
+      <c r="BL334" t="inlineStr"/>
+    </row>
+    <row r="335">
+      <c r="A335" s="1" t="inlineStr">
+        <is>
+          <t>p2PHJ9Dt</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>29.10.2024 14:00</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>Zwayer F.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>Red Bull Arena
+ (Leipzig)</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>47 069</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>40 478</t>
+        </is>
+      </c>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H335" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I335" t="inlineStr">
+        <is>
+          <t>KbS1suSm</t>
+        </is>
+      </c>
+      <c r="J335" t="inlineStr">
+        <is>
+          <t>Advancing to next round
+RB Leipzig</t>
+        </is>
+      </c>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="L335" t="inlineStr">
+        <is>
+          <t>St. Pauli</t>
+        </is>
+      </c>
+      <c r="M335" t="inlineStr"/>
+      <c r="N335" t="inlineStr"/>
+      <c r="O335" t="inlineStr">
+        <is>
+          <t>46%</t>
+        </is>
+      </c>
+      <c r="P335" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="Q335" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="R335" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="S335" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="T335" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="U335" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V335" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="W335" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="X335" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y335" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Z335" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA335" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB335" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC335" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AD335" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AE335" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AF335" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AG335" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AH335" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AI335" t="inlineStr"/>
+      <c r="AJ335" t="inlineStr"/>
+      <c r="AK335" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AL335" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM335" t="inlineStr"/>
+      <c r="AN335" t="inlineStr"/>
+      <c r="AO335" t="inlineStr"/>
+      <c r="AP335" t="inlineStr"/>
+      <c r="AQ335" t="inlineStr"/>
+      <c r="AR335" t="inlineStr"/>
+      <c r="AS335" t="inlineStr">
+        <is>
+          <t>pfoInmcq</t>
+        </is>
+      </c>
+      <c r="AT335" t="inlineStr">
+        <is>
+          <t>rose marko</t>
+        </is>
+      </c>
+      <c r="AU335" t="inlineStr">
+        <is>
+          <t>0jdIgO6t</t>
+        </is>
+      </c>
+      <c r="AV335" t="inlineStr">
+        <is>
+          <t>blessin alexander</t>
+        </is>
+      </c>
+      <c r="AW335" t="n">
+        <v>59</v>
+      </c>
+      <c r="AX335" t="n">
+        <v>593</v>
+      </c>
+      <c r="AY335" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ335" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BA335" t="inlineStr"/>
+      <c r="BB335" t="inlineStr"/>
+      <c r="BC335" t="inlineStr"/>
+      <c r="BD335" t="inlineStr"/>
+      <c r="BE335" t="inlineStr"/>
+      <c r="BF335" t="inlineStr"/>
+      <c r="BG335" t="inlineStr"/>
+      <c r="BH335" t="inlineStr"/>
+      <c r="BI335" t="inlineStr"/>
+      <c r="BJ335" t="inlineStr"/>
+      <c r="BK335" t="inlineStr"/>
+      <c r="BL335" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/germany/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
+++ b/data/germany/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL335"/>
+  <dimension ref="A1:BL353"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66870,15 +66870,11 @@
           <t>26 117</t>
         </is>
       </c>
-      <c r="G320" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H320" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G320" t="n">
+        <v>2</v>
+      </c>
+      <c r="H320" t="n">
+        <v>0</v>
       </c>
       <c r="I320" t="inlineStr">
         <is>
@@ -66913,107 +66909,67 @@
           <t>70%</t>
         </is>
       </c>
-      <c r="Q320" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="R320" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="S320" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="T320" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="U320" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="V320" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="W320" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="X320" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="Y320" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Z320" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA320" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AB320" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC320" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AD320" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="AE320" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AF320" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AG320" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AH320" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+      <c r="Q320" t="n">
+        <v>10</v>
+      </c>
+      <c r="R320" t="n">
+        <v>13</v>
+      </c>
+      <c r="S320" t="n">
+        <v>4</v>
+      </c>
+      <c r="T320" t="n">
+        <v>7</v>
+      </c>
+      <c r="U320" t="n">
+        <v>6</v>
+      </c>
+      <c r="V320" t="n">
+        <v>6</v>
+      </c>
+      <c r="W320" t="n">
+        <v>17</v>
+      </c>
+      <c r="X320" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y320" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z320" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA320" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB320" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC320" t="n">
+        <v>21</v>
+      </c>
+      <c r="AD320" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE320" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF320" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG320" t="n">
+        <v>9</v>
+      </c>
+      <c r="AH320" t="n">
+        <v>16</v>
       </c>
       <c r="AI320" t="inlineStr"/>
       <c r="AJ320" t="inlineStr"/>
-      <c r="AK320" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AL320" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="AK320" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL320" t="n">
+        <v>1</v>
       </c>
       <c r="AM320" t="inlineStr"/>
       <c r="AN320" t="inlineStr"/>
@@ -67101,15 +67057,11 @@
           <t>18 001</t>
         </is>
       </c>
-      <c r="G321" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H321" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G321" t="n">
+        <v>2</v>
+      </c>
+      <c r="H321" t="n">
+        <v>1</v>
       </c>
       <c r="I321" t="inlineStr">
         <is>
@@ -67144,107 +67096,67 @@
           <t>52%</t>
         </is>
       </c>
-      <c r="Q321" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="R321" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="S321" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="T321" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U321" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="V321" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="W321" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="X321" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="Y321" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="Z321" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA321" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB321" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC321" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AD321" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="AE321" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AF321" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AG321" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AH321" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="Q321" t="n">
+        <v>14</v>
+      </c>
+      <c r="R321" t="n">
+        <v>8</v>
+      </c>
+      <c r="S321" t="n">
+        <v>11</v>
+      </c>
+      <c r="T321" t="n">
+        <v>4</v>
+      </c>
+      <c r="U321" t="n">
+        <v>3</v>
+      </c>
+      <c r="V321" t="n">
+        <v>4</v>
+      </c>
+      <c r="W321" t="n">
+        <v>12</v>
+      </c>
+      <c r="X321" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y321" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z321" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA321" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB321" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC321" t="n">
+        <v>18</v>
+      </c>
+      <c r="AD321" t="n">
+        <v>29</v>
+      </c>
+      <c r="AE321" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF321" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG321" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH321" t="n">
+        <v>10</v>
       </c>
       <c r="AI321" t="inlineStr"/>
       <c r="AJ321" t="inlineStr"/>
-      <c r="AK321" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL321" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AK321" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL321" t="n">
+        <v>2</v>
       </c>
       <c r="AM321" t="inlineStr"/>
       <c r="AN321" t="inlineStr"/>
@@ -67332,15 +67244,11 @@
           <t>33 000</t>
         </is>
       </c>
-      <c r="G322" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H322" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="G322" t="n">
+        <v>0</v>
+      </c>
+      <c r="H322" t="n">
+        <v>4</v>
       </c>
       <c r="I322" t="inlineStr">
         <is>
@@ -67375,107 +67283,67 @@
           <t>79%</t>
         </is>
       </c>
-      <c r="Q322" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="R322" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="S322" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="T322" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="U322" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V322" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W322" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="X322" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="Y322" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Z322" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA322" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AB322" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC322" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AD322" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AE322" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AF322" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AG322" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH322" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Q322" t="n">
+        <v>6</v>
+      </c>
+      <c r="R322" t="n">
+        <v>18</v>
+      </c>
+      <c r="S322" t="n">
+        <v>6</v>
+      </c>
+      <c r="T322" t="n">
+        <v>18</v>
+      </c>
+      <c r="U322" t="n">
+        <v>0</v>
+      </c>
+      <c r="V322" t="n">
+        <v>0</v>
+      </c>
+      <c r="W322" t="n">
+        <v>10</v>
+      </c>
+      <c r="X322" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y322" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z322" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA322" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB322" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC322" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD322" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE322" t="n">
+        <v>14</v>
+      </c>
+      <c r="AF322" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG322" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH322" t="n">
+        <v>0</v>
       </c>
       <c r="AI322" t="inlineStr"/>
       <c r="AJ322" t="inlineStr"/>
-      <c r="AK322" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AL322" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="AK322" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL322" t="n">
+        <v>1</v>
       </c>
       <c r="AM322" t="inlineStr"/>
       <c r="AN322" t="inlineStr"/>
@@ -67563,15 +67431,11 @@
           <t>30 070</t>
         </is>
       </c>
-      <c r="G323" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H323" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="G323" t="n">
+        <v>2</v>
+      </c>
+      <c r="H323" t="n">
+        <v>3</v>
       </c>
       <c r="I323" t="inlineStr">
         <is>
@@ -67606,107 +67470,67 @@
           <t>61%</t>
         </is>
       </c>
-      <c r="Q323" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="R323" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="S323" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="T323" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="U323" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="V323" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="W323" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="X323" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="Y323" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="Z323" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA323" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB323" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC323" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="AD323" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="AE323" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AF323" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AG323" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AH323" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
+      <c r="Q323" t="n">
+        <v>17</v>
+      </c>
+      <c r="R323" t="n">
+        <v>13</v>
+      </c>
+      <c r="S323" t="n">
+        <v>8</v>
+      </c>
+      <c r="T323" t="n">
+        <v>9</v>
+      </c>
+      <c r="U323" t="n">
+        <v>9</v>
+      </c>
+      <c r="V323" t="n">
+        <v>4</v>
+      </c>
+      <c r="W323" t="n">
+        <v>21</v>
+      </c>
+      <c r="X323" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y323" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z323" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA323" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB323" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC323" t="n">
+        <v>31</v>
+      </c>
+      <c r="AD323" t="n">
+        <v>34</v>
+      </c>
+      <c r="AE323" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF323" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG323" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH323" t="n">
+        <v>19</v>
       </c>
       <c r="AI323" t="inlineStr"/>
       <c r="AJ323" t="inlineStr"/>
-      <c r="AK323" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL323" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AK323" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL323" t="n">
+        <v>2</v>
       </c>
       <c r="AM323" t="inlineStr"/>
       <c r="AN323" t="inlineStr"/>
@@ -67794,15 +67618,11 @@
           <t>58 000</t>
         </is>
       </c>
-      <c r="G324" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H324" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G324" t="n">
+        <v>2</v>
+      </c>
+      <c r="H324" t="n">
+        <v>1</v>
       </c>
       <c r="I324" t="inlineStr">
         <is>
@@ -67837,115 +67657,71 @@
           <t>60%</t>
         </is>
       </c>
-      <c r="Q324" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R324" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="S324" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="T324" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="U324" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="V324" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="W324" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="X324" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="Y324" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Z324" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA324" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AB324" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC324" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AD324" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="AE324" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AF324" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AG324" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AH324" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI324" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AJ324" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK324" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL324" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="Q324" t="n">
+        <v>9</v>
+      </c>
+      <c r="R324" t="n">
+        <v>15</v>
+      </c>
+      <c r="S324" t="n">
+        <v>5</v>
+      </c>
+      <c r="T324" t="n">
+        <v>5</v>
+      </c>
+      <c r="U324" t="n">
+        <v>4</v>
+      </c>
+      <c r="V324" t="n">
+        <v>10</v>
+      </c>
+      <c r="W324" t="n">
+        <v>18</v>
+      </c>
+      <c r="X324" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y324" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z324" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA324" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB324" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC324" t="n">
+        <v>18</v>
+      </c>
+      <c r="AD324" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE324" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF324" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG324" t="n">
+        <v>7</v>
+      </c>
+      <c r="AH324" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI324" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ324" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK324" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL324" t="n">
+        <v>4</v>
       </c>
       <c r="AM324" t="inlineStr"/>
       <c r="AN324" t="inlineStr"/>
@@ -68033,15 +67809,11 @@
           <t>34 500</t>
         </is>
       </c>
-      <c r="G325" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H325" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G325" t="n">
+        <v>2</v>
+      </c>
+      <c r="H325" t="n">
+        <v>1</v>
       </c>
       <c r="I325" t="inlineStr">
         <is>
@@ -68076,107 +67848,67 @@
           <t>54%</t>
         </is>
       </c>
-      <c r="Q325" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R325" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="S325" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="T325" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="U325" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="V325" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="W325" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="X325" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="Y325" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Z325" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA325" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AB325" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC325" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AD325" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AE325" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AF325" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AG325" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AH325" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="Q325" t="n">
+        <v>9</v>
+      </c>
+      <c r="R325" t="n">
+        <v>7</v>
+      </c>
+      <c r="S325" t="n">
+        <v>6</v>
+      </c>
+      <c r="T325" t="n">
+        <v>3</v>
+      </c>
+      <c r="U325" t="n">
+        <v>3</v>
+      </c>
+      <c r="V325" t="n">
+        <v>4</v>
+      </c>
+      <c r="W325" t="n">
+        <v>9</v>
+      </c>
+      <c r="X325" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y325" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z325" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA325" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB325" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC325" t="n">
+        <v>19</v>
+      </c>
+      <c r="AD325" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE325" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF325" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG325" t="n">
+        <v>8</v>
+      </c>
+      <c r="AH325" t="n">
+        <v>8</v>
       </c>
       <c r="AI325" t="inlineStr"/>
       <c r="AJ325" t="inlineStr"/>
-      <c r="AK325" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AL325" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="AK325" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL325" t="n">
+        <v>1</v>
       </c>
       <c r="AM325" t="inlineStr"/>
       <c r="AN325" t="inlineStr"/>
@@ -68264,15 +67996,11 @@
           <t>43 000</t>
         </is>
       </c>
-      <c r="G326" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H326" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G326" t="n">
+        <v>2</v>
+      </c>
+      <c r="H326" t="n">
+        <v>1</v>
       </c>
       <c r="I326" t="inlineStr">
         <is>
@@ -68307,107 +68035,67 @@
           <t>52%</t>
         </is>
       </c>
-      <c r="Q326" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R326" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="S326" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="T326" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U326" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="V326" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="W326" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="X326" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="Y326" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Z326" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA326" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB326" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC326" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AD326" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="AE326" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AF326" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AG326" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AH326" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="Q326" t="n">
+        <v>9</v>
+      </c>
+      <c r="R326" t="n">
+        <v>6</v>
+      </c>
+      <c r="S326" t="n">
+        <v>6</v>
+      </c>
+      <c r="T326" t="n">
+        <v>2</v>
+      </c>
+      <c r="U326" t="n">
+        <v>3</v>
+      </c>
+      <c r="V326" t="n">
+        <v>4</v>
+      </c>
+      <c r="W326" t="n">
+        <v>12</v>
+      </c>
+      <c r="X326" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y326" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z326" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA326" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB326" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC326" t="n">
+        <v>18</v>
+      </c>
+      <c r="AD326" t="n">
+        <v>31</v>
+      </c>
+      <c r="AE326" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF326" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG326" t="n">
+        <v>21</v>
+      </c>
+      <c r="AH326" t="n">
+        <v>12</v>
       </c>
       <c r="AI326" t="inlineStr"/>
       <c r="AJ326" t="inlineStr"/>
-      <c r="AK326" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AL326" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="AK326" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL326" t="n">
+        <v>1</v>
       </c>
       <c r="AM326" t="inlineStr"/>
       <c r="AN326" t="inlineStr"/>
@@ -68495,15 +68183,11 @@
           <t>15 000</t>
         </is>
       </c>
-      <c r="G327" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H327" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G327" t="n">
+        <v>0</v>
+      </c>
+      <c r="H327" t="n">
+        <v>1</v>
       </c>
       <c r="I327" t="inlineStr">
         <is>
@@ -68538,107 +68222,67 @@
           <t>50%</t>
         </is>
       </c>
-      <c r="Q327" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="R327" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="S327" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="T327" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="U327" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="V327" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="W327" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="X327" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="Y327" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Z327" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA327" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AB327" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC327" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="AD327" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AE327" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AF327" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AG327" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AH327" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="Q327" t="n">
+        <v>15</v>
+      </c>
+      <c r="R327" t="n">
+        <v>8</v>
+      </c>
+      <c r="S327" t="n">
+        <v>9</v>
+      </c>
+      <c r="T327" t="n">
+        <v>5</v>
+      </c>
+      <c r="U327" t="n">
+        <v>6</v>
+      </c>
+      <c r="V327" t="n">
+        <v>3</v>
+      </c>
+      <c r="W327" t="n">
+        <v>10</v>
+      </c>
+      <c r="X327" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y327" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z327" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA327" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB327" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC327" t="n">
+        <v>24</v>
+      </c>
+      <c r="AD327" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE327" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF327" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG327" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH327" t="n">
+        <v>10</v>
       </c>
       <c r="AI327" t="inlineStr"/>
       <c r="AJ327" t="inlineStr"/>
-      <c r="AK327" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL327" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="AK327" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL327" t="n">
+        <v>3</v>
       </c>
       <c r="AM327" t="inlineStr"/>
       <c r="AN327" t="inlineStr"/>
@@ -68726,15 +68370,11 @@
           <t>48 000</t>
         </is>
       </c>
-      <c r="G328" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H328" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G328" t="n">
+        <v>3</v>
+      </c>
+      <c r="H328" t="n">
+        <v>0</v>
       </c>
       <c r="I328" t="inlineStr">
         <is>
@@ -68769,107 +68409,67 @@
           <t>59%</t>
         </is>
       </c>
-      <c r="Q328" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="R328" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="S328" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="T328" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U328" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V328" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="W328" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="X328" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="Y328" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Z328" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA328" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AB328" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC328" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="AD328" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="AE328" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AF328" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AG328" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AH328" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="Q328" t="n">
+        <v>7</v>
+      </c>
+      <c r="R328" t="n">
+        <v>9</v>
+      </c>
+      <c r="S328" t="n">
+        <v>5</v>
+      </c>
+      <c r="T328" t="n">
+        <v>4</v>
+      </c>
+      <c r="U328" t="n">
+        <v>2</v>
+      </c>
+      <c r="V328" t="n">
+        <v>5</v>
+      </c>
+      <c r="W328" t="n">
+        <v>11</v>
+      </c>
+      <c r="X328" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y328" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z328" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA328" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB328" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC328" t="n">
+        <v>22</v>
+      </c>
+      <c r="AD328" t="n">
+        <v>38</v>
+      </c>
+      <c r="AE328" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF328" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG328" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH328" t="n">
+        <v>12</v>
       </c>
       <c r="AI328" t="inlineStr"/>
       <c r="AJ328" t="inlineStr"/>
-      <c r="AK328" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL328" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AK328" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL328" t="n">
+        <v>4</v>
       </c>
       <c r="AM328" t="inlineStr"/>
       <c r="AN328" t="inlineStr"/>
@@ -68957,15 +68557,11 @@
           <t>11 627</t>
         </is>
       </c>
-      <c r="G329" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H329" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G329" t="n">
+        <v>1</v>
+      </c>
+      <c r="H329" t="n">
+        <v>0</v>
       </c>
       <c r="I329" t="inlineStr">
         <is>
@@ -69000,115 +68596,71 @@
           <t>69%</t>
         </is>
       </c>
-      <c r="Q329" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="R329" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="S329" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="T329" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="U329" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="V329" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="W329" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="X329" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="Y329" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Z329" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA329" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB329" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AC329" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="AD329" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="AE329" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AF329" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AG329" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AH329" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AI329" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AJ329" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK329" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AL329" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="Q329" t="n">
+        <v>8</v>
+      </c>
+      <c r="R329" t="n">
+        <v>9</v>
+      </c>
+      <c r="S329" t="n">
+        <v>4</v>
+      </c>
+      <c r="T329" t="n">
+        <v>5</v>
+      </c>
+      <c r="U329" t="n">
+        <v>4</v>
+      </c>
+      <c r="V329" t="n">
+        <v>4</v>
+      </c>
+      <c r="W329" t="n">
+        <v>21</v>
+      </c>
+      <c r="X329" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y329" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z329" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA329" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB329" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC329" t="n">
+        <v>34</v>
+      </c>
+      <c r="AD329" t="n">
+        <v>32</v>
+      </c>
+      <c r="AE329" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF329" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG329" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH329" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI329" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ329" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK329" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL329" t="n">
+        <v>3</v>
       </c>
       <c r="AM329" t="inlineStr"/>
       <c r="AN329" t="inlineStr"/>
@@ -69196,15 +68748,11 @@
           <t>60 000</t>
         </is>
       </c>
-      <c r="G330" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H330" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G330" t="n">
+        <v>2</v>
+      </c>
+      <c r="H330" t="n">
+        <v>1</v>
       </c>
       <c r="I330" t="inlineStr">
         <is>
@@ -69239,107 +68787,67 @@
           <t>29%</t>
         </is>
       </c>
-      <c r="Q330" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="R330" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="S330" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="T330" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U330" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V330" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="W330" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="X330" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="Y330" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Z330" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA330" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB330" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC330" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AD330" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AE330" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AF330" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AG330" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AH330" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
+      <c r="Q330" t="n">
+        <v>15</v>
+      </c>
+      <c r="R330" t="n">
+        <v>7</v>
+      </c>
+      <c r="S330" t="n">
+        <v>8</v>
+      </c>
+      <c r="T330" t="n">
+        <v>2</v>
+      </c>
+      <c r="U330" t="n">
+        <v>7</v>
+      </c>
+      <c r="V330" t="n">
+        <v>5</v>
+      </c>
+      <c r="W330" t="n">
+        <v>15</v>
+      </c>
+      <c r="X330" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y330" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z330" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA330" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB330" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC330" t="n">
+        <v>19</v>
+      </c>
+      <c r="AD330" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE330" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF330" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG330" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH330" t="n">
+        <v>15</v>
       </c>
       <c r="AI330" t="inlineStr"/>
       <c r="AJ330" t="inlineStr"/>
-      <c r="AK330" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL330" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AK330" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL330" t="n">
+        <v>4</v>
       </c>
       <c r="AM330" t="inlineStr"/>
       <c r="AN330" t="inlineStr"/>
@@ -69427,15 +68935,11 @@
           <t>30 000</t>
         </is>
       </c>
-      <c r="G331" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H331" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G331" t="n">
+        <v>1</v>
+      </c>
+      <c r="H331" t="n">
+        <v>0</v>
       </c>
       <c r="I331" t="inlineStr">
         <is>
@@ -69470,107 +68974,67 @@
           <t>58%</t>
         </is>
       </c>
-      <c r="Q331" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="R331" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="S331" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="T331" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U331" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="V331" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="W331" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="X331" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="Y331" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Z331" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA331" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB331" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC331" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="AD331" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AE331" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AF331" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AG331" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="AH331" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
+      <c r="Q331" t="n">
+        <v>13</v>
+      </c>
+      <c r="R331" t="n">
+        <v>10</v>
+      </c>
+      <c r="S331" t="n">
+        <v>4</v>
+      </c>
+      <c r="T331" t="n">
+        <v>4</v>
+      </c>
+      <c r="U331" t="n">
+        <v>9</v>
+      </c>
+      <c r="V331" t="n">
+        <v>6</v>
+      </c>
+      <c r="W331" t="n">
+        <v>19</v>
+      </c>
+      <c r="X331" t="n">
+        <v>26</v>
+      </c>
+      <c r="Y331" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z331" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA331" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB331" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC331" t="n">
+        <v>24</v>
+      </c>
+      <c r="AD331" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE331" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF331" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG331" t="n">
+        <v>22</v>
+      </c>
+      <c r="AH331" t="n">
+        <v>18</v>
       </c>
       <c r="AI331" t="inlineStr"/>
       <c r="AJ331" t="inlineStr"/>
-      <c r="AK331" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL331" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AK331" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL331" t="n">
+        <v>4</v>
       </c>
       <c r="AM331" t="inlineStr"/>
       <c r="AN331" t="inlineStr"/>
@@ -69658,15 +69122,11 @@
           <t>27 511</t>
         </is>
       </c>
-      <c r="G332" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H332" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G332" t="n">
+        <v>3</v>
+      </c>
+      <c r="H332" t="n">
+        <v>0</v>
       </c>
       <c r="I332" t="inlineStr">
         <is>
@@ -69701,107 +69161,67 @@
           <t>47%</t>
         </is>
       </c>
-      <c r="Q332" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="R332" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="S332" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="T332" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="U332" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="V332" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="W332" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="X332" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y332" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Z332" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA332" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB332" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AC332" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AD332" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="AE332" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AF332" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG332" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AH332" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
+      <c r="Q332" t="n">
+        <v>7</v>
+      </c>
+      <c r="R332" t="n">
+        <v>3</v>
+      </c>
+      <c r="S332" t="n">
+        <v>3</v>
+      </c>
+      <c r="T332" t="n">
+        <v>1</v>
+      </c>
+      <c r="U332" t="n">
+        <v>4</v>
+      </c>
+      <c r="V332" t="n">
+        <v>2</v>
+      </c>
+      <c r="W332" t="n">
+        <v>24</v>
+      </c>
+      <c r="X332" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y332" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z332" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA332" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB332" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC332" t="n">
+        <v>18</v>
+      </c>
+      <c r="AD332" t="n">
+        <v>40</v>
+      </c>
+      <c r="AE332" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF332" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG332" t="n">
+        <v>6</v>
+      </c>
+      <c r="AH332" t="n">
+        <v>17</v>
       </c>
       <c r="AI332" t="inlineStr"/>
       <c r="AJ332" t="inlineStr"/>
-      <c r="AK332" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AL332" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AK332" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL332" t="n">
+        <v>4</v>
       </c>
       <c r="AM332" t="inlineStr"/>
       <c r="AN332" t="inlineStr"/>
@@ -69889,15 +69309,11 @@
           <t>29 787</t>
         </is>
       </c>
-      <c r="G333" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H333" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G333" t="n">
+        <v>3</v>
+      </c>
+      <c r="H333" t="n">
+        <v>0</v>
       </c>
       <c r="I333" t="inlineStr">
         <is>
@@ -69932,107 +69348,67 @@
           <t>37%</t>
         </is>
       </c>
-      <c r="Q333" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R333" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="S333" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="T333" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="U333" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V333" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="W333" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="X333" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="Y333" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Z333" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AA333" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB333" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AC333" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AD333" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AE333" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AF333" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AG333" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AH333" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="Q333" t="n">
+        <v>9</v>
+      </c>
+      <c r="R333" t="n">
+        <v>9</v>
+      </c>
+      <c r="S333" t="n">
+        <v>8</v>
+      </c>
+      <c r="T333" t="n">
+        <v>5</v>
+      </c>
+      <c r="U333" t="n">
+        <v>1</v>
+      </c>
+      <c r="V333" t="n">
+        <v>4</v>
+      </c>
+      <c r="W333" t="n">
+        <v>11</v>
+      </c>
+      <c r="X333" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y333" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z333" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA333" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB333" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC333" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD333" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE333" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF333" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG333" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH333" t="n">
+        <v>8</v>
       </c>
       <c r="AI333" t="inlineStr"/>
       <c r="AJ333" t="inlineStr"/>
-      <c r="AK333" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL333" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="AK333" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL333" t="n">
+        <v>1</v>
       </c>
       <c r="AM333" t="inlineStr"/>
       <c r="AN333" t="inlineStr"/>
@@ -70120,15 +69496,11 @@
           <t>20 071</t>
         </is>
       </c>
-      <c r="G334" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H334" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G334" t="n">
+        <v>0</v>
+      </c>
+      <c r="H334" t="n">
+        <v>2</v>
       </c>
       <c r="I334" t="inlineStr">
         <is>
@@ -70163,107 +69535,67 @@
           <t>74%</t>
         </is>
       </c>
-      <c r="Q334" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="R334" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="S334" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="T334" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="U334" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="V334" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="W334" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="X334" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="Y334" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Z334" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA334" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB334" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC334" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="AD334" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AE334" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AF334" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AG334" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AH334" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="Q334" t="n">
+        <v>14</v>
+      </c>
+      <c r="R334" t="n">
+        <v>19</v>
+      </c>
+      <c r="S334" t="n">
+        <v>11</v>
+      </c>
+      <c r="T334" t="n">
+        <v>15</v>
+      </c>
+      <c r="U334" t="n">
+        <v>3</v>
+      </c>
+      <c r="V334" t="n">
+        <v>4</v>
+      </c>
+      <c r="W334" t="n">
+        <v>9</v>
+      </c>
+      <c r="X334" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y334" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z334" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA334" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB334" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC334" t="n">
+        <v>31</v>
+      </c>
+      <c r="AD334" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE334" t="n">
+        <v>13</v>
+      </c>
+      <c r="AF334" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG334" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH334" t="n">
+        <v>3</v>
       </c>
       <c r="AI334" t="inlineStr"/>
       <c r="AJ334" t="inlineStr"/>
-      <c r="AK334" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL334" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AK334" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL334" t="n">
+        <v>0</v>
       </c>
       <c r="AM334" t="inlineStr"/>
       <c r="AN334" t="inlineStr"/>
@@ -70351,15 +69683,11 @@
           <t>40 478</t>
         </is>
       </c>
-      <c r="G335" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H335" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G335" t="n">
+        <v>4</v>
+      </c>
+      <c r="H335" t="n">
+        <v>2</v>
       </c>
       <c r="I335" t="inlineStr">
         <is>
@@ -70394,107 +69722,67 @@
           <t>54%</t>
         </is>
       </c>
-      <c r="Q335" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="R335" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="S335" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="T335" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="U335" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V335" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="W335" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="X335" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y335" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Z335" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA335" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB335" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC335" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AD335" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="AE335" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AF335" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AG335" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AH335" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="Q335" t="n">
+        <v>18</v>
+      </c>
+      <c r="R335" t="n">
+        <v>14</v>
+      </c>
+      <c r="S335" t="n">
+        <v>16</v>
+      </c>
+      <c r="T335" t="n">
+        <v>9</v>
+      </c>
+      <c r="U335" t="n">
+        <v>2</v>
+      </c>
+      <c r="V335" t="n">
+        <v>5</v>
+      </c>
+      <c r="W335" t="n">
+        <v>9</v>
+      </c>
+      <c r="X335" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y335" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z335" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA335" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB335" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC335" t="n">
+        <v>16</v>
+      </c>
+      <c r="AD335" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE335" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF335" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG335" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH335" t="n">
+        <v>8</v>
       </c>
       <c r="AI335" t="inlineStr"/>
       <c r="AJ335" t="inlineStr"/>
-      <c r="AK335" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AL335" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="AK335" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL335" t="n">
+        <v>1</v>
       </c>
       <c r="AM335" t="inlineStr"/>
       <c r="AN335" t="inlineStr"/>
@@ -70549,6 +69837,4898 @@
       <c r="BK335" t="inlineStr"/>
       <c r="BL335" t="inlineStr"/>
     </row>
+    <row r="336">
+      <c r="A336" s="1" t="inlineStr">
+        <is>
+          <t>raQ4MDUN</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>03.11.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>Dankert B.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>Borussia-Park
+ (Mönchengladbach)</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>54 042</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>54 042</t>
+        </is>
+      </c>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H336" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I336" t="inlineStr">
+        <is>
+          <t>88HSzjDr</t>
+        </is>
+      </c>
+      <c r="J336" t="inlineStr">
+        <is>
+          <t>B. Monchengladbach</t>
+        </is>
+      </c>
+      <c r="K336" t="inlineStr">
+        <is>
+          <t>Ig1f1fy3</t>
+        </is>
+      </c>
+      <c r="L336" t="inlineStr">
+        <is>
+          <t>Werder Bremen</t>
+        </is>
+      </c>
+      <c r="M336" t="inlineStr">
+        <is>
+          <t>2.39</t>
+        </is>
+      </c>
+      <c r="N336" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="O336" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="P336" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
+      </c>
+      <c r="Q336" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R336" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="S336" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="T336" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U336" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V336" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="W336" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="X336" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="Y336" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Z336" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA336" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB336" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC336" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AD336" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AE336" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AF336" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AG336" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AH336" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AI336" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AJ336" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AK336" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL336" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AM336" t="inlineStr">
+        <is>
+          <t>486</t>
+        </is>
+      </c>
+      <c r="AN336" t="inlineStr">
+        <is>
+          <t>531</t>
+        </is>
+      </c>
+      <c r="AO336" t="inlineStr">
+        <is>
+          <t>395</t>
+        </is>
+      </c>
+      <c r="AP336" t="inlineStr">
+        <is>
+          <t>453</t>
+        </is>
+      </c>
+      <c r="AQ336" t="inlineStr"/>
+      <c r="AR336" t="inlineStr"/>
+      <c r="AS336" t="inlineStr">
+        <is>
+          <t>M5BRZDsC</t>
+        </is>
+      </c>
+      <c r="AT336" t="inlineStr">
+        <is>
+          <t>seoane gerardo</t>
+        </is>
+      </c>
+      <c r="AU336" t="inlineStr">
+        <is>
+          <t>4fuCGs9P</t>
+        </is>
+      </c>
+      <c r="AV336" t="inlineStr">
+        <is>
+          <t>werner ole</t>
+        </is>
+      </c>
+      <c r="AW336" t="n">
+        <v>59</v>
+      </c>
+      <c r="AX336" t="n">
+        <v>591</v>
+      </c>
+      <c r="AY336" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ336" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BA336" t="inlineStr"/>
+      <c r="BB336" t="inlineStr"/>
+      <c r="BC336" t="inlineStr"/>
+      <c r="BD336" t="inlineStr"/>
+      <c r="BE336" t="inlineStr"/>
+      <c r="BF336" t="inlineStr"/>
+      <c r="BG336" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BH336" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BI336" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BJ336" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="BK336" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="BL336" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="1" t="inlineStr">
+        <is>
+          <t>GnZmQeVb</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>03.11.2024 11:30</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>Brand B.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>Europa-Park Stadion
+ (Freiburg)</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>34 700</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>34 400</t>
+        </is>
+      </c>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H337" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I337" t="inlineStr">
+        <is>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
+      <c r="J337" t="inlineStr">
+        <is>
+          <t>Freiburg</t>
+        </is>
+      </c>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>EuakNmc1</t>
+        </is>
+      </c>
+      <c r="L337" t="inlineStr">
+        <is>
+          <t>Mainz</t>
+        </is>
+      </c>
+      <c r="M337" t="inlineStr">
+        <is>
+          <t>0.77</t>
+        </is>
+      </c>
+      <c r="N337" t="inlineStr">
+        <is>
+          <t>0.53</t>
+        </is>
+      </c>
+      <c r="O337" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="P337" t="inlineStr">
+        <is>
+          <t>49%</t>
+        </is>
+      </c>
+      <c r="Q337" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R337" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="S337" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T337" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U337" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V337" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="W337" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="X337" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y337" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Z337" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA337" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB337" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC337" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AD337" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AE337" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AF337" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AG337" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AH337" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AI337" t="inlineStr"/>
+      <c r="AJ337" t="inlineStr"/>
+      <c r="AK337" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL337" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM337" t="inlineStr">
+        <is>
+          <t>481</t>
+        </is>
+      </c>
+      <c r="AN337" t="inlineStr">
+        <is>
+          <t>459</t>
+        </is>
+      </c>
+      <c r="AO337" t="inlineStr">
+        <is>
+          <t>377</t>
+        </is>
+      </c>
+      <c r="AP337" t="inlineStr">
+        <is>
+          <t>362</t>
+        </is>
+      </c>
+      <c r="AQ337" t="inlineStr"/>
+      <c r="AR337" t="inlineStr"/>
+      <c r="AS337" t="inlineStr">
+        <is>
+          <t>YZPE6Sx7</t>
+        </is>
+      </c>
+      <c r="AT337" t="inlineStr">
+        <is>
+          <t>schuster julian</t>
+        </is>
+      </c>
+      <c r="AU337" t="inlineStr">
+        <is>
+          <t>vZA6VYpf</t>
+        </is>
+      </c>
+      <c r="AV337" t="inlineStr">
+        <is>
+          <t>henriksen bo</t>
+        </is>
+      </c>
+      <c r="AW337" t="n">
+        <v>59</v>
+      </c>
+      <c r="AX337" t="n">
+        <v>591</v>
+      </c>
+      <c r="AY337" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ337" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BA337" t="inlineStr"/>
+      <c r="BB337" t="inlineStr"/>
+      <c r="BC337" t="inlineStr"/>
+      <c r="BD337" t="inlineStr"/>
+      <c r="BE337" t="inlineStr"/>
+      <c r="BF337" t="inlineStr"/>
+      <c r="BG337" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BH337" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="BI337" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BJ337" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BK337" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="BL337" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="1" t="inlineStr">
+        <is>
+          <t>dr2N9zoI</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>02.11.2024 14:30</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>Stieler T.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>Signal Iduna Park
+ (Dortmund)</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>81 365</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>81 365</t>
+        </is>
+      </c>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H338" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I338" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="J338" t="inlineStr">
+        <is>
+          <t>Dortmund</t>
+        </is>
+      </c>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>KbS1suSm</t>
+        </is>
+      </c>
+      <c r="L338" t="inlineStr">
+        <is>
+          <t>RB Leipzig</t>
+        </is>
+      </c>
+      <c r="M338" t="inlineStr">
+        <is>
+          <t>2.71</t>
+        </is>
+      </c>
+      <c r="N338" t="inlineStr">
+        <is>
+          <t>0.41</t>
+        </is>
+      </c>
+      <c r="O338" t="inlineStr">
+        <is>
+          <t>56%</t>
+        </is>
+      </c>
+      <c r="P338" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
+      <c r="Q338" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="R338" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="S338" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T338" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U338" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V338" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W338" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="X338" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="Y338" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Z338" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA338" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB338" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC338" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="AD338" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AE338" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AF338" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AG338" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AH338" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AI338" t="inlineStr"/>
+      <c r="AJ338" t="inlineStr"/>
+      <c r="AK338" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AL338" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AM338" t="inlineStr">
+        <is>
+          <t>512</t>
+        </is>
+      </c>
+      <c r="AN338" t="inlineStr">
+        <is>
+          <t>405</t>
+        </is>
+      </c>
+      <c r="AO338" t="inlineStr">
+        <is>
+          <t>424</t>
+        </is>
+      </c>
+      <c r="AP338" t="inlineStr">
+        <is>
+          <t>321</t>
+        </is>
+      </c>
+      <c r="AQ338" t="inlineStr"/>
+      <c r="AR338" t="inlineStr"/>
+      <c r="AS338" t="inlineStr">
+        <is>
+          <t>IkCftsQm</t>
+        </is>
+      </c>
+      <c r="AT338" t="inlineStr">
+        <is>
+          <t>sahin nuri</t>
+        </is>
+      </c>
+      <c r="AU338" t="inlineStr">
+        <is>
+          <t>pfoInmcq</t>
+        </is>
+      </c>
+      <c r="AV338" t="inlineStr">
+        <is>
+          <t>rose marko</t>
+        </is>
+      </c>
+      <c r="AW338" t="n">
+        <v>59</v>
+      </c>
+      <c r="AX338" t="n">
+        <v>591</v>
+      </c>
+      <c r="AY338" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ338" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BA338" t="inlineStr"/>
+      <c r="BB338" t="inlineStr"/>
+      <c r="BC338" t="inlineStr"/>
+      <c r="BD338" t="inlineStr"/>
+      <c r="BE338" t="inlineStr"/>
+      <c r="BF338" t="inlineStr"/>
+      <c r="BG338" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="BH338" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BI338" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="BJ338" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BK338" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="BL338" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="1" t="inlineStr">
+        <is>
+          <t>jVWMBdG5</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>02.11.2024 11:30</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>Jollenbeck M.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>Allianz Arena
+ (Munich)</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>75 024</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>75 000</t>
+        </is>
+      </c>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H339" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I339" t="inlineStr">
+        <is>
+          <t>nVp0wiqd</t>
+        </is>
+      </c>
+      <c r="J339" t="inlineStr">
+        <is>
+          <t>Bayern Munich</t>
+        </is>
+      </c>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>pzHW4oaE</t>
+        </is>
+      </c>
+      <c r="L339" t="inlineStr">
+        <is>
+          <t>Union Berlin</t>
+        </is>
+      </c>
+      <c r="M339" t="inlineStr">
+        <is>
+          <t>2.48</t>
+        </is>
+      </c>
+      <c r="N339" t="inlineStr">
+        <is>
+          <t>0.50</t>
+        </is>
+      </c>
+      <c r="O339" t="inlineStr">
+        <is>
+          <t>77%</t>
+        </is>
+      </c>
+      <c r="P339" t="inlineStr">
+        <is>
+          <t>23%</t>
+        </is>
+      </c>
+      <c r="Q339" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R339" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="S339" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T339" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U339" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V339" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W339" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="X339" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y339" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Z339" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA339" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB339" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC339" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AD339" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AE339" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AF339" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AG339" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH339" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AI339" t="inlineStr"/>
+      <c r="AJ339" t="inlineStr"/>
+      <c r="AK339" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AL339" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM339" t="inlineStr">
+        <is>
+          <t>863</t>
+        </is>
+      </c>
+      <c r="AN339" t="inlineStr">
+        <is>
+          <t>247</t>
+        </is>
+      </c>
+      <c r="AO339" t="inlineStr">
+        <is>
+          <t>794</t>
+        </is>
+      </c>
+      <c r="AP339" t="inlineStr">
+        <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="AQ339" t="inlineStr"/>
+      <c r="AR339" t="inlineStr"/>
+      <c r="AS339" t="inlineStr">
+        <is>
+          <t>K6A2elS9</t>
+        </is>
+      </c>
+      <c r="AT339" t="inlineStr">
+        <is>
+          <t>kompany vincent</t>
+        </is>
+      </c>
+      <c r="AU339" t="inlineStr">
+        <is>
+          <t>hpYJ6izc</t>
+        </is>
+      </c>
+      <c r="AV339" t="inlineStr">
+        <is>
+          <t>svensson bo</t>
+        </is>
+      </c>
+      <c r="AW339" t="n">
+        <v>59</v>
+      </c>
+      <c r="AX339" t="n">
+        <v>591</v>
+      </c>
+      <c r="AY339" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ339" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BA339" t="inlineStr"/>
+      <c r="BB339" t="inlineStr"/>
+      <c r="BC339" t="inlineStr"/>
+      <c r="BD339" t="inlineStr"/>
+      <c r="BE339" t="inlineStr"/>
+      <c r="BF339" t="inlineStr"/>
+      <c r="BG339" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BH339" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="BI339" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BJ339" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="BK339" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="BL339" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="1" t="inlineStr">
+        <is>
+          <t>485V7EFU</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>02.11.2024 11:30</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>Schlager D.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>Deutsche Bank Park
+ (Frankfurt)</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>58 000</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>58 000</t>
+        </is>
+      </c>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H340" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I340" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="J340" t="inlineStr">
+        <is>
+          <t>Eintracht Frankfurt</t>
+        </is>
+      </c>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>8Y2m6ADe</t>
+        </is>
+      </c>
+      <c r="L340" t="inlineStr">
+        <is>
+          <t>Bochum</t>
+        </is>
+      </c>
+      <c r="M340" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="N340" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="O340" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
+      <c r="P340" t="inlineStr">
+        <is>
+          <t>35%</t>
+        </is>
+      </c>
+      <c r="Q340" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="R340" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="S340" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="T340" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="U340" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V340" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W340" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="X340" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y340" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Z340" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA340" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB340" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC340" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AD340" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AE340" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AF340" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AG340" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AH340" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AI340" t="inlineStr"/>
+      <c r="AJ340" t="inlineStr"/>
+      <c r="AK340" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL340" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM340" t="inlineStr">
+        <is>
+          <t>586</t>
+        </is>
+      </c>
+      <c r="AN340" t="inlineStr">
+        <is>
+          <t>310</t>
+        </is>
+      </c>
+      <c r="AO340" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="AP340" t="inlineStr">
+        <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="AQ340" t="inlineStr"/>
+      <c r="AR340" t="inlineStr"/>
+      <c r="AS340" t="inlineStr">
+        <is>
+          <t>UgdQz0fK</t>
+        </is>
+      </c>
+      <c r="AT340" t="inlineStr">
+        <is>
+          <t>toppmoller dino</t>
+        </is>
+      </c>
+      <c r="AU340" t="inlineStr">
+        <is>
+          <t>UkPWzhq8</t>
+        </is>
+      </c>
+      <c r="AV340" t="inlineStr">
+        <is>
+          <t>feldhoff marcus</t>
+        </is>
+      </c>
+      <c r="AW340" t="n">
+        <v>59</v>
+      </c>
+      <c r="AX340" t="n">
+        <v>591</v>
+      </c>
+      <c r="AY340" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ340" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BA340" t="inlineStr"/>
+      <c r="BB340" t="inlineStr"/>
+      <c r="BC340" t="inlineStr"/>
+      <c r="BD340" t="inlineStr"/>
+      <c r="BE340" t="inlineStr"/>
+      <c r="BF340" t="inlineStr"/>
+      <c r="BG340" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="BH340" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BI340" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="BJ340" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BK340" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="BL340" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="1" t="inlineStr">
+        <is>
+          <t>8MVuSH0n</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>02.11.2024 11:30</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>Stegemann S.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>PreZero Arena
+ (Sinsheim)</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>30 150</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>26 199</t>
+        </is>
+      </c>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H341" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I341" t="inlineStr">
+        <is>
+          <t>hQAtP9Sl</t>
+        </is>
+      </c>
+      <c r="J341" t="inlineStr">
+        <is>
+          <t>Hoffenheim</t>
+        </is>
+      </c>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="L341" t="inlineStr">
+        <is>
+          <t>St. Pauli</t>
+        </is>
+      </c>
+      <c r="M341" t="inlineStr">
+        <is>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="N341" t="inlineStr">
+        <is>
+          <t>0.82</t>
+        </is>
+      </c>
+      <c r="O341" t="inlineStr">
+        <is>
+          <t>68%</t>
+        </is>
+      </c>
+      <c r="P341" t="inlineStr">
+        <is>
+          <t>32%</t>
+        </is>
+      </c>
+      <c r="Q341" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R341" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="S341" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T341" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U341" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V341" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W341" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="X341" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Y341" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Z341" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA341" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB341" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC341" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="AD341" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AE341" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AF341" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AG341" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AH341" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AI341" t="inlineStr"/>
+      <c r="AJ341" t="inlineStr"/>
+      <c r="AK341" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AL341" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM341" t="inlineStr">
+        <is>
+          <t>624</t>
+        </is>
+      </c>
+      <c r="AN341" t="inlineStr">
+        <is>
+          <t>305</t>
+        </is>
+      </c>
+      <c r="AO341" t="inlineStr">
+        <is>
+          <t>525</t>
+        </is>
+      </c>
+      <c r="AP341" t="inlineStr">
+        <is>
+          <t>219</t>
+        </is>
+      </c>
+      <c r="AQ341" t="inlineStr"/>
+      <c r="AR341" t="inlineStr"/>
+      <c r="AS341" t="inlineStr">
+        <is>
+          <t>KUx4Q7x1</t>
+        </is>
+      </c>
+      <c r="AT341" t="inlineStr">
+        <is>
+          <t>matarazzo pellegrino</t>
+        </is>
+      </c>
+      <c r="AU341" t="inlineStr">
+        <is>
+          <t>0jdIgO6t</t>
+        </is>
+      </c>
+      <c r="AV341" t="inlineStr">
+        <is>
+          <t>blessin alexander</t>
+        </is>
+      </c>
+      <c r="AW341" t="n">
+        <v>59</v>
+      </c>
+      <c r="AX341" t="n">
+        <v>591</v>
+      </c>
+      <c r="AY341" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ341" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BA341" t="inlineStr"/>
+      <c r="BB341" t="inlineStr"/>
+      <c r="BC341" t="inlineStr"/>
+      <c r="BD341" t="inlineStr"/>
+      <c r="BE341" t="inlineStr"/>
+      <c r="BF341" t="inlineStr"/>
+      <c r="BG341" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BH341" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BI341" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="BJ341" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="BK341" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="BL341" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="1" t="inlineStr">
+        <is>
+          <t>2q7yHiho</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>02.11.2024 11:30</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>Willenborg F.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>Holstein-Stadion
+ (Kiel)</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>15 034</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>14 000</t>
+        </is>
+      </c>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H342" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I342" t="inlineStr">
+        <is>
+          <t>63WsD2ei</t>
+        </is>
+      </c>
+      <c r="J342" t="inlineStr">
+        <is>
+          <t>Holstein Kiel</t>
+        </is>
+      </c>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>KWixEVWi</t>
+        </is>
+      </c>
+      <c r="L342" t="inlineStr">
+        <is>
+          <t>Heidenheim</t>
+        </is>
+      </c>
+      <c r="M342" t="inlineStr">
+        <is>
+          <t>1.76</t>
+        </is>
+      </c>
+      <c r="N342" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="O342" t="inlineStr">
+        <is>
+          <t>46%</t>
+        </is>
+      </c>
+      <c r="P342" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="Q342" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R342" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="S342" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T342" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U342" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V342" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="W342" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="X342" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="Y342" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Z342" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA342" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB342" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC342" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AD342" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="AE342" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AF342" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AG342" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AH342" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AI342" t="inlineStr"/>
+      <c r="AJ342" t="inlineStr"/>
+      <c r="AK342" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AL342" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AM342" t="inlineStr">
+        <is>
+          <t>329</t>
+        </is>
+      </c>
+      <c r="AN342" t="inlineStr">
+        <is>
+          <t>387</t>
+        </is>
+      </c>
+      <c r="AO342" t="inlineStr">
+        <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="AP342" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="AQ342" t="inlineStr"/>
+      <c r="AR342" t="inlineStr"/>
+      <c r="AS342" t="inlineStr">
+        <is>
+          <t>A15eUM4C</t>
+        </is>
+      </c>
+      <c r="AT342" t="inlineStr">
+        <is>
+          <t>rapp marcel</t>
+        </is>
+      </c>
+      <c r="AU342" t="inlineStr">
+        <is>
+          <t>4ljanukM</t>
+        </is>
+      </c>
+      <c r="AV342" t="inlineStr">
+        <is>
+          <t>schmidt frank</t>
+        </is>
+      </c>
+      <c r="AW342" t="n">
+        <v>59</v>
+      </c>
+      <c r="AX342" t="n">
+        <v>591</v>
+      </c>
+      <c r="AY342" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ342" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BA342" t="inlineStr"/>
+      <c r="BB342" t="inlineStr"/>
+      <c r="BC342" t="inlineStr"/>
+      <c r="BD342" t="inlineStr"/>
+      <c r="BE342" t="inlineStr"/>
+      <c r="BF342" t="inlineStr"/>
+      <c r="BG342" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BH342" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="BI342" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BJ342" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="BK342" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="BL342" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="1" t="inlineStr">
+        <is>
+          <t>AoSdOZaB</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>02.11.2024 11:30</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>Brych F.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>Volkswagen Arena
+ (Wolfsburg)</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>28 917</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>25 000</t>
+        </is>
+      </c>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H343" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I343" t="inlineStr">
+        <is>
+          <t>nwkTahLL</t>
+        </is>
+      </c>
+      <c r="J343" t="inlineStr">
+        <is>
+          <t>Wolfsburg</t>
+        </is>
+      </c>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>fTVNku3I</t>
+        </is>
+      </c>
+      <c r="L343" t="inlineStr">
+        <is>
+          <t>Augsburg</t>
+        </is>
+      </c>
+      <c r="M343" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="N343" t="inlineStr">
+        <is>
+          <t>0.36</t>
+        </is>
+      </c>
+      <c r="O343" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="P343" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="Q343" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="R343" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="S343" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T343" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U343" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V343" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W343" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="X343" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y343" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Z343" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA343" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB343" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC343" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AD343" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AE343" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF343" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AG343" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AH343" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AI343" t="inlineStr"/>
+      <c r="AJ343" t="inlineStr"/>
+      <c r="AK343" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL343" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM343" t="inlineStr">
+        <is>
+          <t>625</t>
+        </is>
+      </c>
+      <c r="AN343" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="AO343" t="inlineStr">
+        <is>
+          <t>533</t>
+        </is>
+      </c>
+      <c r="AP343" t="inlineStr">
+        <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="AQ343" t="inlineStr"/>
+      <c r="AR343" t="inlineStr"/>
+      <c r="AS343" t="inlineStr">
+        <is>
+          <t>f3ddUIXs</t>
+        </is>
+      </c>
+      <c r="AT343" t="inlineStr">
+        <is>
+          <t>hasenhuttl ralph</t>
+        </is>
+      </c>
+      <c r="AU343" t="inlineStr">
+        <is>
+          <t>2VSFgl3c</t>
+        </is>
+      </c>
+      <c r="AV343" t="inlineStr">
+        <is>
+          <t>thorup jess</t>
+        </is>
+      </c>
+      <c r="AW343" t="n">
+        <v>59</v>
+      </c>
+      <c r="AX343" t="n">
+        <v>591</v>
+      </c>
+      <c r="AY343" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ343" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BA343" t="inlineStr"/>
+      <c r="BB343" t="inlineStr"/>
+      <c r="BC343" t="inlineStr"/>
+      <c r="BD343" t="inlineStr"/>
+      <c r="BE343" t="inlineStr"/>
+      <c r="BF343" t="inlineStr"/>
+      <c r="BG343" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="BH343" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BI343" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BJ343" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BK343" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BL343" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="1" t="inlineStr">
+        <is>
+          <t>IHYEDIog</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>01.11.2024 16:30</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>Siebert D.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>BayArena
+ (Leverkusen)</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>30 210</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>30 210</t>
+        </is>
+      </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H344" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I344" t="inlineStr">
+        <is>
+          <t>4jcj2zMd</t>
+        </is>
+      </c>
+      <c r="J344" t="inlineStr">
+        <is>
+          <t>Bayer Leverkusen</t>
+        </is>
+      </c>
+      <c r="K344" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="L344" t="inlineStr">
+        <is>
+          <t>Stuttgart</t>
+        </is>
+      </c>
+      <c r="M344" t="inlineStr">
+        <is>
+          <t>2.19</t>
+        </is>
+      </c>
+      <c r="N344" t="inlineStr">
+        <is>
+          <t>0.28</t>
+        </is>
+      </c>
+      <c r="O344" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="P344" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="Q344" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="R344" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="S344" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T344" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U344" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="V344" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W344" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="X344" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="Y344" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Z344" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA344" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AB344" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC344" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AD344" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AE344" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AF344" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AG344" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AH344" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AI344" t="inlineStr"/>
+      <c r="AJ344" t="inlineStr"/>
+      <c r="AK344" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AL344" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AM344" t="inlineStr">
+        <is>
+          <t>447</t>
+        </is>
+      </c>
+      <c r="AN344" t="inlineStr">
+        <is>
+          <t>434</t>
+        </is>
+      </c>
+      <c r="AO344" t="inlineStr">
+        <is>
+          <t>373</t>
+        </is>
+      </c>
+      <c r="AP344" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="AQ344" t="inlineStr"/>
+      <c r="AR344" t="inlineStr"/>
+      <c r="AS344" t="inlineStr">
+        <is>
+          <t>hAcTWKKN</t>
+        </is>
+      </c>
+      <c r="AT344" t="inlineStr">
+        <is>
+          <t>alonso xabi</t>
+        </is>
+      </c>
+      <c r="AU344" t="inlineStr">
+        <is>
+          <t>GzfvcwRj</t>
+        </is>
+      </c>
+      <c r="AV344" t="inlineStr">
+        <is>
+          <t>hoeness sebastian</t>
+        </is>
+      </c>
+      <c r="AW344" t="n">
+        <v>59</v>
+      </c>
+      <c r="AX344" t="n">
+        <v>591</v>
+      </c>
+      <c r="AY344" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ344" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BA344" t="inlineStr"/>
+      <c r="BB344" t="inlineStr"/>
+      <c r="BC344" t="inlineStr"/>
+      <c r="BD344" t="inlineStr"/>
+      <c r="BE344" t="inlineStr"/>
+      <c r="BF344" t="inlineStr"/>
+      <c r="BG344" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BH344" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BI344" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="BJ344" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BK344" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="BL344" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="1" t="inlineStr">
+        <is>
+          <t>dA6ZHxaL</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>03.11.2024 09:30</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>Bauer T.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>Volksparkstadion
+ (Hamburg)</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>57 274</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>57 000</t>
+        </is>
+      </c>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H345" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I345" t="inlineStr">
+        <is>
+          <t>v9k3aY5F</t>
+        </is>
+      </c>
+      <c r="J345" t="inlineStr">
+        <is>
+          <t>Hamburger SV</t>
+        </is>
+      </c>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>6FDqshzF</t>
+        </is>
+      </c>
+      <c r="L345" t="inlineStr">
+        <is>
+          <t>Nurnberg</t>
+        </is>
+      </c>
+      <c r="M345" t="inlineStr">
+        <is>
+          <t>0.83</t>
+        </is>
+      </c>
+      <c r="N345" t="inlineStr">
+        <is>
+          <t>2.21</t>
+        </is>
+      </c>
+      <c r="O345" t="inlineStr">
+        <is>
+          <t>45%</t>
+        </is>
+      </c>
+      <c r="P345" t="inlineStr">
+        <is>
+          <t>55%</t>
+        </is>
+      </c>
+      <c r="Q345" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R345" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="S345" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T345" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="U345" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V345" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="W345" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="X345" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Y345" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Z345" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AA345" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB345" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC345" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AD345" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AE345" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AF345" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AG345" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AH345" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AI345" t="inlineStr"/>
+      <c r="AJ345" t="inlineStr"/>
+      <c r="AK345" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL345" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM345" t="inlineStr">
+        <is>
+          <t>425</t>
+        </is>
+      </c>
+      <c r="AN345" t="inlineStr">
+        <is>
+          <t>545</t>
+        </is>
+      </c>
+      <c r="AO345" t="inlineStr">
+        <is>
+          <t>374</t>
+        </is>
+      </c>
+      <c r="AP345" t="inlineStr">
+        <is>
+          <t>485</t>
+        </is>
+      </c>
+      <c r="AQ345" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="AR345" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="AS345" t="inlineStr">
+        <is>
+          <t>EDRZkDzS</t>
+        </is>
+      </c>
+      <c r="AT345" t="inlineStr">
+        <is>
+          <t>baumgart steffen</t>
+        </is>
+      </c>
+      <c r="AU345" t="inlineStr">
+        <is>
+          <t>tO31cZrF</t>
+        </is>
+      </c>
+      <c r="AV345" t="inlineStr">
+        <is>
+          <t>klose miroslav</t>
+        </is>
+      </c>
+      <c r="AW345" t="n">
+        <v>59</v>
+      </c>
+      <c r="AX345" t="n">
+        <v>592</v>
+      </c>
+      <c r="AY345" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ345" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BA345" t="inlineStr"/>
+      <c r="BB345" t="inlineStr"/>
+      <c r="BC345" t="inlineStr"/>
+      <c r="BD345" t="inlineStr"/>
+      <c r="BE345" t="inlineStr"/>
+      <c r="BF345" t="inlineStr"/>
+      <c r="BG345" t="inlineStr"/>
+      <c r="BH345" t="inlineStr"/>
+      <c r="BI345" t="inlineStr"/>
+      <c r="BJ345" t="inlineStr"/>
+      <c r="BK345" t="inlineStr"/>
+      <c r="BL345" t="inlineStr"/>
+    </row>
+    <row r="346">
+      <c r="A346" s="1" t="inlineStr">
+        <is>
+          <t>naLHUFrR</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>03.11.2024 09:30</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>Badstubner F.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>Fritz Walter Stadion
+ (Kaiserslautern)</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>49 500</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>45 104</t>
+        </is>
+      </c>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H346" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I346" t="inlineStr">
+        <is>
+          <t>naWckLmC</t>
+        </is>
+      </c>
+      <c r="J346" t="inlineStr">
+        <is>
+          <t>Kaiserslautern</t>
+        </is>
+      </c>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>YFuz2RLm</t>
+        </is>
+      </c>
+      <c r="L346" t="inlineStr">
+        <is>
+          <t>Magdeburg</t>
+        </is>
+      </c>
+      <c r="M346" t="inlineStr">
+        <is>
+          <t>3.65</t>
+        </is>
+      </c>
+      <c r="N346" t="inlineStr">
+        <is>
+          <t>0.96</t>
+        </is>
+      </c>
+      <c r="O346" t="inlineStr">
+        <is>
+          <t>61%</t>
+        </is>
+      </c>
+      <c r="P346" t="inlineStr">
+        <is>
+          <t>39%</t>
+        </is>
+      </c>
+      <c r="Q346" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="R346" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="S346" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T346" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U346" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="V346" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W346" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="X346" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Y346" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="Z346" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA346" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB346" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC346" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="AD346" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AE346" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AF346" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AG346" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AH346" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AI346" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AJ346" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AK346" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL346" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AM346" t="inlineStr">
+        <is>
+          <t>584</t>
+        </is>
+      </c>
+      <c r="AN346" t="inlineStr">
+        <is>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="AO346" t="inlineStr">
+        <is>
+          <t>508</t>
+        </is>
+      </c>
+      <c r="AP346" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="AQ346" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="AR346" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="AS346" t="inlineStr">
+        <is>
+          <t>4bJLk19p</t>
+        </is>
+      </c>
+      <c r="AT346" t="inlineStr">
+        <is>
+          <t>anfang marcus</t>
+        </is>
+      </c>
+      <c r="AU346" t="inlineStr">
+        <is>
+          <t>IgZoGKFn</t>
+        </is>
+      </c>
+      <c r="AV346" t="inlineStr">
+        <is>
+          <t>titz christian</t>
+        </is>
+      </c>
+      <c r="AW346" t="n">
+        <v>59</v>
+      </c>
+      <c r="AX346" t="n">
+        <v>592</v>
+      </c>
+      <c r="AY346" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ346" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BA346" t="inlineStr"/>
+      <c r="BB346" t="inlineStr"/>
+      <c r="BC346" t="inlineStr"/>
+      <c r="BD346" t="inlineStr"/>
+      <c r="BE346" t="inlineStr"/>
+      <c r="BF346" t="inlineStr"/>
+      <c r="BG346" t="inlineStr"/>
+      <c r="BH346" t="inlineStr"/>
+      <c r="BI346" t="inlineStr"/>
+      <c r="BJ346" t="inlineStr"/>
+      <c r="BK346" t="inlineStr"/>
+      <c r="BL346" t="inlineStr"/>
+    </row>
+    <row r="347">
+      <c r="A347" s="1" t="inlineStr">
+        <is>
+          <t>OKjEAfie</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>03.11.2024 09:30</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>Haslberger W.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>Home Deluxe Arena
+ (Paderborn)</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>13 949</t>
+        </is>
+      </c>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H347" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I347" t="inlineStr">
+        <is>
+          <t>G2Op923t</t>
+        </is>
+      </c>
+      <c r="J347" t="inlineStr">
+        <is>
+          <t>Paderborn</t>
+        </is>
+      </c>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>QqLCC3il</t>
+        </is>
+      </c>
+      <c r="L347" t="inlineStr">
+        <is>
+          <t>Braunschweig</t>
+        </is>
+      </c>
+      <c r="M347" t="inlineStr">
+        <is>
+          <t>0.59</t>
+        </is>
+      </c>
+      <c r="N347" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="O347" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="P347" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="Q347" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R347" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="S347" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T347" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U347" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V347" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="W347" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="X347" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y347" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Z347" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA347" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB347" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC347" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AD347" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="AE347" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AF347" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AG347" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AH347" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AI347" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AJ347" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK347" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AL347" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM347" t="inlineStr">
+        <is>
+          <t>444</t>
+        </is>
+      </c>
+      <c r="AN347" t="inlineStr">
+        <is>
+          <t>392</t>
+        </is>
+      </c>
+      <c r="AO347" t="inlineStr">
+        <is>
+          <t>355</t>
+        </is>
+      </c>
+      <c r="AP347" t="inlineStr">
+        <is>
+          <t>310</t>
+        </is>
+      </c>
+      <c r="AQ347" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="AR347" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="AS347" t="inlineStr">
+        <is>
+          <t>0AI1QUJH</t>
+        </is>
+      </c>
+      <c r="AT347" t="inlineStr">
+        <is>
+          <t>kwasniok lukas</t>
+        </is>
+      </c>
+      <c r="AU347" t="inlineStr">
+        <is>
+          <t>SQrxFAMl</t>
+        </is>
+      </c>
+      <c r="AV347" t="inlineStr">
+        <is>
+          <t>scherning daniel</t>
+        </is>
+      </c>
+      <c r="AW347" t="n">
+        <v>59</v>
+      </c>
+      <c r="AX347" t="n">
+        <v>592</v>
+      </c>
+      <c r="AY347" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ347" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BA347" t="inlineStr"/>
+      <c r="BB347" t="inlineStr"/>
+      <c r="BC347" t="inlineStr"/>
+      <c r="BD347" t="inlineStr"/>
+      <c r="BE347" t="inlineStr"/>
+      <c r="BF347" t="inlineStr"/>
+      <c r="BG347" t="inlineStr"/>
+      <c r="BH347" t="inlineStr"/>
+      <c r="BI347" t="inlineStr"/>
+      <c r="BJ347" t="inlineStr"/>
+      <c r="BK347" t="inlineStr"/>
+      <c r="BL347" t="inlineStr"/>
+    </row>
+    <row r="348">
+      <c r="A348" s="1" t="inlineStr">
+        <is>
+          <t>jXR8WyEE</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>02.11.2024 16:30</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>Osmers H.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>Olympiastadion
+ (Berlin)</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>74 667</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>68 763</t>
+        </is>
+      </c>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H348" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I348" t="inlineStr">
+        <is>
+          <t>2y0u8Wrq</t>
+        </is>
+      </c>
+      <c r="J348" t="inlineStr">
+        <is>
+          <t>Hertha Berlin</t>
+        </is>
+      </c>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>WG9pOTse</t>
+        </is>
+      </c>
+      <c r="L348" t="inlineStr">
+        <is>
+          <t>FC Koln</t>
+        </is>
+      </c>
+      <c r="M348" t="inlineStr">
+        <is>
+          <t>0.66</t>
+        </is>
+      </c>
+      <c r="N348" t="inlineStr">
+        <is>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="O348" t="inlineStr">
+        <is>
+          <t>49%</t>
+        </is>
+      </c>
+      <c r="P348" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="Q348" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R348" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="S348" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T348" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U348" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V348" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="W348" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="X348" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="Y348" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Z348" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA348" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB348" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC348" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AD348" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AE348" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AF348" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AG348" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AH348" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AI348" t="inlineStr"/>
+      <c r="AJ348" t="inlineStr"/>
+      <c r="AK348" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AL348" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM348" t="inlineStr">
+        <is>
+          <t>430</t>
+        </is>
+      </c>
+      <c r="AN348" t="inlineStr">
+        <is>
+          <t>487</t>
+        </is>
+      </c>
+      <c r="AO348" t="inlineStr">
+        <is>
+          <t>348</t>
+        </is>
+      </c>
+      <c r="AP348" t="inlineStr">
+        <is>
+          <t>404</t>
+        </is>
+      </c>
+      <c r="AQ348" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="AR348" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="AS348" t="inlineStr">
+        <is>
+          <t>YmfcAeCo</t>
+        </is>
+      </c>
+      <c r="AT348" t="inlineStr">
+        <is>
+          <t>fiel cristian</t>
+        </is>
+      </c>
+      <c r="AU348" t="inlineStr">
+        <is>
+          <t>4fX0k7gg</t>
+        </is>
+      </c>
+      <c r="AV348" t="inlineStr">
+        <is>
+          <t>struber gerhard</t>
+        </is>
+      </c>
+      <c r="AW348" t="n">
+        <v>59</v>
+      </c>
+      <c r="AX348" t="n">
+        <v>592</v>
+      </c>
+      <c r="AY348" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ348" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BA348" t="inlineStr"/>
+      <c r="BB348" t="inlineStr"/>
+      <c r="BC348" t="inlineStr"/>
+      <c r="BD348" t="inlineStr"/>
+      <c r="BE348" t="inlineStr"/>
+      <c r="BF348" t="inlineStr"/>
+      <c r="BG348" t="inlineStr"/>
+      <c r="BH348" t="inlineStr"/>
+      <c r="BI348" t="inlineStr"/>
+      <c r="BJ348" t="inlineStr"/>
+      <c r="BK348" t="inlineStr"/>
+      <c r="BL348" t="inlineStr"/>
+    </row>
+    <row r="349">
+      <c r="A349" s="1" t="inlineStr">
+        <is>
+          <t>pzuN8YL7</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>02.11.2024 09:00</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>Burda M.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>Sportpark Ronhof Thomas Sommer
+ (Fürth)</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>16 626</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>11 161</t>
+        </is>
+      </c>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H349" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I349" t="inlineStr">
+        <is>
+          <t>CCQGbik8</t>
+        </is>
+      </c>
+      <c r="J349" t="inlineStr">
+        <is>
+          <t>Greuther Furth</t>
+        </is>
+      </c>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>S0hPB9rA</t>
+        </is>
+      </c>
+      <c r="L349" t="inlineStr">
+        <is>
+          <t>Darmstadt</t>
+        </is>
+      </c>
+      <c r="M349" t="inlineStr">
+        <is>
+          <t>1.07</t>
+        </is>
+      </c>
+      <c r="N349" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="O349" t="inlineStr">
+        <is>
+          <t>46%</t>
+        </is>
+      </c>
+      <c r="P349" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="Q349" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="R349" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="S349" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T349" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="U349" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="V349" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="W349" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="X349" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y349" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z349" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA349" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB349" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC349" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AD349" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AE349" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AF349" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AG349" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AH349" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AI349" t="inlineStr"/>
+      <c r="AJ349" t="inlineStr"/>
+      <c r="AK349" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL349" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AM349" t="inlineStr">
+        <is>
+          <t>488</t>
+        </is>
+      </c>
+      <c r="AN349" t="inlineStr">
+        <is>
+          <t>734</t>
+        </is>
+      </c>
+      <c r="AO349" t="inlineStr">
+        <is>
+          <t>427</t>
+        </is>
+      </c>
+      <c r="AP349" t="inlineStr">
+        <is>
+          <t>655</t>
+        </is>
+      </c>
+      <c r="AQ349" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="AR349" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="AS349" t="inlineStr">
+        <is>
+          <t>S6Oa4cwI</t>
+        </is>
+      </c>
+      <c r="AT349" t="inlineStr">
+        <is>
+          <t>haas leonhard</t>
+        </is>
+      </c>
+      <c r="AU349" t="inlineStr">
+        <is>
+          <t>4dKVOnA1</t>
+        </is>
+      </c>
+      <c r="AV349" t="inlineStr">
+        <is>
+          <t>kohfeldt florian</t>
+        </is>
+      </c>
+      <c r="AW349" t="n">
+        <v>59</v>
+      </c>
+      <c r="AX349" t="n">
+        <v>592</v>
+      </c>
+      <c r="AY349" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ349" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BA349" t="inlineStr"/>
+      <c r="BB349" t="inlineStr"/>
+      <c r="BC349" t="inlineStr"/>
+      <c r="BD349" t="inlineStr"/>
+      <c r="BE349" t="inlineStr"/>
+      <c r="BF349" t="inlineStr"/>
+      <c r="BG349" t="inlineStr"/>
+      <c r="BH349" t="inlineStr"/>
+      <c r="BI349" t="inlineStr"/>
+      <c r="BJ349" t="inlineStr"/>
+      <c r="BK349" t="inlineStr"/>
+      <c r="BL349" t="inlineStr"/>
+    </row>
+    <row r="350">
+      <c r="A350" s="1" t="inlineStr">
+        <is>
+          <t>Gfm6CGMr</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>02.11.2024 09:00</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>Hempel R.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>Heinz-von-Heiden-Arena
+ (Hannover)</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>49 200</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>38 000</t>
+        </is>
+      </c>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H350" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I350" t="inlineStr">
+        <is>
+          <t>dfNCCCzS</t>
+        </is>
+      </c>
+      <c r="J350" t="inlineStr">
+        <is>
+          <t>Hannover</t>
+        </is>
+      </c>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>EB3q7jbk</t>
+        </is>
+      </c>
+      <c r="L350" t="inlineStr">
+        <is>
+          <t>Karlsruher SC</t>
+        </is>
+      </c>
+      <c r="M350" t="inlineStr">
+        <is>
+          <t>2.26</t>
+        </is>
+      </c>
+      <c r="N350" t="inlineStr">
+        <is>
+          <t>0.79</t>
+        </is>
+      </c>
+      <c r="O350" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="P350" t="inlineStr">
+        <is>
+          <t>46%</t>
+        </is>
+      </c>
+      <c r="Q350" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R350" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="S350" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="T350" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U350" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V350" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="W350" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="X350" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="Y350" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Z350" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA350" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB350" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC350" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AD350" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AE350" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AF350" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AG350" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AH350" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AI350" t="inlineStr"/>
+      <c r="AJ350" t="inlineStr"/>
+      <c r="AK350" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AL350" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM350" t="inlineStr">
+        <is>
+          <t>396</t>
+        </is>
+      </c>
+      <c r="AN350" t="inlineStr">
+        <is>
+          <t>325</t>
+        </is>
+      </c>
+      <c r="AO350" t="inlineStr">
+        <is>
+          <t>337</t>
+        </is>
+      </c>
+      <c r="AP350" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="AQ350" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="AR350" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="AS350" t="inlineStr">
+        <is>
+          <t>t0ZPdkUl</t>
+        </is>
+      </c>
+      <c r="AT350" t="inlineStr">
+        <is>
+          <t>leitl stefan</t>
+        </is>
+      </c>
+      <c r="AU350" t="inlineStr">
+        <is>
+          <t>OzPMRhK3</t>
+        </is>
+      </c>
+      <c r="AV350" t="inlineStr">
+        <is>
+          <t>eichner christian</t>
+        </is>
+      </c>
+      <c r="AW350" t="n">
+        <v>59</v>
+      </c>
+      <c r="AX350" t="n">
+        <v>592</v>
+      </c>
+      <c r="AY350" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ350" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BA350" t="inlineStr"/>
+      <c r="BB350" t="inlineStr"/>
+      <c r="BC350" t="inlineStr"/>
+      <c r="BD350" t="inlineStr"/>
+      <c r="BE350" t="inlineStr"/>
+      <c r="BF350" t="inlineStr"/>
+      <c r="BG350" t="inlineStr"/>
+      <c r="BH350" t="inlineStr"/>
+      <c r="BI350" t="inlineStr"/>
+      <c r="BJ350" t="inlineStr"/>
+      <c r="BK350" t="inlineStr"/>
+      <c r="BL350" t="inlineStr"/>
+    </row>
+    <row r="351">
+      <c r="A351" s="1" t="inlineStr">
+        <is>
+          <t>W4I3LB5D</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>02.11.2024 09:00</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>Weisbach E.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>Jahnstadion Regensburg
+ (Regensburg)</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>15 210</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>9 000</t>
+        </is>
+      </c>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I351" t="inlineStr">
+        <is>
+          <t>UiCmEP56</t>
+        </is>
+      </c>
+      <c r="J351" t="inlineStr">
+        <is>
+          <t>Regensburg</t>
+        </is>
+      </c>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>6in2Eknb</t>
+        </is>
+      </c>
+      <c r="L351" t="inlineStr">
+        <is>
+          <t>Elversberg</t>
+        </is>
+      </c>
+      <c r="M351" t="inlineStr">
+        <is>
+          <t>1.04</t>
+        </is>
+      </c>
+      <c r="N351" t="inlineStr">
+        <is>
+          <t>1.07</t>
+        </is>
+      </c>
+      <c r="O351" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="P351" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="Q351" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R351" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="S351" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T351" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U351" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V351" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="W351" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="X351" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y351" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Z351" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AA351" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB351" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC351" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AD351" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="AE351" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AF351" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AG351" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AH351" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AI351" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AJ351" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK351" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL351" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM351" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="AN351" t="inlineStr">
+        <is>
+          <t>715</t>
+        </is>
+      </c>
+      <c r="AO351" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="AP351" t="inlineStr">
+        <is>
+          <t>637</t>
+        </is>
+      </c>
+      <c r="AQ351" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="AR351" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="AS351" t="inlineStr">
+        <is>
+          <t>zP70fYtq</t>
+        </is>
+      </c>
+      <c r="AT351" t="inlineStr">
+        <is>
+          <t>patz andreas</t>
+        </is>
+      </c>
+      <c r="AU351" t="inlineStr">
+        <is>
+          <t>8E8qmw3d</t>
+        </is>
+      </c>
+      <c r="AV351" t="inlineStr">
+        <is>
+          <t>steffen horst</t>
+        </is>
+      </c>
+      <c r="AW351" t="n">
+        <v>59</v>
+      </c>
+      <c r="AX351" t="n">
+        <v>592</v>
+      </c>
+      <c r="AY351" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ351" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BA351" t="inlineStr"/>
+      <c r="BB351" t="inlineStr"/>
+      <c r="BC351" t="inlineStr"/>
+      <c r="BD351" t="inlineStr"/>
+      <c r="BE351" t="inlineStr"/>
+      <c r="BF351" t="inlineStr"/>
+      <c r="BG351" t="inlineStr"/>
+      <c r="BH351" t="inlineStr"/>
+      <c r="BI351" t="inlineStr"/>
+      <c r="BJ351" t="inlineStr"/>
+      <c r="BK351" t="inlineStr"/>
+      <c r="BL351" t="inlineStr"/>
+    </row>
+    <row r="352">
+      <c r="A352" s="1" t="inlineStr">
+        <is>
+          <t>vc0dNXz1</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>01.11.2024 14:30</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>Bacher M.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>Preussenstadion
+ (Munster)</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>12 794</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>12 422</t>
+        </is>
+      </c>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I352" t="inlineStr">
+        <is>
+          <t>zedZaSL7</t>
+        </is>
+      </c>
+      <c r="J352" t="inlineStr">
+        <is>
+          <t>Preussen Munster</t>
+        </is>
+      </c>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>ne1oL3y7</t>
+        </is>
+      </c>
+      <c r="L352" t="inlineStr">
+        <is>
+          <t>Dusseldorf</t>
+        </is>
+      </c>
+      <c r="M352" t="inlineStr">
+        <is>
+          <t>1.19</t>
+        </is>
+      </c>
+      <c r="N352" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="O352" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="P352" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="Q352" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="R352" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="S352" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T352" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U352" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V352" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="W352" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="X352" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="Y352" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Z352" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AA352" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB352" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC352" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AD352" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="AE352" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AF352" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AG352" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AH352" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AI352" t="inlineStr"/>
+      <c r="AJ352" t="inlineStr"/>
+      <c r="AK352" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AL352" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM352" t="inlineStr">
+        <is>
+          <t>340</t>
+        </is>
+      </c>
+      <c r="AN352" t="inlineStr">
+        <is>
+          <t>628</t>
+        </is>
+      </c>
+      <c r="AO352" t="inlineStr">
+        <is>
+          <t>292</t>
+        </is>
+      </c>
+      <c r="AP352" t="inlineStr">
+        <is>
+          <t>565</t>
+        </is>
+      </c>
+      <c r="AQ352" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="AR352" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="AS352" t="inlineStr">
+        <is>
+          <t>pdPRS0me</t>
+        </is>
+      </c>
+      <c r="AT352" t="inlineStr">
+        <is>
+          <t>hildmann sascha</t>
+        </is>
+      </c>
+      <c r="AU352" t="inlineStr">
+        <is>
+          <t>AoL97rX8</t>
+        </is>
+      </c>
+      <c r="AV352" t="inlineStr">
+        <is>
+          <t>thioune daniel</t>
+        </is>
+      </c>
+      <c r="AW352" t="n">
+        <v>59</v>
+      </c>
+      <c r="AX352" t="n">
+        <v>592</v>
+      </c>
+      <c r="AY352" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ352" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BA352" t="inlineStr"/>
+      <c r="BB352" t="inlineStr"/>
+      <c r="BC352" t="inlineStr"/>
+      <c r="BD352" t="inlineStr"/>
+      <c r="BE352" t="inlineStr"/>
+      <c r="BF352" t="inlineStr"/>
+      <c r="BG352" t="inlineStr"/>
+      <c r="BH352" t="inlineStr"/>
+      <c r="BI352" t="inlineStr"/>
+      <c r="BJ352" t="inlineStr"/>
+      <c r="BK352" t="inlineStr"/>
+      <c r="BL352" t="inlineStr"/>
+    </row>
+    <row r="353">
+      <c r="A353" s="1" t="inlineStr">
+        <is>
+          <t>rV6mPg6l</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>01.11.2024 14:30</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>Prigan F.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>Donaustadion
+ (Ulm)</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>19 500</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>17 000</t>
+        </is>
+      </c>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I353" t="inlineStr">
+        <is>
+          <t>tbC3EcQn</t>
+        </is>
+      </c>
+      <c r="J353" t="inlineStr">
+        <is>
+          <t>Ulm</t>
+        </is>
+      </c>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>0Ija0Ej9</t>
+        </is>
+      </c>
+      <c r="L353" t="inlineStr">
+        <is>
+          <t>Schalke</t>
+        </is>
+      </c>
+      <c r="M353" t="inlineStr">
+        <is>
+          <t>0.71</t>
+        </is>
+      </c>
+      <c r="N353" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="O353" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
+      </c>
+      <c r="P353" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="Q353" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="R353" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S353" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T353" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U353" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="V353" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="W353" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="X353" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y353" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Z353" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA353" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB353" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC353" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AD353" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AE353" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AF353" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AG353" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AH353" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AI353" t="inlineStr"/>
+      <c r="AJ353" t="inlineStr"/>
+      <c r="AK353" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL353" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM353" t="inlineStr">
+        <is>
+          <t>472</t>
+        </is>
+      </c>
+      <c r="AN353" t="inlineStr">
+        <is>
+          <t>395</t>
+        </is>
+      </c>
+      <c r="AO353" t="inlineStr">
+        <is>
+          <t>411</t>
+        </is>
+      </c>
+      <c r="AP353" t="inlineStr">
+        <is>
+          <t>328</t>
+        </is>
+      </c>
+      <c r="AQ353" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="AR353" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="AS353" t="inlineStr">
+        <is>
+          <t>QevvB2nf</t>
+        </is>
+      </c>
+      <c r="AT353" t="inlineStr">
+        <is>
+          <t>worle thomas</t>
+        </is>
+      </c>
+      <c r="AU353" t="inlineStr">
+        <is>
+          <t>SMaB5LKo</t>
+        </is>
+      </c>
+      <c r="AV353" t="inlineStr">
+        <is>
+          <t>van wonderen kees</t>
+        </is>
+      </c>
+      <c r="AW353" t="n">
+        <v>59</v>
+      </c>
+      <c r="AX353" t="n">
+        <v>592</v>
+      </c>
+      <c r="AY353" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ353" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="BA353" t="inlineStr"/>
+      <c r="BB353" t="inlineStr"/>
+      <c r="BC353" t="inlineStr"/>
+      <c r="BD353" t="inlineStr"/>
+      <c r="BE353" t="inlineStr"/>
+      <c r="BF353" t="inlineStr"/>
+      <c r="BG353" t="inlineStr"/>
+      <c r="BH353" t="inlineStr"/>
+      <c r="BI353" t="inlineStr"/>
+      <c r="BJ353" t="inlineStr"/>
+      <c r="BK353" t="inlineStr"/>
+      <c r="BL353" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
